--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1843" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B403573-8B0C-475D-841F-A142B82FEBB3}"/>
+  <xr:revisionPtr revIDLastSave="1847" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4435021-B7F8-474A-9BF9-BB4AF9FD39CF}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1982,10 +1982,6 @@
 </FeaturePropertyBags>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -14530,7 +14526,7 @@
         <v>46196</v>
       </c>
       <c r="L91" s="20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" s="102" t="s">
         <v>333</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1847" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4435021-B7F8-474A-9BF9-BB4AF9FD39CF}"/>
+  <xr:revisionPtr revIDLastSave="1848" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3777CD5-27F2-44C3-B7E1-1FC4C2C0108B}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Water meters " sheetId="1" r:id="rId1"/>
@@ -9971,7 +9971,7 @@
         <v>46171</v>
       </c>
       <c r="I192" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J192" s="101" t="s">
         <v>332</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1848" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3777CD5-27F2-44C3-B7E1-1FC4C2C0108B}"/>
+  <xr:revisionPtr revIDLastSave="1854" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4E23647-6F74-49CD-AA94-8763423563C4}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3032" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3034" uniqueCount="371">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -1152,6 +1152,12 @@
   </si>
   <si>
     <t>MS2</t>
+  </si>
+  <si>
+    <t>10192050</t>
+  </si>
+  <si>
+    <t>10216099</t>
   </si>
 </sst>
 </file>
@@ -4072,7 +4078,9 @@
       <c r="B48" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="C48" s="83"/>
+      <c r="C48" s="83" t="s">
+        <v>370</v>
+      </c>
       <c r="D48" s="83" t="s">
         <v>11</v>
       </c>
@@ -4082,8 +4090,12 @@
       <c r="F48" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
+      <c r="G48" s="6">
+        <v>0.154</v>
+      </c>
+      <c r="H48" s="88">
+        <v>46204</v>
+      </c>
       <c r="I48" s="32" t="b">
         <v>0</v>
       </c>
@@ -4148,7 +4160,9 @@
       <c r="B50" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="C50" s="83"/>
+      <c r="C50" s="83" t="s">
+        <v>369</v>
+      </c>
       <c r="D50" s="83" t="s">
         <v>11</v>
       </c>
@@ -4158,8 +4172,12 @@
       <c r="F50" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
+      <c r="G50" s="6">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="H50" s="88">
+        <v>46204</v>
+      </c>
       <c r="I50" s="32" t="b">
         <v>0</v>
       </c>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1854" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4E23647-6F74-49CD-AA94-8763423563C4}"/>
+  <xr:revisionPtr revIDLastSave="1868" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E1B29A8-BC26-43B7-A66B-F0BC8E2358CE}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4097,7 +4097,7 @@
         <v>46204</v>
       </c>
       <c r="I48" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="101" t="s">
         <v>344</v>
@@ -4179,7 +4179,7 @@
         <v>46204</v>
       </c>
       <c r="I50" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="101" t="s">
         <v>344</v>
@@ -4261,7 +4261,7 @@
         <v>46204</v>
       </c>
       <c r="I52" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="101" t="s">
         <v>344</v>
@@ -4343,7 +4343,7 @@
         <v>46204</v>
       </c>
       <c r="I54" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="101" t="s">
         <v>344</v>
@@ -4425,7 +4425,7 @@
         <v>46204</v>
       </c>
       <c r="I56" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="101" t="s">
         <v>344</v>
@@ -4507,7 +4507,7 @@
         <v>46204</v>
       </c>
       <c r="I58" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="101" t="s">
         <v>344</v>
@@ -4589,7 +4589,7 @@
         <v>46204</v>
       </c>
       <c r="I60" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="101" t="s">
         <v>344</v>
@@ -4891,7 +4891,7 @@
         <v>46204</v>
       </c>
       <c r="I67" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" s="101" t="s">
         <v>346</v>
@@ -4979,7 +4979,7 @@
         <v>46204</v>
       </c>
       <c r="I69" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" s="101" t="s">
         <v>346</v>
@@ -5815,7 +5815,7 @@
         <v>46204</v>
       </c>
       <c r="I88" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" s="101" t="s">
         <v>333</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1868" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E1B29A8-BC26-43B7-A66B-F0BC8E2358CE}"/>
+  <xr:revisionPtr revIDLastSave="1875" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2A4FA20-61AD-4BA3-AAC3-F04073678DBF}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3034" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3035" uniqueCount="373">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -1158,6 +1158,12 @@
   </si>
   <si>
     <t>10216099</t>
+  </si>
+  <si>
+    <t>20mm</t>
+  </si>
+  <si>
+    <t>9993270</t>
   </si>
 </sst>
 </file>
@@ -2338,7 +2344,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -2376,7 +2382,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -2414,7 +2420,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
@@ -2452,7 +2458,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -2490,7 +2496,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
@@ -2528,7 +2534,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
@@ -2566,7 +2572,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -2604,7 +2610,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
@@ -2642,7 +2648,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
@@ -2680,7 +2686,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
@@ -2718,7 +2724,7 @@
         <v>12</v>
       </c>
       <c r="F12" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -2756,7 +2762,7 @@
         <v>12</v>
       </c>
       <c r="F13" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -2794,7 +2800,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -2832,7 +2838,7 @@
         <v>12</v>
       </c>
       <c r="F15" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -2870,7 +2876,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -2908,7 +2914,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -2946,7 +2952,7 @@
         <v>12</v>
       </c>
       <c r="F18" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -2984,7 +2990,7 @@
         <v>12</v>
       </c>
       <c r="F19" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -3022,7 +3028,7 @@
         <v>12</v>
       </c>
       <c r="F20" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -3060,7 +3066,7 @@
         <v>12</v>
       </c>
       <c r="F21" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -3098,7 +3104,7 @@
         <v>12</v>
       </c>
       <c r="F22" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -3136,7 +3142,7 @@
         <v>12</v>
       </c>
       <c r="F23" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -3174,7 +3180,7 @@
         <v>12</v>
       </c>
       <c r="F24" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -3212,7 +3218,7 @@
         <v>12</v>
       </c>
       <c r="F25" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -3250,7 +3256,7 @@
         <v>12</v>
       </c>
       <c r="F26" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
@@ -3288,7 +3294,7 @@
         <v>12</v>
       </c>
       <c r="F27" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
@@ -3326,7 +3332,7 @@
         <v>12</v>
       </c>
       <c r="F28" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
@@ -3364,7 +3370,7 @@
         <v>12</v>
       </c>
       <c r="F29" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
@@ -3402,7 +3408,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
@@ -3440,7 +3446,7 @@
         <v>12</v>
       </c>
       <c r="F31" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
@@ -3478,7 +3484,7 @@
         <v>12</v>
       </c>
       <c r="F32" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
@@ -3516,7 +3522,7 @@
         <v>12</v>
       </c>
       <c r="F33" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
@@ -3554,7 +3560,7 @@
         <v>12</v>
       </c>
       <c r="F34" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
@@ -3592,7 +3598,7 @@
         <v>12</v>
       </c>
       <c r="F35" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
@@ -3630,7 +3636,7 @@
         <v>12</v>
       </c>
       <c r="F36" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
@@ -3668,7 +3674,7 @@
         <v>12</v>
       </c>
       <c r="F37" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
@@ -3706,7 +3712,7 @@
         <v>12</v>
       </c>
       <c r="F38" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
@@ -3744,7 +3750,7 @@
         <v>12</v>
       </c>
       <c r="F39" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
@@ -3782,7 +3788,7 @@
         <v>12</v>
       </c>
       <c r="F40" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
@@ -3820,7 +3826,7 @@
         <v>12</v>
       </c>
       <c r="F41" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
@@ -3858,7 +3864,7 @@
         <v>12</v>
       </c>
       <c r="F42" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
@@ -3896,7 +3902,7 @@
         <v>12</v>
       </c>
       <c r="F43" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
@@ -3934,7 +3940,7 @@
         <v>12</v>
       </c>
       <c r="F44" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
@@ -3972,7 +3978,7 @@
         <v>12</v>
       </c>
       <c r="F45" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
@@ -4010,7 +4016,7 @@
         <v>12</v>
       </c>
       <c r="F46" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
@@ -4048,7 +4054,7 @@
         <v>12</v>
       </c>
       <c r="F47" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
@@ -4088,7 +4094,7 @@
         <v>12</v>
       </c>
       <c r="F48" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G48" s="6">
         <v>0.154</v>
@@ -4130,7 +4136,7 @@
         <v>12</v>
       </c>
       <c r="F49" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
@@ -4170,7 +4176,7 @@
         <v>12</v>
       </c>
       <c r="F50" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G50" s="6">
         <v>6.8000000000000005E-2</v>
@@ -4212,7 +4218,7 @@
         <v>12</v>
       </c>
       <c r="F51" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
@@ -4252,7 +4258,7 @@
         <v>12</v>
       </c>
       <c r="F52" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G52" s="6">
         <v>8.8999999999999996E-2</v>
@@ -4294,7 +4300,7 @@
         <v>12</v>
       </c>
       <c r="F53" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
@@ -4334,7 +4340,7 @@
         <v>12</v>
       </c>
       <c r="F54" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G54" s="6">
         <v>6.7000000000000004E-2</v>
@@ -4376,7 +4382,7 @@
         <v>12</v>
       </c>
       <c r="F55" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
@@ -4416,7 +4422,7 @@
         <v>12</v>
       </c>
       <c r="F56" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G56" s="6">
         <v>9.0999999999999998E-2</v>
@@ -4458,7 +4464,7 @@
         <v>12</v>
       </c>
       <c r="F57" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -4498,7 +4504,7 @@
         <v>12</v>
       </c>
       <c r="F58" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G58" s="6">
         <v>7.5999999999999998E-2</v>
@@ -4540,7 +4546,7 @@
         <v>12</v>
       </c>
       <c r="F59" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
@@ -4580,7 +4586,7 @@
         <v>12</v>
       </c>
       <c r="F60" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G60" s="6">
         <v>8.2000000000000003E-2</v>
@@ -4614,7 +4620,9 @@
       <c r="B61" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C61" s="83"/>
+      <c r="C61" s="83" t="s">
+        <v>372</v>
+      </c>
       <c r="D61" s="83" t="s">
         <v>11</v>
       </c>
@@ -4622,12 +4630,16 @@
         <v>12</v>
       </c>
       <c r="F61" s="83" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
+        <v>371</v>
+      </c>
+      <c r="G61" s="6">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="H61" s="88">
+        <v>46205</v>
+      </c>
       <c r="I61" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" s="101" t="s">
         <v>347</v>
@@ -4662,7 +4674,7 @@
         <v>12</v>
       </c>
       <c r="F62" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G62" s="6">
         <v>6.7000000000000004E-2</v>
@@ -4706,7 +4718,7 @@
         <v>12</v>
       </c>
       <c r="F63" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G63" s="6">
         <v>7.3999999999999996E-2</v>
@@ -4750,7 +4762,7 @@
         <v>12</v>
       </c>
       <c r="F64" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G64" s="6">
         <v>6.6000000000000003E-2</v>
@@ -4794,7 +4806,7 @@
         <v>12</v>
       </c>
       <c r="F65" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G65" s="6">
         <v>8.1000000000000003E-2</v>
@@ -4838,7 +4850,7 @@
         <v>12</v>
       </c>
       <c r="F66" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G66" s="6">
         <v>6.7000000000000004E-2</v>
@@ -4882,7 +4894,7 @@
         <v>12</v>
       </c>
       <c r="F67" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G67" s="6">
         <v>8.2000000000000003E-2</v>
@@ -4926,7 +4938,7 @@
         <v>12</v>
       </c>
       <c r="F68" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G68" s="6">
         <v>6.5000000000000002E-2</v>
@@ -4970,7 +4982,7 @@
         <v>12</v>
       </c>
       <c r="F69" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G69" s="6">
         <v>6.9000000000000006E-2</v>
@@ -5014,7 +5026,7 @@
         <v>12</v>
       </c>
       <c r="F70" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G70" s="6">
         <v>6.6000000000000003E-2</v>
@@ -5058,7 +5070,7 @@
         <v>12</v>
       </c>
       <c r="F71" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G71" s="6">
         <v>7.1999999999999995E-2</v>
@@ -5102,7 +5114,7 @@
         <v>12</v>
       </c>
       <c r="F72" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G72" s="6">
         <v>8.3000000000000004E-2</v>
@@ -5146,7 +5158,7 @@
         <v>12</v>
       </c>
       <c r="F73" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G73" s="6">
         <v>4.2000000000000003E-2</v>
@@ -5190,7 +5202,7 @@
         <v>12</v>
       </c>
       <c r="F74" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G74" s="6">
         <v>7.0000000000000007E-2</v>
@@ -5234,7 +5246,7 @@
         <v>12</v>
       </c>
       <c r="F75" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G75" s="6">
         <v>7.0000000000000007E-2</v>
@@ -5278,7 +5290,7 @@
         <v>12</v>
       </c>
       <c r="F76" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G76" s="6">
         <v>7.1999999999999995E-2</v>
@@ -5322,7 +5334,7 @@
         <v>12</v>
       </c>
       <c r="F77" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G77" s="6">
         <v>0.10199999999999999</v>
@@ -5366,7 +5378,7 @@
         <v>12</v>
       </c>
       <c r="F78" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G78" s="6">
         <v>0.10299999999999999</v>
@@ -5410,7 +5422,7 @@
         <v>12</v>
       </c>
       <c r="F79" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G79" s="6">
         <v>0.10299999999999999</v>
@@ -5454,7 +5466,7 @@
         <v>12</v>
       </c>
       <c r="F80" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G80" s="6">
         <v>9.7000000000000003E-2</v>
@@ -5498,7 +5510,7 @@
         <v>12</v>
       </c>
       <c r="F81" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G81" s="6">
         <v>9.6000000000000002E-2</v>
@@ -5542,7 +5554,7 @@
         <v>12</v>
       </c>
       <c r="F82" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G82" s="6">
         <v>0.10199999999999999</v>
@@ -5586,7 +5598,7 @@
         <v>12</v>
       </c>
       <c r="F83" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G83" s="6">
         <v>0.10199999999999999</v>
@@ -5630,7 +5642,7 @@
         <v>12</v>
       </c>
       <c r="F84" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G84" s="6">
         <v>0.10199999999999999</v>
@@ -5674,7 +5686,7 @@
         <v>12</v>
       </c>
       <c r="F85" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G85" s="6">
         <v>0.10199999999999999</v>
@@ -5718,7 +5730,7 @@
         <v>12</v>
       </c>
       <c r="F86" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G86" s="6">
         <v>0.10100000000000001</v>
@@ -5762,7 +5774,7 @@
         <v>12</v>
       </c>
       <c r="F87" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G87" s="6">
         <v>8.7999999999999995E-2</v>
@@ -5806,7 +5818,7 @@
         <v>12</v>
       </c>
       <c r="F88" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G88" s="6">
         <v>6.9000000000000006E-2</v>
@@ -5850,7 +5862,7 @@
         <v>12</v>
       </c>
       <c r="F89" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G89" s="6">
         <v>8.5000000000000006E-2</v>
@@ -5894,7 +5906,7 @@
         <v>12</v>
       </c>
       <c r="F90" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G90" s="6">
         <v>0.10199999999999999</v>
@@ -5938,7 +5950,7 @@
         <v>12</v>
       </c>
       <c r="F91" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G91" s="6">
         <v>9.7000000000000003E-2</v>
@@ -5982,7 +5994,7 @@
         <v>12</v>
       </c>
       <c r="F92" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G92" s="6">
         <v>9.9000000000000005E-2</v>
@@ -6026,7 +6038,7 @@
         <v>12</v>
       </c>
       <c r="F93" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G93" s="6">
         <v>0.10199999999999999</v>
@@ -6070,7 +6082,7 @@
         <v>12</v>
       </c>
       <c r="F94" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G94" s="6">
         <v>9.5000000000000001E-2</v>
@@ -6114,7 +6126,7 @@
         <v>12</v>
       </c>
       <c r="F95" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G95" s="6">
         <v>8.5999999999999993E-2</v>
@@ -6158,7 +6170,7 @@
         <v>12</v>
       </c>
       <c r="F96" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G96" s="6">
         <v>0.104</v>
@@ -6202,7 +6214,7 @@
         <v>12</v>
       </c>
       <c r="F97" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G97" s="6">
         <v>8.5999999999999993E-2</v>
@@ -6246,7 +6258,7 @@
         <v>12</v>
       </c>
       <c r="F98" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G98" s="6">
         <v>9.9000000000000005E-2</v>
@@ -6290,7 +6302,7 @@
         <v>12</v>
       </c>
       <c r="F99" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G99" s="6">
         <v>0.10199999999999999</v>
@@ -6334,7 +6346,7 @@
         <v>12</v>
       </c>
       <c r="F100" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G100" s="6">
         <v>0.10100000000000001</v>
@@ -6378,7 +6390,7 @@
         <v>12</v>
       </c>
       <c r="F101" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G101" s="6">
         <v>0.10199999999999999</v>
@@ -6422,7 +6434,7 @@
         <v>12</v>
       </c>
       <c r="F102" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G102" s="6">
         <v>9.0999999999999998E-2</v>
@@ -6466,7 +6478,7 @@
         <v>12</v>
       </c>
       <c r="F103" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G103" s="6">
         <v>0.105</v>
@@ -6510,7 +6522,7 @@
         <v>12</v>
       </c>
       <c r="F104" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G104" s="6">
         <v>7.2999999999999995E-2</v>
@@ -6552,7 +6564,7 @@
         <v>12</v>
       </c>
       <c r="F105" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G105" s="6"/>
       <c r="H105" s="6"/>
@@ -6592,7 +6604,7 @@
         <v>12</v>
       </c>
       <c r="F106" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G106" s="6">
         <v>9.2999999999999999E-2</v>
@@ -6634,7 +6646,7 @@
         <v>12</v>
       </c>
       <c r="F107" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G107" s="6"/>
       <c r="H107" s="6"/>
@@ -6674,7 +6686,7 @@
         <v>12</v>
       </c>
       <c r="F108" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G108" s="6">
         <v>8.1000000000000003E-2</v>
@@ -6716,7 +6728,7 @@
         <v>12</v>
       </c>
       <c r="F109" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G109" s="6"/>
       <c r="H109" s="6"/>
@@ -6756,7 +6768,7 @@
         <v>12</v>
       </c>
       <c r="F110" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G110" s="6">
         <v>7.0999999999999994E-2</v>
@@ -6798,7 +6810,7 @@
         <v>12</v>
       </c>
       <c r="F111" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G111" s="6"/>
       <c r="H111" s="6"/>
@@ -6838,7 +6850,7 @@
         <v>12</v>
       </c>
       <c r="F112" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G112" s="6">
         <v>6.8000000000000005E-2</v>
@@ -6880,7 +6892,7 @@
         <v>12</v>
       </c>
       <c r="F113" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G113" s="6"/>
       <c r="H113" s="6"/>
@@ -6920,7 +6932,7 @@
         <v>12</v>
       </c>
       <c r="F114" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G114" s="6">
         <v>9.0999999999999998E-2</v>
@@ -6962,7 +6974,7 @@
         <v>12</v>
       </c>
       <c r="F115" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G115" s="6"/>
       <c r="H115" s="6"/>
@@ -7002,7 +7014,7 @@
         <v>12</v>
       </c>
       <c r="F116" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G116" s="6">
         <v>9.2999999999999999E-2</v>
@@ -7044,7 +7056,7 @@
         <v>12</v>
       </c>
       <c r="F117" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G117" s="6"/>
       <c r="H117" s="6"/>
@@ -7084,7 +7096,7 @@
         <v>12</v>
       </c>
       <c r="F118" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G118" s="6">
         <v>8.2000000000000003E-2</v>
@@ -7126,7 +7138,7 @@
         <v>12</v>
       </c>
       <c r="F119" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G119" s="6"/>
       <c r="H119" s="6"/>
@@ -7166,7 +7178,7 @@
         <v>12</v>
       </c>
       <c r="F120" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G120" s="6">
         <v>0.223</v>
@@ -7208,7 +7220,7 @@
         <v>12</v>
       </c>
       <c r="F121" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G121" s="6"/>
       <c r="H121" s="6"/>
@@ -7248,7 +7260,7 @@
         <v>12</v>
       </c>
       <c r="F122" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G122" s="6">
         <v>0.08</v>
@@ -7290,7 +7302,7 @@
         <v>12</v>
       </c>
       <c r="F123" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G123" s="6"/>
       <c r="H123" s="6"/>
@@ -7330,7 +7342,7 @@
         <v>12</v>
       </c>
       <c r="F124" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G124" s="6">
         <v>7.0999999999999994E-2</v>
@@ -7372,7 +7384,7 @@
         <v>12</v>
       </c>
       <c r="F125" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G125" s="6"/>
       <c r="H125" s="6"/>
@@ -7412,7 +7424,7 @@
         <v>12</v>
       </c>
       <c r="F126" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G126" s="6">
         <v>1.163</v>
@@ -7454,7 +7466,7 @@
         <v>12</v>
       </c>
       <c r="F127" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G127" s="6"/>
       <c r="H127" s="6"/>
@@ -7494,7 +7506,7 @@
         <v>12</v>
       </c>
       <c r="F128" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G128" s="6">
         <v>7.5999999999999998E-2</v>
@@ -7536,7 +7548,7 @@
         <v>12</v>
       </c>
       <c r="F129" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G129" s="6"/>
       <c r="H129" s="6"/>
@@ -7574,7 +7586,7 @@
         <v>12</v>
       </c>
       <c r="F130" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G130" s="6"/>
       <c r="H130" s="6"/>
@@ -7612,7 +7624,7 @@
         <v>12</v>
       </c>
       <c r="F131" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G131" s="6"/>
       <c r="H131" s="6"/>
@@ -7650,7 +7662,7 @@
         <v>12</v>
       </c>
       <c r="F132" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G132" s="6"/>
       <c r="H132" s="6"/>
@@ -7688,7 +7700,7 @@
         <v>12</v>
       </c>
       <c r="F133" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G133" s="6"/>
       <c r="H133" s="6"/>
@@ -7726,7 +7738,7 @@
         <v>12</v>
       </c>
       <c r="F134" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G134" s="6"/>
       <c r="H134" s="6"/>
@@ -7764,7 +7776,7 @@
         <v>12</v>
       </c>
       <c r="F135" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G135" s="6"/>
       <c r="H135" s="6"/>
@@ -7802,7 +7814,7 @@
         <v>12</v>
       </c>
       <c r="F136" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G136" s="6"/>
       <c r="H136" s="6"/>
@@ -7840,7 +7852,7 @@
         <v>12</v>
       </c>
       <c r="F137" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G137" s="6"/>
       <c r="H137" s="6"/>
@@ -7878,7 +7890,7 @@
         <v>12</v>
       </c>
       <c r="F138" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G138" s="6"/>
       <c r="H138" s="6"/>
@@ -7916,7 +7928,7 @@
         <v>12</v>
       </c>
       <c r="F139" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G139" s="6"/>
       <c r="H139" s="6"/>
@@ -7954,7 +7966,7 @@
         <v>12</v>
       </c>
       <c r="F140" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G140" s="6"/>
       <c r="H140" s="6"/>
@@ -7992,7 +8004,7 @@
         <v>12</v>
       </c>
       <c r="F141" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G141" s="6"/>
       <c r="H141" s="6"/>
@@ -8030,7 +8042,7 @@
         <v>12</v>
       </c>
       <c r="F142" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G142" s="6"/>
       <c r="H142" s="6"/>
@@ -8068,7 +8080,7 @@
         <v>12</v>
       </c>
       <c r="F143" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G143" s="6"/>
       <c r="H143" s="6"/>
@@ -8106,7 +8118,7 @@
         <v>12</v>
       </c>
       <c r="F144" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G144" s="6"/>
       <c r="H144" s="6"/>
@@ -8144,7 +8156,7 @@
         <v>12</v>
       </c>
       <c r="F145" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G145" s="6"/>
       <c r="H145" s="6"/>
@@ -8182,7 +8194,7 @@
         <v>12</v>
       </c>
       <c r="F146" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G146" s="6"/>
       <c r="H146" s="6"/>
@@ -8220,7 +8232,7 @@
         <v>12</v>
       </c>
       <c r="F147" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G147" s="6"/>
       <c r="H147" s="6"/>
@@ -8258,7 +8270,7 @@
         <v>12</v>
       </c>
       <c r="F148" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G148" s="6"/>
       <c r="H148" s="6"/>
@@ -8296,7 +8308,7 @@
         <v>12</v>
       </c>
       <c r="F149" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G149" s="6"/>
       <c r="H149" s="6"/>
@@ -8334,7 +8346,7 @@
         <v>12</v>
       </c>
       <c r="F150" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G150" s="6"/>
       <c r="H150" s="6"/>
@@ -8372,7 +8384,7 @@
         <v>12</v>
       </c>
       <c r="F151" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G151" s="6"/>
       <c r="H151" s="6"/>
@@ -8410,7 +8422,7 @@
         <v>12</v>
       </c>
       <c r="F152" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G152" s="6"/>
       <c r="H152" s="6"/>
@@ -8448,7 +8460,7 @@
         <v>12</v>
       </c>
       <c r="F153" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G153" s="6"/>
       <c r="H153" s="6"/>
@@ -8486,7 +8498,7 @@
         <v>12</v>
       </c>
       <c r="F154" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G154" s="6"/>
       <c r="H154" s="6"/>
@@ -8524,7 +8536,7 @@
         <v>12</v>
       </c>
       <c r="F155" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G155" s="6"/>
       <c r="H155" s="6"/>
@@ -8562,7 +8574,7 @@
         <v>12</v>
       </c>
       <c r="F156" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G156" s="6"/>
       <c r="H156" s="6"/>
@@ -8600,7 +8612,7 @@
         <v>12</v>
       </c>
       <c r="F157" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G157" s="6"/>
       <c r="H157" s="6"/>
@@ -8638,7 +8650,7 @@
         <v>12</v>
       </c>
       <c r="F158" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G158" s="6"/>
       <c r="H158" s="6"/>
@@ -8676,7 +8688,7 @@
         <v>12</v>
       </c>
       <c r="F159" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G159" s="6"/>
       <c r="H159" s="6"/>
@@ -8714,7 +8726,7 @@
         <v>12</v>
       </c>
       <c r="F160" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G160" s="6"/>
       <c r="H160" s="6"/>
@@ -8752,7 +8764,7 @@
         <v>12</v>
       </c>
       <c r="F161" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G161" s="6"/>
       <c r="H161" s="6"/>
@@ -8790,7 +8802,7 @@
         <v>12</v>
       </c>
       <c r="F162" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G162" s="6"/>
       <c r="H162" s="6"/>
@@ -8828,7 +8840,7 @@
         <v>12</v>
       </c>
       <c r="F163" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G163" s="6"/>
       <c r="H163" s="6"/>
@@ -8866,7 +8878,7 @@
         <v>12</v>
       </c>
       <c r="F164" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G164" s="6"/>
       <c r="H164" s="6"/>
@@ -8904,7 +8916,7 @@
         <v>12</v>
       </c>
       <c r="F165" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G165" s="6"/>
       <c r="H165" s="6"/>
@@ -8942,7 +8954,7 @@
         <v>12</v>
       </c>
       <c r="F166" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G166" s="6"/>
       <c r="H166" s="6"/>
@@ -8980,7 +8992,7 @@
         <v>12</v>
       </c>
       <c r="F167" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G167" s="6"/>
       <c r="H167" s="6"/>
@@ -9018,7 +9030,7 @@
         <v>12</v>
       </c>
       <c r="F168" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G168" s="6"/>
       <c r="H168" s="6"/>
@@ -9056,7 +9068,7 @@
         <v>12</v>
       </c>
       <c r="F169" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G169" s="6"/>
       <c r="H169" s="6"/>
@@ -9094,7 +9106,7 @@
         <v>12</v>
       </c>
       <c r="F170" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G170" s="6"/>
       <c r="H170" s="6"/>
@@ -9132,7 +9144,7 @@
         <v>12</v>
       </c>
       <c r="F171" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G171" s="6"/>
       <c r="H171" s="6"/>
@@ -9170,7 +9182,7 @@
         <v>12</v>
       </c>
       <c r="F172" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G172" s="6"/>
       <c r="H172" s="6"/>
@@ -9208,7 +9220,7 @@
         <v>12</v>
       </c>
       <c r="F173" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G173" s="6"/>
       <c r="H173" s="6"/>
@@ -9246,7 +9258,7 @@
         <v>12</v>
       </c>
       <c r="F174" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G174" s="6"/>
       <c r="H174" s="6"/>
@@ -9284,7 +9296,7 @@
         <v>12</v>
       </c>
       <c r="F175" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G175" s="6"/>
       <c r="H175" s="6"/>
@@ -9322,7 +9334,7 @@
         <v>12</v>
       </c>
       <c r="F176" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G176" s="6"/>
       <c r="H176" s="6"/>
@@ -9360,7 +9372,7 @@
         <v>12</v>
       </c>
       <c r="F177" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G177" s="6"/>
       <c r="H177" s="6"/>
@@ -9398,7 +9410,7 @@
         <v>12</v>
       </c>
       <c r="F178" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G178" s="6"/>
       <c r="H178" s="6"/>
@@ -9436,7 +9448,7 @@
         <v>12</v>
       </c>
       <c r="F179" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G179" s="6"/>
       <c r="H179" s="6"/>
@@ -9474,7 +9486,7 @@
         <v>12</v>
       </c>
       <c r="F180" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G180" s="6"/>
       <c r="H180" s="6"/>
@@ -9512,7 +9524,7 @@
         <v>12</v>
       </c>
       <c r="F181" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G181" s="6"/>
       <c r="H181" s="6"/>
@@ -9550,7 +9562,7 @@
         <v>12</v>
       </c>
       <c r="F182" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G182" s="6"/>
       <c r="H182" s="6"/>
@@ -9588,7 +9600,7 @@
         <v>12</v>
       </c>
       <c r="F183" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G183" s="6"/>
       <c r="H183" s="6"/>
@@ -9628,7 +9640,7 @@
         <v>12</v>
       </c>
       <c r="F184" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G184" s="6">
         <v>7.4999999999999997E-2</v>
@@ -9672,7 +9684,7 @@
         <v>12</v>
       </c>
       <c r="F185" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G185" s="6">
         <v>6.7000000000000004E-2</v>
@@ -9716,7 +9728,7 @@
         <v>12</v>
       </c>
       <c r="F186" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G186" s="6">
         <v>6.7000000000000004E-2</v>
@@ -9760,7 +9772,7 @@
         <v>12</v>
       </c>
       <c r="F187" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G187" s="6">
         <v>6.6000000000000003E-2</v>
@@ -9804,7 +9816,7 @@
         <v>12</v>
       </c>
       <c r="F188" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G188" s="6">
         <v>6.9000000000000006E-2</v>
@@ -9848,7 +9860,7 @@
         <v>12</v>
       </c>
       <c r="F189" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G189" s="6">
         <v>6.8000000000000005E-2</v>
@@ -9892,7 +9904,7 @@
         <v>12</v>
       </c>
       <c r="F190" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G190" s="6">
         <v>8.6999999999999994E-2</v>
@@ -9936,7 +9948,7 @@
         <v>12</v>
       </c>
       <c r="F191" s="83" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G191" s="6">
         <v>6.9000000000000006E-2</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1875" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2A4FA20-61AD-4BA3-AAC3-F04073678DBF}"/>
+  <xr:revisionPtr revIDLastSave="1891" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D8C9523-006E-440A-ACCC-19308917722B}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3035" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3039" uniqueCount="377">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -1164,6 +1164,18 @@
   </si>
   <si>
     <t>9993270</t>
+  </si>
+  <si>
+    <t>9993264</t>
+  </si>
+  <si>
+    <t>10192024</t>
+  </si>
+  <si>
+    <t>9993269</t>
+  </si>
+  <si>
+    <t>9993263</t>
   </si>
 </sst>
 </file>
@@ -4292,7 +4304,9 @@
       <c r="B53" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C53" s="83"/>
+      <c r="C53" s="83" t="s">
+        <v>376</v>
+      </c>
       <c r="D53" s="83" t="s">
         <v>11</v>
       </c>
@@ -4302,10 +4316,14 @@
       <c r="F53" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
+      <c r="G53" s="6">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="H53" s="88">
+        <v>46205</v>
+      </c>
       <c r="I53" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="101" t="s">
         <v>347</v>
@@ -4374,7 +4392,9 @@
       <c r="B55" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C55" s="83"/>
+      <c r="C55" s="83" t="s">
+        <v>375</v>
+      </c>
       <c r="D55" s="83" t="s">
         <v>11</v>
       </c>
@@ -4384,10 +4404,14 @@
       <c r="F55" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
+      <c r="G55" s="6">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="H55" s="88">
+        <v>46205</v>
+      </c>
       <c r="I55" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="101" t="s">
         <v>347</v>
@@ -4456,7 +4480,9 @@
       <c r="B57" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C57" s="83"/>
+      <c r="C57" s="83" t="s">
+        <v>374</v>
+      </c>
       <c r="D57" s="83" t="s">
         <v>11</v>
       </c>
@@ -4466,10 +4492,14 @@
       <c r="F57" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
+      <c r="G57" s="6">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="H57" s="88">
+        <v>46205</v>
+      </c>
       <c r="I57" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" s="101" t="s">
         <v>347</v>
@@ -4538,7 +4568,9 @@
       <c r="B59" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C59" s="83"/>
+      <c r="C59" s="83" t="s">
+        <v>373</v>
+      </c>
       <c r="D59" s="83" t="s">
         <v>11</v>
       </c>
@@ -4548,10 +4580,14 @@
       <c r="F59" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
+      <c r="G59" s="6">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="H59" s="88">
+        <v>46205</v>
+      </c>
       <c r="I59" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="101" t="s">
         <v>347</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1891" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D8C9523-006E-440A-ACCC-19308917722B}"/>
+  <xr:revisionPtr revIDLastSave="1895" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{780E7EBC-1215-47B9-8E40-6DE1A6E0CA91}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3039" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3040" uniqueCount="378">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -1176,6 +1176,9 @@
   </si>
   <si>
     <t>9993263</t>
+  </si>
+  <si>
+    <t>10192026</t>
   </si>
 </sst>
 </file>
@@ -4222,7 +4225,9 @@
       <c r="B51" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C51" s="83"/>
+      <c r="C51" s="83" t="s">
+        <v>377</v>
+      </c>
       <c r="D51" s="83" t="s">
         <v>11</v>
       </c>
@@ -4232,10 +4237,14 @@
       <c r="F51" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
+      <c r="G51" s="6">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="H51" s="88">
+        <v>46205</v>
+      </c>
       <c r="I51" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="101" t="s">
         <v>347</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1895" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{780E7EBC-1215-47B9-8E40-6DE1A6E0CA91}"/>
+  <xr:revisionPtr revIDLastSave="1904" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9E7D18C-5909-46F4-9428-87DA8558CA5E}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3040" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3042" uniqueCount="380">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -1179,6 +1179,12 @@
   </si>
   <si>
     <t>10192026</t>
+  </si>
+  <si>
+    <t>9993267</t>
+  </si>
+  <si>
+    <t>10192058</t>
   </si>
 </sst>
 </file>
@@ -2009,6 +2015,10 @@
 </FeaturePropertyBags>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4061,7 +4071,9 @@
       <c r="B47" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C47" s="83"/>
+      <c r="C47" s="83" t="s">
+        <v>379</v>
+      </c>
       <c r="D47" s="83" t="s">
         <v>11</v>
       </c>
@@ -4071,10 +4083,14 @@
       <c r="F47" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
+      <c r="G47" s="6">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="H47" s="88">
+        <v>46205</v>
+      </c>
       <c r="I47" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="101" t="s">
         <v>347</v>
@@ -4143,7 +4159,9 @@
       <c r="B49" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C49" s="83"/>
+      <c r="C49" s="83" t="s">
+        <v>378</v>
+      </c>
       <c r="D49" s="83" t="s">
         <v>11</v>
       </c>
@@ -4153,10 +4171,14 @@
       <c r="F49" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
+      <c r="G49" s="6">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="H49" s="88">
+        <v>46205</v>
+      </c>
       <c r="I49" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="101" t="s">
         <v>347</v>
@@ -21332,10 +21354,12 @@
       <c r="D26" s="8">
         <v>0</v>
       </c>
-      <c r="E26" s="10"/>
+      <c r="E26" s="10">
+        <v>54.7</v>
+      </c>
       <c r="F26" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1904" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9E7D18C-5909-46F4-9428-87DA8558CA5E}"/>
+  <xr:revisionPtr revIDLastSave="1914" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BDDAA59-B117-4F63-B55A-3F20661451F5}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3042" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3044" uniqueCount="382">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -1185,6 +1185,12 @@
   </si>
   <si>
     <t>10192058</t>
+  </si>
+  <si>
+    <t>9993254</t>
+  </si>
+  <si>
+    <t>10216100</t>
   </si>
 </sst>
 </file>
@@ -3919,7 +3925,9 @@
       <c r="B43" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="83"/>
+      <c r="C43" s="83" t="s">
+        <v>381</v>
+      </c>
       <c r="D43" s="83" t="s">
         <v>11</v>
       </c>
@@ -3929,10 +3937,14 @@
       <c r="F43" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
+      <c r="G43" s="6">
+        <v>0.155</v>
+      </c>
+      <c r="H43" s="88">
+        <v>46205</v>
+      </c>
       <c r="I43" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="101" t="s">
         <v>348</v>
@@ -3995,7 +4007,9 @@
       <c r="B45" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C45" s="83"/>
+      <c r="C45" s="83" t="s">
+        <v>380</v>
+      </c>
       <c r="D45" s="83" t="s">
         <v>11</v>
       </c>
@@ -4005,10 +4019,14 @@
       <c r="F45" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
+      <c r="G45" s="6">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="H45" s="88">
+        <v>46205</v>
+      </c>
       <c r="I45" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="101" t="s">
         <v>348</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1914" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BDDAA59-B117-4F63-B55A-3F20661451F5}"/>
+  <xr:revisionPtr revIDLastSave="1922" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D404826-00FC-4CDC-AACA-69F27FF074B0}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3044" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3046" uniqueCount="384">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -1191,6 +1191,12 @@
   </si>
   <si>
     <t>10216100</t>
+  </si>
+  <si>
+    <t>10192052</t>
+  </si>
+  <si>
+    <t>10192051</t>
   </si>
 </sst>
 </file>
@@ -3735,7 +3741,9 @@
       <c r="B38" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="83"/>
+      <c r="C38" s="83" t="s">
+        <v>383</v>
+      </c>
       <c r="D38" s="83" t="s">
         <v>11</v>
       </c>
@@ -3745,10 +3753,14 @@
       <c r="F38" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
+      <c r="G38" s="6">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="H38" s="88">
+        <v>46205</v>
+      </c>
       <c r="I38" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="101" t="s">
         <v>345</v>
@@ -3811,7 +3823,9 @@
       <c r="B40" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="C40" s="83"/>
+      <c r="C40" s="83" t="s">
+        <v>382</v>
+      </c>
       <c r="D40" s="83" t="s">
         <v>11</v>
       </c>
@@ -3821,10 +3835,14 @@
       <c r="F40" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
+      <c r="G40" s="6">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="H40" s="88">
+        <v>46205</v>
+      </c>
       <c r="I40" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="101" t="s">
         <v>345</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1922" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D404826-00FC-4CDC-AACA-69F27FF074B0}"/>
+  <xr:revisionPtr revIDLastSave="1926" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55C810BF-CC64-4010-8FD3-1168611897A5}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3046" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3047" uniqueCount="385">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -1197,6 +1197,9 @@
   </si>
   <si>
     <t>10192051</t>
+  </si>
+  <si>
+    <t>10192065</t>
   </si>
 </sst>
 </file>
@@ -3665,7 +3668,9 @@
       <c r="B36" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="83"/>
+      <c r="C36" s="83" t="s">
+        <v>384</v>
+      </c>
       <c r="D36" s="83" t="s">
         <v>11</v>
       </c>
@@ -3675,10 +3680,14 @@
       <c r="F36" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
+      <c r="G36" s="6">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="H36" s="88">
+        <v>46205</v>
+      </c>
       <c r="I36" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="101" t="s">
         <v>345</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1926" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55C810BF-CC64-4010-8FD3-1168611897A5}"/>
+  <xr:revisionPtr revIDLastSave="1939" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60F1F77D-A634-4056-9D0A-68CE8D705D69}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3047" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3050" uniqueCount="388">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -1200,6 +1200,15 @@
   </si>
   <si>
     <t>10192065</t>
+  </si>
+  <si>
+    <t>9993239</t>
+  </si>
+  <si>
+    <t>9993241</t>
+  </si>
+  <si>
+    <t>10192053</t>
   </si>
 </sst>
 </file>
@@ -3914,7 +3923,9 @@
       <c r="B42" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="83"/>
+      <c r="C42" s="83" t="s">
+        <v>386</v>
+      </c>
       <c r="D42" s="83" t="s">
         <v>11</v>
       </c>
@@ -3924,10 +3935,14 @@
       <c r="F42" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
+      <c r="G42" s="6">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="H42" s="88">
+        <v>46205</v>
+      </c>
       <c r="I42" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="101" t="s">
         <v>345</v>
@@ -3996,7 +4011,9 @@
       <c r="B44" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="83"/>
+      <c r="C44" s="83" t="s">
+        <v>385</v>
+      </c>
       <c r="D44" s="83" t="s">
         <v>11</v>
       </c>
@@ -4006,10 +4023,14 @@
       <c r="F44" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
+      <c r="G44" s="6">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="H44" s="88">
+        <v>46205</v>
+      </c>
       <c r="I44" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="101" t="s">
         <v>345</v>
@@ -4078,7 +4099,9 @@
       <c r="B46" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="C46" s="83"/>
+      <c r="C46" s="83" t="s">
+        <v>387</v>
+      </c>
       <c r="D46" s="83" t="s">
         <v>11</v>
       </c>
@@ -4088,10 +4111,14 @@
       <c r="F46" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
+      <c r="G46" s="6">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="H46" s="88">
+        <v>46205</v>
+      </c>
       <c r="I46" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="101" t="s">
         <v>344</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1939" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60F1F77D-A634-4056-9D0A-68CE8D705D69}"/>
+  <xr:revisionPtr revIDLastSave="1947" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AB65D96-74F8-4021-BD23-1AD6229CAA95}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3050" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="390">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -1202,6 +1202,9 @@
     <t>10192065</t>
   </si>
   <si>
+    <t>10192061</t>
+  </si>
+  <si>
     <t>9993239</t>
   </si>
   <si>
@@ -1209,6 +1212,9 @@
   </si>
   <si>
     <t>10192053</t>
+  </si>
+  <si>
+    <t>10192048</t>
   </si>
 </sst>
 </file>
@@ -3803,7 +3809,9 @@
       <c r="B39" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="83"/>
+      <c r="C39" s="83" t="s">
+        <v>389</v>
+      </c>
       <c r="D39" s="83" t="s">
         <v>11</v>
       </c>
@@ -3813,10 +3821,14 @@
       <c r="F39" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
+      <c r="G39" s="6">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="H39" s="88">
+        <v>46205</v>
+      </c>
       <c r="I39" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="101" t="s">
         <v>348</v>
@@ -3885,7 +3897,9 @@
       <c r="B41" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="83"/>
+      <c r="C41" s="83" t="s">
+        <v>385</v>
+      </c>
       <c r="D41" s="83" t="s">
         <v>11</v>
       </c>
@@ -3895,10 +3909,14 @@
       <c r="F41" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
+      <c r="G41" s="6">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="H41" s="88">
+        <v>46205</v>
+      </c>
       <c r="I41" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="101" t="s">
         <v>348</v>
@@ -3924,7 +3942,7 @@
         <v>16</v>
       </c>
       <c r="C42" s="83" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D42" s="83" t="s">
         <v>11</v>
@@ -4012,7 +4030,7 @@
         <v>16</v>
       </c>
       <c r="C44" s="83" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D44" s="83" t="s">
         <v>11</v>
@@ -4100,7 +4118,7 @@
         <v>16</v>
       </c>
       <c r="C46" s="83" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D46" s="83" t="s">
         <v>11</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1947" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AB65D96-74F8-4021-BD23-1AD6229CAA95}"/>
+  <xr:revisionPtr revIDLastSave="1955" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DFF3527-D3B8-4E96-A513-D55F04640F94}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3054" uniqueCount="392">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -1215,6 +1215,12 @@
   </si>
   <si>
     <t>10192048</t>
+  </si>
+  <si>
+    <t>10192049</t>
+  </si>
+  <si>
+    <t>9993262</t>
   </si>
 </sst>
 </file>
@@ -3645,7 +3651,9 @@
       <c r="B35" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="83"/>
+      <c r="C35" s="83" t="s">
+        <v>391</v>
+      </c>
       <c r="D35" s="83" t="s">
         <v>11</v>
       </c>
@@ -3655,10 +3663,14 @@
       <c r="F35" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
+      <c r="G35" s="6">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="H35" s="88">
+        <v>46205</v>
+      </c>
       <c r="I35" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="101" t="s">
         <v>348</v>
@@ -3727,7 +3739,9 @@
       <c r="B37" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="83"/>
+      <c r="C37" s="83" t="s">
+        <v>390</v>
+      </c>
       <c r="D37" s="83" t="s">
         <v>11</v>
       </c>
@@ -3737,10 +3751,14 @@
       <c r="F37" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
+      <c r="G37" s="6">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="H37" s="88">
+        <v>46205</v>
+      </c>
       <c r="I37" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="101" t="s">
         <v>348</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1955" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DFF3527-D3B8-4E96-A513-D55F04640F94}"/>
+  <xr:revisionPtr revIDLastSave="2029" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86204340-3AF9-440D-B5B6-96B8E5075F41}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Water meters " sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3054" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3073" uniqueCount="395">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -1221,6 +1221,15 @@
   </si>
   <si>
     <t>9993262</t>
+  </si>
+  <si>
+    <t>10192010</t>
+  </si>
+  <si>
+    <t>10192016</t>
+  </si>
+  <si>
+    <t>9993259</t>
   </si>
 </sst>
 </file>
@@ -2051,10 +2060,6 @@
 </FeaturePropertyBags>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6770,7 +6775,7 @@
         <v>127</v>
       </c>
       <c r="C106" s="83" t="s">
-        <v>146</v>
+        <v>392</v>
       </c>
       <c r="D106" s="83" t="s">
         <v>11</v>
@@ -6782,7 +6787,7 @@
         <v>371</v>
       </c>
       <c r="G106" s="6">
-        <v>9.2999999999999999E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="H106" s="88">
         <v>46168</v>
@@ -6934,7 +6939,7 @@
         <v>127</v>
       </c>
       <c r="C110" s="83" t="s">
-        <v>152</v>
+        <v>393</v>
       </c>
       <c r="D110" s="83" t="s">
         <v>11</v>
@@ -6946,7 +6951,7 @@
         <v>371</v>
       </c>
       <c r="G110" s="6">
-        <v>7.0999999999999994E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="H110" s="88">
         <v>46142</v>
@@ -7590,7 +7595,7 @@
         <v>127</v>
       </c>
       <c r="C126" s="83" t="s">
-        <v>176</v>
+        <v>394</v>
       </c>
       <c r="D126" s="83" t="s">
         <v>11</v>
@@ -7602,7 +7607,7 @@
         <v>371</v>
       </c>
       <c r="G126" s="6">
-        <v>1.163</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="H126" s="88">
         <v>46168</v>
@@ -11887,7 +11892,9 @@
       <c r="B35" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="5"/>
+      <c r="C35" s="5">
+        <v>14558069275</v>
+      </c>
       <c r="D35" s="5">
         <v>82929684</v>
       </c>
@@ -11900,14 +11907,18 @@
       <c r="G35" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H35" s="5"/>
+      <c r="H35" s="16" t="s">
+        <v>278</v>
+      </c>
       <c r="I35" s="50" t="s">
         <v>295</v>
       </c>
       <c r="J35" s="18">
         <v>0</v>
       </c>
-      <c r="K35" s="5"/>
+      <c r="K35" s="13">
+        <v>46206</v>
+      </c>
       <c r="L35" s="20" t="b">
         <v>0</v>
       </c>
@@ -11934,7 +11945,9 @@
       <c r="B36" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="5"/>
+      <c r="C36" s="5">
+        <v>14558069325</v>
+      </c>
       <c r="D36" s="5">
         <v>82929684</v>
       </c>
@@ -11947,14 +11960,18 @@
       <c r="G36" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H36" s="5"/>
+      <c r="H36" s="17" t="s">
+        <v>277</v>
+      </c>
       <c r="I36" s="50" t="s">
         <v>295</v>
       </c>
       <c r="J36" s="18">
         <v>0</v>
       </c>
-      <c r="K36" s="5"/>
+      <c r="K36" s="13">
+        <v>46206</v>
+      </c>
       <c r="L36" s="20" t="b">
         <v>0</v>
       </c>
@@ -11981,7 +11998,9 @@
       <c r="B37" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="5"/>
+      <c r="C37" s="5">
+        <v>14558069978</v>
+      </c>
       <c r="D37" s="5">
         <v>82929684</v>
       </c>
@@ -11994,14 +12013,18 @@
       <c r="G37" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H37" s="5"/>
+      <c r="H37" s="5" t="s">
+        <v>275</v>
+      </c>
       <c r="I37" s="50" t="s">
         <v>295</v>
       </c>
       <c r="J37" s="18">
         <v>0</v>
       </c>
-      <c r="K37" s="5"/>
+      <c r="K37" s="13">
+        <v>46206</v>
+      </c>
       <c r="L37" s="20" t="b">
         <v>0</v>
       </c>
@@ -12028,7 +12051,9 @@
       <c r="B38" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="5"/>
+      <c r="C38" s="5">
+        <v>14558069283</v>
+      </c>
       <c r="D38" s="5">
         <v>82929684</v>
       </c>
@@ -12041,14 +12066,18 @@
       <c r="G38" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H38" s="5"/>
+      <c r="H38" s="16" t="s">
+        <v>278</v>
+      </c>
       <c r="I38" s="50" t="s">
         <v>295</v>
       </c>
       <c r="J38" s="18">
         <v>0</v>
       </c>
-      <c r="K38" s="5"/>
+      <c r="K38" s="13">
+        <v>46206</v>
+      </c>
       <c r="L38" s="20" t="b">
         <v>0</v>
       </c>
@@ -12075,7 +12104,9 @@
       <c r="B39" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="5"/>
+      <c r="C39" s="5">
+        <v>14558069473</v>
+      </c>
       <c r="D39" s="5">
         <v>82929684</v>
       </c>
@@ -12088,14 +12119,18 @@
       <c r="G39" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H39" s="5"/>
+      <c r="H39" s="16" t="s">
+        <v>278</v>
+      </c>
       <c r="I39" s="51" t="s">
         <v>297</v>
       </c>
       <c r="J39" s="18">
         <v>0</v>
       </c>
-      <c r="K39" s="5"/>
+      <c r="K39" s="13">
+        <v>46206</v>
+      </c>
       <c r="L39" s="20" t="b">
         <v>0</v>
       </c>
@@ -12122,7 +12157,9 @@
       <c r="B40" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C40" s="5"/>
+      <c r="C40" s="5">
+        <v>14558069366</v>
+      </c>
       <c r="D40" s="5">
         <v>82929684</v>
       </c>
@@ -12135,14 +12172,18 @@
       <c r="G40" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H40" s="5"/>
+      <c r="H40" s="5" t="s">
+        <v>275</v>
+      </c>
       <c r="I40" s="51" t="s">
         <v>297</v>
       </c>
       <c r="J40" s="18">
         <v>0</v>
       </c>
-      <c r="K40" s="5"/>
+      <c r="K40" s="13">
+        <v>46206</v>
+      </c>
       <c r="L40" s="20" t="b">
         <v>0</v>
       </c>
@@ -12169,7 +12210,9 @@
       <c r="B41" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="5"/>
+      <c r="C41" s="5">
+        <v>14558069614</v>
+      </c>
       <c r="D41" s="5">
         <v>82929684</v>
       </c>
@@ -12182,14 +12225,18 @@
       <c r="G41" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H41" s="5"/>
+      <c r="H41" s="5" t="s">
+        <v>275</v>
+      </c>
       <c r="I41" s="51" t="s">
         <v>297</v>
       </c>
       <c r="J41" s="18">
         <v>0</v>
       </c>
-      <c r="K41" s="5"/>
+      <c r="K41" s="13">
+        <v>46206</v>
+      </c>
       <c r="L41" s="20" t="b">
         <v>0</v>
       </c>
@@ -12216,7 +12263,9 @@
       <c r="B42" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="5"/>
+      <c r="C42" s="5">
+        <v>14558068905</v>
+      </c>
       <c r="D42" s="5">
         <v>82929684</v>
       </c>
@@ -12229,14 +12278,18 @@
       <c r="G42" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H42" s="5"/>
+      <c r="H42" s="17" t="s">
+        <v>277</v>
+      </c>
       <c r="I42" s="51" t="s">
         <v>297</v>
       </c>
       <c r="J42" s="18">
         <v>0</v>
       </c>
-      <c r="K42" s="5"/>
+      <c r="K42" s="13">
+        <v>46206</v>
+      </c>
       <c r="L42" s="20" t="b">
         <v>0</v>
       </c>
@@ -12263,7 +12316,9 @@
       <c r="B43" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="5"/>
+      <c r="C43" s="5">
+        <v>14558069630</v>
+      </c>
       <c r="D43" s="5">
         <v>82929684</v>
       </c>
@@ -12276,14 +12331,18 @@
       <c r="G43" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H43" s="5"/>
+      <c r="H43" s="17" t="s">
+        <v>277</v>
+      </c>
       <c r="I43" s="51" t="s">
         <v>297</v>
       </c>
       <c r="J43" s="18">
         <v>0</v>
       </c>
-      <c r="K43" s="5"/>
+      <c r="K43" s="13">
+        <v>46206</v>
+      </c>
       <c r="L43" s="20" t="b">
         <v>0</v>
       </c>
@@ -12310,7 +12369,9 @@
       <c r="B44" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="5"/>
+      <c r="C44" s="5">
+        <v>14558068863</v>
+      </c>
       <c r="D44" s="5">
         <v>82929684</v>
       </c>
@@ -12323,14 +12384,18 @@
       <c r="G44" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H44" s="5"/>
+      <c r="H44" s="16" t="s">
+        <v>278</v>
+      </c>
       <c r="I44" s="51" t="s">
         <v>297</v>
       </c>
       <c r="J44" s="18">
         <v>0</v>
       </c>
-      <c r="K44" s="5"/>
+      <c r="K44" s="13">
+        <v>46206</v>
+      </c>
       <c r="L44" s="20" t="b">
         <v>0</v>
       </c>
@@ -12357,7 +12422,9 @@
       <c r="B45" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C45" s="5"/>
+      <c r="C45" s="5">
+        <v>14558069655</v>
+      </c>
       <c r="D45" s="5">
         <v>82929684</v>
       </c>
@@ -12370,14 +12437,18 @@
       <c r="G45" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H45" s="5"/>
+      <c r="H45" s="16" t="s">
+        <v>278</v>
+      </c>
       <c r="I45" s="51" t="s">
         <v>297</v>
       </c>
       <c r="J45" s="18">
         <v>0</v>
       </c>
-      <c r="K45" s="5"/>
+      <c r="K45" s="13">
+        <v>46206</v>
+      </c>
       <c r="L45" s="20" t="b">
         <v>0</v>
       </c>
@@ -12404,7 +12475,9 @@
       <c r="B46" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C46" s="5"/>
+      <c r="C46" s="5">
+        <v>14558069622</v>
+      </c>
       <c r="D46" s="5">
         <v>82929684</v>
       </c>
@@ -12417,14 +12490,18 @@
       <c r="G46" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H46" s="5"/>
+      <c r="H46" s="5" t="s">
+        <v>275</v>
+      </c>
       <c r="I46" s="51" t="s">
         <v>297</v>
       </c>
       <c r="J46" s="18">
         <v>0</v>
       </c>
-      <c r="K46" s="5"/>
+      <c r="K46" s="13">
+        <v>46206</v>
+      </c>
       <c r="L46" s="20" t="b">
         <v>0</v>
       </c>
@@ -12733,7 +12810,9 @@
       <c r="B53" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C53" s="5"/>
+      <c r="C53" s="5">
+        <v>14558069895</v>
+      </c>
       <c r="D53" s="5">
         <v>82929684</v>
       </c>
@@ -12746,14 +12825,18 @@
       <c r="G53" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H53" s="5"/>
+      <c r="H53" s="5" t="s">
+        <v>275</v>
+      </c>
       <c r="I53" s="39" t="s">
         <v>289</v>
       </c>
       <c r="J53" s="18">
         <v>0</v>
       </c>
-      <c r="K53" s="5"/>
+      <c r="K53" s="13">
+        <v>46206</v>
+      </c>
       <c r="L53" s="20" t="b">
         <v>0</v>
       </c>
@@ -12780,7 +12863,9 @@
       <c r="B54" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C54" s="5"/>
+      <c r="C54" s="5">
+        <v>14558069192</v>
+      </c>
       <c r="D54" s="5">
         <v>82929684</v>
       </c>
@@ -12793,14 +12878,18 @@
       <c r="G54" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H54" s="5"/>
+      <c r="H54" s="16" t="s">
+        <v>278</v>
+      </c>
       <c r="I54" s="39" t="s">
         <v>289</v>
       </c>
       <c r="J54" s="18">
         <v>0</v>
       </c>
-      <c r="K54" s="5"/>
+      <c r="K54" s="13">
+        <v>46206</v>
+      </c>
       <c r="L54" s="20" t="b">
         <v>0</v>
       </c>
@@ -12827,7 +12916,9 @@
       <c r="B55" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C55" s="5"/>
+      <c r="C55" s="5">
+        <v>14558068269</v>
+      </c>
       <c r="D55" s="5">
         <v>82929684</v>
       </c>
@@ -12840,14 +12931,18 @@
       <c r="G55" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H55" s="5"/>
+      <c r="H55" s="16" t="s">
+        <v>278</v>
+      </c>
       <c r="I55" s="39" t="s">
         <v>289</v>
       </c>
       <c r="J55" s="18">
         <v>0</v>
       </c>
-      <c r="K55" s="5"/>
+      <c r="K55" s="13">
+        <v>46206</v>
+      </c>
       <c r="L55" s="20" t="b">
         <v>0</v>
       </c>
@@ -12874,7 +12969,9 @@
       <c r="B56" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C56" s="5"/>
+      <c r="C56" s="5">
+        <v>14558068426</v>
+      </c>
       <c r="D56" s="5">
         <v>82929684</v>
       </c>
@@ -12887,14 +12984,18 @@
       <c r="G56" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H56" s="5"/>
+      <c r="H56" s="5" t="s">
+        <v>275</v>
+      </c>
       <c r="I56" s="39" t="s">
         <v>289</v>
       </c>
       <c r="J56" s="18">
         <v>0</v>
       </c>
-      <c r="K56" s="5"/>
+      <c r="K56" s="13">
+        <v>46206</v>
+      </c>
       <c r="L56" s="20" t="b">
         <v>0</v>
       </c>
@@ -12921,7 +13022,9 @@
       <c r="B57" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C57" s="5"/>
+      <c r="C57" s="5">
+        <v>14558069358</v>
+      </c>
       <c r="D57" s="5">
         <v>82929684</v>
       </c>
@@ -12934,14 +13037,18 @@
       <c r="G57" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H57" s="5"/>
+      <c r="H57" s="17" t="s">
+        <v>277</v>
+      </c>
       <c r="I57" s="39" t="s">
         <v>289</v>
       </c>
       <c r="J57" s="18">
         <v>0</v>
       </c>
-      <c r="K57" s="5"/>
+      <c r="K57" s="13">
+        <v>46206</v>
+      </c>
       <c r="L57" s="20" t="b">
         <v>0</v>
       </c>
@@ -12968,7 +13075,9 @@
       <c r="B58" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C58" s="5"/>
+      <c r="C58" s="5">
+        <v>14558068327</v>
+      </c>
       <c r="D58" s="5">
         <v>82929684</v>
       </c>
@@ -12981,14 +13090,18 @@
       <c r="G58" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H58" s="5"/>
+      <c r="H58" s="17" t="s">
+        <v>277</v>
+      </c>
       <c r="I58" s="39" t="s">
         <v>289</v>
       </c>
       <c r="J58" s="18">
         <v>0</v>
       </c>
-      <c r="K58" s="5"/>
+      <c r="K58" s="13">
+        <v>46206</v>
+      </c>
       <c r="L58" s="20" t="b">
         <v>0</v>
       </c>
@@ -13068,7 +13181,9 @@
       <c r="B60" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C60" s="5"/>
+      <c r="C60" s="5">
+        <v>14558069531</v>
+      </c>
       <c r="D60" s="5">
         <v>82929684</v>
       </c>
@@ -13081,14 +13196,18 @@
       <c r="G60" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H60" s="5"/>
+      <c r="H60" s="16" t="s">
+        <v>278</v>
+      </c>
       <c r="I60" s="39" t="s">
         <v>289</v>
       </c>
       <c r="J60" s="18">
         <v>0</v>
       </c>
-      <c r="K60" s="5"/>
+      <c r="K60" s="13">
+        <v>46206</v>
+      </c>
       <c r="L60" s="20" t="b">
         <v>0</v>
       </c>
@@ -21030,10 +21149,12 @@
       <c r="D4" s="7">
         <v>17968.5</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="6">
+        <v>18120.900000000001</v>
+      </c>
       <c r="F4" s="6">
         <f t="shared" si="0"/>
-        <v>-17968.5</v>
+        <v>152.40000000000146</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2029" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86204340-3AF9-440D-B5B6-96B8E5075F41}"/>
+  <xr:revisionPtr revIDLastSave="2047" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E47F5AE-80C1-414C-A309-C7F85769D99E}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3073" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3079" uniqueCount="395">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -12528,7 +12528,9 @@
       <c r="B47" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C47" s="5"/>
+      <c r="C47" s="5">
+        <v>1455868871</v>
+      </c>
       <c r="D47" s="5">
         <v>82929684</v>
       </c>
@@ -12541,14 +12543,18 @@
       <c r="G47" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H47" s="5"/>
+      <c r="H47" s="16" t="s">
+        <v>278</v>
+      </c>
       <c r="I47" s="52" t="s">
         <v>270</v>
       </c>
       <c r="J47" s="18">
         <v>0</v>
       </c>
-      <c r="K47" s="5"/>
+      <c r="K47" s="13">
+        <v>46206</v>
+      </c>
       <c r="L47" s="20" t="b">
         <v>0</v>
       </c>
@@ -12575,7 +12581,9 @@
       <c r="B48" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C48" s="5"/>
+      <c r="C48" s="5">
+        <v>14558066198</v>
+      </c>
       <c r="D48" s="5">
         <v>82929684</v>
       </c>
@@ -12588,14 +12596,18 @@
       <c r="G48" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H48" s="5"/>
+      <c r="H48" s="16" t="s">
+        <v>278</v>
+      </c>
       <c r="I48" s="52" t="s">
         <v>270</v>
       </c>
       <c r="J48" s="18">
         <v>0</v>
       </c>
-      <c r="K48" s="5"/>
+      <c r="K48" s="13">
+        <v>46206</v>
+      </c>
       <c r="L48" s="20" t="b">
         <v>0</v>
       </c>
@@ -12622,7 +12634,9 @@
       <c r="B49" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C49" s="5"/>
+      <c r="C49" s="5">
+        <v>14558066255</v>
+      </c>
       <c r="D49" s="5">
         <v>82929684</v>
       </c>
@@ -12635,14 +12649,18 @@
       <c r="G49" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H49" s="5"/>
+      <c r="H49" s="5" t="s">
+        <v>275</v>
+      </c>
       <c r="I49" s="52" t="s">
         <v>270</v>
       </c>
       <c r="J49" s="18">
         <v>0</v>
       </c>
-      <c r="K49" s="5"/>
+      <c r="K49" s="13">
+        <v>46206</v>
+      </c>
       <c r="L49" s="20" t="b">
         <v>0</v>
       </c>
@@ -12669,7 +12687,9 @@
       <c r="B50" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C50" s="5"/>
+      <c r="C50" s="5">
+        <v>14558066115</v>
+      </c>
       <c r="D50" s="5">
         <v>82929684</v>
       </c>
@@ -12682,14 +12702,18 @@
       <c r="G50" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H50" s="5"/>
+      <c r="H50" s="5" t="s">
+        <v>275</v>
+      </c>
       <c r="I50" s="52" t="s">
         <v>270</v>
       </c>
       <c r="J50" s="18">
         <v>0</v>
       </c>
-      <c r="K50" s="5"/>
+      <c r="K50" s="13">
+        <v>46206</v>
+      </c>
       <c r="L50" s="20" t="b">
         <v>0</v>
       </c>
@@ -12716,7 +12740,9 @@
       <c r="B51" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C51" s="5"/>
+      <c r="C51" s="5">
+        <v>14558068913</v>
+      </c>
       <c r="D51" s="5">
         <v>82929684</v>
       </c>
@@ -12729,14 +12755,18 @@
       <c r="G51" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H51" s="5"/>
+      <c r="H51" s="17" t="s">
+        <v>277</v>
+      </c>
       <c r="I51" s="52" t="s">
         <v>270</v>
       </c>
       <c r="J51" s="18">
         <v>0</v>
       </c>
-      <c r="K51" s="5"/>
+      <c r="K51" s="13">
+        <v>46206</v>
+      </c>
       <c r="L51" s="20" t="b">
         <v>0</v>
       </c>
@@ -12763,7 +12793,9 @@
       <c r="B52" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="5"/>
+      <c r="C52" s="5">
+        <v>14558069010</v>
+      </c>
       <c r="D52" s="5">
         <v>82929684</v>
       </c>
@@ -12776,14 +12808,18 @@
       <c r="G52" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="H52" s="5"/>
+      <c r="H52" s="17" t="s">
+        <v>277</v>
+      </c>
       <c r="I52" s="52" t="s">
         <v>270</v>
       </c>
       <c r="J52" s="18">
         <v>0</v>
       </c>
-      <c r="K52" s="5"/>
+      <c r="K52" s="13">
+        <v>46206</v>
+      </c>
       <c r="L52" s="20" t="b">
         <v>0</v>
       </c>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2124" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65DFE61E-BCAB-470D-82F1-65AA3D76264F}"/>
+  <xr:revisionPtr revIDLastSave="2148" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AAA1884-9E91-478E-9800-06D5D126536A}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Water meters " sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3100" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3103" uniqueCount="397">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -1227,6 +1227,15 @@
   </si>
   <si>
     <t>?</t>
+  </si>
+  <si>
+    <t>Faulty Meter</t>
+  </si>
+  <si>
+    <t>Faulty Replaced</t>
+  </si>
+  <si>
+    <t>Replacement Date</t>
   </si>
 </sst>
 </file>
@@ -1871,28 +1880,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2329,7 +2338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N193"/>
+  <dimension ref="A1:Q193"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
@@ -2340,9 +2349,12 @@
     <col min="10" max="10" width="27.3984375" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="20.19921875" customWidth="1"/>
     <col min="14" max="14" width="35.53125" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" customWidth="1"/>
+    <col min="16" max="16" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2385,8 +2397,17 @@
       <c r="N1" s="1" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O1" s="100" t="s">
+        <v>394</v>
+      </c>
+      <c r="P1" s="100" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q1" s="101" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>9</v>
       </c>
@@ -2423,8 +2444,15 @@
       <c r="N2" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O2" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="19"/>
+    </row>
+    <row r="3" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>14</v>
       </c>
@@ -2461,8 +2489,15 @@
       <c r="N3" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O3" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="19"/>
+    </row>
+    <row r="4" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>15</v>
       </c>
@@ -2499,8 +2534,15 @@
       <c r="N4" s="88">
         <v>46240</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O4" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="19"/>
+    </row>
+    <row r="5" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
         <v>17</v>
       </c>
@@ -2537,8 +2579,15 @@
       <c r="N5" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O5" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="19"/>
+    </row>
+    <row r="6" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>18</v>
       </c>
@@ -2575,8 +2624,15 @@
       <c r="N6" s="88">
         <v>46240</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O6" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="19"/>
+    </row>
+    <row r="7" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="s">
         <v>19</v>
       </c>
@@ -2613,8 +2669,15 @@
       <c r="N7" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O7" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="19"/>
+    </row>
+    <row r="8" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>20</v>
       </c>
@@ -2651,8 +2714,15 @@
       <c r="N8" s="88">
         <v>46240</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O8" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="19"/>
+    </row>
+    <row r="9" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
         <v>21</v>
       </c>
@@ -2689,8 +2759,15 @@
       <c r="N9" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O9" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="19"/>
+    </row>
+    <row r="10" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>22</v>
       </c>
@@ -2727,8 +2804,15 @@
       <c r="N10" s="88">
         <v>46240</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O10" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="19"/>
+    </row>
+    <row r="11" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
         <v>23</v>
       </c>
@@ -2765,8 +2849,15 @@
       <c r="N11" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O11" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="19"/>
+    </row>
+    <row r="12" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>24</v>
       </c>
@@ -2803,8 +2894,15 @@
       <c r="N12" s="88">
         <v>46240</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O12" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="19"/>
+    </row>
+    <row r="13" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A13" s="25" t="s">
         <v>25</v>
       </c>
@@ -2841,8 +2939,15 @@
       <c r="N13" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O13" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="19"/>
+    </row>
+    <row r="14" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>26</v>
       </c>
@@ -2879,8 +2984,15 @@
       <c r="N14" s="88">
         <v>46240</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O14" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="19"/>
+    </row>
+    <row r="15" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
         <v>27</v>
       </c>
@@ -2917,8 +3029,15 @@
       <c r="N15" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O15" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="19"/>
+    </row>
+    <row r="16" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
         <v>28</v>
       </c>
@@ -2955,8 +3074,15 @@
       <c r="N16" s="88">
         <v>46240</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O16" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="19"/>
+    </row>
+    <row r="17" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A17" s="25" t="s">
         <v>29</v>
       </c>
@@ -2993,8 +3119,15 @@
       <c r="N17" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O17" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="19"/>
+    </row>
+    <row r="18" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
         <v>30</v>
       </c>
@@ -3031,8 +3164,15 @@
       <c r="N18" s="88">
         <v>46224</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O18" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="19"/>
+    </row>
+    <row r="19" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
         <v>31</v>
       </c>
@@ -3069,8 +3209,15 @@
       <c r="N19" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O19" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="19"/>
+    </row>
+    <row r="20" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
         <v>32</v>
       </c>
@@ -3107,8 +3254,15 @@
       <c r="N20" s="88">
         <v>46224</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O20" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="19"/>
+    </row>
+    <row r="21" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
         <v>33</v>
       </c>
@@ -3145,8 +3299,15 @@
       <c r="N21" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O21" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="19"/>
+    </row>
+    <row r="22" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
         <v>34</v>
       </c>
@@ -3183,8 +3344,15 @@
       <c r="N22" s="88">
         <v>46224</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O22" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="19"/>
+    </row>
+    <row r="23" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A23" s="25" t="s">
         <v>35</v>
       </c>
@@ -3221,8 +3389,15 @@
       <c r="N23" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O23" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="19"/>
+    </row>
+    <row r="24" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
         <v>36</v>
       </c>
@@ -3259,8 +3434,15 @@
       <c r="N24" s="88">
         <v>46224</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O24" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="19"/>
+    </row>
+    <row r="25" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
         <v>37</v>
       </c>
@@ -3297,8 +3479,15 @@
       <c r="N25" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O25" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="19"/>
+    </row>
+    <row r="26" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
         <v>38</v>
       </c>
@@ -3335,8 +3524,15 @@
       <c r="N26" s="88">
         <v>46224</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O26" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="19"/>
+    </row>
+    <row r="27" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A27" s="25" t="s">
         <v>39</v>
       </c>
@@ -3373,8 +3569,15 @@
       <c r="N27" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O27" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="19"/>
+    </row>
+    <row r="28" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A28" s="25" t="s">
         <v>40</v>
       </c>
@@ -3411,8 +3614,15 @@
       <c r="N28" s="88">
         <v>46224</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O28" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="19"/>
+    </row>
+    <row r="29" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="s">
         <v>41</v>
       </c>
@@ -3449,8 +3659,15 @@
       <c r="N29" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O29" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="19"/>
+    </row>
+    <row r="30" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
         <v>42</v>
       </c>
@@ -3487,8 +3704,15 @@
       <c r="N30" s="88">
         <v>46224</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O30" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="19"/>
+    </row>
+    <row r="31" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A31" s="25" t="s">
         <v>43</v>
       </c>
@@ -3525,8 +3749,15 @@
       <c r="N31" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O31" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="19"/>
+    </row>
+    <row r="32" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
         <v>44</v>
       </c>
@@ -3563,8 +3794,15 @@
       <c r="N32" s="88">
         <v>46224</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O32" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="19"/>
+    </row>
+    <row r="33" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A33" s="25" t="s">
         <v>45</v>
       </c>
@@ -3601,8 +3839,15 @@
       <c r="N33" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O33" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="19"/>
+    </row>
+    <row r="34" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A34" s="25" t="s">
         <v>46</v>
       </c>
@@ -3639,8 +3884,15 @@
       <c r="N34" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O34" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="19"/>
+    </row>
+    <row r="35" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A35" s="25" t="s">
         <v>47</v>
       </c>
@@ -3683,8 +3935,15 @@
       <c r="N35" s="88">
         <v>46221</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O35" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="19"/>
+    </row>
+    <row r="36" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A36" s="25" t="s">
         <v>48</v>
       </c>
@@ -3727,8 +3986,15 @@
       <c r="N36" s="88">
         <v>46207</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O36" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="19"/>
+    </row>
+    <row r="37" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A37" s="25" t="s">
         <v>49</v>
       </c>
@@ -3771,8 +4037,15 @@
       <c r="N37" s="88">
         <v>46221</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O37" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="19"/>
+    </row>
+    <row r="38" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A38" s="25" t="s">
         <v>50</v>
       </c>
@@ -3815,8 +4088,15 @@
       <c r="N38" s="88">
         <v>46207</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O38" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="19"/>
+    </row>
+    <row r="39" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A39" s="25" t="s">
         <v>51</v>
       </c>
@@ -3859,8 +4139,15 @@
       <c r="N39" s="88">
         <v>46221</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O39" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="19"/>
+    </row>
+    <row r="40" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A40" s="25" t="s">
         <v>52</v>
       </c>
@@ -3903,8 +4190,15 @@
       <c r="N40" s="88">
         <v>46207</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O40" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="19"/>
+    </row>
+    <row r="41" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A41" s="25" t="s">
         <v>53</v>
       </c>
@@ -3947,8 +4241,15 @@
       <c r="N41" s="88">
         <v>46221</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O41" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="19"/>
+    </row>
+    <row r="42" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A42" s="25" t="s">
         <v>54</v>
       </c>
@@ -3991,8 +4292,15 @@
       <c r="N42" s="88">
         <v>46207</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O42" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P42" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="19"/>
+    </row>
+    <row r="43" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A43" s="25" t="s">
         <v>55</v>
       </c>
@@ -4035,8 +4343,15 @@
       <c r="N43" s="88">
         <v>46221</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O43" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="19"/>
+    </row>
+    <row r="44" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A44" s="25" t="s">
         <v>56</v>
       </c>
@@ -4079,8 +4394,15 @@
       <c r="N44" s="88">
         <v>46207</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O44" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P44" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="19"/>
+    </row>
+    <row r="45" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A45" s="25" t="s">
         <v>57</v>
       </c>
@@ -4123,8 +4445,15 @@
       <c r="N45" s="88">
         <v>46221</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O45" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P45" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="19"/>
+    </row>
+    <row r="46" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A46" s="25" t="s">
         <v>58</v>
       </c>
@@ -4167,8 +4496,15 @@
       <c r="N46" s="88">
         <v>46195</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O46" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P46" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="19"/>
+    </row>
+    <row r="47" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A47" s="25" t="s">
         <v>59</v>
       </c>
@@ -4211,8 +4547,15 @@
       <c r="N47" s="88">
         <v>46207</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O47" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P47" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="19"/>
+    </row>
+    <row r="48" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A48" s="25" t="s">
         <v>60</v>
       </c>
@@ -4255,8 +4598,15 @@
       <c r="N48" s="88">
         <v>46195</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O48" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="19"/>
+    </row>
+    <row r="49" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A49" s="25" t="s">
         <v>61</v>
       </c>
@@ -4299,8 +4649,15 @@
       <c r="N49" s="88">
         <v>46207</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O49" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="19"/>
+    </row>
+    <row r="50" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A50" s="25" t="s">
         <v>62</v>
       </c>
@@ -4343,8 +4700,15 @@
       <c r="N50" s="88">
         <v>46195</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O50" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P50" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="19"/>
+    </row>
+    <row r="51" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A51" s="25" t="s">
         <v>63</v>
       </c>
@@ -4387,8 +4751,15 @@
       <c r="N51" s="88">
         <v>46207</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O51" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P51" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="19"/>
+    </row>
+    <row r="52" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A52" s="25" t="s">
         <v>64</v>
       </c>
@@ -4431,8 +4802,15 @@
       <c r="N52" s="88">
         <v>46195</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O52" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="19"/>
+    </row>
+    <row r="53" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A53" s="25" t="s">
         <v>65</v>
       </c>
@@ -4475,8 +4853,15 @@
       <c r="N53" s="88">
         <v>46207</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O53" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="19"/>
+    </row>
+    <row r="54" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A54" s="25" t="s">
         <v>66</v>
       </c>
@@ -4519,8 +4904,15 @@
       <c r="N54" s="88">
         <v>46195</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O54" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="19"/>
+    </row>
+    <row r="55" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A55" s="25" t="s">
         <v>67</v>
       </c>
@@ -4563,8 +4955,15 @@
       <c r="N55" s="88">
         <v>46207</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O55" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="19"/>
+    </row>
+    <row r="56" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A56" s="25" t="s">
         <v>68</v>
       </c>
@@ -4607,8 +5006,15 @@
       <c r="N56" s="88">
         <v>46195</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O56" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="19"/>
+    </row>
+    <row r="57" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A57" s="25" t="s">
         <v>69</v>
       </c>
@@ -4651,8 +5057,15 @@
       <c r="N57" s="88">
         <v>46207</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O57" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="19"/>
+    </row>
+    <row r="58" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A58" s="25" t="s">
         <v>70</v>
       </c>
@@ -4695,8 +5108,15 @@
       <c r="N58" s="88">
         <v>46195</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O58" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P58" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="19"/>
+    </row>
+    <row r="59" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A59" s="25" t="s">
         <v>71</v>
       </c>
@@ -4739,8 +5159,15 @@
       <c r="N59" s="88">
         <v>46207</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O59" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P59" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="19"/>
+    </row>
+    <row r="60" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A60" s="25" t="s">
         <v>72</v>
       </c>
@@ -4783,8 +5210,15 @@
       <c r="N60" s="88">
         <v>46195</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O60" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P60" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="19"/>
+    </row>
+    <row r="61" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A61" s="25" t="s">
         <v>73</v>
       </c>
@@ -4827,8 +5261,15 @@
       <c r="N61" s="88">
         <v>46207</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O61" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P61" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="19"/>
+    </row>
+    <row r="62" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A62" s="25" t="s">
         <v>74</v>
       </c>
@@ -4871,8 +5312,15 @@
       <c r="N62" s="88">
         <v>46179</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O62" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P62" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="19"/>
+    </row>
+    <row r="63" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A63" s="25" t="s">
         <v>76</v>
       </c>
@@ -4915,8 +5363,15 @@
       <c r="N63" s="88">
         <v>46195</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O63" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="19"/>
+    </row>
+    <row r="64" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A64" s="25" t="s">
         <v>78</v>
       </c>
@@ -4959,8 +5414,15 @@
       <c r="N64" s="88">
         <v>46179</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O64" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P64" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="19"/>
+    </row>
+    <row r="65" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A65" s="25" t="s">
         <v>80</v>
       </c>
@@ -5003,8 +5465,15 @@
       <c r="N65" s="88">
         <v>46195</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O65" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P65" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="19"/>
+    </row>
+    <row r="66" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A66" s="25" t="s">
         <v>82</v>
       </c>
@@ -5047,8 +5516,15 @@
       <c r="N66" s="88">
         <v>46179</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O66" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P66" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="19"/>
+    </row>
+    <row r="67" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A67" s="25" t="s">
         <v>84</v>
       </c>
@@ -5091,8 +5567,15 @@
       <c r="N67" s="88">
         <v>46195</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O67" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P67" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="19"/>
+    </row>
+    <row r="68" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A68" s="25" t="s">
         <v>85</v>
       </c>
@@ -5135,8 +5618,15 @@
       <c r="N68" s="88">
         <v>46179</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O68" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P68" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="19"/>
+    </row>
+    <row r="69" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A69" s="25" t="s">
         <v>87</v>
       </c>
@@ -5179,8 +5669,15 @@
       <c r="N69" s="88">
         <v>46195</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O69" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="19"/>
+    </row>
+    <row r="70" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A70" s="25" t="s">
         <v>88</v>
       </c>
@@ -5223,8 +5720,15 @@
       <c r="N70" s="88">
         <v>46179</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O70" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P70" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="19"/>
+    </row>
+    <row r="71" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A71" s="25" t="s">
         <v>90</v>
       </c>
@@ -5267,8 +5771,15 @@
       <c r="N71" s="88">
         <v>46195</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O71" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P71" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="19"/>
+    </row>
+    <row r="72" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A72" s="25" t="s">
         <v>92</v>
       </c>
@@ -5311,8 +5822,15 @@
       <c r="N72" s="88">
         <v>46179</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O72" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P72" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="19"/>
+    </row>
+    <row r="73" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A73" s="25" t="s">
         <v>94</v>
       </c>
@@ -5355,8 +5873,15 @@
       <c r="N73" s="88">
         <v>46195</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O73" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P73" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="19"/>
+    </row>
+    <row r="74" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A74" s="25" t="s">
         <v>96</v>
       </c>
@@ -5399,8 +5924,15 @@
       <c r="N74" s="88">
         <v>46179</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O74" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P74" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="19"/>
+    </row>
+    <row r="75" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A75" s="25" t="s">
         <v>98</v>
       </c>
@@ -5443,8 +5975,15 @@
       <c r="N75" s="88">
         <v>46195</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O75" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P75" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="19"/>
+    </row>
+    <row r="76" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A76" s="25" t="s">
         <v>100</v>
       </c>
@@ -5487,8 +6026,15 @@
       <c r="N76" s="88">
         <v>46179</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O76" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P76" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="19"/>
+    </row>
+    <row r="77" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A77" s="25" t="s">
         <v>102</v>
       </c>
@@ -5531,8 +6077,15 @@
       <c r="N77" s="88">
         <v>46217</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O77" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P77" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="19"/>
+    </row>
+    <row r="78" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A78" s="25" t="s">
         <v>105</v>
       </c>
@@ -5575,8 +6128,15 @@
       <c r="N78" s="88">
         <v>46217</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O78" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P78" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="19"/>
+    </row>
+    <row r="79" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A79" s="25" t="s">
         <v>107</v>
       </c>
@@ -5619,8 +6179,15 @@
       <c r="N79" s="88">
         <v>46217</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O79" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P79" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="19"/>
+    </row>
+    <row r="80" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A80" s="25" t="s">
         <v>108</v>
       </c>
@@ -5663,8 +6230,15 @@
       <c r="N80" s="88">
         <v>46217</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O80" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P80" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="19"/>
+    </row>
+    <row r="81" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A81" s="25" t="s">
         <v>110</v>
       </c>
@@ -5707,8 +6281,15 @@
       <c r="N81" s="88">
         <v>46203</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O81" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P81" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="19"/>
+    </row>
+    <row r="82" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A82" s="25" t="s">
         <v>111</v>
       </c>
@@ -5751,8 +6332,15 @@
       <c r="N82" s="88">
         <v>46203</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O82" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P82" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="19"/>
+    </row>
+    <row r="83" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A83" s="25" t="s">
         <v>112</v>
       </c>
@@ -5795,8 +6383,15 @@
       <c r="N83" s="88">
         <v>46203</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O83" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P83" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="19"/>
+    </row>
+    <row r="84" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A84" s="25" t="s">
         <v>113</v>
       </c>
@@ -5839,8 +6434,15 @@
       <c r="N84" s="88">
         <v>46203</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O84" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P84" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="19"/>
+    </row>
+    <row r="85" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A85" s="25" t="s">
         <v>114</v>
       </c>
@@ -5883,8 +6485,15 @@
       <c r="N85" s="88">
         <v>46203</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O85" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P85" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="19"/>
+    </row>
+    <row r="86" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A86" s="25" t="s">
         <v>115</v>
       </c>
@@ -5927,8 +6536,15 @@
       <c r="N86" s="88">
         <v>46203</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O86" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P86" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="19"/>
+    </row>
+    <row r="87" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A87" s="25" t="s">
         <v>116</v>
       </c>
@@ -5971,8 +6587,15 @@
       <c r="N87" s="88">
         <v>46203</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O87" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P87" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="19"/>
+    </row>
+    <row r="88" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A88" s="25" t="s">
         <v>118</v>
       </c>
@@ -6015,8 +6638,15 @@
       <c r="N88" s="88">
         <v>46182</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O88" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P88" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="19"/>
+    </row>
+    <row r="89" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A89" s="25" t="s">
         <v>120</v>
       </c>
@@ -6059,8 +6689,15 @@
       <c r="N89" s="88">
         <v>46182</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O89" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P89" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="19"/>
+    </row>
+    <row r="90" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A90" s="25" t="s">
         <v>121</v>
       </c>
@@ -6103,8 +6740,15 @@
       <c r="N90" s="88">
         <v>46182</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O90" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P90" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="19"/>
+    </row>
+    <row r="91" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A91" s="25" t="s">
         <v>122</v>
       </c>
@@ -6147,8 +6791,15 @@
       <c r="N91" s="88">
         <v>46182</v>
       </c>
-    </row>
-    <row r="92" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O91" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P91" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="19"/>
+    </row>
+    <row r="92" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A92" s="25" t="s">
         <v>124</v>
       </c>
@@ -6191,8 +6842,15 @@
       <c r="N92" s="88">
         <v>46182</v>
       </c>
-    </row>
-    <row r="93" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O92" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P92" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="19"/>
+    </row>
+    <row r="93" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A93" s="25" t="s">
         <v>125</v>
       </c>
@@ -6235,8 +6893,15 @@
       <c r="N93" s="88">
         <v>46168</v>
       </c>
-    </row>
-    <row r="94" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O93" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P93" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="19"/>
+    </row>
+    <row r="94" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A94" s="25" t="s">
         <v>126</v>
       </c>
@@ -6279,8 +6944,15 @@
       <c r="N94" s="88">
         <v>46163</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O94" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P94" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="19"/>
+    </row>
+    <row r="95" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A95" s="25" t="s">
         <v>129</v>
       </c>
@@ -6323,8 +6995,15 @@
       <c r="N95" s="88">
         <v>46168</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O95" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P95" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="19"/>
+    </row>
+    <row r="96" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A96" s="25" t="s">
         <v>130</v>
       </c>
@@ -6367,8 +7046,15 @@
       <c r="N96" s="88">
         <v>46163</v>
       </c>
-    </row>
-    <row r="97" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O96" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P96" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="19"/>
+    </row>
+    <row r="97" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A97" s="25" t="s">
         <v>132</v>
       </c>
@@ -6411,8 +7097,15 @@
       <c r="N97" s="88">
         <v>46168</v>
       </c>
-    </row>
-    <row r="98" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O97" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P97" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="19"/>
+    </row>
+    <row r="98" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A98" s="25" t="s">
         <v>133</v>
       </c>
@@ -6455,8 +7148,15 @@
       <c r="N98" s="88">
         <v>46163</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O98" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P98" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="19"/>
+    </row>
+    <row r="99" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A99" s="25" t="s">
         <v>135</v>
       </c>
@@ -6499,8 +7199,15 @@
       <c r="N99" s="88">
         <v>46168</v>
       </c>
-    </row>
-    <row r="100" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O99" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P99" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="19"/>
+    </row>
+    <row r="100" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A100" s="25" t="s">
         <v>136</v>
       </c>
@@ -6543,8 +7250,15 @@
       <c r="N100" s="88">
         <v>46163</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O100" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P100" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="19"/>
+    </row>
+    <row r="101" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A101" s="25" t="s">
         <v>138</v>
       </c>
@@ -6587,8 +7301,15 @@
       <c r="N101" s="88">
         <v>46168</v>
       </c>
-    </row>
-    <row r="102" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O101" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P101" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="19"/>
+    </row>
+    <row r="102" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A102" s="25" t="s">
         <v>139</v>
       </c>
@@ -6631,8 +7352,15 @@
       <c r="N102" s="88">
         <v>46163</v>
       </c>
-    </row>
-    <row r="103" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O102" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P102" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="19"/>
+    </row>
+    <row r="103" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A103" s="25" t="s">
         <v>141</v>
       </c>
@@ -6675,8 +7403,15 @@
       <c r="N103" s="88">
         <v>46168</v>
       </c>
-    </row>
-    <row r="104" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O103" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P103" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="19"/>
+    </row>
+    <row r="104" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A104" s="25" t="s">
         <v>142</v>
       </c>
@@ -6719,8 +7454,15 @@
       <c r="N104" s="88">
         <v>46163</v>
       </c>
-    </row>
-    <row r="105" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O104" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P104" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="19"/>
+    </row>
+    <row r="105" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A105" s="25" t="s">
         <v>144</v>
       </c>
@@ -6757,8 +7499,15 @@
       <c r="N105" s="88">
         <v>46240</v>
       </c>
-    </row>
-    <row r="106" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O105" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P105" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="19"/>
+    </row>
+    <row r="106" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A106" s="25" t="s">
         <v>145</v>
       </c>
@@ -6801,8 +7550,15 @@
       <c r="N106" s="88">
         <v>46163</v>
       </c>
-    </row>
-    <row r="107" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O106" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P106" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q106" s="19"/>
+    </row>
+    <row r="107" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A107" s="25" t="s">
         <v>147</v>
       </c>
@@ -6839,8 +7595,15 @@
       <c r="N107" s="88">
         <v>46240</v>
       </c>
-    </row>
-    <row r="108" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O107" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P107" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="19"/>
+    </row>
+    <row r="108" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A108" s="25" t="s">
         <v>148</v>
       </c>
@@ -6883,8 +7646,15 @@
       <c r="N108" s="88">
         <v>46163</v>
       </c>
-    </row>
-    <row r="109" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O108" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P108" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="19"/>
+    </row>
+    <row r="109" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A109" s="25" t="s">
         <v>150</v>
       </c>
@@ -6921,8 +7691,15 @@
       <c r="N109" s="88">
         <v>46240</v>
       </c>
-    </row>
-    <row r="110" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O109" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P109" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="19"/>
+    </row>
+    <row r="110" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A110" s="25" t="s">
         <v>151</v>
       </c>
@@ -6965,8 +7742,15 @@
       <c r="N110" s="88">
         <v>46163</v>
       </c>
-    </row>
-    <row r="111" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O110" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P110" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q110" s="19"/>
+    </row>
+    <row r="111" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A111" s="25" t="s">
         <v>153</v>
       </c>
@@ -7003,8 +7787,15 @@
       <c r="N111" s="88">
         <v>46240</v>
       </c>
-    </row>
-    <row r="112" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O111" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P111" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="19"/>
+    </row>
+    <row r="112" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A112" s="25" t="s">
         <v>154</v>
       </c>
@@ -7047,8 +7838,15 @@
       <c r="N112" s="88">
         <v>46163</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O112" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P112" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="19"/>
+    </row>
+    <row r="113" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A113" s="25" t="s">
         <v>156</v>
       </c>
@@ -7085,8 +7883,15 @@
       <c r="N113" s="88">
         <v>46240</v>
       </c>
-    </row>
-    <row r="114" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O113" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P113" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="19"/>
+    </row>
+    <row r="114" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A114" s="25" t="s">
         <v>157</v>
       </c>
@@ -7129,8 +7934,15 @@
       <c r="N114" s="88">
         <v>46154</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O114" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P114" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="19"/>
+    </row>
+    <row r="115" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A115" s="25" t="s">
         <v>159</v>
       </c>
@@ -7167,8 +7979,15 @@
       <c r="N115" s="88">
         <v>46240</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O115" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P115" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="19"/>
+    </row>
+    <row r="116" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A116" s="25" t="s">
         <v>160</v>
       </c>
@@ -7211,8 +8030,15 @@
       <c r="N116" s="88">
         <v>46154</v>
       </c>
-    </row>
-    <row r="117" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O116" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P116" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="19"/>
+    </row>
+    <row r="117" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A117" s="25" t="s">
         <v>162</v>
       </c>
@@ -7249,8 +8075,15 @@
       <c r="N117" s="88">
         <v>46240</v>
       </c>
-    </row>
-    <row r="118" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O117" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P117" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q117" s="19"/>
+    </row>
+    <row r="118" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A118" s="25" t="s">
         <v>163</v>
       </c>
@@ -7293,8 +8126,15 @@
       <c r="N118" s="88">
         <v>46154</v>
       </c>
-    </row>
-    <row r="119" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O118" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P118" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q118" s="19"/>
+    </row>
+    <row r="119" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A119" s="25" t="s">
         <v>165</v>
       </c>
@@ -7331,8 +8171,15 @@
       <c r="N119" s="88">
         <v>46240</v>
       </c>
-    </row>
-    <row r="120" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O119" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P119" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="19"/>
+    </row>
+    <row r="120" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A120" s="25" t="s">
         <v>166</v>
       </c>
@@ -7375,8 +8222,15 @@
       <c r="N120" s="88">
         <v>46154</v>
       </c>
-    </row>
-    <row r="121" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O120" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P120" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="19"/>
+    </row>
+    <row r="121" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A121" s="25" t="s">
         <v>168</v>
       </c>
@@ -7413,8 +8267,15 @@
       <c r="N121" s="88">
         <v>46255</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O121" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P121" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="19"/>
+    </row>
+    <row r="122" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A122" s="25" t="s">
         <v>169</v>
       </c>
@@ -7457,8 +8318,15 @@
       <c r="N122" s="88">
         <v>46154</v>
       </c>
-    </row>
-    <row r="123" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O122" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P122" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="19"/>
+    </row>
+    <row r="123" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A123" s="25" t="s">
         <v>171</v>
       </c>
@@ -7495,8 +8363,15 @@
       <c r="N123" s="88">
         <v>46255</v>
       </c>
-    </row>
-    <row r="124" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O123" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P123" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="19"/>
+    </row>
+    <row r="124" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A124" s="25" t="s">
         <v>172</v>
       </c>
@@ -7539,8 +8414,15 @@
       <c r="N124" s="88">
         <v>46154</v>
       </c>
-    </row>
-    <row r="125" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O124" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P124" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="19"/>
+    </row>
+    <row r="125" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A125" s="25" t="s">
         <v>174</v>
       </c>
@@ -7577,8 +8459,15 @@
       <c r="N125" s="88">
         <v>46255</v>
       </c>
-    </row>
-    <row r="126" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O125" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P125" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="19"/>
+    </row>
+    <row r="126" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A126" s="25" t="s">
         <v>175</v>
       </c>
@@ -7621,8 +8510,15 @@
       <c r="N126" s="88">
         <v>46154</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O126" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P126" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q126" s="19"/>
+    </row>
+    <row r="127" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A127" s="25" t="s">
         <v>177</v>
       </c>
@@ -7659,8 +8555,15 @@
       <c r="N127" s="88">
         <v>46255</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O127" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P127" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="19"/>
+    </row>
+    <row r="128" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A128" s="25" t="s">
         <v>178</v>
       </c>
@@ -7703,8 +8606,15 @@
       <c r="N128" s="88">
         <v>46154</v>
       </c>
-    </row>
-    <row r="129" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O128" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P128" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q128" s="19"/>
+    </row>
+    <row r="129" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A129" s="25" t="s">
         <v>180</v>
       </c>
@@ -7741,8 +8651,15 @@
       <c r="N129" s="88">
         <v>46255</v>
       </c>
-    </row>
-    <row r="130" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O129" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P129" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q129" s="19"/>
+    </row>
+    <row r="130" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A130" s="25" t="s">
         <v>181</v>
       </c>
@@ -7779,8 +8696,15 @@
       <c r="N130" s="88">
         <v>46255</v>
       </c>
-    </row>
-    <row r="131" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O130" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P130" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q130" s="19"/>
+    </row>
+    <row r="131" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A131" s="25" t="s">
         <v>182</v>
       </c>
@@ -7817,8 +8741,15 @@
       <c r="N131" s="88">
         <v>46255</v>
       </c>
-    </row>
-    <row r="132" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O131" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P131" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q131" s="19"/>
+    </row>
+    <row r="132" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A132" s="25" t="s">
         <v>183</v>
       </c>
@@ -7855,8 +8786,15 @@
       <c r="N132" s="88">
         <v>46255</v>
       </c>
-    </row>
-    <row r="133" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O132" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P132" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q132" s="19"/>
+    </row>
+    <row r="133" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A133" s="25" t="s">
         <v>184</v>
       </c>
@@ -7893,8 +8831,15 @@
       <c r="N133" s="88">
         <v>46270</v>
       </c>
-    </row>
-    <row r="134" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O133" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P133" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q133" s="19"/>
+    </row>
+    <row r="134" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A134" s="25" t="s">
         <v>185</v>
       </c>
@@ -7931,8 +8876,15 @@
       <c r="N134" s="88">
         <v>46270</v>
       </c>
-    </row>
-    <row r="135" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O134" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P134" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q134" s="19"/>
+    </row>
+    <row r="135" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A135" s="25" t="s">
         <v>186</v>
       </c>
@@ -7969,8 +8921,15 @@
       <c r="N135" s="88">
         <v>46270</v>
       </c>
-    </row>
-    <row r="136" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O135" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P135" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="19"/>
+    </row>
+    <row r="136" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A136" s="25" t="s">
         <v>187</v>
       </c>
@@ -8007,8 +8966,15 @@
       <c r="N136" s="88">
         <v>46270</v>
       </c>
-    </row>
-    <row r="137" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O136" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P136" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q136" s="19"/>
+    </row>
+    <row r="137" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A137" s="25" t="s">
         <v>188</v>
       </c>
@@ -8045,8 +9011,15 @@
       <c r="N137" s="88">
         <v>46270</v>
       </c>
-    </row>
-    <row r="138" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O137" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P137" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q137" s="19"/>
+    </row>
+    <row r="138" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A138" s="25" t="s">
         <v>189</v>
       </c>
@@ -8083,8 +9056,15 @@
       <c r="N138" s="88">
         <v>46270</v>
       </c>
-    </row>
-    <row r="139" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O138" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P138" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q138" s="19"/>
+    </row>
+    <row r="139" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A139" s="25" t="s">
         <v>190</v>
       </c>
@@ -8121,8 +9101,15 @@
       <c r="N139" s="88">
         <v>46270</v>
       </c>
-    </row>
-    <row r="140" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O139" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P139" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q139" s="19"/>
+    </row>
+    <row r="140" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A140" s="25" t="s">
         <v>191</v>
       </c>
@@ -8159,8 +9146,15 @@
       <c r="N140" s="88">
         <v>46270</v>
       </c>
-    </row>
-    <row r="141" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O140" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P140" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q140" s="19"/>
+    </row>
+    <row r="141" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A141" s="25" t="s">
         <v>192</v>
       </c>
@@ -8197,8 +9191,15 @@
       <c r="N141" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="142" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O141" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P141" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q141" s="19"/>
+    </row>
+    <row r="142" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A142" s="25" t="s">
         <v>193</v>
       </c>
@@ -8235,8 +9236,15 @@
       <c r="N142" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="143" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O142" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P142" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q142" s="19"/>
+    </row>
+    <row r="143" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A143" s="25" t="s">
         <v>194</v>
       </c>
@@ -8273,8 +9281,15 @@
       <c r="N143" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="144" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O143" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P143" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q143" s="19"/>
+    </row>
+    <row r="144" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A144" s="25" t="s">
         <v>195</v>
       </c>
@@ -8311,8 +9326,15 @@
       <c r="N144" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="145" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O144" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P144" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q144" s="19"/>
+    </row>
+    <row r="145" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A145" s="25" t="s">
         <v>196</v>
       </c>
@@ -8349,8 +9371,15 @@
       <c r="N145" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="146" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O145" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P145" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="19"/>
+    </row>
+    <row r="146" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A146" s="25" t="s">
         <v>197</v>
       </c>
@@ -8387,8 +9416,15 @@
       <c r="N146" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="147" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O146" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P146" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q146" s="19"/>
+    </row>
+    <row r="147" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A147" s="25" t="s">
         <v>198</v>
       </c>
@@ -8425,8 +9461,15 @@
       <c r="N147" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="148" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O147" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P147" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q147" s="19"/>
+    </row>
+    <row r="148" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A148" s="25" t="s">
         <v>199</v>
       </c>
@@ -8463,8 +9506,15 @@
       <c r="N148" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="149" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O148" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P148" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q148" s="19"/>
+    </row>
+    <row r="149" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A149" s="25" t="s">
         <v>200</v>
       </c>
@@ -8501,8 +9551,15 @@
       <c r="N149" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="150" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O149" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P149" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q149" s="19"/>
+    </row>
+    <row r="150" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A150" s="25" t="s">
         <v>201</v>
       </c>
@@ -8539,8 +9596,15 @@
       <c r="N150" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="151" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O150" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P150" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q150" s="19"/>
+    </row>
+    <row r="151" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A151" s="25" t="s">
         <v>202</v>
       </c>
@@ -8577,8 +9641,15 @@
       <c r="N151" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="152" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O151" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P151" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q151" s="19"/>
+    </row>
+    <row r="152" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A152" s="25" t="s">
         <v>203</v>
       </c>
@@ -8615,8 +9686,15 @@
       <c r="N152" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="153" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O152" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P152" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q152" s="19"/>
+    </row>
+    <row r="153" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A153" s="25" t="s">
         <v>204</v>
       </c>
@@ -8653,8 +9731,15 @@
       <c r="N153" s="88">
         <v>46301</v>
       </c>
-    </row>
-    <row r="154" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O153" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P153" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q153" s="19"/>
+    </row>
+    <row r="154" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A154" s="25" t="s">
         <v>205</v>
       </c>
@@ -8691,8 +9776,15 @@
       <c r="N154" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="155" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O154" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P154" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q154" s="19"/>
+    </row>
+    <row r="155" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A155" s="25" t="s">
         <v>206</v>
       </c>
@@ -8729,8 +9821,15 @@
       <c r="N155" s="88">
         <v>46286</v>
       </c>
-    </row>
-    <row r="156" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O155" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P155" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q155" s="19"/>
+    </row>
+    <row r="156" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A156" s="25" t="s">
         <v>207</v>
       </c>
@@ -8767,8 +9866,15 @@
       <c r="N156" s="88">
         <v>46254</v>
       </c>
-    </row>
-    <row r="157" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O156" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P156" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q156" s="19"/>
+    </row>
+    <row r="157" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A157" s="25" t="s">
         <v>208</v>
       </c>
@@ -8805,8 +9911,15 @@
       <c r="N157" s="88">
         <v>46254</v>
       </c>
-    </row>
-    <row r="158" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O157" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P157" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q157" s="19"/>
+    </row>
+    <row r="158" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A158" s="25" t="s">
         <v>209</v>
       </c>
@@ -8843,8 +9956,15 @@
       <c r="N158" s="88">
         <v>46254</v>
       </c>
-    </row>
-    <row r="159" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O158" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P158" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q158" s="19"/>
+    </row>
+    <row r="159" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A159" s="25" t="s">
         <v>210</v>
       </c>
@@ -8881,8 +10001,15 @@
       <c r="N159" s="88">
         <v>46254</v>
       </c>
-    </row>
-    <row r="160" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O159" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P159" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q159" s="19"/>
+    </row>
+    <row r="160" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A160" s="25" t="s">
         <v>211</v>
       </c>
@@ -8919,8 +10046,15 @@
       <c r="N160" s="88">
         <v>46254</v>
       </c>
-    </row>
-    <row r="161" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O160" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P160" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q160" s="19"/>
+    </row>
+    <row r="161" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A161" s="25" t="s">
         <v>212</v>
       </c>
@@ -8957,8 +10091,15 @@
       <c r="N161" s="88">
         <v>46254</v>
       </c>
-    </row>
-    <row r="162" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O161" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P161" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q161" s="19"/>
+    </row>
+    <row r="162" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A162" s="25" t="s">
         <v>213</v>
       </c>
@@ -8995,8 +10136,15 @@
       <c r="N162" s="88">
         <v>46254</v>
       </c>
-    </row>
-    <row r="163" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O162" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P162" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q162" s="19"/>
+    </row>
+    <row r="163" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A163" s="25" t="s">
         <v>214</v>
       </c>
@@ -9033,8 +10181,15 @@
       <c r="N163" s="88">
         <v>46254</v>
       </c>
-    </row>
-    <row r="164" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O163" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P163" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q163" s="19"/>
+    </row>
+    <row r="164" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A164" s="25" t="s">
         <v>215</v>
       </c>
@@ -9071,8 +10226,15 @@
       <c r="N164" s="88">
         <v>46238</v>
       </c>
-    </row>
-    <row r="165" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O164" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P164" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q164" s="19"/>
+    </row>
+    <row r="165" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A165" s="25" t="s">
         <v>216</v>
       </c>
@@ -9109,8 +10271,15 @@
       <c r="N165" s="88">
         <v>46238</v>
       </c>
-    </row>
-    <row r="166" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O165" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P165" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q165" s="19"/>
+    </row>
+    <row r="166" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A166" s="25" t="s">
         <v>217</v>
       </c>
@@ -9147,8 +10316,15 @@
       <c r="N166" s="88">
         <v>46238</v>
       </c>
-    </row>
-    <row r="167" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O166" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P166" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q166" s="19"/>
+    </row>
+    <row r="167" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A167" s="25" t="s">
         <v>218</v>
       </c>
@@ -9185,8 +10361,15 @@
       <c r="N167" s="88">
         <v>46238</v>
       </c>
-    </row>
-    <row r="168" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O167" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P167" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q167" s="19"/>
+    </row>
+    <row r="168" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A168" s="25" t="s">
         <v>219</v>
       </c>
@@ -9223,8 +10406,15 @@
       <c r="N168" s="88">
         <v>46238</v>
       </c>
-    </row>
-    <row r="169" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O168" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P168" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q168" s="19"/>
+    </row>
+    <row r="169" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A169" s="25" t="s">
         <v>220</v>
       </c>
@@ -9261,8 +10451,15 @@
       <c r="N169" s="88">
         <v>46238</v>
       </c>
-    </row>
-    <row r="170" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O169" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P169" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q169" s="19"/>
+    </row>
+    <row r="170" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A170" s="25" t="s">
         <v>221</v>
       </c>
@@ -9299,8 +10496,15 @@
       <c r="N170" s="88">
         <v>46238</v>
       </c>
-    </row>
-    <row r="171" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O170" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P170" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q170" s="19"/>
+    </row>
+    <row r="171" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A171" s="25" t="s">
         <v>222</v>
       </c>
@@ -9337,8 +10541,15 @@
       <c r="N171" s="88">
         <v>46266</v>
       </c>
-    </row>
-    <row r="172" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O171" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P171" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q171" s="19"/>
+    </row>
+    <row r="172" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A172" s="25" t="s">
         <v>223</v>
       </c>
@@ -9375,8 +10586,15 @@
       <c r="N172" s="88">
         <v>46266</v>
       </c>
-    </row>
-    <row r="173" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O172" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P172" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q172" s="19"/>
+    </row>
+    <row r="173" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A173" s="25" t="s">
         <v>224</v>
       </c>
@@ -9413,8 +10631,15 @@
       <c r="N173" s="88">
         <v>46266</v>
       </c>
-    </row>
-    <row r="174" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O173" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P173" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q173" s="19"/>
+    </row>
+    <row r="174" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A174" s="25" t="s">
         <v>225</v>
       </c>
@@ -9451,8 +10676,15 @@
       <c r="N174" s="88">
         <v>46266</v>
       </c>
-    </row>
-    <row r="175" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O174" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P174" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="19"/>
+    </row>
+    <row r="175" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A175" s="25" t="s">
         <v>226</v>
       </c>
@@ -9489,8 +10721,15 @@
       <c r="N175" s="88">
         <v>46266</v>
       </c>
-    </row>
-    <row r="176" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O175" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P175" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q175" s="19"/>
+    </row>
+    <row r="176" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A176" s="25" t="s">
         <v>227</v>
       </c>
@@ -9527,8 +10766,15 @@
       <c r="N176" s="88">
         <v>46252</v>
       </c>
-    </row>
-    <row r="177" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O176" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P176" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q176" s="19"/>
+    </row>
+    <row r="177" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A177" s="25" t="s">
         <v>228</v>
       </c>
@@ -9565,8 +10811,15 @@
       <c r="N177" s="88">
         <v>46252</v>
       </c>
-    </row>
-    <row r="178" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O177" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P177" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q177" s="19"/>
+    </row>
+    <row r="178" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A178" s="25" t="s">
         <v>229</v>
       </c>
@@ -9603,8 +10856,15 @@
       <c r="N178" s="88">
         <v>46252</v>
       </c>
-    </row>
-    <row r="179" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O178" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P178" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q178" s="19"/>
+    </row>
+    <row r="179" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A179" s="25" t="s">
         <v>230</v>
       </c>
@@ -9641,8 +10901,15 @@
       <c r="N179" s="88">
         <v>46252</v>
       </c>
-    </row>
-    <row r="180" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O179" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P179" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q179" s="19"/>
+    </row>
+    <row r="180" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A180" s="25" t="s">
         <v>231</v>
       </c>
@@ -9679,8 +10946,15 @@
       <c r="N180" s="88">
         <v>46252</v>
       </c>
-    </row>
-    <row r="181" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O180" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P180" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q180" s="19"/>
+    </row>
+    <row r="181" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A181" s="25" t="s">
         <v>232</v>
       </c>
@@ -9717,8 +10991,15 @@
       <c r="N181" s="88">
         <v>46252</v>
       </c>
-    </row>
-    <row r="182" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O181" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P181" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q181" s="19"/>
+    </row>
+    <row r="182" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A182" s="25" t="s">
         <v>233</v>
       </c>
@@ -9755,8 +11036,15 @@
       <c r="N182" s="88">
         <v>46252</v>
       </c>
-    </row>
-    <row r="183" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O182" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P182" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q182" s="19"/>
+    </row>
+    <row r="183" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A183" s="25" t="s">
         <v>234</v>
       </c>
@@ -9793,8 +11081,15 @@
       <c r="N183" s="88">
         <v>46252</v>
       </c>
-    </row>
-    <row r="184" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O183" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P183" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q183" s="19"/>
+    </row>
+    <row r="184" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A184" s="25" t="s">
         <v>235</v>
       </c>
@@ -9837,8 +11132,15 @@
       <c r="N184" s="88">
         <v>46238</v>
       </c>
-    </row>
-    <row r="185" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O184" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P184" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q184" s="19"/>
+    </row>
+    <row r="185" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A185" s="25" t="s">
         <v>237</v>
       </c>
@@ -9881,8 +11183,15 @@
       <c r="N185" s="88">
         <v>46238</v>
       </c>
-    </row>
-    <row r="186" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O185" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P185" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q185" s="19"/>
+    </row>
+    <row r="186" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A186" s="25" t="s">
         <v>239</v>
       </c>
@@ -9925,8 +11234,15 @@
       <c r="N186" s="88">
         <v>46238</v>
       </c>
-    </row>
-    <row r="187" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O186" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P186" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q186" s="19"/>
+    </row>
+    <row r="187" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A187" s="25" t="s">
         <v>241</v>
       </c>
@@ -9969,8 +11285,15 @@
       <c r="N187" s="88">
         <v>46238</v>
       </c>
-    </row>
-    <row r="188" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O187" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P187" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q187" s="19"/>
+    </row>
+    <row r="188" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A188" s="25" t="s">
         <v>243</v>
       </c>
@@ -10013,8 +11336,15 @@
       <c r="N188" s="88">
         <v>46238</v>
       </c>
-    </row>
-    <row r="189" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O188" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P188" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q188" s="19"/>
+    </row>
+    <row r="189" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A189" s="25" t="s">
         <v>245</v>
       </c>
@@ -10057,8 +11387,15 @@
       <c r="N189" s="88">
         <v>46238</v>
       </c>
-    </row>
-    <row r="190" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O189" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P189" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q189" s="19"/>
+    </row>
+    <row r="190" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A190" s="25" t="s">
         <v>247</v>
       </c>
@@ -10101,8 +11438,15 @@
       <c r="N190" s="88">
         <v>46238</v>
       </c>
-    </row>
-    <row r="191" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O190" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P190" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q190" s="19"/>
+    </row>
+    <row r="191" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A191" s="25" t="s">
         <v>249</v>
       </c>
@@ -10145,8 +11489,15 @@
       <c r="N191" s="88">
         <v>46238</v>
       </c>
-    </row>
-    <row r="192" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O191" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P191" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q191" s="19"/>
+    </row>
+    <row r="192" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>251</v>
       </c>
@@ -10189,8 +11540,15 @@
       <c r="N192" s="88">
         <v>46163</v>
       </c>
-    </row>
-    <row r="193" spans="1:14" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="O192" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P192" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q192" s="19"/>
+    </row>
+    <row r="193" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>254</v>
       </c>
@@ -10233,6 +11591,13 @@
       <c r="N193" s="88">
         <v>46163</v>
       </c>
+      <c r="O193" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P193" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q193" s="19"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N193">
@@ -20055,34 +21420,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="98" t="s">
         <v>303</v>
       </c>
-      <c r="B1" s="94" t="s">
+      <c r="B1" s="98" t="s">
         <v>304</v>
       </c>
-      <c r="C1" s="94" t="s">
+      <c r="C1" s="98" t="s">
         <v>305</v>
       </c>
-      <c r="D1" s="95" t="s">
+      <c r="D1" s="99" t="s">
         <v>306</v>
       </c>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99" t="s">
         <v>307</v>
       </c>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
       <c r="J1" s="19"/>
       <c r="K1" s="67" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A2" s="94"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
       <c r="D2" s="18" t="s">
         <v>308</v>
       </c>
@@ -21215,1090 +22580,1090 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="94" t="s">
         <v>321</v>
       </c>
-      <c r="B1" s="98" t="s">
+      <c r="B1" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="99" t="s">
+      <c r="C1" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="98" t="s">
+      <c r="D1" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="97" t="s">
+      <c r="E1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="F1" s="97" t="s">
+      <c r="F1" s="1" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A2" s="96">
+      <c r="A2" s="3">
         <v>22</v>
       </c>
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C2" s="96">
+      <c r="C2" s="3">
         <v>67573323</v>
       </c>
-      <c r="D2" s="96">
+      <c r="D2" s="3">
         <v>19375.900000000001</v>
       </c>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3">
         <f t="shared" ref="F2:F34" si="0">E2-D2</f>
         <v>-19375.900000000001</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A3" s="96">
+      <c r="A3" s="3">
         <v>44</v>
       </c>
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C3" s="96">
+      <c r="C3" s="3">
         <v>67021362</v>
       </c>
-      <c r="D3" s="96">
+      <c r="D3" s="3">
         <v>56032.6</v>
       </c>
-      <c r="E3" s="96"/>
-      <c r="F3" s="96">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3">
         <f t="shared" si="0"/>
         <v>-56032.6</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A4" s="96">
+      <c r="A4" s="3">
         <v>53</v>
       </c>
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C4" s="96">
+      <c r="C4" s="3">
         <v>67573216</v>
       </c>
-      <c r="D4" s="96">
+      <c r="D4" s="3">
         <v>17968.5</v>
       </c>
-      <c r="E4" s="96">
+      <c r="E4" s="3">
         <v>18120.900000000001</v>
       </c>
-      <c r="F4" s="96">
+      <c r="F4" s="3">
         <f t="shared" si="0"/>
         <v>152.40000000000146</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A5" s="100">
+      <c r="A5" s="96">
         <v>58</v>
       </c>
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C5" s="100">
+      <c r="C5" s="96">
         <v>42607693</v>
       </c>
-      <c r="D5" s="100">
+      <c r="D5" s="96">
         <v>59659</v>
       </c>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
         <f t="shared" si="0"/>
         <v>-59659</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A6" s="100">
+      <c r="A6" s="96">
         <v>60</v>
       </c>
-      <c r="B6" s="96" t="s">
+      <c r="B6" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C6" s="100">
+      <c r="C6" s="96">
         <v>42607645</v>
       </c>
-      <c r="D6" s="100">
+      <c r="D6" s="96">
         <v>97390</v>
       </c>
-      <c r="E6" s="96"/>
-      <c r="F6" s="96">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3">
         <f t="shared" si="0"/>
         <v>-97390</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A7" s="100">
+      <c r="A7" s="96">
         <v>61</v>
       </c>
-      <c r="B7" s="96" t="s">
+      <c r="B7" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="100">
+      <c r="C7" s="96">
         <v>42607493</v>
       </c>
-      <c r="D7" s="100">
+      <c r="D7" s="96">
         <v>23184</v>
       </c>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3">
         <f t="shared" si="0"/>
         <v>-23184</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A8" s="100">
+      <c r="A8" s="96">
         <v>62</v>
       </c>
-      <c r="B8" s="96" t="s">
+      <c r="B8" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C8" s="100">
+      <c r="C8" s="96">
         <v>42607616</v>
       </c>
-      <c r="D8" s="100">
+      <c r="D8" s="96">
         <v>7889</v>
       </c>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96">
+      <c r="E8" s="3"/>
+      <c r="F8" s="3">
         <f t="shared" si="0"/>
         <v>-7889</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A9" s="100">
+      <c r="A9" s="96">
         <v>63</v>
       </c>
-      <c r="B9" s="96" t="s">
+      <c r="B9" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C9" s="100">
+      <c r="C9" s="96">
         <v>42607457</v>
       </c>
-      <c r="D9" s="100">
+      <c r="D9" s="96">
         <v>27096</v>
       </c>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96">
+      <c r="E9" s="3"/>
+      <c r="F9" s="3">
         <f t="shared" si="0"/>
         <v>-27096</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A10" s="100">
+      <c r="A10" s="96">
         <v>64</v>
       </c>
-      <c r="B10" s="96" t="s">
+      <c r="B10" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C10" s="100">
+      <c r="C10" s="96">
         <v>42607809</v>
       </c>
-      <c r="D10" s="100">
+      <c r="D10" s="96">
         <v>15280</v>
       </c>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96">
+      <c r="E10" s="3"/>
+      <c r="F10" s="3">
         <f t="shared" si="0"/>
         <v>-15280</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A11" s="100">
+      <c r="A11" s="96">
         <v>65</v>
       </c>
-      <c r="B11" s="96" t="s">
+      <c r="B11" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C11" s="100">
+      <c r="C11" s="96">
         <v>42607653</v>
       </c>
-      <c r="D11" s="100">
+      <c r="D11" s="96">
         <v>20310</v>
       </c>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96">
+      <c r="E11" s="3"/>
+      <c r="F11" s="3">
         <f t="shared" si="0"/>
         <v>-20310</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A12" s="100">
+      <c r="A12" s="96">
         <v>66</v>
       </c>
-      <c r="B12" s="96" t="s">
+      <c r="B12" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C12" s="100">
+      <c r="C12" s="96">
         <v>42607631</v>
       </c>
-      <c r="D12" s="100">
+      <c r="D12" s="96">
         <v>24100</v>
       </c>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96">
+      <c r="E12" s="3"/>
+      <c r="F12" s="3">
         <f t="shared" si="0"/>
         <v>-24100</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A13" s="100">
+      <c r="A13" s="96">
         <v>67</v>
       </c>
-      <c r="B13" s="96" t="s">
+      <c r="B13" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C13" s="100">
+      <c r="C13" s="96">
         <v>46886910</v>
       </c>
-      <c r="D13" s="100">
+      <c r="D13" s="96">
         <v>172161.6</v>
       </c>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96">
+      <c r="E13" s="3"/>
+      <c r="F13" s="3">
         <f t="shared" si="0"/>
         <v>-172161.6</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A14" s="100">
+      <c r="A14" s="96">
         <v>68</v>
       </c>
-      <c r="B14" s="96" t="s">
+      <c r="B14" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C14" s="100">
+      <c r="C14" s="96">
         <v>42607609</v>
       </c>
-      <c r="D14" s="100">
+      <c r="D14" s="96">
         <v>11718</v>
       </c>
-      <c r="E14" s="96">
+      <c r="E14" s="3">
         <v>11718</v>
       </c>
-      <c r="F14" s="96">
+      <c r="F14" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A15" s="100">
+      <c r="A15" s="96">
         <v>69</v>
       </c>
-      <c r="B15" s="96" t="s">
+      <c r="B15" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C15" s="100">
+      <c r="C15" s="96">
         <v>47512547</v>
       </c>
-      <c r="D15" s="100">
+      <c r="D15" s="96">
         <v>38143</v>
       </c>
-      <c r="E15" s="96">
+      <c r="E15" s="3">
         <v>38145</v>
       </c>
-      <c r="F15" s="96">
+      <c r="F15" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A16" s="100">
+      <c r="A16" s="96">
         <v>70</v>
       </c>
-      <c r="B16" s="96" t="s">
+      <c r="B16" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C16" s="100">
+      <c r="C16" s="96">
         <v>47511635</v>
       </c>
-      <c r="D16" s="100">
+      <c r="D16" s="96">
         <v>35381.199999999997</v>
       </c>
-      <c r="E16" s="96">
+      <c r="E16" s="3">
         <v>35381.199999999997</v>
       </c>
-      <c r="F16" s="96">
+      <c r="F16" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A17" s="100">
+      <c r="A17" s="96">
         <v>71</v>
       </c>
-      <c r="B17" s="96" t="s">
+      <c r="B17" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C17" s="100">
+      <c r="C17" s="96">
         <v>4260700</v>
       </c>
-      <c r="D17" s="100">
+      <c r="D17" s="96">
         <v>179707</v>
       </c>
-      <c r="E17" s="96">
+      <c r="E17" s="3">
         <v>179707</v>
       </c>
-      <c r="F17" s="96">
+      <c r="F17" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A18" s="100">
+      <c r="A18" s="96">
         <v>72</v>
       </c>
-      <c r="B18" s="96" t="s">
+      <c r="B18" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C18" s="100">
+      <c r="C18" s="96">
         <v>46886909</v>
       </c>
-      <c r="D18" s="100">
+      <c r="D18" s="96">
         <v>103115.8</v>
       </c>
-      <c r="E18" s="96">
+      <c r="E18" s="3">
         <v>103121.8</v>
       </c>
-      <c r="F18" s="96">
+      <c r="F18" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A19" s="100">
+      <c r="A19" s="96">
         <v>73</v>
       </c>
-      <c r="B19" s="96" t="s">
+      <c r="B19" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C19" s="100">
+      <c r="C19" s="96">
         <v>47369448</v>
       </c>
-      <c r="D19" s="100" t="s">
+      <c r="D19" s="96" t="s">
         <v>393</v>
       </c>
-      <c r="E19" s="96"/>
-      <c r="F19" s="96" t="e">
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A20" s="100">
+      <c r="A20" s="96">
         <v>74</v>
       </c>
-      <c r="B20" s="96" t="s">
+      <c r="B20" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C20" s="100">
+      <c r="C20" s="96">
         <v>47511330</v>
       </c>
-      <c r="D20" s="100">
+      <c r="D20" s="96">
         <v>72558.399999999994</v>
       </c>
-      <c r="E20" s="96">
+      <c r="E20" s="3">
         <v>72558.399999999994</v>
       </c>
-      <c r="F20" s="96">
+      <c r="F20" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A21" s="100">
+      <c r="A21" s="96">
         <v>75</v>
       </c>
-      <c r="B21" s="96" t="s">
+      <c r="B21" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C21" s="100">
+      <c r="C21" s="96">
         <v>42607467</v>
       </c>
-      <c r="D21" s="100">
+      <c r="D21" s="96">
         <v>12607</v>
       </c>
-      <c r="E21" s="96">
+      <c r="E21" s="3">
         <v>12608</v>
       </c>
-      <c r="F21" s="96">
+      <c r="F21" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A22" s="100">
+      <c r="A22" s="96">
         <v>82</v>
       </c>
-      <c r="B22" s="96"/>
-      <c r="C22" s="100">
+      <c r="B22" s="3"/>
+      <c r="C22" s="96">
         <v>91733392</v>
       </c>
-      <c r="D22" s="100" t="s">
+      <c r="D22" s="96" t="s">
         <v>393</v>
       </c>
-      <c r="E22" s="96">
+      <c r="E22" s="3">
         <v>274.60000000000002</v>
       </c>
-      <c r="F22" s="96" t="e">
+      <c r="F22" s="3" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A23" s="100">
+      <c r="A23" s="96">
         <v>87</v>
       </c>
-      <c r="B23" s="96" t="s">
+      <c r="B23" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C23" s="100">
+      <c r="C23" s="96">
         <v>67021344</v>
       </c>
-      <c r="D23" s="100">
+      <c r="D23" s="96">
         <v>30522</v>
       </c>
-      <c r="E23" s="96"/>
-      <c r="F23" s="96">
+      <c r="E23" s="3"/>
+      <c r="F23" s="3">
         <f t="shared" si="0"/>
         <v>-30522</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A24" s="100">
+      <c r="A24" s="96">
         <v>88</v>
       </c>
-      <c r="B24" s="96" t="s">
+      <c r="B24" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C24" s="100">
+      <c r="C24" s="96">
         <v>67021354</v>
       </c>
-      <c r="D24" s="100">
+      <c r="D24" s="96">
         <v>42174</v>
       </c>
-      <c r="E24" s="96"/>
-      <c r="F24" s="96">
+      <c r="E24" s="3"/>
+      <c r="F24" s="3">
         <f t="shared" si="0"/>
         <v>-42174</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A25" s="100">
+      <c r="A25" s="96">
         <v>89</v>
       </c>
-      <c r="B25" s="96" t="s">
+      <c r="B25" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C25" s="100">
+      <c r="C25" s="96">
         <v>91546861</v>
       </c>
-      <c r="D25" s="100">
-        <v>0</v>
-      </c>
-      <c r="E25" s="96">
+      <c r="D25" s="96">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
         <v>101.9</v>
       </c>
-      <c r="F25" s="96">
+      <c r="F25" s="3">
         <f t="shared" si="0"/>
         <v>101.9</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A26" s="100">
+      <c r="A26" s="96">
         <v>90</v>
       </c>
-      <c r="B26" s="96" t="s">
+      <c r="B26" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C26" s="100">
+      <c r="C26" s="96">
         <v>66599353</v>
       </c>
-      <c r="D26" s="100">
-        <v>0</v>
-      </c>
-      <c r="E26" s="96"/>
-      <c r="F26" s="96">
+      <c r="D26" s="96">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A27" s="100">
+      <c r="A27" s="96">
         <v>91</v>
       </c>
-      <c r="B27" s="96" t="s">
+      <c r="B27" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C27" s="100">
+      <c r="C27" s="96">
         <v>87778411</v>
       </c>
-      <c r="D27" s="100">
-        <v>0</v>
-      </c>
-      <c r="E27" s="96">
+      <c r="D27" s="96">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>54.7</v>
       </c>
-      <c r="F27" s="96">
+      <c r="F27" s="3">
         <f t="shared" si="0"/>
         <v>54.7</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A28" s="100">
+      <c r="A28" s="96">
         <v>92</v>
       </c>
-      <c r="B28" s="96" t="s">
+      <c r="B28" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C28" s="100">
+      <c r="C28" s="96">
         <v>67573171</v>
       </c>
-      <c r="D28" s="100">
+      <c r="D28" s="96">
         <v>55276.2</v>
       </c>
-      <c r="E28" s="96">
+      <c r="E28" s="3">
         <v>55295.6</v>
       </c>
-      <c r="F28" s="96">
+      <c r="F28" s="3">
         <f t="shared" si="0"/>
         <v>19.400000000001455</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A29" s="96">
+      <c r="A29" s="3">
         <v>93</v>
       </c>
-      <c r="B29" s="96" t="s">
+      <c r="B29" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C29" s="96">
+      <c r="C29" s="3">
         <v>90007553</v>
       </c>
-      <c r="D29" s="96">
+      <c r="D29" s="3">
         <v>1076.4000000000001</v>
       </c>
-      <c r="E29" s="96">
+      <c r="E29" s="3">
         <v>1234.5</v>
       </c>
-      <c r="F29" s="96">
+      <c r="F29" s="3">
         <f t="shared" si="0"/>
         <v>158.09999999999991</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A30" s="100">
+      <c r="A30" s="96">
         <v>94</v>
       </c>
-      <c r="B30" s="96" t="s">
+      <c r="B30" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C30" s="100">
+      <c r="C30" s="96">
         <v>67573207</v>
       </c>
-      <c r="D30" s="100">
+      <c r="D30" s="96">
         <v>26813.1</v>
       </c>
-      <c r="E30" s="96">
+      <c r="E30" s="3">
         <v>26832.799999999999</v>
       </c>
-      <c r="F30" s="96">
+      <c r="F30" s="3">
         <f t="shared" si="0"/>
         <v>19.700000000000728</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A31" s="96">
+      <c r="A31" s="3">
         <v>95</v>
       </c>
-      <c r="B31" s="96" t="s">
+      <c r="B31" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C31" s="96">
+      <c r="C31" s="3">
         <v>42607759</v>
       </c>
-      <c r="D31" s="96">
+      <c r="D31" s="3">
         <v>26313</v>
       </c>
-      <c r="E31" s="96">
+      <c r="E31" s="3">
         <v>139657</v>
       </c>
-      <c r="F31" s="96">
+      <c r="F31" s="3">
         <f t="shared" si="0"/>
         <v>113344</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A32" s="100">
+      <c r="A32" s="96">
         <v>96</v>
       </c>
-      <c r="B32" s="96" t="s">
+      <c r="B32" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C32" s="100">
+      <c r="C32" s="96">
         <v>67573298</v>
       </c>
-      <c r="D32" s="100">
+      <c r="D32" s="96">
         <v>16956.2</v>
       </c>
-      <c r="E32" s="96">
+      <c r="E32" s="3">
         <v>16978.099999999999</v>
       </c>
-      <c r="F32" s="96">
+      <c r="F32" s="3">
         <f t="shared" si="0"/>
         <v>21.899999999997817</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A33" s="96">
+      <c r="A33" s="3">
         <v>97</v>
       </c>
-      <c r="B33" s="96" t="s">
+      <c r="B33" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C33" s="96">
+      <c r="C33" s="3">
         <v>67573203</v>
       </c>
-      <c r="D33" s="96">
+      <c r="D33" s="3">
         <v>36948.800000000003</v>
       </c>
-      <c r="E33" s="96" t="s">
+      <c r="E33" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="F33" s="96" t="e">
+      <c r="F33" s="3" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A34" s="100">
+      <c r="A34" s="96">
         <v>98</v>
       </c>
-      <c r="B34" s="96" t="s">
+      <c r="B34" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C34" s="100">
+      <c r="C34" s="96">
         <v>67573191</v>
       </c>
-      <c r="D34" s="100">
+      <c r="D34" s="96">
         <v>43330.5</v>
       </c>
-      <c r="E34" s="96"/>
-      <c r="F34" s="96">
+      <c r="E34" s="3"/>
+      <c r="F34" s="3">
         <f t="shared" si="0"/>
         <v>-43330.5</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A35" s="96">
+      <c r="A35" s="3">
         <v>99</v>
       </c>
-      <c r="B35" s="96" t="s">
+      <c r="B35" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C35" s="96">
+      <c r="C35" s="3">
         <v>67572944</v>
       </c>
-      <c r="D35" s="96">
+      <c r="D35" s="3">
         <v>21735.7</v>
       </c>
-      <c r="E35" s="96">
+      <c r="E35" s="3">
         <v>21789.1</v>
       </c>
-      <c r="F35" s="96">
+      <c r="F35" s="3">
         <f t="shared" ref="F35:F54" si="1">E35-D35</f>
         <v>53.399999999997817</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A36" s="100">
+      <c r="A36" s="96">
         <v>100</v>
       </c>
-      <c r="B36" s="96" t="s">
+      <c r="B36" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C36" s="100">
+      <c r="C36" s="96">
         <v>67573201</v>
       </c>
-      <c r="D36" s="100">
+      <c r="D36" s="96">
         <v>28815.3</v>
       </c>
-      <c r="E36" s="96"/>
-      <c r="F36" s="96">
+      <c r="E36" s="3"/>
+      <c r="F36" s="3">
         <f t="shared" si="1"/>
         <v>-28815.3</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A37" s="96">
+      <c r="A37" s="3">
         <v>101</v>
       </c>
-      <c r="B37" s="96" t="s">
+      <c r="B37" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C37" s="96">
+      <c r="C37" s="3">
         <v>67021339</v>
       </c>
-      <c r="D37" s="96">
+      <c r="D37" s="3">
         <v>30210.7</v>
       </c>
-      <c r="E37" s="96">
+      <c r="E37" s="3">
         <v>30259.5</v>
       </c>
-      <c r="F37" s="96">
+      <c r="F37" s="3">
         <f t="shared" si="1"/>
         <v>48.799999999999272</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A38" s="100">
+      <c r="A38" s="96">
         <v>102</v>
       </c>
-      <c r="B38" s="96" t="s">
+      <c r="B38" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C38" s="100">
+      <c r="C38" s="96">
         <v>90008040</v>
       </c>
-      <c r="D38" s="100">
+      <c r="D38" s="96">
         <v>1849.3</v>
       </c>
-      <c r="E38" s="96">
+      <c r="E38" s="3">
         <v>1881.8</v>
       </c>
-      <c r="F38" s="96">
+      <c r="F38" s="3">
         <f t="shared" si="1"/>
         <v>32.5</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A39" s="96">
+      <c r="A39" s="3">
         <v>103</v>
       </c>
-      <c r="B39" s="96" t="s">
+      <c r="B39" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C39" s="96">
+      <c r="C39" s="3">
         <v>46886935</v>
       </c>
-      <c r="D39" s="96">
+      <c r="D39" s="3">
         <v>82275</v>
       </c>
-      <c r="E39" s="96">
+      <c r="E39" s="3">
         <v>82330</v>
       </c>
-      <c r="F39" s="96">
+      <c r="F39" s="3">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A40" s="96">
+      <c r="A40" s="3">
         <v>105</v>
       </c>
-      <c r="B40" s="96" t="s">
+      <c r="B40" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C40" s="96">
+      <c r="C40" s="3">
         <v>67572955</v>
       </c>
-      <c r="D40" s="96">
+      <c r="D40" s="3">
         <v>28976.3</v>
       </c>
-      <c r="E40" s="96">
+      <c r="E40" s="3">
         <v>29012.7</v>
       </c>
-      <c r="F40" s="96">
+      <c r="F40" s="3">
         <f t="shared" si="1"/>
         <v>36.400000000001455</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A41" s="96">
+      <c r="A41" s="3">
         <v>107</v>
       </c>
-      <c r="B41" s="96" t="s">
+      <c r="B41" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C41" s="96">
+      <c r="C41" s="3">
         <v>42607429</v>
       </c>
-      <c r="D41" s="96">
+      <c r="D41" s="3">
         <v>19376</v>
       </c>
-      <c r="E41" s="96"/>
-      <c r="F41" s="96">
+      <c r="E41" s="3"/>
+      <c r="F41" s="3">
         <f t="shared" si="1"/>
         <v>-19376</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A42" s="96">
+      <c r="A42" s="3">
         <v>109</v>
       </c>
-      <c r="B42" s="96" t="s">
+      <c r="B42" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C42" s="96">
+      <c r="C42" s="3">
         <v>67021338</v>
       </c>
-      <c r="D42" s="96">
+      <c r="D42" s="3">
         <v>29281.599999999999</v>
       </c>
-      <c r="E42" s="96">
+      <c r="E42" s="3">
         <v>29406.1</v>
       </c>
-      <c r="F42" s="96">
+      <c r="F42" s="3">
         <f t="shared" si="1"/>
         <v>124.5</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A43" s="96">
+      <c r="A43" s="3">
         <v>111</v>
       </c>
-      <c r="B43" s="96" t="s">
+      <c r="B43" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C43" s="96">
+      <c r="C43" s="3">
         <v>42607771</v>
       </c>
-      <c r="D43" s="96">
+      <c r="D43" s="3">
         <v>5509</v>
       </c>
-      <c r="E43" s="96">
+      <c r="E43" s="3">
         <v>5516</v>
       </c>
-      <c r="F43" s="96">
+      <c r="F43" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A44" s="96">
+      <c r="A44" s="3">
         <v>113</v>
       </c>
-      <c r="B44" s="96" t="s">
+      <c r="B44" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C44" s="96">
+      <c r="C44" s="3">
         <v>67573205</v>
       </c>
-      <c r="D44" s="96">
+      <c r="D44" s="3">
         <v>38016.9</v>
       </c>
-      <c r="E44" s="96">
+      <c r="E44" s="3">
         <v>38086</v>
       </c>
-      <c r="F44" s="96">
+      <c r="F44" s="3">
         <f t="shared" si="1"/>
         <v>69.099999999998545</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A45" s="96">
+      <c r="A45" s="3">
         <v>115</v>
       </c>
-      <c r="B45" s="96" t="s">
+      <c r="B45" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C45" s="96">
+      <c r="C45" s="3">
         <v>67573265</v>
       </c>
-      <c r="D45" s="96">
+      <c r="D45" s="3">
         <v>71144.2</v>
       </c>
-      <c r="E45" s="96">
+      <c r="E45" s="3">
         <v>71214.8</v>
       </c>
-      <c r="F45" s="96">
+      <c r="F45" s="3">
         <f t="shared" si="1"/>
         <v>70.600000000005821</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A46" s="96">
+      <c r="A46" s="3">
         <v>117</v>
       </c>
-      <c r="B46" s="96" t="s">
+      <c r="B46" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C46" s="96">
+      <c r="C46" s="3">
         <v>66599401</v>
       </c>
-      <c r="D46" s="96">
+      <c r="D46" s="3">
         <v>63803.5</v>
       </c>
-      <c r="E46" s="96">
+      <c r="E46" s="3">
         <v>63860.4</v>
       </c>
-      <c r="F46" s="96">
+      <c r="F46" s="3">
         <f t="shared" si="1"/>
         <v>56.900000000001455</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A47" s="96">
+      <c r="A47" s="3">
         <v>119</v>
       </c>
-      <c r="B47" s="96" t="s">
+      <c r="B47" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C47" s="96">
+      <c r="C47" s="3">
         <v>67573188</v>
       </c>
-      <c r="D47" s="96">
+      <c r="D47" s="3">
         <v>29124.2</v>
       </c>
-      <c r="E47" s="96">
+      <c r="E47" s="3">
         <v>29208.6</v>
       </c>
-      <c r="F47" s="96">
+      <c r="F47" s="3">
         <f t="shared" si="1"/>
         <v>84.399999999997817</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A48" s="96">
+      <c r="A48" s="3">
         <v>121</v>
       </c>
-      <c r="B48" s="96" t="s">
+      <c r="B48" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C48" s="96">
+      <c r="C48" s="3">
         <v>84039773</v>
       </c>
-      <c r="D48" s="96">
+      <c r="D48" s="3">
         <v>9600.1</v>
       </c>
-      <c r="E48" s="96">
+      <c r="E48" s="3">
         <v>9668.1</v>
       </c>
-      <c r="F48" s="96">
+      <c r="F48" s="3">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A49" s="96">
+      <c r="A49" s="3">
         <v>123</v>
       </c>
-      <c r="B49" s="96" t="s">
+      <c r="B49" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C49" s="96">
+      <c r="C49" s="3">
         <v>67573376</v>
       </c>
-      <c r="D49" s="96">
+      <c r="D49" s="3">
         <v>89289.8</v>
       </c>
-      <c r="E49" s="96">
+      <c r="E49" s="3">
         <v>89352.7</v>
       </c>
-      <c r="F49" s="96">
+      <c r="F49" s="3">
         <f t="shared" si="1"/>
         <v>62.899999999994179</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A50" s="96">
+      <c r="A50" s="3">
         <v>125</v>
       </c>
-      <c r="B50" s="96" t="s">
+      <c r="B50" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C50" s="96">
+      <c r="C50" s="3">
         <v>67573196</v>
       </c>
-      <c r="D50" s="96">
+      <c r="D50" s="3">
         <v>89182.7</v>
       </c>
-      <c r="E50" s="96">
+      <c r="E50" s="3">
         <v>89225.2</v>
       </c>
-      <c r="F50" s="96">
+      <c r="F50" s="3">
         <f t="shared" si="1"/>
         <v>42.5</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A51" s="96">
+      <c r="A51" s="3">
         <v>127</v>
       </c>
-      <c r="B51" s="96" t="s">
+      <c r="B51" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C51" s="96">
+      <c r="C51" s="3">
         <v>67573307</v>
       </c>
-      <c r="D51" s="96">
+      <c r="D51" s="3">
         <v>25290.799999999999</v>
       </c>
-      <c r="E51" s="96">
+      <c r="E51" s="3">
         <v>25372.1</v>
       </c>
-      <c r="F51" s="96">
+      <c r="F51" s="3">
         <f t="shared" si="1"/>
         <v>81.299999999999272</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A52" s="96">
+      <c r="A52" s="3">
         <v>163</v>
       </c>
-      <c r="B52" s="96" t="s">
+      <c r="B52" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C52" s="96">
+      <c r="C52" s="3">
         <v>70694930</v>
       </c>
-      <c r="D52" s="96">
+      <c r="D52" s="3">
         <v>35892.800000000003</v>
       </c>
-      <c r="E52" s="96"/>
-      <c r="F52" s="96">
+      <c r="E52" s="3"/>
+      <c r="F52" s="3">
         <f t="shared" si="1"/>
         <v>-35892.800000000003</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A53" s="96">
+      <c r="A53" s="3">
         <v>186</v>
       </c>
-      <c r="B53" s="101"/>
-      <c r="C53" s="96">
+      <c r="B53" s="97"/>
+      <c r="C53" s="3">
         <v>91546036</v>
       </c>
-      <c r="D53" s="96" t="s">
+      <c r="D53" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="E53" s="96">
+      <c r="E53" s="3">
         <v>488.5</v>
       </c>
-      <c r="F53" s="96" t="e">
+      <c r="F53" s="3" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A54" s="96">
+      <c r="A54" s="3">
         <v>179</v>
       </c>
-      <c r="B54" s="101"/>
-      <c r="C54" s="96">
+      <c r="B54" s="97"/>
+      <c r="C54" s="3">
         <v>91546509</v>
       </c>
-      <c r="D54" s="101" t="s">
+      <c r="D54" s="97" t="s">
         <v>393</v>
       </c>
-      <c r="E54" s="96">
+      <c r="E54" s="3">
         <v>649.9</v>
       </c>
-      <c r="F54" s="96" t="e">
+      <c r="F54" s="3" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -22337,19 +23702,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="98" t="s">
         <v>325</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
     </row>
     <row r="2" spans="1:11" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -23082,16 +24447,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="98" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2148" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AAA1884-9E91-478E-9800-06D5D126536A}"/>
+  <xr:revisionPtr revIDLastSave="2159" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C542235-3299-4716-A8F3-4093F730D3CB}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Water meters " sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Elec Meters'!$A$1:$Q$192</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Water meters '!$A$1:$N$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Water meters '!$A$1:$Q$193</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1597,7 +1597,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1892,17 +1892,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2338,7 +2335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q193"/>
+  <dimension ref="A1:Q204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
@@ -2349,9 +2346,9 @@
     <col min="10" max="10" width="27.3984375" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="20.19921875" customWidth="1"/>
     <col min="14" max="14" width="35.53125" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" customWidth="1"/>
-    <col min="16" max="16" width="17.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.1328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.06640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.9296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18" x14ac:dyDescent="0.3">
@@ -2397,13 +2394,13 @@
       <c r="N1" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="O1" s="100" t="s">
+      <c r="O1" s="98" t="s">
         <v>394</v>
       </c>
-      <c r="P1" s="100" t="s">
+      <c r="P1" s="98" t="s">
         <v>395</v>
       </c>
-      <c r="Q1" s="101" t="s">
+      <c r="Q1" s="1" t="s">
         <v>396</v>
       </c>
     </row>
@@ -7556,7 +7553,9 @@
       <c r="P106" s="23" t="b">
         <v>1</v>
       </c>
-      <c r="Q106" s="19"/>
+      <c r="Q106" s="78">
+        <v>46206</v>
+      </c>
     </row>
     <row r="107" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A107" s="25" t="s">
@@ -7748,7 +7747,9 @@
       <c r="P110" s="23" t="b">
         <v>1</v>
       </c>
-      <c r="Q110" s="19"/>
+      <c r="Q110" s="78">
+        <v>46206</v>
+      </c>
     </row>
     <row r="111" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A111" s="25" t="s">
@@ -8516,7 +8517,9 @@
       <c r="P126" s="23" t="b">
         <v>1</v>
       </c>
-      <c r="Q126" s="19"/>
+      <c r="Q126" s="78">
+        <v>46206</v>
+      </c>
     </row>
     <row r="127" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A127" s="25" t="s">
@@ -11598,6 +11601,11 @@
         <v>0</v>
       </c>
       <c r="Q193" s="19"/>
+    </row>
+    <row r="204" spans="1:17" ht="18" x14ac:dyDescent="0.3">
+      <c r="Q204" s="78">
+        <v>46206</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N193">
@@ -21420,34 +21428,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="99" t="s">
         <v>303</v>
       </c>
-      <c r="B1" s="98" t="s">
+      <c r="B1" s="99" t="s">
         <v>304</v>
       </c>
-      <c r="C1" s="98" t="s">
+      <c r="C1" s="99" t="s">
         <v>305</v>
       </c>
-      <c r="D1" s="99" t="s">
+      <c r="D1" s="100" t="s">
         <v>306</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99" t="s">
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100" t="s">
         <v>307</v>
       </c>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
       <c r="J1" s="19"/>
       <c r="K1" s="67" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A2" s="98"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
+      <c r="A2" s="99"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
       <c r="D2" s="18" t="s">
         <v>308</v>
       </c>
@@ -23702,19 +23710,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="99" t="s">
         <v>325</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
     </row>
     <row r="2" spans="1:11" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -24447,16 +24455,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="99" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2235" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F09BE78-4057-413F-ABEA-F21BBAD87E41}"/>
+  <xr:revisionPtr revIDLastSave="2246" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF516590-4E44-4B9A-9CEB-F6D696FF7B22}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="-1530" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FS Elec" sheetId="4" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4966" uniqueCount="1190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4967" uniqueCount="1192">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -3617,6 +3617,12 @@
   </si>
   <si>
     <t>MS3</t>
+  </si>
+  <si>
+    <t>9993247</t>
+  </si>
+  <si>
+    <t>10192047</t>
   </si>
 </sst>
 </file>
@@ -19628,8 +19634,8 @@
       <c r="B97" s="79" t="s">
         <v>119</v>
       </c>
-      <c r="C97" s="73">
-        <v>10172132</v>
+      <c r="C97" s="73" t="s">
+        <v>1190</v>
       </c>
       <c r="D97" s="73" t="s">
         <v>11</v>
@@ -19668,9 +19674,11 @@
         <v>1</v>
       </c>
       <c r="P97" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="Q97" s="78">
+        <v>46216</v>
+      </c>
     </row>
     <row r="98" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A98" s="25" t="s">
@@ -19692,7 +19700,7 @@
         <v>369</v>
       </c>
       <c r="G98" s="3">
-        <v>9.9000000000000005E-2</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="H98" s="78">
         <v>46168</v>
@@ -19986,7 +19994,7 @@
         <v>127</v>
       </c>
       <c r="C104" s="73" t="s">
-        <v>143</v>
+        <v>1191</v>
       </c>
       <c r="D104" s="73" t="s">
         <v>11</v>
@@ -19998,7 +20006,7 @@
         <v>369</v>
       </c>
       <c r="G104" s="3">
-        <v>7.2999999999999995E-2</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="H104" s="78">
         <v>46168</v>
@@ -20025,9 +20033,11 @@
         <v>1</v>
       </c>
       <c r="P104" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="Q104" s="78">
+        <v>46216</v>
+      </c>
     </row>
     <row r="105" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A105" s="25" t="s">
@@ -24614,7 +24624,7 @@
         <v>690</v>
       </c>
       <c r="C21" s="100">
-        <v>87818204</v>
+        <v>87819204</v>
       </c>
       <c r="D21" s="103">
         <v>87818877</v>
@@ -27954,7 +27964,7 @@
         <v>846</v>
       </c>
       <c r="C188" s="100">
-        <v>90008072</v>
+        <v>90008082</v>
       </c>
       <c r="D188" s="101">
         <v>83013891</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2356" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9A5DA56-4CD4-46C6-AAD7-235815223520}"/>
+  <xr:revisionPtr revIDLastSave="2357" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4F478B0-D9EA-4E2A-BD15-2B5C94F123DB}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-2565" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19937,7 +19937,7 @@
         <v>46168</v>
       </c>
       <c r="O95" s="21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P95" s="21" t="b">
         <v>0</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2357" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4F478B0-D9EA-4E2A-BD15-2B5C94F123DB}"/>
+  <xr:revisionPtr revIDLastSave="2367" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B61E1940-154F-4124-BDB1-4868691471E2}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-2565" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="-2565" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FS Elec" sheetId="4" r:id="rId1"/>
@@ -4248,7 +4248,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="37" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4725,14 +4725,20 @@
     <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4957,10 +4963,6 @@
     </a>
   </bag>
 </FeaturePropertyBags>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15236,7 +15238,7 @@
       <c r="L192" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="M192" s="160"/>
+      <c r="M192" s="158"/>
       <c r="N192" s="64" t="s">
         <v>173</v>
       </c>
@@ -18209,7 +18211,7 @@
       <c r="Q61" s="17"/>
     </row>
     <row r="62" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
-      <c r="A62" s="23" t="s">
+      <c r="A62" s="162" t="s">
         <v>102</v>
       </c>
       <c r="B62" s="60" t="s">
@@ -19537,14 +19539,14 @@
       <c r="Q87" s="17"/>
     </row>
     <row r="88" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
-      <c r="A88" s="23" t="s">
+      <c r="A88" s="162" t="s">
         <v>136</v>
       </c>
       <c r="B88" s="58" t="s">
         <v>137</v>
       </c>
       <c r="C88" s="53" t="s">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="D88" s="53" t="s">
         <v>283</v>
@@ -24245,14 +24247,14 @@
       <c r="Q187" s="17"/>
     </row>
     <row r="188" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
-      <c r="A188" s="23" t="s">
+      <c r="A188" s="161" t="s">
         <v>265</v>
       </c>
       <c r="B188" s="59" t="s">
         <v>121</v>
       </c>
       <c r="C188" s="53" t="s">
-        <v>356</v>
+        <v>331</v>
       </c>
       <c r="D188" s="53" t="s">
         <v>283</v>
@@ -34613,34 +34615,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="159" t="s">
         <v>1159</v>
       </c>
-      <c r="B1" s="158" t="s">
+      <c r="B1" s="159" t="s">
         <v>1160</v>
       </c>
-      <c r="C1" s="158" t="s">
+      <c r="C1" s="159" t="s">
         <v>1161</v>
       </c>
-      <c r="D1" s="159" t="s">
+      <c r="D1" s="160" t="s">
         <v>1162</v>
       </c>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
-      <c r="G1" s="159" t="s">
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160" t="s">
         <v>1163</v>
       </c>
-      <c r="H1" s="159"/>
-      <c r="I1" s="159"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
       <c r="J1" s="109"/>
       <c r="K1" s="110" t="s">
         <v>1164</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A2" s="158"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
+      <c r="A2" s="159"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
       <c r="D2" s="108" t="s">
         <v>1165</v>
       </c>
@@ -37072,19 +37074,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="159" t="s">
         <v>1184</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
     </row>
     <row r="2" spans="1:11" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A2" s="135" t="s">
@@ -37817,16 +37819,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="159" t="s">
         <v>1185</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="151" t="s">

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2367" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B61E1940-154F-4124-BDB1-4868691471E2}"/>
+  <xr:revisionPtr revIDLastSave="2373" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9C64EBD-16E9-425D-9EBB-05D7919B5398}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-2565" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4248,7 +4248,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="37" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4733,9 +4733,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -18211,7 +18208,7 @@
       <c r="Q61" s="17"/>
     </row>
     <row r="62" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
-      <c r="A62" s="162" t="s">
+      <c r="A62" s="161" t="s">
         <v>102</v>
       </c>
       <c r="B62" s="60" t="s">
@@ -19539,14 +19536,14 @@
       <c r="Q87" s="17"/>
     </row>
     <row r="88" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
-      <c r="A88" s="162" t="s">
+      <c r="A88" s="161" t="s">
         <v>136</v>
       </c>
       <c r="B88" s="58" t="s">
         <v>137</v>
       </c>
       <c r="C88" s="53" t="s">
-        <v>356</v>
+        <v>331</v>
       </c>
       <c r="D88" s="53" t="s">
         <v>283</v>
@@ -24254,7 +24251,7 @@
         <v>121</v>
       </c>
       <c r="C188" s="53" t="s">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="D188" s="53" t="s">
         <v>283</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2444" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A47FEE63-9793-4298-864B-BEC6537C68C4}"/>
+  <xr:revisionPtr revIDLastSave="2575" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C5BF501-A530-4B8C-A6AB-77A70641A1B2}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-2565" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="21720" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FS Elec" sheetId="4" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4987" uniqueCount="1193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5000" uniqueCount="1194">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -3626,6 +3626,9 @@
   </si>
   <si>
     <t>10192062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">removal date </t>
   </si>
 </sst>
 </file>
@@ -4248,7 +4251,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="37" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4735,6 +4738,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5755,7 +5764,9 @@
       <c r="B11" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="2">
+        <v>14558066248</v>
+      </c>
       <c r="D11" s="2">
         <v>82929702</v>
       </c>
@@ -5768,14 +5779,18 @@
       <c r="G11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="2"/>
+      <c r="H11" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="I11" s="46" t="s">
         <v>35</v>
       </c>
       <c r="J11" s="9">
         <v>0</v>
       </c>
-      <c r="K11" s="2"/>
+      <c r="K11" s="4">
+        <v>46218</v>
+      </c>
       <c r="L11" s="11" t="b">
         <v>0</v>
       </c>
@@ -5803,7 +5818,9 @@
       <c r="B12" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="2"/>
+      <c r="C12" s="2">
+        <v>14558069416</v>
+      </c>
       <c r="D12" s="2">
         <v>82929702</v>
       </c>
@@ -5816,14 +5833,18 @@
       <c r="G12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="I12" s="46" t="s">
         <v>35</v>
       </c>
       <c r="J12" s="9">
         <v>0</v>
       </c>
-      <c r="K12" s="2"/>
+      <c r="K12" s="4">
+        <v>46218</v>
+      </c>
       <c r="L12" s="11" t="b">
         <v>0</v>
       </c>
@@ -5851,7 +5872,9 @@
       <c r="B13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="2">
+        <v>14558069465</v>
+      </c>
       <c r="D13" s="2">
         <v>82929702</v>
       </c>
@@ -5864,14 +5887,18 @@
       <c r="G13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="2"/>
+      <c r="H13" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="I13" s="46" t="s">
         <v>35</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
       </c>
-      <c r="K13" s="2"/>
+      <c r="K13" s="4">
+        <v>46218</v>
+      </c>
       <c r="L13" s="11" t="b">
         <v>0</v>
       </c>
@@ -5947,7 +5974,9 @@
       <c r="B15" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="2">
+        <v>14558066305</v>
+      </c>
       <c r="D15" s="2">
         <v>82929702</v>
       </c>
@@ -5960,14 +5989,18 @@
       <c r="G15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="2"/>
+      <c r="H15" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="I15" s="46" t="s">
         <v>35</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
       </c>
-      <c r="K15" s="2"/>
+      <c r="K15" s="4">
+        <v>46218</v>
+      </c>
       <c r="L15" s="11" t="b">
         <v>0</v>
       </c>
@@ -6043,7 +6076,9 @@
       <c r="B17" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="2"/>
+      <c r="C17" s="2">
+        <v>14558068939</v>
+      </c>
       <c r="D17" s="2">
         <v>82929702</v>
       </c>
@@ -6056,14 +6091,18 @@
       <c r="G17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="I17" s="46" t="s">
         <v>35</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
       </c>
-      <c r="K17" s="2"/>
+      <c r="K17" s="4">
+        <v>46218</v>
+      </c>
       <c r="L17" s="11" t="b">
         <v>0</v>
       </c>
@@ -6139,7 +6178,9 @@
       <c r="B19" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="2"/>
+      <c r="C19" s="2">
+        <v>14558066099</v>
+      </c>
       <c r="D19" s="2">
         <v>82929702</v>
       </c>
@@ -6152,14 +6193,18 @@
       <c r="G19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H19" s="2"/>
+      <c r="H19" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="I19" s="46" t="s">
         <v>35</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
       </c>
-      <c r="K19" s="2"/>
+      <c r="K19" s="4">
+        <v>46218</v>
+      </c>
       <c r="L19" s="11" t="b">
         <v>0</v>
       </c>
@@ -6187,7 +6232,9 @@
       <c r="B20" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="2"/>
+      <c r="C20" s="2">
+        <v>14558069481</v>
+      </c>
       <c r="D20" s="2">
         <v>82929702</v>
       </c>
@@ -6200,14 +6247,18 @@
       <c r="G20" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H20" s="2"/>
+      <c r="H20" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="I20" s="40" t="s">
         <v>46</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
       </c>
-      <c r="K20" s="2"/>
+      <c r="K20" s="4">
+        <v>46218</v>
+      </c>
       <c r="L20" s="11" t="b">
         <v>0</v>
       </c>
@@ -6235,7 +6286,9 @@
       <c r="B21" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="2"/>
+      <c r="C21" s="2">
+        <v>14558068434</v>
+      </c>
       <c r="D21" s="2">
         <v>82929702</v>
       </c>
@@ -6248,14 +6301,18 @@
       <c r="G21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H21" s="2"/>
+      <c r="H21" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="I21" s="40" t="s">
         <v>46</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
       </c>
-      <c r="K21" s="2"/>
+      <c r="K21" s="4">
+        <v>46218</v>
+      </c>
       <c r="L21" s="11" t="b">
         <v>0</v>
       </c>
@@ -6283,7 +6340,9 @@
       <c r="B22" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="2"/>
+      <c r="C22" s="2">
+        <v>14558068798</v>
+      </c>
       <c r="D22" s="2">
         <v>82929702</v>
       </c>
@@ -6296,14 +6355,18 @@
       <c r="G22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H22" s="2"/>
+      <c r="H22" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="I22" s="40" t="s">
         <v>46</v>
       </c>
       <c r="J22" s="9">
         <v>0</v>
       </c>
-      <c r="K22" s="2"/>
+      <c r="K22" s="4">
+        <v>46218</v>
+      </c>
       <c r="L22" s="11" t="b">
         <v>0</v>
       </c>
@@ -6331,7 +6394,9 @@
       <c r="B23" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="2"/>
+      <c r="C23" s="2">
+        <v>14558069002</v>
+      </c>
       <c r="D23" s="2">
         <v>82929702</v>
       </c>
@@ -6344,14 +6409,18 @@
       <c r="G23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H23" s="2"/>
+      <c r="H23" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="I23" s="40" t="s">
         <v>46</v>
       </c>
       <c r="J23" s="9">
         <v>0</v>
       </c>
-      <c r="K23" s="2"/>
+      <c r="K23" s="4">
+        <v>46218</v>
+      </c>
       <c r="L23" s="11" t="b">
         <v>0</v>
       </c>
@@ -6379,7 +6448,9 @@
       <c r="B24" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="2"/>
+      <c r="C24" s="163">
+        <v>14558068921</v>
+      </c>
       <c r="D24" s="2">
         <v>82929702</v>
       </c>
@@ -6392,14 +6463,18 @@
       <c r="G24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="2"/>
+      <c r="H24" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="I24" s="40" t="s">
         <v>46</v>
       </c>
       <c r="J24" s="9">
         <v>0</v>
       </c>
-      <c r="K24" s="2"/>
+      <c r="K24" s="4">
+        <v>46218</v>
+      </c>
       <c r="L24" s="11" t="b">
         <v>0</v>
       </c>
@@ -6427,7 +6502,9 @@
       <c r="B25" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="2"/>
+      <c r="C25" s="2">
+        <v>14558069374</v>
+      </c>
       <c r="D25" s="2">
         <v>82929702</v>
       </c>
@@ -6440,14 +6517,18 @@
       <c r="G25" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="2"/>
+      <c r="H25" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="I25" s="40" t="s">
         <v>46</v>
       </c>
       <c r="J25" s="9">
         <v>0</v>
       </c>
-      <c r="K25" s="2"/>
+      <c r="K25" s="4">
+        <v>46218</v>
+      </c>
       <c r="L25" s="11" t="b">
         <v>0</v>
       </c>
@@ -8827,7 +8908,9 @@
       <c r="L69" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M69" s="2"/>
+      <c r="M69" s="2">
+        <v>6</v>
+      </c>
       <c r="N69" s="64" t="s">
         <v>105</v>
       </c>
@@ -8879,9 +8962,11 @@
         <v>46197</v>
       </c>
       <c r="L70" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M70" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M70" s="2">
+        <v>5</v>
+      </c>
       <c r="N70" s="64" t="s">
         <v>103</v>
       </c>
@@ -8935,7 +9020,9 @@
       <c r="L71" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M71" s="2"/>
+      <c r="M71" s="2">
+        <v>7</v>
+      </c>
       <c r="N71" s="64" t="s">
         <v>105</v>
       </c>
@@ -8987,9 +9074,11 @@
         <v>46197</v>
       </c>
       <c r="L72" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M72" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M72" s="2">
+        <v>1</v>
+      </c>
       <c r="N72" s="64" t="s">
         <v>103</v>
       </c>
@@ -9041,9 +9130,11 @@
         <v>46197</v>
       </c>
       <c r="L73" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M73" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M73" s="2">
+        <v>8</v>
+      </c>
       <c r="N73" s="64" t="s">
         <v>105</v>
       </c>
@@ -9097,7 +9188,9 @@
       <c r="L74" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M74" s="2"/>
+      <c r="M74" s="2">
+        <v>2</v>
+      </c>
       <c r="N74" s="64" t="s">
         <v>103</v>
       </c>
@@ -9149,9 +9242,11 @@
         <v>46197</v>
       </c>
       <c r="L75" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M75" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M75" s="2">
+        <v>4</v>
+      </c>
       <c r="N75" s="64" t="s">
         <v>105</v>
       </c>
@@ -9203,9 +9298,11 @@
         <v>46197</v>
       </c>
       <c r="L76" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M76" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M76" s="2">
+        <v>3</v>
+      </c>
       <c r="N76" s="64" t="s">
         <v>103</v>
       </c>
@@ -14523,7 +14620,9 @@
       <c r="L177" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M177" s="2"/>
+      <c r="M177" s="2">
+        <v>1</v>
+      </c>
       <c r="N177" s="64" t="s">
         <v>250</v>
       </c>
@@ -14577,7 +14676,9 @@
       <c r="L178" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M178" s="2"/>
+      <c r="M178" s="2">
+        <v>2</v>
+      </c>
       <c r="N178" s="64" t="s">
         <v>250</v>
       </c>
@@ -14631,7 +14732,9 @@
       <c r="L179" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M179" s="2"/>
+      <c r="M179" s="2">
+        <v>3</v>
+      </c>
       <c r="N179" s="64" t="s">
         <v>250</v>
       </c>
@@ -14683,9 +14786,11 @@
         <v>46210</v>
       </c>
       <c r="L180" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M180" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M180" s="2">
+        <v>4</v>
+      </c>
       <c r="N180" s="64" t="s">
         <v>250</v>
       </c>
@@ -14739,7 +14844,9 @@
       <c r="L181" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M181" s="2"/>
+      <c r="M181" s="2">
+        <v>5</v>
+      </c>
       <c r="N181" s="64" t="s">
         <v>250</v>
       </c>
@@ -14793,7 +14900,9 @@
       <c r="L182" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M182" s="2"/>
+      <c r="M182" s="2">
+        <v>6</v>
+      </c>
       <c r="N182" s="64" t="s">
         <v>250</v>
       </c>
@@ -14847,7 +14956,9 @@
       <c r="L183" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M183" s="2"/>
+      <c r="M183" s="2">
+        <v>1</v>
+      </c>
       <c r="N183" s="64" t="s">
         <v>250</v>
       </c>
@@ -14901,7 +15012,9 @@
       <c r="L184" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M184" s="2"/>
+      <c r="M184" s="2">
+        <v>2</v>
+      </c>
       <c r="N184" s="64" t="s">
         <v>261</v>
       </c>
@@ -14955,7 +15068,9 @@
       <c r="L185" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M185" s="2"/>
+      <c r="M185" s="2">
+        <v>3</v>
+      </c>
       <c r="N185" s="64" t="s">
         <v>261</v>
       </c>
@@ -15009,7 +15124,9 @@
       <c r="L186" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M186" s="2"/>
+      <c r="M186" s="2">
+        <v>4</v>
+      </c>
       <c r="N186" s="64" t="s">
         <v>261</v>
       </c>
@@ -15061,9 +15178,11 @@
         <v>46210</v>
       </c>
       <c r="L187" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M187" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M187" s="2">
+        <v>5</v>
+      </c>
       <c r="N187" s="64" t="s">
         <v>261</v>
       </c>
@@ -15115,9 +15234,11 @@
         <v>46210</v>
       </c>
       <c r="L188" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M188" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M188" s="2">
+        <v>6</v>
+      </c>
       <c r="N188" s="64" t="s">
         <v>261</v>
       </c>
@@ -15361,7 +15482,7 @@
     <sortCondition ref="A2:A192"/>
   </sortState>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="C2:C192">
+  <conditionalFormatting sqref="C25:C192 C2:C23">
     <cfRule type="duplicateValues" dxfId="16" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C117:C122">
@@ -18406,7 +18527,7 @@
         <v>46195</v>
       </c>
       <c r="O63" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P63" s="21" t="b">
         <v>0</v>
@@ -35864,20 +35985,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.73046875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.265625" customWidth="1"/>
     <col min="3" max="3" width="25.265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="127" t="s">
         <v>1178</v>
       </c>
@@ -35894,16 +36015,19 @@
         <v>1179</v>
       </c>
       <c r="F1" s="129" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G1" s="129" t="s">
         <v>1180</v>
       </c>
-      <c r="G1" s="129" t="s">
+      <c r="H1" s="129" t="s">
         <v>1181</v>
       </c>
-      <c r="H1" s="105" t="s">
+      <c r="I1" s="105" t="s">
         <v>1179</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="2" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A2" s="130">
         <v>22</v>
       </c>
@@ -35917,14 +36041,19 @@
         <v>19375.900000000001</v>
       </c>
       <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="131">
-        <f t="shared" ref="G2:G34" si="0">F2-D2</f>
-        <v>-19375.900000000001</v>
-      </c>
-      <c r="H2" s="106"/>
-    </row>
-    <row r="3" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="F2" s="162">
+        <v>46218</v>
+      </c>
+      <c r="G2" s="130">
+        <v>19888.099999999999</v>
+      </c>
+      <c r="H2" s="131">
+        <f t="shared" ref="H2:H34" si="0">G2-D2</f>
+        <v>512.19999999999709</v>
+      </c>
+      <c r="I2" s="106"/>
+    </row>
+    <row r="3" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A3" s="130">
         <v>44</v>
       </c>
@@ -35938,16 +36067,17 @@
         <v>56032.6</v>
       </c>
       <c r="E3" s="130"/>
-      <c r="F3" s="130">
+      <c r="F3" s="162"/>
+      <c r="G3" s="130">
         <v>56111.5</v>
       </c>
-      <c r="G3" s="131">
+      <c r="H3" s="131">
         <f t="shared" si="0"/>
         <v>78.900000000001455</v>
       </c>
-      <c r="H3" s="106"/>
-    </row>
-    <row r="4" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I3" s="106"/>
+    </row>
+    <row r="4" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A4" s="130">
         <v>53</v>
       </c>
@@ -35961,16 +36091,17 @@
         <v>17968.5</v>
       </c>
       <c r="E4" s="130"/>
-      <c r="F4" s="130">
+      <c r="F4" s="162"/>
+      <c r="G4" s="130">
         <v>18120.900000000001</v>
       </c>
-      <c r="G4" s="131">
+      <c r="H4" s="131">
         <f t="shared" si="0"/>
         <v>152.40000000000146</v>
       </c>
-      <c r="H4" s="106"/>
-    </row>
-    <row r="5" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I4" s="106"/>
+    </row>
+    <row r="5" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A5" s="132">
         <v>58</v>
       </c>
@@ -35984,16 +36115,17 @@
         <v>59659</v>
       </c>
       <c r="E5" s="132"/>
-      <c r="F5" s="130">
+      <c r="F5" s="162"/>
+      <c r="G5" s="130">
         <v>59659</v>
       </c>
-      <c r="G5" s="131">
+      <c r="H5" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H5" s="106"/>
-    </row>
-    <row r="6" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I5" s="106"/>
+    </row>
+    <row r="6" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A6" s="132">
         <v>60</v>
       </c>
@@ -36007,16 +36139,17 @@
         <v>97390</v>
       </c>
       <c r="E6" s="132"/>
-      <c r="F6" s="130">
+      <c r="F6" s="162"/>
+      <c r="G6" s="130">
         <v>97390</v>
       </c>
-      <c r="G6" s="131">
+      <c r="H6" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H6" s="106"/>
-    </row>
-    <row r="7" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I6" s="106"/>
+    </row>
+    <row r="7" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A7" s="132">
         <v>61</v>
       </c>
@@ -36030,16 +36163,17 @@
         <v>23184</v>
       </c>
       <c r="E7" s="132"/>
-      <c r="F7" s="130">
+      <c r="F7" s="162"/>
+      <c r="G7" s="130">
         <v>23184</v>
       </c>
-      <c r="G7" s="131">
+      <c r="H7" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H7" s="106"/>
-    </row>
-    <row r="8" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I7" s="106"/>
+    </row>
+    <row r="8" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A8" s="132">
         <v>62</v>
       </c>
@@ -36053,16 +36187,17 @@
         <v>7889</v>
       </c>
       <c r="E8" s="132"/>
-      <c r="F8" s="130">
+      <c r="F8" s="162"/>
+      <c r="G8" s="130">
         <v>7889</v>
       </c>
-      <c r="G8" s="131">
+      <c r="H8" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="106"/>
-    </row>
-    <row r="9" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I8" s="106"/>
+    </row>
+    <row r="9" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A9" s="132">
         <v>63</v>
       </c>
@@ -36076,16 +36211,17 @@
         <v>27096</v>
       </c>
       <c r="E9" s="132"/>
-      <c r="F9" s="130">
+      <c r="F9" s="162"/>
+      <c r="G9" s="130">
         <v>27095</v>
       </c>
-      <c r="G9" s="131">
+      <c r="H9" s="131">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="H9" s="106"/>
-    </row>
-    <row r="10" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I9" s="106"/>
+    </row>
+    <row r="10" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A10" s="132">
         <v>64</v>
       </c>
@@ -36099,16 +36235,17 @@
         <v>15280</v>
       </c>
       <c r="E10" s="132"/>
-      <c r="F10" s="130">
+      <c r="F10" s="162"/>
+      <c r="G10" s="130">
         <v>15280</v>
       </c>
-      <c r="G10" s="131">
+      <c r="H10" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="106"/>
-    </row>
-    <row r="11" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I10" s="106"/>
+    </row>
+    <row r="11" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A11" s="132">
         <v>65</v>
       </c>
@@ -36122,16 +36259,17 @@
         <v>20310</v>
       </c>
       <c r="E11" s="132"/>
-      <c r="F11" s="130">
+      <c r="F11" s="162"/>
+      <c r="G11" s="130">
         <v>20310</v>
       </c>
-      <c r="G11" s="131">
+      <c r="H11" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="106"/>
-    </row>
-    <row r="12" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I11" s="106"/>
+    </row>
+    <row r="12" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A12" s="132">
         <v>66</v>
       </c>
@@ -36145,16 +36283,17 @@
         <v>24100</v>
       </c>
       <c r="E12" s="132"/>
-      <c r="F12" s="130">
+      <c r="F12" s="162"/>
+      <c r="G12" s="130">
         <v>24100</v>
       </c>
-      <c r="G12" s="131">
+      <c r="H12" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="106"/>
-    </row>
-    <row r="13" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I12" s="106"/>
+    </row>
+    <row r="13" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A13" s="132">
         <v>67</v>
       </c>
@@ -36168,16 +36307,17 @@
         <v>172161.6</v>
       </c>
       <c r="E13" s="132"/>
-      <c r="F13" s="130">
+      <c r="F13" s="162"/>
+      <c r="G13" s="130">
         <v>172161.6</v>
       </c>
-      <c r="G13" s="131">
+      <c r="H13" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="106"/>
-    </row>
-    <row r="14" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I13" s="106"/>
+    </row>
+    <row r="14" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A14" s="132">
         <v>68</v>
       </c>
@@ -36191,16 +36331,17 @@
         <v>11718</v>
       </c>
       <c r="E14" s="132"/>
-      <c r="F14" s="130">
+      <c r="F14" s="162"/>
+      <c r="G14" s="130">
         <v>11718</v>
       </c>
-      <c r="G14" s="131">
+      <c r="H14" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="106"/>
-    </row>
-    <row r="15" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I14" s="106"/>
+    </row>
+    <row r="15" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A15" s="132">
         <v>69</v>
       </c>
@@ -36214,16 +36355,17 @@
         <v>38143</v>
       </c>
       <c r="E15" s="132"/>
-      <c r="F15" s="130">
+      <c r="F15" s="162"/>
+      <c r="G15" s="130">
         <v>38145</v>
       </c>
-      <c r="G15" s="131">
+      <c r="H15" s="131">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H15" s="106"/>
-    </row>
-    <row r="16" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I15" s="106"/>
+    </row>
+    <row r="16" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A16" s="132">
         <v>70</v>
       </c>
@@ -36237,16 +36379,17 @@
         <v>35381.199999999997</v>
       </c>
       <c r="E16" s="132"/>
-      <c r="F16" s="130">
+      <c r="F16" s="162"/>
+      <c r="G16" s="130">
         <v>35381.199999999997</v>
       </c>
-      <c r="G16" s="131">
+      <c r="H16" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="106"/>
-    </row>
-    <row r="17" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I16" s="106"/>
+    </row>
+    <row r="17" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A17" s="132">
         <v>71</v>
       </c>
@@ -36260,16 +36403,17 @@
         <v>179707</v>
       </c>
       <c r="E17" s="132"/>
-      <c r="F17" s="130">
+      <c r="F17" s="162"/>
+      <c r="G17" s="130">
         <v>179707</v>
       </c>
-      <c r="G17" s="131">
+      <c r="H17" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="106"/>
-    </row>
-    <row r="18" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I17" s="106"/>
+    </row>
+    <row r="18" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A18" s="132">
         <v>72</v>
       </c>
@@ -36283,16 +36427,17 @@
         <v>103115.8</v>
       </c>
       <c r="E18" s="132"/>
-      <c r="F18" s="130">
+      <c r="F18" s="162"/>
+      <c r="G18" s="130">
         <v>103121.8</v>
       </c>
-      <c r="G18" s="131">
+      <c r="H18" s="131">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H18" s="106"/>
-    </row>
-    <row r="19" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I18" s="106"/>
+    </row>
+    <row r="19" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A19" s="132">
         <v>73</v>
       </c>
@@ -36306,16 +36451,17 @@
         <v>18870</v>
       </c>
       <c r="E19" s="132"/>
-      <c r="F19" s="130">
+      <c r="F19" s="162"/>
+      <c r="G19" s="130">
         <v>18870</v>
       </c>
-      <c r="G19" s="131">
+      <c r="H19" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H19" s="106"/>
-    </row>
-    <row r="20" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I19" s="106"/>
+    </row>
+    <row r="20" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A20" s="132">
         <v>74</v>
       </c>
@@ -36329,16 +36475,17 @@
         <v>72558.399999999994</v>
       </c>
       <c r="E20" s="132"/>
-      <c r="F20" s="130">
+      <c r="F20" s="162"/>
+      <c r="G20" s="130">
         <v>72558.399999999994</v>
       </c>
-      <c r="G20" s="131">
+      <c r="H20" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H20" s="106"/>
-    </row>
-    <row r="21" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I20" s="106"/>
+    </row>
+    <row r="21" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A21" s="132">
         <v>75</v>
       </c>
@@ -36352,16 +36499,17 @@
         <v>12607</v>
       </c>
       <c r="E21" s="132"/>
-      <c r="F21" s="130">
+      <c r="F21" s="162"/>
+      <c r="G21" s="130">
         <v>12608</v>
       </c>
-      <c r="G21" s="131">
+      <c r="H21" s="131">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H21" s="106"/>
-    </row>
-    <row r="22" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I21" s="106"/>
+    </row>
+    <row r="22" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A22" s="132">
         <v>82</v>
       </c>
@@ -36373,16 +36521,17 @@
         <v>0</v>
       </c>
       <c r="E22" s="132"/>
-      <c r="F22" s="130">
+      <c r="F22" s="162"/>
+      <c r="G22" s="130">
         <v>274.60000000000002</v>
       </c>
-      <c r="G22" s="131">
+      <c r="H22" s="131">
         <f t="shared" si="0"/>
         <v>274.60000000000002</v>
       </c>
-      <c r="H22" s="106"/>
-    </row>
-    <row r="23" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I22" s="106"/>
+    </row>
+    <row r="23" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A23" s="132">
         <v>87</v>
       </c>
@@ -36396,16 +36545,17 @@
         <v>30522</v>
       </c>
       <c r="E23" s="132"/>
-      <c r="F23" s="130">
+      <c r="F23" s="162"/>
+      <c r="G23" s="130">
         <v>30522</v>
       </c>
-      <c r="G23" s="131">
+      <c r="H23" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H23" s="106"/>
-    </row>
-    <row r="24" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I23" s="106"/>
+    </row>
+    <row r="24" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A24" s="132">
         <v>88</v>
       </c>
@@ -36419,16 +36569,17 @@
         <v>42174</v>
       </c>
       <c r="E24" s="132"/>
-      <c r="F24" s="130">
+      <c r="F24" s="162"/>
+      <c r="G24" s="130">
         <v>42174</v>
       </c>
-      <c r="G24" s="131">
+      <c r="H24" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H24" s="106"/>
-    </row>
-    <row r="25" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I24" s="106"/>
+    </row>
+    <row r="25" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A25" s="132">
         <v>89</v>
       </c>
@@ -36442,16 +36593,17 @@
         <v>0</v>
       </c>
       <c r="E25" s="132"/>
-      <c r="F25" s="130">
+      <c r="F25" s="162"/>
+      <c r="G25" s="130">
         <v>101.9</v>
       </c>
-      <c r="G25" s="131">
+      <c r="H25" s="131">
         <f t="shared" si="0"/>
         <v>101.9</v>
       </c>
-      <c r="H25" s="106"/>
-    </row>
-    <row r="26" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I25" s="106"/>
+    </row>
+    <row r="26" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A26" s="132">
         <v>90</v>
       </c>
@@ -36465,16 +36617,17 @@
         <v>0</v>
       </c>
       <c r="E26" s="132"/>
-      <c r="F26" s="130">
+      <c r="F26" s="162"/>
+      <c r="G26" s="130">
         <v>47842.5</v>
       </c>
-      <c r="G26" s="131">
+      <c r="H26" s="131">
         <f t="shared" si="0"/>
         <v>47842.5</v>
       </c>
-      <c r="H26" s="106"/>
-    </row>
-    <row r="27" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I26" s="106"/>
+    </row>
+    <row r="27" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A27" s="132">
         <v>91</v>
       </c>
@@ -36488,16 +36641,17 @@
         <v>0</v>
       </c>
       <c r="E27" s="132"/>
-      <c r="F27" s="130">
+      <c r="F27" s="162"/>
+      <c r="G27" s="130">
         <v>54.7</v>
       </c>
-      <c r="G27" s="131">
+      <c r="H27" s="131">
         <f t="shared" si="0"/>
         <v>54.7</v>
       </c>
-      <c r="H27" s="106"/>
-    </row>
-    <row r="28" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I27" s="106"/>
+    </row>
+    <row r="28" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A28" s="132">
         <v>92</v>
       </c>
@@ -36511,16 +36665,17 @@
         <v>55276.2</v>
       </c>
       <c r="E28" s="132"/>
-      <c r="F28" s="130">
+      <c r="F28" s="162"/>
+      <c r="G28" s="130">
         <v>55295.6</v>
       </c>
-      <c r="G28" s="131">
+      <c r="H28" s="131">
         <f t="shared" si="0"/>
         <v>19.400000000001455</v>
       </c>
-      <c r="H28" s="106"/>
-    </row>
-    <row r="29" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I28" s="106"/>
+    </row>
+    <row r="29" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A29" s="130">
         <v>93</v>
       </c>
@@ -36534,16 +36689,17 @@
         <v>1076.4000000000001</v>
       </c>
       <c r="E29" s="130"/>
-      <c r="F29" s="130">
+      <c r="F29" s="162"/>
+      <c r="G29" s="130">
         <v>1234.5</v>
       </c>
-      <c r="G29" s="131">
+      <c r="H29" s="131">
         <f t="shared" si="0"/>
         <v>158.09999999999991</v>
       </c>
-      <c r="H29" s="106"/>
-    </row>
-    <row r="30" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I29" s="106"/>
+    </row>
+    <row r="30" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A30" s="132">
         <v>94</v>
       </c>
@@ -36557,16 +36713,17 @@
         <v>26813.1</v>
       </c>
       <c r="E30" s="132"/>
-      <c r="F30" s="130">
+      <c r="F30" s="162"/>
+      <c r="G30" s="130">
         <v>26832.799999999999</v>
       </c>
-      <c r="G30" s="131">
+      <c r="H30" s="131">
         <f t="shared" si="0"/>
         <v>19.700000000000728</v>
       </c>
-      <c r="H30" s="106"/>
-    </row>
-    <row r="31" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I30" s="106"/>
+    </row>
+    <row r="31" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A31" s="130">
         <v>95</v>
       </c>
@@ -36580,16 +36737,17 @@
         <v>26313</v>
       </c>
       <c r="E31" s="130"/>
-      <c r="F31" s="130">
+      <c r="F31" s="162"/>
+      <c r="G31" s="130">
         <v>139657</v>
       </c>
-      <c r="G31" s="131">
+      <c r="H31" s="131">
         <f t="shared" si="0"/>
         <v>113344</v>
       </c>
-      <c r="H31" s="106"/>
-    </row>
-    <row r="32" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I31" s="106"/>
+    </row>
+    <row r="32" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A32" s="132">
         <v>96</v>
       </c>
@@ -36603,16 +36761,17 @@
         <v>16956.2</v>
       </c>
       <c r="E32" s="132"/>
-      <c r="F32" s="130">
+      <c r="F32" s="162"/>
+      <c r="G32" s="130">
         <v>16978.099999999999</v>
       </c>
-      <c r="G32" s="131">
+      <c r="H32" s="131">
         <f t="shared" si="0"/>
         <v>21.899999999997817</v>
       </c>
-      <c r="H32" s="106"/>
-    </row>
-    <row r="33" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I32" s="106"/>
+    </row>
+    <row r="33" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A33" s="130">
         <v>97</v>
       </c>
@@ -36626,16 +36785,17 @@
         <v>36948.800000000003</v>
       </c>
       <c r="E33" s="130"/>
-      <c r="F33" s="130">
+      <c r="F33" s="162"/>
+      <c r="G33" s="130">
         <v>36948.800000000003</v>
       </c>
-      <c r="G33" s="131">
+      <c r="H33" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H33" s="106"/>
-    </row>
-    <row r="34" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I33" s="106"/>
+    </row>
+    <row r="34" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A34" s="132">
         <v>98</v>
       </c>
@@ -36649,16 +36809,17 @@
         <v>43330.5</v>
       </c>
       <c r="E34" s="132"/>
-      <c r="F34" s="130">
+      <c r="F34" s="162"/>
+      <c r="G34" s="130">
         <v>43364.7</v>
       </c>
-      <c r="G34" s="131">
+      <c r="H34" s="131">
         <f t="shared" si="0"/>
         <v>34.19999999999709</v>
       </c>
-      <c r="H34" s="106"/>
-    </row>
-    <row r="35" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I34" s="106"/>
+    </row>
+    <row r="35" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A35" s="130">
         <v>99</v>
       </c>
@@ -36672,16 +36833,17 @@
         <v>21735.7</v>
       </c>
       <c r="E35" s="130"/>
-      <c r="F35" s="130">
+      <c r="F35" s="162"/>
+      <c r="G35" s="130">
         <v>21789.1</v>
       </c>
-      <c r="G35" s="131">
-        <f t="shared" ref="G35:G54" si="1">F35-D35</f>
+      <c r="H35" s="131">
+        <f t="shared" ref="H35:H54" si="1">G35-D35</f>
         <v>53.399999999997817</v>
       </c>
-      <c r="H35" s="106"/>
-    </row>
-    <row r="36" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I35" s="106"/>
+    </row>
+    <row r="36" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A36" s="132">
         <v>100</v>
       </c>
@@ -36695,16 +36857,17 @@
         <v>28815.3</v>
       </c>
       <c r="E36" s="132"/>
-      <c r="F36" s="130">
+      <c r="F36" s="162"/>
+      <c r="G36" s="130">
         <v>28847.1</v>
       </c>
-      <c r="G36" s="131">
+      <c r="H36" s="131">
         <f t="shared" si="1"/>
         <v>31.799999999999272</v>
       </c>
-      <c r="H36" s="106"/>
-    </row>
-    <row r="37" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I36" s="106"/>
+    </row>
+    <row r="37" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A37" s="130">
         <v>101</v>
       </c>
@@ -36718,16 +36881,17 @@
         <v>30210.7</v>
       </c>
       <c r="E37" s="130"/>
-      <c r="F37" s="130">
+      <c r="F37" s="162"/>
+      <c r="G37" s="130">
         <v>30259.5</v>
       </c>
-      <c r="G37" s="131">
+      <c r="H37" s="131">
         <f t="shared" si="1"/>
         <v>48.799999999999272</v>
       </c>
-      <c r="H37" s="106"/>
-    </row>
-    <row r="38" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I37" s="106"/>
+    </row>
+    <row r="38" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A38" s="132">
         <v>102</v>
       </c>
@@ -36741,16 +36905,17 @@
         <v>1849.3</v>
       </c>
       <c r="E38" s="132"/>
-      <c r="F38" s="130">
+      <c r="F38" s="162"/>
+      <c r="G38" s="130">
         <v>1881.8</v>
       </c>
-      <c r="G38" s="131">
+      <c r="H38" s="131">
         <f t="shared" si="1"/>
         <v>32.5</v>
       </c>
-      <c r="H38" s="106"/>
-    </row>
-    <row r="39" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I38" s="106"/>
+    </row>
+    <row r="39" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A39" s="130">
         <v>103</v>
       </c>
@@ -36764,16 +36929,17 @@
         <v>82275</v>
       </c>
       <c r="E39" s="130"/>
-      <c r="F39" s="130">
+      <c r="F39" s="162"/>
+      <c r="G39" s="130">
         <v>82330</v>
       </c>
-      <c r="G39" s="131">
+      <c r="H39" s="131">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="H39" s="106"/>
-    </row>
-    <row r="40" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I39" s="106"/>
+    </row>
+    <row r="40" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A40" s="130">
         <v>105</v>
       </c>
@@ -36787,16 +36953,17 @@
         <v>28976.3</v>
       </c>
       <c r="E40" s="130"/>
-      <c r="F40" s="130">
+      <c r="F40" s="162"/>
+      <c r="G40" s="130">
         <v>29012.7</v>
       </c>
-      <c r="G40" s="131">
+      <c r="H40" s="131">
         <f t="shared" si="1"/>
         <v>36.400000000001455</v>
       </c>
-      <c r="H40" s="106"/>
-    </row>
-    <row r="41" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I40" s="106"/>
+    </row>
+    <row r="41" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A41" s="130">
         <v>107</v>
       </c>
@@ -36810,16 +36977,17 @@
         <v>19376</v>
       </c>
       <c r="E41" s="130"/>
-      <c r="F41" s="130"/>
-      <c r="G41" s="131">
+      <c r="F41" s="162"/>
+      <c r="G41" s="130"/>
+      <c r="H41" s="131">
         <f t="shared" si="1"/>
         <v>-19376</v>
       </c>
-      <c r="H41" s="106" t="s">
+      <c r="I41" s="106" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="42" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A42" s="130">
         <v>109</v>
       </c>
@@ -36833,18 +37001,19 @@
         <v>29281.599999999999</v>
       </c>
       <c r="E42" s="130"/>
-      <c r="F42" s="130">
+      <c r="F42" s="162"/>
+      <c r="G42" s="130">
         <v>29406.1</v>
       </c>
-      <c r="G42" s="131">
+      <c r="H42" s="131">
         <f t="shared" si="1"/>
         <v>124.5</v>
       </c>
-      <c r="H42" s="106" t="s">
+      <c r="I42" s="106" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="43" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A43" s="130">
         <v>111</v>
       </c>
@@ -36858,18 +37027,19 @@
         <v>5509</v>
       </c>
       <c r="E43" s="130"/>
-      <c r="F43" s="130">
+      <c r="F43" s="162"/>
+      <c r="G43" s="130">
         <v>5516</v>
       </c>
-      <c r="G43" s="131">
+      <c r="H43" s="131">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="H43" s="106" t="s">
+      <c r="I43" s="106" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="44" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A44" s="130">
         <v>113</v>
       </c>
@@ -36883,18 +37053,19 @@
         <v>38016.9</v>
       </c>
       <c r="E44" s="130"/>
-      <c r="F44" s="130">
+      <c r="F44" s="162"/>
+      <c r="G44" s="130">
         <v>38086</v>
       </c>
-      <c r="G44" s="131">
+      <c r="H44" s="131">
         <f t="shared" si="1"/>
         <v>69.099999999998545</v>
       </c>
-      <c r="H44" s="106" t="s">
+      <c r="I44" s="106" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="45" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A45" s="130">
         <v>115</v>
       </c>
@@ -36908,18 +37079,19 @@
         <v>71144.2</v>
       </c>
       <c r="E45" s="130"/>
-      <c r="F45" s="130">
+      <c r="F45" s="162"/>
+      <c r="G45" s="130">
         <v>71214.8</v>
       </c>
-      <c r="G45" s="131">
+      <c r="H45" s="131">
         <f t="shared" si="1"/>
         <v>70.600000000005821</v>
       </c>
-      <c r="H45" s="106" t="s">
+      <c r="I45" s="106" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="46" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A46" s="130">
         <v>117</v>
       </c>
@@ -36933,18 +37105,19 @@
         <v>63803.5</v>
       </c>
       <c r="E46" s="130"/>
-      <c r="F46" s="130">
+      <c r="F46" s="162"/>
+      <c r="G46" s="130">
         <v>63860.4</v>
       </c>
-      <c r="G46" s="131">
+      <c r="H46" s="131">
         <f t="shared" si="1"/>
         <v>56.900000000001455</v>
       </c>
-      <c r="H46" s="106" t="s">
+      <c r="I46" s="106" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="47" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A47" s="130">
         <v>119</v>
       </c>
@@ -36958,18 +37131,19 @@
         <v>29124.2</v>
       </c>
       <c r="E47" s="130"/>
-      <c r="F47" s="130">
+      <c r="F47" s="162"/>
+      <c r="G47" s="130">
         <v>29208.6</v>
       </c>
-      <c r="G47" s="131">
+      <c r="H47" s="131">
         <f t="shared" si="1"/>
         <v>84.399999999997817</v>
       </c>
-      <c r="H47" s="106" t="s">
+      <c r="I47" s="106" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="48" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A48" s="130">
         <v>121</v>
       </c>
@@ -36983,18 +37157,19 @@
         <v>9600.1</v>
       </c>
       <c r="E48" s="130"/>
-      <c r="F48" s="130">
+      <c r="F48" s="162"/>
+      <c r="G48" s="130">
         <v>9668.1</v>
       </c>
-      <c r="G48" s="131">
+      <c r="H48" s="131">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
-      <c r="H48" s="106" t="s">
+      <c r="I48" s="106" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="49" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A49" s="130">
         <v>123</v>
       </c>
@@ -37008,18 +37183,19 @@
         <v>89289.8</v>
       </c>
       <c r="E49" s="130"/>
-      <c r="F49" s="130">
+      <c r="F49" s="162"/>
+      <c r="G49" s="130">
         <v>89352.7</v>
       </c>
-      <c r="G49" s="131">
+      <c r="H49" s="131">
         <f t="shared" si="1"/>
         <v>62.899999999994179</v>
       </c>
-      <c r="H49" s="106" t="s">
+      <c r="I49" s="106" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="50" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A50" s="130">
         <v>125</v>
       </c>
@@ -37033,18 +37209,19 @@
         <v>89182.7</v>
       </c>
       <c r="E50" s="130"/>
-      <c r="F50" s="130">
+      <c r="F50" s="162"/>
+      <c r="G50" s="130">
         <v>89225.2</v>
       </c>
-      <c r="G50" s="131">
+      <c r="H50" s="131">
         <f t="shared" si="1"/>
         <v>42.5</v>
       </c>
-      <c r="H50" s="106" t="s">
+      <c r="I50" s="106" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="51" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A51" s="130">
         <v>127</v>
       </c>
@@ -37058,18 +37235,19 @@
         <v>25290.799999999999</v>
       </c>
       <c r="E51" s="130"/>
-      <c r="F51" s="130">
+      <c r="F51" s="162"/>
+      <c r="G51" s="130">
         <v>25372.1</v>
       </c>
-      <c r="G51" s="131">
+      <c r="H51" s="131">
         <f t="shared" si="1"/>
         <v>81.299999999999272</v>
       </c>
-      <c r="H51" s="106" t="s">
+      <c r="I51" s="106" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="52" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A52" s="130">
         <v>163</v>
       </c>
@@ -37083,14 +37261,15 @@
         <v>35892.800000000003</v>
       </c>
       <c r="E52" s="130"/>
-      <c r="F52" s="130"/>
-      <c r="G52" s="131">
+      <c r="F52" s="162"/>
+      <c r="G52" s="130"/>
+      <c r="H52" s="131">
         <f t="shared" si="1"/>
         <v>-35892.800000000003</v>
       </c>
-      <c r="H52" s="106"/>
-    </row>
-    <row r="53" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+      <c r="I52" s="106"/>
+    </row>
+    <row r="53" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A53" s="130">
         <v>186</v>
       </c>
@@ -37102,18 +37281,19 @@
         <v>0</v>
       </c>
       <c r="E53" s="130"/>
-      <c r="F53" s="130">
+      <c r="F53" s="162"/>
+      <c r="G53" s="130">
         <v>488.5</v>
       </c>
-      <c r="G53" s="131">
+      <c r="H53" s="131">
         <f t="shared" si="1"/>
         <v>488.5</v>
       </c>
-      <c r="H53" s="106" t="s">
+      <c r="I53" s="106" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="54" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A54" s="130">
         <v>179</v>
       </c>
@@ -37125,23 +37305,24 @@
         <v>0</v>
       </c>
       <c r="E54" s="133"/>
-      <c r="F54" s="130">
+      <c r="F54" s="162"/>
+      <c r="G54" s="130">
         <v>649.9</v>
       </c>
-      <c r="G54" s="131">
+      <c r="H54" s="131">
         <f t="shared" si="1"/>
         <v>649.9</v>
       </c>
-      <c r="H54" s="106" t="s">
+      <c r="I54" s="106" t="s">
         <v>1183</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G52">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H52">
     <sortCondition ref="A2:A52"/>
   </sortState>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576 E1:E1048576" xr:uid="{2C5E24F2-5EB5-480F-A2A4-FF792E3FE22F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576 E1:E1048576 F55:F1048576" xr:uid="{2C5E24F2-5EB5-480F-A2A4-FF792E3FE22F}">
       <formula1>"Yes"</formula1>
     </dataValidation>
   </dataValidations>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2575" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C5BF501-A530-4B8C-A6AB-77A70641A1B2}"/>
+  <xr:revisionPtr revIDLastSave="2597" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6260444-4B2A-403D-B895-B1128DEFD2DC}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="21720" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="-7455" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FS Elec" sheetId="4" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5000" uniqueCount="1194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5006" uniqueCount="1197">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -3629,6 +3629,15 @@
   </si>
   <si>
     <t xml:space="preserve">removal date </t>
+  </si>
+  <si>
+    <t>10191968</t>
+  </si>
+  <si>
+    <t>10192055</t>
+  </si>
+  <si>
+    <t>10192063</t>
   </si>
 </sst>
 </file>
@@ -4251,7 +4260,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="37" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4728,23 +4737,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5926,7 +5929,9 @@
       <c r="B14" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="2">
+        <v>14558068988</v>
+      </c>
       <c r="D14" s="2">
         <v>82929702</v>
       </c>
@@ -5939,14 +5944,18 @@
       <c r="G14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="2"/>
+      <c r="H14" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="I14" s="46" t="s">
         <v>35</v>
       </c>
       <c r="J14" s="9">
         <v>0</v>
       </c>
-      <c r="K14" s="2"/>
+      <c r="K14" s="4">
+        <v>46219</v>
+      </c>
       <c r="L14" s="11" t="b">
         <v>0</v>
       </c>
@@ -6028,7 +6037,9 @@
       <c r="B16" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="2"/>
+      <c r="C16" s="2">
+        <v>14558068962</v>
+      </c>
       <c r="D16" s="2">
         <v>82929702</v>
       </c>
@@ -6041,14 +6052,18 @@
       <c r="G16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="2"/>
+      <c r="H16" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="I16" s="46" t="s">
         <v>35</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
       </c>
-      <c r="K16" s="2"/>
+      <c r="K16" s="4">
+        <v>46219</v>
+      </c>
       <c r="L16" s="11" t="b">
         <v>0</v>
       </c>
@@ -6130,7 +6145,9 @@
       <c r="B18" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="2">
+        <v>14558069549</v>
+      </c>
       <c r="D18" s="2">
         <v>82929702</v>
       </c>
@@ -6143,14 +6160,18 @@
       <c r="G18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="2"/>
+      <c r="H18" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="I18" s="46" t="s">
         <v>35</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
       </c>
-      <c r="K18" s="2"/>
+      <c r="K18" s="4">
+        <v>46219</v>
+      </c>
       <c r="L18" s="11" t="b">
         <v>0</v>
       </c>
@@ -6448,7 +6469,7 @@
       <c r="B24" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="163">
+      <c r="C24" s="5">
         <v>14558068921</v>
       </c>
       <c r="D24" s="2">
@@ -9656,7 +9677,7 @@
       <c r="B83" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="C83" s="161">
+      <c r="C83" s="158">
         <v>14558069077</v>
       </c>
       <c r="D83" s="2">
@@ -18433,7 +18454,7 @@
       <c r="Q61" s="17"/>
     </row>
     <row r="62" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
-      <c r="A62" s="160" t="s">
+      <c r="A62" s="23" t="s">
         <v>102</v>
       </c>
       <c r="B62" s="60" t="s">
@@ -19761,7 +19782,7 @@
       <c r="Q87" s="17"/>
     </row>
     <row r="88" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
-      <c r="A88" s="160" t="s">
+      <c r="A88" s="23" t="s">
         <v>136</v>
       </c>
       <c r="B88" s="58" t="s">
@@ -23956,7 +23977,9 @@
       <c r="B177" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="C177" s="53"/>
+      <c r="C177" s="53" t="s">
+        <v>1196</v>
+      </c>
       <c r="D177" s="53" t="s">
         <v>283</v>
       </c>
@@ -23966,10 +23989,14 @@
       <c r="F177" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="G177" s="3"/>
-      <c r="H177" s="3"/>
+      <c r="G177" s="3">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="H177" s="57">
+        <v>46219</v>
+      </c>
       <c r="I177" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J177" s="63" t="s">
         <v>250</v>
@@ -24091,7 +24118,9 @@
       <c r="B180" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="C180" s="53"/>
+      <c r="C180" s="53" t="s">
+        <v>1195</v>
+      </c>
       <c r="D180" s="53" t="s">
         <v>283</v>
       </c>
@@ -24101,10 +24130,14 @@
       <c r="F180" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="G180" s="3"/>
-      <c r="H180" s="3"/>
+      <c r="G180" s="3">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="H180" s="57">
+        <v>46219</v>
+      </c>
       <c r="I180" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J180" s="63" t="s">
         <v>250</v>
@@ -24136,7 +24169,9 @@
       <c r="B181" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="C181" s="53"/>
+      <c r="C181" s="53" t="s">
+        <v>1194</v>
+      </c>
       <c r="D181" s="53" t="s">
         <v>283</v>
       </c>
@@ -24146,10 +24181,14 @@
       <c r="F181" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="G181" s="3"/>
-      <c r="H181" s="3"/>
+      <c r="G181" s="3">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="H181" s="57">
+        <v>46219</v>
+      </c>
       <c r="I181" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J181" s="63" t="s">
         <v>250</v>
@@ -24469,7 +24508,7 @@
       <c r="Q187" s="17"/>
     </row>
     <row r="188" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
-      <c r="A188" s="160" t="s">
+      <c r="A188" s="23" t="s">
         <v>265</v>
       </c>
       <c r="B188" s="59" t="s">
@@ -34837,34 +34876,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="160" t="s">
         <v>1159</v>
       </c>
-      <c r="B1" s="158" t="s">
+      <c r="B1" s="160" t="s">
         <v>1160</v>
       </c>
-      <c r="C1" s="158" t="s">
+      <c r="C1" s="160" t="s">
         <v>1161</v>
       </c>
-      <c r="D1" s="159" t="s">
+      <c r="D1" s="161" t="s">
         <v>1162</v>
       </c>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
-      <c r="G1" s="159" t="s">
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161" t="s">
         <v>1163</v>
       </c>
-      <c r="H1" s="159"/>
-      <c r="I1" s="159"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
       <c r="J1" s="108"/>
       <c r="K1" s="109" t="s">
         <v>1164</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A2" s="158"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
+      <c r="A2" s="160"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
       <c r="D2" s="107" t="s">
         <v>1165</v>
       </c>
@@ -36041,7 +36080,7 @@
         <v>19375.900000000001</v>
       </c>
       <c r="E2" s="130"/>
-      <c r="F2" s="162">
+      <c r="F2" s="159">
         <v>46218</v>
       </c>
       <c r="G2" s="130">
@@ -36067,7 +36106,7 @@
         <v>56032.6</v>
       </c>
       <c r="E3" s="130"/>
-      <c r="F3" s="162"/>
+      <c r="F3" s="159"/>
       <c r="G3" s="130">
         <v>56111.5</v>
       </c>
@@ -36091,7 +36130,7 @@
         <v>17968.5</v>
       </c>
       <c r="E4" s="130"/>
-      <c r="F4" s="162"/>
+      <c r="F4" s="159"/>
       <c r="G4" s="130">
         <v>18120.900000000001</v>
       </c>
@@ -36115,7 +36154,7 @@
         <v>59659</v>
       </c>
       <c r="E5" s="132"/>
-      <c r="F5" s="162"/>
+      <c r="F5" s="159"/>
       <c r="G5" s="130">
         <v>59659</v>
       </c>
@@ -36139,7 +36178,7 @@
         <v>97390</v>
       </c>
       <c r="E6" s="132"/>
-      <c r="F6" s="162"/>
+      <c r="F6" s="159"/>
       <c r="G6" s="130">
         <v>97390</v>
       </c>
@@ -36163,7 +36202,7 @@
         <v>23184</v>
       </c>
       <c r="E7" s="132"/>
-      <c r="F7" s="162"/>
+      <c r="F7" s="159"/>
       <c r="G7" s="130">
         <v>23184</v>
       </c>
@@ -36187,7 +36226,7 @@
         <v>7889</v>
       </c>
       <c r="E8" s="132"/>
-      <c r="F8" s="162"/>
+      <c r="F8" s="159"/>
       <c r="G8" s="130">
         <v>7889</v>
       </c>
@@ -36211,7 +36250,7 @@
         <v>27096</v>
       </c>
       <c r="E9" s="132"/>
-      <c r="F9" s="162"/>
+      <c r="F9" s="159"/>
       <c r="G9" s="130">
         <v>27095</v>
       </c>
@@ -36235,7 +36274,7 @@
         <v>15280</v>
       </c>
       <c r="E10" s="132"/>
-      <c r="F10" s="162"/>
+      <c r="F10" s="159"/>
       <c r="G10" s="130">
         <v>15280</v>
       </c>
@@ -36259,7 +36298,7 @@
         <v>20310</v>
       </c>
       <c r="E11" s="132"/>
-      <c r="F11" s="162"/>
+      <c r="F11" s="159"/>
       <c r="G11" s="130">
         <v>20310</v>
       </c>
@@ -36283,7 +36322,7 @@
         <v>24100</v>
       </c>
       <c r="E12" s="132"/>
-      <c r="F12" s="162"/>
+      <c r="F12" s="159"/>
       <c r="G12" s="130">
         <v>24100</v>
       </c>
@@ -36307,7 +36346,7 @@
         <v>172161.6</v>
       </c>
       <c r="E13" s="132"/>
-      <c r="F13" s="162"/>
+      <c r="F13" s="159"/>
       <c r="G13" s="130">
         <v>172161.6</v>
       </c>
@@ -36331,7 +36370,7 @@
         <v>11718</v>
       </c>
       <c r="E14" s="132"/>
-      <c r="F14" s="162"/>
+      <c r="F14" s="159"/>
       <c r="G14" s="130">
         <v>11718</v>
       </c>
@@ -36355,7 +36394,7 @@
         <v>38143</v>
       </c>
       <c r="E15" s="132"/>
-      <c r="F15" s="162"/>
+      <c r="F15" s="159"/>
       <c r="G15" s="130">
         <v>38145</v>
       </c>
@@ -36379,7 +36418,7 @@
         <v>35381.199999999997</v>
       </c>
       <c r="E16" s="132"/>
-      <c r="F16" s="162"/>
+      <c r="F16" s="159"/>
       <c r="G16" s="130">
         <v>35381.199999999997</v>
       </c>
@@ -36403,7 +36442,7 @@
         <v>179707</v>
       </c>
       <c r="E17" s="132"/>
-      <c r="F17" s="162"/>
+      <c r="F17" s="159"/>
       <c r="G17" s="130">
         <v>179707</v>
       </c>
@@ -36427,7 +36466,7 @@
         <v>103115.8</v>
       </c>
       <c r="E18" s="132"/>
-      <c r="F18" s="162"/>
+      <c r="F18" s="159"/>
       <c r="G18" s="130">
         <v>103121.8</v>
       </c>
@@ -36451,7 +36490,7 @@
         <v>18870</v>
       </c>
       <c r="E19" s="132"/>
-      <c r="F19" s="162"/>
+      <c r="F19" s="159"/>
       <c r="G19" s="130">
         <v>18870</v>
       </c>
@@ -36475,7 +36514,7 @@
         <v>72558.399999999994</v>
       </c>
       <c r="E20" s="132"/>
-      <c r="F20" s="162"/>
+      <c r="F20" s="159"/>
       <c r="G20" s="130">
         <v>72558.399999999994</v>
       </c>
@@ -36499,7 +36538,7 @@
         <v>12607</v>
       </c>
       <c r="E21" s="132"/>
-      <c r="F21" s="162"/>
+      <c r="F21" s="159"/>
       <c r="G21" s="130">
         <v>12608</v>
       </c>
@@ -36521,7 +36560,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="132"/>
-      <c r="F22" s="162"/>
+      <c r="F22" s="159"/>
       <c r="G22" s="130">
         <v>274.60000000000002</v>
       </c>
@@ -36545,7 +36584,7 @@
         <v>30522</v>
       </c>
       <c r="E23" s="132"/>
-      <c r="F23" s="162"/>
+      <c r="F23" s="159"/>
       <c r="G23" s="130">
         <v>30522</v>
       </c>
@@ -36569,7 +36608,7 @@
         <v>42174</v>
       </c>
       <c r="E24" s="132"/>
-      <c r="F24" s="162"/>
+      <c r="F24" s="159"/>
       <c r="G24" s="130">
         <v>42174</v>
       </c>
@@ -36593,7 +36632,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="132"/>
-      <c r="F25" s="162"/>
+      <c r="F25" s="159"/>
       <c r="G25" s="130">
         <v>101.9</v>
       </c>
@@ -36617,7 +36656,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="132"/>
-      <c r="F26" s="162"/>
+      <c r="F26" s="159"/>
       <c r="G26" s="130">
         <v>47842.5</v>
       </c>
@@ -36641,7 +36680,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="132"/>
-      <c r="F27" s="162"/>
+      <c r="F27" s="159"/>
       <c r="G27" s="130">
         <v>54.7</v>
       </c>
@@ -36665,7 +36704,7 @@
         <v>55276.2</v>
       </c>
       <c r="E28" s="132"/>
-      <c r="F28" s="162"/>
+      <c r="F28" s="159"/>
       <c r="G28" s="130">
         <v>55295.6</v>
       </c>
@@ -36689,7 +36728,7 @@
         <v>1076.4000000000001</v>
       </c>
       <c r="E29" s="130"/>
-      <c r="F29" s="162"/>
+      <c r="F29" s="159"/>
       <c r="G29" s="130">
         <v>1234.5</v>
       </c>
@@ -36713,7 +36752,7 @@
         <v>26813.1</v>
       </c>
       <c r="E30" s="132"/>
-      <c r="F30" s="162"/>
+      <c r="F30" s="159"/>
       <c r="G30" s="130">
         <v>26832.799999999999</v>
       </c>
@@ -36737,7 +36776,7 @@
         <v>26313</v>
       </c>
       <c r="E31" s="130"/>
-      <c r="F31" s="162"/>
+      <c r="F31" s="159"/>
       <c r="G31" s="130">
         <v>139657</v>
       </c>
@@ -36761,7 +36800,7 @@
         <v>16956.2</v>
       </c>
       <c r="E32" s="132"/>
-      <c r="F32" s="162"/>
+      <c r="F32" s="159"/>
       <c r="G32" s="130">
         <v>16978.099999999999</v>
       </c>
@@ -36785,7 +36824,7 @@
         <v>36948.800000000003</v>
       </c>
       <c r="E33" s="130"/>
-      <c r="F33" s="162"/>
+      <c r="F33" s="159"/>
       <c r="G33" s="130">
         <v>36948.800000000003</v>
       </c>
@@ -36809,7 +36848,7 @@
         <v>43330.5</v>
       </c>
       <c r="E34" s="132"/>
-      <c r="F34" s="162"/>
+      <c r="F34" s="159"/>
       <c r="G34" s="130">
         <v>43364.7</v>
       </c>
@@ -36833,7 +36872,7 @@
         <v>21735.7</v>
       </c>
       <c r="E35" s="130"/>
-      <c r="F35" s="162"/>
+      <c r="F35" s="159"/>
       <c r="G35" s="130">
         <v>21789.1</v>
       </c>
@@ -36857,7 +36896,7 @@
         <v>28815.3</v>
       </c>
       <c r="E36" s="132"/>
-      <c r="F36" s="162"/>
+      <c r="F36" s="159"/>
       <c r="G36" s="130">
         <v>28847.1</v>
       </c>
@@ -36881,7 +36920,7 @@
         <v>30210.7</v>
       </c>
       <c r="E37" s="130"/>
-      <c r="F37" s="162"/>
+      <c r="F37" s="159"/>
       <c r="G37" s="130">
         <v>30259.5</v>
       </c>
@@ -36905,7 +36944,7 @@
         <v>1849.3</v>
       </c>
       <c r="E38" s="132"/>
-      <c r="F38" s="162"/>
+      <c r="F38" s="159"/>
       <c r="G38" s="130">
         <v>1881.8</v>
       </c>
@@ -36929,7 +36968,7 @@
         <v>82275</v>
       </c>
       <c r="E39" s="130"/>
-      <c r="F39" s="162"/>
+      <c r="F39" s="159"/>
       <c r="G39" s="130">
         <v>82330</v>
       </c>
@@ -36953,7 +36992,7 @@
         <v>28976.3</v>
       </c>
       <c r="E40" s="130"/>
-      <c r="F40" s="162"/>
+      <c r="F40" s="159"/>
       <c r="G40" s="130">
         <v>29012.7</v>
       </c>
@@ -36977,7 +37016,7 @@
         <v>19376</v>
       </c>
       <c r="E41" s="130"/>
-      <c r="F41" s="162"/>
+      <c r="F41" s="159"/>
       <c r="G41" s="130"/>
       <c r="H41" s="131">
         <f t="shared" si="1"/>
@@ -37001,7 +37040,7 @@
         <v>29281.599999999999</v>
       </c>
       <c r="E42" s="130"/>
-      <c r="F42" s="162"/>
+      <c r="F42" s="159"/>
       <c r="G42" s="130">
         <v>29406.1</v>
       </c>
@@ -37027,7 +37066,7 @@
         <v>5509</v>
       </c>
       <c r="E43" s="130"/>
-      <c r="F43" s="162"/>
+      <c r="F43" s="159"/>
       <c r="G43" s="130">
         <v>5516</v>
       </c>
@@ -37053,7 +37092,7 @@
         <v>38016.9</v>
       </c>
       <c r="E44" s="130"/>
-      <c r="F44" s="162"/>
+      <c r="F44" s="159"/>
       <c r="G44" s="130">
         <v>38086</v>
       </c>
@@ -37079,7 +37118,7 @@
         <v>71144.2</v>
       </c>
       <c r="E45" s="130"/>
-      <c r="F45" s="162"/>
+      <c r="F45" s="159"/>
       <c r="G45" s="130">
         <v>71214.8</v>
       </c>
@@ -37105,7 +37144,7 @@
         <v>63803.5</v>
       </c>
       <c r="E46" s="130"/>
-      <c r="F46" s="162"/>
+      <c r="F46" s="159"/>
       <c r="G46" s="130">
         <v>63860.4</v>
       </c>
@@ -37131,7 +37170,7 @@
         <v>29124.2</v>
       </c>
       <c r="E47" s="130"/>
-      <c r="F47" s="162"/>
+      <c r="F47" s="159"/>
       <c r="G47" s="130">
         <v>29208.6</v>
       </c>
@@ -37157,7 +37196,7 @@
         <v>9600.1</v>
       </c>
       <c r="E48" s="130"/>
-      <c r="F48" s="162"/>
+      <c r="F48" s="159"/>
       <c r="G48" s="130">
         <v>9668.1</v>
       </c>
@@ -37183,7 +37222,7 @@
         <v>89289.8</v>
       </c>
       <c r="E49" s="130"/>
-      <c r="F49" s="162"/>
+      <c r="F49" s="159"/>
       <c r="G49" s="130">
         <v>89352.7</v>
       </c>
@@ -37209,7 +37248,7 @@
         <v>89182.7</v>
       </c>
       <c r="E50" s="130"/>
-      <c r="F50" s="162"/>
+      <c r="F50" s="159"/>
       <c r="G50" s="130">
         <v>89225.2</v>
       </c>
@@ -37235,7 +37274,7 @@
         <v>25290.799999999999</v>
       </c>
       <c r="E51" s="130"/>
-      <c r="F51" s="162"/>
+      <c r="F51" s="159"/>
       <c r="G51" s="130">
         <v>25372.1</v>
       </c>
@@ -37261,7 +37300,7 @@
         <v>35892.800000000003</v>
       </c>
       <c r="E52" s="130"/>
-      <c r="F52" s="162"/>
+      <c r="F52" s="159"/>
       <c r="G52" s="130"/>
       <c r="H52" s="131">
         <f t="shared" si="1"/>
@@ -37281,7 +37320,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="130"/>
-      <c r="F53" s="162"/>
+      <c r="F53" s="159"/>
       <c r="G53" s="130">
         <v>488.5</v>
       </c>
@@ -37305,7 +37344,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="133"/>
-      <c r="F54" s="162"/>
+      <c r="F54" s="159"/>
       <c r="G54" s="130">
         <v>649.9</v>
       </c>
@@ -37356,19 +37395,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="160" t="s">
         <v>1184</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
+      <c r="K1" s="160"/>
     </row>
     <row r="2" spans="1:11" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A2" s="134" t="s">
@@ -38101,16 +38140,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="160" t="s">
         <v>1185</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="150" t="s">

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2597" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6260444-4B2A-403D-B895-B1128DEFD2DC}"/>
+  <xr:revisionPtr revIDLastSave="2644" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{671B272E-058D-41BA-9C16-F8B3AC8C9731}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-7455" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5006" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5019" uniqueCount="1203">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -3638,6 +3638,24 @@
   </si>
   <si>
     <t>10192063</t>
+  </si>
+  <si>
+    <t>Kamstrup</t>
+  </si>
+  <si>
+    <t>FlowIQ2200</t>
+  </si>
+  <si>
+    <t>54554431</t>
+  </si>
+  <si>
+    <t>10192057</t>
+  </si>
+  <si>
+    <t>10192056</t>
+  </si>
+  <si>
+    <t>10191967</t>
   </si>
 </sst>
 </file>
@@ -5335,7 +5353,9 @@
       <c r="B2" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="2">
+        <v>14558066321</v>
+      </c>
       <c r="D2" s="2">
         <v>82929702</v>
       </c>
@@ -5348,14 +5368,18 @@
       <c r="G2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="2"/>
+      <c r="H2" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="I2" s="39" t="s">
         <v>22</v>
       </c>
       <c r="J2" s="9">
         <v>0</v>
       </c>
-      <c r="K2" s="2"/>
+      <c r="K2" s="4">
+        <v>46219</v>
+      </c>
       <c r="L2" s="11" t="b">
         <v>0</v>
       </c>
@@ -5383,7 +5407,9 @@
       <c r="B3" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2"/>
+      <c r="C3" s="2">
+        <v>14558069515</v>
+      </c>
       <c r="D3" s="2">
         <v>82929702</v>
       </c>
@@ -5396,14 +5422,18 @@
       <c r="G3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="2"/>
+      <c r="H3" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="I3" s="39" t="s">
         <v>22</v>
       </c>
       <c r="J3" s="9">
         <v>0</v>
       </c>
-      <c r="K3" s="2"/>
+      <c r="K3" s="4">
+        <v>46219</v>
+      </c>
       <c r="L3" s="11" t="b">
         <v>0</v>
       </c>
@@ -5431,7 +5461,9 @@
       <c r="B4" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="2"/>
+      <c r="C4" s="2">
+        <v>14558069051</v>
+      </c>
       <c r="D4" s="2">
         <v>82929702</v>
       </c>
@@ -5444,14 +5476,18 @@
       <c r="G4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="I4" s="39" t="s">
         <v>22</v>
       </c>
       <c r="J4" s="9">
         <v>0</v>
       </c>
-      <c r="K4" s="2"/>
+      <c r="K4" s="4">
+        <v>46219</v>
+      </c>
       <c r="L4" s="11" t="b">
         <v>0</v>
       </c>
@@ -5479,7 +5515,9 @@
       <c r="B5" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="2">
+        <v>14558069440</v>
+      </c>
       <c r="D5" s="2">
         <v>82929702</v>
       </c>
@@ -5492,14 +5530,18 @@
       <c r="G5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="2"/>
+      <c r="H5" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="I5" s="39" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="9">
         <v>0</v>
       </c>
-      <c r="K5" s="2"/>
+      <c r="K5" s="4">
+        <v>46219</v>
+      </c>
       <c r="L5" s="11" t="b">
         <v>0</v>
       </c>
@@ -5527,7 +5569,9 @@
       <c r="B6" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="2">
+        <v>14558068418</v>
+      </c>
       <c r="D6" s="2">
         <v>82929702</v>
       </c>
@@ -5540,14 +5584,18 @@
       <c r="G6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="2"/>
+      <c r="H6" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="I6" s="39" t="s">
         <v>22</v>
       </c>
       <c r="J6" s="9">
         <v>0</v>
       </c>
-      <c r="K6" s="2"/>
+      <c r="K6" s="4">
+        <v>46219</v>
+      </c>
       <c r="L6" s="11" t="b">
         <v>0</v>
       </c>
@@ -5575,7 +5623,9 @@
       <c r="B7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="C7" s="2">
+        <v>14558068459</v>
+      </c>
       <c r="D7" s="2">
         <v>82929702</v>
       </c>
@@ -5588,14 +5638,18 @@
       <c r="G7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="I7" s="39" t="s">
         <v>22</v>
       </c>
       <c r="J7" s="9">
         <v>0</v>
       </c>
-      <c r="K7" s="2"/>
+      <c r="K7" s="4">
+        <v>46219</v>
+      </c>
       <c r="L7" s="11" t="b">
         <v>0</v>
       </c>
@@ -5623,7 +5677,9 @@
       <c r="B8" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="2">
+        <v>14558069572</v>
+      </c>
       <c r="D8" s="2">
         <v>82929702</v>
       </c>
@@ -5636,14 +5692,18 @@
       <c r="G8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="I8" s="39" t="s">
         <v>22</v>
       </c>
       <c r="J8" s="9">
         <v>0</v>
       </c>
-      <c r="K8" s="2"/>
+      <c r="K8" s="4">
+        <v>46219</v>
+      </c>
       <c r="L8" s="11" t="b">
         <v>0</v>
       </c>
@@ -5671,7 +5731,9 @@
       <c r="B9" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="2"/>
+      <c r="C9" s="2">
+        <v>14558069408</v>
+      </c>
       <c r="D9" s="2">
         <v>82929702</v>
       </c>
@@ -5684,14 +5746,18 @@
       <c r="G9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="2"/>
+      <c r="H9" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="I9" s="39" t="s">
         <v>22</v>
       </c>
       <c r="J9" s="9">
         <v>0</v>
       </c>
-      <c r="K9" s="2"/>
+      <c r="K9" s="4">
+        <v>46219</v>
+      </c>
       <c r="L9" s="11" t="b">
         <v>0</v>
       </c>
@@ -5719,7 +5785,9 @@
       <c r="B10" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="2"/>
+      <c r="C10" s="2">
+        <v>14558069523</v>
+      </c>
       <c r="D10" s="2">
         <v>82929702</v>
       </c>
@@ -5732,14 +5800,18 @@
       <c r="G10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="2"/>
+      <c r="H10" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="I10" s="39" t="s">
         <v>22</v>
       </c>
       <c r="J10" s="9">
         <v>0</v>
       </c>
-      <c r="K10" s="2"/>
+      <c r="K10" s="4">
+        <v>46219</v>
+      </c>
       <c r="L10" s="11" t="b">
         <v>0</v>
       </c>
@@ -23887,7 +23959,9 @@
       <c r="B175" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="C175" s="53"/>
+      <c r="C175" s="53" t="s">
+        <v>1202</v>
+      </c>
       <c r="D175" s="53" t="s">
         <v>283</v>
       </c>
@@ -23897,10 +23971,14 @@
       <c r="F175" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="G175" s="3"/>
-      <c r="H175" s="3"/>
+      <c r="G175" s="3">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="H175" s="57">
+        <v>46219</v>
+      </c>
       <c r="I175" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J175" s="63" t="s">
         <v>244</v>
@@ -23932,18 +24010,24 @@
       <c r="B176" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="C176" s="53"/>
+      <c r="C176" s="53" t="s">
+        <v>1199</v>
+      </c>
       <c r="D176" s="53" t="s">
-        <v>283</v>
+        <v>1197</v>
       </c>
       <c r="E176" s="53" t="s">
-        <v>284</v>
+        <v>1198</v>
       </c>
       <c r="F176" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="G176" s="3"/>
-      <c r="H176" s="3"/>
+      <c r="G176" s="3">
+        <v>0.161</v>
+      </c>
+      <c r="H176" s="57">
+        <v>46219</v>
+      </c>
       <c r="I176" s="21" t="b">
         <v>0</v>
       </c>
@@ -24028,7 +24112,9 @@
       <c r="B178" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="C178" s="53"/>
+      <c r="C178" s="53" t="s">
+        <v>1200</v>
+      </c>
       <c r="D178" s="53" t="s">
         <v>283</v>
       </c>
@@ -24038,10 +24124,14 @@
       <c r="F178" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="G178" s="3"/>
-      <c r="H178" s="3"/>
+      <c r="G178" s="3">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="H178" s="57">
+        <v>46219</v>
+      </c>
       <c r="I178" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J178" s="63" t="s">
         <v>250</v>
@@ -24073,7 +24163,9 @@
       <c r="B179" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="C179" s="53"/>
+      <c r="C179" s="53" t="s">
+        <v>1201</v>
+      </c>
       <c r="D179" s="53" t="s">
         <v>283</v>
       </c>
@@ -24083,10 +24175,14 @@
       <c r="F179" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="G179" s="3"/>
-      <c r="H179" s="3"/>
+      <c r="G179" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="H179" s="57">
+        <v>46219</v>
+      </c>
       <c r="I179" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J179" s="63" t="s">
         <v>250</v>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2745" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD9F566C-F058-4A88-B16A-1AEEDA2C67FB}"/>
+  <xr:revisionPtr revIDLastSave="2772" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62980A75-8457-4502-B976-4FDC60B88EDD}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-7455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,6 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FS Water'!$A$1:$Q$193</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5036" uniqueCount="1204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5044" uniqueCount="1204">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -4761,14 +4762,14 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6556,7 +6557,7 @@
       <c r="B24" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="161">
+      <c r="C24" s="159">
         <v>14558068921</v>
       </c>
       <c r="D24" s="2">
@@ -9768,7 +9769,7 @@
       <c r="B83" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C83" s="161">
+      <c r="C83" s="159">
         <v>14558069077</v>
       </c>
       <c r="D83" s="2">
@@ -13232,7 +13233,9 @@
       <c r="B147" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C147" s="2"/>
+      <c r="C147" s="2">
+        <v>14558069812</v>
+      </c>
       <c r="D147" s="2">
         <v>71205556</v>
       </c>
@@ -13245,14 +13248,18 @@
       <c r="G147" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H147" s="2"/>
+      <c r="H147" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="I147" s="31" t="s">
         <v>46</v>
       </c>
       <c r="J147" s="9">
         <v>0</v>
       </c>
-      <c r="K147" s="2"/>
+      <c r="K147" s="4">
+        <v>46224</v>
+      </c>
       <c r="L147" s="11" t="b">
         <v>0</v>
       </c>
@@ -13328,7 +13335,9 @@
       <c r="B149" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C149" s="2"/>
+      <c r="C149" s="2">
+        <v>14558069754</v>
+      </c>
       <c r="D149" s="2">
         <v>71205556</v>
       </c>
@@ -13341,14 +13350,18 @@
       <c r="G149" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H149" s="2"/>
+      <c r="H149" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="I149" s="31" t="s">
         <v>46</v>
       </c>
       <c r="J149" s="9">
         <v>0</v>
       </c>
-      <c r="K149" s="2"/>
+      <c r="K149" s="4">
+        <v>46224</v>
+      </c>
       <c r="L149" s="11" t="b">
         <v>0</v>
       </c>
@@ -13376,7 +13389,9 @@
       <c r="B150" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C150" s="2"/>
+      <c r="C150" s="2">
+        <v>14558067931</v>
+      </c>
       <c r="D150" s="2">
         <v>71205556</v>
       </c>
@@ -13389,14 +13404,18 @@
       <c r="G150" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H150" s="2"/>
+      <c r="H150" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="I150" s="31" t="s">
         <v>46</v>
       </c>
       <c r="J150" s="9">
         <v>0</v>
       </c>
-      <c r="K150" s="2"/>
+      <c r="K150" s="4">
+        <v>46224</v>
+      </c>
       <c r="L150" s="11" t="b">
         <v>0</v>
       </c>
@@ -13424,7 +13443,9 @@
       <c r="B151" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C151" s="2"/>
+      <c r="C151" s="2">
+        <v>14558069788</v>
+      </c>
       <c r="D151" s="2">
         <v>71205556</v>
       </c>
@@ -13437,14 +13458,18 @@
       <c r="G151" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H151" s="2"/>
+      <c r="H151" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="I151" s="31" t="s">
         <v>46</v>
       </c>
       <c r="J151" s="9">
         <v>0</v>
       </c>
-      <c r="K151" s="2"/>
+      <c r="K151" s="4">
+        <v>46224</v>
+      </c>
       <c r="L151" s="11" t="b">
         <v>0</v>
       </c>
@@ -13472,7 +13497,9 @@
       <c r="B152" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C152" s="2"/>
+      <c r="C152" s="2">
+        <v>14558067956</v>
+      </c>
       <c r="D152" s="2">
         <v>71205556</v>
       </c>
@@ -13485,14 +13512,18 @@
       <c r="G152" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H152" s="2"/>
+      <c r="H152" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="I152" s="31" t="s">
         <v>46</v>
       </c>
       <c r="J152" s="9">
         <v>0</v>
       </c>
-      <c r="K152" s="2"/>
+      <c r="K152" s="4">
+        <v>46224</v>
+      </c>
       <c r="L152" s="11" t="b">
         <v>0</v>
       </c>
@@ -13520,7 +13551,9 @@
       <c r="B153" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C153" s="2"/>
+      <c r="C153" s="2">
+        <v>14558069747</v>
+      </c>
       <c r="D153" s="2">
         <v>71205556</v>
       </c>
@@ -13533,14 +13566,18 @@
       <c r="G153" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H153" s="2"/>
+      <c r="H153" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="I153" s="31" t="s">
         <v>46</v>
       </c>
       <c r="J153" s="9">
         <v>0</v>
       </c>
-      <c r="K153" s="2"/>
+      <c r="K153" s="4">
+        <v>46224</v>
+      </c>
       <c r="L153" s="11" t="b">
         <v>0</v>
       </c>
@@ -13568,7 +13605,9 @@
       <c r="B154" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C154" s="2"/>
+      <c r="C154" s="2">
+        <v>14558069879</v>
+      </c>
       <c r="D154" s="2">
         <v>71205556</v>
       </c>
@@ -13581,14 +13620,18 @@
       <c r="G154" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H154" s="2"/>
+      <c r="H154" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="I154" s="31" t="s">
         <v>46</v>
       </c>
       <c r="J154" s="9">
         <v>0</v>
       </c>
-      <c r="K154" s="2"/>
+      <c r="K154" s="4">
+        <v>46224</v>
+      </c>
       <c r="L154" s="11" t="b">
         <v>0</v>
       </c>
@@ -13616,7 +13659,9 @@
       <c r="B155" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C155" s="2"/>
+      <c r="C155" s="2">
+        <v>14558069861</v>
+      </c>
       <c r="D155" s="2">
         <v>71205556</v>
       </c>
@@ -13629,14 +13674,18 @@
       <c r="G155" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H155" s="2"/>
+      <c r="H155" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="I155" s="31" t="s">
         <v>46</v>
       </c>
       <c r="J155" s="9">
         <v>0</v>
       </c>
-      <c r="K155" s="2"/>
+      <c r="K155" s="4">
+        <v>46224</v>
+      </c>
       <c r="L155" s="11" t="b">
         <v>0</v>
       </c>
@@ -15747,12 +15796,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.46484375" customWidth="1"/>
-    <col min="3" max="3" width="30.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.86328125" customWidth="1"/>
     <col min="4" max="4" width="21.59765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.73046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.59765625" bestFit="1" customWidth="1"/>
@@ -15820,7 +15870,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>116</v>
       </c>
@@ -15865,7 +15915,7 @@
       </c>
       <c r="Q2" s="17"/>
     </row>
-    <row r="3" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>119</v>
       </c>
@@ -15910,7 +15960,7 @@
       </c>
       <c r="Q3" s="17"/>
     </row>
-    <row r="4" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
         <v>120</v>
       </c>
@@ -15955,7 +16005,7 @@
       </c>
       <c r="Q4" s="17"/>
     </row>
-    <row r="5" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
         <v>122</v>
       </c>
@@ -16000,7 +16050,7 @@
       </c>
       <c r="Q5" s="17"/>
     </row>
-    <row r="6" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
         <v>123</v>
       </c>
@@ -16045,7 +16095,7 @@
       </c>
       <c r="Q6" s="17"/>
     </row>
-    <row r="7" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
         <v>124</v>
       </c>
@@ -16090,7 +16140,7 @@
       </c>
       <c r="Q7" s="17"/>
     </row>
-    <row r="8" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
         <v>125</v>
       </c>
@@ -16135,7 +16185,7 @@
       </c>
       <c r="Q8" s="17"/>
     </row>
-    <row r="9" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
         <v>126</v>
       </c>
@@ -16180,7 +16230,7 @@
       </c>
       <c r="Q9" s="17"/>
     </row>
-    <row r="10" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
         <v>127</v>
       </c>
@@ -16225,7 +16275,7 @@
       </c>
       <c r="Q10" s="17"/>
     </row>
-    <row r="11" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
         <v>150</v>
       </c>
@@ -16270,7 +16320,7 @@
       </c>
       <c r="Q11" s="17"/>
     </row>
-    <row r="12" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
         <v>152</v>
       </c>
@@ -16315,7 +16365,7 @@
       </c>
       <c r="Q12" s="17"/>
     </row>
-    <row r="13" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="s">
         <v>153</v>
       </c>
@@ -16360,7 +16410,7 @@
       </c>
       <c r="Q13" s="17"/>
     </row>
-    <row r="14" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="23" t="s">
         <v>154</v>
       </c>
@@ -16405,7 +16455,7 @@
       </c>
       <c r="Q14" s="17"/>
     </row>
-    <row r="15" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>155</v>
       </c>
@@ -16450,7 +16500,7 @@
       </c>
       <c r="Q15" s="17"/>
     </row>
-    <row r="16" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
         <v>156</v>
       </c>
@@ -16495,7 +16545,7 @@
       </c>
       <c r="Q16" s="17"/>
     </row>
-    <row r="17" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
         <v>157</v>
       </c>
@@ -16540,7 +16590,7 @@
       </c>
       <c r="Q17" s="17"/>
     </row>
-    <row r="18" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="23" t="s">
         <v>158</v>
       </c>
@@ -16585,7 +16635,7 @@
       </c>
       <c r="Q18" s="17"/>
     </row>
-    <row r="19" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="23" t="s">
         <v>160</v>
       </c>
@@ -16630,7 +16680,7 @@
       </c>
       <c r="Q19" s="17"/>
     </row>
-    <row r="20" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="23" t="s">
         <v>181</v>
       </c>
@@ -16675,7 +16725,7 @@
       </c>
       <c r="Q20" s="17"/>
     </row>
-    <row r="21" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="s">
         <v>183</v>
       </c>
@@ -16720,7 +16770,7 @@
       </c>
       <c r="Q21" s="17"/>
     </row>
-    <row r="22" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="23" t="s">
         <v>185</v>
       </c>
@@ -16765,7 +16815,7 @@
       </c>
       <c r="Q22" s="17"/>
     </row>
-    <row r="23" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="s">
         <v>186</v>
       </c>
@@ -16810,7 +16860,7 @@
       </c>
       <c r="Q23" s="17"/>
     </row>
-    <row r="24" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="23" t="s">
         <v>187</v>
       </c>
@@ -16855,7 +16905,7 @@
       </c>
       <c r="Q24" s="17"/>
     </row>
-    <row r="25" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="23" t="s">
         <v>188</v>
       </c>
@@ -16900,7 +16950,7 @@
       </c>
       <c r="Q25" s="17"/>
     </row>
-    <row r="26" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
         <v>203</v>
       </c>
@@ -16945,7 +16995,7 @@
       </c>
       <c r="Q26" s="17"/>
     </row>
-    <row r="27" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="23" t="s">
         <v>205</v>
       </c>
@@ -16990,7 +17040,7 @@
       </c>
       <c r="Q27" s="17"/>
     </row>
-    <row r="28" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="23" t="s">
         <v>206</v>
       </c>
@@ -17035,7 +17085,7 @@
       </c>
       <c r="Q28" s="17"/>
     </row>
-    <row r="29" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="s">
         <v>207</v>
       </c>
@@ -17080,7 +17130,7 @@
       </c>
       <c r="Q29" s="17"/>
     </row>
-    <row r="30" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23" t="s">
         <v>208</v>
       </c>
@@ -17125,7 +17175,7 @@
       </c>
       <c r="Q30" s="17"/>
     </row>
-    <row r="31" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
         <v>209</v>
       </c>
@@ -17170,7 +17220,7 @@
       </c>
       <c r="Q31" s="17"/>
     </row>
-    <row r="32" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="23" t="s">
         <v>210</v>
       </c>
@@ -17215,7 +17265,7 @@
       </c>
       <c r="Q32" s="17"/>
     </row>
-    <row r="33" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="23" t="s">
         <v>211</v>
       </c>
@@ -17260,7 +17310,7 @@
       </c>
       <c r="Q33" s="17"/>
     </row>
-    <row r="34" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
         <v>212</v>
       </c>
@@ -20881,7 +20931,7 @@
         <v>46216</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="s">
         <v>139</v>
       </c>
@@ -20979,7 +21029,7 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="23" t="s">
         <v>141</v>
       </c>
@@ -21075,7 +21125,7 @@
       </c>
       <c r="Q108" s="17"/>
     </row>
-    <row r="109" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="23" t="s">
         <v>144</v>
       </c>
@@ -21173,7 +21223,7 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="23" t="s">
         <v>146</v>
       </c>
@@ -21269,7 +21319,7 @@
       </c>
       <c r="Q112" s="17"/>
     </row>
-    <row r="113" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="23" t="s">
         <v>105</v>
       </c>
@@ -21365,7 +21415,7 @@
       </c>
       <c r="Q114" s="17"/>
     </row>
-    <row r="115" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="23" t="s">
         <v>108</v>
       </c>
@@ -21461,7 +21511,7 @@
       </c>
       <c r="Q116" s="17"/>
     </row>
-    <row r="117" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="23" t="s">
         <v>109</v>
       </c>
@@ -21557,7 +21607,7 @@
       </c>
       <c r="Q118" s="17"/>
     </row>
-    <row r="119" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="23" t="s">
         <v>111</v>
       </c>
@@ -21653,7 +21703,7 @@
       </c>
       <c r="Q120" s="17"/>
     </row>
-    <row r="121" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="23" t="s">
         <v>113</v>
       </c>
@@ -21749,7 +21799,7 @@
       </c>
       <c r="Q122" s="17"/>
     </row>
-    <row r="123" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="23" t="s">
         <v>74</v>
       </c>
@@ -21845,7 +21895,7 @@
       </c>
       <c r="Q124" s="17"/>
     </row>
-    <row r="125" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="23" t="s">
         <v>77</v>
       </c>
@@ -21943,7 +21993,7 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="23" t="s">
         <v>81</v>
       </c>
@@ -22039,7 +22089,7 @@
       </c>
       <c r="Q128" s="17"/>
     </row>
-    <row r="129" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="23" t="s">
         <v>83</v>
       </c>
@@ -22084,7 +22134,7 @@
       </c>
       <c r="Q129" s="17"/>
     </row>
-    <row r="130" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="23" t="s">
         <v>84</v>
       </c>
@@ -22129,7 +22179,7 @@
       </c>
       <c r="Q130" s="17"/>
     </row>
-    <row r="131" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="23" t="s">
         <v>85</v>
       </c>
@@ -22174,7 +22224,7 @@
       </c>
       <c r="Q131" s="17"/>
     </row>
-    <row r="132" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="23" t="s">
         <v>86</v>
       </c>
@@ -22219,7 +22269,7 @@
       </c>
       <c r="Q132" s="17"/>
     </row>
-    <row r="133" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="23" t="s">
         <v>260</v>
       </c>
@@ -22264,7 +22314,7 @@
       </c>
       <c r="Q133" s="17"/>
     </row>
-    <row r="134" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="23" t="s">
         <v>263</v>
       </c>
@@ -22309,7 +22359,7 @@
       </c>
       <c r="Q134" s="17"/>
     </row>
-    <row r="135" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="23" t="s">
         <v>264</v>
       </c>
@@ -22354,7 +22404,7 @@
       </c>
       <c r="Q135" s="17"/>
     </row>
-    <row r="136" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="23" t="s">
         <v>265</v>
       </c>
@@ -22399,7 +22449,7 @@
       </c>
       <c r="Q136" s="17"/>
     </row>
-    <row r="137" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="23" t="s">
         <v>266</v>
       </c>
@@ -22444,7 +22494,7 @@
       </c>
       <c r="Q137" s="17"/>
     </row>
-    <row r="138" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="23" t="s">
         <v>267</v>
       </c>
@@ -22489,7 +22539,7 @@
       </c>
       <c r="Q138" s="17"/>
     </row>
-    <row r="139" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="23" t="s">
         <v>268</v>
       </c>
@@ -22534,7 +22584,7 @@
       </c>
       <c r="Q139" s="17"/>
     </row>
-    <row r="140" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="23" t="s">
         <v>269</v>
       </c>
@@ -22579,7 +22629,7 @@
       </c>
       <c r="Q140" s="17"/>
     </row>
-    <row r="141" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="23" t="s">
         <v>35</v>
       </c>
@@ -22624,7 +22674,7 @@
       </c>
       <c r="Q141" s="17"/>
     </row>
-    <row r="142" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="23" t="s">
         <v>38</v>
       </c>
@@ -22669,7 +22719,7 @@
       </c>
       <c r="Q142" s="17"/>
     </row>
-    <row r="143" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="23" t="s">
         <v>40</v>
       </c>
@@ -22714,7 +22764,7 @@
       </c>
       <c r="Q143" s="17"/>
     </row>
-    <row r="144" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="23" t="s">
         <v>41</v>
       </c>
@@ -22759,7 +22809,7 @@
       </c>
       <c r="Q144" s="17"/>
     </row>
-    <row r="145" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="23" t="s">
         <v>42</v>
       </c>
@@ -22804,7 +22854,7 @@
       </c>
       <c r="Q145" s="17"/>
     </row>
-    <row r="146" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="23" t="s">
         <v>43</v>
       </c>
@@ -22849,7 +22899,7 @@
       </c>
       <c r="Q146" s="17"/>
     </row>
-    <row r="147" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="23" t="s">
         <v>45</v>
       </c>
@@ -22894,7 +22944,7 @@
       </c>
       <c r="Q147" s="17"/>
     </row>
-    <row r="148" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="23" t="s">
         <v>44</v>
       </c>
@@ -22939,7 +22989,7 @@
       </c>
       <c r="Q148" s="17"/>
     </row>
-    <row r="149" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="23" t="s">
         <v>47</v>
       </c>
@@ -22984,7 +23034,7 @@
       </c>
       <c r="Q149" s="17"/>
     </row>
-    <row r="150" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="23" t="s">
         <v>48</v>
       </c>
@@ -23029,7 +23079,7 @@
       </c>
       <c r="Q150" s="17"/>
     </row>
-    <row r="151" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="23" t="s">
         <v>49</v>
       </c>
@@ -23074,7 +23124,7 @@
       </c>
       <c r="Q151" s="17"/>
     </row>
-    <row r="152" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="23" t="s">
         <v>50</v>
       </c>
@@ -23119,7 +23169,7 @@
       </c>
       <c r="Q152" s="17"/>
     </row>
-    <row r="153" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="23" t="s">
         <v>51</v>
       </c>
@@ -23164,7 +23214,7 @@
       </c>
       <c r="Q153" s="17"/>
     </row>
-    <row r="154" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="23" t="s">
         <v>52</v>
       </c>
@@ -23209,7 +23259,7 @@
       </c>
       <c r="Q154" s="17"/>
     </row>
-    <row r="155" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="23" t="s">
         <v>53</v>
       </c>
@@ -23254,7 +23304,7 @@
       </c>
       <c r="Q155" s="17"/>
     </row>
-    <row r="156" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="23" t="s">
         <v>54</v>
       </c>
@@ -23299,7 +23349,7 @@
       </c>
       <c r="Q156" s="17"/>
     </row>
-    <row r="157" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="23" t="s">
         <v>57</v>
       </c>
@@ -23344,7 +23394,7 @@
       </c>
       <c r="Q157" s="17"/>
     </row>
-    <row r="158" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="23" t="s">
         <v>58</v>
       </c>
@@ -23389,7 +23439,7 @@
       </c>
       <c r="Q158" s="17"/>
     </row>
-    <row r="159" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="23" t="s">
         <v>59</v>
       </c>
@@ -23434,7 +23484,7 @@
       </c>
       <c r="Q159" s="17"/>
     </row>
-    <row r="160" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="23" t="s">
         <v>60</v>
       </c>
@@ -23479,7 +23529,7 @@
       </c>
       <c r="Q160" s="17"/>
     </row>
-    <row r="161" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="23" t="s">
         <v>61</v>
       </c>
@@ -23524,7 +23574,7 @@
       </c>
       <c r="Q161" s="17"/>
     </row>
-    <row r="162" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="23" t="s">
         <v>62</v>
       </c>
@@ -23569,7 +23619,7 @@
       </c>
       <c r="Q162" s="17"/>
     </row>
-    <row r="163" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="23" t="s">
         <v>63</v>
       </c>
@@ -23614,7 +23664,7 @@
       </c>
       <c r="Q163" s="17"/>
     </row>
-    <row r="164" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="23" t="s">
         <v>87</v>
       </c>
@@ -23659,7 +23709,7 @@
       </c>
       <c r="Q164" s="17"/>
     </row>
-    <row r="165" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="23" t="s">
         <v>90</v>
       </c>
@@ -23704,7 +23754,7 @@
       </c>
       <c r="Q165" s="17"/>
     </row>
-    <row r="166" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="23" t="s">
         <v>91</v>
       </c>
@@ -23749,7 +23799,7 @@
       </c>
       <c r="Q166" s="17"/>
     </row>
-    <row r="167" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="23" t="s">
         <v>92</v>
       </c>
@@ -23794,7 +23844,7 @@
       </c>
       <c r="Q167" s="17"/>
     </row>
-    <row r="168" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="23" t="s">
         <v>93</v>
       </c>
@@ -23839,7 +23889,7 @@
       </c>
       <c r="Q168" s="17"/>
     </row>
-    <row r="169" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="23" t="s">
         <v>94</v>
       </c>
@@ -23884,7 +23934,7 @@
       </c>
       <c r="Q169" s="17"/>
     </row>
-    <row r="170" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="23" t="s">
         <v>95</v>
       </c>
@@ -23929,7 +23979,7 @@
       </c>
       <c r="Q170" s="17"/>
     </row>
-    <row r="171" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="23" t="s">
         <v>220</v>
       </c>
@@ -23974,7 +24024,7 @@
       </c>
       <c r="Q171" s="17"/>
     </row>
-    <row r="172" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="23" t="s">
         <v>223</v>
       </c>
@@ -24019,7 +24069,7 @@
       </c>
       <c r="Q172" s="17"/>
     </row>
-    <row r="173" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="23" t="s">
         <v>224</v>
       </c>
@@ -24064,7 +24114,7 @@
       </c>
       <c r="Q173" s="17"/>
     </row>
-    <row r="174" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="23" t="s">
         <v>225</v>
       </c>
@@ -24466,7 +24516,7 @@
       </c>
       <c r="Q181" s="17"/>
     </row>
-    <row r="182" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="23" t="s">
         <v>219</v>
       </c>
@@ -24511,7 +24561,7 @@
       </c>
       <c r="Q182" s="17"/>
     </row>
-    <row r="183" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="23" t="s">
         <v>64</v>
       </c>
@@ -25072,6 +25122,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q193" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N193">
     <sortCondition ref="A2:A193"/>
   </sortState>
@@ -35129,34 +35186,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A1" s="159" t="s">
+      <c r="A1" s="160" t="s">
         <v>1170</v>
       </c>
-      <c r="B1" s="159" t="s">
+      <c r="B1" s="160" t="s">
         <v>1171</v>
       </c>
-      <c r="C1" s="159" t="s">
+      <c r="C1" s="160" t="s">
         <v>1172</v>
       </c>
-      <c r="D1" s="160" t="s">
+      <c r="D1" s="161" t="s">
         <v>1173</v>
       </c>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160" t="s">
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161" t="s">
         <v>1174</v>
       </c>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
       <c r="J1" s="108"/>
       <c r="K1" s="109" t="s">
         <v>1175</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A2" s="159"/>
-      <c r="B2" s="159"/>
-      <c r="C2" s="159"/>
+      <c r="A2" s="160"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
       <c r="D2" s="107" t="s">
         <v>1176</v>
       </c>
@@ -37676,19 +37733,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="159" t="s">
+      <c r="A1" s="160" t="s">
         <v>1197</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
-      <c r="G1" s="159"/>
-      <c r="H1" s="159"/>
-      <c r="I1" s="159"/>
-      <c r="J1" s="159"/>
-      <c r="K1" s="159"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
+      <c r="K1" s="160"/>
     </row>
     <row r="2" spans="1:11" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A2" s="134" t="s">
@@ -38421,16 +38478,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="159" t="s">
+      <c r="A1" s="160" t="s">
         <v>1198</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
-      <c r="G1" s="159"/>
-      <c r="H1" s="159"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="150" t="s">

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2772" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62980A75-8457-4502-B976-4FDC60B88EDD}"/>
+  <xr:revisionPtr revIDLastSave="2790" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C34928C-039F-478B-A0BD-B91D78B154EC}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-7455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="21720" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FS Elec" sheetId="4" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5044" uniqueCount="1204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5050" uniqueCount="1204">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -12939,7 +12939,9 @@
       <c r="B141" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C141" s="2"/>
+      <c r="C141" s="2">
+        <v>14558069556</v>
+      </c>
       <c r="D141" s="2">
         <v>71205556</v>
       </c>
@@ -12952,14 +12954,18 @@
       <c r="G141" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H141" s="2"/>
+      <c r="H141" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="I141" s="30" t="s">
         <v>36</v>
       </c>
       <c r="J141" s="9">
         <v>0</v>
       </c>
-      <c r="K141" s="2"/>
+      <c r="K141" s="4">
+        <v>46224</v>
+      </c>
       <c r="L141" s="11" t="b">
         <v>0</v>
       </c>
@@ -12987,7 +12993,9 @@
       <c r="B142" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C142" s="2"/>
+      <c r="C142" s="2">
+        <v>14558069721</v>
+      </c>
       <c r="D142" s="2">
         <v>71205556</v>
       </c>
@@ -13000,14 +13008,18 @@
       <c r="G142" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H142" s="2"/>
+      <c r="H142" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="I142" s="30" t="s">
         <v>36</v>
       </c>
       <c r="J142" s="9">
         <v>0</v>
       </c>
-      <c r="K142" s="2"/>
+      <c r="K142" s="4">
+        <v>46224</v>
+      </c>
       <c r="L142" s="11" t="b">
         <v>0</v>
       </c>
@@ -13035,7 +13047,9 @@
       <c r="B143" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C143" s="2"/>
+      <c r="C143" s="2">
+        <v>14558068038</v>
+      </c>
       <c r="D143" s="2">
         <v>71205556</v>
       </c>
@@ -13048,14 +13062,18 @@
       <c r="G143" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H143" s="2"/>
+      <c r="H143" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="I143" s="30" t="s">
         <v>36</v>
       </c>
       <c r="J143" s="9">
         <v>0</v>
       </c>
-      <c r="K143" s="2"/>
+      <c r="K143" s="4">
+        <v>46224</v>
+      </c>
       <c r="L143" s="11" t="b">
         <v>0</v>
       </c>
@@ -13083,7 +13101,9 @@
       <c r="B144" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C144" s="2"/>
+      <c r="C144" s="2">
+        <v>14558069135</v>
+      </c>
       <c r="D144" s="2">
         <v>71205556</v>
       </c>
@@ -13096,14 +13116,18 @@
       <c r="G144" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H144" s="2"/>
+      <c r="H144" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="I144" s="30" t="s">
         <v>36</v>
       </c>
       <c r="J144" s="9">
         <v>0</v>
       </c>
-      <c r="K144" s="2"/>
+      <c r="K144" s="4">
+        <v>46224</v>
+      </c>
       <c r="L144" s="11" t="b">
         <v>0</v>
       </c>
@@ -13131,7 +13155,9 @@
       <c r="B145" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C145" s="2"/>
+      <c r="C145" s="2">
+        <v>14558068103</v>
+      </c>
       <c r="D145" s="2">
         <v>71205556</v>
       </c>
@@ -13144,14 +13170,18 @@
       <c r="G145" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H145" s="2"/>
+      <c r="H145" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="I145" s="30" t="s">
         <v>36</v>
       </c>
       <c r="J145" s="9">
         <v>0</v>
       </c>
-      <c r="K145" s="2"/>
+      <c r="K145" s="4">
+        <v>46224</v>
+      </c>
       <c r="L145" s="11" t="b">
         <v>0</v>
       </c>
@@ -13287,7 +13317,9 @@
       <c r="B148" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C148" s="2"/>
+      <c r="C148" s="2">
+        <v>14558069838</v>
+      </c>
       <c r="D148" s="2">
         <v>71205556</v>
       </c>
@@ -13300,14 +13332,18 @@
       <c r="G148" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H148" s="2"/>
+      <c r="H148" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="I148" s="30" t="s">
         <v>36</v>
       </c>
       <c r="J148" s="9">
         <v>0</v>
       </c>
-      <c r="K148" s="2"/>
+      <c r="K148" s="4">
+        <v>46224</v>
+      </c>
       <c r="L148" s="11" t="b">
         <v>0</v>
       </c>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2790" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C34928C-039F-478B-A0BD-B91D78B154EC}"/>
+  <xr:revisionPtr revIDLastSave="3005" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7467957-B839-4D09-90B9-38C40F023491}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="21720" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="-8550" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FS Elec" sheetId="4" r:id="rId1"/>
@@ -20,14 +20,14 @@
     <sheet name="Kiosk Plan" sheetId="5" r:id="rId5"/>
     <sheet name="Temp ME162 open and closings" sheetId="2" r:id="rId6"/>
     <sheet name="Elec Meters for invoicing" sheetId="6" r:id="rId7"/>
-    <sheet name="Water Meters for invoicing" sheetId="7" r:id="rId8"/>
+    <sheet name="Water invoice 1" sheetId="7" r:id="rId8"/>
+    <sheet name="Water invoice 2" sheetId="10" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FS Elec'!$A$1:$R$192</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FS Water'!$A$1:$Q$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FS Elec'!$A$1:$T$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FS Water'!$A$1:$S$193</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5050" uniqueCount="1204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5560" uniqueCount="1223">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -3660,6 +3660,63 @@
   </si>
   <si>
     <t>9898001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handover Date </t>
+  </si>
+  <si>
+    <t>Closing Reading</t>
+  </si>
+  <si>
+    <t>TBC</t>
+  </si>
+  <si>
+    <t>3.47</t>
+  </si>
+  <si>
+    <t>3.19</t>
+  </si>
+  <si>
+    <t>11.05</t>
+  </si>
+  <si>
+    <t>4.42</t>
+  </si>
+  <si>
+    <t>8.92</t>
+  </si>
+  <si>
+    <t>7.78</t>
+  </si>
+  <si>
+    <t>7.59</t>
+  </si>
+  <si>
+    <t>14.26</t>
+  </si>
+  <si>
+    <t>11.58</t>
+  </si>
+  <si>
+    <t>8.42</t>
+  </si>
+  <si>
+    <t>4.56</t>
+  </si>
+  <si>
+    <t>4.73</t>
+  </si>
+  <si>
+    <t>23.56</t>
+  </si>
+  <si>
+    <t>4.43</t>
+  </si>
+  <si>
+    <t>13.63</t>
+  </si>
+  <si>
+    <t>10.17</t>
   </si>
 </sst>
 </file>
@@ -4282,7 +4339,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="37" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4771,13 +4828,88 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Excel Built-in Good" xfId="2" xr:uid="{73A7683C-93AE-4DD2-A667-1D9B92981758}"/>
     <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{EDB79C3E-33DC-4A47-B5C8-E4BE66ABEE17}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5278,7 +5410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB9F803-2DDE-485F-989C-C0688D786923}">
-  <dimension ref="A1:R192"/>
+  <dimension ref="A1:T192"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.3984375" style="5" bestFit="1" customWidth="1"/>
@@ -5296,9 +5428,11 @@
     <col min="13" max="13" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.3984375" bestFit="1" customWidth="1"/>
     <col min="15" max="18" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5353,8 +5487,14 @@
       <c r="R1" s="22" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S1" s="162" t="s">
+        <v>1204</v>
+      </c>
+      <c r="T1" s="162" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>116</v>
       </c>
@@ -5407,8 +5547,10 @@
       <c r="R2" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S2" s="163"/>
+      <c r="T2" s="163"/>
+    </row>
+    <row r="3" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>119</v>
       </c>
@@ -5461,8 +5603,10 @@
       <c r="R3" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S3" s="163"/>
+      <c r="T3" s="163"/>
+    </row>
+    <row r="4" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>120</v>
       </c>
@@ -5515,8 +5659,10 @@
       <c r="R4" s="65">
         <v>46240</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S4" s="163"/>
+      <c r="T4" s="163"/>
+    </row>
+    <row r="5" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>122</v>
       </c>
@@ -5569,8 +5715,10 @@
       <c r="R5" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S5" s="163"/>
+      <c r="T5" s="163"/>
+    </row>
+    <row r="6" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>123</v>
       </c>
@@ -5623,8 +5771,10 @@
       <c r="R6" s="65">
         <v>46240</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S6" s="163"/>
+      <c r="T6" s="163"/>
+    </row>
+    <row r="7" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>124</v>
       </c>
@@ -5677,8 +5827,10 @@
       <c r="R7" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S7" s="163"/>
+      <c r="T7" s="163"/>
+    </row>
+    <row r="8" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>125</v>
       </c>
@@ -5731,8 +5883,10 @@
       <c r="R8" s="65">
         <v>46240</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S8" s="163"/>
+      <c r="T8" s="163"/>
+    </row>
+    <row r="9" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>126</v>
       </c>
@@ -5785,8 +5939,10 @@
       <c r="R9" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S9" s="163"/>
+      <c r="T9" s="163"/>
+    </row>
+    <row r="10" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>127</v>
       </c>
@@ -5839,8 +5995,10 @@
       <c r="R10" s="65">
         <v>46240</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S10" s="163"/>
+      <c r="T10" s="163"/>
+    </row>
+    <row r="11" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>150</v>
       </c>
@@ -5893,8 +6051,10 @@
       <c r="R11" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S11" s="163"/>
+      <c r="T11" s="163"/>
+    </row>
+    <row r="12" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>152</v>
       </c>
@@ -5947,8 +6107,10 @@
       <c r="R12" s="65">
         <v>46240</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S12" s="163"/>
+      <c r="T12" s="163"/>
+    </row>
+    <row r="13" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
         <v>153</v>
       </c>
@@ -6001,8 +6163,10 @@
       <c r="R13" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S13" s="163"/>
+      <c r="T13" s="163"/>
+    </row>
+    <row r="14" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>154</v>
       </c>
@@ -6055,8 +6219,10 @@
       <c r="R14" s="65">
         <v>46240</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S14" s="163"/>
+      <c r="T14" s="163"/>
+    </row>
+    <row r="15" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>155</v>
       </c>
@@ -6109,8 +6275,10 @@
       <c r="R15" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S15" s="163"/>
+      <c r="T15" s="163"/>
+    </row>
+    <row r="16" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>156</v>
       </c>
@@ -6163,8 +6331,10 @@
       <c r="R16" s="65">
         <v>46240</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S16" s="163"/>
+      <c r="T16" s="163"/>
+    </row>
+    <row r="17" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
         <v>157</v>
       </c>
@@ -6217,8 +6387,10 @@
       <c r="R17" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S17" s="163"/>
+      <c r="T17" s="163"/>
+    </row>
+    <row r="18" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>158</v>
       </c>
@@ -6271,8 +6443,10 @@
       <c r="R18" s="65">
         <v>46224</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S18" s="163"/>
+      <c r="T18" s="163"/>
+    </row>
+    <row r="19" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
         <v>160</v>
       </c>
@@ -6325,8 +6499,10 @@
       <c r="R19" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S19" s="163"/>
+      <c r="T19" s="163"/>
+    </row>
+    <row r="20" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>181</v>
       </c>
@@ -6381,8 +6557,10 @@
       <c r="R20" s="65">
         <v>46224</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S20" s="163"/>
+      <c r="T20" s="163"/>
+    </row>
+    <row r="21" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
         <v>183</v>
       </c>
@@ -6437,8 +6615,10 @@
       <c r="R21" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S21" s="163"/>
+      <c r="T21" s="163"/>
+    </row>
+    <row r="22" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>185</v>
       </c>
@@ -6493,8 +6673,10 @@
       <c r="R22" s="65">
         <v>46224</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S22" s="163"/>
+      <c r="T22" s="163"/>
+    </row>
+    <row r="23" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>186</v>
       </c>
@@ -6549,8 +6731,10 @@
       <c r="R23" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S23" s="163"/>
+      <c r="T23" s="163"/>
+    </row>
+    <row r="24" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>187</v>
       </c>
@@ -6605,8 +6789,10 @@
       <c r="R24" s="65">
         <v>46224</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S24" s="163"/>
+      <c r="T24" s="163"/>
+    </row>
+    <row r="25" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>188</v>
       </c>
@@ -6661,8 +6847,10 @@
       <c r="R25" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S25" s="163"/>
+      <c r="T25" s="163"/>
+    </row>
+    <row r="26" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>203</v>
       </c>
@@ -6715,8 +6903,10 @@
       <c r="R26" s="65">
         <v>46224</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S26" s="163"/>
+      <c r="T26" s="163"/>
+    </row>
+    <row r="27" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
         <v>205</v>
       </c>
@@ -6769,8 +6959,10 @@
       <c r="R27" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S27" s="163"/>
+      <c r="T27" s="163"/>
+    </row>
+    <row r="28" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>206</v>
       </c>
@@ -6823,8 +7015,10 @@
       <c r="R28" s="65">
         <v>46224</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S28" s="163"/>
+      <c r="T28" s="163"/>
+    </row>
+    <row r="29" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>207</v>
       </c>
@@ -6877,8 +7071,10 @@
       <c r="R29" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S29" s="163"/>
+      <c r="T29" s="163"/>
+    </row>
+    <row r="30" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
         <v>208</v>
       </c>
@@ -6931,8 +7127,10 @@
       <c r="R30" s="65">
         <v>46224</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S30" s="163"/>
+      <c r="T30" s="163"/>
+    </row>
+    <row r="31" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
         <v>209</v>
       </c>
@@ -6985,8 +7183,10 @@
       <c r="R31" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S31" s="163"/>
+      <c r="T31" s="163"/>
+    </row>
+    <row r="32" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
         <v>210</v>
       </c>
@@ -7039,8 +7239,10 @@
       <c r="R32" s="65">
         <v>46224</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S32" s="163"/>
+      <c r="T32" s="163"/>
+    </row>
+    <row r="33" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
         <v>211</v>
       </c>
@@ -7093,8 +7295,10 @@
       <c r="R33" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S33" s="163"/>
+      <c r="T33" s="163"/>
+    </row>
+    <row r="34" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
         <v>212</v>
       </c>
@@ -7147,8 +7351,10 @@
       <c r="R34" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S34" s="163"/>
+      <c r="T34" s="163"/>
+    </row>
+    <row r="35" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
         <v>233</v>
       </c>
@@ -7201,8 +7407,10 @@
       <c r="R35" s="65">
         <v>46221</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S35" s="163"/>
+      <c r="T35" s="163"/>
+    </row>
+    <row r="36" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
         <v>236</v>
       </c>
@@ -7255,8 +7463,10 @@
       <c r="R36" s="65">
         <v>46207</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S36" s="163"/>
+      <c r="T36" s="163"/>
+    </row>
+    <row r="37" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
         <v>238</v>
       </c>
@@ -7309,8 +7519,10 @@
       <c r="R37" s="65">
         <v>46221</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S37" s="163"/>
+      <c r="T37" s="163"/>
+    </row>
+    <row r="38" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>239</v>
       </c>
@@ -7363,8 +7575,10 @@
       <c r="R38" s="65">
         <v>46207</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S38" s="163"/>
+      <c r="T38" s="163"/>
+    </row>
+    <row r="39" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
         <v>251</v>
       </c>
@@ -7417,8 +7631,10 @@
       <c r="R39" s="65">
         <v>46221</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S39" s="163"/>
+      <c r="T39" s="163"/>
+    </row>
+    <row r="40" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
         <v>253</v>
       </c>
@@ -7471,8 +7687,10 @@
       <c r="R40" s="65">
         <v>46207</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S40" s="163"/>
+      <c r="T40" s="163"/>
+    </row>
+    <row r="41" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
         <v>254</v>
       </c>
@@ -7525,8 +7743,10 @@
       <c r="R41" s="65">
         <v>46221</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S41" s="163"/>
+      <c r="T41" s="163"/>
+    </row>
+    <row r="42" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
         <v>255</v>
       </c>
@@ -7579,8 +7799,10 @@
       <c r="R42" s="65">
         <v>46207</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S42" s="163"/>
+      <c r="T42" s="163"/>
+    </row>
+    <row r="43" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
         <v>256</v>
       </c>
@@ -7633,8 +7855,10 @@
       <c r="R43" s="65">
         <v>46221</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S43" s="163"/>
+      <c r="T43" s="163"/>
+    </row>
+    <row r="44" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
         <v>257</v>
       </c>
@@ -7687,8 +7911,10 @@
       <c r="R44" s="65">
         <v>46207</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S44" s="163"/>
+      <c r="T44" s="163"/>
+    </row>
+    <row r="45" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
         <v>258</v>
       </c>
@@ -7741,8 +7967,10 @@
       <c r="R45" s="65">
         <v>46221</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S45" s="163"/>
+      <c r="T45" s="163"/>
+    </row>
+    <row r="46" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
         <v>259</v>
       </c>
@@ -7795,8 +8023,10 @@
       <c r="R46" s="65">
         <v>46195</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S46" s="163"/>
+      <c r="T46" s="163"/>
+    </row>
+    <row r="47" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
         <v>18</v>
       </c>
@@ -7849,8 +8079,10 @@
       <c r="R47" s="65">
         <v>46207</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S47" s="163"/>
+      <c r="T47" s="163"/>
+    </row>
+    <row r="48" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
         <v>26</v>
       </c>
@@ -7903,8 +8135,10 @@
       <c r="R48" s="65">
         <v>46195</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S48" s="163"/>
+      <c r="T48" s="163"/>
+    </row>
+    <row r="49" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
         <v>29</v>
       </c>
@@ -7957,8 +8191,10 @@
       <c r="R49" s="65">
         <v>46207</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S49" s="163"/>
+      <c r="T49" s="163"/>
+    </row>
+    <row r="50" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
         <v>31</v>
       </c>
@@ -8011,8 +8247,10 @@
       <c r="R50" s="65">
         <v>46195</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S50" s="163"/>
+      <c r="T50" s="163"/>
+    </row>
+    <row r="51" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
         <v>32</v>
       </c>
@@ -8065,8 +8303,10 @@
       <c r="R51" s="65">
         <v>46207</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S51" s="163"/>
+      <c r="T51" s="163"/>
+    </row>
+    <row r="52" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
         <v>34</v>
       </c>
@@ -8119,8 +8359,10 @@
       <c r="R52" s="65">
         <v>46195</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S52" s="163"/>
+      <c r="T52" s="163"/>
+    </row>
+    <row r="53" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
         <v>189</v>
       </c>
@@ -8173,8 +8415,10 @@
       <c r="R53" s="65">
         <v>46207</v>
       </c>
-    </row>
-    <row r="54" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S53" s="163"/>
+      <c r="T53" s="163"/>
+    </row>
+    <row r="54" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
         <v>191</v>
       </c>
@@ -8227,8 +8471,10 @@
       <c r="R54" s="65">
         <v>46195</v>
       </c>
-    </row>
-    <row r="55" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S54" s="163"/>
+      <c r="T54" s="163"/>
+    </row>
+    <row r="55" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
         <v>192</v>
       </c>
@@ -8281,8 +8527,10 @@
       <c r="R55" s="65">
         <v>46207</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S55" s="163"/>
+      <c r="T55" s="163"/>
+    </row>
+    <row r="56" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>193</v>
       </c>
@@ -8335,8 +8583,10 @@
       <c r="R56" s="65">
         <v>46195</v>
       </c>
-    </row>
-    <row r="57" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S56" s="163"/>
+      <c r="T56" s="163"/>
+    </row>
+    <row r="57" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
         <v>194</v>
       </c>
@@ -8389,8 +8639,10 @@
       <c r="R57" s="65">
         <v>46207</v>
       </c>
-    </row>
-    <row r="58" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S57" s="163"/>
+      <c r="T57" s="163"/>
+    </row>
+    <row r="58" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
         <v>195</v>
       </c>
@@ -8443,8 +8695,10 @@
       <c r="R58" s="65">
         <v>46195</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S58" s="163"/>
+      <c r="T58" s="163"/>
+    </row>
+    <row r="59" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
         <v>161</v>
       </c>
@@ -8497,8 +8751,10 @@
       <c r="R59" s="65">
         <v>46207</v>
       </c>
-    </row>
-    <row r="60" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S59" s="163"/>
+      <c r="T59" s="163"/>
+    </row>
+    <row r="60" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
         <v>196</v>
       </c>
@@ -8551,8 +8807,10 @@
       <c r="R60" s="65">
         <v>46195</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S60" s="163"/>
+      <c r="T60" s="163"/>
+    </row>
+    <row r="61" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
         <v>163</v>
       </c>
@@ -8605,8 +8863,10 @@
       <c r="R61" s="65">
         <v>46207</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S61" s="163"/>
+      <c r="T61" s="163"/>
+    </row>
+    <row r="62" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
         <v>164</v>
       </c>
@@ -8659,8 +8919,10 @@
       <c r="R62" s="65">
         <v>46179</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S62" s="163"/>
+      <c r="T62" s="163"/>
+    </row>
+    <row r="63" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A63" s="12" t="s">
         <v>165</v>
       </c>
@@ -8713,8 +8975,10 @@
       <c r="R63" s="65">
         <v>46195</v>
       </c>
-    </row>
-    <row r="64" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S63" s="163"/>
+      <c r="T63" s="163"/>
+    </row>
+    <row r="64" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A64" s="12" t="s">
         <v>166</v>
       </c>
@@ -8767,8 +9031,10 @@
       <c r="R64" s="65">
         <v>46179</v>
       </c>
-    </row>
-    <row r="65" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S64" s="163"/>
+      <c r="T64" s="163"/>
+    </row>
+    <row r="65" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A65" s="12" t="s">
         <v>167</v>
       </c>
@@ -8821,8 +9087,10 @@
       <c r="R65" s="65">
         <v>46195</v>
       </c>
-    </row>
-    <row r="66" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S65" s="163"/>
+      <c r="T65" s="163"/>
+    </row>
+    <row r="66" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
         <v>168</v>
       </c>
@@ -8875,8 +9143,10 @@
       <c r="R66" s="65">
         <v>46179</v>
       </c>
-    </row>
-    <row r="67" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S66" s="163"/>
+      <c r="T66" s="163"/>
+    </row>
+    <row r="67" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A67" s="12" t="s">
         <v>169</v>
       </c>
@@ -8929,8 +9199,10 @@
       <c r="R67" s="65">
         <v>46195</v>
       </c>
-    </row>
-    <row r="68" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S67" s="163"/>
+      <c r="T67" s="163"/>
+    </row>
+    <row r="68" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
         <v>170</v>
       </c>
@@ -8983,8 +9255,10 @@
       <c r="R68" s="65">
         <v>46179</v>
       </c>
-    </row>
-    <row r="69" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S68" s="163"/>
+      <c r="T68" s="163"/>
+    </row>
+    <row r="69" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A69" s="12" t="s">
         <v>128</v>
       </c>
@@ -9039,8 +9313,10 @@
       <c r="R69" s="65">
         <v>46195</v>
       </c>
-    </row>
-    <row r="70" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S69" s="163"/>
+      <c r="T69" s="163"/>
+    </row>
+    <row r="70" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>131</v>
       </c>
@@ -9095,8 +9371,10 @@
       <c r="R70" s="65">
         <v>46179</v>
       </c>
-    </row>
-    <row r="71" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S70" s="163"/>
+      <c r="T70" s="163"/>
+    </row>
+    <row r="71" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A71" s="12" t="s">
         <v>133</v>
       </c>
@@ -9151,8 +9429,10 @@
       <c r="R71" s="65">
         <v>46195</v>
       </c>
-    </row>
-    <row r="72" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S71" s="163"/>
+      <c r="T71" s="163"/>
+    </row>
+    <row r="72" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
         <v>134</v>
       </c>
@@ -9207,8 +9487,10 @@
       <c r="R72" s="65">
         <v>46179</v>
       </c>
-    </row>
-    <row r="73" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S72" s="163"/>
+      <c r="T72" s="163"/>
+    </row>
+    <row r="73" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
         <v>135</v>
       </c>
@@ -9263,8 +9545,10 @@
       <c r="R73" s="65">
         <v>46195</v>
       </c>
-    </row>
-    <row r="74" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S73" s="163"/>
+      <c r="T73" s="163"/>
+    </row>
+    <row r="74" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
         <v>136</v>
       </c>
@@ -9319,8 +9603,10 @@
       <c r="R74" s="65">
         <v>46179</v>
       </c>
-    </row>
-    <row r="75" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S74" s="163"/>
+      <c r="T74" s="163"/>
+    </row>
+    <row r="75" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
         <v>137</v>
       </c>
@@ -9375,8 +9661,10 @@
       <c r="R75" s="65">
         <v>46195</v>
       </c>
-    </row>
-    <row r="76" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S75" s="163"/>
+      <c r="T75" s="163"/>
+    </row>
+    <row r="76" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
         <v>138</v>
       </c>
@@ -9431,8 +9719,10 @@
       <c r="R76" s="65">
         <v>46179</v>
       </c>
-    </row>
-    <row r="77" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S76" s="163"/>
+      <c r="T76" s="163"/>
+    </row>
+    <row r="77" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
         <v>96</v>
       </c>
@@ -9487,8 +9777,14 @@
       <c r="R77" s="65">
         <v>46217</v>
       </c>
-    </row>
-    <row r="78" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S77" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T77" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
         <v>99</v>
       </c>
@@ -9543,8 +9839,14 @@
       <c r="R78" s="65">
         <v>46217</v>
       </c>
-    </row>
-    <row r="79" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S78" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T78" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A79" s="12" t="s">
         <v>100</v>
       </c>
@@ -9599,8 +9901,14 @@
       <c r="R79" s="65">
         <v>46217</v>
       </c>
-    </row>
-    <row r="80" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S79" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T79" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
         <v>101</v>
       </c>
@@ -9655,8 +9963,14 @@
       <c r="R80" s="65">
         <v>46217</v>
       </c>
-    </row>
-    <row r="81" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S80" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T80" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
         <v>240</v>
       </c>
@@ -9678,7 +9992,9 @@
       <c r="G81" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H81" s="2"/>
+      <c r="H81" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="I81" s="49" t="s">
         <v>241</v>
       </c>
@@ -9707,8 +10023,14 @@
       <c r="R81" s="65">
         <v>46203</v>
       </c>
-    </row>
-    <row r="82" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S81" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T81" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
         <v>243</v>
       </c>
@@ -9761,8 +10083,14 @@
       <c r="R82" s="65">
         <v>46203</v>
       </c>
-    </row>
-    <row r="83" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S82" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T82" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A83" s="12" t="s">
         <v>244</v>
       </c>
@@ -9815,8 +10143,14 @@
       <c r="R83" s="65">
         <v>46203</v>
       </c>
-    </row>
-    <row r="84" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S83" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T83" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
         <v>245</v>
       </c>
@@ -9869,8 +10203,14 @@
       <c r="R84" s="65">
         <v>46203</v>
       </c>
-    </row>
-    <row r="85" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S84" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T84" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A85" s="12" t="s">
         <v>246</v>
       </c>
@@ -9923,8 +10263,14 @@
       <c r="R85" s="65">
         <v>46203</v>
       </c>
-    </row>
-    <row r="86" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S85" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T85" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A86" s="12" t="s">
         <v>247</v>
       </c>
@@ -9977,8 +10323,14 @@
       <c r="R86" s="65">
         <v>46203</v>
       </c>
-    </row>
-    <row r="87" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S86" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T86" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
         <v>248</v>
       </c>
@@ -10031,8 +10383,14 @@
       <c r="R87" s="65">
         <v>46203</v>
       </c>
-    </row>
-    <row r="88" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S87" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T87" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A88" s="12" t="s">
         <v>249</v>
       </c>
@@ -10085,8 +10443,14 @@
       <c r="R88" s="65">
         <v>46182</v>
       </c>
-    </row>
-    <row r="89" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S88" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T88" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A89" s="12" t="s">
         <v>250</v>
       </c>
@@ -10139,8 +10503,14 @@
       <c r="R89" s="65">
         <v>46182</v>
       </c>
-    </row>
-    <row r="90" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S89" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T89" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A90" s="12" t="s">
         <v>228</v>
       </c>
@@ -10175,7 +10545,7 @@
         <v>46196</v>
       </c>
       <c r="L90" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2">
         <v>1</v>
@@ -10195,8 +10565,14 @@
       <c r="R90" s="65">
         <v>46182</v>
       </c>
-    </row>
-    <row r="91" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S90" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T90" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A91" s="12" t="s">
         <v>231</v>
       </c>
@@ -10231,7 +10607,7 @@
         <v>46196</v>
       </c>
       <c r="L91" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2">
         <v>2</v>
@@ -10251,8 +10627,14 @@
       <c r="R91" s="65">
         <v>46182</v>
       </c>
-    </row>
-    <row r="92" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S91" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T91" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A92" s="12" t="s">
         <v>232</v>
       </c>
@@ -10307,8 +10689,14 @@
       <c r="R92" s="65">
         <v>46182</v>
       </c>
-    </row>
-    <row r="93" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S92" s="166">
+        <v>46234</v>
+      </c>
+      <c r="T92" s="163" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A93" s="12" t="s">
         <v>197</v>
       </c>
@@ -10363,8 +10751,14 @@
       <c r="R93" s="65">
         <v>46168</v>
       </c>
-    </row>
-    <row r="94" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S93" s="166">
+        <v>46204.919444444444</v>
+      </c>
+      <c r="T93" s="163">
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A94" s="12" t="s">
         <v>199</v>
       </c>
@@ -10419,8 +10813,14 @@
       <c r="R94" s="65">
         <v>46163</v>
       </c>
-    </row>
-    <row r="95" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S94" s="164">
+        <v>46204.657638888886</v>
+      </c>
+      <c r="T94" s="165">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A95" s="12" t="s">
         <v>200</v>
       </c>
@@ -10475,8 +10875,14 @@
       <c r="R95" s="65">
         <v>46168</v>
       </c>
-    </row>
-    <row r="96" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S95" s="166">
+        <v>46204.919444444444</v>
+      </c>
+      <c r="T95" s="163">
+        <v>100.4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A96" s="12" t="s">
         <v>201</v>
       </c>
@@ -10531,8 +10937,14 @@
       <c r="R96" s="65">
         <v>46163</v>
       </c>
-    </row>
-    <row r="97" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S96" s="164">
+        <v>46204.919444444444</v>
+      </c>
+      <c r="T96" s="165">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A97" s="12" t="s">
         <v>202</v>
       </c>
@@ -10587,8 +10999,14 @@
       <c r="R97" s="65">
         <v>46168</v>
       </c>
-    </row>
-    <row r="98" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S97" s="166">
+        <v>46204.919444444444</v>
+      </c>
+      <c r="T97" s="163">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A98" s="12" t="s">
         <v>171</v>
       </c>
@@ -10643,8 +11061,14 @@
       <c r="R98" s="65">
         <v>46163</v>
       </c>
-    </row>
-    <row r="99" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S98" s="164">
+        <v>46204.65625</v>
+      </c>
+      <c r="T98" s="165">
+        <v>47.1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A99" s="12" t="s">
         <v>173</v>
       </c>
@@ -10699,8 +11123,14 @@
       <c r="R99" s="65">
         <v>46168</v>
       </c>
-    </row>
-    <row r="100" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S99" s="166">
+        <v>46204.918749999997</v>
+      </c>
+      <c r="T99" s="163">
+        <v>38.9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A100" s="12" t="s">
         <v>175</v>
       </c>
@@ -10755,8 +11185,14 @@
       <c r="R100" s="65">
         <v>46163</v>
       </c>
-    </row>
-    <row r="101" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S100" s="164">
+        <v>46204.875</v>
+      </c>
+      <c r="T100" s="165">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A101" s="12" t="s">
         <v>176</v>
       </c>
@@ -10811,8 +11247,14 @@
       <c r="R101" s="65">
         <v>46168</v>
       </c>
-    </row>
-    <row r="102" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S101" s="166">
+        <v>46204.657638888886</v>
+      </c>
+      <c r="T101" s="163">
+        <v>61.851999999999997</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A102" s="12" t="s">
         <v>177</v>
       </c>
@@ -10867,8 +11309,14 @@
       <c r="R102" s="65">
         <v>46163</v>
       </c>
-    </row>
-    <row r="103" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S102" s="164">
+        <v>46204.65625</v>
+      </c>
+      <c r="T102" s="165">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A103" s="12" t="s">
         <v>178</v>
       </c>
@@ -10923,8 +11371,14 @@
       <c r="R103" s="65">
         <v>46168</v>
       </c>
-    </row>
-    <row r="104" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S103" s="166">
+        <v>46204.918749999997</v>
+      </c>
+      <c r="T103" s="163">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A104" s="12" t="s">
         <v>179</v>
       </c>
@@ -10979,8 +11433,14 @@
       <c r="R104" s="65">
         <v>46163</v>
       </c>
-    </row>
-    <row r="105" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S104" s="164">
+        <v>46204.65625</v>
+      </c>
+      <c r="T104" s="165">
+        <v>47.1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A105" s="12" t="s">
         <v>139</v>
       </c>
@@ -11035,8 +11495,10 @@
       <c r="R105" s="65">
         <v>46240</v>
       </c>
-    </row>
-    <row r="106" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S105" s="163"/>
+      <c r="T105" s="163"/>
+    </row>
+    <row r="106" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A106" s="12" t="s">
         <v>180</v>
       </c>
@@ -11091,8 +11553,14 @@
       <c r="R106" s="65">
         <v>46163</v>
       </c>
-    </row>
-    <row r="107" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S106" s="164">
+        <v>46204.65625</v>
+      </c>
+      <c r="T106" s="165">
+        <v>56.3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A107" s="12" t="s">
         <v>141</v>
       </c>
@@ -11147,8 +11615,10 @@
       <c r="R107" s="65">
         <v>46240</v>
       </c>
-    </row>
-    <row r="108" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S107" s="163"/>
+      <c r="T107" s="163"/>
+    </row>
+    <row r="108" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A108" s="12" t="s">
         <v>142</v>
       </c>
@@ -11203,8 +11673,14 @@
       <c r="R108" s="65">
         <v>46163</v>
       </c>
-    </row>
-    <row r="109" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S108" s="164">
+        <v>46204.70416666667</v>
+      </c>
+      <c r="T108" s="165">
+        <v>102.95</v>
+      </c>
+    </row>
+    <row r="109" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A109" s="12" t="s">
         <v>144</v>
       </c>
@@ -11259,8 +11735,10 @@
       <c r="R109" s="65">
         <v>46240</v>
       </c>
-    </row>
-    <row r="110" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S109" s="163"/>
+      <c r="T109" s="163"/>
+    </row>
+    <row r="110" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A110" s="12" t="s">
         <v>145</v>
       </c>
@@ -11315,8 +11793,14 @@
       <c r="R110" s="65">
         <v>46163</v>
       </c>
-    </row>
-    <row r="111" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S110" s="164">
+        <v>46204.657638888886</v>
+      </c>
+      <c r="T110" s="165">
+        <v>70.277000000000001</v>
+      </c>
+    </row>
+    <row r="111" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A111" s="12" t="s">
         <v>146</v>
       </c>
@@ -11371,8 +11855,10 @@
       <c r="R111" s="65">
         <v>46240</v>
       </c>
-    </row>
-    <row r="112" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S111" s="163"/>
+      <c r="T111" s="163"/>
+    </row>
+    <row r="112" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A112" s="12" t="s">
         <v>147</v>
       </c>
@@ -11427,8 +11913,14 @@
       <c r="R112" s="65">
         <v>46163</v>
       </c>
-    </row>
-    <row r="113" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S112" s="164">
+        <v>46204.413194444445</v>
+      </c>
+      <c r="T112" s="165">
+        <v>77.23</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A113" s="12" t="s">
         <v>105</v>
       </c>
@@ -11483,8 +11975,10 @@
       <c r="R113" s="65">
         <v>46240</v>
       </c>
-    </row>
-    <row r="114" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S113" s="163"/>
+      <c r="T113" s="163"/>
+    </row>
+    <row r="114" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A114" s="12" t="s">
         <v>148</v>
       </c>
@@ -11539,8 +12033,14 @@
       <c r="R114" s="65">
         <v>46154</v>
       </c>
-    </row>
-    <row r="115" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S114" s="164">
+        <v>46204.426388888889</v>
+      </c>
+      <c r="T114" s="165">
+        <v>25.35</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A115" s="12" t="s">
         <v>108</v>
       </c>
@@ -11595,8 +12095,10 @@
       <c r="R115" s="65">
         <v>46240</v>
       </c>
-    </row>
-    <row r="116" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S115" s="163"/>
+      <c r="T115" s="163"/>
+    </row>
+    <row r="116" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A116" s="12" t="s">
         <v>149</v>
       </c>
@@ -11651,8 +12153,14 @@
       <c r="R116" s="65">
         <v>46154</v>
       </c>
-    </row>
-    <row r="117" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S116" s="164">
+        <v>46204.657638888886</v>
+      </c>
+      <c r="T116" s="165">
+        <v>45.284999999999997</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A117" s="12" t="s">
         <v>109</v>
       </c>
@@ -11707,8 +12215,10 @@
       <c r="R117" s="65">
         <v>46240</v>
       </c>
-    </row>
-    <row r="118" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S117" s="163"/>
+      <c r="T117" s="163"/>
+    </row>
+    <row r="118" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A118" s="12" t="s">
         <v>110</v>
       </c>
@@ -11763,8 +12273,14 @@
       <c r="R118" s="65">
         <v>46154</v>
       </c>
-    </row>
-    <row r="119" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S118" s="164">
+        <v>46204.425000000003</v>
+      </c>
+      <c r="T118" s="165">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A119" s="12" t="s">
         <v>111</v>
       </c>
@@ -11819,8 +12335,10 @@
       <c r="R119" s="65">
         <v>46240</v>
       </c>
-    </row>
-    <row r="120" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S119" s="163"/>
+      <c r="T119" s="163"/>
+    </row>
+    <row r="120" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A120" s="12" t="s">
         <v>112</v>
       </c>
@@ -11875,8 +12393,14 @@
       <c r="R120" s="65">
         <v>46154</v>
       </c>
-    </row>
-    <row r="121" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S120" s="164">
+        <v>46204.704861111109</v>
+      </c>
+      <c r="T120" s="165">
+        <v>39.33</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A121" s="12" t="s">
         <v>113</v>
       </c>
@@ -11931,8 +12455,10 @@
       <c r="R121" s="65">
         <v>46255</v>
       </c>
-    </row>
-    <row r="122" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S121" s="163"/>
+      <c r="T121" s="163"/>
+    </row>
+    <row r="122" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A122" s="12" t="s">
         <v>114</v>
       </c>
@@ -11987,8 +12513,14 @@
       <c r="R122" s="65">
         <v>46154</v>
       </c>
-    </row>
-    <row r="123" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S122" s="164">
+        <v>46204.424305555556</v>
+      </c>
+      <c r="T122" s="165">
+        <v>35.67</v>
+      </c>
+    </row>
+    <row r="123" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A123" s="12" t="s">
         <v>74</v>
       </c>
@@ -12043,8 +12575,10 @@
       <c r="R123" s="65">
         <v>46255</v>
       </c>
-    </row>
-    <row r="124" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S123" s="163"/>
+      <c r="T123" s="163"/>
+    </row>
+    <row r="124" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A124" s="12" t="s">
         <v>115</v>
       </c>
@@ -12099,8 +12633,14 @@
       <c r="R124" s="65">
         <v>46154</v>
       </c>
-    </row>
-    <row r="125" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S124" s="164">
+        <v>46204.657638888886</v>
+      </c>
+      <c r="T124" s="165">
+        <v>37.427999999999997</v>
+      </c>
+    </row>
+    <row r="125" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A125" s="12" t="s">
         <v>77</v>
       </c>
@@ -12155,8 +12695,10 @@
       <c r="R125" s="65">
         <v>46255</v>
       </c>
-    </row>
-    <row r="126" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S125" s="163"/>
+      <c r="T125" s="163"/>
+    </row>
+    <row r="126" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A126" s="12" t="s">
         <v>78</v>
       </c>
@@ -12211,8 +12753,14 @@
       <c r="R126" s="65">
         <v>46154</v>
       </c>
-    </row>
-    <row r="127" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S126" s="164">
+        <v>46204.652083333334</v>
+      </c>
+      <c r="T126" s="165">
+        <v>36.700000000000003</v>
+      </c>
+    </row>
+    <row r="127" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A127" s="12" t="s">
         <v>81</v>
       </c>
@@ -12267,8 +12815,10 @@
       <c r="R127" s="65">
         <v>46255</v>
       </c>
-    </row>
-    <row r="128" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S127" s="163"/>
+      <c r="T127" s="163"/>
+    </row>
+    <row r="128" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A128" s="12" t="s">
         <v>82</v>
       </c>
@@ -12323,8 +12873,14 @@
       <c r="R128" s="65">
         <v>46154</v>
       </c>
-    </row>
-    <row r="129" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S128" s="164">
+        <v>46204.714583333334</v>
+      </c>
+      <c r="T128" s="165">
+        <v>11.590999999999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A129" s="12" t="s">
         <v>83</v>
       </c>
@@ -12379,8 +12935,10 @@
       <c r="R129" s="65">
         <v>46255</v>
       </c>
-    </row>
-    <row r="130" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S129" s="163"/>
+      <c r="T129" s="163"/>
+    </row>
+    <row r="130" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A130" s="12" t="s">
         <v>84</v>
       </c>
@@ -12435,8 +12993,10 @@
       <c r="R130" s="65">
         <v>46255</v>
       </c>
-    </row>
-    <row r="131" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S130" s="163"/>
+      <c r="T130" s="163"/>
+    </row>
+    <row r="131" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A131" s="12" t="s">
         <v>85</v>
       </c>
@@ -12491,8 +13051,10 @@
       <c r="R131" s="65">
         <v>46255</v>
       </c>
-    </row>
-    <row r="132" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S131" s="163"/>
+      <c r="T131" s="163"/>
+    </row>
+    <row r="132" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A132" s="12" t="s">
         <v>86</v>
       </c>
@@ -12547,8 +13109,10 @@
       <c r="R132" s="65">
         <v>46255</v>
       </c>
-    </row>
-    <row r="133" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S132" s="163"/>
+      <c r="T132" s="163"/>
+    </row>
+    <row r="133" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A133" s="12" t="s">
         <v>260</v>
       </c>
@@ -12595,8 +13159,10 @@
       <c r="R133" s="65">
         <v>46270</v>
       </c>
-    </row>
-    <row r="134" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S133" s="163"/>
+      <c r="T133" s="163"/>
+    </row>
+    <row r="134" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A134" s="12" t="s">
         <v>263</v>
       </c>
@@ -12643,15 +13209,19 @@
       <c r="R134" s="65">
         <v>46270</v>
       </c>
-    </row>
-    <row r="135" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S134" s="163"/>
+      <c r="T134" s="163"/>
+    </row>
+    <row r="135" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A135" s="12" t="s">
         <v>264</v>
       </c>
       <c r="B135" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C135" s="2"/>
+      <c r="C135" s="2">
+        <v>14558068814</v>
+      </c>
       <c r="D135" s="2">
         <v>71205556</v>
       </c>
@@ -12664,14 +13234,18 @@
       <c r="G135" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H135" s="2"/>
+      <c r="H135" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="I135" s="50" t="s">
         <v>261</v>
       </c>
       <c r="J135" s="9">
         <v>0</v>
       </c>
-      <c r="K135" s="2"/>
+      <c r="K135" s="4">
+        <v>46225</v>
+      </c>
       <c r="L135" s="11" t="b">
         <v>0</v>
       </c>
@@ -12691,15 +13265,19 @@
       <c r="R135" s="65">
         <v>46270</v>
       </c>
-    </row>
-    <row r="136" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S135" s="163"/>
+      <c r="T135" s="163"/>
+    </row>
+    <row r="136" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A136" s="12" t="s">
         <v>265</v>
       </c>
       <c r="B136" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C136" s="2"/>
+      <c r="C136" s="2">
+        <v>14558068996</v>
+      </c>
       <c r="D136" s="2">
         <v>71205556</v>
       </c>
@@ -12712,14 +13290,18 @@
       <c r="G136" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H136" s="2"/>
+      <c r="H136" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="I136" s="50" t="s">
         <v>261</v>
       </c>
       <c r="J136" s="9">
         <v>0</v>
       </c>
-      <c r="K136" s="2"/>
+      <c r="K136" s="4">
+        <v>46225</v>
+      </c>
       <c r="L136" s="11" t="b">
         <v>0</v>
       </c>
@@ -12739,15 +13321,19 @@
       <c r="R136" s="65">
         <v>46270</v>
       </c>
-    </row>
-    <row r="137" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S136" s="163"/>
+      <c r="T136" s="163"/>
+    </row>
+    <row r="137" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A137" s="12" t="s">
         <v>266</v>
       </c>
       <c r="B137" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C137" s="2"/>
+      <c r="C137" s="2">
+        <v>14558069457</v>
+      </c>
       <c r="D137" s="2">
         <v>71205556</v>
       </c>
@@ -12760,14 +13346,18 @@
       <c r="G137" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H137" s="2"/>
+      <c r="H137" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="I137" s="50" t="s">
         <v>261</v>
       </c>
       <c r="J137" s="9">
         <v>0</v>
       </c>
-      <c r="K137" s="2"/>
+      <c r="K137" s="4">
+        <v>46225</v>
+      </c>
       <c r="L137" s="11" t="b">
         <v>0</v>
       </c>
@@ -12787,15 +13377,19 @@
       <c r="R137" s="65">
         <v>46270</v>
       </c>
-    </row>
-    <row r="138" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S137" s="163"/>
+      <c r="T137" s="163"/>
+    </row>
+    <row r="138" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A138" s="12" t="s">
         <v>267</v>
       </c>
       <c r="B138" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C138" s="2"/>
+      <c r="C138" s="2">
+        <v>14558069028</v>
+      </c>
       <c r="D138" s="2">
         <v>71205556</v>
       </c>
@@ -12808,14 +13402,18 @@
       <c r="G138" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H138" s="2"/>
+      <c r="H138" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="I138" s="50" t="s">
         <v>261</v>
       </c>
       <c r="J138" s="9">
         <v>0</v>
       </c>
-      <c r="K138" s="2"/>
+      <c r="K138" s="4">
+        <v>46225</v>
+      </c>
       <c r="L138" s="11" t="b">
         <v>0</v>
       </c>
@@ -12835,15 +13433,19 @@
       <c r="R138" s="65">
         <v>46270</v>
       </c>
-    </row>
-    <row r="139" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S138" s="163"/>
+      <c r="T138" s="163"/>
+    </row>
+    <row r="139" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A139" s="12" t="s">
         <v>268</v>
       </c>
       <c r="B139" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C139" s="2"/>
+      <c r="C139" s="2">
+        <v>14558069218</v>
+      </c>
       <c r="D139" s="2">
         <v>71205556</v>
       </c>
@@ -12856,14 +13458,18 @@
       <c r="G139" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H139" s="2"/>
+      <c r="H139" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="I139" s="50" t="s">
         <v>261</v>
       </c>
       <c r="J139" s="9">
         <v>0</v>
       </c>
-      <c r="K139" s="2"/>
+      <c r="K139" s="4">
+        <v>46225</v>
+      </c>
       <c r="L139" s="11" t="b">
         <v>0</v>
       </c>
@@ -12883,15 +13489,19 @@
       <c r="R139" s="65">
         <v>46270</v>
       </c>
-    </row>
-    <row r="140" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S139" s="163"/>
+      <c r="T139" s="163"/>
+    </row>
+    <row r="140" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A140" s="12" t="s">
         <v>269</v>
       </c>
       <c r="B140" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C140" s="2"/>
+      <c r="C140" s="2">
+        <v>14558069648</v>
+      </c>
       <c r="D140" s="2">
         <v>71205556</v>
       </c>
@@ -12904,14 +13514,18 @@
       <c r="G140" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H140" s="2"/>
+      <c r="H140" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="I140" s="50" t="s">
         <v>261</v>
       </c>
       <c r="J140" s="9">
         <v>0</v>
       </c>
-      <c r="K140" s="2"/>
+      <c r="K140" s="4">
+        <v>46225</v>
+      </c>
       <c r="L140" s="11" t="b">
         <v>0</v>
       </c>
@@ -12931,8 +13545,10 @@
       <c r="R140" s="65">
         <v>46270</v>
       </c>
-    </row>
-    <row r="141" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S140" s="163"/>
+      <c r="T140" s="163"/>
+    </row>
+    <row r="141" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A141" s="12" t="s">
         <v>35</v>
       </c>
@@ -12985,8 +13601,10 @@
       <c r="R141" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="142" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S141" s="163"/>
+      <c r="T141" s="163"/>
+    </row>
+    <row r="142" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A142" s="12" t="s">
         <v>38</v>
       </c>
@@ -13039,8 +13657,10 @@
       <c r="R142" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="143" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S142" s="163"/>
+      <c r="T142" s="163"/>
+    </row>
+    <row r="143" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A143" s="12" t="s">
         <v>40</v>
       </c>
@@ -13093,8 +13713,10 @@
       <c r="R143" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="144" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S143" s="163"/>
+      <c r="T143" s="163"/>
+    </row>
+    <row r="144" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A144" s="12" t="s">
         <v>41</v>
       </c>
@@ -13147,8 +13769,10 @@
       <c r="R144" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="145" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S144" s="163"/>
+      <c r="T144" s="163"/>
+    </row>
+    <row r="145" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A145" s="12" t="s">
         <v>42</v>
       </c>
@@ -13201,8 +13825,10 @@
       <c r="R145" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="146" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S145" s="163"/>
+      <c r="T145" s="163"/>
+    </row>
+    <row r="146" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A146" s="12" t="s">
         <v>43</v>
       </c>
@@ -13255,8 +13881,10 @@
       <c r="R146" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="147" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S146" s="163"/>
+      <c r="T146" s="163"/>
+    </row>
+    <row r="147" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A147" s="12" t="s">
         <v>45</v>
       </c>
@@ -13309,8 +13937,10 @@
       <c r="R147" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="148" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S147" s="163"/>
+      <c r="T147" s="163"/>
+    </row>
+    <row r="148" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A148" s="12" t="s">
         <v>44</v>
       </c>
@@ -13363,8 +13993,10 @@
       <c r="R148" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="149" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S148" s="163"/>
+      <c r="T148" s="163"/>
+    </row>
+    <row r="149" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A149" s="12" t="s">
         <v>47</v>
       </c>
@@ -13417,8 +14049,10 @@
       <c r="R149" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="150" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S149" s="163"/>
+      <c r="T149" s="163"/>
+    </row>
+    <row r="150" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A150" s="12" t="s">
         <v>48</v>
       </c>
@@ -13471,8 +14105,10 @@
       <c r="R150" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="151" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S150" s="163"/>
+      <c r="T150" s="163"/>
+    </row>
+    <row r="151" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A151" s="12" t="s">
         <v>49</v>
       </c>
@@ -13525,8 +14161,10 @@
       <c r="R151" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="152" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S151" s="163"/>
+      <c r="T151" s="163"/>
+    </row>
+    <row r="152" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A152" s="12" t="s">
         <v>50</v>
       </c>
@@ -13579,8 +14217,10 @@
       <c r="R152" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="153" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S152" s="163"/>
+      <c r="T152" s="163"/>
+    </row>
+    <row r="153" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A153" s="12" t="s">
         <v>51</v>
       </c>
@@ -13633,8 +14273,10 @@
       <c r="R153" s="65">
         <v>46301</v>
       </c>
-    </row>
-    <row r="154" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S153" s="163"/>
+      <c r="T153" s="163"/>
+    </row>
+    <row r="154" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A154" s="12" t="s">
         <v>52</v>
       </c>
@@ -13687,8 +14329,10 @@
       <c r="R154" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="155" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S154" s="163"/>
+      <c r="T154" s="163"/>
+    </row>
+    <row r="155" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A155" s="12" t="s">
         <v>53</v>
       </c>
@@ -13741,8 +14385,10 @@
       <c r="R155" s="65">
         <v>46286</v>
       </c>
-    </row>
-    <row r="156" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S155" s="163"/>
+      <c r="T155" s="163"/>
+    </row>
+    <row r="156" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A156" s="12" t="s">
         <v>54</v>
       </c>
@@ -13797,8 +14443,10 @@
       <c r="R156" s="65">
         <v>46254</v>
       </c>
-    </row>
-    <row r="157" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S156" s="163"/>
+      <c r="T156" s="163"/>
+    </row>
+    <row r="157" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A157" s="12" t="s">
         <v>57</v>
       </c>
@@ -13853,8 +14501,10 @@
       <c r="R157" s="65">
         <v>46254</v>
       </c>
-    </row>
-    <row r="158" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S157" s="163"/>
+      <c r="T157" s="163"/>
+    </row>
+    <row r="158" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A158" s="12" t="s">
         <v>58</v>
       </c>
@@ -13909,8 +14559,10 @@
       <c r="R158" s="65">
         <v>46254</v>
       </c>
-    </row>
-    <row r="159" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S158" s="163"/>
+      <c r="T158" s="163"/>
+    </row>
+    <row r="159" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A159" s="12" t="s">
         <v>59</v>
       </c>
@@ -13965,8 +14617,10 @@
       <c r="R159" s="65">
         <v>46254</v>
       </c>
-    </row>
-    <row r="160" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S159" s="163"/>
+      <c r="T159" s="163"/>
+    </row>
+    <row r="160" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A160" s="12" t="s">
         <v>60</v>
       </c>
@@ -14021,8 +14675,10 @@
       <c r="R160" s="65">
         <v>46254</v>
       </c>
-    </row>
-    <row r="161" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S160" s="163"/>
+      <c r="T160" s="163"/>
+    </row>
+    <row r="161" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A161" s="12" t="s">
         <v>61</v>
       </c>
@@ -14077,8 +14733,10 @@
       <c r="R161" s="65">
         <v>46254</v>
       </c>
-    </row>
-    <row r="162" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S161" s="163"/>
+      <c r="T161" s="163"/>
+    </row>
+    <row r="162" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A162" s="12" t="s">
         <v>62</v>
       </c>
@@ -14133,8 +14791,10 @@
       <c r="R162" s="65">
         <v>46254</v>
       </c>
-    </row>
-    <row r="163" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S162" s="163"/>
+      <c r="T162" s="163"/>
+    </row>
+    <row r="163" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A163" s="12" t="s">
         <v>63</v>
       </c>
@@ -14189,8 +14849,10 @@
       <c r="R163" s="65">
         <v>46254</v>
       </c>
-    </row>
-    <row r="164" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S163" s="163"/>
+      <c r="T163" s="163"/>
+    </row>
+    <row r="164" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A164" s="12" t="s">
         <v>87</v>
       </c>
@@ -14245,8 +14907,10 @@
       <c r="R164" s="65">
         <v>46238</v>
       </c>
-    </row>
-    <row r="165" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S164" s="163"/>
+      <c r="T164" s="163"/>
+    </row>
+    <row r="165" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A165" s="12" t="s">
         <v>90</v>
       </c>
@@ -14301,8 +14965,10 @@
       <c r="R165" s="65">
         <v>46238</v>
       </c>
-    </row>
-    <row r="166" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S165" s="163"/>
+      <c r="T165" s="163"/>
+    </row>
+    <row r="166" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A166" s="12" t="s">
         <v>91</v>
       </c>
@@ -14357,8 +15023,10 @@
       <c r="R166" s="65">
         <v>46238</v>
       </c>
-    </row>
-    <row r="167" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S166" s="163"/>
+      <c r="T166" s="163"/>
+    </row>
+    <row r="167" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A167" s="12" t="s">
         <v>92</v>
       </c>
@@ -14413,8 +15081,10 @@
       <c r="R167" s="65">
         <v>46238</v>
       </c>
-    </row>
-    <row r="168" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S167" s="163"/>
+      <c r="T167" s="163"/>
+    </row>
+    <row r="168" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A168" s="12" t="s">
         <v>93</v>
       </c>
@@ -14469,8 +15139,10 @@
       <c r="R168" s="65">
         <v>46238</v>
       </c>
-    </row>
-    <row r="169" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S168" s="163"/>
+      <c r="T168" s="163"/>
+    </row>
+    <row r="169" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A169" s="12" t="s">
         <v>94</v>
       </c>
@@ -14525,8 +15197,10 @@
       <c r="R169" s="65">
         <v>46238</v>
       </c>
-    </row>
-    <row r="170" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S169" s="163"/>
+      <c r="T169" s="163"/>
+    </row>
+    <row r="170" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A170" s="12" t="s">
         <v>95</v>
       </c>
@@ -14581,8 +15255,10 @@
       <c r="R170" s="65">
         <v>46238</v>
       </c>
-    </row>
-    <row r="171" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S170" s="163"/>
+      <c r="T170" s="163"/>
+    </row>
+    <row r="171" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A171" s="12" t="s">
         <v>220</v>
       </c>
@@ -14637,8 +15313,10 @@
       <c r="R171" s="65">
         <v>46266</v>
       </c>
-    </row>
-    <row r="172" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S171" s="163"/>
+      <c r="T171" s="163"/>
+    </row>
+    <row r="172" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A172" s="12" t="s">
         <v>223</v>
       </c>
@@ -14693,8 +15371,10 @@
       <c r="R172" s="65">
         <v>46266</v>
       </c>
-    </row>
-    <row r="173" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S172" s="163"/>
+      <c r="T172" s="163"/>
+    </row>
+    <row r="173" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A173" s="12" t="s">
         <v>224</v>
       </c>
@@ -14749,8 +15429,10 @@
       <c r="R173" s="65">
         <v>46266</v>
       </c>
-    </row>
-    <row r="174" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S173" s="163"/>
+      <c r="T173" s="163"/>
+    </row>
+    <row r="174" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A174" s="12" t="s">
         <v>225</v>
       </c>
@@ -14805,8 +15487,10 @@
       <c r="R174" s="65">
         <v>46266</v>
       </c>
-    </row>
-    <row r="175" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S174" s="163"/>
+      <c r="T174" s="163"/>
+    </row>
+    <row r="175" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A175" s="12" t="s">
         <v>226</v>
       </c>
@@ -14861,8 +15545,10 @@
       <c r="R175" s="65">
         <v>46266</v>
       </c>
-    </row>
-    <row r="176" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S175" s="163"/>
+      <c r="T175" s="163"/>
+    </row>
+    <row r="176" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A176" s="12" t="s">
         <v>227</v>
       </c>
@@ -14917,8 +15603,10 @@
       <c r="R176" s="65">
         <v>46252</v>
       </c>
-    </row>
-    <row r="177" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S176" s="163"/>
+      <c r="T176" s="163"/>
+    </row>
+    <row r="177" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A177" s="12" t="s">
         <v>213</v>
       </c>
@@ -14973,8 +15661,10 @@
       <c r="R177" s="65">
         <v>46252</v>
       </c>
-    </row>
-    <row r="178" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S177" s="163"/>
+      <c r="T177" s="163"/>
+    </row>
+    <row r="178" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A178" s="12" t="s">
         <v>215</v>
       </c>
@@ -15029,8 +15719,10 @@
       <c r="R178" s="65">
         <v>46252</v>
       </c>
-    </row>
-    <row r="179" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S178" s="163"/>
+      <c r="T178" s="163"/>
+    </row>
+    <row r="179" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A179" s="12" t="s">
         <v>216</v>
       </c>
@@ -15085,8 +15777,10 @@
       <c r="R179" s="65">
         <v>46252</v>
       </c>
-    </row>
-    <row r="180" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S179" s="163"/>
+      <c r="T179" s="163"/>
+    </row>
+    <row r="180" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A180" s="12" t="s">
         <v>217</v>
       </c>
@@ -15141,8 +15835,10 @@
       <c r="R180" s="65">
         <v>46252</v>
       </c>
-    </row>
-    <row r="181" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S180" s="163"/>
+      <c r="T180" s="163"/>
+    </row>
+    <row r="181" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A181" s="12" t="s">
         <v>218</v>
       </c>
@@ -15197,8 +15893,10 @@
       <c r="R181" s="65">
         <v>46252</v>
       </c>
-    </row>
-    <row r="182" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S181" s="163"/>
+      <c r="T181" s="163"/>
+    </row>
+    <row r="182" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A182" s="12" t="s">
         <v>219</v>
       </c>
@@ -15253,8 +15951,10 @@
       <c r="R182" s="65">
         <v>46252</v>
       </c>
-    </row>
-    <row r="183" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S182" s="163"/>
+      <c r="T182" s="163"/>
+    </row>
+    <row r="183" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A183" s="12" t="s">
         <v>64</v>
       </c>
@@ -15309,8 +16009,10 @@
       <c r="R183" s="65">
         <v>46252</v>
       </c>
-    </row>
-    <row r="184" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S183" s="163"/>
+      <c r="T183" s="163"/>
+    </row>
+    <row r="184" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A184" s="12" t="s">
         <v>68</v>
       </c>
@@ -15365,8 +16067,10 @@
       <c r="R184" s="65">
         <v>46238</v>
       </c>
-    </row>
-    <row r="185" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S184" s="163"/>
+      <c r="T184" s="163"/>
+    </row>
+    <row r="185" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A185" s="12" t="s">
         <v>70</v>
       </c>
@@ -15421,8 +16125,10 @@
       <c r="R185" s="65">
         <v>46238</v>
       </c>
-    </row>
-    <row r="186" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S185" s="163"/>
+      <c r="T185" s="163"/>
+    </row>
+    <row r="186" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A186" s="12" t="s">
         <v>71</v>
       </c>
@@ -15477,8 +16183,10 @@
       <c r="R186" s="65">
         <v>46238</v>
       </c>
-    </row>
-    <row r="187" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S186" s="163"/>
+      <c r="T186" s="163"/>
+    </row>
+    <row r="187" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A187" s="12" t="s">
         <v>72</v>
       </c>
@@ -15533,8 +16241,10 @@
       <c r="R187" s="65">
         <v>46238</v>
       </c>
-    </row>
-    <row r="188" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S187" s="163"/>
+      <c r="T187" s="163"/>
+    </row>
+    <row r="188" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A188" s="12" t="s">
         <v>73</v>
       </c>
@@ -15589,8 +16299,10 @@
       <c r="R188" s="65">
         <v>46238</v>
       </c>
-    </row>
-    <row r="189" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S188" s="163"/>
+      <c r="T188" s="163"/>
+    </row>
+    <row r="189" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A189" s="12" t="s">
         <v>102</v>
       </c>
@@ -15645,8 +16357,10 @@
       <c r="R189" s="65">
         <v>46238</v>
       </c>
-    </row>
-    <row r="190" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S189" s="163"/>
+      <c r="T189" s="163"/>
+    </row>
+    <row r="190" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A190" s="12" t="s">
         <v>103</v>
       </c>
@@ -15701,8 +16415,10 @@
       <c r="R190" s="65">
         <v>46238</v>
       </c>
-    </row>
-    <row r="191" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S190" s="163"/>
+      <c r="T190" s="163"/>
+    </row>
+    <row r="191" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A191" s="12" t="s">
         <v>104</v>
       </c>
@@ -15757,8 +16473,10 @@
       <c r="R191" s="65">
         <v>46238</v>
       </c>
-    </row>
-    <row r="192" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="S191" s="163"/>
+      <c r="T191" s="163"/>
+    </row>
+    <row r="192" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A192" s="14" t="s">
         <v>270</v>
       </c>
@@ -15811,6 +16529,8 @@
       <c r="R192" s="65">
         <v>46154</v>
       </c>
+      <c r="S192" s="163"/>
+      <c r="T192" s="163"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R192">
@@ -15818,13 +16538,13 @@
   </sortState>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="C25:C192 C2:C23">
-    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C117:C122">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C124:C132">
-    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15832,13 +16552,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q204"/>
+  <dimension ref="A1:S204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.46484375" customWidth="1"/>
-    <col min="3" max="3" width="30.86328125" customWidth="1"/>
+    <col min="2" max="2" width="20.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" customWidth="1"/>
     <col min="4" max="4" width="21.59765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.73046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.59765625" bestFit="1" customWidth="1"/>
@@ -15850,10 +16569,12 @@
     <col min="14" max="14" width="35.46484375" customWidth="1"/>
     <col min="15" max="15" width="20.1328125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25.86328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="29.265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.265625" customWidth="1"/>
+    <col min="18" max="18" width="22.86328125" customWidth="1"/>
+    <col min="19" max="19" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15905,8 +16626,14 @@
       <c r="Q1" s="1" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R1" s="162" t="s">
+        <v>1204</v>
+      </c>
+      <c r="S1" s="162" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>116</v>
       </c>
@@ -15950,8 +16677,10 @@
         <v>0</v>
       </c>
       <c r="Q2" s="17"/>
-    </row>
-    <row r="3" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R2" s="163"/>
+      <c r="S2" s="163"/>
+    </row>
+    <row r="3" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>119</v>
       </c>
@@ -15995,8 +16724,10 @@
         <v>0</v>
       </c>
       <c r="Q3" s="17"/>
-    </row>
-    <row r="4" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R3" s="163"/>
+      <c r="S3" s="163"/>
+    </row>
+    <row r="4" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
         <v>120</v>
       </c>
@@ -16040,8 +16771,10 @@
         <v>0</v>
       </c>
       <c r="Q4" s="17"/>
-    </row>
-    <row r="5" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R4" s="163"/>
+      <c r="S4" s="163"/>
+    </row>
+    <row r="5" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
         <v>122</v>
       </c>
@@ -16085,8 +16818,10 @@
         <v>0</v>
       </c>
       <c r="Q5" s="17"/>
-    </row>
-    <row r="6" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R5" s="163"/>
+      <c r="S5" s="163"/>
+    </row>
+    <row r="6" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
         <v>123</v>
       </c>
@@ -16130,8 +16865,10 @@
         <v>0</v>
       </c>
       <c r="Q6" s="17"/>
-    </row>
-    <row r="7" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R6" s="163"/>
+      <c r="S6" s="163"/>
+    </row>
+    <row r="7" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
         <v>124</v>
       </c>
@@ -16175,8 +16912,10 @@
         <v>0</v>
       </c>
       <c r="Q7" s="17"/>
-    </row>
-    <row r="8" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R7" s="163"/>
+      <c r="S7" s="163"/>
+    </row>
+    <row r="8" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
         <v>125</v>
       </c>
@@ -16220,8 +16959,10 @@
         <v>0</v>
       </c>
       <c r="Q8" s="17"/>
-    </row>
-    <row r="9" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R8" s="163"/>
+      <c r="S8" s="163"/>
+    </row>
+    <row r="9" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
         <v>126</v>
       </c>
@@ -16265,8 +17006,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="17"/>
-    </row>
-    <row r="10" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R9" s="163"/>
+      <c r="S9" s="163"/>
+    </row>
+    <row r="10" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
         <v>127</v>
       </c>
@@ -16310,8 +17053,10 @@
         <v>0</v>
       </c>
       <c r="Q10" s="17"/>
-    </row>
-    <row r="11" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R10" s="163"/>
+      <c r="S10" s="163"/>
+    </row>
+    <row r="11" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
         <v>150</v>
       </c>
@@ -16355,8 +17100,10 @@
         <v>0</v>
       </c>
       <c r="Q11" s="17"/>
-    </row>
-    <row r="12" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R11" s="163"/>
+      <c r="S11" s="163"/>
+    </row>
+    <row r="12" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
         <v>152</v>
       </c>
@@ -16400,8 +17147,10 @@
         <v>0</v>
       </c>
       <c r="Q12" s="17"/>
-    </row>
-    <row r="13" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R12" s="163"/>
+      <c r="S12" s="163"/>
+    </row>
+    <row r="13" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="s">
         <v>153</v>
       </c>
@@ -16445,8 +17194,10 @@
         <v>0</v>
       </c>
       <c r="Q13" s="17"/>
-    </row>
-    <row r="14" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R13" s="163"/>
+      <c r="S13" s="163"/>
+    </row>
+    <row r="14" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A14" s="23" t="s">
         <v>154</v>
       </c>
@@ -16490,8 +17241,10 @@
         <v>0</v>
       </c>
       <c r="Q14" s="17"/>
-    </row>
-    <row r="15" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R14" s="163"/>
+      <c r="S14" s="163"/>
+    </row>
+    <row r="15" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>155</v>
       </c>
@@ -16535,8 +17288,10 @@
         <v>0</v>
       </c>
       <c r="Q15" s="17"/>
-    </row>
-    <row r="16" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R15" s="163"/>
+      <c r="S15" s="163"/>
+    </row>
+    <row r="16" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
         <v>156</v>
       </c>
@@ -16580,8 +17335,10 @@
         <v>0</v>
       </c>
       <c r="Q16" s="17"/>
-    </row>
-    <row r="17" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R16" s="163"/>
+      <c r="S16" s="163"/>
+    </row>
+    <row r="17" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
         <v>157</v>
       </c>
@@ -16625,8 +17382,10 @@
         <v>0</v>
       </c>
       <c r="Q17" s="17"/>
-    </row>
-    <row r="18" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R17" s="163"/>
+      <c r="S17" s="163"/>
+    </row>
+    <row r="18" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A18" s="23" t="s">
         <v>158</v>
       </c>
@@ -16670,8 +17429,10 @@
         <v>0</v>
       </c>
       <c r="Q18" s="17"/>
-    </row>
-    <row r="19" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R18" s="163"/>
+      <c r="S18" s="163"/>
+    </row>
+    <row r="19" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A19" s="23" t="s">
         <v>160</v>
       </c>
@@ -16715,8 +17476,10 @@
         <v>0</v>
       </c>
       <c r="Q19" s="17"/>
-    </row>
-    <row r="20" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R19" s="163"/>
+      <c r="S19" s="163"/>
+    </row>
+    <row r="20" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A20" s="23" t="s">
         <v>181</v>
       </c>
@@ -16760,8 +17523,10 @@
         <v>0</v>
       </c>
       <c r="Q20" s="17"/>
-    </row>
-    <row r="21" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R20" s="163"/>
+      <c r="S20" s="163"/>
+    </row>
+    <row r="21" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="s">
         <v>183</v>
       </c>
@@ -16805,8 +17570,10 @@
         <v>0</v>
       </c>
       <c r="Q21" s="17"/>
-    </row>
-    <row r="22" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R21" s="163"/>
+      <c r="S21" s="163"/>
+    </row>
+    <row r="22" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A22" s="23" t="s">
         <v>185</v>
       </c>
@@ -16850,8 +17617,10 @@
         <v>0</v>
       </c>
       <c r="Q22" s="17"/>
-    </row>
-    <row r="23" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R22" s="163"/>
+      <c r="S22" s="163"/>
+    </row>
+    <row r="23" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="s">
         <v>186</v>
       </c>
@@ -16895,8 +17664,10 @@
         <v>0</v>
       </c>
       <c r="Q23" s="17"/>
-    </row>
-    <row r="24" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R23" s="163"/>
+      <c r="S23" s="163"/>
+    </row>
+    <row r="24" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A24" s="23" t="s">
         <v>187</v>
       </c>
@@ -16940,8 +17711,10 @@
         <v>0</v>
       </c>
       <c r="Q24" s="17"/>
-    </row>
-    <row r="25" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R24" s="163"/>
+      <c r="S24" s="163"/>
+    </row>
+    <row r="25" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A25" s="23" t="s">
         <v>188</v>
       </c>
@@ -16985,8 +17758,10 @@
         <v>0</v>
       </c>
       <c r="Q25" s="17"/>
-    </row>
-    <row r="26" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R25" s="163"/>
+      <c r="S25" s="163"/>
+    </row>
+    <row r="26" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
         <v>203</v>
       </c>
@@ -17030,8 +17805,10 @@
         <v>0</v>
       </c>
       <c r="Q26" s="17"/>
-    </row>
-    <row r="27" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R26" s="163"/>
+      <c r="S26" s="163"/>
+    </row>
+    <row r="27" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A27" s="23" t="s">
         <v>205</v>
       </c>
@@ -17075,8 +17852,10 @@
         <v>0</v>
       </c>
       <c r="Q27" s="17"/>
-    </row>
-    <row r="28" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R27" s="163"/>
+      <c r="S27" s="163"/>
+    </row>
+    <row r="28" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A28" s="23" t="s">
         <v>206</v>
       </c>
@@ -17120,8 +17899,10 @@
         <v>0</v>
       </c>
       <c r="Q28" s="17"/>
-    </row>
-    <row r="29" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R28" s="163"/>
+      <c r="S28" s="163"/>
+    </row>
+    <row r="29" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="s">
         <v>207</v>
       </c>
@@ -17165,8 +17946,10 @@
         <v>0</v>
       </c>
       <c r="Q29" s="17"/>
-    </row>
-    <row r="30" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R29" s="163"/>
+      <c r="S29" s="163"/>
+    </row>
+    <row r="30" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A30" s="23" t="s">
         <v>208</v>
       </c>
@@ -17210,8 +17993,10 @@
         <v>0</v>
       </c>
       <c r="Q30" s="17"/>
-    </row>
-    <row r="31" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R30" s="163"/>
+      <c r="S30" s="163"/>
+    </row>
+    <row r="31" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
         <v>209</v>
       </c>
@@ -17255,8 +18040,10 @@
         <v>0</v>
       </c>
       <c r="Q31" s="17"/>
-    </row>
-    <row r="32" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R31" s="163"/>
+      <c r="S31" s="163"/>
+    </row>
+    <row r="32" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A32" s="23" t="s">
         <v>210</v>
       </c>
@@ -17300,8 +18087,10 @@
         <v>0</v>
       </c>
       <c r="Q32" s="17"/>
-    </row>
-    <row r="33" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R32" s="163"/>
+      <c r="S32" s="163"/>
+    </row>
+    <row r="33" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A33" s="23" t="s">
         <v>211</v>
       </c>
@@ -17345,8 +18134,10 @@
         <v>0</v>
       </c>
       <c r="Q33" s="17"/>
-    </row>
-    <row r="34" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R33" s="163"/>
+      <c r="S33" s="163"/>
+    </row>
+    <row r="34" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
         <v>212</v>
       </c>
@@ -17390,8 +18181,10 @@
         <v>0</v>
       </c>
       <c r="Q34" s="17"/>
-    </row>
-    <row r="35" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R34" s="163"/>
+      <c r="S34" s="163"/>
+    </row>
+    <row r="35" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A35" s="23" t="s">
         <v>233</v>
       </c>
@@ -17441,8 +18234,10 @@
         <v>0</v>
       </c>
       <c r="Q35" s="17"/>
-    </row>
-    <row r="36" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R35" s="163"/>
+      <c r="S35" s="163"/>
+    </row>
+    <row r="36" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A36" s="23" t="s">
         <v>236</v>
       </c>
@@ -17492,8 +18287,10 @@
         <v>0</v>
       </c>
       <c r="Q36" s="17"/>
-    </row>
-    <row r="37" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R36" s="163"/>
+      <c r="S36" s="163"/>
+    </row>
+    <row r="37" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A37" s="23" t="s">
         <v>238</v>
       </c>
@@ -17543,8 +18340,10 @@
         <v>0</v>
       </c>
       <c r="Q37" s="17"/>
-    </row>
-    <row r="38" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R37" s="163"/>
+      <c r="S37" s="163"/>
+    </row>
+    <row r="38" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A38" s="23" t="s">
         <v>239</v>
       </c>
@@ -17594,8 +18393,10 @@
         <v>0</v>
       </c>
       <c r="Q38" s="17"/>
-    </row>
-    <row r="39" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R38" s="163"/>
+      <c r="S38" s="163"/>
+    </row>
+    <row r="39" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
         <v>251</v>
       </c>
@@ -17645,8 +18446,10 @@
         <v>0</v>
       </c>
       <c r="Q39" s="17"/>
-    </row>
-    <row r="40" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R39" s="163"/>
+      <c r="S39" s="163"/>
+    </row>
+    <row r="40" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A40" s="23" t="s">
         <v>253</v>
       </c>
@@ -17696,8 +18499,10 @@
         <v>0</v>
       </c>
       <c r="Q40" s="17"/>
-    </row>
-    <row r="41" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R40" s="163"/>
+      <c r="S40" s="163"/>
+    </row>
+    <row r="41" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A41" s="23" t="s">
         <v>254</v>
       </c>
@@ -17747,8 +18552,10 @@
         <v>0</v>
       </c>
       <c r="Q41" s="17"/>
-    </row>
-    <row r="42" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R41" s="163"/>
+      <c r="S41" s="163"/>
+    </row>
+    <row r="42" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A42" s="23" t="s">
         <v>255</v>
       </c>
@@ -17798,8 +18605,10 @@
         <v>0</v>
       </c>
       <c r="Q42" s="17"/>
-    </row>
-    <row r="43" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R42" s="163"/>
+      <c r="S42" s="163"/>
+    </row>
+    <row r="43" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A43" s="23" t="s">
         <v>256</v>
       </c>
@@ -17849,8 +18658,10 @@
         <v>0</v>
       </c>
       <c r="Q43" s="17"/>
-    </row>
-    <row r="44" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R43" s="163"/>
+      <c r="S43" s="163"/>
+    </row>
+    <row r="44" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A44" s="23" t="s">
         <v>257</v>
       </c>
@@ -17900,8 +18711,10 @@
         <v>0</v>
       </c>
       <c r="Q44" s="17"/>
-    </row>
-    <row r="45" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R44" s="163"/>
+      <c r="S44" s="163"/>
+    </row>
+    <row r="45" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A45" s="23" t="s">
         <v>258</v>
       </c>
@@ -17951,8 +18764,10 @@
         <v>0</v>
       </c>
       <c r="Q45" s="17"/>
-    </row>
-    <row r="46" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R45" s="163"/>
+      <c r="S45" s="163"/>
+    </row>
+    <row r="46" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A46" s="23" t="s">
         <v>259</v>
       </c>
@@ -18002,8 +18817,10 @@
         <v>0</v>
       </c>
       <c r="Q46" s="17"/>
-    </row>
-    <row r="47" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R46" s="163"/>
+      <c r="S46" s="163"/>
+    </row>
+    <row r="47" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A47" s="23" t="s">
         <v>18</v>
       </c>
@@ -18053,8 +18870,10 @@
         <v>0</v>
       </c>
       <c r="Q47" s="17"/>
-    </row>
-    <row r="48" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R47" s="163"/>
+      <c r="S47" s="163"/>
+    </row>
+    <row r="48" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A48" s="23" t="s">
         <v>26</v>
       </c>
@@ -18104,8 +18923,10 @@
         <v>0</v>
       </c>
       <c r="Q48" s="17"/>
-    </row>
-    <row r="49" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R48" s="163"/>
+      <c r="S48" s="163"/>
+    </row>
+    <row r="49" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A49" s="23" t="s">
         <v>29</v>
       </c>
@@ -18155,8 +18976,10 @@
         <v>0</v>
       </c>
       <c r="Q49" s="17"/>
-    </row>
-    <row r="50" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R49" s="163"/>
+      <c r="S49" s="163"/>
+    </row>
+    <row r="50" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A50" s="23" t="s">
         <v>31</v>
       </c>
@@ -18206,8 +19029,10 @@
         <v>0</v>
       </c>
       <c r="Q50" s="17"/>
-    </row>
-    <row r="51" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R50" s="163"/>
+      <c r="S50" s="163"/>
+    </row>
+    <row r="51" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A51" s="23" t="s">
         <v>32</v>
       </c>
@@ -18257,8 +19082,10 @@
         <v>0</v>
       </c>
       <c r="Q51" s="17"/>
-    </row>
-    <row r="52" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R51" s="163"/>
+      <c r="S51" s="163"/>
+    </row>
+    <row r="52" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A52" s="23" t="s">
         <v>34</v>
       </c>
@@ -18308,8 +19135,10 @@
         <v>0</v>
       </c>
       <c r="Q52" s="17"/>
-    </row>
-    <row r="53" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R52" s="163"/>
+      <c r="S52" s="163"/>
+    </row>
+    <row r="53" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A53" s="23" t="s">
         <v>189</v>
       </c>
@@ -18359,8 +19188,10 @@
         <v>0</v>
       </c>
       <c r="Q53" s="17"/>
-    </row>
-    <row r="54" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R53" s="163"/>
+      <c r="S53" s="163"/>
+    </row>
+    <row r="54" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A54" s="23" t="s">
         <v>191</v>
       </c>
@@ -18410,8 +19241,10 @@
         <v>0</v>
       </c>
       <c r="Q54" s="17"/>
-    </row>
-    <row r="55" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R54" s="163"/>
+      <c r="S54" s="163"/>
+    </row>
+    <row r="55" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A55" s="23" t="s">
         <v>192</v>
       </c>
@@ -18461,8 +19294,10 @@
         <v>0</v>
       </c>
       <c r="Q55" s="17"/>
-    </row>
-    <row r="56" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R55" s="163"/>
+      <c r="S55" s="163"/>
+    </row>
+    <row r="56" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A56" s="23" t="s">
         <v>193</v>
       </c>
@@ -18512,8 +19347,10 @@
         <v>0</v>
       </c>
       <c r="Q56" s="17"/>
-    </row>
-    <row r="57" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R56" s="163"/>
+      <c r="S56" s="163"/>
+    </row>
+    <row r="57" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A57" s="23" t="s">
         <v>194</v>
       </c>
@@ -18563,8 +19400,10 @@
         <v>0</v>
       </c>
       <c r="Q57" s="17"/>
-    </row>
-    <row r="58" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R57" s="163"/>
+      <c r="S57" s="163"/>
+    </row>
+    <row r="58" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A58" s="23" t="s">
         <v>195</v>
       </c>
@@ -18614,8 +19453,10 @@
         <v>0</v>
       </c>
       <c r="Q58" s="17"/>
-    </row>
-    <row r="59" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R58" s="163"/>
+      <c r="S58" s="163"/>
+    </row>
+    <row r="59" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A59" s="23" t="s">
         <v>161</v>
       </c>
@@ -18665,8 +19506,10 @@
         <v>0</v>
       </c>
       <c r="Q59" s="17"/>
-    </row>
-    <row r="60" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R59" s="163"/>
+      <c r="S59" s="163"/>
+    </row>
+    <row r="60" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A60" s="23" t="s">
         <v>196</v>
       </c>
@@ -18716,8 +19559,10 @@
         <v>0</v>
       </c>
       <c r="Q60" s="17"/>
-    </row>
-    <row r="61" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R60" s="163"/>
+      <c r="S60" s="163"/>
+    </row>
+    <row r="61" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
         <v>163</v>
       </c>
@@ -18767,8 +19612,10 @@
         <v>0</v>
       </c>
       <c r="Q61" s="17"/>
-    </row>
-    <row r="62" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R61" s="163"/>
+      <c r="S61" s="163"/>
+    </row>
+    <row r="62" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A62" s="23" t="s">
         <v>164</v>
       </c>
@@ -18818,8 +19665,10 @@
         <v>0</v>
       </c>
       <c r="Q62" s="17"/>
-    </row>
-    <row r="63" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R62" s="163"/>
+      <c r="S62" s="163"/>
+    </row>
+    <row r="63" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A63" s="23" t="s">
         <v>165</v>
       </c>
@@ -18869,8 +19718,10 @@
         <v>0</v>
       </c>
       <c r="Q63" s="17"/>
-    </row>
-    <row r="64" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R63" s="163"/>
+      <c r="S63" s="163"/>
+    </row>
+    <row r="64" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A64" s="23" t="s">
         <v>166</v>
       </c>
@@ -18920,8 +19771,10 @@
         <v>0</v>
       </c>
       <c r="Q64" s="17"/>
-    </row>
-    <row r="65" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R64" s="163"/>
+      <c r="S64" s="163"/>
+    </row>
+    <row r="65" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A65" s="23" t="s">
         <v>167</v>
       </c>
@@ -18971,8 +19824,10 @@
         <v>0</v>
       </c>
       <c r="Q65" s="17"/>
-    </row>
-    <row r="66" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R65" s="163"/>
+      <c r="S65" s="163"/>
+    </row>
+    <row r="66" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A66" s="23" t="s">
         <v>168</v>
       </c>
@@ -19022,8 +19877,10 @@
         <v>0</v>
       </c>
       <c r="Q66" s="17"/>
-    </row>
-    <row r="67" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R66" s="163"/>
+      <c r="S66" s="163"/>
+    </row>
+    <row r="67" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A67" s="23" t="s">
         <v>169</v>
       </c>
@@ -19073,8 +19930,10 @@
         <v>0</v>
       </c>
       <c r="Q67" s="17"/>
-    </row>
-    <row r="68" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R67" s="163"/>
+      <c r="S67" s="163"/>
+    </row>
+    <row r="68" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A68" s="23" t="s">
         <v>170</v>
       </c>
@@ -19124,8 +19983,10 @@
         <v>0</v>
       </c>
       <c r="Q68" s="17"/>
-    </row>
-    <row r="69" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R68" s="163"/>
+      <c r="S68" s="163"/>
+    </row>
+    <row r="69" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A69" s="23" t="s">
         <v>128</v>
       </c>
@@ -19175,8 +20036,10 @@
         <v>0</v>
       </c>
       <c r="Q69" s="17"/>
-    </row>
-    <row r="70" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R69" s="163"/>
+      <c r="S69" s="163"/>
+    </row>
+    <row r="70" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A70" s="23" t="s">
         <v>131</v>
       </c>
@@ -19226,8 +20089,10 @@
         <v>0</v>
       </c>
       <c r="Q70" s="17"/>
-    </row>
-    <row r="71" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R70" s="163"/>
+      <c r="S70" s="163"/>
+    </row>
+    <row r="71" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A71" s="23" t="s">
         <v>133</v>
       </c>
@@ -19277,8 +20142,10 @@
         <v>0</v>
       </c>
       <c r="Q71" s="17"/>
-    </row>
-    <row r="72" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R71" s="163"/>
+      <c r="S71" s="163"/>
+    </row>
+    <row r="72" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A72" s="23" t="s">
         <v>134</v>
       </c>
@@ -19328,8 +20195,10 @@
         <v>0</v>
       </c>
       <c r="Q72" s="17"/>
-    </row>
-    <row r="73" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R72" s="163"/>
+      <c r="S72" s="163"/>
+    </row>
+    <row r="73" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A73" s="23" t="s">
         <v>135</v>
       </c>
@@ -19379,8 +20248,10 @@
         <v>0</v>
       </c>
       <c r="Q73" s="17"/>
-    </row>
-    <row r="74" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R73" s="163"/>
+      <c r="S73" s="163"/>
+    </row>
+    <row r="74" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A74" s="23" t="s">
         <v>136</v>
       </c>
@@ -19430,8 +20301,10 @@
         <v>0</v>
       </c>
       <c r="Q74" s="17"/>
-    </row>
-    <row r="75" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R74" s="163"/>
+      <c r="S74" s="163"/>
+    </row>
+    <row r="75" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A75" s="23" t="s">
         <v>137</v>
       </c>
@@ -19481,8 +20354,10 @@
         <v>0</v>
       </c>
       <c r="Q75" s="17"/>
-    </row>
-    <row r="76" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R75" s="163"/>
+      <c r="S75" s="163"/>
+    </row>
+    <row r="76" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A76" s="23" t="s">
         <v>138</v>
       </c>
@@ -19532,8 +20407,10 @@
         <v>0</v>
       </c>
       <c r="Q76" s="17"/>
-    </row>
-    <row r="77" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R76" s="163"/>
+      <c r="S76" s="163"/>
+    </row>
+    <row r="77" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A77" s="23" t="s">
         <v>96</v>
       </c>
@@ -19585,8 +20462,14 @@
       <c r="Q77" s="57">
         <v>46216</v>
       </c>
-    </row>
-    <row r="78" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R77" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S77" s="163" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A78" s="23" t="s">
         <v>99</v>
       </c>
@@ -19636,8 +20519,14 @@
         <v>0</v>
       </c>
       <c r="Q78" s="17"/>
-    </row>
-    <row r="79" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R78" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S78" s="163" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A79" s="23" t="s">
         <v>100</v>
       </c>
@@ -19687,8 +20576,14 @@
         <v>0</v>
       </c>
       <c r="Q79" s="17"/>
-    </row>
-    <row r="80" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R79" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S79" s="163" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A80" s="23" t="s">
         <v>101</v>
       </c>
@@ -19738,8 +20633,14 @@
         <v>0</v>
       </c>
       <c r="Q80" s="17"/>
-    </row>
-    <row r="81" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R80" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S80" s="163" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A81" s="23" t="s">
         <v>240</v>
       </c>
@@ -19789,8 +20690,14 @@
         <v>0</v>
       </c>
       <c r="Q81" s="17"/>
-    </row>
-    <row r="82" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R81" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S81" s="163" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A82" s="23" t="s">
         <v>243</v>
       </c>
@@ -19840,8 +20747,14 @@
         <v>0</v>
       </c>
       <c r="Q82" s="17"/>
-    </row>
-    <row r="83" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R82" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S82" s="163" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A83" s="23" t="s">
         <v>244</v>
       </c>
@@ -19891,8 +20804,14 @@
         <v>0</v>
       </c>
       <c r="Q83" s="17"/>
-    </row>
-    <row r="84" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R83" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S83" s="163" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A84" s="23" t="s">
         <v>245</v>
       </c>
@@ -19942,8 +20861,14 @@
         <v>0</v>
       </c>
       <c r="Q84" s="17"/>
-    </row>
-    <row r="85" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R84" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S84" s="163" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A85" s="23" t="s">
         <v>246</v>
       </c>
@@ -19993,8 +20918,14 @@
         <v>0</v>
       </c>
       <c r="Q85" s="17"/>
-    </row>
-    <row r="86" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R85" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S85" s="163" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A86" s="23" t="s">
         <v>247</v>
       </c>
@@ -20044,8 +20975,14 @@
         <v>0</v>
       </c>
       <c r="Q86" s="17"/>
-    </row>
-    <row r="87" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R86" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S86" s="163" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A87" s="23" t="s">
         <v>248</v>
       </c>
@@ -20095,8 +21032,14 @@
         <v>0</v>
       </c>
       <c r="Q87" s="17"/>
-    </row>
-    <row r="88" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R87" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S87" s="163" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A88" s="23" t="s">
         <v>249</v>
       </c>
@@ -20146,8 +21089,14 @@
         <v>0</v>
       </c>
       <c r="Q88" s="17"/>
-    </row>
-    <row r="89" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R88" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S88" s="163" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A89" s="23" t="s">
         <v>250</v>
       </c>
@@ -20194,11 +21143,17 @@
         <v>0</v>
       </c>
       <c r="P89" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" s="17"/>
-    </row>
-    <row r="90" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R89" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S89" s="163" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A90" s="23" t="s">
         <v>228</v>
       </c>
@@ -20248,8 +21203,14 @@
         <v>0</v>
       </c>
       <c r="Q90" s="17"/>
-    </row>
-    <row r="91" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R90" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S90" s="163" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A91" s="23" t="s">
         <v>231</v>
       </c>
@@ -20299,8 +21260,14 @@
         <v>0</v>
       </c>
       <c r="Q91" s="17"/>
-    </row>
-    <row r="92" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R91" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S91" s="163" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A92" s="23" t="s">
         <v>232</v>
       </c>
@@ -20350,8 +21317,14 @@
         <v>0</v>
       </c>
       <c r="Q92" s="17"/>
-    </row>
-    <row r="93" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R92" s="166">
+        <v>46234</v>
+      </c>
+      <c r="S92" s="163" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A93" s="23" t="s">
         <v>197</v>
       </c>
@@ -20401,8 +21374,14 @@
         <v>0</v>
       </c>
       <c r="Q93" s="17"/>
-    </row>
-    <row r="94" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R93" s="166">
+        <v>46204.240972222222</v>
+      </c>
+      <c r="S93" s="163">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A94" s="23" t="s">
         <v>199</v>
       </c>
@@ -20452,8 +21431,14 @@
         <v>0</v>
       </c>
       <c r="Q94" s="17"/>
-    </row>
-    <row r="95" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R94" s="166">
+        <v>46204.455555555556</v>
+      </c>
+      <c r="S94" s="163">
+        <v>11.769</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A95" s="23" t="s">
         <v>200</v>
       </c>
@@ -20503,8 +21488,14 @@
         <v>0</v>
       </c>
       <c r="Q95" s="57"/>
-    </row>
-    <row r="96" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R95" s="166">
+        <v>46204.240972222222</v>
+      </c>
+      <c r="S95" s="163">
+        <v>8.2000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A96" s="23" t="s">
         <v>201</v>
       </c>
@@ -20554,8 +21545,14 @@
         <v>0</v>
       </c>
       <c r="Q96" s="17"/>
-    </row>
-    <row r="97" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R96" s="166">
+        <v>46204.697916666664</v>
+      </c>
+      <c r="S96" s="163">
+        <v>2.952</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A97" s="23" t="s">
         <v>202</v>
       </c>
@@ -20607,8 +21604,14 @@
       <c r="Q97" s="57">
         <v>46216</v>
       </c>
-    </row>
-    <row r="98" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R97" s="166">
+        <v>46204.657638888886</v>
+      </c>
+      <c r="S97" s="163">
+        <v>8.5999999999999993E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A98" s="23" t="s">
         <v>171</v>
       </c>
@@ -20658,8 +21661,14 @@
         <v>0</v>
       </c>
       <c r="Q98" s="17"/>
-    </row>
-    <row r="99" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R98" s="166">
+        <v>46204.699305555558</v>
+      </c>
+      <c r="S98" s="163">
+        <v>32.673999999999999</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A99" s="23" t="s">
         <v>173</v>
       </c>
@@ -20709,8 +21718,14 @@
         <v>0</v>
       </c>
       <c r="Q99" s="17"/>
-    </row>
-    <row r="100" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R99" s="166">
+        <v>46204.657638888886</v>
+      </c>
+      <c r="S99" s="163">
+        <v>4.1719999999999997</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A100" s="23" t="s">
         <v>175</v>
       </c>
@@ -20760,8 +21775,14 @@
         <v>0</v>
       </c>
       <c r="Q100" s="17"/>
-    </row>
-    <row r="101" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R100" s="166">
+        <v>46204.459027777775</v>
+      </c>
+      <c r="S100" s="163">
+        <v>4.3360000000000003</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="s">
         <v>176</v>
       </c>
@@ -20811,8 +21832,14 @@
         <v>0</v>
       </c>
       <c r="Q101" s="17"/>
-    </row>
-    <row r="102" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R101" s="166">
+        <v>46204.329861111109</v>
+      </c>
+      <c r="S101" s="163">
+        <v>4.3209</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A102" s="23" t="s">
         <v>177</v>
       </c>
@@ -20862,8 +21889,14 @@
         <v>0</v>
       </c>
       <c r="Q102" s="17"/>
-    </row>
-    <row r="103" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R102" s="166">
+        <v>46204.677083333336</v>
+      </c>
+      <c r="S102" s="163">
+        <v>9.7119999999999997</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A103" s="23" t="s">
         <v>178</v>
       </c>
@@ -20913,8 +21946,14 @@
         <v>0</v>
       </c>
       <c r="Q103" s="17"/>
-    </row>
-    <row r="104" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R103" s="166">
+        <v>46204.330555555556</v>
+      </c>
+      <c r="S103" s="163">
+        <v>4.1757999999999997</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A104" s="23" t="s">
         <v>179</v>
       </c>
@@ -20966,8 +22005,14 @@
       <c r="Q104" s="57">
         <v>46216</v>
       </c>
-    </row>
-    <row r="105" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R104" s="166">
+        <v>46204.677083333336</v>
+      </c>
+      <c r="S104" s="165">
+        <v>9.7000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="s">
         <v>139</v>
       </c>
@@ -21011,8 +22056,10 @@
         <v>0</v>
       </c>
       <c r="Q105" s="17"/>
-    </row>
-    <row r="106" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R105" s="163"/>
+      <c r="S105" s="163"/>
+    </row>
+    <row r="106" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A106" s="23" t="s">
         <v>180</v>
       </c>
@@ -21064,8 +22111,14 @@
       <c r="Q106" s="57">
         <v>46206</v>
       </c>
-    </row>
-    <row r="107" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R106" s="166">
+        <v>46204.677083333336</v>
+      </c>
+      <c r="S106" s="165">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A107" s="23" t="s">
         <v>141</v>
       </c>
@@ -21109,8 +22162,10 @@
         <v>0</v>
       </c>
       <c r="Q107" s="17"/>
-    </row>
-    <row r="108" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R107" s="163"/>
+      <c r="S107" s="163"/>
+    </row>
+    <row r="108" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A108" s="23" t="s">
         <v>142</v>
       </c>
@@ -21160,8 +22215,14 @@
         <v>0</v>
       </c>
       <c r="Q108" s="17"/>
-    </row>
-    <row r="109" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R108" s="164">
+        <v>46204.702777777777</v>
+      </c>
+      <c r="S108" s="165">
+        <v>20.81</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A109" s="23" t="s">
         <v>144</v>
       </c>
@@ -21205,8 +22266,10 @@
         <v>0</v>
       </c>
       <c r="Q109" s="17"/>
-    </row>
-    <row r="110" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R109" s="163"/>
+      <c r="S109" s="163"/>
+    </row>
+    <row r="110" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A110" s="23" t="s">
         <v>145</v>
       </c>
@@ -21258,8 +22321,14 @@
       <c r="Q110" s="57">
         <v>46206</v>
       </c>
-    </row>
-    <row r="111" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R110" s="164">
+        <v>46204.702777777777</v>
+      </c>
+      <c r="S110" s="165">
+        <v>6.8000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A111" s="23" t="s">
         <v>146</v>
       </c>
@@ -21303,8 +22372,10 @@
         <v>0</v>
       </c>
       <c r="Q111" s="17"/>
-    </row>
-    <row r="112" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R111" s="163"/>
+      <c r="S111" s="163"/>
+    </row>
+    <row r="112" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A112" s="23" t="s">
         <v>147</v>
       </c>
@@ -21354,8 +22425,14 @@
         <v>0</v>
       </c>
       <c r="Q112" s="17"/>
-    </row>
-    <row r="113" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R112" s="166">
+        <v>46204.462500000001</v>
+      </c>
+      <c r="S112" s="163">
+        <v>8.8550000000000004</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A113" s="23" t="s">
         <v>105</v>
       </c>
@@ -21399,8 +22476,10 @@
         <v>0</v>
       </c>
       <c r="Q113" s="17"/>
-    </row>
-    <row r="114" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R113" s="163"/>
+      <c r="S113" s="163"/>
+    </row>
+    <row r="114" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A114" s="23" t="s">
         <v>148</v>
       </c>
@@ -21450,8 +22529,14 @@
         <v>0</v>
       </c>
       <c r="Q114" s="17"/>
-    </row>
-    <row r="115" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R114" s="166">
+        <v>46204.448611111111</v>
+      </c>
+      <c r="S114" s="163">
+        <v>6.4509999999999996</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A115" s="23" t="s">
         <v>108</v>
       </c>
@@ -21495,8 +22580,10 @@
         <v>0</v>
       </c>
       <c r="Q115" s="17"/>
-    </row>
-    <row r="116" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R115" s="163"/>
+      <c r="S115" s="163"/>
+    </row>
+    <row r="116" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A116" s="23" t="s">
         <v>149</v>
       </c>
@@ -21546,8 +22633,14 @@
         <v>0</v>
       </c>
       <c r="Q116" s="17"/>
-    </row>
-    <row r="117" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R116" s="166">
+        <v>46204.448611111111</v>
+      </c>
+      <c r="S116" s="163">
+        <v>4.7329999999999997</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A117" s="23" t="s">
         <v>109</v>
       </c>
@@ -21591,8 +22684,10 @@
         <v>0</v>
       </c>
       <c r="Q117" s="17"/>
-    </row>
-    <row r="118" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R117" s="163"/>
+      <c r="S117" s="163"/>
+    </row>
+    <row r="118" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A118" s="23" t="s">
         <v>110</v>
       </c>
@@ -21642,8 +22737,14 @@
         <v>0</v>
       </c>
       <c r="Q118" s="17"/>
-    </row>
-    <row r="119" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R118" s="166">
+        <v>46204.448611111111</v>
+      </c>
+      <c r="S118" s="163">
+        <v>20.442</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A119" s="23" t="s">
         <v>111</v>
       </c>
@@ -21687,8 +22788,10 @@
         <v>0</v>
       </c>
       <c r="Q119" s="17"/>
-    </row>
-    <row r="120" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R119" s="163"/>
+      <c r="S119" s="163"/>
+    </row>
+    <row r="120" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A120" s="23" t="s">
         <v>112</v>
       </c>
@@ -21738,8 +22841,14 @@
         <v>0</v>
       </c>
       <c r="Q120" s="17"/>
-    </row>
-    <row r="121" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R120" s="166">
+        <v>46204.448611111111</v>
+      </c>
+      <c r="S120" s="163">
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A121" s="23" t="s">
         <v>113</v>
       </c>
@@ -21783,8 +22892,10 @@
         <v>0</v>
       </c>
       <c r="Q121" s="17"/>
-    </row>
-    <row r="122" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R121" s="163"/>
+      <c r="S121" s="163"/>
+    </row>
+    <row r="122" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A122" s="23" t="s">
         <v>114</v>
       </c>
@@ -21834,8 +22945,14 @@
         <v>0</v>
       </c>
       <c r="Q122" s="17"/>
-    </row>
-    <row r="123" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R122" s="166">
+        <v>46204.448611111111</v>
+      </c>
+      <c r="S122" s="163">
+        <v>7.593</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A123" s="23" t="s">
         <v>74</v>
       </c>
@@ -21879,8 +22996,10 @@
         <v>0</v>
       </c>
       <c r="Q123" s="17"/>
-    </row>
-    <row r="124" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R123" s="163"/>
+      <c r="S123" s="163"/>
+    </row>
+    <row r="124" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A124" s="23" t="s">
         <v>115</v>
       </c>
@@ -21930,8 +23049,14 @@
         <v>0</v>
       </c>
       <c r="Q124" s="17"/>
-    </row>
-    <row r="125" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R124" s="166">
+        <v>46204.448611111111</v>
+      </c>
+      <c r="S124" s="163">
+        <v>3.8929999999999998</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A125" s="23" t="s">
         <v>77</v>
       </c>
@@ -21975,8 +23100,10 @@
         <v>0</v>
       </c>
       <c r="Q125" s="17"/>
-    </row>
-    <row r="126" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R125" s="163"/>
+      <c r="S125" s="163"/>
+    </row>
+    <row r="126" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A126" s="23" t="s">
         <v>78</v>
       </c>
@@ -22028,8 +23155,14 @@
       <c r="Q126" s="57">
         <v>46206</v>
       </c>
-    </row>
-    <row r="127" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R126" s="166">
+        <v>46204.448611111111</v>
+      </c>
+      <c r="S126" s="163">
+        <v>1.163</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A127" s="23" t="s">
         <v>81</v>
       </c>
@@ -22073,8 +23206,10 @@
         <v>0</v>
       </c>
       <c r="Q127" s="17"/>
-    </row>
-    <row r="128" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R127" s="163"/>
+      <c r="S127" s="163"/>
+    </row>
+    <row r="128" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A128" s="23" t="s">
         <v>82</v>
       </c>
@@ -22124,8 +23259,14 @@
         <v>0</v>
       </c>
       <c r="Q128" s="17"/>
-    </row>
-    <row r="129" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R128" s="166">
+        <v>46204.448611111111</v>
+      </c>
+      <c r="S128" s="163">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A129" s="23" t="s">
         <v>83</v>
       </c>
@@ -22169,8 +23310,10 @@
         <v>0</v>
       </c>
       <c r="Q129" s="17"/>
-    </row>
-    <row r="130" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R129" s="163"/>
+      <c r="S129" s="163"/>
+    </row>
+    <row r="130" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A130" s="23" t="s">
         <v>84</v>
       </c>
@@ -22214,8 +23357,10 @@
         <v>0</v>
       </c>
       <c r="Q130" s="17"/>
-    </row>
-    <row r="131" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R130" s="163"/>
+      <c r="S130" s="163"/>
+    </row>
+    <row r="131" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A131" s="23" t="s">
         <v>85</v>
       </c>
@@ -22259,8 +23404,10 @@
         <v>0</v>
       </c>
       <c r="Q131" s="17"/>
-    </row>
-    <row r="132" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R131" s="163"/>
+      <c r="S131" s="163"/>
+    </row>
+    <row r="132" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A132" s="23" t="s">
         <v>86</v>
       </c>
@@ -22304,8 +23451,10 @@
         <v>0</v>
       </c>
       <c r="Q132" s="17"/>
-    </row>
-    <row r="133" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R132" s="163"/>
+      <c r="S132" s="163"/>
+    </row>
+    <row r="133" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A133" s="23" t="s">
         <v>260</v>
       </c>
@@ -22349,8 +23498,10 @@
         <v>0</v>
       </c>
       <c r="Q133" s="17"/>
-    </row>
-    <row r="134" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R133" s="163"/>
+      <c r="S133" s="163"/>
+    </row>
+    <row r="134" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A134" s="23" t="s">
         <v>263</v>
       </c>
@@ -22394,8 +23545,10 @@
         <v>0</v>
       </c>
       <c r="Q134" s="17"/>
-    </row>
-    <row r="135" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R134" s="163"/>
+      <c r="S134" s="163"/>
+    </row>
+    <row r="135" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A135" s="23" t="s">
         <v>264</v>
       </c>
@@ -22439,8 +23592,10 @@
         <v>0</v>
       </c>
       <c r="Q135" s="17"/>
-    </row>
-    <row r="136" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R135" s="163"/>
+      <c r="S135" s="163"/>
+    </row>
+    <row r="136" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A136" s="23" t="s">
         <v>265</v>
       </c>
@@ -22484,8 +23639,10 @@
         <v>0</v>
       </c>
       <c r="Q136" s="17"/>
-    </row>
-    <row r="137" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R136" s="163"/>
+      <c r="S136" s="163"/>
+    </row>
+    <row r="137" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A137" s="23" t="s">
         <v>266</v>
       </c>
@@ -22529,8 +23686,10 @@
         <v>0</v>
       </c>
       <c r="Q137" s="17"/>
-    </row>
-    <row r="138" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R137" s="163"/>
+      <c r="S137" s="163"/>
+    </row>
+    <row r="138" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A138" s="23" t="s">
         <v>267</v>
       </c>
@@ -22574,8 +23733,10 @@
         <v>0</v>
       </c>
       <c r="Q138" s="17"/>
-    </row>
-    <row r="139" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R138" s="163"/>
+      <c r="S138" s="163"/>
+    </row>
+    <row r="139" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A139" s="23" t="s">
         <v>268</v>
       </c>
@@ -22619,8 +23780,10 @@
         <v>0</v>
       </c>
       <c r="Q139" s="17"/>
-    </row>
-    <row r="140" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R139" s="163"/>
+      <c r="S139" s="163"/>
+    </row>
+    <row r="140" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A140" s="23" t="s">
         <v>269</v>
       </c>
@@ -22664,8 +23827,10 @@
         <v>0</v>
       </c>
       <c r="Q140" s="17"/>
-    </row>
-    <row r="141" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R140" s="163"/>
+      <c r="S140" s="163"/>
+    </row>
+    <row r="141" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A141" s="23" t="s">
         <v>35</v>
       </c>
@@ -22709,8 +23874,10 @@
         <v>0</v>
       </c>
       <c r="Q141" s="17"/>
-    </row>
-    <row r="142" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R141" s="163"/>
+      <c r="S141" s="163"/>
+    </row>
+    <row r="142" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A142" s="23" t="s">
         <v>38</v>
       </c>
@@ -22754,8 +23921,10 @@
         <v>0</v>
       </c>
       <c r="Q142" s="17"/>
-    </row>
-    <row r="143" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R142" s="163"/>
+      <c r="S142" s="163"/>
+    </row>
+    <row r="143" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A143" s="23" t="s">
         <v>40</v>
       </c>
@@ -22799,8 +23968,10 @@
         <v>0</v>
       </c>
       <c r="Q143" s="17"/>
-    </row>
-    <row r="144" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R143" s="163"/>
+      <c r="S143" s="163"/>
+    </row>
+    <row r="144" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A144" s="23" t="s">
         <v>41</v>
       </c>
@@ -22844,8 +24015,10 @@
         <v>0</v>
       </c>
       <c r="Q144" s="17"/>
-    </row>
-    <row r="145" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R144" s="163"/>
+      <c r="S144" s="163"/>
+    </row>
+    <row r="145" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A145" s="23" t="s">
         <v>42</v>
       </c>
@@ -22889,8 +24062,10 @@
         <v>0</v>
       </c>
       <c r="Q145" s="17"/>
-    </row>
-    <row r="146" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R145" s="163"/>
+      <c r="S145" s="163"/>
+    </row>
+    <row r="146" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A146" s="23" t="s">
         <v>43</v>
       </c>
@@ -22934,8 +24109,10 @@
         <v>0</v>
       </c>
       <c r="Q146" s="17"/>
-    </row>
-    <row r="147" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R146" s="163"/>
+      <c r="S146" s="163"/>
+    </row>
+    <row r="147" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A147" s="23" t="s">
         <v>45</v>
       </c>
@@ -22979,8 +24156,10 @@
         <v>0</v>
       </c>
       <c r="Q147" s="17"/>
-    </row>
-    <row r="148" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R147" s="163"/>
+      <c r="S147" s="163"/>
+    </row>
+    <row r="148" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A148" s="23" t="s">
         <v>44</v>
       </c>
@@ -23024,8 +24203,10 @@
         <v>0</v>
       </c>
       <c r="Q148" s="17"/>
-    </row>
-    <row r="149" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R148" s="163"/>
+      <c r="S148" s="163"/>
+    </row>
+    <row r="149" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A149" s="23" t="s">
         <v>47</v>
       </c>
@@ -23069,8 +24250,10 @@
         <v>0</v>
       </c>
       <c r="Q149" s="17"/>
-    </row>
-    <row r="150" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R149" s="163"/>
+      <c r="S149" s="163"/>
+    </row>
+    <row r="150" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A150" s="23" t="s">
         <v>48</v>
       </c>
@@ -23114,8 +24297,10 @@
         <v>0</v>
       </c>
       <c r="Q150" s="17"/>
-    </row>
-    <row r="151" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R150" s="163"/>
+      <c r="S150" s="163"/>
+    </row>
+    <row r="151" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A151" s="23" t="s">
         <v>49</v>
       </c>
@@ -23159,8 +24344,10 @@
         <v>0</v>
       </c>
       <c r="Q151" s="17"/>
-    </row>
-    <row r="152" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R151" s="163"/>
+      <c r="S151" s="163"/>
+    </row>
+    <row r="152" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A152" s="23" t="s">
         <v>50</v>
       </c>
@@ -23204,8 +24391,10 @@
         <v>0</v>
       </c>
       <c r="Q152" s="17"/>
-    </row>
-    <row r="153" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R152" s="163"/>
+      <c r="S152" s="163"/>
+    </row>
+    <row r="153" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A153" s="23" t="s">
         <v>51</v>
       </c>
@@ -23249,8 +24438,10 @@
         <v>0</v>
       </c>
       <c r="Q153" s="17"/>
-    </row>
-    <row r="154" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R153" s="163"/>
+      <c r="S153" s="163"/>
+    </row>
+    <row r="154" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A154" s="23" t="s">
         <v>52</v>
       </c>
@@ -23294,8 +24485,10 @@
         <v>0</v>
       </c>
       <c r="Q154" s="17"/>
-    </row>
-    <row r="155" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R154" s="163"/>
+      <c r="S154" s="163"/>
+    </row>
+    <row r="155" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A155" s="23" t="s">
         <v>53</v>
       </c>
@@ -23339,8 +24532,10 @@
         <v>0</v>
       </c>
       <c r="Q155" s="17"/>
-    </row>
-    <row r="156" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R155" s="163"/>
+      <c r="S155" s="163"/>
+    </row>
+    <row r="156" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A156" s="23" t="s">
         <v>54</v>
       </c>
@@ -23384,8 +24579,10 @@
         <v>0</v>
       </c>
       <c r="Q156" s="17"/>
-    </row>
-    <row r="157" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R156" s="163"/>
+      <c r="S156" s="163"/>
+    </row>
+    <row r="157" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A157" s="23" t="s">
         <v>57</v>
       </c>
@@ -23429,8 +24626,10 @@
         <v>0</v>
       </c>
       <c r="Q157" s="17"/>
-    </row>
-    <row r="158" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R157" s="163"/>
+      <c r="S157" s="163"/>
+    </row>
+    <row r="158" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A158" s="23" t="s">
         <v>58</v>
       </c>
@@ -23474,8 +24673,10 @@
         <v>0</v>
       </c>
       <c r="Q158" s="17"/>
-    </row>
-    <row r="159" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R158" s="163"/>
+      <c r="S158" s="163"/>
+    </row>
+    <row r="159" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A159" s="23" t="s">
         <v>59</v>
       </c>
@@ -23519,8 +24720,10 @@
         <v>0</v>
       </c>
       <c r="Q159" s="17"/>
-    </row>
-    <row r="160" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R159" s="163"/>
+      <c r="S159" s="163"/>
+    </row>
+    <row r="160" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A160" s="23" t="s">
         <v>60</v>
       </c>
@@ -23564,8 +24767,10 @@
         <v>0</v>
       </c>
       <c r="Q160" s="17"/>
-    </row>
-    <row r="161" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R160" s="163"/>
+      <c r="S160" s="163"/>
+    </row>
+    <row r="161" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A161" s="23" t="s">
         <v>61</v>
       </c>
@@ -23609,8 +24814,10 @@
         <v>0</v>
       </c>
       <c r="Q161" s="17"/>
-    </row>
-    <row r="162" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R161" s="163"/>
+      <c r="S161" s="163"/>
+    </row>
+    <row r="162" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A162" s="23" t="s">
         <v>62</v>
       </c>
@@ -23654,8 +24861,10 @@
         <v>0</v>
       </c>
       <c r="Q162" s="17"/>
-    </row>
-    <row r="163" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R162" s="163"/>
+      <c r="S162" s="163"/>
+    </row>
+    <row r="163" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A163" s="23" t="s">
         <v>63</v>
       </c>
@@ -23699,8 +24908,10 @@
         <v>0</v>
       </c>
       <c r="Q163" s="17"/>
-    </row>
-    <row r="164" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R163" s="163"/>
+      <c r="S163" s="163"/>
+    </row>
+    <row r="164" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A164" s="23" t="s">
         <v>87</v>
       </c>
@@ -23744,8 +24955,10 @@
         <v>0</v>
       </c>
       <c r="Q164" s="17"/>
-    </row>
-    <row r="165" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R164" s="163"/>
+      <c r="S164" s="163"/>
+    </row>
+    <row r="165" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A165" s="23" t="s">
         <v>90</v>
       </c>
@@ -23789,8 +25002,10 @@
         <v>0</v>
       </c>
       <c r="Q165" s="17"/>
-    </row>
-    <row r="166" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R165" s="163"/>
+      <c r="S165" s="163"/>
+    </row>
+    <row r="166" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A166" s="23" t="s">
         <v>91</v>
       </c>
@@ -23834,8 +25049,10 @@
         <v>0</v>
       </c>
       <c r="Q166" s="17"/>
-    </row>
-    <row r="167" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R166" s="163"/>
+      <c r="S166" s="163"/>
+    </row>
+    <row r="167" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A167" s="23" t="s">
         <v>92</v>
       </c>
@@ -23879,8 +25096,10 @@
         <v>0</v>
       </c>
       <c r="Q167" s="17"/>
-    </row>
-    <row r="168" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R167" s="163"/>
+      <c r="S167" s="163"/>
+    </row>
+    <row r="168" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A168" s="23" t="s">
         <v>93</v>
       </c>
@@ -23924,8 +25143,10 @@
         <v>0</v>
       </c>
       <c r="Q168" s="17"/>
-    </row>
-    <row r="169" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R168" s="163"/>
+      <c r="S168" s="163"/>
+    </row>
+    <row r="169" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A169" s="23" t="s">
         <v>94</v>
       </c>
@@ -23969,8 +25190,10 @@
         <v>0</v>
       </c>
       <c r="Q169" s="17"/>
-    </row>
-    <row r="170" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R169" s="163"/>
+      <c r="S169" s="163"/>
+    </row>
+    <row r="170" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A170" s="23" t="s">
         <v>95</v>
       </c>
@@ -24014,8 +25237,10 @@
         <v>0</v>
       </c>
       <c r="Q170" s="17"/>
-    </row>
-    <row r="171" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R170" s="163"/>
+      <c r="S170" s="163"/>
+    </row>
+    <row r="171" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A171" s="23" t="s">
         <v>220</v>
       </c>
@@ -24059,8 +25284,10 @@
         <v>0</v>
       </c>
       <c r="Q171" s="17"/>
-    </row>
-    <row r="172" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R171" s="163"/>
+      <c r="S171" s="163"/>
+    </row>
+    <row r="172" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A172" s="23" t="s">
         <v>223</v>
       </c>
@@ -24104,8 +25331,10 @@
         <v>0</v>
       </c>
       <c r="Q172" s="17"/>
-    </row>
-    <row r="173" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R172" s="163"/>
+      <c r="S172" s="163"/>
+    </row>
+    <row r="173" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A173" s="23" t="s">
         <v>224</v>
       </c>
@@ -24149,8 +25378,10 @@
         <v>0</v>
       </c>
       <c r="Q173" s="17"/>
-    </row>
-    <row r="174" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R173" s="163"/>
+      <c r="S173" s="163"/>
+    </row>
+    <row r="174" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A174" s="23" t="s">
         <v>225</v>
       </c>
@@ -24194,8 +25425,10 @@
         <v>0</v>
       </c>
       <c r="Q174" s="17"/>
-    </row>
-    <row r="175" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R174" s="163"/>
+      <c r="S174" s="163"/>
+    </row>
+    <row r="175" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A175" s="23" t="s">
         <v>226</v>
       </c>
@@ -24245,8 +25478,10 @@
         <v>0</v>
       </c>
       <c r="Q175" s="17"/>
-    </row>
-    <row r="176" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R175" s="163"/>
+      <c r="S175" s="163"/>
+    </row>
+    <row r="176" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A176" s="23" t="s">
         <v>227</v>
       </c>
@@ -24296,8 +25531,10 @@
         <v>0</v>
       </c>
       <c r="Q176" s="17"/>
-    </row>
-    <row r="177" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R176" s="163"/>
+      <c r="S176" s="163"/>
+    </row>
+    <row r="177" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A177" s="23" t="s">
         <v>213</v>
       </c>
@@ -24347,8 +25584,10 @@
         <v>0</v>
       </c>
       <c r="Q177" s="17"/>
-    </row>
-    <row r="178" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R177" s="163"/>
+      <c r="S177" s="163"/>
+    </row>
+    <row r="178" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A178" s="23" t="s">
         <v>215</v>
       </c>
@@ -24398,8 +25637,10 @@
         <v>0</v>
       </c>
       <c r="Q178" s="17"/>
-    </row>
-    <row r="179" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R178" s="163"/>
+      <c r="S178" s="163"/>
+    </row>
+    <row r="179" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A179" s="23" t="s">
         <v>216</v>
       </c>
@@ -24449,8 +25690,10 @@
         <v>0</v>
       </c>
       <c r="Q179" s="17"/>
-    </row>
-    <row r="180" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R179" s="163"/>
+      <c r="S179" s="163"/>
+    </row>
+    <row r="180" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A180" s="23" t="s">
         <v>217</v>
       </c>
@@ -24500,8 +25743,10 @@
         <v>0</v>
       </c>
       <c r="Q180" s="17"/>
-    </row>
-    <row r="181" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R180" s="163"/>
+      <c r="S180" s="163"/>
+    </row>
+    <row r="181" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A181" s="23" t="s">
         <v>218</v>
       </c>
@@ -24551,8 +25796,10 @@
         <v>0</v>
       </c>
       <c r="Q181" s="17"/>
-    </row>
-    <row r="182" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R181" s="163"/>
+      <c r="S181" s="163"/>
+    </row>
+    <row r="182" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A182" s="23" t="s">
         <v>219</v>
       </c>
@@ -24596,8 +25843,10 @@
         <v>0</v>
       </c>
       <c r="Q182" s="17"/>
-    </row>
-    <row r="183" spans="1:17" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R182" s="163"/>
+      <c r="S182" s="163"/>
+    </row>
+    <row r="183" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A183" s="23" t="s">
         <v>64</v>
       </c>
@@ -24641,8 +25890,10 @@
         <v>0</v>
       </c>
       <c r="Q183" s="17"/>
-    </row>
-    <row r="184" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R183" s="163"/>
+      <c r="S183" s="163"/>
+    </row>
+    <row r="184" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A184" s="23" t="s">
         <v>68</v>
       </c>
@@ -24692,8 +25943,10 @@
         <v>0</v>
       </c>
       <c r="Q184" s="17"/>
-    </row>
-    <row r="185" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R184" s="163"/>
+      <c r="S184" s="163"/>
+    </row>
+    <row r="185" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A185" s="23" t="s">
         <v>70</v>
       </c>
@@ -24743,8 +25996,10 @@
         <v>0</v>
       </c>
       <c r="Q185" s="17"/>
-    </row>
-    <row r="186" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R185" s="163"/>
+      <c r="S185" s="163"/>
+    </row>
+    <row r="186" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A186" s="23" t="s">
         <v>71</v>
       </c>
@@ -24794,8 +26049,10 @@
         <v>0</v>
       </c>
       <c r="Q186" s="17"/>
-    </row>
-    <row r="187" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R186" s="163"/>
+      <c r="S186" s="163"/>
+    </row>
+    <row r="187" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A187" s="23" t="s">
         <v>72</v>
       </c>
@@ -24845,8 +26102,10 @@
         <v>0</v>
       </c>
       <c r="Q187" s="17"/>
-    </row>
-    <row r="188" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R187" s="163"/>
+      <c r="S187" s="163"/>
+    </row>
+    <row r="188" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A188" s="23" t="s">
         <v>73</v>
       </c>
@@ -24896,8 +26155,10 @@
         <v>0</v>
       </c>
       <c r="Q188" s="17"/>
-    </row>
-    <row r="189" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R188" s="163"/>
+      <c r="S188" s="163"/>
+    </row>
+    <row r="189" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A189" s="23" t="s">
         <v>102</v>
       </c>
@@ -24947,8 +26208,10 @@
         <v>0</v>
       </c>
       <c r="Q189" s="17"/>
-    </row>
-    <row r="190" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R189" s="163"/>
+      <c r="S189" s="163"/>
+    </row>
+    <row r="190" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A190" s="23" t="s">
         <v>103</v>
       </c>
@@ -24998,8 +26261,10 @@
         <v>0</v>
       </c>
       <c r="Q190" s="17"/>
-    </row>
-    <row r="191" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R190" s="163"/>
+      <c r="S190" s="163"/>
+    </row>
+    <row r="191" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A191" s="23" t="s">
         <v>104</v>
       </c>
@@ -25049,8 +26314,10 @@
         <v>0</v>
       </c>
       <c r="Q191" s="17"/>
-    </row>
-    <row r="192" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R191" s="163"/>
+      <c r="S191" s="163"/>
+    </row>
+    <row r="192" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>371</v>
       </c>
@@ -25100,8 +26367,10 @@
         <v>0</v>
       </c>
       <c r="Q192" s="17"/>
-    </row>
-    <row r="193" spans="1:17" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R192" s="163"/>
+      <c r="S192" s="163"/>
+    </row>
+    <row r="193" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>374</v>
       </c>
@@ -25151,29 +26420,24 @@
         <v>0</v>
       </c>
       <c r="Q193" s="17"/>
-    </row>
-    <row r="204" spans="1:17" ht="18" x14ac:dyDescent="0.3">
+      <c r="R193" s="163"/>
+      <c r="S193" s="163"/>
+    </row>
+    <row r="204" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="Q204" s="57">
         <v>46206</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q193" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N193">
     <sortCondition ref="A2:A193"/>
   </sortState>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="C2:C63">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -30895,7 +32159,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C143:C164 C165:D176 C255:D268 C177:C254">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -35182,22 +36446,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:D125">
-    <cfRule type="duplicateValues" dxfId="8" priority="6" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="6" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C126:D251">
-    <cfRule type="duplicateValues" dxfId="7" priority="5" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="5" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E126:E251">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"Maybe"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38486,13 +39750,13 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:C17">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:C20">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L21">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -39076,6 +40340,2117 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="A3:A22">
+    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FE5B361-E32F-4CF6-B29A-00267F96CE17}">
+  <dimension ref="A1:H80"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.53125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="150" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="151" t="s">
+        <v>276</v>
+      </c>
+      <c r="D1" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="150" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="150" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1" s="150" t="s">
+        <v>278</v>
+      </c>
+      <c r="H1" s="152" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E2" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G2" s="3">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="H2" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>288</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F3" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G3" s="3">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="H3" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>289</v>
+      </c>
+      <c r="D4" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E4" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G4" s="3">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="H4" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A5" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>290</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E5" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G5" s="3">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="H5" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A6" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>291</v>
+      </c>
+      <c r="D6" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E6" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G6" s="3">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="H6" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A7" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="B7" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>292</v>
+      </c>
+      <c r="D7" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F7" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G7" s="3">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="H7" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A8" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>293</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F8" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G8" s="3">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="H8" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A9" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>294</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E9" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F9" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G9" s="3">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="H9" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A10" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>295</v>
+      </c>
+      <c r="D10" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F10" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.155</v>
+      </c>
+      <c r="H10" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A11" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>296</v>
+      </c>
+      <c r="D11" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F11" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G11" s="3">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="H11" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A12" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>297</v>
+      </c>
+      <c r="D12" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G12" s="3">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="H12" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>298</v>
+      </c>
+      <c r="D13" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E13" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F13" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G13" s="3">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="H13" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A14" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>299</v>
+      </c>
+      <c r="D14" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E14" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F14" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G14" s="3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="H14" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A15" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>300</v>
+      </c>
+      <c r="D15" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E15" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F15" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="H15" s="57">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A16" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>301</v>
+      </c>
+      <c r="D16" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E16" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G16" s="3">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="H16" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A17" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>302</v>
+      </c>
+      <c r="D17" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F17" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G17" s="3">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="H17" s="57">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A18" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>303</v>
+      </c>
+      <c r="D18" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E18" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F18" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G18" s="3">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="H18" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A19" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>304</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F19" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G19" s="3">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="H19" s="57">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A20" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>305</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E20" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G20" s="3">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="H20" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>306</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F21" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G21" s="3">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="H21" s="57">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A22" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B22" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>307</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E22" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G22" s="3">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="H22" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A23" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="B23" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E23" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F23" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G23" s="3">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="H23" s="57">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A24" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>309</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F24" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G24" s="3">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="H24" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A25" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="B25" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>310</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E25" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F25" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G25" s="3">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="H25" s="57">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A26" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>311</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E26" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F26" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G26" s="3">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="H26" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A27" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>312</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E27" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F27" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G27" s="3">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="H27" s="57">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A28" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="B28" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>313</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F28" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G28" s="3">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="H28" s="57">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A29" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B29" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>314</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F29" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G29" s="3">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="H29" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A30" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="B30" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>315</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G30" s="3">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="H30" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A31" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="B31" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>316</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F31" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G31" s="3">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="H31" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A32" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="B32" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>317</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F32" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G32" s="3">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="H32" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A33" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="B33" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>318</v>
+      </c>
+      <c r="D33" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F33" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G33" s="3">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="H33" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="21" x14ac:dyDescent="0.3">
+      <c r="A34" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="B34" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="66" t="s">
+        <v>319</v>
+      </c>
+      <c r="D34" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F34" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G34" s="3">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="H34" s="57">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A35" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="B35" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>320</v>
+      </c>
+      <c r="D35" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E35" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F35" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G35" s="3">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="H35" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A36" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="D36" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F36" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G36" s="3">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="H36" s="57">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A37" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B37" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="53" t="s">
+        <v>322</v>
+      </c>
+      <c r="D37" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E37" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F37" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G37" s="3">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="H37" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A38" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="B38" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>323</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E38" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F38" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G38" s="3">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="H38" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A39" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>324</v>
+      </c>
+      <c r="D39" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E39" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F39" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G39" s="3">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="H39" s="57">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A40" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B40" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="53" t="s">
+        <v>325</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E40" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F40" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G40" s="3">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="H40" s="57">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A41" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="B41" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>326</v>
+      </c>
+      <c r="D41" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E41" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F41" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G41" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H41" s="57">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A42" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="B42" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>327</v>
+      </c>
+      <c r="D42" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E42" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F42" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G42" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H42" s="57">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A43" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B43" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>328</v>
+      </c>
+      <c r="D43" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E43" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F43" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G43" s="3">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="H43" s="57">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A44" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="53" t="s">
+        <v>329</v>
+      </c>
+      <c r="D44" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E44" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F44" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G44" s="3">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="H44" s="57">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A45" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" s="53" t="s">
+        <v>330</v>
+      </c>
+      <c r="D45" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E45" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F45" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="H45" s="57">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A46" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" s="53">
+        <v>10172260</v>
+      </c>
+      <c r="D46" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E46" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F46" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G46" s="3">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="H46" s="57">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A47" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B47" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="53" t="s">
+        <v>331</v>
+      </c>
+      <c r="D47" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E47" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F47" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G47" s="3">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="H47" s="57">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A48" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="B48" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48" s="53">
+        <v>10172248</v>
+      </c>
+      <c r="D48" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E48" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F48" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G48" s="3">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="H48" s="57">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A49" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="B49" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49" s="53">
+        <v>10172263</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E49" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F49" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="H49" s="57">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A50" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="B50" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C50" s="53">
+        <v>10172257</v>
+      </c>
+      <c r="D50" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E50" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F50" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G50" s="3">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="H50" s="57">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A51" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="B51" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C51" s="53">
+        <v>10172256</v>
+      </c>
+      <c r="D51" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E51" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F51" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G51" s="3">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="H51" s="57">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A52" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="B52" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C52" s="53">
+        <v>10172262</v>
+      </c>
+      <c r="D52" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E52" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F52" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="H52" s="57">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A53" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="B53" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53" s="53">
+        <v>10172253</v>
+      </c>
+      <c r="D53" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E53" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F53" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G53" s="3">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="H53" s="57">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A54" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="B54" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C54" s="53" t="s">
+        <v>332</v>
+      </c>
+      <c r="D54" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E54" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F54" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G54" s="3">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="H54" s="57">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A55" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="B55" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C55" s="53" t="s">
+        <v>333</v>
+      </c>
+      <c r="D55" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E55" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F55" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G55" s="3">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="H55" s="57">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A56" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="B56" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C56" s="53">
+        <v>10172138</v>
+      </c>
+      <c r="D56" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E56" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F56" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G56" s="3">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="H56" s="57">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A57" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="B57" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C57" s="53">
+        <v>10172265</v>
+      </c>
+      <c r="D57" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E57" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F57" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="H57" s="57">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A58" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="B58" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C58" s="53" t="s">
+        <v>334</v>
+      </c>
+      <c r="D58" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E58" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F58" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G58" s="3">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="H58" s="57">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A59" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="B59" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C59" s="53">
+        <v>10172249</v>
+      </c>
+      <c r="D59" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E59" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F59" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G59" s="3">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="H59" s="57">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A60" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="B60" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C60" s="53">
+        <v>10172255</v>
+      </c>
+      <c r="D60" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E60" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F60" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G60" s="3">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="H60" s="57">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A61" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="B61" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C61" s="53">
+        <v>10172140</v>
+      </c>
+      <c r="D61" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E61" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F61" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G61" s="3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="H61" s="57">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A62" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="B62" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C62" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="D62" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E62" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F62" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G62" s="3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="H62" s="57">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A63" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="B63" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C63" s="53">
+        <v>10172259</v>
+      </c>
+      <c r="D63" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E63" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F63" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G63" s="3">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="H63" s="57">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A64" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="B64" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C64" s="53">
+        <v>10172254</v>
+      </c>
+      <c r="D64" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E64" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F64" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G64" s="3">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="H64" s="57">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A65" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B65" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C65" s="53">
+        <v>10172264</v>
+      </c>
+      <c r="D65" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E65" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F65" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G65" s="3">
+        <v>0.105</v>
+      </c>
+      <c r="H65" s="57">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A66" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="B66" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C66" s="53" t="s">
+        <v>354</v>
+      </c>
+      <c r="D66" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E66" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F66" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G66" s="3">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="H66" s="57">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A67" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="B67" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C67" s="53" t="s">
+        <v>355</v>
+      </c>
+      <c r="D67" s="53" t="s">
+        <v>356</v>
+      </c>
+      <c r="E67" s="53" t="s">
+        <v>357</v>
+      </c>
+      <c r="F67" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G67" s="3">
+        <v>0.161</v>
+      </c>
+      <c r="H67" s="57">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A68" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="B68" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C68" s="53" t="s">
+        <v>358</v>
+      </c>
+      <c r="D68" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E68" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F68" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G68" s="3">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="H68" s="57">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A69" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="B69" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C69" s="53" t="s">
+        <v>359</v>
+      </c>
+      <c r="D69" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E69" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F69" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G69" s="3">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="H69" s="57">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A70" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="B70" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C70" s="53" t="s">
+        <v>360</v>
+      </c>
+      <c r="D70" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E70" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F70" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="H70" s="57">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A71" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="B71" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C71" s="53" t="s">
+        <v>361</v>
+      </c>
+      <c r="D71" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E71" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F71" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G71" s="3">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="H71" s="57">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A72" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B72" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C72" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="D72" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E72" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F72" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G72" s="3">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="H72" s="57">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A73" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B73" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C73" s="53" t="s">
+        <v>363</v>
+      </c>
+      <c r="D73" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E73" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F73" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G73" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="H73" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A74" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B74" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C74" s="53" t="s">
+        <v>364</v>
+      </c>
+      <c r="D74" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E74" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F74" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G74" s="3">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="H74" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A75" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B75" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C75" s="53" t="s">
+        <v>365</v>
+      </c>
+      <c r="D75" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E75" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F75" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G75" s="3">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="H75" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A76" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B76" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C76" s="53" t="s">
+        <v>366</v>
+      </c>
+      <c r="D76" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E76" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F76" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G76" s="3">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="H76" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A77" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B77" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C77" s="53" t="s">
+        <v>367</v>
+      </c>
+      <c r="D77" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E77" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F77" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G77" s="3">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="H77" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A78" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B78" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C78" s="53" t="s">
+        <v>368</v>
+      </c>
+      <c r="D78" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E78" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F78" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G78" s="3">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="H78" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A79" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="B79" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C79" s="53" t="s">
+        <v>369</v>
+      </c>
+      <c r="D79" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E79" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F79" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G79" s="3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="H79" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A80" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B80" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C80" s="53" t="s">
+        <v>370</v>
+      </c>
+      <c r="D80" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E80" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="F80" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="G80" s="3">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="H80" s="57">
+        <v>46186</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:A80">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C30">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3005" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7467957-B839-4D09-90B9-38C40F023491}"/>
+  <xr:revisionPtr revIDLastSave="3032" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F874E045-42FB-441D-999D-153DF8B6F201}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-8550" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="-8550" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FS Elec" sheetId="4" r:id="rId1"/>
@@ -4339,7 +4339,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="37" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4822,15 +4822,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4842,6 +4833,12 @@
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5126,10 +5123,6 @@
     </a>
   </bag>
 </FeaturePropertyBags>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5487,10 +5480,10 @@
       <c r="R1" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="162" t="s">
+      <c r="S1" s="22" t="s">
         <v>1204</v>
       </c>
-      <c r="T1" s="162" t="s">
+      <c r="T1" s="22" t="s">
         <v>1205</v>
       </c>
     </row>
@@ -5531,7 +5524,9 @@
       <c r="L2" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M2" s="2"/>
+      <c r="M2" s="2">
+        <v>1</v>
+      </c>
       <c r="N2" s="64" t="s">
         <v>118</v>
       </c>
@@ -5547,8 +5542,8 @@
       <c r="R2" s="65">
         <v>46301</v>
       </c>
-      <c r="S2" s="163"/>
-      <c r="T2" s="163"/>
+      <c r="S2" s="160"/>
+      <c r="T2" s="160"/>
     </row>
     <row r="3" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -5587,7 +5582,9 @@
       <c r="L3" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M3" s="2"/>
+      <c r="M3" s="2">
+        <v>2</v>
+      </c>
       <c r="N3" s="64" t="s">
         <v>118</v>
       </c>
@@ -5603,8 +5600,8 @@
       <c r="R3" s="65">
         <v>46301</v>
       </c>
-      <c r="S3" s="163"/>
-      <c r="T3" s="163"/>
+      <c r="S3" s="160"/>
+      <c r="T3" s="160"/>
     </row>
     <row r="4" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
@@ -5643,7 +5640,9 @@
       <c r="L4" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M4" s="2"/>
+      <c r="M4" s="2">
+        <v>6</v>
+      </c>
       <c r="N4" s="64" t="s">
         <v>121</v>
       </c>
@@ -5659,8 +5658,8 @@
       <c r="R4" s="65">
         <v>46240</v>
       </c>
-      <c r="S4" s="163"/>
-      <c r="T4" s="163"/>
+      <c r="S4" s="160"/>
+      <c r="T4" s="160"/>
     </row>
     <row r="5" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
@@ -5699,7 +5698,9 @@
       <c r="L5" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M5" s="2"/>
+      <c r="M5" s="2">
+        <v>3</v>
+      </c>
       <c r="N5" s="64" t="s">
         <v>118</v>
       </c>
@@ -5715,8 +5716,8 @@
       <c r="R5" s="65">
         <v>46301</v>
       </c>
-      <c r="S5" s="163"/>
-      <c r="T5" s="163"/>
+      <c r="S5" s="160"/>
+      <c r="T5" s="160"/>
     </row>
     <row r="6" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
@@ -5755,7 +5756,9 @@
       <c r="L6" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M6" s="2"/>
+      <c r="M6" s="2">
+        <v>7</v>
+      </c>
       <c r="N6" s="64" t="s">
         <v>121</v>
       </c>
@@ -5771,8 +5774,8 @@
       <c r="R6" s="65">
         <v>46240</v>
       </c>
-      <c r="S6" s="163"/>
-      <c r="T6" s="163"/>
+      <c r="S6" s="160"/>
+      <c r="T6" s="160"/>
     </row>
     <row r="7" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
@@ -5811,7 +5814,9 @@
       <c r="L7" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M7" s="2"/>
+      <c r="M7" s="2">
+        <v>4</v>
+      </c>
       <c r="N7" s="64" t="s">
         <v>118</v>
       </c>
@@ -5827,8 +5832,8 @@
       <c r="R7" s="65">
         <v>46301</v>
       </c>
-      <c r="S7" s="163"/>
-      <c r="T7" s="163"/>
+      <c r="S7" s="160"/>
+      <c r="T7" s="160"/>
     </row>
     <row r="8" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
@@ -5867,7 +5872,9 @@
       <c r="L8" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M8" s="2"/>
+      <c r="M8" s="2">
+        <v>5</v>
+      </c>
       <c r="N8" s="64" t="s">
         <v>121</v>
       </c>
@@ -5883,8 +5890,8 @@
       <c r="R8" s="65">
         <v>46240</v>
       </c>
-      <c r="S8" s="163"/>
-      <c r="T8" s="163"/>
+      <c r="S8" s="160"/>
+      <c r="T8" s="160"/>
     </row>
     <row r="9" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
@@ -5923,7 +5930,9 @@
       <c r="L9" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M9" s="2"/>
+      <c r="M9" s="2">
+        <v>9</v>
+      </c>
       <c r="N9" s="64" t="s">
         <v>118</v>
       </c>
@@ -5939,8 +5948,8 @@
       <c r="R9" s="65">
         <v>46301</v>
       </c>
-      <c r="S9" s="163"/>
-      <c r="T9" s="163"/>
+      <c r="S9" s="160"/>
+      <c r="T9" s="160"/>
     </row>
     <row r="10" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
@@ -5979,7 +5988,9 @@
       <c r="L10" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M10" s="2"/>
+      <c r="M10" s="2">
+        <v>8</v>
+      </c>
       <c r="N10" s="64" t="s">
         <v>121</v>
       </c>
@@ -5995,8 +6006,8 @@
       <c r="R10" s="65">
         <v>46240</v>
       </c>
-      <c r="S10" s="163"/>
-      <c r="T10" s="163"/>
+      <c r="S10" s="160"/>
+      <c r="T10" s="160"/>
     </row>
     <row r="11" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
@@ -6035,7 +6046,9 @@
       <c r="L11" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M11" s="2"/>
+      <c r="M11" s="2">
+        <v>3</v>
+      </c>
       <c r="N11" s="64" t="s">
         <v>118</v>
       </c>
@@ -6051,8 +6064,8 @@
       <c r="R11" s="65">
         <v>46301</v>
       </c>
-      <c r="S11" s="163"/>
-      <c r="T11" s="163"/>
+      <c r="S11" s="160"/>
+      <c r="T11" s="160"/>
     </row>
     <row r="12" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
@@ -6091,7 +6104,9 @@
       <c r="L12" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M12" s="2"/>
+      <c r="M12" s="2">
+        <v>5</v>
+      </c>
       <c r="N12" s="64" t="s">
         <v>121</v>
       </c>
@@ -6107,8 +6122,8 @@
       <c r="R12" s="65">
         <v>46240</v>
       </c>
-      <c r="S12" s="163"/>
-      <c r="T12" s="163"/>
+      <c r="S12" s="160"/>
+      <c r="T12" s="160"/>
     </row>
     <row r="13" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
@@ -6147,7 +6162,9 @@
       <c r="L13" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M13" s="2"/>
+      <c r="M13" s="2">
+        <v>2</v>
+      </c>
       <c r="N13" s="64" t="s">
         <v>118</v>
       </c>
@@ -6163,8 +6180,8 @@
       <c r="R13" s="65">
         <v>46301</v>
       </c>
-      <c r="S13" s="163"/>
-      <c r="T13" s="163"/>
+      <c r="S13" s="160"/>
+      <c r="T13" s="160"/>
     </row>
     <row r="14" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
@@ -6203,7 +6220,9 @@
       <c r="L14" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M14" s="2"/>
+      <c r="M14" s="2">
+        <v>9</v>
+      </c>
       <c r="N14" s="64" t="s">
         <v>121</v>
       </c>
@@ -6219,8 +6238,8 @@
       <c r="R14" s="65">
         <v>46240</v>
       </c>
-      <c r="S14" s="163"/>
-      <c r="T14" s="163"/>
+      <c r="S14" s="160"/>
+      <c r="T14" s="160"/>
     </row>
     <row r="15" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
@@ -6259,7 +6278,9 @@
       <c r="L15" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M15" s="2"/>
+      <c r="M15" s="2">
+        <v>1</v>
+      </c>
       <c r="N15" s="64" t="s">
         <v>118</v>
       </c>
@@ -6275,8 +6296,8 @@
       <c r="R15" s="65">
         <v>46301</v>
       </c>
-      <c r="S15" s="163"/>
-      <c r="T15" s="163"/>
+      <c r="S15" s="160"/>
+      <c r="T15" s="160"/>
     </row>
     <row r="16" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
@@ -6315,7 +6336,9 @@
       <c r="L16" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M16" s="2"/>
+      <c r="M16" s="2">
+        <v>8</v>
+      </c>
       <c r="N16" s="64" t="s">
         <v>121</v>
       </c>
@@ -6331,8 +6354,8 @@
       <c r="R16" s="65">
         <v>46240</v>
       </c>
-      <c r="S16" s="163"/>
-      <c r="T16" s="163"/>
+      <c r="S16" s="160"/>
+      <c r="T16" s="160"/>
     </row>
     <row r="17" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
@@ -6371,7 +6394,9 @@
       <c r="L17" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M17" s="2"/>
+      <c r="M17" s="2">
+        <v>6</v>
+      </c>
       <c r="N17" s="64" t="s">
         <v>118</v>
       </c>
@@ -6387,8 +6412,8 @@
       <c r="R17" s="65">
         <v>46301</v>
       </c>
-      <c r="S17" s="163"/>
-      <c r="T17" s="163"/>
+      <c r="S17" s="160"/>
+      <c r="T17" s="160"/>
     </row>
     <row r="18" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
@@ -6427,7 +6452,9 @@
       <c r="L18" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M18" s="2"/>
+      <c r="M18" s="2">
+        <v>7</v>
+      </c>
       <c r="N18" s="64" t="s">
         <v>159</v>
       </c>
@@ -6443,8 +6470,8 @@
       <c r="R18" s="65">
         <v>46224</v>
       </c>
-      <c r="S18" s="163"/>
-      <c r="T18" s="163"/>
+      <c r="S18" s="160"/>
+      <c r="T18" s="160"/>
     </row>
     <row r="19" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
@@ -6483,7 +6510,9 @@
       <c r="L19" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M19" s="2"/>
+      <c r="M19" s="2">
+        <v>4</v>
+      </c>
       <c r="N19" s="64" t="s">
         <v>118</v>
       </c>
@@ -6499,8 +6528,8 @@
       <c r="R19" s="65">
         <v>46301</v>
       </c>
-      <c r="S19" s="163"/>
-      <c r="T19" s="163"/>
+      <c r="S19" s="160"/>
+      <c r="T19" s="160"/>
     </row>
     <row r="20" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
@@ -6557,8 +6586,8 @@
       <c r="R20" s="65">
         <v>46224</v>
       </c>
-      <c r="S20" s="163"/>
-      <c r="T20" s="163"/>
+      <c r="S20" s="160"/>
+      <c r="T20" s="160"/>
     </row>
     <row r="21" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
@@ -6615,8 +6644,8 @@
       <c r="R21" s="65">
         <v>46286</v>
       </c>
-      <c r="S21" s="163"/>
-      <c r="T21" s="163"/>
+      <c r="S21" s="160"/>
+      <c r="T21" s="160"/>
     </row>
     <row r="22" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
@@ -6673,8 +6702,8 @@
       <c r="R22" s="65">
         <v>46224</v>
       </c>
-      <c r="S22" s="163"/>
-      <c r="T22" s="163"/>
+      <c r="S22" s="160"/>
+      <c r="T22" s="160"/>
     </row>
     <row r="23" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
@@ -6731,8 +6760,8 @@
       <c r="R23" s="65">
         <v>46286</v>
       </c>
-      <c r="S23" s="163"/>
-      <c r="T23" s="163"/>
+      <c r="S23" s="160"/>
+      <c r="T23" s="160"/>
     </row>
     <row r="24" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
@@ -6789,8 +6818,8 @@
       <c r="R24" s="65">
         <v>46224</v>
       </c>
-      <c r="S24" s="163"/>
-      <c r="T24" s="163"/>
+      <c r="S24" s="160"/>
+      <c r="T24" s="160"/>
     </row>
     <row r="25" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
@@ -6847,8 +6876,8 @@
       <c r="R25" s="65">
         <v>46286</v>
       </c>
-      <c r="S25" s="163"/>
-      <c r="T25" s="163"/>
+      <c r="S25" s="160"/>
+      <c r="T25" s="160"/>
     </row>
     <row r="26" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
@@ -6887,7 +6916,9 @@
       <c r="L26" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M26" s="2"/>
+      <c r="M26" s="2">
+        <v>5</v>
+      </c>
       <c r="N26" s="64" t="s">
         <v>159</v>
       </c>
@@ -6903,8 +6934,8 @@
       <c r="R26" s="65">
         <v>46224</v>
       </c>
-      <c r="S26" s="163"/>
-      <c r="T26" s="163"/>
+      <c r="S26" s="160"/>
+      <c r="T26" s="160"/>
     </row>
     <row r="27" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
@@ -6943,7 +6974,9 @@
       <c r="L27" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M27" s="2"/>
+      <c r="M27" s="2">
+        <v>7</v>
+      </c>
       <c r="N27" s="64" t="s">
         <v>184</v>
       </c>
@@ -6959,8 +6992,8 @@
       <c r="R27" s="65">
         <v>46286</v>
       </c>
-      <c r="S27" s="163"/>
-      <c r="T27" s="163"/>
+      <c r="S27" s="160"/>
+      <c r="T27" s="160"/>
     </row>
     <row r="28" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
@@ -6999,7 +7032,9 @@
       <c r="L28" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M28" s="2"/>
+      <c r="M28" s="2">
+        <v>9</v>
+      </c>
       <c r="N28" s="64" t="s">
         <v>159</v>
       </c>
@@ -7015,8 +7050,8 @@
       <c r="R28" s="65">
         <v>46224</v>
       </c>
-      <c r="S28" s="163"/>
-      <c r="T28" s="163"/>
+      <c r="S28" s="160"/>
+      <c r="T28" s="160"/>
     </row>
     <row r="29" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
@@ -7055,7 +7090,9 @@
       <c r="L29" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M29" s="2"/>
+      <c r="M29" s="2">
+        <v>3</v>
+      </c>
       <c r="N29" s="64" t="s">
         <v>184</v>
       </c>
@@ -7071,8 +7108,8 @@
       <c r="R29" s="65">
         <v>46286</v>
       </c>
-      <c r="S29" s="163"/>
-      <c r="T29" s="163"/>
+      <c r="S29" s="160"/>
+      <c r="T29" s="160"/>
     </row>
     <row r="30" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
@@ -7111,7 +7148,9 @@
       <c r="L30" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M30" s="2"/>
+      <c r="M30" s="2">
+        <v>1</v>
+      </c>
       <c r="N30" s="64" t="s">
         <v>159</v>
       </c>
@@ -7127,8 +7166,8 @@
       <c r="R30" s="65">
         <v>46224</v>
       </c>
-      <c r="S30" s="163"/>
-      <c r="T30" s="163"/>
+      <c r="S30" s="160"/>
+      <c r="T30" s="160"/>
     </row>
     <row r="31" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
@@ -7167,7 +7206,9 @@
       <c r="L31" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M31" s="2"/>
+      <c r="M31" s="2">
+        <v>2</v>
+      </c>
       <c r="N31" s="64" t="s">
         <v>184</v>
       </c>
@@ -7183,8 +7224,8 @@
       <c r="R31" s="65">
         <v>46286</v>
       </c>
-      <c r="S31" s="163"/>
-      <c r="T31" s="163"/>
+      <c r="S31" s="160"/>
+      <c r="T31" s="160"/>
     </row>
     <row r="32" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
@@ -7223,7 +7264,9 @@
       <c r="L32" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M32" s="2"/>
+      <c r="M32" s="2">
+        <v>8</v>
+      </c>
       <c r="N32" s="64" t="s">
         <v>159</v>
       </c>
@@ -7239,8 +7282,8 @@
       <c r="R32" s="65">
         <v>46224</v>
       </c>
-      <c r="S32" s="163"/>
-      <c r="T32" s="163"/>
+      <c r="S32" s="160"/>
+      <c r="T32" s="160"/>
     </row>
     <row r="33" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
@@ -7279,7 +7322,9 @@
       <c r="L33" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M33" s="2"/>
+      <c r="M33" s="2">
+        <v>4</v>
+      </c>
       <c r="N33" s="64" t="s">
         <v>184</v>
       </c>
@@ -7295,8 +7340,8 @@
       <c r="R33" s="65">
         <v>46286</v>
       </c>
-      <c r="S33" s="163"/>
-      <c r="T33" s="163"/>
+      <c r="S33" s="160"/>
+      <c r="T33" s="160"/>
     </row>
     <row r="34" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
@@ -7335,7 +7380,9 @@
       <c r="L34" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M34" s="2"/>
+      <c r="M34" s="2">
+        <v>6</v>
+      </c>
       <c r="N34" s="64" t="s">
         <v>184</v>
       </c>
@@ -7351,8 +7398,8 @@
       <c r="R34" s="65">
         <v>46286</v>
       </c>
-      <c r="S34" s="163"/>
-      <c r="T34" s="163"/>
+      <c r="S34" s="160"/>
+      <c r="T34" s="160"/>
     </row>
     <row r="35" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
@@ -7407,8 +7454,8 @@
       <c r="R35" s="65">
         <v>46221</v>
       </c>
-      <c r="S35" s="163"/>
-      <c r="T35" s="163"/>
+      <c r="S35" s="160"/>
+      <c r="T35" s="160"/>
     </row>
     <row r="36" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
@@ -7463,8 +7510,8 @@
       <c r="R36" s="65">
         <v>46207</v>
       </c>
-      <c r="S36" s="163"/>
-      <c r="T36" s="163"/>
+      <c r="S36" s="160"/>
+      <c r="T36" s="160"/>
     </row>
     <row r="37" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
@@ -7519,8 +7566,8 @@
       <c r="R37" s="65">
         <v>46221</v>
       </c>
-      <c r="S37" s="163"/>
-      <c r="T37" s="163"/>
+      <c r="S37" s="160"/>
+      <c r="T37" s="160"/>
     </row>
     <row r="38" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
@@ -7575,8 +7622,8 @@
       <c r="R38" s="65">
         <v>46207</v>
       </c>
-      <c r="S38" s="163"/>
-      <c r="T38" s="163"/>
+      <c r="S38" s="160"/>
+      <c r="T38" s="160"/>
     </row>
     <row r="39" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
@@ -7631,8 +7678,8 @@
       <c r="R39" s="65">
         <v>46221</v>
       </c>
-      <c r="S39" s="163"/>
-      <c r="T39" s="163"/>
+      <c r="S39" s="160"/>
+      <c r="T39" s="160"/>
     </row>
     <row r="40" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
@@ -7687,8 +7734,8 @@
       <c r="R40" s="65">
         <v>46207</v>
       </c>
-      <c r="S40" s="163"/>
-      <c r="T40" s="163"/>
+      <c r="S40" s="160"/>
+      <c r="T40" s="160"/>
     </row>
     <row r="41" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
@@ -7743,8 +7790,8 @@
       <c r="R41" s="65">
         <v>46221</v>
       </c>
-      <c r="S41" s="163"/>
-      <c r="T41" s="163"/>
+      <c r="S41" s="160"/>
+      <c r="T41" s="160"/>
     </row>
     <row r="42" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
@@ -7799,8 +7846,8 @@
       <c r="R42" s="65">
         <v>46207</v>
       </c>
-      <c r="S42" s="163"/>
-      <c r="T42" s="163"/>
+      <c r="S42" s="160"/>
+      <c r="T42" s="160"/>
     </row>
     <row r="43" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
@@ -7855,8 +7902,8 @@
       <c r="R43" s="65">
         <v>46221</v>
       </c>
-      <c r="S43" s="163"/>
-      <c r="T43" s="163"/>
+      <c r="S43" s="160"/>
+      <c r="T43" s="160"/>
     </row>
     <row r="44" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
@@ -7911,8 +7958,8 @@
       <c r="R44" s="65">
         <v>46207</v>
       </c>
-      <c r="S44" s="163"/>
-      <c r="T44" s="163"/>
+      <c r="S44" s="160"/>
+      <c r="T44" s="160"/>
     </row>
     <row r="45" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
@@ -7967,8 +8014,8 @@
       <c r="R45" s="65">
         <v>46221</v>
       </c>
-      <c r="S45" s="163"/>
-      <c r="T45" s="163"/>
+      <c r="S45" s="160"/>
+      <c r="T45" s="160"/>
     </row>
     <row r="46" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
@@ -8023,8 +8070,8 @@
       <c r="R46" s="65">
         <v>46195</v>
       </c>
-      <c r="S46" s="163"/>
-      <c r="T46" s="163"/>
+      <c r="S46" s="160"/>
+      <c r="T46" s="160"/>
     </row>
     <row r="47" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
@@ -8079,8 +8126,8 @@
       <c r="R47" s="65">
         <v>46207</v>
       </c>
-      <c r="S47" s="163"/>
-      <c r="T47" s="163"/>
+      <c r="S47" s="160"/>
+      <c r="T47" s="160"/>
     </row>
     <row r="48" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
@@ -8135,8 +8182,8 @@
       <c r="R48" s="65">
         <v>46195</v>
       </c>
-      <c r="S48" s="163"/>
-      <c r="T48" s="163"/>
+      <c r="S48" s="160"/>
+      <c r="T48" s="160"/>
     </row>
     <row r="49" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
@@ -8191,8 +8238,8 @@
       <c r="R49" s="65">
         <v>46207</v>
       </c>
-      <c r="S49" s="163"/>
-      <c r="T49" s="163"/>
+      <c r="S49" s="160"/>
+      <c r="T49" s="160"/>
     </row>
     <row r="50" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
@@ -8247,8 +8294,8 @@
       <c r="R50" s="65">
         <v>46195</v>
       </c>
-      <c r="S50" s="163"/>
-      <c r="T50" s="163"/>
+      <c r="S50" s="160"/>
+      <c r="T50" s="160"/>
     </row>
     <row r="51" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
@@ -8303,8 +8350,8 @@
       <c r="R51" s="65">
         <v>46207</v>
       </c>
-      <c r="S51" s="163"/>
-      <c r="T51" s="163"/>
+      <c r="S51" s="160"/>
+      <c r="T51" s="160"/>
     </row>
     <row r="52" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
@@ -8359,8 +8406,8 @@
       <c r="R52" s="65">
         <v>46195</v>
       </c>
-      <c r="S52" s="163"/>
-      <c r="T52" s="163"/>
+      <c r="S52" s="160"/>
+      <c r="T52" s="160"/>
     </row>
     <row r="53" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
@@ -8415,8 +8462,8 @@
       <c r="R53" s="65">
         <v>46207</v>
       </c>
-      <c r="S53" s="163"/>
-      <c r="T53" s="163"/>
+      <c r="S53" s="160"/>
+      <c r="T53" s="160"/>
     </row>
     <row r="54" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
@@ -8471,8 +8518,8 @@
       <c r="R54" s="65">
         <v>46195</v>
       </c>
-      <c r="S54" s="163"/>
-      <c r="T54" s="163"/>
+      <c r="S54" s="160"/>
+      <c r="T54" s="160"/>
     </row>
     <row r="55" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
@@ -8527,8 +8574,8 @@
       <c r="R55" s="65">
         <v>46207</v>
       </c>
-      <c r="S55" s="163"/>
-      <c r="T55" s="163"/>
+      <c r="S55" s="160"/>
+      <c r="T55" s="160"/>
     </row>
     <row r="56" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
@@ -8583,8 +8630,8 @@
       <c r="R56" s="65">
         <v>46195</v>
       </c>
-      <c r="S56" s="163"/>
-      <c r="T56" s="163"/>
+      <c r="S56" s="160"/>
+      <c r="T56" s="160"/>
     </row>
     <row r="57" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
@@ -8639,8 +8686,8 @@
       <c r="R57" s="65">
         <v>46207</v>
       </c>
-      <c r="S57" s="163"/>
-      <c r="T57" s="163"/>
+      <c r="S57" s="160"/>
+      <c r="T57" s="160"/>
     </row>
     <row r="58" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
@@ -8695,8 +8742,8 @@
       <c r="R58" s="65">
         <v>46195</v>
       </c>
-      <c r="S58" s="163"/>
-      <c r="T58" s="163"/>
+      <c r="S58" s="160"/>
+      <c r="T58" s="160"/>
     </row>
     <row r="59" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
@@ -8751,8 +8798,8 @@
       <c r="R59" s="65">
         <v>46207</v>
       </c>
-      <c r="S59" s="163"/>
-      <c r="T59" s="163"/>
+      <c r="S59" s="160"/>
+      <c r="T59" s="160"/>
     </row>
     <row r="60" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
@@ -8807,8 +8854,8 @@
       <c r="R60" s="65">
         <v>46195</v>
       </c>
-      <c r="S60" s="163"/>
-      <c r="T60" s="163"/>
+      <c r="S60" s="160"/>
+      <c r="T60" s="160"/>
     </row>
     <row r="61" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
@@ -8863,8 +8910,8 @@
       <c r="R61" s="65">
         <v>46207</v>
       </c>
-      <c r="S61" s="163"/>
-      <c r="T61" s="163"/>
+      <c r="S61" s="160"/>
+      <c r="T61" s="160"/>
     </row>
     <row r="62" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
@@ -8919,8 +8966,8 @@
       <c r="R62" s="65">
         <v>46179</v>
       </c>
-      <c r="S62" s="163"/>
-      <c r="T62" s="163"/>
+      <c r="S62" s="160"/>
+      <c r="T62" s="160"/>
     </row>
     <row r="63" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A63" s="12" t="s">
@@ -8975,8 +9022,8 @@
       <c r="R63" s="65">
         <v>46195</v>
       </c>
-      <c r="S63" s="163"/>
-      <c r="T63" s="163"/>
+      <c r="S63" s="160"/>
+      <c r="T63" s="160"/>
     </row>
     <row r="64" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A64" s="12" t="s">
@@ -9031,8 +9078,8 @@
       <c r="R64" s="65">
         <v>46179</v>
       </c>
-      <c r="S64" s="163"/>
-      <c r="T64" s="163"/>
+      <c r="S64" s="160"/>
+      <c r="T64" s="160"/>
     </row>
     <row r="65" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A65" s="12" t="s">
@@ -9087,8 +9134,8 @@
       <c r="R65" s="65">
         <v>46195</v>
       </c>
-      <c r="S65" s="163"/>
-      <c r="T65" s="163"/>
+      <c r="S65" s="160"/>
+      <c r="T65" s="160"/>
     </row>
     <row r="66" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
@@ -9143,8 +9190,8 @@
       <c r="R66" s="65">
         <v>46179</v>
       </c>
-      <c r="S66" s="163"/>
-      <c r="T66" s="163"/>
+      <c r="S66" s="160"/>
+      <c r="T66" s="160"/>
     </row>
     <row r="67" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A67" s="12" t="s">
@@ -9199,8 +9246,8 @@
       <c r="R67" s="65">
         <v>46195</v>
       </c>
-      <c r="S67" s="163"/>
-      <c r="T67" s="163"/>
+      <c r="S67" s="160"/>
+      <c r="T67" s="160"/>
     </row>
     <row r="68" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
@@ -9255,8 +9302,8 @@
       <c r="R68" s="65">
         <v>46179</v>
       </c>
-      <c r="S68" s="163"/>
-      <c r="T68" s="163"/>
+      <c r="S68" s="160"/>
+      <c r="T68" s="160"/>
     </row>
     <row r="69" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A69" s="12" t="s">
@@ -9313,8 +9360,8 @@
       <c r="R69" s="65">
         <v>46195</v>
       </c>
-      <c r="S69" s="163"/>
-      <c r="T69" s="163"/>
+      <c r="S69" s="160"/>
+      <c r="T69" s="160"/>
     </row>
     <row r="70" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
@@ -9371,8 +9418,8 @@
       <c r="R70" s="65">
         <v>46179</v>
       </c>
-      <c r="S70" s="163"/>
-      <c r="T70" s="163"/>
+      <c r="S70" s="160"/>
+      <c r="T70" s="160"/>
     </row>
     <row r="71" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A71" s="12" t="s">
@@ -9429,8 +9476,8 @@
       <c r="R71" s="65">
         <v>46195</v>
       </c>
-      <c r="S71" s="163"/>
-      <c r="T71" s="163"/>
+      <c r="S71" s="160"/>
+      <c r="T71" s="160"/>
     </row>
     <row r="72" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
@@ -9487,8 +9534,8 @@
       <c r="R72" s="65">
         <v>46179</v>
       </c>
-      <c r="S72" s="163"/>
-      <c r="T72" s="163"/>
+      <c r="S72" s="160"/>
+      <c r="T72" s="160"/>
     </row>
     <row r="73" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
@@ -9545,8 +9592,8 @@
       <c r="R73" s="65">
         <v>46195</v>
       </c>
-      <c r="S73" s="163"/>
-      <c r="T73" s="163"/>
+      <c r="S73" s="160"/>
+      <c r="T73" s="160"/>
     </row>
     <row r="74" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
@@ -9603,8 +9650,8 @@
       <c r="R74" s="65">
         <v>46179</v>
       </c>
-      <c r="S74" s="163"/>
-      <c r="T74" s="163"/>
+      <c r="S74" s="160"/>
+      <c r="T74" s="160"/>
     </row>
     <row r="75" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
@@ -9661,8 +9708,8 @@
       <c r="R75" s="65">
         <v>46195</v>
       </c>
-      <c r="S75" s="163"/>
-      <c r="T75" s="163"/>
+      <c r="S75" s="160"/>
+      <c r="T75" s="160"/>
     </row>
     <row r="76" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
@@ -9719,8 +9766,8 @@
       <c r="R76" s="65">
         <v>46179</v>
       </c>
-      <c r="S76" s="163"/>
-      <c r="T76" s="163"/>
+      <c r="S76" s="160"/>
+      <c r="T76" s="160"/>
     </row>
     <row r="77" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
@@ -9777,10 +9824,10 @@
       <c r="R77" s="65">
         <v>46217</v>
       </c>
-      <c r="S77" s="166">
+      <c r="S77" s="163">
         <v>46234</v>
       </c>
-      <c r="T77" s="163" t="s">
+      <c r="T77" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -9839,10 +9886,10 @@
       <c r="R78" s="65">
         <v>46217</v>
       </c>
-      <c r="S78" s="166">
+      <c r="S78" s="163">
         <v>46234</v>
       </c>
-      <c r="T78" s="163" t="s">
+      <c r="T78" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -9901,10 +9948,10 @@
       <c r="R79" s="65">
         <v>46217</v>
       </c>
-      <c r="S79" s="166">
+      <c r="S79" s="163">
         <v>46234</v>
       </c>
-      <c r="T79" s="163" t="s">
+      <c r="T79" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -9963,10 +10010,10 @@
       <c r="R80" s="65">
         <v>46217</v>
       </c>
-      <c r="S80" s="166">
+      <c r="S80" s="163">
         <v>46234</v>
       </c>
-      <c r="T80" s="163" t="s">
+      <c r="T80" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10023,10 +10070,10 @@
       <c r="R81" s="65">
         <v>46203</v>
       </c>
-      <c r="S81" s="166">
+      <c r="S81" s="163">
         <v>46234</v>
       </c>
-      <c r="T81" s="163" t="s">
+      <c r="T81" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10083,10 +10130,10 @@
       <c r="R82" s="65">
         <v>46203</v>
       </c>
-      <c r="S82" s="166">
+      <c r="S82" s="163">
         <v>46234</v>
       </c>
-      <c r="T82" s="163" t="s">
+      <c r="T82" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10143,10 +10190,10 @@
       <c r="R83" s="65">
         <v>46203</v>
       </c>
-      <c r="S83" s="166">
+      <c r="S83" s="163">
         <v>46234</v>
       </c>
-      <c r="T83" s="163" t="s">
+      <c r="T83" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10203,10 +10250,10 @@
       <c r="R84" s="65">
         <v>46203</v>
       </c>
-      <c r="S84" s="166">
+      <c r="S84" s="163">
         <v>46234</v>
       </c>
-      <c r="T84" s="163" t="s">
+      <c r="T84" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10263,10 +10310,10 @@
       <c r="R85" s="65">
         <v>46203</v>
       </c>
-      <c r="S85" s="166">
+      <c r="S85" s="163">
         <v>46234</v>
       </c>
-      <c r="T85" s="163" t="s">
+      <c r="T85" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10323,10 +10370,10 @@
       <c r="R86" s="65">
         <v>46203</v>
       </c>
-      <c r="S86" s="166">
+      <c r="S86" s="163">
         <v>46234</v>
       </c>
-      <c r="T86" s="163" t="s">
+      <c r="T86" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10383,10 +10430,10 @@
       <c r="R87" s="65">
         <v>46203</v>
       </c>
-      <c r="S87" s="166">
+      <c r="S87" s="163">
         <v>46234</v>
       </c>
-      <c r="T87" s="163" t="s">
+      <c r="T87" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10443,10 +10490,10 @@
       <c r="R88" s="65">
         <v>46182</v>
       </c>
-      <c r="S88" s="166">
+      <c r="S88" s="163">
         <v>46234</v>
       </c>
-      <c r="T88" s="163" t="s">
+      <c r="T88" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10503,10 +10550,10 @@
       <c r="R89" s="65">
         <v>46182</v>
       </c>
-      <c r="S89" s="166">
+      <c r="S89" s="163">
         <v>46234</v>
       </c>
-      <c r="T89" s="163" t="s">
+      <c r="T89" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10565,10 +10612,10 @@
       <c r="R90" s="65">
         <v>46182</v>
       </c>
-      <c r="S90" s="166">
+      <c r="S90" s="163">
         <v>46234</v>
       </c>
-      <c r="T90" s="163" t="s">
+      <c r="T90" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10627,10 +10674,10 @@
       <c r="R91" s="65">
         <v>46182</v>
       </c>
-      <c r="S91" s="166">
+      <c r="S91" s="163">
         <v>46234</v>
       </c>
-      <c r="T91" s="163" t="s">
+      <c r="T91" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10689,10 +10736,10 @@
       <c r="R92" s="65">
         <v>46182</v>
       </c>
-      <c r="S92" s="166">
+      <c r="S92" s="163">
         <v>46234</v>
       </c>
-      <c r="T92" s="163" t="s">
+      <c r="T92" s="160" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10751,10 +10798,10 @@
       <c r="R93" s="65">
         <v>46168</v>
       </c>
-      <c r="S93" s="166">
+      <c r="S93" s="163">
         <v>46204.919444444444</v>
       </c>
-      <c r="T93" s="163">
+      <c r="T93" s="160">
         <v>76.2</v>
       </c>
     </row>
@@ -10813,10 +10860,10 @@
       <c r="R94" s="65">
         <v>46163</v>
       </c>
-      <c r="S94" s="164">
+      <c r="S94" s="161">
         <v>46204.657638888886</v>
       </c>
-      <c r="T94" s="165">
+      <c r="T94" s="162">
         <v>31.8</v>
       </c>
     </row>
@@ -10875,10 +10922,10 @@
       <c r="R95" s="65">
         <v>46168</v>
       </c>
-      <c r="S95" s="166">
+      <c r="S95" s="163">
         <v>46204.919444444444</v>
       </c>
-      <c r="T95" s="163">
+      <c r="T95" s="160">
         <v>100.4</v>
       </c>
     </row>
@@ -10937,10 +10984,10 @@
       <c r="R96" s="65">
         <v>46163</v>
       </c>
-      <c r="S96" s="164">
+      <c r="S96" s="161">
         <v>46204.919444444444</v>
       </c>
-      <c r="T96" s="165">
+      <c r="T96" s="162">
         <v>73</v>
       </c>
     </row>
@@ -10999,10 +11046,10 @@
       <c r="R97" s="65">
         <v>46168</v>
       </c>
-      <c r="S97" s="166">
+      <c r="S97" s="163">
         <v>46204.919444444444</v>
       </c>
-      <c r="T97" s="163">
+      <c r="T97" s="160">
         <v>55.5</v>
       </c>
     </row>
@@ -11061,10 +11108,10 @@
       <c r="R98" s="65">
         <v>46163</v>
       </c>
-      <c r="S98" s="164">
+      <c r="S98" s="161">
         <v>46204.65625</v>
       </c>
-      <c r="T98" s="165">
+      <c r="T98" s="162">
         <v>47.1</v>
       </c>
     </row>
@@ -11123,10 +11170,10 @@
       <c r="R99" s="65">
         <v>46168</v>
       </c>
-      <c r="S99" s="166">
+      <c r="S99" s="163">
         <v>46204.918749999997</v>
       </c>
-      <c r="T99" s="163">
+      <c r="T99" s="160">
         <v>38.9</v>
       </c>
     </row>
@@ -11185,10 +11232,10 @@
       <c r="R100" s="65">
         <v>46163</v>
       </c>
-      <c r="S100" s="164">
+      <c r="S100" s="161">
         <v>46204.875</v>
       </c>
-      <c r="T100" s="165">
+      <c r="T100" s="162">
         <v>53.9</v>
       </c>
     </row>
@@ -11247,10 +11294,10 @@
       <c r="R101" s="65">
         <v>46168</v>
       </c>
-      <c r="S101" s="166">
+      <c r="S101" s="163">
         <v>46204.657638888886</v>
       </c>
-      <c r="T101" s="163">
+      <c r="T101" s="160">
         <v>61.851999999999997</v>
       </c>
     </row>
@@ -11309,10 +11356,10 @@
       <c r="R102" s="65">
         <v>46163</v>
       </c>
-      <c r="S102" s="164">
+      <c r="S102" s="161">
         <v>46204.65625</v>
       </c>
-      <c r="T102" s="165">
+      <c r="T102" s="162">
         <v>47.4</v>
       </c>
     </row>
@@ -11371,10 +11418,10 @@
       <c r="R103" s="65">
         <v>46168</v>
       </c>
-      <c r="S103" s="166">
+      <c r="S103" s="163">
         <v>46204.918749999997</v>
       </c>
-      <c r="T103" s="163">
+      <c r="T103" s="160">
         <v>43.3</v>
       </c>
     </row>
@@ -11433,10 +11480,10 @@
       <c r="R104" s="65">
         <v>46163</v>
       </c>
-      <c r="S104" s="164">
+      <c r="S104" s="161">
         <v>46204.65625</v>
       </c>
-      <c r="T104" s="165">
+      <c r="T104" s="162">
         <v>47.1</v>
       </c>
     </row>
@@ -11495,8 +11542,8 @@
       <c r="R105" s="65">
         <v>46240</v>
       </c>
-      <c r="S105" s="163"/>
-      <c r="T105" s="163"/>
+      <c r="S105" s="160"/>
+      <c r="T105" s="160"/>
     </row>
     <row r="106" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A106" s="12" t="s">
@@ -11553,10 +11600,10 @@
       <c r="R106" s="65">
         <v>46163</v>
       </c>
-      <c r="S106" s="164">
+      <c r="S106" s="161">
         <v>46204.65625</v>
       </c>
-      <c r="T106" s="165">
+      <c r="T106" s="162">
         <v>56.3</v>
       </c>
     </row>
@@ -11615,8 +11662,8 @@
       <c r="R107" s="65">
         <v>46240</v>
       </c>
-      <c r="S107" s="163"/>
-      <c r="T107" s="163"/>
+      <c r="S107" s="160"/>
+      <c r="T107" s="160"/>
     </row>
     <row r="108" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A108" s="12" t="s">
@@ -11673,10 +11720,10 @@
       <c r="R108" s="65">
         <v>46163</v>
       </c>
-      <c r="S108" s="164">
+      <c r="S108" s="161">
         <v>46204.70416666667</v>
       </c>
-      <c r="T108" s="165">
+      <c r="T108" s="162">
         <v>102.95</v>
       </c>
     </row>
@@ -11735,8 +11782,8 @@
       <c r="R109" s="65">
         <v>46240</v>
       </c>
-      <c r="S109" s="163"/>
-      <c r="T109" s="163"/>
+      <c r="S109" s="160"/>
+      <c r="T109" s="160"/>
     </row>
     <row r="110" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A110" s="12" t="s">
@@ -11793,10 +11840,10 @@
       <c r="R110" s="65">
         <v>46163</v>
       </c>
-      <c r="S110" s="164">
+      <c r="S110" s="161">
         <v>46204.657638888886</v>
       </c>
-      <c r="T110" s="165">
+      <c r="T110" s="162">
         <v>70.277000000000001</v>
       </c>
     </row>
@@ -11855,8 +11902,8 @@
       <c r="R111" s="65">
         <v>46240</v>
       </c>
-      <c r="S111" s="163"/>
-      <c r="T111" s="163"/>
+      <c r="S111" s="160"/>
+      <c r="T111" s="160"/>
     </row>
     <row r="112" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A112" s="12" t="s">
@@ -11913,10 +11960,10 @@
       <c r="R112" s="65">
         <v>46163</v>
       </c>
-      <c r="S112" s="164">
+      <c r="S112" s="161">
         <v>46204.413194444445</v>
       </c>
-      <c r="T112" s="165">
+      <c r="T112" s="162">
         <v>77.23</v>
       </c>
     </row>
@@ -11975,8 +12022,8 @@
       <c r="R113" s="65">
         <v>46240</v>
       </c>
-      <c r="S113" s="163"/>
-      <c r="T113" s="163"/>
+      <c r="S113" s="160"/>
+      <c r="T113" s="160"/>
     </row>
     <row r="114" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A114" s="12" t="s">
@@ -12033,10 +12080,10 @@
       <c r="R114" s="65">
         <v>46154</v>
       </c>
-      <c r="S114" s="164">
+      <c r="S114" s="161">
         <v>46204.426388888889</v>
       </c>
-      <c r="T114" s="165">
+      <c r="T114" s="162">
         <v>25.35</v>
       </c>
     </row>
@@ -12095,8 +12142,8 @@
       <c r="R115" s="65">
         <v>46240</v>
       </c>
-      <c r="S115" s="163"/>
-      <c r="T115" s="163"/>
+      <c r="S115" s="160"/>
+      <c r="T115" s="160"/>
     </row>
     <row r="116" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A116" s="12" t="s">
@@ -12153,10 +12200,10 @@
       <c r="R116" s="65">
         <v>46154</v>
       </c>
-      <c r="S116" s="164">
+      <c r="S116" s="161">
         <v>46204.657638888886</v>
       </c>
-      <c r="T116" s="165">
+      <c r="T116" s="162">
         <v>45.284999999999997</v>
       </c>
     </row>
@@ -12215,8 +12262,8 @@
       <c r="R117" s="65">
         <v>46240</v>
       </c>
-      <c r="S117" s="163"/>
-      <c r="T117" s="163"/>
+      <c r="S117" s="160"/>
+      <c r="T117" s="160"/>
     </row>
     <row r="118" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A118" s="12" t="s">
@@ -12273,10 +12320,10 @@
       <c r="R118" s="65">
         <v>46154</v>
       </c>
-      <c r="S118" s="164">
+      <c r="S118" s="161">
         <v>46204.425000000003</v>
       </c>
-      <c r="T118" s="165">
+      <c r="T118" s="162">
         <v>19.7</v>
       </c>
     </row>
@@ -12335,8 +12382,8 @@
       <c r="R119" s="65">
         <v>46240</v>
       </c>
-      <c r="S119" s="163"/>
-      <c r="T119" s="163"/>
+      <c r="S119" s="160"/>
+      <c r="T119" s="160"/>
     </row>
     <row r="120" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A120" s="12" t="s">
@@ -12393,10 +12440,10 @@
       <c r="R120" s="65">
         <v>46154</v>
       </c>
-      <c r="S120" s="164">
+      <c r="S120" s="161">
         <v>46204.704861111109</v>
       </c>
-      <c r="T120" s="165">
+      <c r="T120" s="162">
         <v>39.33</v>
       </c>
     </row>
@@ -12455,8 +12502,8 @@
       <c r="R121" s="65">
         <v>46255</v>
       </c>
-      <c r="S121" s="163"/>
-      <c r="T121" s="163"/>
+      <c r="S121" s="160"/>
+      <c r="T121" s="160"/>
     </row>
     <row r="122" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A122" s="12" t="s">
@@ -12513,10 +12560,10 @@
       <c r="R122" s="65">
         <v>46154</v>
       </c>
-      <c r="S122" s="164">
+      <c r="S122" s="161">
         <v>46204.424305555556</v>
       </c>
-      <c r="T122" s="165">
+      <c r="T122" s="162">
         <v>35.67</v>
       </c>
     </row>
@@ -12575,8 +12622,8 @@
       <c r="R123" s="65">
         <v>46255</v>
       </c>
-      <c r="S123" s="163"/>
-      <c r="T123" s="163"/>
+      <c r="S123" s="160"/>
+      <c r="T123" s="160"/>
     </row>
     <row r="124" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A124" s="12" t="s">
@@ -12633,10 +12680,10 @@
       <c r="R124" s="65">
         <v>46154</v>
       </c>
-      <c r="S124" s="164">
+      <c r="S124" s="161">
         <v>46204.657638888886</v>
       </c>
-      <c r="T124" s="165">
+      <c r="T124" s="162">
         <v>37.427999999999997</v>
       </c>
     </row>
@@ -12695,8 +12742,8 @@
       <c r="R125" s="65">
         <v>46255</v>
       </c>
-      <c r="S125" s="163"/>
-      <c r="T125" s="163"/>
+      <c r="S125" s="160"/>
+      <c r="T125" s="160"/>
     </row>
     <row r="126" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A126" s="12" t="s">
@@ -12753,10 +12800,10 @@
       <c r="R126" s="65">
         <v>46154</v>
       </c>
-      <c r="S126" s="164">
+      <c r="S126" s="161">
         <v>46204.652083333334</v>
       </c>
-      <c r="T126" s="165">
+      <c r="T126" s="162">
         <v>36.700000000000003</v>
       </c>
     </row>
@@ -12815,8 +12862,8 @@
       <c r="R127" s="65">
         <v>46255</v>
       </c>
-      <c r="S127" s="163"/>
-      <c r="T127" s="163"/>
+      <c r="S127" s="160"/>
+      <c r="T127" s="160"/>
     </row>
     <row r="128" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A128" s="12" t="s">
@@ -12873,10 +12920,10 @@
       <c r="R128" s="65">
         <v>46154</v>
       </c>
-      <c r="S128" s="164">
+      <c r="S128" s="161">
         <v>46204.714583333334</v>
       </c>
-      <c r="T128" s="165">
+      <c r="T128" s="162">
         <v>11.590999999999999</v>
       </c>
     </row>
@@ -12935,8 +12982,8 @@
       <c r="R129" s="65">
         <v>46255</v>
       </c>
-      <c r="S129" s="163"/>
-      <c r="T129" s="163"/>
+      <c r="S129" s="160"/>
+      <c r="T129" s="160"/>
     </row>
     <row r="130" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A130" s="12" t="s">
@@ -12993,8 +13040,8 @@
       <c r="R130" s="65">
         <v>46255</v>
       </c>
-      <c r="S130" s="163"/>
-      <c r="T130" s="163"/>
+      <c r="S130" s="160"/>
+      <c r="T130" s="160"/>
     </row>
     <row r="131" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A131" s="12" t="s">
@@ -13051,8 +13098,8 @@
       <c r="R131" s="65">
         <v>46255</v>
       </c>
-      <c r="S131" s="163"/>
-      <c r="T131" s="163"/>
+      <c r="S131" s="160"/>
+      <c r="T131" s="160"/>
     </row>
     <row r="132" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A132" s="12" t="s">
@@ -13109,8 +13156,8 @@
       <c r="R132" s="65">
         <v>46255</v>
       </c>
-      <c r="S132" s="163"/>
-      <c r="T132" s="163"/>
+      <c r="S132" s="160"/>
+      <c r="T132" s="160"/>
     </row>
     <row r="133" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A133" s="12" t="s">
@@ -13159,8 +13206,8 @@
       <c r="R133" s="65">
         <v>46270</v>
       </c>
-      <c r="S133" s="163"/>
-      <c r="T133" s="163"/>
+      <c r="S133" s="160"/>
+      <c r="T133" s="160"/>
     </row>
     <row r="134" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A134" s="12" t="s">
@@ -13209,8 +13256,8 @@
       <c r="R134" s="65">
         <v>46270</v>
       </c>
-      <c r="S134" s="163"/>
-      <c r="T134" s="163"/>
+      <c r="S134" s="160"/>
+      <c r="T134" s="160"/>
     </row>
     <row r="135" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A135" s="12" t="s">
@@ -13265,8 +13312,8 @@
       <c r="R135" s="65">
         <v>46270</v>
       </c>
-      <c r="S135" s="163"/>
-      <c r="T135" s="163"/>
+      <c r="S135" s="160"/>
+      <c r="T135" s="160"/>
     </row>
     <row r="136" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A136" s="12" t="s">
@@ -13321,8 +13368,8 @@
       <c r="R136" s="65">
         <v>46270</v>
       </c>
-      <c r="S136" s="163"/>
-      <c r="T136" s="163"/>
+      <c r="S136" s="160"/>
+      <c r="T136" s="160"/>
     </row>
     <row r="137" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A137" s="12" t="s">
@@ -13377,8 +13424,8 @@
       <c r="R137" s="65">
         <v>46270</v>
       </c>
-      <c r="S137" s="163"/>
-      <c r="T137" s="163"/>
+      <c r="S137" s="160"/>
+      <c r="T137" s="160"/>
     </row>
     <row r="138" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A138" s="12" t="s">
@@ -13433,8 +13480,8 @@
       <c r="R138" s="65">
         <v>46270</v>
       </c>
-      <c r="S138" s="163"/>
-      <c r="T138" s="163"/>
+      <c r="S138" s="160"/>
+      <c r="T138" s="160"/>
     </row>
     <row r="139" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A139" s="12" t="s">
@@ -13489,8 +13536,8 @@
       <c r="R139" s="65">
         <v>46270</v>
       </c>
-      <c r="S139" s="163"/>
-      <c r="T139" s="163"/>
+      <c r="S139" s="160"/>
+      <c r="T139" s="160"/>
     </row>
     <row r="140" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A140" s="12" t="s">
@@ -13545,8 +13592,8 @@
       <c r="R140" s="65">
         <v>46270</v>
       </c>
-      <c r="S140" s="163"/>
-      <c r="T140" s="163"/>
+      <c r="S140" s="160"/>
+      <c r="T140" s="160"/>
     </row>
     <row r="141" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A141" s="12" t="s">
@@ -13601,8 +13648,8 @@
       <c r="R141" s="65">
         <v>46301</v>
       </c>
-      <c r="S141" s="163"/>
-      <c r="T141" s="163"/>
+      <c r="S141" s="160"/>
+      <c r="T141" s="160"/>
     </row>
     <row r="142" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A142" s="12" t="s">
@@ -13657,8 +13704,8 @@
       <c r="R142" s="65">
         <v>46286</v>
       </c>
-      <c r="S142" s="163"/>
-      <c r="T142" s="163"/>
+      <c r="S142" s="160"/>
+      <c r="T142" s="160"/>
     </row>
     <row r="143" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A143" s="12" t="s">
@@ -13713,8 +13760,8 @@
       <c r="R143" s="65">
         <v>46301</v>
       </c>
-      <c r="S143" s="163"/>
-      <c r="T143" s="163"/>
+      <c r="S143" s="160"/>
+      <c r="T143" s="160"/>
     </row>
     <row r="144" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A144" s="12" t="s">
@@ -13769,8 +13816,8 @@
       <c r="R144" s="65">
         <v>46286</v>
       </c>
-      <c r="S144" s="163"/>
-      <c r="T144" s="163"/>
+      <c r="S144" s="160"/>
+      <c r="T144" s="160"/>
     </row>
     <row r="145" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A145" s="12" t="s">
@@ -13825,8 +13872,8 @@
       <c r="R145" s="65">
         <v>46301</v>
       </c>
-      <c r="S145" s="163"/>
-      <c r="T145" s="163"/>
+      <c r="S145" s="160"/>
+      <c r="T145" s="160"/>
     </row>
     <row r="146" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A146" s="12" t="s">
@@ -13881,8 +13928,8 @@
       <c r="R146" s="65">
         <v>46286</v>
       </c>
-      <c r="S146" s="163"/>
-      <c r="T146" s="163"/>
+      <c r="S146" s="160"/>
+      <c r="T146" s="160"/>
     </row>
     <row r="147" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A147" s="12" t="s">
@@ -13937,8 +13984,8 @@
       <c r="R147" s="65">
         <v>46301</v>
       </c>
-      <c r="S147" s="163"/>
-      <c r="T147" s="163"/>
+      <c r="S147" s="160"/>
+      <c r="T147" s="160"/>
     </row>
     <row r="148" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A148" s="12" t="s">
@@ -13993,8 +14040,8 @@
       <c r="R148" s="65">
         <v>46286</v>
       </c>
-      <c r="S148" s="163"/>
-      <c r="T148" s="163"/>
+      <c r="S148" s="160"/>
+      <c r="T148" s="160"/>
     </row>
     <row r="149" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A149" s="12" t="s">
@@ -14049,8 +14096,8 @@
       <c r="R149" s="65">
         <v>46301</v>
       </c>
-      <c r="S149" s="163"/>
-      <c r="T149" s="163"/>
+      <c r="S149" s="160"/>
+      <c r="T149" s="160"/>
     </row>
     <row r="150" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A150" s="12" t="s">
@@ -14105,8 +14152,8 @@
       <c r="R150" s="65">
         <v>46286</v>
       </c>
-      <c r="S150" s="163"/>
-      <c r="T150" s="163"/>
+      <c r="S150" s="160"/>
+      <c r="T150" s="160"/>
     </row>
     <row r="151" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A151" s="12" t="s">
@@ -14161,8 +14208,8 @@
       <c r="R151" s="65">
         <v>46301</v>
       </c>
-      <c r="S151" s="163"/>
-      <c r="T151" s="163"/>
+      <c r="S151" s="160"/>
+      <c r="T151" s="160"/>
     </row>
     <row r="152" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A152" s="12" t="s">
@@ -14217,8 +14264,8 @@
       <c r="R152" s="65">
         <v>46286</v>
       </c>
-      <c r="S152" s="163"/>
-      <c r="T152" s="163"/>
+      <c r="S152" s="160"/>
+      <c r="T152" s="160"/>
     </row>
     <row r="153" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A153" s="12" t="s">
@@ -14273,8 +14320,8 @@
       <c r="R153" s="65">
         <v>46301</v>
       </c>
-      <c r="S153" s="163"/>
-      <c r="T153" s="163"/>
+      <c r="S153" s="160"/>
+      <c r="T153" s="160"/>
     </row>
     <row r="154" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A154" s="12" t="s">
@@ -14329,8 +14376,8 @@
       <c r="R154" s="65">
         <v>46286</v>
       </c>
-      <c r="S154" s="163"/>
-      <c r="T154" s="163"/>
+      <c r="S154" s="160"/>
+      <c r="T154" s="160"/>
     </row>
     <row r="155" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A155" s="12" t="s">
@@ -14385,8 +14432,8 @@
       <c r="R155" s="65">
         <v>46286</v>
       </c>
-      <c r="S155" s="163"/>
-      <c r="T155" s="163"/>
+      <c r="S155" s="160"/>
+      <c r="T155" s="160"/>
     </row>
     <row r="156" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A156" s="12" t="s">
@@ -14443,8 +14490,8 @@
       <c r="R156" s="65">
         <v>46254</v>
       </c>
-      <c r="S156" s="163"/>
-      <c r="T156" s="163"/>
+      <c r="S156" s="160"/>
+      <c r="T156" s="160"/>
     </row>
     <row r="157" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A157" s="12" t="s">
@@ -14501,8 +14548,8 @@
       <c r="R157" s="65">
         <v>46254</v>
       </c>
-      <c r="S157" s="163"/>
-      <c r="T157" s="163"/>
+      <c r="S157" s="160"/>
+      <c r="T157" s="160"/>
     </row>
     <row r="158" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A158" s="12" t="s">
@@ -14559,8 +14606,8 @@
       <c r="R158" s="65">
         <v>46254</v>
       </c>
-      <c r="S158" s="163"/>
-      <c r="T158" s="163"/>
+      <c r="S158" s="160"/>
+      <c r="T158" s="160"/>
     </row>
     <row r="159" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A159" s="12" t="s">
@@ -14617,8 +14664,8 @@
       <c r="R159" s="65">
         <v>46254</v>
       </c>
-      <c r="S159" s="163"/>
-      <c r="T159" s="163"/>
+      <c r="S159" s="160"/>
+      <c r="T159" s="160"/>
     </row>
     <row r="160" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A160" s="12" t="s">
@@ -14675,8 +14722,8 @@
       <c r="R160" s="65">
         <v>46254</v>
       </c>
-      <c r="S160" s="163"/>
-      <c r="T160" s="163"/>
+      <c r="S160" s="160"/>
+      <c r="T160" s="160"/>
     </row>
     <row r="161" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A161" s="12" t="s">
@@ -14733,8 +14780,8 @@
       <c r="R161" s="65">
         <v>46254</v>
       </c>
-      <c r="S161" s="163"/>
-      <c r="T161" s="163"/>
+      <c r="S161" s="160"/>
+      <c r="T161" s="160"/>
     </row>
     <row r="162" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A162" s="12" t="s">
@@ -14791,8 +14838,8 @@
       <c r="R162" s="65">
         <v>46254</v>
       </c>
-      <c r="S162" s="163"/>
-      <c r="T162" s="163"/>
+      <c r="S162" s="160"/>
+      <c r="T162" s="160"/>
     </row>
     <row r="163" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A163" s="12" t="s">
@@ -14849,8 +14896,8 @@
       <c r="R163" s="65">
         <v>46254</v>
       </c>
-      <c r="S163" s="163"/>
-      <c r="T163" s="163"/>
+      <c r="S163" s="160"/>
+      <c r="T163" s="160"/>
     </row>
     <row r="164" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A164" s="12" t="s">
@@ -14907,8 +14954,8 @@
       <c r="R164" s="65">
         <v>46238</v>
       </c>
-      <c r="S164" s="163"/>
-      <c r="T164" s="163"/>
+      <c r="S164" s="160"/>
+      <c r="T164" s="160"/>
     </row>
     <row r="165" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A165" s="12" t="s">
@@ -14965,8 +15012,8 @@
       <c r="R165" s="65">
         <v>46238</v>
       </c>
-      <c r="S165" s="163"/>
-      <c r="T165" s="163"/>
+      <c r="S165" s="160"/>
+      <c r="T165" s="160"/>
     </row>
     <row r="166" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A166" s="12" t="s">
@@ -15023,8 +15070,8 @@
       <c r="R166" s="65">
         <v>46238</v>
       </c>
-      <c r="S166" s="163"/>
-      <c r="T166" s="163"/>
+      <c r="S166" s="160"/>
+      <c r="T166" s="160"/>
     </row>
     <row r="167" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A167" s="12" t="s">
@@ -15081,8 +15128,8 @@
       <c r="R167" s="65">
         <v>46238</v>
       </c>
-      <c r="S167" s="163"/>
-      <c r="T167" s="163"/>
+      <c r="S167" s="160"/>
+      <c r="T167" s="160"/>
     </row>
     <row r="168" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A168" s="12" t="s">
@@ -15139,8 +15186,8 @@
       <c r="R168" s="65">
         <v>46238</v>
       </c>
-      <c r="S168" s="163"/>
-      <c r="T168" s="163"/>
+      <c r="S168" s="160"/>
+      <c r="T168" s="160"/>
     </row>
     <row r="169" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A169" s="12" t="s">
@@ -15197,8 +15244,8 @@
       <c r="R169" s="65">
         <v>46238</v>
       </c>
-      <c r="S169" s="163"/>
-      <c r="T169" s="163"/>
+      <c r="S169" s="160"/>
+      <c r="T169" s="160"/>
     </row>
     <row r="170" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A170" s="12" t="s">
@@ -15255,8 +15302,8 @@
       <c r="R170" s="65">
         <v>46238</v>
       </c>
-      <c r="S170" s="163"/>
-      <c r="T170" s="163"/>
+      <c r="S170" s="160"/>
+      <c r="T170" s="160"/>
     </row>
     <row r="171" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A171" s="12" t="s">
@@ -15313,8 +15360,8 @@
       <c r="R171" s="65">
         <v>46266</v>
       </c>
-      <c r="S171" s="163"/>
-      <c r="T171" s="163"/>
+      <c r="S171" s="160"/>
+      <c r="T171" s="160"/>
     </row>
     <row r="172" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A172" s="12" t="s">
@@ -15371,8 +15418,8 @@
       <c r="R172" s="65">
         <v>46266</v>
       </c>
-      <c r="S172" s="163"/>
-      <c r="T172" s="163"/>
+      <c r="S172" s="160"/>
+      <c r="T172" s="160"/>
     </row>
     <row r="173" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A173" s="12" t="s">
@@ -15429,8 +15476,8 @@
       <c r="R173" s="65">
         <v>46266</v>
       </c>
-      <c r="S173" s="163"/>
-      <c r="T173" s="163"/>
+      <c r="S173" s="160"/>
+      <c r="T173" s="160"/>
     </row>
     <row r="174" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A174" s="12" t="s">
@@ -15487,8 +15534,8 @@
       <c r="R174" s="65">
         <v>46266</v>
       </c>
-      <c r="S174" s="163"/>
-      <c r="T174" s="163"/>
+      <c r="S174" s="160"/>
+      <c r="T174" s="160"/>
     </row>
     <row r="175" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A175" s="12" t="s">
@@ -15545,8 +15592,8 @@
       <c r="R175" s="65">
         <v>46266</v>
       </c>
-      <c r="S175" s="163"/>
-      <c r="T175" s="163"/>
+      <c r="S175" s="160"/>
+      <c r="T175" s="160"/>
     </row>
     <row r="176" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A176" s="12" t="s">
@@ -15603,8 +15650,8 @@
       <c r="R176" s="65">
         <v>46252</v>
       </c>
-      <c r="S176" s="163"/>
-      <c r="T176" s="163"/>
+      <c r="S176" s="160"/>
+      <c r="T176" s="160"/>
     </row>
     <row r="177" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A177" s="12" t="s">
@@ -15661,8 +15708,8 @@
       <c r="R177" s="65">
         <v>46252</v>
       </c>
-      <c r="S177" s="163"/>
-      <c r="T177" s="163"/>
+      <c r="S177" s="160"/>
+      <c r="T177" s="160"/>
     </row>
     <row r="178" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A178" s="12" t="s">
@@ -15719,8 +15766,8 @@
       <c r="R178" s="65">
         <v>46252</v>
       </c>
-      <c r="S178" s="163"/>
-      <c r="T178" s="163"/>
+      <c r="S178" s="160"/>
+      <c r="T178" s="160"/>
     </row>
     <row r="179" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A179" s="12" t="s">
@@ -15777,8 +15824,8 @@
       <c r="R179" s="65">
         <v>46252</v>
       </c>
-      <c r="S179" s="163"/>
-      <c r="T179" s="163"/>
+      <c r="S179" s="160"/>
+      <c r="T179" s="160"/>
     </row>
     <row r="180" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A180" s="12" t="s">
@@ -15835,8 +15882,8 @@
       <c r="R180" s="65">
         <v>46252</v>
       </c>
-      <c r="S180" s="163"/>
-      <c r="T180" s="163"/>
+      <c r="S180" s="160"/>
+      <c r="T180" s="160"/>
     </row>
     <row r="181" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A181" s="12" t="s">
@@ -15893,8 +15940,8 @@
       <c r="R181" s="65">
         <v>46252</v>
       </c>
-      <c r="S181" s="163"/>
-      <c r="T181" s="163"/>
+      <c r="S181" s="160"/>
+      <c r="T181" s="160"/>
     </row>
     <row r="182" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A182" s="12" t="s">
@@ -15951,8 +15998,8 @@
       <c r="R182" s="65">
         <v>46252</v>
       </c>
-      <c r="S182" s="163"/>
-      <c r="T182" s="163"/>
+      <c r="S182" s="160"/>
+      <c r="T182" s="160"/>
     </row>
     <row r="183" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A183" s="12" t="s">
@@ -16009,8 +16056,8 @@
       <c r="R183" s="65">
         <v>46252</v>
       </c>
-      <c r="S183" s="163"/>
-      <c r="T183" s="163"/>
+      <c r="S183" s="160"/>
+      <c r="T183" s="160"/>
     </row>
     <row r="184" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A184" s="12" t="s">
@@ -16067,8 +16114,8 @@
       <c r="R184" s="65">
         <v>46238</v>
       </c>
-      <c r="S184" s="163"/>
-      <c r="T184" s="163"/>
+      <c r="S184" s="160"/>
+      <c r="T184" s="160"/>
     </row>
     <row r="185" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A185" s="12" t="s">
@@ -16125,8 +16172,8 @@
       <c r="R185" s="65">
         <v>46238</v>
       </c>
-      <c r="S185" s="163"/>
-      <c r="T185" s="163"/>
+      <c r="S185" s="160"/>
+      <c r="T185" s="160"/>
     </row>
     <row r="186" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A186" s="12" t="s">
@@ -16183,8 +16230,8 @@
       <c r="R186" s="65">
         <v>46238</v>
       </c>
-      <c r="S186" s="163"/>
-      <c r="T186" s="163"/>
+      <c r="S186" s="160"/>
+      <c r="T186" s="160"/>
     </row>
     <row r="187" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A187" s="12" t="s">
@@ -16241,8 +16288,8 @@
       <c r="R187" s="65">
         <v>46238</v>
       </c>
-      <c r="S187" s="163"/>
-      <c r="T187" s="163"/>
+      <c r="S187" s="160"/>
+      <c r="T187" s="160"/>
     </row>
     <row r="188" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A188" s="12" t="s">
@@ -16299,8 +16346,8 @@
       <c r="R188" s="65">
         <v>46238</v>
       </c>
-      <c r="S188" s="163"/>
-      <c r="T188" s="163"/>
+      <c r="S188" s="160"/>
+      <c r="T188" s="160"/>
     </row>
     <row r="189" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A189" s="12" t="s">
@@ -16357,8 +16404,8 @@
       <c r="R189" s="65">
         <v>46238</v>
       </c>
-      <c r="S189" s="163"/>
-      <c r="T189" s="163"/>
+      <c r="S189" s="160"/>
+      <c r="T189" s="160"/>
     </row>
     <row r="190" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A190" s="12" t="s">
@@ -16415,8 +16462,8 @@
       <c r="R190" s="65">
         <v>46238</v>
       </c>
-      <c r="S190" s="163"/>
-      <c r="T190" s="163"/>
+      <c r="S190" s="160"/>
+      <c r="T190" s="160"/>
     </row>
     <row r="191" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A191" s="12" t="s">
@@ -16473,8 +16520,8 @@
       <c r="R191" s="65">
         <v>46238</v>
       </c>
-      <c r="S191" s="163"/>
-      <c r="T191" s="163"/>
+      <c r="S191" s="160"/>
+      <c r="T191" s="160"/>
     </row>
     <row r="192" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A192" s="14" t="s">
@@ -16529,8 +16576,8 @@
       <c r="R192" s="65">
         <v>46154</v>
       </c>
-      <c r="S192" s="163"/>
-      <c r="T192" s="163"/>
+      <c r="S192" s="160"/>
+      <c r="T192" s="160"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R192">
@@ -16626,10 +16673,10 @@
       <c r="Q1" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="R1" s="162" t="s">
+      <c r="R1" s="22" t="s">
         <v>1204</v>
       </c>
-      <c r="S1" s="162" t="s">
+      <c r="S1" s="22" t="s">
         <v>1205</v>
       </c>
     </row>
@@ -16677,8 +16724,8 @@
         <v>0</v>
       </c>
       <c r="Q2" s="17"/>
-      <c r="R2" s="163"/>
-      <c r="S2" s="163"/>
+      <c r="R2" s="160"/>
+      <c r="S2" s="160"/>
     </row>
     <row r="3" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
@@ -16724,8 +16771,8 @@
         <v>0</v>
       </c>
       <c r="Q3" s="17"/>
-      <c r="R3" s="163"/>
-      <c r="S3" s="163"/>
+      <c r="R3" s="160"/>
+      <c r="S3" s="160"/>
     </row>
     <row r="4" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
@@ -16771,8 +16818,8 @@
         <v>0</v>
       </c>
       <c r="Q4" s="17"/>
-      <c r="R4" s="163"/>
-      <c r="S4" s="163"/>
+      <c r="R4" s="160"/>
+      <c r="S4" s="160"/>
     </row>
     <row r="5" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
@@ -16818,8 +16865,8 @@
         <v>0</v>
       </c>
       <c r="Q5" s="17"/>
-      <c r="R5" s="163"/>
-      <c r="S5" s="163"/>
+      <c r="R5" s="160"/>
+      <c r="S5" s="160"/>
     </row>
     <row r="6" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
@@ -16865,8 +16912,8 @@
         <v>0</v>
       </c>
       <c r="Q6" s="17"/>
-      <c r="R6" s="163"/>
-      <c r="S6" s="163"/>
+      <c r="R6" s="160"/>
+      <c r="S6" s="160"/>
     </row>
     <row r="7" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
@@ -16912,8 +16959,8 @@
         <v>0</v>
       </c>
       <c r="Q7" s="17"/>
-      <c r="R7" s="163"/>
-      <c r="S7" s="163"/>
+      <c r="R7" s="160"/>
+      <c r="S7" s="160"/>
     </row>
     <row r="8" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
@@ -16959,8 +17006,8 @@
         <v>0</v>
       </c>
       <c r="Q8" s="17"/>
-      <c r="R8" s="163"/>
-      <c r="S8" s="163"/>
+      <c r="R8" s="160"/>
+      <c r="S8" s="160"/>
     </row>
     <row r="9" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
@@ -17006,8 +17053,8 @@
         <v>0</v>
       </c>
       <c r="Q9" s="17"/>
-      <c r="R9" s="163"/>
-      <c r="S9" s="163"/>
+      <c r="R9" s="160"/>
+      <c r="S9" s="160"/>
     </row>
     <row r="10" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
@@ -17053,8 +17100,8 @@
         <v>0</v>
       </c>
       <c r="Q10" s="17"/>
-      <c r="R10" s="163"/>
-      <c r="S10" s="163"/>
+      <c r="R10" s="160"/>
+      <c r="S10" s="160"/>
     </row>
     <row r="11" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
@@ -17100,8 +17147,8 @@
         <v>0</v>
       </c>
       <c r="Q11" s="17"/>
-      <c r="R11" s="163"/>
-      <c r="S11" s="163"/>
+      <c r="R11" s="160"/>
+      <c r="S11" s="160"/>
     </row>
     <row r="12" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
@@ -17147,8 +17194,8 @@
         <v>0</v>
       </c>
       <c r="Q12" s="17"/>
-      <c r="R12" s="163"/>
-      <c r="S12" s="163"/>
+      <c r="R12" s="160"/>
+      <c r="S12" s="160"/>
     </row>
     <row r="13" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="s">
@@ -17194,8 +17241,8 @@
         <v>0</v>
       </c>
       <c r="Q13" s="17"/>
-      <c r="R13" s="163"/>
-      <c r="S13" s="163"/>
+      <c r="R13" s="160"/>
+      <c r="S13" s="160"/>
     </row>
     <row r="14" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A14" s="23" t="s">
@@ -17241,8 +17288,8 @@
         <v>0</v>
       </c>
       <c r="Q14" s="17"/>
-      <c r="R14" s="163"/>
-      <c r="S14" s="163"/>
+      <c r="R14" s="160"/>
+      <c r="S14" s="160"/>
     </row>
     <row r="15" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
@@ -17288,8 +17335,8 @@
         <v>0</v>
       </c>
       <c r="Q15" s="17"/>
-      <c r="R15" s="163"/>
-      <c r="S15" s="163"/>
+      <c r="R15" s="160"/>
+      <c r="S15" s="160"/>
     </row>
     <row r="16" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
@@ -17335,8 +17382,8 @@
         <v>0</v>
       </c>
       <c r="Q16" s="17"/>
-      <c r="R16" s="163"/>
-      <c r="S16" s="163"/>
+      <c r="R16" s="160"/>
+      <c r="S16" s="160"/>
     </row>
     <row r="17" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
@@ -17382,8 +17429,8 @@
         <v>0</v>
       </c>
       <c r="Q17" s="17"/>
-      <c r="R17" s="163"/>
-      <c r="S17" s="163"/>
+      <c r="R17" s="160"/>
+      <c r="S17" s="160"/>
     </row>
     <row r="18" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A18" s="23" t="s">
@@ -17429,8 +17476,8 @@
         <v>0</v>
       </c>
       <c r="Q18" s="17"/>
-      <c r="R18" s="163"/>
-      <c r="S18" s="163"/>
+      <c r="R18" s="160"/>
+      <c r="S18" s="160"/>
     </row>
     <row r="19" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A19" s="23" t="s">
@@ -17476,8 +17523,8 @@
         <v>0</v>
       </c>
       <c r="Q19" s="17"/>
-      <c r="R19" s="163"/>
-      <c r="S19" s="163"/>
+      <c r="R19" s="160"/>
+      <c r="S19" s="160"/>
     </row>
     <row r="20" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A20" s="23" t="s">
@@ -17523,8 +17570,8 @@
         <v>0</v>
       </c>
       <c r="Q20" s="17"/>
-      <c r="R20" s="163"/>
-      <c r="S20" s="163"/>
+      <c r="R20" s="160"/>
+      <c r="S20" s="160"/>
     </row>
     <row r="21" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="s">
@@ -17570,8 +17617,8 @@
         <v>0</v>
       </c>
       <c r="Q21" s="17"/>
-      <c r="R21" s="163"/>
-      <c r="S21" s="163"/>
+      <c r="R21" s="160"/>
+      <c r="S21" s="160"/>
     </row>
     <row r="22" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A22" s="23" t="s">
@@ -17617,8 +17664,8 @@
         <v>0</v>
       </c>
       <c r="Q22" s="17"/>
-      <c r="R22" s="163"/>
-      <c r="S22" s="163"/>
+      <c r="R22" s="160"/>
+      <c r="S22" s="160"/>
     </row>
     <row r="23" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="s">
@@ -17664,8 +17711,8 @@
         <v>0</v>
       </c>
       <c r="Q23" s="17"/>
-      <c r="R23" s="163"/>
-      <c r="S23" s="163"/>
+      <c r="R23" s="160"/>
+      <c r="S23" s="160"/>
     </row>
     <row r="24" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A24" s="23" t="s">
@@ -17711,8 +17758,8 @@
         <v>0</v>
       </c>
       <c r="Q24" s="17"/>
-      <c r="R24" s="163"/>
-      <c r="S24" s="163"/>
+      <c r="R24" s="160"/>
+      <c r="S24" s="160"/>
     </row>
     <row r="25" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A25" s="23" t="s">
@@ -17758,8 +17805,8 @@
         <v>0</v>
       </c>
       <c r="Q25" s="17"/>
-      <c r="R25" s="163"/>
-      <c r="S25" s="163"/>
+      <c r="R25" s="160"/>
+      <c r="S25" s="160"/>
     </row>
     <row r="26" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
@@ -17805,8 +17852,8 @@
         <v>0</v>
       </c>
       <c r="Q26" s="17"/>
-      <c r="R26" s="163"/>
-      <c r="S26" s="163"/>
+      <c r="R26" s="160"/>
+      <c r="S26" s="160"/>
     </row>
     <row r="27" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A27" s="23" t="s">
@@ -17852,8 +17899,8 @@
         <v>0</v>
       </c>
       <c r="Q27" s="17"/>
-      <c r="R27" s="163"/>
-      <c r="S27" s="163"/>
+      <c r="R27" s="160"/>
+      <c r="S27" s="160"/>
     </row>
     <row r="28" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A28" s="23" t="s">
@@ -17899,8 +17946,8 @@
         <v>0</v>
       </c>
       <c r="Q28" s="17"/>
-      <c r="R28" s="163"/>
-      <c r="S28" s="163"/>
+      <c r="R28" s="160"/>
+      <c r="S28" s="160"/>
     </row>
     <row r="29" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="s">
@@ -17946,8 +17993,8 @@
         <v>0</v>
       </c>
       <c r="Q29" s="17"/>
-      <c r="R29" s="163"/>
-      <c r="S29" s="163"/>
+      <c r="R29" s="160"/>
+      <c r="S29" s="160"/>
     </row>
     <row r="30" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A30" s="23" t="s">
@@ -17993,8 +18040,8 @@
         <v>0</v>
       </c>
       <c r="Q30" s="17"/>
-      <c r="R30" s="163"/>
-      <c r="S30" s="163"/>
+      <c r="R30" s="160"/>
+      <c r="S30" s="160"/>
     </row>
     <row r="31" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
@@ -18040,8 +18087,8 @@
         <v>0</v>
       </c>
       <c r="Q31" s="17"/>
-      <c r="R31" s="163"/>
-      <c r="S31" s="163"/>
+      <c r="R31" s="160"/>
+      <c r="S31" s="160"/>
     </row>
     <row r="32" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A32" s="23" t="s">
@@ -18087,8 +18134,8 @@
         <v>0</v>
       </c>
       <c r="Q32" s="17"/>
-      <c r="R32" s="163"/>
-      <c r="S32" s="163"/>
+      <c r="R32" s="160"/>
+      <c r="S32" s="160"/>
     </row>
     <row r="33" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A33" s="23" t="s">
@@ -18134,8 +18181,8 @@
         <v>0</v>
       </c>
       <c r="Q33" s="17"/>
-      <c r="R33" s="163"/>
-      <c r="S33" s="163"/>
+      <c r="R33" s="160"/>
+      <c r="S33" s="160"/>
     </row>
     <row r="34" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
@@ -18181,8 +18228,8 @@
         <v>0</v>
       </c>
       <c r="Q34" s="17"/>
-      <c r="R34" s="163"/>
-      <c r="S34" s="163"/>
+      <c r="R34" s="160"/>
+      <c r="S34" s="160"/>
     </row>
     <row r="35" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A35" s="23" t="s">
@@ -18234,8 +18281,8 @@
         <v>0</v>
       </c>
       <c r="Q35" s="17"/>
-      <c r="R35" s="163"/>
-      <c r="S35" s="163"/>
+      <c r="R35" s="160"/>
+      <c r="S35" s="160"/>
     </row>
     <row r="36" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A36" s="23" t="s">
@@ -18287,8 +18334,8 @@
         <v>0</v>
       </c>
       <c r="Q36" s="17"/>
-      <c r="R36" s="163"/>
-      <c r="S36" s="163"/>
+      <c r="R36" s="160"/>
+      <c r="S36" s="160"/>
     </row>
     <row r="37" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A37" s="23" t="s">
@@ -18340,8 +18387,8 @@
         <v>0</v>
       </c>
       <c r="Q37" s="17"/>
-      <c r="R37" s="163"/>
-      <c r="S37" s="163"/>
+      <c r="R37" s="160"/>
+      <c r="S37" s="160"/>
     </row>
     <row r="38" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A38" s="23" t="s">
@@ -18393,8 +18440,8 @@
         <v>0</v>
       </c>
       <c r="Q38" s="17"/>
-      <c r="R38" s="163"/>
-      <c r="S38" s="163"/>
+      <c r="R38" s="160"/>
+      <c r="S38" s="160"/>
     </row>
     <row r="39" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
@@ -18446,8 +18493,8 @@
         <v>0</v>
       </c>
       <c r="Q39" s="17"/>
-      <c r="R39" s="163"/>
-      <c r="S39" s="163"/>
+      <c r="R39" s="160"/>
+      <c r="S39" s="160"/>
     </row>
     <row r="40" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A40" s="23" t="s">
@@ -18499,8 +18546,8 @@
         <v>0</v>
       </c>
       <c r="Q40" s="17"/>
-      <c r="R40" s="163"/>
-      <c r="S40" s="163"/>
+      <c r="R40" s="160"/>
+      <c r="S40" s="160"/>
     </row>
     <row r="41" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A41" s="23" t="s">
@@ -18552,8 +18599,8 @@
         <v>0</v>
       </c>
       <c r="Q41" s="17"/>
-      <c r="R41" s="163"/>
-      <c r="S41" s="163"/>
+      <c r="R41" s="160"/>
+      <c r="S41" s="160"/>
     </row>
     <row r="42" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A42" s="23" t="s">
@@ -18605,8 +18652,8 @@
         <v>0</v>
       </c>
       <c r="Q42" s="17"/>
-      <c r="R42" s="163"/>
-      <c r="S42" s="163"/>
+      <c r="R42" s="160"/>
+      <c r="S42" s="160"/>
     </row>
     <row r="43" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A43" s="23" t="s">
@@ -18658,8 +18705,8 @@
         <v>0</v>
       </c>
       <c r="Q43" s="17"/>
-      <c r="R43" s="163"/>
-      <c r="S43" s="163"/>
+      <c r="R43" s="160"/>
+      <c r="S43" s="160"/>
     </row>
     <row r="44" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A44" s="23" t="s">
@@ -18711,8 +18758,8 @@
         <v>0</v>
       </c>
       <c r="Q44" s="17"/>
-      <c r="R44" s="163"/>
-      <c r="S44" s="163"/>
+      <c r="R44" s="160"/>
+      <c r="S44" s="160"/>
     </row>
     <row r="45" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A45" s="23" t="s">
@@ -18764,8 +18811,8 @@
         <v>0</v>
       </c>
       <c r="Q45" s="17"/>
-      <c r="R45" s="163"/>
-      <c r="S45" s="163"/>
+      <c r="R45" s="160"/>
+      <c r="S45" s="160"/>
     </row>
     <row r="46" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A46" s="23" t="s">
@@ -18817,8 +18864,8 @@
         <v>0</v>
       </c>
       <c r="Q46" s="17"/>
-      <c r="R46" s="163"/>
-      <c r="S46" s="163"/>
+      <c r="R46" s="160"/>
+      <c r="S46" s="160"/>
     </row>
     <row r="47" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A47" s="23" t="s">
@@ -18870,8 +18917,8 @@
         <v>0</v>
       </c>
       <c r="Q47" s="17"/>
-      <c r="R47" s="163"/>
-      <c r="S47" s="163"/>
+      <c r="R47" s="160"/>
+      <c r="S47" s="160"/>
     </row>
     <row r="48" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A48" s="23" t="s">
@@ -18923,8 +18970,8 @@
         <v>0</v>
       </c>
       <c r="Q48" s="17"/>
-      <c r="R48" s="163"/>
-      <c r="S48" s="163"/>
+      <c r="R48" s="160"/>
+      <c r="S48" s="160"/>
     </row>
     <row r="49" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A49" s="23" t="s">
@@ -18976,8 +19023,8 @@
         <v>0</v>
       </c>
       <c r="Q49" s="17"/>
-      <c r="R49" s="163"/>
-      <c r="S49" s="163"/>
+      <c r="R49" s="160"/>
+      <c r="S49" s="160"/>
     </row>
     <row r="50" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A50" s="23" t="s">
@@ -19029,8 +19076,8 @@
         <v>0</v>
       </c>
       <c r="Q50" s="17"/>
-      <c r="R50" s="163"/>
-      <c r="S50" s="163"/>
+      <c r="R50" s="160"/>
+      <c r="S50" s="160"/>
     </row>
     <row r="51" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A51" s="23" t="s">
@@ -19082,8 +19129,8 @@
         <v>0</v>
       </c>
       <c r="Q51" s="17"/>
-      <c r="R51" s="163"/>
-      <c r="S51" s="163"/>
+      <c r="R51" s="160"/>
+      <c r="S51" s="160"/>
     </row>
     <row r="52" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A52" s="23" t="s">
@@ -19135,8 +19182,8 @@
         <v>0</v>
       </c>
       <c r="Q52" s="17"/>
-      <c r="R52" s="163"/>
-      <c r="S52" s="163"/>
+      <c r="R52" s="160"/>
+      <c r="S52" s="160"/>
     </row>
     <row r="53" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A53" s="23" t="s">
@@ -19188,8 +19235,8 @@
         <v>0</v>
       </c>
       <c r="Q53" s="17"/>
-      <c r="R53" s="163"/>
-      <c r="S53" s="163"/>
+      <c r="R53" s="160"/>
+      <c r="S53" s="160"/>
     </row>
     <row r="54" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A54" s="23" t="s">
@@ -19241,8 +19288,8 @@
         <v>0</v>
       </c>
       <c r="Q54" s="17"/>
-      <c r="R54" s="163"/>
-      <c r="S54" s="163"/>
+      <c r="R54" s="160"/>
+      <c r="S54" s="160"/>
     </row>
     <row r="55" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A55" s="23" t="s">
@@ -19294,8 +19341,8 @@
         <v>0</v>
       </c>
       <c r="Q55" s="17"/>
-      <c r="R55" s="163"/>
-      <c r="S55" s="163"/>
+      <c r="R55" s="160"/>
+      <c r="S55" s="160"/>
     </row>
     <row r="56" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A56" s="23" t="s">
@@ -19347,8 +19394,8 @@
         <v>0</v>
       </c>
       <c r="Q56" s="17"/>
-      <c r="R56" s="163"/>
-      <c r="S56" s="163"/>
+      <c r="R56" s="160"/>
+      <c r="S56" s="160"/>
     </row>
     <row r="57" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A57" s="23" t="s">
@@ -19400,8 +19447,8 @@
         <v>0</v>
       </c>
       <c r="Q57" s="17"/>
-      <c r="R57" s="163"/>
-      <c r="S57" s="163"/>
+      <c r="R57" s="160"/>
+      <c r="S57" s="160"/>
     </row>
     <row r="58" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A58" s="23" t="s">
@@ -19453,8 +19500,8 @@
         <v>0</v>
       </c>
       <c r="Q58" s="17"/>
-      <c r="R58" s="163"/>
-      <c r="S58" s="163"/>
+      <c r="R58" s="160"/>
+      <c r="S58" s="160"/>
     </row>
     <row r="59" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A59" s="23" t="s">
@@ -19506,8 +19553,8 @@
         <v>0</v>
       </c>
       <c r="Q59" s="17"/>
-      <c r="R59" s="163"/>
-      <c r="S59" s="163"/>
+      <c r="R59" s="160"/>
+      <c r="S59" s="160"/>
     </row>
     <row r="60" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A60" s="23" t="s">
@@ -19559,8 +19606,8 @@
         <v>0</v>
       </c>
       <c r="Q60" s="17"/>
-      <c r="R60" s="163"/>
-      <c r="S60" s="163"/>
+      <c r="R60" s="160"/>
+      <c r="S60" s="160"/>
     </row>
     <row r="61" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
@@ -19612,8 +19659,8 @@
         <v>0</v>
       </c>
       <c r="Q61" s="17"/>
-      <c r="R61" s="163"/>
-      <c r="S61" s="163"/>
+      <c r="R61" s="160"/>
+      <c r="S61" s="160"/>
     </row>
     <row r="62" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A62" s="23" t="s">
@@ -19665,8 +19712,8 @@
         <v>0</v>
       </c>
       <c r="Q62" s="17"/>
-      <c r="R62" s="163"/>
-      <c r="S62" s="163"/>
+      <c r="R62" s="160"/>
+      <c r="S62" s="160"/>
     </row>
     <row r="63" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A63" s="23" t="s">
@@ -19718,8 +19765,8 @@
         <v>0</v>
       </c>
       <c r="Q63" s="17"/>
-      <c r="R63" s="163"/>
-      <c r="S63" s="163"/>
+      <c r="R63" s="160"/>
+      <c r="S63" s="160"/>
     </row>
     <row r="64" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A64" s="23" t="s">
@@ -19771,8 +19818,8 @@
         <v>0</v>
       </c>
       <c r="Q64" s="17"/>
-      <c r="R64" s="163"/>
-      <c r="S64" s="163"/>
+      <c r="R64" s="160"/>
+      <c r="S64" s="160"/>
     </row>
     <row r="65" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A65" s="23" t="s">
@@ -19824,8 +19871,8 @@
         <v>0</v>
       </c>
       <c r="Q65" s="17"/>
-      <c r="R65" s="163"/>
-      <c r="S65" s="163"/>
+      <c r="R65" s="160"/>
+      <c r="S65" s="160"/>
     </row>
     <row r="66" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A66" s="23" t="s">
@@ -19877,8 +19924,8 @@
         <v>0</v>
       </c>
       <c r="Q66" s="17"/>
-      <c r="R66" s="163"/>
-      <c r="S66" s="163"/>
+      <c r="R66" s="160"/>
+      <c r="S66" s="160"/>
     </row>
     <row r="67" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A67" s="23" t="s">
@@ -19930,8 +19977,8 @@
         <v>0</v>
       </c>
       <c r="Q67" s="17"/>
-      <c r="R67" s="163"/>
-      <c r="S67" s="163"/>
+      <c r="R67" s="160"/>
+      <c r="S67" s="160"/>
     </row>
     <row r="68" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A68" s="23" t="s">
@@ -19983,8 +20030,8 @@
         <v>0</v>
       </c>
       <c r="Q68" s="17"/>
-      <c r="R68" s="163"/>
-      <c r="S68" s="163"/>
+      <c r="R68" s="160"/>
+      <c r="S68" s="160"/>
     </row>
     <row r="69" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A69" s="23" t="s">
@@ -20036,8 +20083,8 @@
         <v>0</v>
       </c>
       <c r="Q69" s="17"/>
-      <c r="R69" s="163"/>
-      <c r="S69" s="163"/>
+      <c r="R69" s="160"/>
+      <c r="S69" s="160"/>
     </row>
     <row r="70" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A70" s="23" t="s">
@@ -20089,8 +20136,8 @@
         <v>0</v>
       </c>
       <c r="Q70" s="17"/>
-      <c r="R70" s="163"/>
-      <c r="S70" s="163"/>
+      <c r="R70" s="160"/>
+      <c r="S70" s="160"/>
     </row>
     <row r="71" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A71" s="23" t="s">
@@ -20142,8 +20189,8 @@
         <v>0</v>
       </c>
       <c r="Q71" s="17"/>
-      <c r="R71" s="163"/>
-      <c r="S71" s="163"/>
+      <c r="R71" s="160"/>
+      <c r="S71" s="160"/>
     </row>
     <row r="72" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A72" s="23" t="s">
@@ -20195,8 +20242,8 @@
         <v>0</v>
       </c>
       <c r="Q72" s="17"/>
-      <c r="R72" s="163"/>
-      <c r="S72" s="163"/>
+      <c r="R72" s="160"/>
+      <c r="S72" s="160"/>
     </row>
     <row r="73" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A73" s="23" t="s">
@@ -20248,8 +20295,8 @@
         <v>0</v>
       </c>
       <c r="Q73" s="17"/>
-      <c r="R73" s="163"/>
-      <c r="S73" s="163"/>
+      <c r="R73" s="160"/>
+      <c r="S73" s="160"/>
     </row>
     <row r="74" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A74" s="23" t="s">
@@ -20301,8 +20348,8 @@
         <v>0</v>
       </c>
       <c r="Q74" s="17"/>
-      <c r="R74" s="163"/>
-      <c r="S74" s="163"/>
+      <c r="R74" s="160"/>
+      <c r="S74" s="160"/>
     </row>
     <row r="75" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A75" s="23" t="s">
@@ -20354,8 +20401,8 @@
         <v>0</v>
       </c>
       <c r="Q75" s="17"/>
-      <c r="R75" s="163"/>
-      <c r="S75" s="163"/>
+      <c r="R75" s="160"/>
+      <c r="S75" s="160"/>
     </row>
     <row r="76" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A76" s="23" t="s">
@@ -20407,8 +20454,8 @@
         <v>0</v>
       </c>
       <c r="Q76" s="17"/>
-      <c r="R76" s="163"/>
-      <c r="S76" s="163"/>
+      <c r="R76" s="160"/>
+      <c r="S76" s="160"/>
     </row>
     <row r="77" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A77" s="23" t="s">
@@ -20462,10 +20509,10 @@
       <c r="Q77" s="57">
         <v>46216</v>
       </c>
-      <c r="R77" s="166">
+      <c r="R77" s="163">
         <v>46234</v>
       </c>
-      <c r="S77" s="163" t="s">
+      <c r="S77" s="160" t="s">
         <v>1207</v>
       </c>
     </row>
@@ -20519,10 +20566,10 @@
         <v>0</v>
       </c>
       <c r="Q78" s="17"/>
-      <c r="R78" s="166">
+      <c r="R78" s="163">
         <v>46234</v>
       </c>
-      <c r="S78" s="163" t="s">
+      <c r="S78" s="160" t="s">
         <v>1208</v>
       </c>
     </row>
@@ -20576,10 +20623,10 @@
         <v>0</v>
       </c>
       <c r="Q79" s="17"/>
-      <c r="R79" s="166">
+      <c r="R79" s="163">
         <v>46234</v>
       </c>
-      <c r="S79" s="163" t="s">
+      <c r="S79" s="160" t="s">
         <v>1209</v>
       </c>
     </row>
@@ -20633,10 +20680,10 @@
         <v>0</v>
       </c>
       <c r="Q80" s="17"/>
-      <c r="R80" s="166">
+      <c r="R80" s="163">
         <v>46234</v>
       </c>
-      <c r="S80" s="163" t="s">
+      <c r="S80" s="160" t="s">
         <v>1210</v>
       </c>
     </row>
@@ -20690,10 +20737,10 @@
         <v>0</v>
       </c>
       <c r="Q81" s="17"/>
-      <c r="R81" s="166">
+      <c r="R81" s="163">
         <v>46234</v>
       </c>
-      <c r="S81" s="163" t="s">
+      <c r="S81" s="160" t="s">
         <v>1211</v>
       </c>
     </row>
@@ -20747,10 +20794,10 @@
         <v>0</v>
       </c>
       <c r="Q82" s="17"/>
-      <c r="R82" s="166">
+      <c r="R82" s="163">
         <v>46234</v>
       </c>
-      <c r="S82" s="163" t="s">
+      <c r="S82" s="160" t="s">
         <v>1212</v>
       </c>
     </row>
@@ -20804,10 +20851,10 @@
         <v>0</v>
       </c>
       <c r="Q83" s="17"/>
-      <c r="R83" s="166">
+      <c r="R83" s="163">
         <v>46234</v>
       </c>
-      <c r="S83" s="163" t="s">
+      <c r="S83" s="160" t="s">
         <v>1213</v>
       </c>
     </row>
@@ -20861,10 +20908,10 @@
         <v>0</v>
       </c>
       <c r="Q84" s="17"/>
-      <c r="R84" s="166">
+      <c r="R84" s="163">
         <v>46234</v>
       </c>
-      <c r="S84" s="163" t="s">
+      <c r="S84" s="160" t="s">
         <v>1214</v>
       </c>
     </row>
@@ -20918,10 +20965,10 @@
         <v>0</v>
       </c>
       <c r="Q85" s="17"/>
-      <c r="R85" s="166">
+      <c r="R85" s="163">
         <v>46234</v>
       </c>
-      <c r="S85" s="163" t="s">
+      <c r="S85" s="160" t="s">
         <v>1215</v>
       </c>
     </row>
@@ -20975,10 +21022,10 @@
         <v>0</v>
       </c>
       <c r="Q86" s="17"/>
-      <c r="R86" s="166">
+      <c r="R86" s="163">
         <v>46234</v>
       </c>
-      <c r="S86" s="163" t="s">
+      <c r="S86" s="160" t="s">
         <v>1216</v>
       </c>
     </row>
@@ -21032,10 +21079,10 @@
         <v>0</v>
       </c>
       <c r="Q87" s="17"/>
-      <c r="R87" s="166">
+      <c r="R87" s="163">
         <v>46234</v>
       </c>
-      <c r="S87" s="163" t="s">
+      <c r="S87" s="160" t="s">
         <v>1217</v>
       </c>
     </row>
@@ -21089,10 +21136,10 @@
         <v>0</v>
       </c>
       <c r="Q88" s="17"/>
-      <c r="R88" s="166">
+      <c r="R88" s="163">
         <v>46234</v>
       </c>
-      <c r="S88" s="163" t="s">
+      <c r="S88" s="160" t="s">
         <v>1218</v>
       </c>
     </row>
@@ -21146,10 +21193,10 @@
         <v>1</v>
       </c>
       <c r="Q89" s="17"/>
-      <c r="R89" s="166">
+      <c r="R89" s="163">
         <v>46234</v>
       </c>
-      <c r="S89" s="163" t="s">
+      <c r="S89" s="160" t="s">
         <v>1219</v>
       </c>
     </row>
@@ -21203,10 +21250,10 @@
         <v>0</v>
       </c>
       <c r="Q90" s="17"/>
-      <c r="R90" s="166">
+      <c r="R90" s="163">
         <v>46234</v>
       </c>
-      <c r="S90" s="163" t="s">
+      <c r="S90" s="160" t="s">
         <v>1220</v>
       </c>
     </row>
@@ -21260,10 +21307,10 @@
         <v>0</v>
       </c>
       <c r="Q91" s="17"/>
-      <c r="R91" s="166">
+      <c r="R91" s="163">
         <v>46234</v>
       </c>
-      <c r="S91" s="163" t="s">
+      <c r="S91" s="160" t="s">
         <v>1221</v>
       </c>
     </row>
@@ -21317,10 +21364,10 @@
         <v>0</v>
       </c>
       <c r="Q92" s="17"/>
-      <c r="R92" s="166">
+      <c r="R92" s="163">
         <v>46234</v>
       </c>
-      <c r="S92" s="163" t="s">
+      <c r="S92" s="160" t="s">
         <v>1222</v>
       </c>
     </row>
@@ -21374,10 +21421,10 @@
         <v>0</v>
       </c>
       <c r="Q93" s="17"/>
-      <c r="R93" s="166">
+      <c r="R93" s="163">
         <v>46204.240972222222</v>
       </c>
-      <c r="S93" s="163">
+      <c r="S93" s="160">
         <v>3.81</v>
       </c>
     </row>
@@ -21431,10 +21478,10 @@
         <v>0</v>
       </c>
       <c r="Q94" s="17"/>
-      <c r="R94" s="166">
+      <c r="R94" s="163">
         <v>46204.455555555556</v>
       </c>
-      <c r="S94" s="163">
+      <c r="S94" s="160">
         <v>11.769</v>
       </c>
     </row>
@@ -21488,10 +21535,10 @@
         <v>0</v>
       </c>
       <c r="Q95" s="57"/>
-      <c r="R95" s="166">
+      <c r="R95" s="163">
         <v>46204.240972222222</v>
       </c>
-      <c r="S95" s="163">
+      <c r="S95" s="160">
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
@@ -21545,10 +21592,10 @@
         <v>0</v>
       </c>
       <c r="Q96" s="17"/>
-      <c r="R96" s="166">
+      <c r="R96" s="163">
         <v>46204.697916666664</v>
       </c>
-      <c r="S96" s="163">
+      <c r="S96" s="160">
         <v>2.952</v>
       </c>
     </row>
@@ -21604,10 +21651,10 @@
       <c r="Q97" s="57">
         <v>46216</v>
       </c>
-      <c r="R97" s="166">
+      <c r="R97" s="163">
         <v>46204.657638888886</v>
       </c>
-      <c r="S97" s="163">
+      <c r="S97" s="160">
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
@@ -21661,10 +21708,10 @@
         <v>0</v>
       </c>
       <c r="Q98" s="17"/>
-      <c r="R98" s="166">
+      <c r="R98" s="163">
         <v>46204.699305555558</v>
       </c>
-      <c r="S98" s="163">
+      <c r="S98" s="160">
         <v>32.673999999999999</v>
       </c>
     </row>
@@ -21718,10 +21765,10 @@
         <v>0</v>
       </c>
       <c r="Q99" s="17"/>
-      <c r="R99" s="166">
+      <c r="R99" s="163">
         <v>46204.657638888886</v>
       </c>
-      <c r="S99" s="163">
+      <c r="S99" s="160">
         <v>4.1719999999999997</v>
       </c>
     </row>
@@ -21775,10 +21822,10 @@
         <v>0</v>
       </c>
       <c r="Q100" s="17"/>
-      <c r="R100" s="166">
+      <c r="R100" s="163">
         <v>46204.459027777775</v>
       </c>
-      <c r="S100" s="163">
+      <c r="S100" s="160">
         <v>4.3360000000000003</v>
       </c>
     </row>
@@ -21832,10 +21879,10 @@
         <v>0</v>
       </c>
       <c r="Q101" s="17"/>
-      <c r="R101" s="166">
+      <c r="R101" s="163">
         <v>46204.329861111109</v>
       </c>
-      <c r="S101" s="163">
+      <c r="S101" s="160">
         <v>4.3209</v>
       </c>
     </row>
@@ -21889,10 +21936,10 @@
         <v>0</v>
       </c>
       <c r="Q102" s="17"/>
-      <c r="R102" s="166">
+      <c r="R102" s="163">
         <v>46204.677083333336</v>
       </c>
-      <c r="S102" s="163">
+      <c r="S102" s="160">
         <v>9.7119999999999997</v>
       </c>
     </row>
@@ -21946,10 +21993,10 @@
         <v>0</v>
       </c>
       <c r="Q103" s="17"/>
-      <c r="R103" s="166">
+      <c r="R103" s="163">
         <v>46204.330555555556</v>
       </c>
-      <c r="S103" s="163">
+      <c r="S103" s="160">
         <v>4.1757999999999997</v>
       </c>
     </row>
@@ -22005,10 +22052,10 @@
       <c r="Q104" s="57">
         <v>46216</v>
       </c>
-      <c r="R104" s="166">
+      <c r="R104" s="163">
         <v>46204.677083333336</v>
       </c>
-      <c r="S104" s="165">
+      <c r="S104" s="162">
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
@@ -22056,8 +22103,8 @@
         <v>0</v>
       </c>
       <c r="Q105" s="17"/>
-      <c r="R105" s="163"/>
-      <c r="S105" s="163"/>
+      <c r="R105" s="160"/>
+      <c r="S105" s="160"/>
     </row>
     <row r="106" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A106" s="23" t="s">
@@ -22111,10 +22158,10 @@
       <c r="Q106" s="57">
         <v>46206</v>
       </c>
-      <c r="R106" s="166">
+      <c r="R106" s="163">
         <v>46204.677083333336</v>
       </c>
-      <c r="S106" s="165">
+      <c r="S106" s="162">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
@@ -22162,8 +22209,8 @@
         <v>0</v>
       </c>
       <c r="Q107" s="17"/>
-      <c r="R107" s="163"/>
-      <c r="S107" s="163"/>
+      <c r="R107" s="160"/>
+      <c r="S107" s="160"/>
     </row>
     <row r="108" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A108" s="23" t="s">
@@ -22215,10 +22262,10 @@
         <v>0</v>
       </c>
       <c r="Q108" s="17"/>
-      <c r="R108" s="164">
+      <c r="R108" s="161">
         <v>46204.702777777777</v>
       </c>
-      <c r="S108" s="165">
+      <c r="S108" s="162">
         <v>20.81</v>
       </c>
     </row>
@@ -22266,8 +22313,8 @@
         <v>0</v>
       </c>
       <c r="Q109" s="17"/>
-      <c r="R109" s="163"/>
-      <c r="S109" s="163"/>
+      <c r="R109" s="160"/>
+      <c r="S109" s="160"/>
     </row>
     <row r="110" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A110" s="23" t="s">
@@ -22321,10 +22368,10 @@
       <c r="Q110" s="57">
         <v>46206</v>
       </c>
-      <c r="R110" s="164">
+      <c r="R110" s="161">
         <v>46204.702777777777</v>
       </c>
-      <c r="S110" s="165">
+      <c r="S110" s="162">
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
@@ -22372,8 +22419,8 @@
         <v>0</v>
       </c>
       <c r="Q111" s="17"/>
-      <c r="R111" s="163"/>
-      <c r="S111" s="163"/>
+      <c r="R111" s="160"/>
+      <c r="S111" s="160"/>
     </row>
     <row r="112" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A112" s="23" t="s">
@@ -22425,10 +22472,10 @@
         <v>0</v>
       </c>
       <c r="Q112" s="17"/>
-      <c r="R112" s="166">
+      <c r="R112" s="163">
         <v>46204.462500000001</v>
       </c>
-      <c r="S112" s="163">
+      <c r="S112" s="160">
         <v>8.8550000000000004</v>
       </c>
     </row>
@@ -22476,8 +22523,8 @@
         <v>0</v>
       </c>
       <c r="Q113" s="17"/>
-      <c r="R113" s="163"/>
-      <c r="S113" s="163"/>
+      <c r="R113" s="160"/>
+      <c r="S113" s="160"/>
     </row>
     <row r="114" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A114" s="23" t="s">
@@ -22529,10 +22576,10 @@
         <v>0</v>
       </c>
       <c r="Q114" s="17"/>
-      <c r="R114" s="166">
+      <c r="R114" s="163">
         <v>46204.448611111111</v>
       </c>
-      <c r="S114" s="163">
+      <c r="S114" s="160">
         <v>6.4509999999999996</v>
       </c>
     </row>
@@ -22580,8 +22627,8 @@
         <v>0</v>
       </c>
       <c r="Q115" s="17"/>
-      <c r="R115" s="163"/>
-      <c r="S115" s="163"/>
+      <c r="R115" s="160"/>
+      <c r="S115" s="160"/>
     </row>
     <row r="116" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A116" s="23" t="s">
@@ -22633,10 +22680,10 @@
         <v>0</v>
       </c>
       <c r="Q116" s="17"/>
-      <c r="R116" s="166">
+      <c r="R116" s="163">
         <v>46204.448611111111</v>
       </c>
-      <c r="S116" s="163">
+      <c r="S116" s="160">
         <v>4.7329999999999997</v>
       </c>
     </row>
@@ -22684,8 +22731,8 @@
         <v>0</v>
       </c>
       <c r="Q117" s="17"/>
-      <c r="R117" s="163"/>
-      <c r="S117" s="163"/>
+      <c r="R117" s="160"/>
+      <c r="S117" s="160"/>
     </row>
     <row r="118" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A118" s="23" t="s">
@@ -22737,10 +22784,10 @@
         <v>0</v>
       </c>
       <c r="Q118" s="17"/>
-      <c r="R118" s="166">
+      <c r="R118" s="163">
         <v>46204.448611111111</v>
       </c>
-      <c r="S118" s="163">
+      <c r="S118" s="160">
         <v>20.442</v>
       </c>
     </row>
@@ -22788,8 +22835,8 @@
         <v>0</v>
       </c>
       <c r="Q119" s="17"/>
-      <c r="R119" s="163"/>
-      <c r="S119" s="163"/>
+      <c r="R119" s="160"/>
+      <c r="S119" s="160"/>
     </row>
     <row r="120" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A120" s="23" t="s">
@@ -22841,10 +22888,10 @@
         <v>0</v>
       </c>
       <c r="Q120" s="17"/>
-      <c r="R120" s="166">
+      <c r="R120" s="163">
         <v>46204.448611111111</v>
       </c>
-      <c r="S120" s="163">
+      <c r="S120" s="160">
         <v>0.223</v>
       </c>
     </row>
@@ -22892,8 +22939,8 @@
         <v>0</v>
       </c>
       <c r="Q121" s="17"/>
-      <c r="R121" s="163"/>
-      <c r="S121" s="163"/>
+      <c r="R121" s="160"/>
+      <c r="S121" s="160"/>
     </row>
     <row r="122" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A122" s="23" t="s">
@@ -22945,10 +22992,10 @@
         <v>0</v>
       </c>
       <c r="Q122" s="17"/>
-      <c r="R122" s="166">
+      <c r="R122" s="163">
         <v>46204.448611111111</v>
       </c>
-      <c r="S122" s="163">
+      <c r="S122" s="160">
         <v>7.593</v>
       </c>
     </row>
@@ -22996,8 +23043,8 @@
         <v>0</v>
       </c>
       <c r="Q123" s="17"/>
-      <c r="R123" s="163"/>
-      <c r="S123" s="163"/>
+      <c r="R123" s="160"/>
+      <c r="S123" s="160"/>
     </row>
     <row r="124" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A124" s="23" t="s">
@@ -23049,10 +23096,10 @@
         <v>0</v>
       </c>
       <c r="Q124" s="17"/>
-      <c r="R124" s="166">
+      <c r="R124" s="163">
         <v>46204.448611111111</v>
       </c>
-      <c r="S124" s="163">
+      <c r="S124" s="160">
         <v>3.8929999999999998</v>
       </c>
     </row>
@@ -23100,8 +23147,8 @@
         <v>0</v>
       </c>
       <c r="Q125" s="17"/>
-      <c r="R125" s="163"/>
-      <c r="S125" s="163"/>
+      <c r="R125" s="160"/>
+      <c r="S125" s="160"/>
     </row>
     <row r="126" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A126" s="23" t="s">
@@ -23155,10 +23202,10 @@
       <c r="Q126" s="57">
         <v>46206</v>
       </c>
-      <c r="R126" s="166">
+      <c r="R126" s="163">
         <v>46204.448611111111</v>
       </c>
-      <c r="S126" s="163">
+      <c r="S126" s="160">
         <v>1.163</v>
       </c>
     </row>
@@ -23206,8 +23253,8 @@
         <v>0</v>
       </c>
       <c r="Q127" s="17"/>
-      <c r="R127" s="163"/>
-      <c r="S127" s="163"/>
+      <c r="R127" s="160"/>
+      <c r="S127" s="160"/>
     </row>
     <row r="128" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A128" s="23" t="s">
@@ -23259,10 +23306,10 @@
         <v>0</v>
       </c>
       <c r="Q128" s="17"/>
-      <c r="R128" s="166">
+      <c r="R128" s="163">
         <v>46204.448611111111</v>
       </c>
-      <c r="S128" s="163">
+      <c r="S128" s="160">
         <v>22.7</v>
       </c>
     </row>
@@ -23310,8 +23357,8 @@
         <v>0</v>
       </c>
       <c r="Q129" s="17"/>
-      <c r="R129" s="163"/>
-      <c r="S129" s="163"/>
+      <c r="R129" s="160"/>
+      <c r="S129" s="160"/>
     </row>
     <row r="130" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A130" s="23" t="s">
@@ -23357,8 +23404,8 @@
         <v>0</v>
       </c>
       <c r="Q130" s="17"/>
-      <c r="R130" s="163"/>
-      <c r="S130" s="163"/>
+      <c r="R130" s="160"/>
+      <c r="S130" s="160"/>
     </row>
     <row r="131" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A131" s="23" t="s">
@@ -23404,8 +23451,8 @@
         <v>0</v>
       </c>
       <c r="Q131" s="17"/>
-      <c r="R131" s="163"/>
-      <c r="S131" s="163"/>
+      <c r="R131" s="160"/>
+      <c r="S131" s="160"/>
     </row>
     <row r="132" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A132" s="23" t="s">
@@ -23451,8 +23498,8 @@
         <v>0</v>
       </c>
       <c r="Q132" s="17"/>
-      <c r="R132" s="163"/>
-      <c r="S132" s="163"/>
+      <c r="R132" s="160"/>
+      <c r="S132" s="160"/>
     </row>
     <row r="133" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A133" s="23" t="s">
@@ -23498,8 +23545,8 @@
         <v>0</v>
       </c>
       <c r="Q133" s="17"/>
-      <c r="R133" s="163"/>
-      <c r="S133" s="163"/>
+      <c r="R133" s="160"/>
+      <c r="S133" s="160"/>
     </row>
     <row r="134" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A134" s="23" t="s">
@@ -23545,8 +23592,8 @@
         <v>0</v>
       </c>
       <c r="Q134" s="17"/>
-      <c r="R134" s="163"/>
-      <c r="S134" s="163"/>
+      <c r="R134" s="160"/>
+      <c r="S134" s="160"/>
     </row>
     <row r="135" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A135" s="23" t="s">
@@ -23592,8 +23639,8 @@
         <v>0</v>
       </c>
       <c r="Q135" s="17"/>
-      <c r="R135" s="163"/>
-      <c r="S135" s="163"/>
+      <c r="R135" s="160"/>
+      <c r="S135" s="160"/>
     </row>
     <row r="136" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A136" s="23" t="s">
@@ -23639,8 +23686,8 @@
         <v>0</v>
       </c>
       <c r="Q136" s="17"/>
-      <c r="R136" s="163"/>
-      <c r="S136" s="163"/>
+      <c r="R136" s="160"/>
+      <c r="S136" s="160"/>
     </row>
     <row r="137" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A137" s="23" t="s">
@@ -23686,8 +23733,8 @@
         <v>0</v>
       </c>
       <c r="Q137" s="17"/>
-      <c r="R137" s="163"/>
-      <c r="S137" s="163"/>
+      <c r="R137" s="160"/>
+      <c r="S137" s="160"/>
     </row>
     <row r="138" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A138" s="23" t="s">
@@ -23733,8 +23780,8 @@
         <v>0</v>
       </c>
       <c r="Q138" s="17"/>
-      <c r="R138" s="163"/>
-      <c r="S138" s="163"/>
+      <c r="R138" s="160"/>
+      <c r="S138" s="160"/>
     </row>
     <row r="139" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A139" s="23" t="s">
@@ -23780,8 +23827,8 @@
         <v>0</v>
       </c>
       <c r="Q139" s="17"/>
-      <c r="R139" s="163"/>
-      <c r="S139" s="163"/>
+      <c r="R139" s="160"/>
+      <c r="S139" s="160"/>
     </row>
     <row r="140" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A140" s="23" t="s">
@@ -23827,8 +23874,8 @@
         <v>0</v>
       </c>
       <c r="Q140" s="17"/>
-      <c r="R140" s="163"/>
-      <c r="S140" s="163"/>
+      <c r="R140" s="160"/>
+      <c r="S140" s="160"/>
     </row>
     <row r="141" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A141" s="23" t="s">
@@ -23874,8 +23921,8 @@
         <v>0</v>
       </c>
       <c r="Q141" s="17"/>
-      <c r="R141" s="163"/>
-      <c r="S141" s="163"/>
+      <c r="R141" s="160"/>
+      <c r="S141" s="160"/>
     </row>
     <row r="142" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A142" s="23" t="s">
@@ -23921,8 +23968,8 @@
         <v>0</v>
       </c>
       <c r="Q142" s="17"/>
-      <c r="R142" s="163"/>
-      <c r="S142" s="163"/>
+      <c r="R142" s="160"/>
+      <c r="S142" s="160"/>
     </row>
     <row r="143" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A143" s="23" t="s">
@@ -23968,8 +24015,8 @@
         <v>0</v>
       </c>
       <c r="Q143" s="17"/>
-      <c r="R143" s="163"/>
-      <c r="S143" s="163"/>
+      <c r="R143" s="160"/>
+      <c r="S143" s="160"/>
     </row>
     <row r="144" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A144" s="23" t="s">
@@ -24015,8 +24062,8 @@
         <v>0</v>
       </c>
       <c r="Q144" s="17"/>
-      <c r="R144" s="163"/>
-      <c r="S144" s="163"/>
+      <c r="R144" s="160"/>
+      <c r="S144" s="160"/>
     </row>
     <row r="145" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A145" s="23" t="s">
@@ -24062,8 +24109,8 @@
         <v>0</v>
       </c>
       <c r="Q145" s="17"/>
-      <c r="R145" s="163"/>
-      <c r="S145" s="163"/>
+      <c r="R145" s="160"/>
+      <c r="S145" s="160"/>
     </row>
     <row r="146" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A146" s="23" t="s">
@@ -24109,8 +24156,8 @@
         <v>0</v>
       </c>
       <c r="Q146" s="17"/>
-      <c r="R146" s="163"/>
-      <c r="S146" s="163"/>
+      <c r="R146" s="160"/>
+      <c r="S146" s="160"/>
     </row>
     <row r="147" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A147" s="23" t="s">
@@ -24156,8 +24203,8 @@
         <v>0</v>
       </c>
       <c r="Q147" s="17"/>
-      <c r="R147" s="163"/>
-      <c r="S147" s="163"/>
+      <c r="R147" s="160"/>
+      <c r="S147" s="160"/>
     </row>
     <row r="148" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A148" s="23" t="s">
@@ -24203,8 +24250,8 @@
         <v>0</v>
       </c>
       <c r="Q148" s="17"/>
-      <c r="R148" s="163"/>
-      <c r="S148" s="163"/>
+      <c r="R148" s="160"/>
+      <c r="S148" s="160"/>
     </row>
     <row r="149" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A149" s="23" t="s">
@@ -24250,8 +24297,8 @@
         <v>0</v>
       </c>
       <c r="Q149" s="17"/>
-      <c r="R149" s="163"/>
-      <c r="S149" s="163"/>
+      <c r="R149" s="160"/>
+      <c r="S149" s="160"/>
     </row>
     <row r="150" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A150" s="23" t="s">
@@ -24297,8 +24344,8 @@
         <v>0</v>
       </c>
       <c r="Q150" s="17"/>
-      <c r="R150" s="163"/>
-      <c r="S150" s="163"/>
+      <c r="R150" s="160"/>
+      <c r="S150" s="160"/>
     </row>
     <row r="151" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A151" s="23" t="s">
@@ -24344,8 +24391,8 @@
         <v>0</v>
       </c>
       <c r="Q151" s="17"/>
-      <c r="R151" s="163"/>
-      <c r="S151" s="163"/>
+      <c r="R151" s="160"/>
+      <c r="S151" s="160"/>
     </row>
     <row r="152" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A152" s="23" t="s">
@@ -24391,8 +24438,8 @@
         <v>0</v>
       </c>
       <c r="Q152" s="17"/>
-      <c r="R152" s="163"/>
-      <c r="S152" s="163"/>
+      <c r="R152" s="160"/>
+      <c r="S152" s="160"/>
     </row>
     <row r="153" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A153" s="23" t="s">
@@ -24438,8 +24485,8 @@
         <v>0</v>
       </c>
       <c r="Q153" s="17"/>
-      <c r="R153" s="163"/>
-      <c r="S153" s="163"/>
+      <c r="R153" s="160"/>
+      <c r="S153" s="160"/>
     </row>
     <row r="154" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A154" s="23" t="s">
@@ -24485,8 +24532,8 @@
         <v>0</v>
       </c>
       <c r="Q154" s="17"/>
-      <c r="R154" s="163"/>
-      <c r="S154" s="163"/>
+      <c r="R154" s="160"/>
+      <c r="S154" s="160"/>
     </row>
     <row r="155" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A155" s="23" t="s">
@@ -24532,8 +24579,8 @@
         <v>0</v>
       </c>
       <c r="Q155" s="17"/>
-      <c r="R155" s="163"/>
-      <c r="S155" s="163"/>
+      <c r="R155" s="160"/>
+      <c r="S155" s="160"/>
     </row>
     <row r="156" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A156" s="23" t="s">
@@ -24579,8 +24626,8 @@
         <v>0</v>
       </c>
       <c r="Q156" s="17"/>
-      <c r="R156" s="163"/>
-      <c r="S156" s="163"/>
+      <c r="R156" s="160"/>
+      <c r="S156" s="160"/>
     </row>
     <row r="157" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A157" s="23" t="s">
@@ -24626,8 +24673,8 @@
         <v>0</v>
       </c>
       <c r="Q157" s="17"/>
-      <c r="R157" s="163"/>
-      <c r="S157" s="163"/>
+      <c r="R157" s="160"/>
+      <c r="S157" s="160"/>
     </row>
     <row r="158" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A158" s="23" t="s">
@@ -24673,8 +24720,8 @@
         <v>0</v>
       </c>
       <c r="Q158" s="17"/>
-      <c r="R158" s="163"/>
-      <c r="S158" s="163"/>
+      <c r="R158" s="160"/>
+      <c r="S158" s="160"/>
     </row>
     <row r="159" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A159" s="23" t="s">
@@ -24720,8 +24767,8 @@
         <v>0</v>
       </c>
       <c r="Q159" s="17"/>
-      <c r="R159" s="163"/>
-      <c r="S159" s="163"/>
+      <c r="R159" s="160"/>
+      <c r="S159" s="160"/>
     </row>
     <row r="160" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A160" s="23" t="s">
@@ -24767,8 +24814,8 @@
         <v>0</v>
       </c>
       <c r="Q160" s="17"/>
-      <c r="R160" s="163"/>
-      <c r="S160" s="163"/>
+      <c r="R160" s="160"/>
+      <c r="S160" s="160"/>
     </row>
     <row r="161" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A161" s="23" t="s">
@@ -24814,8 +24861,8 @@
         <v>0</v>
       </c>
       <c r="Q161" s="17"/>
-      <c r="R161" s="163"/>
-      <c r="S161" s="163"/>
+      <c r="R161" s="160"/>
+      <c r="S161" s="160"/>
     </row>
     <row r="162" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A162" s="23" t="s">
@@ -24861,8 +24908,8 @@
         <v>0</v>
       </c>
       <c r="Q162" s="17"/>
-      <c r="R162" s="163"/>
-      <c r="S162" s="163"/>
+      <c r="R162" s="160"/>
+      <c r="S162" s="160"/>
     </row>
     <row r="163" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A163" s="23" t="s">
@@ -24908,8 +24955,8 @@
         <v>0</v>
       </c>
       <c r="Q163" s="17"/>
-      <c r="R163" s="163"/>
-      <c r="S163" s="163"/>
+      <c r="R163" s="160"/>
+      <c r="S163" s="160"/>
     </row>
     <row r="164" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A164" s="23" t="s">
@@ -24955,8 +25002,8 @@
         <v>0</v>
       </c>
       <c r="Q164" s="17"/>
-      <c r="R164" s="163"/>
-      <c r="S164" s="163"/>
+      <c r="R164" s="160"/>
+      <c r="S164" s="160"/>
     </row>
     <row r="165" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A165" s="23" t="s">
@@ -25002,8 +25049,8 @@
         <v>0</v>
       </c>
       <c r="Q165" s="17"/>
-      <c r="R165" s="163"/>
-      <c r="S165" s="163"/>
+      <c r="R165" s="160"/>
+      <c r="S165" s="160"/>
     </row>
     <row r="166" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A166" s="23" t="s">
@@ -25049,8 +25096,8 @@
         <v>0</v>
       </c>
       <c r="Q166" s="17"/>
-      <c r="R166" s="163"/>
-      <c r="S166" s="163"/>
+      <c r="R166" s="160"/>
+      <c r="S166" s="160"/>
     </row>
     <row r="167" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A167" s="23" t="s">
@@ -25096,8 +25143,8 @@
         <v>0</v>
       </c>
       <c r="Q167" s="17"/>
-      <c r="R167" s="163"/>
-      <c r="S167" s="163"/>
+      <c r="R167" s="160"/>
+      <c r="S167" s="160"/>
     </row>
     <row r="168" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A168" s="23" t="s">
@@ -25143,8 +25190,8 @@
         <v>0</v>
       </c>
       <c r="Q168" s="17"/>
-      <c r="R168" s="163"/>
-      <c r="S168" s="163"/>
+      <c r="R168" s="160"/>
+      <c r="S168" s="160"/>
     </row>
     <row r="169" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A169" s="23" t="s">
@@ -25190,8 +25237,8 @@
         <v>0</v>
       </c>
       <c r="Q169" s="17"/>
-      <c r="R169" s="163"/>
-      <c r="S169" s="163"/>
+      <c r="R169" s="160"/>
+      <c r="S169" s="160"/>
     </row>
     <row r="170" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A170" s="23" t="s">
@@ -25237,8 +25284,8 @@
         <v>0</v>
       </c>
       <c r="Q170" s="17"/>
-      <c r="R170" s="163"/>
-      <c r="S170" s="163"/>
+      <c r="R170" s="160"/>
+      <c r="S170" s="160"/>
     </row>
     <row r="171" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A171" s="23" t="s">
@@ -25284,8 +25331,8 @@
         <v>0</v>
       </c>
       <c r="Q171" s="17"/>
-      <c r="R171" s="163"/>
-      <c r="S171" s="163"/>
+      <c r="R171" s="160"/>
+      <c r="S171" s="160"/>
     </row>
     <row r="172" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A172" s="23" t="s">
@@ -25331,8 +25378,8 @@
         <v>0</v>
       </c>
       <c r="Q172" s="17"/>
-      <c r="R172" s="163"/>
-      <c r="S172" s="163"/>
+      <c r="R172" s="160"/>
+      <c r="S172" s="160"/>
     </row>
     <row r="173" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A173" s="23" t="s">
@@ -25378,8 +25425,8 @@
         <v>0</v>
       </c>
       <c r="Q173" s="17"/>
-      <c r="R173" s="163"/>
-      <c r="S173" s="163"/>
+      <c r="R173" s="160"/>
+      <c r="S173" s="160"/>
     </row>
     <row r="174" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A174" s="23" t="s">
@@ -25425,8 +25472,8 @@
         <v>0</v>
       </c>
       <c r="Q174" s="17"/>
-      <c r="R174" s="163"/>
-      <c r="S174" s="163"/>
+      <c r="R174" s="160"/>
+      <c r="S174" s="160"/>
     </row>
     <row r="175" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A175" s="23" t="s">
@@ -25478,8 +25525,8 @@
         <v>0</v>
       </c>
       <c r="Q175" s="17"/>
-      <c r="R175" s="163"/>
-      <c r="S175" s="163"/>
+      <c r="R175" s="160"/>
+      <c r="S175" s="160"/>
     </row>
     <row r="176" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A176" s="23" t="s">
@@ -25531,8 +25578,8 @@
         <v>0</v>
       </c>
       <c r="Q176" s="17"/>
-      <c r="R176" s="163"/>
-      <c r="S176" s="163"/>
+      <c r="R176" s="160"/>
+      <c r="S176" s="160"/>
     </row>
     <row r="177" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A177" s="23" t="s">
@@ -25584,8 +25631,8 @@
         <v>0</v>
       </c>
       <c r="Q177" s="17"/>
-      <c r="R177" s="163"/>
-      <c r="S177" s="163"/>
+      <c r="R177" s="160"/>
+      <c r="S177" s="160"/>
     </row>
     <row r="178" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A178" s="23" t="s">
@@ -25637,8 +25684,8 @@
         <v>0</v>
       </c>
       <c r="Q178" s="17"/>
-      <c r="R178" s="163"/>
-      <c r="S178" s="163"/>
+      <c r="R178" s="160"/>
+      <c r="S178" s="160"/>
     </row>
     <row r="179" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A179" s="23" t="s">
@@ -25690,8 +25737,8 @@
         <v>0</v>
       </c>
       <c r="Q179" s="17"/>
-      <c r="R179" s="163"/>
-      <c r="S179" s="163"/>
+      <c r="R179" s="160"/>
+      <c r="S179" s="160"/>
     </row>
     <row r="180" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A180" s="23" t="s">
@@ -25743,8 +25790,8 @@
         <v>0</v>
       </c>
       <c r="Q180" s="17"/>
-      <c r="R180" s="163"/>
-      <c r="S180" s="163"/>
+      <c r="R180" s="160"/>
+      <c r="S180" s="160"/>
     </row>
     <row r="181" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A181" s="23" t="s">
@@ -25796,8 +25843,8 @@
         <v>0</v>
       </c>
       <c r="Q181" s="17"/>
-      <c r="R181" s="163"/>
-      <c r="S181" s="163"/>
+      <c r="R181" s="160"/>
+      <c r="S181" s="160"/>
     </row>
     <row r="182" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A182" s="23" t="s">
@@ -25843,8 +25890,8 @@
         <v>0</v>
       </c>
       <c r="Q182" s="17"/>
-      <c r="R182" s="163"/>
-      <c r="S182" s="163"/>
+      <c r="R182" s="160"/>
+      <c r="S182" s="160"/>
     </row>
     <row r="183" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A183" s="23" t="s">
@@ -25890,8 +25937,8 @@
         <v>0</v>
       </c>
       <c r="Q183" s="17"/>
-      <c r="R183" s="163"/>
-      <c r="S183" s="163"/>
+      <c r="R183" s="160"/>
+      <c r="S183" s="160"/>
     </row>
     <row r="184" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A184" s="23" t="s">
@@ -25943,8 +25990,8 @@
         <v>0</v>
       </c>
       <c r="Q184" s="17"/>
-      <c r="R184" s="163"/>
-      <c r="S184" s="163"/>
+      <c r="R184" s="160"/>
+      <c r="S184" s="160"/>
     </row>
     <row r="185" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A185" s="23" t="s">
@@ -25996,8 +26043,8 @@
         <v>0</v>
       </c>
       <c r="Q185" s="17"/>
-      <c r="R185" s="163"/>
-      <c r="S185" s="163"/>
+      <c r="R185" s="160"/>
+      <c r="S185" s="160"/>
     </row>
     <row r="186" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A186" s="23" t="s">
@@ -26049,8 +26096,8 @@
         <v>0</v>
       </c>
       <c r="Q186" s="17"/>
-      <c r="R186" s="163"/>
-      <c r="S186" s="163"/>
+      <c r="R186" s="160"/>
+      <c r="S186" s="160"/>
     </row>
     <row r="187" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A187" s="23" t="s">
@@ -26102,8 +26149,8 @@
         <v>0</v>
       </c>
       <c r="Q187" s="17"/>
-      <c r="R187" s="163"/>
-      <c r="S187" s="163"/>
+      <c r="R187" s="160"/>
+      <c r="S187" s="160"/>
     </row>
     <row r="188" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A188" s="23" t="s">
@@ -26155,8 +26202,8 @@
         <v>0</v>
       </c>
       <c r="Q188" s="17"/>
-      <c r="R188" s="163"/>
-      <c r="S188" s="163"/>
+      <c r="R188" s="160"/>
+      <c r="S188" s="160"/>
     </row>
     <row r="189" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A189" s="23" t="s">
@@ -26208,8 +26255,8 @@
         <v>0</v>
       </c>
       <c r="Q189" s="17"/>
-      <c r="R189" s="163"/>
-      <c r="S189" s="163"/>
+      <c r="R189" s="160"/>
+      <c r="S189" s="160"/>
     </row>
     <row r="190" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A190" s="23" t="s">
@@ -26261,8 +26308,8 @@
         <v>0</v>
       </c>
       <c r="Q190" s="17"/>
-      <c r="R190" s="163"/>
-      <c r="S190" s="163"/>
+      <c r="R190" s="160"/>
+      <c r="S190" s="160"/>
     </row>
     <row r="191" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A191" s="23" t="s">
@@ -26314,8 +26361,8 @@
         <v>0</v>
       </c>
       <c r="Q191" s="17"/>
-      <c r="R191" s="163"/>
-      <c r="S191" s="163"/>
+      <c r="R191" s="160"/>
+      <c r="S191" s="160"/>
     </row>
     <row r="192" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
@@ -26367,8 +26414,8 @@
         <v>0</v>
       </c>
       <c r="Q192" s="17"/>
-      <c r="R192" s="163"/>
-      <c r="S192" s="163"/>
+      <c r="R192" s="160"/>
+      <c r="S192" s="160"/>
     </row>
     <row r="193" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
@@ -26420,8 +26467,8 @@
         <v>0</v>
       </c>
       <c r="Q193" s="17"/>
-      <c r="R193" s="163"/>
-      <c r="S193" s="163"/>
+      <c r="R193" s="160"/>
+      <c r="S193" s="160"/>
     </row>
     <row r="204" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="Q204" s="57">
@@ -36486,34 +36533,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="164" t="s">
         <v>1170</v>
       </c>
-      <c r="B1" s="160" t="s">
+      <c r="B1" s="164" t="s">
         <v>1171</v>
       </c>
-      <c r="C1" s="160" t="s">
+      <c r="C1" s="164" t="s">
         <v>1172</v>
       </c>
-      <c r="D1" s="161" t="s">
+      <c r="D1" s="165" t="s">
         <v>1173</v>
       </c>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="161" t="s">
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165" t="s">
         <v>1174</v>
       </c>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
       <c r="J1" s="108"/>
       <c r="K1" s="109" t="s">
         <v>1175</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A2" s="160"/>
-      <c r="B2" s="160"/>
-      <c r="C2" s="160"/>
+      <c r="A2" s="164"/>
+      <c r="B2" s="164"/>
+      <c r="C2" s="164"/>
       <c r="D2" s="107" t="s">
         <v>1176</v>
       </c>
@@ -39033,19 +39080,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="164" t="s">
         <v>1197</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
+      <c r="B1" s="164"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="164"/>
+      <c r="H1" s="164"/>
+      <c r="I1" s="164"/>
+      <c r="J1" s="164"/>
+      <c r="K1" s="164"/>
     </row>
     <row r="2" spans="1:11" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A2" s="134" t="s">
@@ -39778,16 +39825,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="164" t="s">
         <v>1198</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
+      <c r="B1" s="164"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="164"/>
+      <c r="H1" s="164"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="150" t="s">

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3032" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F874E045-42FB-441D-999D-153DF8B6F201}"/>
+  <xr:revisionPtr revIDLastSave="3070" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F6E5F56-803A-4B07-B7EB-19DD52C84E86}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="-8550" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="-8550" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FS Elec" sheetId="4" r:id="rId1"/>
@@ -4819,9 +4819,6 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4839,6 +4836,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5542,8 +5542,8 @@
       <c r="R2" s="65">
         <v>46301</v>
       </c>
-      <c r="S2" s="160"/>
-      <c r="T2" s="160"/>
+      <c r="S2" s="159"/>
+      <c r="T2" s="159"/>
     </row>
     <row r="3" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -5600,8 +5600,8 @@
       <c r="R3" s="65">
         <v>46301</v>
       </c>
-      <c r="S3" s="160"/>
-      <c r="T3" s="160"/>
+      <c r="S3" s="159"/>
+      <c r="T3" s="159"/>
     </row>
     <row r="4" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
@@ -5658,8 +5658,8 @@
       <c r="R4" s="65">
         <v>46240</v>
       </c>
-      <c r="S4" s="160"/>
-      <c r="T4" s="160"/>
+      <c r="S4" s="159"/>
+      <c r="T4" s="159"/>
     </row>
     <row r="5" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
@@ -5716,8 +5716,8 @@
       <c r="R5" s="65">
         <v>46301</v>
       </c>
-      <c r="S5" s="160"/>
-      <c r="T5" s="160"/>
+      <c r="S5" s="159"/>
+      <c r="T5" s="159"/>
     </row>
     <row r="6" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
@@ -5774,8 +5774,8 @@
       <c r="R6" s="65">
         <v>46240</v>
       </c>
-      <c r="S6" s="160"/>
-      <c r="T6" s="160"/>
+      <c r="S6" s="159"/>
+      <c r="T6" s="159"/>
     </row>
     <row r="7" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
@@ -5832,8 +5832,8 @@
       <c r="R7" s="65">
         <v>46301</v>
       </c>
-      <c r="S7" s="160"/>
-      <c r="T7" s="160"/>
+      <c r="S7" s="159"/>
+      <c r="T7" s="159"/>
     </row>
     <row r="8" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
@@ -5890,8 +5890,8 @@
       <c r="R8" s="65">
         <v>46240</v>
       </c>
-      <c r="S8" s="160"/>
-      <c r="T8" s="160"/>
+      <c r="S8" s="159"/>
+      <c r="T8" s="159"/>
     </row>
     <row r="9" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
@@ -5948,8 +5948,8 @@
       <c r="R9" s="65">
         <v>46301</v>
       </c>
-      <c r="S9" s="160"/>
-      <c r="T9" s="160"/>
+      <c r="S9" s="159"/>
+      <c r="T9" s="159"/>
     </row>
     <row r="10" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
@@ -6006,8 +6006,8 @@
       <c r="R10" s="65">
         <v>46240</v>
       </c>
-      <c r="S10" s="160"/>
-      <c r="T10" s="160"/>
+      <c r="S10" s="159"/>
+      <c r="T10" s="159"/>
     </row>
     <row r="11" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
@@ -6064,8 +6064,8 @@
       <c r="R11" s="65">
         <v>46301</v>
       </c>
-      <c r="S11" s="160"/>
-      <c r="T11" s="160"/>
+      <c r="S11" s="159"/>
+      <c r="T11" s="159"/>
     </row>
     <row r="12" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
@@ -6122,8 +6122,8 @@
       <c r="R12" s="65">
         <v>46240</v>
       </c>
-      <c r="S12" s="160"/>
-      <c r="T12" s="160"/>
+      <c r="S12" s="159"/>
+      <c r="T12" s="159"/>
     </row>
     <row r="13" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
@@ -6180,8 +6180,8 @@
       <c r="R13" s="65">
         <v>46301</v>
       </c>
-      <c r="S13" s="160"/>
-      <c r="T13" s="160"/>
+      <c r="S13" s="159"/>
+      <c r="T13" s="159"/>
     </row>
     <row r="14" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
@@ -6238,8 +6238,8 @@
       <c r="R14" s="65">
         <v>46240</v>
       </c>
-      <c r="S14" s="160"/>
-      <c r="T14" s="160"/>
+      <c r="S14" s="159"/>
+      <c r="T14" s="159"/>
     </row>
     <row r="15" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
@@ -6296,8 +6296,8 @@
       <c r="R15" s="65">
         <v>46301</v>
       </c>
-      <c r="S15" s="160"/>
-      <c r="T15" s="160"/>
+      <c r="S15" s="159"/>
+      <c r="T15" s="159"/>
     </row>
     <row r="16" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
@@ -6354,8 +6354,8 @@
       <c r="R16" s="65">
         <v>46240</v>
       </c>
-      <c r="S16" s="160"/>
-      <c r="T16" s="160"/>
+      <c r="S16" s="159"/>
+      <c r="T16" s="159"/>
     </row>
     <row r="17" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
@@ -6412,8 +6412,8 @@
       <c r="R17" s="65">
         <v>46301</v>
       </c>
-      <c r="S17" s="160"/>
-      <c r="T17" s="160"/>
+      <c r="S17" s="159"/>
+      <c r="T17" s="159"/>
     </row>
     <row r="18" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
@@ -6470,8 +6470,8 @@
       <c r="R18" s="65">
         <v>46224</v>
       </c>
-      <c r="S18" s="160"/>
-      <c r="T18" s="160"/>
+      <c r="S18" s="159"/>
+      <c r="T18" s="159"/>
     </row>
     <row r="19" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
@@ -6528,8 +6528,8 @@
       <c r="R19" s="65">
         <v>46301</v>
       </c>
-      <c r="S19" s="160"/>
-      <c r="T19" s="160"/>
+      <c r="S19" s="159"/>
+      <c r="T19" s="159"/>
     </row>
     <row r="20" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
@@ -6586,8 +6586,8 @@
       <c r="R20" s="65">
         <v>46224</v>
       </c>
-      <c r="S20" s="160"/>
-      <c r="T20" s="160"/>
+      <c r="S20" s="159"/>
+      <c r="T20" s="159"/>
     </row>
     <row r="21" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
@@ -6644,8 +6644,8 @@
       <c r="R21" s="65">
         <v>46286</v>
       </c>
-      <c r="S21" s="160"/>
-      <c r="T21" s="160"/>
+      <c r="S21" s="159"/>
+      <c r="T21" s="159"/>
     </row>
     <row r="22" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
@@ -6702,8 +6702,8 @@
       <c r="R22" s="65">
         <v>46224</v>
       </c>
-      <c r="S22" s="160"/>
-      <c r="T22" s="160"/>
+      <c r="S22" s="159"/>
+      <c r="T22" s="159"/>
     </row>
     <row r="23" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
@@ -6760,8 +6760,8 @@
       <c r="R23" s="65">
         <v>46286</v>
       </c>
-      <c r="S23" s="160"/>
-      <c r="T23" s="160"/>
+      <c r="S23" s="159"/>
+      <c r="T23" s="159"/>
     </row>
     <row r="24" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
@@ -6770,7 +6770,7 @@
       <c r="B24" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="159">
+      <c r="C24" s="165">
         <v>14558068921</v>
       </c>
       <c r="D24" s="2">
@@ -6818,8 +6818,8 @@
       <c r="R24" s="65">
         <v>46224</v>
       </c>
-      <c r="S24" s="160"/>
-      <c r="T24" s="160"/>
+      <c r="S24" s="159"/>
+      <c r="T24" s="159"/>
     </row>
     <row r="25" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
@@ -6876,8 +6876,8 @@
       <c r="R25" s="65">
         <v>46286</v>
       </c>
-      <c r="S25" s="160"/>
-      <c r="T25" s="160"/>
+      <c r="S25" s="159"/>
+      <c r="T25" s="159"/>
     </row>
     <row r="26" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
@@ -6934,8 +6934,8 @@
       <c r="R26" s="65">
         <v>46224</v>
       </c>
-      <c r="S26" s="160"/>
-      <c r="T26" s="160"/>
+      <c r="S26" s="159"/>
+      <c r="T26" s="159"/>
     </row>
     <row r="27" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
@@ -6992,8 +6992,8 @@
       <c r="R27" s="65">
         <v>46286</v>
       </c>
-      <c r="S27" s="160"/>
-      <c r="T27" s="160"/>
+      <c r="S27" s="159"/>
+      <c r="T27" s="159"/>
     </row>
     <row r="28" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
@@ -7050,8 +7050,8 @@
       <c r="R28" s="65">
         <v>46224</v>
       </c>
-      <c r="S28" s="160"/>
-      <c r="T28" s="160"/>
+      <c r="S28" s="159"/>
+      <c r="T28" s="159"/>
     </row>
     <row r="29" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
@@ -7108,8 +7108,8 @@
       <c r="R29" s="65">
         <v>46286</v>
       </c>
-      <c r="S29" s="160"/>
-      <c r="T29" s="160"/>
+      <c r="S29" s="159"/>
+      <c r="T29" s="159"/>
     </row>
     <row r="30" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
@@ -7166,8 +7166,8 @@
       <c r="R30" s="65">
         <v>46224</v>
       </c>
-      <c r="S30" s="160"/>
-      <c r="T30" s="160"/>
+      <c r="S30" s="159"/>
+      <c r="T30" s="159"/>
     </row>
     <row r="31" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
@@ -7224,8 +7224,8 @@
       <c r="R31" s="65">
         <v>46286</v>
       </c>
-      <c r="S31" s="160"/>
-      <c r="T31" s="160"/>
+      <c r="S31" s="159"/>
+      <c r="T31" s="159"/>
     </row>
     <row r="32" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
@@ -7282,8 +7282,8 @@
       <c r="R32" s="65">
         <v>46224</v>
       </c>
-      <c r="S32" s="160"/>
-      <c r="T32" s="160"/>
+      <c r="S32" s="159"/>
+      <c r="T32" s="159"/>
     </row>
     <row r="33" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
@@ -7340,8 +7340,8 @@
       <c r="R33" s="65">
         <v>46286</v>
       </c>
-      <c r="S33" s="160"/>
-      <c r="T33" s="160"/>
+      <c r="S33" s="159"/>
+      <c r="T33" s="159"/>
     </row>
     <row r="34" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
@@ -7398,8 +7398,8 @@
       <c r="R34" s="65">
         <v>46286</v>
       </c>
-      <c r="S34" s="160"/>
-      <c r="T34" s="160"/>
+      <c r="S34" s="159"/>
+      <c r="T34" s="159"/>
     </row>
     <row r="35" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
@@ -7454,8 +7454,8 @@
       <c r="R35" s="65">
         <v>46221</v>
       </c>
-      <c r="S35" s="160"/>
-      <c r="T35" s="160"/>
+      <c r="S35" s="159"/>
+      <c r="T35" s="159"/>
     </row>
     <row r="36" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
@@ -7510,8 +7510,8 @@
       <c r="R36" s="65">
         <v>46207</v>
       </c>
-      <c r="S36" s="160"/>
-      <c r="T36" s="160"/>
+      <c r="S36" s="159"/>
+      <c r="T36" s="159"/>
     </row>
     <row r="37" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
@@ -7566,8 +7566,8 @@
       <c r="R37" s="65">
         <v>46221</v>
       </c>
-      <c r="S37" s="160"/>
-      <c r="T37" s="160"/>
+      <c r="S37" s="159"/>
+      <c r="T37" s="159"/>
     </row>
     <row r="38" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
@@ -7622,8 +7622,8 @@
       <c r="R38" s="65">
         <v>46207</v>
       </c>
-      <c r="S38" s="160"/>
-      <c r="T38" s="160"/>
+      <c r="S38" s="159"/>
+      <c r="T38" s="159"/>
     </row>
     <row r="39" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
@@ -7678,8 +7678,8 @@
       <c r="R39" s="65">
         <v>46221</v>
       </c>
-      <c r="S39" s="160"/>
-      <c r="T39" s="160"/>
+      <c r="S39" s="159"/>
+      <c r="T39" s="159"/>
     </row>
     <row r="40" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
@@ -7734,8 +7734,8 @@
       <c r="R40" s="65">
         <v>46207</v>
       </c>
-      <c r="S40" s="160"/>
-      <c r="T40" s="160"/>
+      <c r="S40" s="159"/>
+      <c r="T40" s="159"/>
     </row>
     <row r="41" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
@@ -7790,8 +7790,8 @@
       <c r="R41" s="65">
         <v>46221</v>
       </c>
-      <c r="S41" s="160"/>
-      <c r="T41" s="160"/>
+      <c r="S41" s="159"/>
+      <c r="T41" s="159"/>
     </row>
     <row r="42" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
@@ -7846,8 +7846,8 @@
       <c r="R42" s="65">
         <v>46207</v>
       </c>
-      <c r="S42" s="160"/>
-      <c r="T42" s="160"/>
+      <c r="S42" s="159"/>
+      <c r="T42" s="159"/>
     </row>
     <row r="43" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
@@ -7902,8 +7902,8 @@
       <c r="R43" s="65">
         <v>46221</v>
       </c>
-      <c r="S43" s="160"/>
-      <c r="T43" s="160"/>
+      <c r="S43" s="159"/>
+      <c r="T43" s="159"/>
     </row>
     <row r="44" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
@@ -7958,8 +7958,8 @@
       <c r="R44" s="65">
         <v>46207</v>
       </c>
-      <c r="S44" s="160"/>
-      <c r="T44" s="160"/>
+      <c r="S44" s="159"/>
+      <c r="T44" s="159"/>
     </row>
     <row r="45" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
@@ -8014,8 +8014,8 @@
       <c r="R45" s="65">
         <v>46221</v>
       </c>
-      <c r="S45" s="160"/>
-      <c r="T45" s="160"/>
+      <c r="S45" s="159"/>
+      <c r="T45" s="159"/>
     </row>
     <row r="46" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
@@ -8070,8 +8070,8 @@
       <c r="R46" s="65">
         <v>46195</v>
       </c>
-      <c r="S46" s="160"/>
-      <c r="T46" s="160"/>
+      <c r="S46" s="159"/>
+      <c r="T46" s="159"/>
     </row>
     <row r="47" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
@@ -8126,8 +8126,8 @@
       <c r="R47" s="65">
         <v>46207</v>
       </c>
-      <c r="S47" s="160"/>
-      <c r="T47" s="160"/>
+      <c r="S47" s="159"/>
+      <c r="T47" s="159"/>
     </row>
     <row r="48" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
@@ -8182,8 +8182,8 @@
       <c r="R48" s="65">
         <v>46195</v>
       </c>
-      <c r="S48" s="160"/>
-      <c r="T48" s="160"/>
+      <c r="S48" s="159"/>
+      <c r="T48" s="159"/>
     </row>
     <row r="49" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
@@ -8238,8 +8238,8 @@
       <c r="R49" s="65">
         <v>46207</v>
       </c>
-      <c r="S49" s="160"/>
-      <c r="T49" s="160"/>
+      <c r="S49" s="159"/>
+      <c r="T49" s="159"/>
     </row>
     <row r="50" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
@@ -8294,8 +8294,8 @@
       <c r="R50" s="65">
         <v>46195</v>
       </c>
-      <c r="S50" s="160"/>
-      <c r="T50" s="160"/>
+      <c r="S50" s="159"/>
+      <c r="T50" s="159"/>
     </row>
     <row r="51" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
@@ -8350,8 +8350,8 @@
       <c r="R51" s="65">
         <v>46207</v>
       </c>
-      <c r="S51" s="160"/>
-      <c r="T51" s="160"/>
+      <c r="S51" s="159"/>
+      <c r="T51" s="159"/>
     </row>
     <row r="52" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
@@ -8406,8 +8406,8 @@
       <c r="R52" s="65">
         <v>46195</v>
       </c>
-      <c r="S52" s="160"/>
-      <c r="T52" s="160"/>
+      <c r="S52" s="159"/>
+      <c r="T52" s="159"/>
     </row>
     <row r="53" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
@@ -8462,8 +8462,8 @@
       <c r="R53" s="65">
         <v>46207</v>
       </c>
-      <c r="S53" s="160"/>
-      <c r="T53" s="160"/>
+      <c r="S53" s="159"/>
+      <c r="T53" s="159"/>
     </row>
     <row r="54" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
@@ -8518,8 +8518,8 @@
       <c r="R54" s="65">
         <v>46195</v>
       </c>
-      <c r="S54" s="160"/>
-      <c r="T54" s="160"/>
+      <c r="S54" s="159"/>
+      <c r="T54" s="159"/>
     </row>
     <row r="55" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
@@ -8574,8 +8574,8 @@
       <c r="R55" s="65">
         <v>46207</v>
       </c>
-      <c r="S55" s="160"/>
-      <c r="T55" s="160"/>
+      <c r="S55" s="159"/>
+      <c r="T55" s="159"/>
     </row>
     <row r="56" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
@@ -8630,8 +8630,8 @@
       <c r="R56" s="65">
         <v>46195</v>
       </c>
-      <c r="S56" s="160"/>
-      <c r="T56" s="160"/>
+      <c r="S56" s="159"/>
+      <c r="T56" s="159"/>
     </row>
     <row r="57" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
@@ -8686,8 +8686,8 @@
       <c r="R57" s="65">
         <v>46207</v>
       </c>
-      <c r="S57" s="160"/>
-      <c r="T57" s="160"/>
+      <c r="S57" s="159"/>
+      <c r="T57" s="159"/>
     </row>
     <row r="58" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
@@ -8742,8 +8742,8 @@
       <c r="R58" s="65">
         <v>46195</v>
       </c>
-      <c r="S58" s="160"/>
-      <c r="T58" s="160"/>
+      <c r="S58" s="159"/>
+      <c r="T58" s="159"/>
     </row>
     <row r="59" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
@@ -8798,8 +8798,8 @@
       <c r="R59" s="65">
         <v>46207</v>
       </c>
-      <c r="S59" s="160"/>
-      <c r="T59" s="160"/>
+      <c r="S59" s="159"/>
+      <c r="T59" s="159"/>
     </row>
     <row r="60" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
@@ -8854,8 +8854,8 @@
       <c r="R60" s="65">
         <v>46195</v>
       </c>
-      <c r="S60" s="160"/>
-      <c r="T60" s="160"/>
+      <c r="S60" s="159"/>
+      <c r="T60" s="159"/>
     </row>
     <row r="61" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
@@ -8910,8 +8910,8 @@
       <c r="R61" s="65">
         <v>46207</v>
       </c>
-      <c r="S61" s="160"/>
-      <c r="T61" s="160"/>
+      <c r="S61" s="159"/>
+      <c r="T61" s="159"/>
     </row>
     <row r="62" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
@@ -8966,8 +8966,8 @@
       <c r="R62" s="65">
         <v>46179</v>
       </c>
-      <c r="S62" s="160"/>
-      <c r="T62" s="160"/>
+      <c r="S62" s="159"/>
+      <c r="T62" s="159"/>
     </row>
     <row r="63" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A63" s="12" t="s">
@@ -9022,8 +9022,8 @@
       <c r="R63" s="65">
         <v>46195</v>
       </c>
-      <c r="S63" s="160"/>
-      <c r="T63" s="160"/>
+      <c r="S63" s="159"/>
+      <c r="T63" s="159"/>
     </row>
     <row r="64" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A64" s="12" t="s">
@@ -9078,8 +9078,8 @@
       <c r="R64" s="65">
         <v>46179</v>
       </c>
-      <c r="S64" s="160"/>
-      <c r="T64" s="160"/>
+      <c r="S64" s="159"/>
+      <c r="T64" s="159"/>
     </row>
     <row r="65" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A65" s="12" t="s">
@@ -9134,8 +9134,8 @@
       <c r="R65" s="65">
         <v>46195</v>
       </c>
-      <c r="S65" s="160"/>
-      <c r="T65" s="160"/>
+      <c r="S65" s="159"/>
+      <c r="T65" s="159"/>
     </row>
     <row r="66" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
@@ -9190,8 +9190,8 @@
       <c r="R66" s="65">
         <v>46179</v>
       </c>
-      <c r="S66" s="160"/>
-      <c r="T66" s="160"/>
+      <c r="S66" s="159"/>
+      <c r="T66" s="159"/>
     </row>
     <row r="67" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A67" s="12" t="s">
@@ -9246,8 +9246,8 @@
       <c r="R67" s="65">
         <v>46195</v>
       </c>
-      <c r="S67" s="160"/>
-      <c r="T67" s="160"/>
+      <c r="S67" s="159"/>
+      <c r="T67" s="159"/>
     </row>
     <row r="68" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
@@ -9302,8 +9302,8 @@
       <c r="R68" s="65">
         <v>46179</v>
       </c>
-      <c r="S68" s="160"/>
-      <c r="T68" s="160"/>
+      <c r="S68" s="159"/>
+      <c r="T68" s="159"/>
     </row>
     <row r="69" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A69" s="12" t="s">
@@ -9360,8 +9360,8 @@
       <c r="R69" s="65">
         <v>46195</v>
       </c>
-      <c r="S69" s="160"/>
-      <c r="T69" s="160"/>
+      <c r="S69" s="159"/>
+      <c r="T69" s="159"/>
     </row>
     <row r="70" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
@@ -9418,8 +9418,8 @@
       <c r="R70" s="65">
         <v>46179</v>
       </c>
-      <c r="S70" s="160"/>
-      <c r="T70" s="160"/>
+      <c r="S70" s="159"/>
+      <c r="T70" s="159"/>
     </row>
     <row r="71" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A71" s="12" t="s">
@@ -9476,8 +9476,8 @@
       <c r="R71" s="65">
         <v>46195</v>
       </c>
-      <c r="S71" s="160"/>
-      <c r="T71" s="160"/>
+      <c r="S71" s="159"/>
+      <c r="T71" s="159"/>
     </row>
     <row r="72" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
@@ -9534,8 +9534,8 @@
       <c r="R72" s="65">
         <v>46179</v>
       </c>
-      <c r="S72" s="160"/>
-      <c r="T72" s="160"/>
+      <c r="S72" s="159"/>
+      <c r="T72" s="159"/>
     </row>
     <row r="73" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
@@ -9592,8 +9592,8 @@
       <c r="R73" s="65">
         <v>46195</v>
       </c>
-      <c r="S73" s="160"/>
-      <c r="T73" s="160"/>
+      <c r="S73" s="159"/>
+      <c r="T73" s="159"/>
     </row>
     <row r="74" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
@@ -9650,8 +9650,8 @@
       <c r="R74" s="65">
         <v>46179</v>
       </c>
-      <c r="S74" s="160"/>
-      <c r="T74" s="160"/>
+      <c r="S74" s="159"/>
+      <c r="T74" s="159"/>
     </row>
     <row r="75" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
@@ -9708,8 +9708,8 @@
       <c r="R75" s="65">
         <v>46195</v>
       </c>
-      <c r="S75" s="160"/>
-      <c r="T75" s="160"/>
+      <c r="S75" s="159"/>
+      <c r="T75" s="159"/>
     </row>
     <row r="76" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
@@ -9766,8 +9766,8 @@
       <c r="R76" s="65">
         <v>46179</v>
       </c>
-      <c r="S76" s="160"/>
-      <c r="T76" s="160"/>
+      <c r="S76" s="159"/>
+      <c r="T76" s="159"/>
     </row>
     <row r="77" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
@@ -9824,10 +9824,10 @@
       <c r="R77" s="65">
         <v>46217</v>
       </c>
-      <c r="S77" s="163">
+      <c r="S77" s="162">
         <v>46234</v>
       </c>
-      <c r="T77" s="160" t="s">
+      <c r="T77" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -9886,10 +9886,10 @@
       <c r="R78" s="65">
         <v>46217</v>
       </c>
-      <c r="S78" s="163">
+      <c r="S78" s="162">
         <v>46234</v>
       </c>
-      <c r="T78" s="160" t="s">
+      <c r="T78" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -9948,10 +9948,10 @@
       <c r="R79" s="65">
         <v>46217</v>
       </c>
-      <c r="S79" s="163">
+      <c r="S79" s="162">
         <v>46234</v>
       </c>
-      <c r="T79" s="160" t="s">
+      <c r="T79" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10010,10 +10010,10 @@
       <c r="R80" s="65">
         <v>46217</v>
       </c>
-      <c r="S80" s="163">
+      <c r="S80" s="162">
         <v>46234</v>
       </c>
-      <c r="T80" s="160" t="s">
+      <c r="T80" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10070,10 +10070,10 @@
       <c r="R81" s="65">
         <v>46203</v>
       </c>
-      <c r="S81" s="163">
+      <c r="S81" s="162">
         <v>46234</v>
       </c>
-      <c r="T81" s="160" t="s">
+      <c r="T81" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10130,10 +10130,10 @@
       <c r="R82" s="65">
         <v>46203</v>
       </c>
-      <c r="S82" s="163">
+      <c r="S82" s="162">
         <v>46234</v>
       </c>
-      <c r="T82" s="160" t="s">
+      <c r="T82" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10144,7 +10144,7 @@
       <c r="B83" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C83" s="159">
+      <c r="C83" s="165">
         <v>14558069077</v>
       </c>
       <c r="D83" s="2">
@@ -10190,10 +10190,10 @@
       <c r="R83" s="65">
         <v>46203</v>
       </c>
-      <c r="S83" s="163">
+      <c r="S83" s="162">
         <v>46234</v>
       </c>
-      <c r="T83" s="160" t="s">
+      <c r="T83" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10250,10 +10250,10 @@
       <c r="R84" s="65">
         <v>46203</v>
       </c>
-      <c r="S84" s="163">
+      <c r="S84" s="162">
         <v>46234</v>
       </c>
-      <c r="T84" s="160" t="s">
+      <c r="T84" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10310,10 +10310,10 @@
       <c r="R85" s="65">
         <v>46203</v>
       </c>
-      <c r="S85" s="163">
+      <c r="S85" s="162">
         <v>46234</v>
       </c>
-      <c r="T85" s="160" t="s">
+      <c r="T85" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10370,10 +10370,10 @@
       <c r="R86" s="65">
         <v>46203</v>
       </c>
-      <c r="S86" s="163">
+      <c r="S86" s="162">
         <v>46234</v>
       </c>
-      <c r="T86" s="160" t="s">
+      <c r="T86" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10430,10 +10430,10 @@
       <c r="R87" s="65">
         <v>46203</v>
       </c>
-      <c r="S87" s="163">
+      <c r="S87" s="162">
         <v>46234</v>
       </c>
-      <c r="T87" s="160" t="s">
+      <c r="T87" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10490,10 +10490,10 @@
       <c r="R88" s="65">
         <v>46182</v>
       </c>
-      <c r="S88" s="163">
+      <c r="S88" s="162">
         <v>46234</v>
       </c>
-      <c r="T88" s="160" t="s">
+      <c r="T88" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10550,10 +10550,10 @@
       <c r="R89" s="65">
         <v>46182</v>
       </c>
-      <c r="S89" s="163">
+      <c r="S89" s="162">
         <v>46234</v>
       </c>
-      <c r="T89" s="160" t="s">
+      <c r="T89" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10612,10 +10612,10 @@
       <c r="R90" s="65">
         <v>46182</v>
       </c>
-      <c r="S90" s="163">
+      <c r="S90" s="162">
         <v>46234</v>
       </c>
-      <c r="T90" s="160" t="s">
+      <c r="T90" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10674,10 +10674,10 @@
       <c r="R91" s="65">
         <v>46182</v>
       </c>
-      <c r="S91" s="163">
+      <c r="S91" s="162">
         <v>46234</v>
       </c>
-      <c r="T91" s="160" t="s">
+      <c r="T91" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10736,10 +10736,10 @@
       <c r="R92" s="65">
         <v>46182</v>
       </c>
-      <c r="S92" s="163">
+      <c r="S92" s="162">
         <v>46234</v>
       </c>
-      <c r="T92" s="160" t="s">
+      <c r="T92" s="159" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -10798,10 +10798,10 @@
       <c r="R93" s="65">
         <v>46168</v>
       </c>
-      <c r="S93" s="163">
+      <c r="S93" s="162">
         <v>46204.919444444444</v>
       </c>
-      <c r="T93" s="160">
+      <c r="T93" s="159">
         <v>76.2</v>
       </c>
     </row>
@@ -10860,10 +10860,10 @@
       <c r="R94" s="65">
         <v>46163</v>
       </c>
-      <c r="S94" s="161">
+      <c r="S94" s="160">
         <v>46204.657638888886</v>
       </c>
-      <c r="T94" s="162">
+      <c r="T94" s="161">
         <v>31.8</v>
       </c>
     </row>
@@ -10922,10 +10922,10 @@
       <c r="R95" s="65">
         <v>46168</v>
       </c>
-      <c r="S95" s="163">
+      <c r="S95" s="162">
         <v>46204.919444444444</v>
       </c>
-      <c r="T95" s="160">
+      <c r="T95" s="159">
         <v>100.4</v>
       </c>
     </row>
@@ -10984,10 +10984,10 @@
       <c r="R96" s="65">
         <v>46163</v>
       </c>
-      <c r="S96" s="161">
+      <c r="S96" s="160">
         <v>46204.919444444444</v>
       </c>
-      <c r="T96" s="162">
+      <c r="T96" s="161">
         <v>73</v>
       </c>
     </row>
@@ -11046,10 +11046,10 @@
       <c r="R97" s="65">
         <v>46168</v>
       </c>
-      <c r="S97" s="163">
+      <c r="S97" s="162">
         <v>46204.919444444444</v>
       </c>
-      <c r="T97" s="160">
+      <c r="T97" s="159">
         <v>55.5</v>
       </c>
     </row>
@@ -11108,10 +11108,10 @@
       <c r="R98" s="65">
         <v>46163</v>
       </c>
-      <c r="S98" s="161">
+      <c r="S98" s="160">
         <v>46204.65625</v>
       </c>
-      <c r="T98" s="162">
+      <c r="T98" s="161">
         <v>47.1</v>
       </c>
     </row>
@@ -11170,10 +11170,10 @@
       <c r="R99" s="65">
         <v>46168</v>
       </c>
-      <c r="S99" s="163">
+      <c r="S99" s="162">
         <v>46204.918749999997</v>
       </c>
-      <c r="T99" s="160">
+      <c r="T99" s="159">
         <v>38.9</v>
       </c>
     </row>
@@ -11232,10 +11232,10 @@
       <c r="R100" s="65">
         <v>46163</v>
       </c>
-      <c r="S100" s="161">
+      <c r="S100" s="160">
         <v>46204.875</v>
       </c>
-      <c r="T100" s="162">
+      <c r="T100" s="161">
         <v>53.9</v>
       </c>
     </row>
@@ -11294,10 +11294,10 @@
       <c r="R101" s="65">
         <v>46168</v>
       </c>
-      <c r="S101" s="163">
+      <c r="S101" s="162">
         <v>46204.657638888886</v>
       </c>
-      <c r="T101" s="160">
+      <c r="T101" s="159">
         <v>61.851999999999997</v>
       </c>
     </row>
@@ -11356,10 +11356,10 @@
       <c r="R102" s="65">
         <v>46163</v>
       </c>
-      <c r="S102" s="161">
+      <c r="S102" s="160">
         <v>46204.65625</v>
       </c>
-      <c r="T102" s="162">
+      <c r="T102" s="161">
         <v>47.4</v>
       </c>
     </row>
@@ -11418,10 +11418,10 @@
       <c r="R103" s="65">
         <v>46168</v>
       </c>
-      <c r="S103" s="163">
+      <c r="S103" s="162">
         <v>46204.918749999997</v>
       </c>
-      <c r="T103" s="160">
+      <c r="T103" s="159">
         <v>43.3</v>
       </c>
     </row>
@@ -11480,10 +11480,10 @@
       <c r="R104" s="65">
         <v>46163</v>
       </c>
-      <c r="S104" s="161">
+      <c r="S104" s="160">
         <v>46204.65625</v>
       </c>
-      <c r="T104" s="162">
+      <c r="T104" s="161">
         <v>47.1</v>
       </c>
     </row>
@@ -11542,8 +11542,8 @@
       <c r="R105" s="65">
         <v>46240</v>
       </c>
-      <c r="S105" s="160"/>
-      <c r="T105" s="160"/>
+      <c r="S105" s="159"/>
+      <c r="T105" s="159"/>
     </row>
     <row r="106" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A106" s="12" t="s">
@@ -11600,10 +11600,10 @@
       <c r="R106" s="65">
         <v>46163</v>
       </c>
-      <c r="S106" s="161">
+      <c r="S106" s="160">
         <v>46204.65625</v>
       </c>
-      <c r="T106" s="162">
+      <c r="T106" s="161">
         <v>56.3</v>
       </c>
     </row>
@@ -11662,8 +11662,8 @@
       <c r="R107" s="65">
         <v>46240</v>
       </c>
-      <c r="S107" s="160"/>
-      <c r="T107" s="160"/>
+      <c r="S107" s="159"/>
+      <c r="T107" s="159"/>
     </row>
     <row r="108" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A108" s="12" t="s">
@@ -11720,10 +11720,10 @@
       <c r="R108" s="65">
         <v>46163</v>
       </c>
-      <c r="S108" s="161">
+      <c r="S108" s="160">
         <v>46204.70416666667</v>
       </c>
-      <c r="T108" s="162">
+      <c r="T108" s="161">
         <v>102.95</v>
       </c>
     </row>
@@ -11782,8 +11782,8 @@
       <c r="R109" s="65">
         <v>46240</v>
       </c>
-      <c r="S109" s="160"/>
-      <c r="T109" s="160"/>
+      <c r="S109" s="159"/>
+      <c r="T109" s="159"/>
     </row>
     <row r="110" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A110" s="12" t="s">
@@ -11840,10 +11840,10 @@
       <c r="R110" s="65">
         <v>46163</v>
       </c>
-      <c r="S110" s="161">
+      <c r="S110" s="160">
         <v>46204.657638888886</v>
       </c>
-      <c r="T110" s="162">
+      <c r="T110" s="161">
         <v>70.277000000000001</v>
       </c>
     </row>
@@ -11902,8 +11902,8 @@
       <c r="R111" s="65">
         <v>46240</v>
       </c>
-      <c r="S111" s="160"/>
-      <c r="T111" s="160"/>
+      <c r="S111" s="159"/>
+      <c r="T111" s="159"/>
     </row>
     <row r="112" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A112" s="12" t="s">
@@ -11960,10 +11960,10 @@
       <c r="R112" s="65">
         <v>46163</v>
       </c>
-      <c r="S112" s="161">
+      <c r="S112" s="160">
         <v>46204.413194444445</v>
       </c>
-      <c r="T112" s="162">
+      <c r="T112" s="161">
         <v>77.23</v>
       </c>
     </row>
@@ -12022,8 +12022,8 @@
       <c r="R113" s="65">
         <v>46240</v>
       </c>
-      <c r="S113" s="160"/>
-      <c r="T113" s="160"/>
+      <c r="S113" s="159"/>
+      <c r="T113" s="159"/>
     </row>
     <row r="114" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A114" s="12" t="s">
@@ -12080,10 +12080,10 @@
       <c r="R114" s="65">
         <v>46154</v>
       </c>
-      <c r="S114" s="161">
+      <c r="S114" s="160">
         <v>46204.426388888889</v>
       </c>
-      <c r="T114" s="162">
+      <c r="T114" s="161">
         <v>25.35</v>
       </c>
     </row>
@@ -12142,8 +12142,8 @@
       <c r="R115" s="65">
         <v>46240</v>
       </c>
-      <c r="S115" s="160"/>
-      <c r="T115" s="160"/>
+      <c r="S115" s="159"/>
+      <c r="T115" s="159"/>
     </row>
     <row r="116" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A116" s="12" t="s">
@@ -12200,10 +12200,10 @@
       <c r="R116" s="65">
         <v>46154</v>
       </c>
-      <c r="S116" s="161">
+      <c r="S116" s="160">
         <v>46204.657638888886</v>
       </c>
-      <c r="T116" s="162">
+      <c r="T116" s="161">
         <v>45.284999999999997</v>
       </c>
     </row>
@@ -12262,8 +12262,8 @@
       <c r="R117" s="65">
         <v>46240</v>
       </c>
-      <c r="S117" s="160"/>
-      <c r="T117" s="160"/>
+      <c r="S117" s="159"/>
+      <c r="T117" s="159"/>
     </row>
     <row r="118" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A118" s="12" t="s">
@@ -12320,10 +12320,10 @@
       <c r="R118" s="65">
         <v>46154</v>
       </c>
-      <c r="S118" s="161">
+      <c r="S118" s="160">
         <v>46204.425000000003</v>
       </c>
-      <c r="T118" s="162">
+      <c r="T118" s="161">
         <v>19.7</v>
       </c>
     </row>
@@ -12382,8 +12382,8 @@
       <c r="R119" s="65">
         <v>46240</v>
       </c>
-      <c r="S119" s="160"/>
-      <c r="T119" s="160"/>
+      <c r="S119" s="159"/>
+      <c r="T119" s="159"/>
     </row>
     <row r="120" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A120" s="12" t="s">
@@ -12440,10 +12440,10 @@
       <c r="R120" s="65">
         <v>46154</v>
       </c>
-      <c r="S120" s="161">
+      <c r="S120" s="160">
         <v>46204.704861111109</v>
       </c>
-      <c r="T120" s="162">
+      <c r="T120" s="161">
         <v>39.33</v>
       </c>
     </row>
@@ -12502,8 +12502,8 @@
       <c r="R121" s="65">
         <v>46255</v>
       </c>
-      <c r="S121" s="160"/>
-      <c r="T121" s="160"/>
+      <c r="S121" s="159"/>
+      <c r="T121" s="159"/>
     </row>
     <row r="122" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A122" s="12" t="s">
@@ -12560,10 +12560,10 @@
       <c r="R122" s="65">
         <v>46154</v>
       </c>
-      <c r="S122" s="161">
+      <c r="S122" s="160">
         <v>46204.424305555556</v>
       </c>
-      <c r="T122" s="162">
+      <c r="T122" s="161">
         <v>35.67</v>
       </c>
     </row>
@@ -12622,8 +12622,8 @@
       <c r="R123" s="65">
         <v>46255</v>
       </c>
-      <c r="S123" s="160"/>
-      <c r="T123" s="160"/>
+      <c r="S123" s="159"/>
+      <c r="T123" s="159"/>
     </row>
     <row r="124" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A124" s="12" t="s">
@@ -12680,10 +12680,10 @@
       <c r="R124" s="65">
         <v>46154</v>
       </c>
-      <c r="S124" s="161">
+      <c r="S124" s="160">
         <v>46204.657638888886</v>
       </c>
-      <c r="T124" s="162">
+      <c r="T124" s="161">
         <v>37.427999999999997</v>
       </c>
     </row>
@@ -12742,8 +12742,8 @@
       <c r="R125" s="65">
         <v>46255</v>
       </c>
-      <c r="S125" s="160"/>
-      <c r="T125" s="160"/>
+      <c r="S125" s="159"/>
+      <c r="T125" s="159"/>
     </row>
     <row r="126" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A126" s="12" t="s">
@@ -12800,10 +12800,10 @@
       <c r="R126" s="65">
         <v>46154</v>
       </c>
-      <c r="S126" s="161">
+      <c r="S126" s="160">
         <v>46204.652083333334</v>
       </c>
-      <c r="T126" s="162">
+      <c r="T126" s="161">
         <v>36.700000000000003</v>
       </c>
     </row>
@@ -12862,8 +12862,8 @@
       <c r="R127" s="65">
         <v>46255</v>
       </c>
-      <c r="S127" s="160"/>
-      <c r="T127" s="160"/>
+      <c r="S127" s="159"/>
+      <c r="T127" s="159"/>
     </row>
     <row r="128" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A128" s="12" t="s">
@@ -12920,10 +12920,10 @@
       <c r="R128" s="65">
         <v>46154</v>
       </c>
-      <c r="S128" s="161">
+      <c r="S128" s="160">
         <v>46204.714583333334</v>
       </c>
-      <c r="T128" s="162">
+      <c r="T128" s="161">
         <v>11.590999999999999</v>
       </c>
     </row>
@@ -12982,8 +12982,8 @@
       <c r="R129" s="65">
         <v>46255</v>
       </c>
-      <c r="S129" s="160"/>
-      <c r="T129" s="160"/>
+      <c r="S129" s="159"/>
+      <c r="T129" s="159"/>
     </row>
     <row r="130" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A130" s="12" t="s">
@@ -13040,8 +13040,8 @@
       <c r="R130" s="65">
         <v>46255</v>
       </c>
-      <c r="S130" s="160"/>
-      <c r="T130" s="160"/>
+      <c r="S130" s="159"/>
+      <c r="T130" s="159"/>
     </row>
     <row r="131" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A131" s="12" t="s">
@@ -13098,8 +13098,8 @@
       <c r="R131" s="65">
         <v>46255</v>
       </c>
-      <c r="S131" s="160"/>
-      <c r="T131" s="160"/>
+      <c r="S131" s="159"/>
+      <c r="T131" s="159"/>
     </row>
     <row r="132" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A132" s="12" t="s">
@@ -13156,8 +13156,8 @@
       <c r="R132" s="65">
         <v>46255</v>
       </c>
-      <c r="S132" s="160"/>
-      <c r="T132" s="160"/>
+      <c r="S132" s="159"/>
+      <c r="T132" s="159"/>
     </row>
     <row r="133" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A133" s="12" t="s">
@@ -13206,8 +13206,8 @@
       <c r="R133" s="65">
         <v>46270</v>
       </c>
-      <c r="S133" s="160"/>
-      <c r="T133" s="160"/>
+      <c r="S133" s="159"/>
+      <c r="T133" s="159"/>
     </row>
     <row r="134" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A134" s="12" t="s">
@@ -13256,8 +13256,8 @@
       <c r="R134" s="65">
         <v>46270</v>
       </c>
-      <c r="S134" s="160"/>
-      <c r="T134" s="160"/>
+      <c r="S134" s="159"/>
+      <c r="T134" s="159"/>
     </row>
     <row r="135" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A135" s="12" t="s">
@@ -13312,8 +13312,8 @@
       <c r="R135" s="65">
         <v>46270</v>
       </c>
-      <c r="S135" s="160"/>
-      <c r="T135" s="160"/>
+      <c r="S135" s="159"/>
+      <c r="T135" s="159"/>
     </row>
     <row r="136" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A136" s="12" t="s">
@@ -13368,8 +13368,8 @@
       <c r="R136" s="65">
         <v>46270</v>
       </c>
-      <c r="S136" s="160"/>
-      <c r="T136" s="160"/>
+      <c r="S136" s="159"/>
+      <c r="T136" s="159"/>
     </row>
     <row r="137" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A137" s="12" t="s">
@@ -13424,8 +13424,8 @@
       <c r="R137" s="65">
         <v>46270</v>
       </c>
-      <c r="S137" s="160"/>
-      <c r="T137" s="160"/>
+      <c r="S137" s="159"/>
+      <c r="T137" s="159"/>
     </row>
     <row r="138" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A138" s="12" t="s">
@@ -13480,8 +13480,8 @@
       <c r="R138" s="65">
         <v>46270</v>
       </c>
-      <c r="S138" s="160"/>
-      <c r="T138" s="160"/>
+      <c r="S138" s="159"/>
+      <c r="T138" s="159"/>
     </row>
     <row r="139" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A139" s="12" t="s">
@@ -13536,8 +13536,8 @@
       <c r="R139" s="65">
         <v>46270</v>
       </c>
-      <c r="S139" s="160"/>
-      <c r="T139" s="160"/>
+      <c r="S139" s="159"/>
+      <c r="T139" s="159"/>
     </row>
     <row r="140" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A140" s="12" t="s">
@@ -13592,8 +13592,8 @@
       <c r="R140" s="65">
         <v>46270</v>
       </c>
-      <c r="S140" s="160"/>
-      <c r="T140" s="160"/>
+      <c r="S140" s="159"/>
+      <c r="T140" s="159"/>
     </row>
     <row r="141" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A141" s="12" t="s">
@@ -13648,8 +13648,8 @@
       <c r="R141" s="65">
         <v>46301</v>
       </c>
-      <c r="S141" s="160"/>
-      <c r="T141" s="160"/>
+      <c r="S141" s="159"/>
+      <c r="T141" s="159"/>
     </row>
     <row r="142" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A142" s="12" t="s">
@@ -13704,8 +13704,8 @@
       <c r="R142" s="65">
         <v>46286</v>
       </c>
-      <c r="S142" s="160"/>
-      <c r="T142" s="160"/>
+      <c r="S142" s="159"/>
+      <c r="T142" s="159"/>
     </row>
     <row r="143" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A143" s="12" t="s">
@@ -13760,8 +13760,8 @@
       <c r="R143" s="65">
         <v>46301</v>
       </c>
-      <c r="S143" s="160"/>
-      <c r="T143" s="160"/>
+      <c r="S143" s="159"/>
+      <c r="T143" s="159"/>
     </row>
     <row r="144" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A144" s="12" t="s">
@@ -13816,8 +13816,8 @@
       <c r="R144" s="65">
         <v>46286</v>
       </c>
-      <c r="S144" s="160"/>
-      <c r="T144" s="160"/>
+      <c r="S144" s="159"/>
+      <c r="T144" s="159"/>
     </row>
     <row r="145" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A145" s="12" t="s">
@@ -13872,8 +13872,8 @@
       <c r="R145" s="65">
         <v>46301</v>
       </c>
-      <c r="S145" s="160"/>
-      <c r="T145" s="160"/>
+      <c r="S145" s="159"/>
+      <c r="T145" s="159"/>
     </row>
     <row r="146" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A146" s="12" t="s">
@@ -13928,8 +13928,8 @@
       <c r="R146" s="65">
         <v>46286</v>
       </c>
-      <c r="S146" s="160"/>
-      <c r="T146" s="160"/>
+      <c r="S146" s="159"/>
+      <c r="T146" s="159"/>
     </row>
     <row r="147" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A147" s="12" t="s">
@@ -13984,8 +13984,8 @@
       <c r="R147" s="65">
         <v>46301</v>
       </c>
-      <c r="S147" s="160"/>
-      <c r="T147" s="160"/>
+      <c r="S147" s="159"/>
+      <c r="T147" s="159"/>
     </row>
     <row r="148" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A148" s="12" t="s">
@@ -14040,8 +14040,8 @@
       <c r="R148" s="65">
         <v>46286</v>
       </c>
-      <c r="S148" s="160"/>
-      <c r="T148" s="160"/>
+      <c r="S148" s="159"/>
+      <c r="T148" s="159"/>
     </row>
     <row r="149" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A149" s="12" t="s">
@@ -14096,8 +14096,8 @@
       <c r="R149" s="65">
         <v>46301</v>
       </c>
-      <c r="S149" s="160"/>
-      <c r="T149" s="160"/>
+      <c r="S149" s="159"/>
+      <c r="T149" s="159"/>
     </row>
     <row r="150" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A150" s="12" t="s">
@@ -14152,8 +14152,8 @@
       <c r="R150" s="65">
         <v>46286</v>
       </c>
-      <c r="S150" s="160"/>
-      <c r="T150" s="160"/>
+      <c r="S150" s="159"/>
+      <c r="T150" s="159"/>
     </row>
     <row r="151" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A151" s="12" t="s">
@@ -14208,8 +14208,8 @@
       <c r="R151" s="65">
         <v>46301</v>
       </c>
-      <c r="S151" s="160"/>
-      <c r="T151" s="160"/>
+      <c r="S151" s="159"/>
+      <c r="T151" s="159"/>
     </row>
     <row r="152" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A152" s="12" t="s">
@@ -14264,8 +14264,8 @@
       <c r="R152" s="65">
         <v>46286</v>
       </c>
-      <c r="S152" s="160"/>
-      <c r="T152" s="160"/>
+      <c r="S152" s="159"/>
+      <c r="T152" s="159"/>
     </row>
     <row r="153" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A153" s="12" t="s">
@@ -14320,8 +14320,8 @@
       <c r="R153" s="65">
         <v>46301</v>
       </c>
-      <c r="S153" s="160"/>
-      <c r="T153" s="160"/>
+      <c r="S153" s="159"/>
+      <c r="T153" s="159"/>
     </row>
     <row r="154" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A154" s="12" t="s">
@@ -14376,8 +14376,8 @@
       <c r="R154" s="65">
         <v>46286</v>
       </c>
-      <c r="S154" s="160"/>
-      <c r="T154" s="160"/>
+      <c r="S154" s="159"/>
+      <c r="T154" s="159"/>
     </row>
     <row r="155" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A155" s="12" t="s">
@@ -14432,8 +14432,8 @@
       <c r="R155" s="65">
         <v>46286</v>
       </c>
-      <c r="S155" s="160"/>
-      <c r="T155" s="160"/>
+      <c r="S155" s="159"/>
+      <c r="T155" s="159"/>
     </row>
     <row r="156" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A156" s="12" t="s">
@@ -14490,8 +14490,8 @@
       <c r="R156" s="65">
         <v>46254</v>
       </c>
-      <c r="S156" s="160"/>
-      <c r="T156" s="160"/>
+      <c r="S156" s="159"/>
+      <c r="T156" s="159"/>
     </row>
     <row r="157" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A157" s="12" t="s">
@@ -14548,8 +14548,8 @@
       <c r="R157" s="65">
         <v>46254</v>
       </c>
-      <c r="S157" s="160"/>
-      <c r="T157" s="160"/>
+      <c r="S157" s="159"/>
+      <c r="T157" s="159"/>
     </row>
     <row r="158" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A158" s="12" t="s">
@@ -14606,8 +14606,8 @@
       <c r="R158" s="65">
         <v>46254</v>
       </c>
-      <c r="S158" s="160"/>
-      <c r="T158" s="160"/>
+      <c r="S158" s="159"/>
+      <c r="T158" s="159"/>
     </row>
     <row r="159" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A159" s="12" t="s">
@@ -14664,8 +14664,8 @@
       <c r="R159" s="65">
         <v>46254</v>
       </c>
-      <c r="S159" s="160"/>
-      <c r="T159" s="160"/>
+      <c r="S159" s="159"/>
+      <c r="T159" s="159"/>
     </row>
     <row r="160" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A160" s="12" t="s">
@@ -14722,8 +14722,8 @@
       <c r="R160" s="65">
         <v>46254</v>
       </c>
-      <c r="S160" s="160"/>
-      <c r="T160" s="160"/>
+      <c r="S160" s="159"/>
+      <c r="T160" s="159"/>
     </row>
     <row r="161" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A161" s="12" t="s">
@@ -14780,8 +14780,8 @@
       <c r="R161" s="65">
         <v>46254</v>
       </c>
-      <c r="S161" s="160"/>
-      <c r="T161" s="160"/>
+      <c r="S161" s="159"/>
+      <c r="T161" s="159"/>
     </row>
     <row r="162" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A162" s="12" t="s">
@@ -14838,8 +14838,8 @@
       <c r="R162" s="65">
         <v>46254</v>
       </c>
-      <c r="S162" s="160"/>
-      <c r="T162" s="160"/>
+      <c r="S162" s="159"/>
+      <c r="T162" s="159"/>
     </row>
     <row r="163" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A163" s="12" t="s">
@@ -14896,8 +14896,8 @@
       <c r="R163" s="65">
         <v>46254</v>
       </c>
-      <c r="S163" s="160"/>
-      <c r="T163" s="160"/>
+      <c r="S163" s="159"/>
+      <c r="T163" s="159"/>
     </row>
     <row r="164" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A164" s="12" t="s">
@@ -14954,8 +14954,8 @@
       <c r="R164" s="65">
         <v>46238</v>
       </c>
-      <c r="S164" s="160"/>
-      <c r="T164" s="160"/>
+      <c r="S164" s="159"/>
+      <c r="T164" s="159"/>
     </row>
     <row r="165" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A165" s="12" t="s">
@@ -15012,8 +15012,8 @@
       <c r="R165" s="65">
         <v>46238</v>
       </c>
-      <c r="S165" s="160"/>
-      <c r="T165" s="160"/>
+      <c r="S165" s="159"/>
+      <c r="T165" s="159"/>
     </row>
     <row r="166" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A166" s="12" t="s">
@@ -15070,8 +15070,8 @@
       <c r="R166" s="65">
         <v>46238</v>
       </c>
-      <c r="S166" s="160"/>
-      <c r="T166" s="160"/>
+      <c r="S166" s="159"/>
+      <c r="T166" s="159"/>
     </row>
     <row r="167" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A167" s="12" t="s">
@@ -15128,8 +15128,8 @@
       <c r="R167" s="65">
         <v>46238</v>
       </c>
-      <c r="S167" s="160"/>
-      <c r="T167" s="160"/>
+      <c r="S167" s="159"/>
+      <c r="T167" s="159"/>
     </row>
     <row r="168" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A168" s="12" t="s">
@@ -15186,8 +15186,8 @@
       <c r="R168" s="65">
         <v>46238</v>
       </c>
-      <c r="S168" s="160"/>
-      <c r="T168" s="160"/>
+      <c r="S168" s="159"/>
+      <c r="T168" s="159"/>
     </row>
     <row r="169" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A169" s="12" t="s">
@@ -15244,8 +15244,8 @@
       <c r="R169" s="65">
         <v>46238</v>
       </c>
-      <c r="S169" s="160"/>
-      <c r="T169" s="160"/>
+      <c r="S169" s="159"/>
+      <c r="T169" s="159"/>
     </row>
     <row r="170" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A170" s="12" t="s">
@@ -15302,8 +15302,8 @@
       <c r="R170" s="65">
         <v>46238</v>
       </c>
-      <c r="S170" s="160"/>
-      <c r="T170" s="160"/>
+      <c r="S170" s="159"/>
+      <c r="T170" s="159"/>
     </row>
     <row r="171" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A171" s="12" t="s">
@@ -15360,8 +15360,8 @@
       <c r="R171" s="65">
         <v>46266</v>
       </c>
-      <c r="S171" s="160"/>
-      <c r="T171" s="160"/>
+      <c r="S171" s="159"/>
+      <c r="T171" s="159"/>
     </row>
     <row r="172" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A172" s="12" t="s">
@@ -15418,8 +15418,8 @@
       <c r="R172" s="65">
         <v>46266</v>
       </c>
-      <c r="S172" s="160"/>
-      <c r="T172" s="160"/>
+      <c r="S172" s="159"/>
+      <c r="T172" s="159"/>
     </row>
     <row r="173" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A173" s="12" t="s">
@@ -15476,8 +15476,8 @@
       <c r="R173" s="65">
         <v>46266</v>
       </c>
-      <c r="S173" s="160"/>
-      <c r="T173" s="160"/>
+      <c r="S173" s="159"/>
+      <c r="T173" s="159"/>
     </row>
     <row r="174" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A174" s="12" t="s">
@@ -15534,8 +15534,8 @@
       <c r="R174" s="65">
         <v>46266</v>
       </c>
-      <c r="S174" s="160"/>
-      <c r="T174" s="160"/>
+      <c r="S174" s="159"/>
+      <c r="T174" s="159"/>
     </row>
     <row r="175" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A175" s="12" t="s">
@@ -15592,8 +15592,8 @@
       <c r="R175" s="65">
         <v>46266</v>
       </c>
-      <c r="S175" s="160"/>
-      <c r="T175" s="160"/>
+      <c r="S175" s="159"/>
+      <c r="T175" s="159"/>
     </row>
     <row r="176" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A176" s="12" t="s">
@@ -15650,8 +15650,8 @@
       <c r="R176" s="65">
         <v>46252</v>
       </c>
-      <c r="S176" s="160"/>
-      <c r="T176" s="160"/>
+      <c r="S176" s="159"/>
+      <c r="T176" s="159"/>
     </row>
     <row r="177" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A177" s="12" t="s">
@@ -15708,8 +15708,8 @@
       <c r="R177" s="65">
         <v>46252</v>
       </c>
-      <c r="S177" s="160"/>
-      <c r="T177" s="160"/>
+      <c r="S177" s="159"/>
+      <c r="T177" s="159"/>
     </row>
     <row r="178" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A178" s="12" t="s">
@@ -15766,8 +15766,8 @@
       <c r="R178" s="65">
         <v>46252</v>
       </c>
-      <c r="S178" s="160"/>
-      <c r="T178" s="160"/>
+      <c r="S178" s="159"/>
+      <c r="T178" s="159"/>
     </row>
     <row r="179" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A179" s="12" t="s">
@@ -15824,8 +15824,8 @@
       <c r="R179" s="65">
         <v>46252</v>
       </c>
-      <c r="S179" s="160"/>
-      <c r="T179" s="160"/>
+      <c r="S179" s="159"/>
+      <c r="T179" s="159"/>
     </row>
     <row r="180" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A180" s="12" t="s">
@@ -15882,8 +15882,8 @@
       <c r="R180" s="65">
         <v>46252</v>
       </c>
-      <c r="S180" s="160"/>
-      <c r="T180" s="160"/>
+      <c r="S180" s="159"/>
+      <c r="T180" s="159"/>
     </row>
     <row r="181" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A181" s="12" t="s">
@@ -15940,8 +15940,8 @@
       <c r="R181" s="65">
         <v>46252</v>
       </c>
-      <c r="S181" s="160"/>
-      <c r="T181" s="160"/>
+      <c r="S181" s="159"/>
+      <c r="T181" s="159"/>
     </row>
     <row r="182" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A182" s="12" t="s">
@@ -15998,8 +15998,8 @@
       <c r="R182" s="65">
         <v>46252</v>
       </c>
-      <c r="S182" s="160"/>
-      <c r="T182" s="160"/>
+      <c r="S182" s="159"/>
+      <c r="T182" s="159"/>
     </row>
     <row r="183" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A183" s="12" t="s">
@@ -16056,8 +16056,8 @@
       <c r="R183" s="65">
         <v>46252</v>
       </c>
-      <c r="S183" s="160"/>
-      <c r="T183" s="160"/>
+      <c r="S183" s="159"/>
+      <c r="T183" s="159"/>
     </row>
     <row r="184" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A184" s="12" t="s">
@@ -16114,8 +16114,8 @@
       <c r="R184" s="65">
         <v>46238</v>
       </c>
-      <c r="S184" s="160"/>
-      <c r="T184" s="160"/>
+      <c r="S184" s="159"/>
+      <c r="T184" s="159"/>
     </row>
     <row r="185" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A185" s="12" t="s">
@@ -16172,8 +16172,8 @@
       <c r="R185" s="65">
         <v>46238</v>
       </c>
-      <c r="S185" s="160"/>
-      <c r="T185" s="160"/>
+      <c r="S185" s="159"/>
+      <c r="T185" s="159"/>
     </row>
     <row r="186" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A186" s="12" t="s">
@@ -16230,8 +16230,8 @@
       <c r="R186" s="65">
         <v>46238</v>
       </c>
-      <c r="S186" s="160"/>
-      <c r="T186" s="160"/>
+      <c r="S186" s="159"/>
+      <c r="T186" s="159"/>
     </row>
     <row r="187" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A187" s="12" t="s">
@@ -16288,8 +16288,8 @@
       <c r="R187" s="65">
         <v>46238</v>
       </c>
-      <c r="S187" s="160"/>
-      <c r="T187" s="160"/>
+      <c r="S187" s="159"/>
+      <c r="T187" s="159"/>
     </row>
     <row r="188" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A188" s="12" t="s">
@@ -16346,8 +16346,8 @@
       <c r="R188" s="65">
         <v>46238</v>
       </c>
-      <c r="S188" s="160"/>
-      <c r="T188" s="160"/>
+      <c r="S188" s="159"/>
+      <c r="T188" s="159"/>
     </row>
     <row r="189" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A189" s="12" t="s">
@@ -16404,8 +16404,8 @@
       <c r="R189" s="65">
         <v>46238</v>
       </c>
-      <c r="S189" s="160"/>
-      <c r="T189" s="160"/>
+      <c r="S189" s="159"/>
+      <c r="T189" s="159"/>
     </row>
     <row r="190" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A190" s="12" t="s">
@@ -16462,8 +16462,8 @@
       <c r="R190" s="65">
         <v>46238</v>
       </c>
-      <c r="S190" s="160"/>
-      <c r="T190" s="160"/>
+      <c r="S190" s="159"/>
+      <c r="T190" s="159"/>
     </row>
     <row r="191" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A191" s="12" t="s">
@@ -16520,8 +16520,8 @@
       <c r="R191" s="65">
         <v>46238</v>
       </c>
-      <c r="S191" s="160"/>
-      <c r="T191" s="160"/>
+      <c r="S191" s="159"/>
+      <c r="T191" s="159"/>
     </row>
     <row r="192" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A192" s="14" t="s">
@@ -16576,11 +16576,11 @@
       <c r="R192" s="65">
         <v>46154</v>
       </c>
-      <c r="S192" s="160"/>
-      <c r="T192" s="160"/>
+      <c r="S192" s="159"/>
+      <c r="T192" s="159"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R192">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T192">
     <sortCondition ref="A2:A192"/>
   </sortState>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -16599,6 +16599,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:S204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16680,7 +16681,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>116</v>
       </c>
@@ -16724,10 +16725,10 @@
         <v>0</v>
       </c>
       <c r="Q2" s="17"/>
-      <c r="R2" s="160"/>
-      <c r="S2" s="160"/>
-    </row>
-    <row r="3" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R2" s="159"/>
+      <c r="S2" s="159"/>
+    </row>
+    <row r="3" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>119</v>
       </c>
@@ -16771,10 +16772,10 @@
         <v>0</v>
       </c>
       <c r="Q3" s="17"/>
-      <c r="R3" s="160"/>
-      <c r="S3" s="160"/>
-    </row>
-    <row r="4" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R3" s="159"/>
+      <c r="S3" s="159"/>
+    </row>
+    <row r="4" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
         <v>120</v>
       </c>
@@ -16818,10 +16819,10 @@
         <v>0</v>
       </c>
       <c r="Q4" s="17"/>
-      <c r="R4" s="160"/>
-      <c r="S4" s="160"/>
-    </row>
-    <row r="5" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R4" s="159"/>
+      <c r="S4" s="159"/>
+    </row>
+    <row r="5" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
         <v>122</v>
       </c>
@@ -16865,10 +16866,10 @@
         <v>0</v>
       </c>
       <c r="Q5" s="17"/>
-      <c r="R5" s="160"/>
-      <c r="S5" s="160"/>
-    </row>
-    <row r="6" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R5" s="159"/>
+      <c r="S5" s="159"/>
+    </row>
+    <row r="6" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
         <v>123</v>
       </c>
@@ -16912,10 +16913,10 @@
         <v>0</v>
       </c>
       <c r="Q6" s="17"/>
-      <c r="R6" s="160"/>
-      <c r="S6" s="160"/>
-    </row>
-    <row r="7" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R6" s="159"/>
+      <c r="S6" s="159"/>
+    </row>
+    <row r="7" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
         <v>124</v>
       </c>
@@ -16959,10 +16960,10 @@
         <v>0</v>
       </c>
       <c r="Q7" s="17"/>
-      <c r="R7" s="160"/>
-      <c r="S7" s="160"/>
-    </row>
-    <row r="8" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R7" s="159"/>
+      <c r="S7" s="159"/>
+    </row>
+    <row r="8" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
         <v>125</v>
       </c>
@@ -17006,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="Q8" s="17"/>
-      <c r="R8" s="160"/>
-      <c r="S8" s="160"/>
-    </row>
-    <row r="9" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R8" s="159"/>
+      <c r="S8" s="159"/>
+    </row>
+    <row r="9" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
         <v>126</v>
       </c>
@@ -17053,10 +17054,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="17"/>
-      <c r="R9" s="160"/>
-      <c r="S9" s="160"/>
-    </row>
-    <row r="10" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R9" s="159"/>
+      <c r="S9" s="159"/>
+    </row>
+    <row r="10" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
         <v>127</v>
       </c>
@@ -17100,10 +17101,10 @@
         <v>0</v>
       </c>
       <c r="Q10" s="17"/>
-      <c r="R10" s="160"/>
-      <c r="S10" s="160"/>
-    </row>
-    <row r="11" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R10" s="159"/>
+      <c r="S10" s="159"/>
+    </row>
+    <row r="11" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
         <v>150</v>
       </c>
@@ -17147,10 +17148,10 @@
         <v>0</v>
       </c>
       <c r="Q11" s="17"/>
-      <c r="R11" s="160"/>
-      <c r="S11" s="160"/>
-    </row>
-    <row r="12" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R11" s="159"/>
+      <c r="S11" s="159"/>
+    </row>
+    <row r="12" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
         <v>152</v>
       </c>
@@ -17194,10 +17195,10 @@
         <v>0</v>
       </c>
       <c r="Q12" s="17"/>
-      <c r="R12" s="160"/>
-      <c r="S12" s="160"/>
-    </row>
-    <row r="13" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R12" s="159"/>
+      <c r="S12" s="159"/>
+    </row>
+    <row r="13" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="s">
         <v>153</v>
       </c>
@@ -17241,10 +17242,10 @@
         <v>0</v>
       </c>
       <c r="Q13" s="17"/>
-      <c r="R13" s="160"/>
-      <c r="S13" s="160"/>
-    </row>
-    <row r="14" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R13" s="159"/>
+      <c r="S13" s="159"/>
+    </row>
+    <row r="14" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="23" t="s">
         <v>154</v>
       </c>
@@ -17288,10 +17289,10 @@
         <v>0</v>
       </c>
       <c r="Q14" s="17"/>
-      <c r="R14" s="160"/>
-      <c r="S14" s="160"/>
-    </row>
-    <row r="15" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R14" s="159"/>
+      <c r="S14" s="159"/>
+    </row>
+    <row r="15" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>155</v>
       </c>
@@ -17335,10 +17336,10 @@
         <v>0</v>
       </c>
       <c r="Q15" s="17"/>
-      <c r="R15" s="160"/>
-      <c r="S15" s="160"/>
-    </row>
-    <row r="16" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R15" s="159"/>
+      <c r="S15" s="159"/>
+    </row>
+    <row r="16" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
         <v>156</v>
       </c>
@@ -17382,10 +17383,10 @@
         <v>0</v>
       </c>
       <c r="Q16" s="17"/>
-      <c r="R16" s="160"/>
-      <c r="S16" s="160"/>
-    </row>
-    <row r="17" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R16" s="159"/>
+      <c r="S16" s="159"/>
+    </row>
+    <row r="17" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
         <v>157</v>
       </c>
@@ -17429,10 +17430,10 @@
         <v>0</v>
       </c>
       <c r="Q17" s="17"/>
-      <c r="R17" s="160"/>
-      <c r="S17" s="160"/>
-    </row>
-    <row r="18" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R17" s="159"/>
+      <c r="S17" s="159"/>
+    </row>
+    <row r="18" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="23" t="s">
         <v>158</v>
       </c>
@@ -17476,10 +17477,10 @@
         <v>0</v>
       </c>
       <c r="Q18" s="17"/>
-      <c r="R18" s="160"/>
-      <c r="S18" s="160"/>
-    </row>
-    <row r="19" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R18" s="159"/>
+      <c r="S18" s="159"/>
+    </row>
+    <row r="19" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="23" t="s">
         <v>160</v>
       </c>
@@ -17523,10 +17524,10 @@
         <v>0</v>
       </c>
       <c r="Q19" s="17"/>
-      <c r="R19" s="160"/>
-      <c r="S19" s="160"/>
-    </row>
-    <row r="20" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R19" s="159"/>
+      <c r="S19" s="159"/>
+    </row>
+    <row r="20" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="23" t="s">
         <v>181</v>
       </c>
@@ -17570,10 +17571,10 @@
         <v>0</v>
       </c>
       <c r="Q20" s="17"/>
-      <c r="R20" s="160"/>
-      <c r="S20" s="160"/>
-    </row>
-    <row r="21" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R20" s="159"/>
+      <c r="S20" s="159"/>
+    </row>
+    <row r="21" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="s">
         <v>183</v>
       </c>
@@ -17617,10 +17618,10 @@
         <v>0</v>
       </c>
       <c r="Q21" s="17"/>
-      <c r="R21" s="160"/>
-      <c r="S21" s="160"/>
-    </row>
-    <row r="22" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R21" s="159"/>
+      <c r="S21" s="159"/>
+    </row>
+    <row r="22" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="23" t="s">
         <v>185</v>
       </c>
@@ -17664,10 +17665,10 @@
         <v>0</v>
       </c>
       <c r="Q22" s="17"/>
-      <c r="R22" s="160"/>
-      <c r="S22" s="160"/>
-    </row>
-    <row r="23" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R22" s="159"/>
+      <c r="S22" s="159"/>
+    </row>
+    <row r="23" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="s">
         <v>186</v>
       </c>
@@ -17711,10 +17712,10 @@
         <v>0</v>
       </c>
       <c r="Q23" s="17"/>
-      <c r="R23" s="160"/>
-      <c r="S23" s="160"/>
-    </row>
-    <row r="24" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R23" s="159"/>
+      <c r="S23" s="159"/>
+    </row>
+    <row r="24" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="23" t="s">
         <v>187</v>
       </c>
@@ -17758,10 +17759,10 @@
         <v>0</v>
       </c>
       <c r="Q24" s="17"/>
-      <c r="R24" s="160"/>
-      <c r="S24" s="160"/>
-    </row>
-    <row r="25" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R24" s="159"/>
+      <c r="S24" s="159"/>
+    </row>
+    <row r="25" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="23" t="s">
         <v>188</v>
       </c>
@@ -17805,10 +17806,10 @@
         <v>0</v>
       </c>
       <c r="Q25" s="17"/>
-      <c r="R25" s="160"/>
-      <c r="S25" s="160"/>
-    </row>
-    <row r="26" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R25" s="159"/>
+      <c r="S25" s="159"/>
+    </row>
+    <row r="26" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
         <v>203</v>
       </c>
@@ -17852,10 +17853,10 @@
         <v>0</v>
       </c>
       <c r="Q26" s="17"/>
-      <c r="R26" s="160"/>
-      <c r="S26" s="160"/>
-    </row>
-    <row r="27" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R26" s="159"/>
+      <c r="S26" s="159"/>
+    </row>
+    <row r="27" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="23" t="s">
         <v>205</v>
       </c>
@@ -17899,10 +17900,10 @@
         <v>0</v>
       </c>
       <c r="Q27" s="17"/>
-      <c r="R27" s="160"/>
-      <c r="S27" s="160"/>
-    </row>
-    <row r="28" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R27" s="159"/>
+      <c r="S27" s="159"/>
+    </row>
+    <row r="28" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="23" t="s">
         <v>206</v>
       </c>
@@ -17946,10 +17947,10 @@
         <v>0</v>
       </c>
       <c r="Q28" s="17"/>
-      <c r="R28" s="160"/>
-      <c r="S28" s="160"/>
-    </row>
-    <row r="29" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R28" s="159"/>
+      <c r="S28" s="159"/>
+    </row>
+    <row r="29" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="s">
         <v>207</v>
       </c>
@@ -17993,10 +17994,10 @@
         <v>0</v>
       </c>
       <c r="Q29" s="17"/>
-      <c r="R29" s="160"/>
-      <c r="S29" s="160"/>
-    </row>
-    <row r="30" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R29" s="159"/>
+      <c r="S29" s="159"/>
+    </row>
+    <row r="30" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23" t="s">
         <v>208</v>
       </c>
@@ -18040,10 +18041,10 @@
         <v>0</v>
       </c>
       <c r="Q30" s="17"/>
-      <c r="R30" s="160"/>
-      <c r="S30" s="160"/>
-    </row>
-    <row r="31" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R30" s="159"/>
+      <c r="S30" s="159"/>
+    </row>
+    <row r="31" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
         <v>209</v>
       </c>
@@ -18087,10 +18088,10 @@
         <v>0</v>
       </c>
       <c r="Q31" s="17"/>
-      <c r="R31" s="160"/>
-      <c r="S31" s="160"/>
-    </row>
-    <row r="32" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R31" s="159"/>
+      <c r="S31" s="159"/>
+    </row>
+    <row r="32" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="23" t="s">
         <v>210</v>
       </c>
@@ -18134,10 +18135,10 @@
         <v>0</v>
       </c>
       <c r="Q32" s="17"/>
-      <c r="R32" s="160"/>
-      <c r="S32" s="160"/>
-    </row>
-    <row r="33" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R32" s="159"/>
+      <c r="S32" s="159"/>
+    </row>
+    <row r="33" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="23" t="s">
         <v>211</v>
       </c>
@@ -18181,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="Q33" s="17"/>
-      <c r="R33" s="160"/>
-      <c r="S33" s="160"/>
-    </row>
-    <row r="34" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R33" s="159"/>
+      <c r="S33" s="159"/>
+    </row>
+    <row r="34" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
         <v>212</v>
       </c>
@@ -18228,8 +18229,8 @@
         <v>0</v>
       </c>
       <c r="Q34" s="17"/>
-      <c r="R34" s="160"/>
-      <c r="S34" s="160"/>
+      <c r="R34" s="159"/>
+      <c r="S34" s="159"/>
     </row>
     <row r="35" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A35" s="23" t="s">
@@ -18281,8 +18282,8 @@
         <v>0</v>
       </c>
       <c r="Q35" s="17"/>
-      <c r="R35" s="160"/>
-      <c r="S35" s="160"/>
+      <c r="R35" s="159"/>
+      <c r="S35" s="159"/>
     </row>
     <row r="36" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A36" s="23" t="s">
@@ -18334,8 +18335,8 @@
         <v>0</v>
       </c>
       <c r="Q36" s="17"/>
-      <c r="R36" s="160"/>
-      <c r="S36" s="160"/>
+      <c r="R36" s="159"/>
+      <c r="S36" s="159"/>
     </row>
     <row r="37" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A37" s="23" t="s">
@@ -18387,8 +18388,8 @@
         <v>0</v>
       </c>
       <c r="Q37" s="17"/>
-      <c r="R37" s="160"/>
-      <c r="S37" s="160"/>
+      <c r="R37" s="159"/>
+      <c r="S37" s="159"/>
     </row>
     <row r="38" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A38" s="23" t="s">
@@ -18440,8 +18441,8 @@
         <v>0</v>
       </c>
       <c r="Q38" s="17"/>
-      <c r="R38" s="160"/>
-      <c r="S38" s="160"/>
+      <c r="R38" s="159"/>
+      <c r="S38" s="159"/>
     </row>
     <row r="39" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
@@ -18493,8 +18494,8 @@
         <v>0</v>
       </c>
       <c r="Q39" s="17"/>
-      <c r="R39" s="160"/>
-      <c r="S39" s="160"/>
+      <c r="R39" s="159"/>
+      <c r="S39" s="159"/>
     </row>
     <row r="40" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A40" s="23" t="s">
@@ -18546,8 +18547,8 @@
         <v>0</v>
       </c>
       <c r="Q40" s="17"/>
-      <c r="R40" s="160"/>
-      <c r="S40" s="160"/>
+      <c r="R40" s="159"/>
+      <c r="S40" s="159"/>
     </row>
     <row r="41" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A41" s="23" t="s">
@@ -18599,8 +18600,8 @@
         <v>0</v>
       </c>
       <c r="Q41" s="17"/>
-      <c r="R41" s="160"/>
-      <c r="S41" s="160"/>
+      <c r="R41" s="159"/>
+      <c r="S41" s="159"/>
     </row>
     <row r="42" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A42" s="23" t="s">
@@ -18652,8 +18653,8 @@
         <v>0</v>
       </c>
       <c r="Q42" s="17"/>
-      <c r="R42" s="160"/>
-      <c r="S42" s="160"/>
+      <c r="R42" s="159"/>
+      <c r="S42" s="159"/>
     </row>
     <row r="43" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A43" s="23" t="s">
@@ -18705,8 +18706,8 @@
         <v>0</v>
       </c>
       <c r="Q43" s="17"/>
-      <c r="R43" s="160"/>
-      <c r="S43" s="160"/>
+      <c r="R43" s="159"/>
+      <c r="S43" s="159"/>
     </row>
     <row r="44" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A44" s="23" t="s">
@@ -18758,8 +18759,8 @@
         <v>0</v>
       </c>
       <c r="Q44" s="17"/>
-      <c r="R44" s="160"/>
-      <c r="S44" s="160"/>
+      <c r="R44" s="159"/>
+      <c r="S44" s="159"/>
     </row>
     <row r="45" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A45" s="23" t="s">
@@ -18811,8 +18812,8 @@
         <v>0</v>
       </c>
       <c r="Q45" s="17"/>
-      <c r="R45" s="160"/>
-      <c r="S45" s="160"/>
+      <c r="R45" s="159"/>
+      <c r="S45" s="159"/>
     </row>
     <row r="46" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A46" s="23" t="s">
@@ -18864,8 +18865,8 @@
         <v>0</v>
       </c>
       <c r="Q46" s="17"/>
-      <c r="R46" s="160"/>
-      <c r="S46" s="160"/>
+      <c r="R46" s="159"/>
+      <c r="S46" s="159"/>
     </row>
     <row r="47" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A47" s="23" t="s">
@@ -18917,8 +18918,8 @@
         <v>0</v>
       </c>
       <c r="Q47" s="17"/>
-      <c r="R47" s="160"/>
-      <c r="S47" s="160"/>
+      <c r="R47" s="159"/>
+      <c r="S47" s="159"/>
     </row>
     <row r="48" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A48" s="23" t="s">
@@ -18970,8 +18971,8 @@
         <v>0</v>
       </c>
       <c r="Q48" s="17"/>
-      <c r="R48" s="160"/>
-      <c r="S48" s="160"/>
+      <c r="R48" s="159"/>
+      <c r="S48" s="159"/>
     </row>
     <row r="49" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A49" s="23" t="s">
@@ -19023,8 +19024,8 @@
         <v>0</v>
       </c>
       <c r="Q49" s="17"/>
-      <c r="R49" s="160"/>
-      <c r="S49" s="160"/>
+      <c r="R49" s="159"/>
+      <c r="S49" s="159"/>
     </row>
     <row r="50" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A50" s="23" t="s">
@@ -19076,8 +19077,8 @@
         <v>0</v>
       </c>
       <c r="Q50" s="17"/>
-      <c r="R50" s="160"/>
-      <c r="S50" s="160"/>
+      <c r="R50" s="159"/>
+      <c r="S50" s="159"/>
     </row>
     <row r="51" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A51" s="23" t="s">
@@ -19129,8 +19130,8 @@
         <v>0</v>
       </c>
       <c r="Q51" s="17"/>
-      <c r="R51" s="160"/>
-      <c r="S51" s="160"/>
+      <c r="R51" s="159"/>
+      <c r="S51" s="159"/>
     </row>
     <row r="52" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A52" s="23" t="s">
@@ -19182,8 +19183,8 @@
         <v>0</v>
       </c>
       <c r="Q52" s="17"/>
-      <c r="R52" s="160"/>
-      <c r="S52" s="160"/>
+      <c r="R52" s="159"/>
+      <c r="S52" s="159"/>
     </row>
     <row r="53" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A53" s="23" t="s">
@@ -19235,8 +19236,8 @@
         <v>0</v>
       </c>
       <c r="Q53" s="17"/>
-      <c r="R53" s="160"/>
-      <c r="S53" s="160"/>
+      <c r="R53" s="159"/>
+      <c r="S53" s="159"/>
     </row>
     <row r="54" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A54" s="23" t="s">
@@ -19288,8 +19289,8 @@
         <v>0</v>
       </c>
       <c r="Q54" s="17"/>
-      <c r="R54" s="160"/>
-      <c r="S54" s="160"/>
+      <c r="R54" s="159"/>
+      <c r="S54" s="159"/>
     </row>
     <row r="55" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A55" s="23" t="s">
@@ -19341,8 +19342,8 @@
         <v>0</v>
       </c>
       <c r="Q55" s="17"/>
-      <c r="R55" s="160"/>
-      <c r="S55" s="160"/>
+      <c r="R55" s="159"/>
+      <c r="S55" s="159"/>
     </row>
     <row r="56" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A56" s="23" t="s">
@@ -19394,8 +19395,8 @@
         <v>0</v>
       </c>
       <c r="Q56" s="17"/>
-      <c r="R56" s="160"/>
-      <c r="S56" s="160"/>
+      <c r="R56" s="159"/>
+      <c r="S56" s="159"/>
     </row>
     <row r="57" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A57" s="23" t="s">
@@ -19447,8 +19448,8 @@
         <v>0</v>
       </c>
       <c r="Q57" s="17"/>
-      <c r="R57" s="160"/>
-      <c r="S57" s="160"/>
+      <c r="R57" s="159"/>
+      <c r="S57" s="159"/>
     </row>
     <row r="58" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A58" s="23" t="s">
@@ -19500,8 +19501,8 @@
         <v>0</v>
       </c>
       <c r="Q58" s="17"/>
-      <c r="R58" s="160"/>
-      <c r="S58" s="160"/>
+      <c r="R58" s="159"/>
+      <c r="S58" s="159"/>
     </row>
     <row r="59" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A59" s="23" t="s">
@@ -19553,8 +19554,8 @@
         <v>0</v>
       </c>
       <c r="Q59" s="17"/>
-      <c r="R59" s="160"/>
-      <c r="S59" s="160"/>
+      <c r="R59" s="159"/>
+      <c r="S59" s="159"/>
     </row>
     <row r="60" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A60" s="23" t="s">
@@ -19606,8 +19607,8 @@
         <v>0</v>
       </c>
       <c r="Q60" s="17"/>
-      <c r="R60" s="160"/>
-      <c r="S60" s="160"/>
+      <c r="R60" s="159"/>
+      <c r="S60" s="159"/>
     </row>
     <row r="61" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
@@ -19659,8 +19660,8 @@
         <v>0</v>
       </c>
       <c r="Q61" s="17"/>
-      <c r="R61" s="160"/>
-      <c r="S61" s="160"/>
+      <c r="R61" s="159"/>
+      <c r="S61" s="159"/>
     </row>
     <row r="62" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A62" s="23" t="s">
@@ -19712,8 +19713,8 @@
         <v>0</v>
       </c>
       <c r="Q62" s="17"/>
-      <c r="R62" s="160"/>
-      <c r="S62" s="160"/>
+      <c r="R62" s="159"/>
+      <c r="S62" s="159"/>
     </row>
     <row r="63" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A63" s="23" t="s">
@@ -19765,8 +19766,8 @@
         <v>0</v>
       </c>
       <c r="Q63" s="17"/>
-      <c r="R63" s="160"/>
-      <c r="S63" s="160"/>
+      <c r="R63" s="159"/>
+      <c r="S63" s="159"/>
     </row>
     <row r="64" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A64" s="23" t="s">
@@ -19818,8 +19819,8 @@
         <v>0</v>
       </c>
       <c r="Q64" s="17"/>
-      <c r="R64" s="160"/>
-      <c r="S64" s="160"/>
+      <c r="R64" s="159"/>
+      <c r="S64" s="159"/>
     </row>
     <row r="65" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A65" s="23" t="s">
@@ -19871,8 +19872,8 @@
         <v>0</v>
       </c>
       <c r="Q65" s="17"/>
-      <c r="R65" s="160"/>
-      <c r="S65" s="160"/>
+      <c r="R65" s="159"/>
+      <c r="S65" s="159"/>
     </row>
     <row r="66" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A66" s="23" t="s">
@@ -19924,8 +19925,8 @@
         <v>0</v>
       </c>
       <c r="Q66" s="17"/>
-      <c r="R66" s="160"/>
-      <c r="S66" s="160"/>
+      <c r="R66" s="159"/>
+      <c r="S66" s="159"/>
     </row>
     <row r="67" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A67" s="23" t="s">
@@ -19977,8 +19978,8 @@
         <v>0</v>
       </c>
       <c r="Q67" s="17"/>
-      <c r="R67" s="160"/>
-      <c r="S67" s="160"/>
+      <c r="R67" s="159"/>
+      <c r="S67" s="159"/>
     </row>
     <row r="68" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A68" s="23" t="s">
@@ -20030,8 +20031,8 @@
         <v>0</v>
       </c>
       <c r="Q68" s="17"/>
-      <c r="R68" s="160"/>
-      <c r="S68" s="160"/>
+      <c r="R68" s="159"/>
+      <c r="S68" s="159"/>
     </row>
     <row r="69" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A69" s="23" t="s">
@@ -20083,8 +20084,8 @@
         <v>0</v>
       </c>
       <c r="Q69" s="17"/>
-      <c r="R69" s="160"/>
-      <c r="S69" s="160"/>
+      <c r="R69" s="159"/>
+      <c r="S69" s="159"/>
     </row>
     <row r="70" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A70" s="23" t="s">
@@ -20136,8 +20137,8 @@
         <v>0</v>
       </c>
       <c r="Q70" s="17"/>
-      <c r="R70" s="160"/>
-      <c r="S70" s="160"/>
+      <c r="R70" s="159"/>
+      <c r="S70" s="159"/>
     </row>
     <row r="71" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A71" s="23" t="s">
@@ -20189,8 +20190,8 @@
         <v>0</v>
       </c>
       <c r="Q71" s="17"/>
-      <c r="R71" s="160"/>
-      <c r="S71" s="160"/>
+      <c r="R71" s="159"/>
+      <c r="S71" s="159"/>
     </row>
     <row r="72" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A72" s="23" t="s">
@@ -20242,8 +20243,8 @@
         <v>0</v>
       </c>
       <c r="Q72" s="17"/>
-      <c r="R72" s="160"/>
-      <c r="S72" s="160"/>
+      <c r="R72" s="159"/>
+      <c r="S72" s="159"/>
     </row>
     <row r="73" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A73" s="23" t="s">
@@ -20295,8 +20296,8 @@
         <v>0</v>
       </c>
       <c r="Q73" s="17"/>
-      <c r="R73" s="160"/>
-      <c r="S73" s="160"/>
+      <c r="R73" s="159"/>
+      <c r="S73" s="159"/>
     </row>
     <row r="74" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A74" s="23" t="s">
@@ -20348,8 +20349,8 @@
         <v>0</v>
       </c>
       <c r="Q74" s="17"/>
-      <c r="R74" s="160"/>
-      <c r="S74" s="160"/>
+      <c r="R74" s="159"/>
+      <c r="S74" s="159"/>
     </row>
     <row r="75" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A75" s="23" t="s">
@@ -20401,8 +20402,8 @@
         <v>0</v>
       </c>
       <c r="Q75" s="17"/>
-      <c r="R75" s="160"/>
-      <c r="S75" s="160"/>
+      <c r="R75" s="159"/>
+      <c r="S75" s="159"/>
     </row>
     <row r="76" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A76" s="23" t="s">
@@ -20454,8 +20455,8 @@
         <v>0</v>
       </c>
       <c r="Q76" s="17"/>
-      <c r="R76" s="160"/>
-      <c r="S76" s="160"/>
+      <c r="R76" s="159"/>
+      <c r="S76" s="159"/>
     </row>
     <row r="77" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A77" s="23" t="s">
@@ -20509,10 +20510,10 @@
       <c r="Q77" s="57">
         <v>46216</v>
       </c>
-      <c r="R77" s="163">
+      <c r="R77" s="162">
         <v>46234</v>
       </c>
-      <c r="S77" s="160" t="s">
+      <c r="S77" s="159" t="s">
         <v>1207</v>
       </c>
     </row>
@@ -20566,10 +20567,10 @@
         <v>0</v>
       </c>
       <c r="Q78" s="17"/>
-      <c r="R78" s="163">
+      <c r="R78" s="162">
         <v>46234</v>
       </c>
-      <c r="S78" s="160" t="s">
+      <c r="S78" s="159" t="s">
         <v>1208</v>
       </c>
     </row>
@@ -20623,10 +20624,10 @@
         <v>0</v>
       </c>
       <c r="Q79" s="17"/>
-      <c r="R79" s="163">
+      <c r="R79" s="162">
         <v>46234</v>
       </c>
-      <c r="S79" s="160" t="s">
+      <c r="S79" s="159" t="s">
         <v>1209</v>
       </c>
     </row>
@@ -20680,10 +20681,10 @@
         <v>0</v>
       </c>
       <c r="Q80" s="17"/>
-      <c r="R80" s="163">
+      <c r="R80" s="162">
         <v>46234</v>
       </c>
-      <c r="S80" s="160" t="s">
+      <c r="S80" s="159" t="s">
         <v>1210</v>
       </c>
     </row>
@@ -20737,10 +20738,10 @@
         <v>0</v>
       </c>
       <c r="Q81" s="17"/>
-      <c r="R81" s="163">
+      <c r="R81" s="162">
         <v>46234</v>
       </c>
-      <c r="S81" s="160" t="s">
+      <c r="S81" s="159" t="s">
         <v>1211</v>
       </c>
     </row>
@@ -20794,10 +20795,10 @@
         <v>0</v>
       </c>
       <c r="Q82" s="17"/>
-      <c r="R82" s="163">
+      <c r="R82" s="162">
         <v>46234</v>
       </c>
-      <c r="S82" s="160" t="s">
+      <c r="S82" s="159" t="s">
         <v>1212</v>
       </c>
     </row>
@@ -20851,10 +20852,10 @@
         <v>0</v>
       </c>
       <c r="Q83" s="17"/>
-      <c r="R83" s="163">
+      <c r="R83" s="162">
         <v>46234</v>
       </c>
-      <c r="S83" s="160" t="s">
+      <c r="S83" s="159" t="s">
         <v>1213</v>
       </c>
     </row>
@@ -20908,10 +20909,10 @@
         <v>0</v>
       </c>
       <c r="Q84" s="17"/>
-      <c r="R84" s="163">
+      <c r="R84" s="162">
         <v>46234</v>
       </c>
-      <c r="S84" s="160" t="s">
+      <c r="S84" s="159" t="s">
         <v>1214</v>
       </c>
     </row>
@@ -20965,10 +20966,10 @@
         <v>0</v>
       </c>
       <c r="Q85" s="17"/>
-      <c r="R85" s="163">
+      <c r="R85" s="162">
         <v>46234</v>
       </c>
-      <c r="S85" s="160" t="s">
+      <c r="S85" s="159" t="s">
         <v>1215</v>
       </c>
     </row>
@@ -21022,10 +21023,10 @@
         <v>0</v>
       </c>
       <c r="Q86" s="17"/>
-      <c r="R86" s="163">
+      <c r="R86" s="162">
         <v>46234</v>
       </c>
-      <c r="S86" s="160" t="s">
+      <c r="S86" s="159" t="s">
         <v>1216</v>
       </c>
     </row>
@@ -21079,10 +21080,10 @@
         <v>0</v>
       </c>
       <c r="Q87" s="17"/>
-      <c r="R87" s="163">
+      <c r="R87" s="162">
         <v>46234</v>
       </c>
-      <c r="S87" s="160" t="s">
+      <c r="S87" s="159" t="s">
         <v>1217</v>
       </c>
     </row>
@@ -21136,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="Q88" s="17"/>
-      <c r="R88" s="163">
+      <c r="R88" s="162">
         <v>46234</v>
       </c>
-      <c r="S88" s="160" t="s">
+      <c r="S88" s="159" t="s">
         <v>1218</v>
       </c>
     </row>
@@ -21190,13 +21191,13 @@
         <v>0</v>
       </c>
       <c r="P89" s="21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="17"/>
-      <c r="R89" s="163">
+      <c r="R89" s="162">
         <v>46234</v>
       </c>
-      <c r="S89" s="160" t="s">
+      <c r="S89" s="159" t="s">
         <v>1219</v>
       </c>
     </row>
@@ -21250,10 +21251,10 @@
         <v>0</v>
       </c>
       <c r="Q90" s="17"/>
-      <c r="R90" s="163">
+      <c r="R90" s="162">
         <v>46234</v>
       </c>
-      <c r="S90" s="160" t="s">
+      <c r="S90" s="159" t="s">
         <v>1220</v>
       </c>
     </row>
@@ -21307,10 +21308,10 @@
         <v>0</v>
       </c>
       <c r="Q91" s="17"/>
-      <c r="R91" s="163">
+      <c r="R91" s="162">
         <v>46234</v>
       </c>
-      <c r="S91" s="160" t="s">
+      <c r="S91" s="159" t="s">
         <v>1221</v>
       </c>
     </row>
@@ -21364,10 +21365,10 @@
         <v>0</v>
       </c>
       <c r="Q92" s="17"/>
-      <c r="R92" s="163">
+      <c r="R92" s="162">
         <v>46234</v>
       </c>
-      <c r="S92" s="160" t="s">
+      <c r="S92" s="159" t="s">
         <v>1222</v>
       </c>
     </row>
@@ -21421,10 +21422,10 @@
         <v>0</v>
       </c>
       <c r="Q93" s="17"/>
-      <c r="R93" s="163">
+      <c r="R93" s="162">
         <v>46204.240972222222</v>
       </c>
-      <c r="S93" s="160">
+      <c r="S93" s="159">
         <v>3.81</v>
       </c>
     </row>
@@ -21478,10 +21479,10 @@
         <v>0</v>
       </c>
       <c r="Q94" s="17"/>
-      <c r="R94" s="163">
+      <c r="R94" s="162">
         <v>46204.455555555556</v>
       </c>
-      <c r="S94" s="160">
+      <c r="S94" s="159">
         <v>11.769</v>
       </c>
     </row>
@@ -21535,10 +21536,10 @@
         <v>0</v>
       </c>
       <c r="Q95" s="57"/>
-      <c r="R95" s="163">
+      <c r="R95" s="162">
         <v>46204.240972222222</v>
       </c>
-      <c r="S95" s="160">
+      <c r="S95" s="159">
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
@@ -21592,10 +21593,10 @@
         <v>0</v>
       </c>
       <c r="Q96" s="17"/>
-      <c r="R96" s="163">
+      <c r="R96" s="162">
         <v>46204.697916666664</v>
       </c>
-      <c r="S96" s="160">
+      <c r="S96" s="159">
         <v>2.952</v>
       </c>
     </row>
@@ -21651,10 +21652,10 @@
       <c r="Q97" s="57">
         <v>46216</v>
       </c>
-      <c r="R97" s="163">
+      <c r="R97" s="162">
         <v>46204.657638888886</v>
       </c>
-      <c r="S97" s="160">
+      <c r="S97" s="159">
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
@@ -21708,10 +21709,10 @@
         <v>0</v>
       </c>
       <c r="Q98" s="17"/>
-      <c r="R98" s="163">
+      <c r="R98" s="162">
         <v>46204.699305555558</v>
       </c>
-      <c r="S98" s="160">
+      <c r="S98" s="159">
         <v>32.673999999999999</v>
       </c>
     </row>
@@ -21765,10 +21766,10 @@
         <v>0</v>
       </c>
       <c r="Q99" s="17"/>
-      <c r="R99" s="163">
+      <c r="R99" s="162">
         <v>46204.657638888886</v>
       </c>
-      <c r="S99" s="160">
+      <c r="S99" s="159">
         <v>4.1719999999999997</v>
       </c>
     </row>
@@ -21822,10 +21823,10 @@
         <v>0</v>
       </c>
       <c r="Q100" s="17"/>
-      <c r="R100" s="163">
+      <c r="R100" s="162">
         <v>46204.459027777775</v>
       </c>
-      <c r="S100" s="160">
+      <c r="S100" s="159">
         <v>4.3360000000000003</v>
       </c>
     </row>
@@ -21879,10 +21880,10 @@
         <v>0</v>
       </c>
       <c r="Q101" s="17"/>
-      <c r="R101" s="163">
+      <c r="R101" s="162">
         <v>46204.329861111109</v>
       </c>
-      <c r="S101" s="160">
+      <c r="S101" s="159">
         <v>4.3209</v>
       </c>
     </row>
@@ -21936,10 +21937,10 @@
         <v>0</v>
       </c>
       <c r="Q102" s="17"/>
-      <c r="R102" s="163">
+      <c r="R102" s="162">
         <v>46204.677083333336</v>
       </c>
-      <c r="S102" s="160">
+      <c r="S102" s="159">
         <v>9.7119999999999997</v>
       </c>
     </row>
@@ -21993,10 +21994,10 @@
         <v>0</v>
       </c>
       <c r="Q103" s="17"/>
-      <c r="R103" s="163">
+      <c r="R103" s="162">
         <v>46204.330555555556</v>
       </c>
-      <c r="S103" s="160">
+      <c r="S103" s="159">
         <v>4.1757999999999997</v>
       </c>
     </row>
@@ -22052,14 +22053,14 @@
       <c r="Q104" s="57">
         <v>46216</v>
       </c>
-      <c r="R104" s="163">
+      <c r="R104" s="162">
         <v>46204.677083333336</v>
       </c>
-      <c r="S104" s="162">
+      <c r="S104" s="161">
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="s">
         <v>139</v>
       </c>
@@ -22103,8 +22104,8 @@
         <v>0</v>
       </c>
       <c r="Q105" s="17"/>
-      <c r="R105" s="160"/>
-      <c r="S105" s="160"/>
+      <c r="R105" s="159"/>
+      <c r="S105" s="159"/>
     </row>
     <row r="106" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A106" s="23" t="s">
@@ -22158,14 +22159,14 @@
       <c r="Q106" s="57">
         <v>46206</v>
       </c>
-      <c r="R106" s="163">
+      <c r="R106" s="162">
         <v>46204.677083333336</v>
       </c>
-      <c r="S106" s="162">
+      <c r="S106" s="161">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="23" t="s">
         <v>141</v>
       </c>
@@ -22209,8 +22210,8 @@
         <v>0</v>
       </c>
       <c r="Q107" s="17"/>
-      <c r="R107" s="160"/>
-      <c r="S107" s="160"/>
+      <c r="R107" s="159"/>
+      <c r="S107" s="159"/>
     </row>
     <row r="108" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A108" s="23" t="s">
@@ -22262,14 +22263,14 @@
         <v>0</v>
       </c>
       <c r="Q108" s="17"/>
-      <c r="R108" s="161">
+      <c r="R108" s="160">
         <v>46204.702777777777</v>
       </c>
-      <c r="S108" s="162">
+      <c r="S108" s="161">
         <v>20.81</v>
       </c>
     </row>
-    <row r="109" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="23" t="s">
         <v>144</v>
       </c>
@@ -22313,8 +22314,8 @@
         <v>0</v>
       </c>
       <c r="Q109" s="17"/>
-      <c r="R109" s="160"/>
-      <c r="S109" s="160"/>
+      <c r="R109" s="159"/>
+      <c r="S109" s="159"/>
     </row>
     <row r="110" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A110" s="23" t="s">
@@ -22368,14 +22369,14 @@
       <c r="Q110" s="57">
         <v>46206</v>
       </c>
-      <c r="R110" s="161">
+      <c r="R110" s="160">
         <v>46204.702777777777</v>
       </c>
-      <c r="S110" s="162">
+      <c r="S110" s="161">
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="23" t="s">
         <v>146</v>
       </c>
@@ -22419,8 +22420,8 @@
         <v>0</v>
       </c>
       <c r="Q111" s="17"/>
-      <c r="R111" s="160"/>
-      <c r="S111" s="160"/>
+      <c r="R111" s="159"/>
+      <c r="S111" s="159"/>
     </row>
     <row r="112" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A112" s="23" t="s">
@@ -22472,14 +22473,14 @@
         <v>0</v>
       </c>
       <c r="Q112" s="17"/>
-      <c r="R112" s="163">
+      <c r="R112" s="162">
         <v>46204.462500000001</v>
       </c>
-      <c r="S112" s="160">
+      <c r="S112" s="159">
         <v>8.8550000000000004</v>
       </c>
     </row>
-    <row r="113" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="23" t="s">
         <v>105</v>
       </c>
@@ -22523,8 +22524,8 @@
         <v>0</v>
       </c>
       <c r="Q113" s="17"/>
-      <c r="R113" s="160"/>
-      <c r="S113" s="160"/>
+      <c r="R113" s="159"/>
+      <c r="S113" s="159"/>
     </row>
     <row r="114" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A114" s="23" t="s">
@@ -22576,14 +22577,14 @@
         <v>0</v>
       </c>
       <c r="Q114" s="17"/>
-      <c r="R114" s="163">
+      <c r="R114" s="162">
         <v>46204.448611111111</v>
       </c>
-      <c r="S114" s="160">
+      <c r="S114" s="159">
         <v>6.4509999999999996</v>
       </c>
     </row>
-    <row r="115" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="23" t="s">
         <v>108</v>
       </c>
@@ -22627,8 +22628,8 @@
         <v>0</v>
       </c>
       <c r="Q115" s="17"/>
-      <c r="R115" s="160"/>
-      <c r="S115" s="160"/>
+      <c r="R115" s="159"/>
+      <c r="S115" s="159"/>
     </row>
     <row r="116" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A116" s="23" t="s">
@@ -22680,14 +22681,14 @@
         <v>0</v>
       </c>
       <c r="Q116" s="17"/>
-      <c r="R116" s="163">
+      <c r="R116" s="162">
         <v>46204.448611111111</v>
       </c>
-      <c r="S116" s="160">
+      <c r="S116" s="159">
         <v>4.7329999999999997</v>
       </c>
     </row>
-    <row r="117" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="23" t="s">
         <v>109</v>
       </c>
@@ -22731,8 +22732,8 @@
         <v>0</v>
       </c>
       <c r="Q117" s="17"/>
-      <c r="R117" s="160"/>
-      <c r="S117" s="160"/>
+      <c r="R117" s="159"/>
+      <c r="S117" s="159"/>
     </row>
     <row r="118" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A118" s="23" t="s">
@@ -22784,14 +22785,14 @@
         <v>0</v>
       </c>
       <c r="Q118" s="17"/>
-      <c r="R118" s="163">
+      <c r="R118" s="162">
         <v>46204.448611111111</v>
       </c>
-      <c r="S118" s="160">
+      <c r="S118" s="159">
         <v>20.442</v>
       </c>
     </row>
-    <row r="119" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="23" t="s">
         <v>111</v>
       </c>
@@ -22835,8 +22836,8 @@
         <v>0</v>
       </c>
       <c r="Q119" s="17"/>
-      <c r="R119" s="160"/>
-      <c r="S119" s="160"/>
+      <c r="R119" s="159"/>
+      <c r="S119" s="159"/>
     </row>
     <row r="120" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A120" s="23" t="s">
@@ -22888,14 +22889,14 @@
         <v>0</v>
       </c>
       <c r="Q120" s="17"/>
-      <c r="R120" s="163">
+      <c r="R120" s="162">
         <v>46204.448611111111</v>
       </c>
-      <c r="S120" s="160">
+      <c r="S120" s="159">
         <v>0.223</v>
       </c>
     </row>
-    <row r="121" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="23" t="s">
         <v>113</v>
       </c>
@@ -22939,8 +22940,8 @@
         <v>0</v>
       </c>
       <c r="Q121" s="17"/>
-      <c r="R121" s="160"/>
-      <c r="S121" s="160"/>
+      <c r="R121" s="159"/>
+      <c r="S121" s="159"/>
     </row>
     <row r="122" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A122" s="23" t="s">
@@ -22992,14 +22993,14 @@
         <v>0</v>
       </c>
       <c r="Q122" s="17"/>
-      <c r="R122" s="163">
+      <c r="R122" s="162">
         <v>46204.448611111111</v>
       </c>
-      <c r="S122" s="160">
+      <c r="S122" s="159">
         <v>7.593</v>
       </c>
     </row>
-    <row r="123" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="23" t="s">
         <v>74</v>
       </c>
@@ -23043,8 +23044,8 @@
         <v>0</v>
       </c>
       <c r="Q123" s="17"/>
-      <c r="R123" s="160"/>
-      <c r="S123" s="160"/>
+      <c r="R123" s="159"/>
+      <c r="S123" s="159"/>
     </row>
     <row r="124" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A124" s="23" t="s">
@@ -23096,14 +23097,14 @@
         <v>0</v>
       </c>
       <c r="Q124" s="17"/>
-      <c r="R124" s="163">
+      <c r="R124" s="162">
         <v>46204.448611111111</v>
       </c>
-      <c r="S124" s="160">
+      <c r="S124" s="159">
         <v>3.8929999999999998</v>
       </c>
     </row>
-    <row r="125" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="23" t="s">
         <v>77</v>
       </c>
@@ -23147,8 +23148,8 @@
         <v>0</v>
       </c>
       <c r="Q125" s="17"/>
-      <c r="R125" s="160"/>
-      <c r="S125" s="160"/>
+      <c r="R125" s="159"/>
+      <c r="S125" s="159"/>
     </row>
     <row r="126" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A126" s="23" t="s">
@@ -23202,14 +23203,14 @@
       <c r="Q126" s="57">
         <v>46206</v>
       </c>
-      <c r="R126" s="163">
+      <c r="R126" s="162">
         <v>46204.448611111111</v>
       </c>
-      <c r="S126" s="160">
+      <c r="S126" s="159">
         <v>1.163</v>
       </c>
     </row>
-    <row r="127" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="23" t="s">
         <v>81</v>
       </c>
@@ -23253,8 +23254,8 @@
         <v>0</v>
       </c>
       <c r="Q127" s="17"/>
-      <c r="R127" s="160"/>
-      <c r="S127" s="160"/>
+      <c r="R127" s="159"/>
+      <c r="S127" s="159"/>
     </row>
     <row r="128" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A128" s="23" t="s">
@@ -23306,14 +23307,14 @@
         <v>0</v>
       </c>
       <c r="Q128" s="17"/>
-      <c r="R128" s="163">
+      <c r="R128" s="162">
         <v>46204.448611111111</v>
       </c>
-      <c r="S128" s="160">
+      <c r="S128" s="159">
         <v>22.7</v>
       </c>
     </row>
-    <row r="129" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="23" t="s">
         <v>83</v>
       </c>
@@ -23357,10 +23358,10 @@
         <v>0</v>
       </c>
       <c r="Q129" s="17"/>
-      <c r="R129" s="160"/>
-      <c r="S129" s="160"/>
-    </row>
-    <row r="130" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R129" s="159"/>
+      <c r="S129" s="159"/>
+    </row>
+    <row r="130" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="23" t="s">
         <v>84</v>
       </c>
@@ -23404,10 +23405,10 @@
         <v>0</v>
       </c>
       <c r="Q130" s="17"/>
-      <c r="R130" s="160"/>
-      <c r="S130" s="160"/>
-    </row>
-    <row r="131" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R130" s="159"/>
+      <c r="S130" s="159"/>
+    </row>
+    <row r="131" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="23" t="s">
         <v>85</v>
       </c>
@@ -23451,10 +23452,10 @@
         <v>0</v>
       </c>
       <c r="Q131" s="17"/>
-      <c r="R131" s="160"/>
-      <c r="S131" s="160"/>
-    </row>
-    <row r="132" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R131" s="159"/>
+      <c r="S131" s="159"/>
+    </row>
+    <row r="132" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="23" t="s">
         <v>86</v>
       </c>
@@ -23498,10 +23499,10 @@
         <v>0</v>
       </c>
       <c r="Q132" s="17"/>
-      <c r="R132" s="160"/>
-      <c r="S132" s="160"/>
-    </row>
-    <row r="133" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R132" s="159"/>
+      <c r="S132" s="159"/>
+    </row>
+    <row r="133" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="23" t="s">
         <v>260</v>
       </c>
@@ -23545,10 +23546,10 @@
         <v>0</v>
       </c>
       <c r="Q133" s="17"/>
-      <c r="R133" s="160"/>
-      <c r="S133" s="160"/>
-    </row>
-    <row r="134" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R133" s="159"/>
+      <c r="S133" s="159"/>
+    </row>
+    <row r="134" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="23" t="s">
         <v>263</v>
       </c>
@@ -23592,10 +23593,10 @@
         <v>0</v>
       </c>
       <c r="Q134" s="17"/>
-      <c r="R134" s="160"/>
-      <c r="S134" s="160"/>
-    </row>
-    <row r="135" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R134" s="159"/>
+      <c r="S134" s="159"/>
+    </row>
+    <row r="135" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="23" t="s">
         <v>264</v>
       </c>
@@ -23639,10 +23640,10 @@
         <v>0</v>
       </c>
       <c r="Q135" s="17"/>
-      <c r="R135" s="160"/>
-      <c r="S135" s="160"/>
-    </row>
-    <row r="136" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R135" s="159"/>
+      <c r="S135" s="159"/>
+    </row>
+    <row r="136" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="23" t="s">
         <v>265</v>
       </c>
@@ -23686,10 +23687,10 @@
         <v>0</v>
       </c>
       <c r="Q136" s="17"/>
-      <c r="R136" s="160"/>
-      <c r="S136" s="160"/>
-    </row>
-    <row r="137" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R136" s="159"/>
+      <c r="S136" s="159"/>
+    </row>
+    <row r="137" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="23" t="s">
         <v>266</v>
       </c>
@@ -23733,10 +23734,10 @@
         <v>0</v>
       </c>
       <c r="Q137" s="17"/>
-      <c r="R137" s="160"/>
-      <c r="S137" s="160"/>
-    </row>
-    <row r="138" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R137" s="159"/>
+      <c r="S137" s="159"/>
+    </row>
+    <row r="138" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="23" t="s">
         <v>267</v>
       </c>
@@ -23780,10 +23781,10 @@
         <v>0</v>
       </c>
       <c r="Q138" s="17"/>
-      <c r="R138" s="160"/>
-      <c r="S138" s="160"/>
-    </row>
-    <row r="139" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R138" s="159"/>
+      <c r="S138" s="159"/>
+    </row>
+    <row r="139" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="23" t="s">
         <v>268</v>
       </c>
@@ -23827,10 +23828,10 @@
         <v>0</v>
       </c>
       <c r="Q139" s="17"/>
-      <c r="R139" s="160"/>
-      <c r="S139" s="160"/>
-    </row>
-    <row r="140" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R139" s="159"/>
+      <c r="S139" s="159"/>
+    </row>
+    <row r="140" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="23" t="s">
         <v>269</v>
       </c>
@@ -23874,10 +23875,10 @@
         <v>0</v>
       </c>
       <c r="Q140" s="17"/>
-      <c r="R140" s="160"/>
-      <c r="S140" s="160"/>
-    </row>
-    <row r="141" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R140" s="159"/>
+      <c r="S140" s="159"/>
+    </row>
+    <row r="141" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="23" t="s">
         <v>35</v>
       </c>
@@ -23921,10 +23922,10 @@
         <v>0</v>
       </c>
       <c r="Q141" s="17"/>
-      <c r="R141" s="160"/>
-      <c r="S141" s="160"/>
-    </row>
-    <row r="142" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R141" s="159"/>
+      <c r="S141" s="159"/>
+    </row>
+    <row r="142" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="23" t="s">
         <v>38</v>
       </c>
@@ -23968,10 +23969,10 @@
         <v>0</v>
       </c>
       <c r="Q142" s="17"/>
-      <c r="R142" s="160"/>
-      <c r="S142" s="160"/>
-    </row>
-    <row r="143" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R142" s="159"/>
+      <c r="S142" s="159"/>
+    </row>
+    <row r="143" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="23" t="s">
         <v>40</v>
       </c>
@@ -24015,10 +24016,10 @@
         <v>0</v>
       </c>
       <c r="Q143" s="17"/>
-      <c r="R143" s="160"/>
-      <c r="S143" s="160"/>
-    </row>
-    <row r="144" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R143" s="159"/>
+      <c r="S143" s="159"/>
+    </row>
+    <row r="144" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="23" t="s">
         <v>41</v>
       </c>
@@ -24062,10 +24063,10 @@
         <v>0</v>
       </c>
       <c r="Q144" s="17"/>
-      <c r="R144" s="160"/>
-      <c r="S144" s="160"/>
-    </row>
-    <row r="145" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R144" s="159"/>
+      <c r="S144" s="159"/>
+    </row>
+    <row r="145" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="23" t="s">
         <v>42</v>
       </c>
@@ -24109,10 +24110,10 @@
         <v>0</v>
       </c>
       <c r="Q145" s="17"/>
-      <c r="R145" s="160"/>
-      <c r="S145" s="160"/>
-    </row>
-    <row r="146" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R145" s="159"/>
+      <c r="S145" s="159"/>
+    </row>
+    <row r="146" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="23" t="s">
         <v>43</v>
       </c>
@@ -24156,10 +24157,10 @@
         <v>0</v>
       </c>
       <c r="Q146" s="17"/>
-      <c r="R146" s="160"/>
-      <c r="S146" s="160"/>
-    </row>
-    <row r="147" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R146" s="159"/>
+      <c r="S146" s="159"/>
+    </row>
+    <row r="147" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="23" t="s">
         <v>45</v>
       </c>
@@ -24203,10 +24204,10 @@
         <v>0</v>
       </c>
       <c r="Q147" s="17"/>
-      <c r="R147" s="160"/>
-      <c r="S147" s="160"/>
-    </row>
-    <row r="148" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R147" s="159"/>
+      <c r="S147" s="159"/>
+    </row>
+    <row r="148" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="23" t="s">
         <v>44</v>
       </c>
@@ -24250,10 +24251,10 @@
         <v>0</v>
       </c>
       <c r="Q148" s="17"/>
-      <c r="R148" s="160"/>
-      <c r="S148" s="160"/>
-    </row>
-    <row r="149" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R148" s="159"/>
+      <c r="S148" s="159"/>
+    </row>
+    <row r="149" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="23" t="s">
         <v>47</v>
       </c>
@@ -24297,10 +24298,10 @@
         <v>0</v>
       </c>
       <c r="Q149" s="17"/>
-      <c r="R149" s="160"/>
-      <c r="S149" s="160"/>
-    </row>
-    <row r="150" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R149" s="159"/>
+      <c r="S149" s="159"/>
+    </row>
+    <row r="150" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="23" t="s">
         <v>48</v>
       </c>
@@ -24344,10 +24345,10 @@
         <v>0</v>
       </c>
       <c r="Q150" s="17"/>
-      <c r="R150" s="160"/>
-      <c r="S150" s="160"/>
-    </row>
-    <row r="151" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R150" s="159"/>
+      <c r="S150" s="159"/>
+    </row>
+    <row r="151" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="23" t="s">
         <v>49</v>
       </c>
@@ -24391,10 +24392,10 @@
         <v>0</v>
       </c>
       <c r="Q151" s="17"/>
-      <c r="R151" s="160"/>
-      <c r="S151" s="160"/>
-    </row>
-    <row r="152" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R151" s="159"/>
+      <c r="S151" s="159"/>
+    </row>
+    <row r="152" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="23" t="s">
         <v>50</v>
       </c>
@@ -24438,10 +24439,10 @@
         <v>0</v>
       </c>
       <c r="Q152" s="17"/>
-      <c r="R152" s="160"/>
-      <c r="S152" s="160"/>
-    </row>
-    <row r="153" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R152" s="159"/>
+      <c r="S152" s="159"/>
+    </row>
+    <row r="153" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="23" t="s">
         <v>51</v>
       </c>
@@ -24485,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="Q153" s="17"/>
-      <c r="R153" s="160"/>
-      <c r="S153" s="160"/>
-    </row>
-    <row r="154" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R153" s="159"/>
+      <c r="S153" s="159"/>
+    </row>
+    <row r="154" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="23" t="s">
         <v>52</v>
       </c>
@@ -24532,10 +24533,10 @@
         <v>0</v>
       </c>
       <c r="Q154" s="17"/>
-      <c r="R154" s="160"/>
-      <c r="S154" s="160"/>
-    </row>
-    <row r="155" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R154" s="159"/>
+      <c r="S154" s="159"/>
+    </row>
+    <row r="155" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="23" t="s">
         <v>53</v>
       </c>
@@ -24579,10 +24580,10 @@
         <v>0</v>
       </c>
       <c r="Q155" s="17"/>
-      <c r="R155" s="160"/>
-      <c r="S155" s="160"/>
-    </row>
-    <row r="156" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R155" s="159"/>
+      <c r="S155" s="159"/>
+    </row>
+    <row r="156" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="23" t="s">
         <v>54</v>
       </c>
@@ -24626,10 +24627,10 @@
         <v>0</v>
       </c>
       <c r="Q156" s="17"/>
-      <c r="R156" s="160"/>
-      <c r="S156" s="160"/>
-    </row>
-    <row r="157" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R156" s="159"/>
+      <c r="S156" s="159"/>
+    </row>
+    <row r="157" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="23" t="s">
         <v>57</v>
       </c>
@@ -24673,10 +24674,10 @@
         <v>0</v>
       </c>
       <c r="Q157" s="17"/>
-      <c r="R157" s="160"/>
-      <c r="S157" s="160"/>
-    </row>
-    <row r="158" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R157" s="159"/>
+      <c r="S157" s="159"/>
+    </row>
+    <row r="158" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="23" t="s">
         <v>58</v>
       </c>
@@ -24720,10 +24721,10 @@
         <v>0</v>
       </c>
       <c r="Q158" s="17"/>
-      <c r="R158" s="160"/>
-      <c r="S158" s="160"/>
-    </row>
-    <row r="159" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R158" s="159"/>
+      <c r="S158" s="159"/>
+    </row>
+    <row r="159" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="23" t="s">
         <v>59</v>
       </c>
@@ -24767,10 +24768,10 @@
         <v>0</v>
       </c>
       <c r="Q159" s="17"/>
-      <c r="R159" s="160"/>
-      <c r="S159" s="160"/>
-    </row>
-    <row r="160" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R159" s="159"/>
+      <c r="S159" s="159"/>
+    </row>
+    <row r="160" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="23" t="s">
         <v>60</v>
       </c>
@@ -24814,10 +24815,10 @@
         <v>0</v>
       </c>
       <c r="Q160" s="17"/>
-      <c r="R160" s="160"/>
-      <c r="S160" s="160"/>
-    </row>
-    <row r="161" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R160" s="159"/>
+      <c r="S160" s="159"/>
+    </row>
+    <row r="161" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="23" t="s">
         <v>61</v>
       </c>
@@ -24861,10 +24862,10 @@
         <v>0</v>
       </c>
       <c r="Q161" s="17"/>
-      <c r="R161" s="160"/>
-      <c r="S161" s="160"/>
-    </row>
-    <row r="162" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R161" s="159"/>
+      <c r="S161" s="159"/>
+    </row>
+    <row r="162" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="23" t="s">
         <v>62</v>
       </c>
@@ -24908,10 +24909,10 @@
         <v>0</v>
       </c>
       <c r="Q162" s="17"/>
-      <c r="R162" s="160"/>
-      <c r="S162" s="160"/>
-    </row>
-    <row r="163" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R162" s="159"/>
+      <c r="S162" s="159"/>
+    </row>
+    <row r="163" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="23" t="s">
         <v>63</v>
       </c>
@@ -24955,10 +24956,10 @@
         <v>0</v>
       </c>
       <c r="Q163" s="17"/>
-      <c r="R163" s="160"/>
-      <c r="S163" s="160"/>
-    </row>
-    <row r="164" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R163" s="159"/>
+      <c r="S163" s="159"/>
+    </row>
+    <row r="164" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="23" t="s">
         <v>87</v>
       </c>
@@ -25002,10 +25003,10 @@
         <v>0</v>
       </c>
       <c r="Q164" s="17"/>
-      <c r="R164" s="160"/>
-      <c r="S164" s="160"/>
-    </row>
-    <row r="165" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R164" s="159"/>
+      <c r="S164" s="159"/>
+    </row>
+    <row r="165" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="23" t="s">
         <v>90</v>
       </c>
@@ -25049,10 +25050,10 @@
         <v>0</v>
       </c>
       <c r="Q165" s="17"/>
-      <c r="R165" s="160"/>
-      <c r="S165" s="160"/>
-    </row>
-    <row r="166" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R165" s="159"/>
+      <c r="S165" s="159"/>
+    </row>
+    <row r="166" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="23" t="s">
         <v>91</v>
       </c>
@@ -25096,10 +25097,10 @@
         <v>0</v>
       </c>
       <c r="Q166" s="17"/>
-      <c r="R166" s="160"/>
-      <c r="S166" s="160"/>
-    </row>
-    <row r="167" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R166" s="159"/>
+      <c r="S166" s="159"/>
+    </row>
+    <row r="167" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="23" t="s">
         <v>92</v>
       </c>
@@ -25143,10 +25144,10 @@
         <v>0</v>
       </c>
       <c r="Q167" s="17"/>
-      <c r="R167" s="160"/>
-      <c r="S167" s="160"/>
-    </row>
-    <row r="168" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R167" s="159"/>
+      <c r="S167" s="159"/>
+    </row>
+    <row r="168" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="23" t="s">
         <v>93</v>
       </c>
@@ -25190,10 +25191,10 @@
         <v>0</v>
       </c>
       <c r="Q168" s="17"/>
-      <c r="R168" s="160"/>
-      <c r="S168" s="160"/>
-    </row>
-    <row r="169" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R168" s="159"/>
+      <c r="S168" s="159"/>
+    </row>
+    <row r="169" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="23" t="s">
         <v>94</v>
       </c>
@@ -25237,10 +25238,10 @@
         <v>0</v>
       </c>
       <c r="Q169" s="17"/>
-      <c r="R169" s="160"/>
-      <c r="S169" s="160"/>
-    </row>
-    <row r="170" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R169" s="159"/>
+      <c r="S169" s="159"/>
+    </row>
+    <row r="170" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="23" t="s">
         <v>95</v>
       </c>
@@ -25284,10 +25285,10 @@
         <v>0</v>
       </c>
       <c r="Q170" s="17"/>
-      <c r="R170" s="160"/>
-      <c r="S170" s="160"/>
-    </row>
-    <row r="171" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R170" s="159"/>
+      <c r="S170" s="159"/>
+    </row>
+    <row r="171" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="23" t="s">
         <v>220</v>
       </c>
@@ -25331,10 +25332,10 @@
         <v>0</v>
       </c>
       <c r="Q171" s="17"/>
-      <c r="R171" s="160"/>
-      <c r="S171" s="160"/>
-    </row>
-    <row r="172" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R171" s="159"/>
+      <c r="S171" s="159"/>
+    </row>
+    <row r="172" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="23" t="s">
         <v>223</v>
       </c>
@@ -25378,10 +25379,10 @@
         <v>0</v>
       </c>
       <c r="Q172" s="17"/>
-      <c r="R172" s="160"/>
-      <c r="S172" s="160"/>
-    </row>
-    <row r="173" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R172" s="159"/>
+      <c r="S172" s="159"/>
+    </row>
+    <row r="173" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="23" t="s">
         <v>224</v>
       </c>
@@ -25425,10 +25426,10 @@
         <v>0</v>
       </c>
       <c r="Q173" s="17"/>
-      <c r="R173" s="160"/>
-      <c r="S173" s="160"/>
-    </row>
-    <row r="174" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R173" s="159"/>
+      <c r="S173" s="159"/>
+    </row>
+    <row r="174" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="23" t="s">
         <v>225</v>
       </c>
@@ -25472,8 +25473,8 @@
         <v>0</v>
       </c>
       <c r="Q174" s="17"/>
-      <c r="R174" s="160"/>
-      <c r="S174" s="160"/>
+      <c r="R174" s="159"/>
+      <c r="S174" s="159"/>
     </row>
     <row r="175" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A175" s="23" t="s">
@@ -25525,8 +25526,8 @@
         <v>0</v>
       </c>
       <c r="Q175" s="17"/>
-      <c r="R175" s="160"/>
-      <c r="S175" s="160"/>
+      <c r="R175" s="159"/>
+      <c r="S175" s="159"/>
     </row>
     <row r="176" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A176" s="23" t="s">
@@ -25578,8 +25579,8 @@
         <v>0</v>
       </c>
       <c r="Q176" s="17"/>
-      <c r="R176" s="160"/>
-      <c r="S176" s="160"/>
+      <c r="R176" s="159"/>
+      <c r="S176" s="159"/>
     </row>
     <row r="177" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A177" s="23" t="s">
@@ -25631,8 +25632,8 @@
         <v>0</v>
       </c>
       <c r="Q177" s="17"/>
-      <c r="R177" s="160"/>
-      <c r="S177" s="160"/>
+      <c r="R177" s="159"/>
+      <c r="S177" s="159"/>
     </row>
     <row r="178" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A178" s="23" t="s">
@@ -25684,8 +25685,8 @@
         <v>0</v>
       </c>
       <c r="Q178" s="17"/>
-      <c r="R178" s="160"/>
-      <c r="S178" s="160"/>
+      <c r="R178" s="159"/>
+      <c r="S178" s="159"/>
     </row>
     <row r="179" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A179" s="23" t="s">
@@ -25737,8 +25738,8 @@
         <v>0</v>
       </c>
       <c r="Q179" s="17"/>
-      <c r="R179" s="160"/>
-      <c r="S179" s="160"/>
+      <c r="R179" s="159"/>
+      <c r="S179" s="159"/>
     </row>
     <row r="180" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A180" s="23" t="s">
@@ -25790,8 +25791,8 @@
         <v>0</v>
       </c>
       <c r="Q180" s="17"/>
-      <c r="R180" s="160"/>
-      <c r="S180" s="160"/>
+      <c r="R180" s="159"/>
+      <c r="S180" s="159"/>
     </row>
     <row r="181" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A181" s="23" t="s">
@@ -25843,10 +25844,10 @@
         <v>0</v>
       </c>
       <c r="Q181" s="17"/>
-      <c r="R181" s="160"/>
-      <c r="S181" s="160"/>
-    </row>
-    <row r="182" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R181" s="159"/>
+      <c r="S181" s="159"/>
+    </row>
+    <row r="182" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="23" t="s">
         <v>219</v>
       </c>
@@ -25890,10 +25891,10 @@
         <v>0</v>
       </c>
       <c r="Q182" s="17"/>
-      <c r="R182" s="160"/>
-      <c r="S182" s="160"/>
-    </row>
-    <row r="183" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="R182" s="159"/>
+      <c r="S182" s="159"/>
+    </row>
+    <row r="183" spans="1:19" ht="21.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="23" t="s">
         <v>64</v>
       </c>
@@ -25937,8 +25938,8 @@
         <v>0</v>
       </c>
       <c r="Q183" s="17"/>
-      <c r="R183" s="160"/>
-      <c r="S183" s="160"/>
+      <c r="R183" s="159"/>
+      <c r="S183" s="159"/>
     </row>
     <row r="184" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A184" s="23" t="s">
@@ -25990,8 +25991,8 @@
         <v>0</v>
       </c>
       <c r="Q184" s="17"/>
-      <c r="R184" s="160"/>
-      <c r="S184" s="160"/>
+      <c r="R184" s="159"/>
+      <c r="S184" s="159"/>
     </row>
     <row r="185" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A185" s="23" t="s">
@@ -26043,8 +26044,8 @@
         <v>0</v>
       </c>
       <c r="Q185" s="17"/>
-      <c r="R185" s="160"/>
-      <c r="S185" s="160"/>
+      <c r="R185" s="159"/>
+      <c r="S185" s="159"/>
     </row>
     <row r="186" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A186" s="23" t="s">
@@ -26096,8 +26097,8 @@
         <v>0</v>
       </c>
       <c r="Q186" s="17"/>
-      <c r="R186" s="160"/>
-      <c r="S186" s="160"/>
+      <c r="R186" s="159"/>
+      <c r="S186" s="159"/>
     </row>
     <row r="187" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A187" s="23" t="s">
@@ -26149,8 +26150,8 @@
         <v>0</v>
       </c>
       <c r="Q187" s="17"/>
-      <c r="R187" s="160"/>
-      <c r="S187" s="160"/>
+      <c r="R187" s="159"/>
+      <c r="S187" s="159"/>
     </row>
     <row r="188" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A188" s="23" t="s">
@@ -26202,8 +26203,8 @@
         <v>0</v>
       </c>
       <c r="Q188" s="17"/>
-      <c r="R188" s="160"/>
-      <c r="S188" s="160"/>
+      <c r="R188" s="159"/>
+      <c r="S188" s="159"/>
     </row>
     <row r="189" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A189" s="23" t="s">
@@ -26255,8 +26256,8 @@
         <v>0</v>
       </c>
       <c r="Q189" s="17"/>
-      <c r="R189" s="160"/>
-      <c r="S189" s="160"/>
+      <c r="R189" s="159"/>
+      <c r="S189" s="159"/>
     </row>
     <row r="190" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A190" s="23" t="s">
@@ -26308,8 +26309,8 @@
         <v>0</v>
       </c>
       <c r="Q190" s="17"/>
-      <c r="R190" s="160"/>
-      <c r="S190" s="160"/>
+      <c r="R190" s="159"/>
+      <c r="S190" s="159"/>
     </row>
     <row r="191" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A191" s="23" t="s">
@@ -26361,8 +26362,8 @@
         <v>0</v>
       </c>
       <c r="Q191" s="17"/>
-      <c r="R191" s="160"/>
-      <c r="S191" s="160"/>
+      <c r="R191" s="159"/>
+      <c r="S191" s="159"/>
     </row>
     <row r="192" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
@@ -26414,8 +26415,8 @@
         <v>0</v>
       </c>
       <c r="Q192" s="17"/>
-      <c r="R192" s="160"/>
-      <c r="S192" s="160"/>
+      <c r="R192" s="159"/>
+      <c r="S192" s="159"/>
     </row>
     <row r="193" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
@@ -26467,8 +26468,8 @@
         <v>0</v>
       </c>
       <c r="Q193" s="17"/>
-      <c r="R193" s="160"/>
-      <c r="S193" s="160"/>
+      <c r="R193" s="159"/>
+      <c r="S193" s="159"/>
     </row>
     <row r="204" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="Q204" s="57">
@@ -26476,6 +26477,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:S193" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N193">
     <sortCondition ref="A2:A193"/>
   </sortState>
@@ -36533,34 +36541,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="163" t="s">
         <v>1170</v>
       </c>
-      <c r="B1" s="164" t="s">
+      <c r="B1" s="163" t="s">
         <v>1171</v>
       </c>
-      <c r="C1" s="164" t="s">
+      <c r="C1" s="163" t="s">
         <v>1172</v>
       </c>
-      <c r="D1" s="165" t="s">
+      <c r="D1" s="164" t="s">
         <v>1173</v>
       </c>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
-      <c r="G1" s="165" t="s">
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="164" t="s">
         <v>1174</v>
       </c>
-      <c r="H1" s="165"/>
-      <c r="I1" s="165"/>
+      <c r="H1" s="164"/>
+      <c r="I1" s="164"/>
       <c r="J1" s="108"/>
       <c r="K1" s="109" t="s">
         <v>1175</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A2" s="164"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
+      <c r="A2" s="163"/>
+      <c r="B2" s="163"/>
+      <c r="C2" s="163"/>
       <c r="D2" s="107" t="s">
         <v>1176</v>
       </c>
@@ -39080,19 +39088,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="163" t="s">
         <v>1197</v>
       </c>
-      <c r="B1" s="164"/>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
-      <c r="G1" s="164"/>
-      <c r="H1" s="164"/>
-      <c r="I1" s="164"/>
-      <c r="J1" s="164"/>
-      <c r="K1" s="164"/>
+      <c r="B1" s="163"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="163"/>
+      <c r="G1" s="163"/>
+      <c r="H1" s="163"/>
+      <c r="I1" s="163"/>
+      <c r="J1" s="163"/>
+      <c r="K1" s="163"/>
     </row>
     <row r="2" spans="1:11" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A2" s="134" t="s">
@@ -39825,16 +39833,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="163" t="s">
         <v>1198</v>
       </c>
-      <c r="B1" s="164"/>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
-      <c r="G1" s="164"/>
-      <c r="H1" s="164"/>
+      <c r="B1" s="163"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="163"/>
+      <c r="G1" s="163"/>
+      <c r="H1" s="163"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="150" t="s">

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3098" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A24925D5-DCAB-4418-88A3-25690234B499}"/>
+  <xr:revisionPtr revIDLastSave="3154" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C3E3831-1778-47D4-B8ED-D86CBD3605A8}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="-8550" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="-8550" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FS Elec" sheetId="4" r:id="rId1"/>
-    <sheet name="FS Water" sheetId="1" r:id="rId2"/>
-    <sheet name="Aprt Elec" sheetId="8" r:id="rId3"/>
-    <sheet name="Aprt Water" sheetId="9" r:id="rId4"/>
-    <sheet name="Kiosk Plan" sheetId="5" r:id="rId5"/>
-    <sheet name="Temp ME162 open and closings" sheetId="2" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId2"/>
+    <sheet name="FS Water" sheetId="1" r:id="rId3"/>
+    <sheet name="Aprt Elec" sheetId="8" r:id="rId4"/>
+    <sheet name="Aprt Water" sheetId="9" r:id="rId5"/>
+    <sheet name="Kiosk Plan" sheetId="5" r:id="rId6"/>
+    <sheet name="Temp ME162 open and closings" sheetId="2" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FS Elec'!$A$1:$T$192</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FS Water'!$A$1:$S$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FS Elec'!$A$1:$U$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'FS Water'!$A$1:$S$193</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4822" uniqueCount="1218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4941" uniqueCount="1235">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -3699,6 +3700,57 @@
   </si>
   <si>
     <t>10172257</t>
+  </si>
+  <si>
+    <t>BO Board serial</t>
+  </si>
+  <si>
+    <t>2cf7f1207290340e</t>
+  </si>
+  <si>
+    <t>2cf7f12073100e80</t>
+  </si>
+  <si>
+    <t>2cf7f12072901cf5</t>
+  </si>
+  <si>
+    <t>2cf7f12073100ebc</t>
+  </si>
+  <si>
+    <t>2cf7f12073100145</t>
+  </si>
+  <si>
+    <t>2cf7f120729029f5</t>
+  </si>
+  <si>
+    <t>2cf7f12073100d7c</t>
+  </si>
+  <si>
+    <t>2cf7f120731005ba</t>
+  </si>
+  <si>
+    <t>2cf7f12072903342</t>
+  </si>
+  <si>
+    <t>2cf7f12072902d37</t>
+  </si>
+  <si>
+    <t>2cf7f12072902ba2</t>
+  </si>
+  <si>
+    <t>2cf7f12073100f68</t>
+  </si>
+  <si>
+    <t>2cf7f12072903334</t>
+  </si>
+  <si>
+    <t>2cf7f12072902d3a</t>
+  </si>
+  <si>
+    <t>2cf7f120729020d2</t>
+  </si>
+  <si>
+    <t>2cf7f12072901fa5</t>
   </si>
 </sst>
 </file>
@@ -5214,7 +5266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB9F803-2DDE-485F-989C-C0688D786923}">
-  <dimension ref="A1:T192"/>
+  <dimension ref="A1:U192"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.3984375" style="5" bestFit="1" customWidth="1"/>
@@ -5228,15 +5280,15 @@
     <col min="9" max="9" width="16.59765625" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26.3984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="27.265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.3984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.86328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.1328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="16.59765625" customWidth="1"/>
+    <col min="14" max="14" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5273,32 +5325,35 @@
       <c r="L1" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="47" t="s">
+      <c r="M1" s="6" t="s">
+        <v>1218</v>
+      </c>
+      <c r="N1" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="O1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="P1" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="Q1" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="22" t="s">
+      <c r="R1" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="22" t="s">
+      <c r="S1" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="T1" s="22" t="s">
         <v>1197</v>
       </c>
-      <c r="T1" s="22" t="s">
+      <c r="U1" s="22" t="s">
         <v>1198</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>18</v>
       </c>
@@ -5336,25 +5391,26 @@
         <v>0</v>
       </c>
       <c r="M2" s="2"/>
-      <c r="N2" s="64" t="s">
+      <c r="N2" s="2"/>
+      <c r="O2" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="65">
+      <c r="P2" s="65">
         <v>46179</v>
       </c>
-      <c r="P2" s="65">
+      <c r="Q2" s="65">
         <v>46186</v>
       </c>
-      <c r="Q2" s="65">
+      <c r="R2" s="65">
         <v>46202</v>
       </c>
-      <c r="R2" s="65">
+      <c r="S2" s="65">
         <v>46207</v>
       </c>
-      <c r="S2" s="136"/>
       <c r="T2" s="136"/>
-    </row>
-    <row r="3" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U2" s="136"/>
+    </row>
+    <row r="3" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>26</v>
       </c>
@@ -5392,25 +5448,26 @@
         <v>0</v>
       </c>
       <c r="M3" s="2"/>
-      <c r="N3" s="64" t="s">
+      <c r="N3" s="2"/>
+      <c r="O3" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="65">
+      <c r="P3" s="65">
         <v>46167</v>
       </c>
-      <c r="P3" s="65">
+      <c r="Q3" s="65">
         <v>46174</v>
       </c>
-      <c r="Q3" s="65">
+      <c r="R3" s="65">
         <v>46188</v>
       </c>
-      <c r="R3" s="65">
+      <c r="S3" s="65">
         <v>46195</v>
       </c>
-      <c r="S3" s="136"/>
       <c r="T3" s="136"/>
-    </row>
-    <row r="4" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U3" s="136"/>
+    </row>
+    <row r="4" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>29</v>
       </c>
@@ -5448,25 +5505,26 @@
         <v>0</v>
       </c>
       <c r="M4" s="2"/>
-      <c r="N4" s="64" t="s">
+      <c r="N4" s="2"/>
+      <c r="O4" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="65">
+      <c r="P4" s="65">
         <v>46179</v>
       </c>
-      <c r="P4" s="65">
+      <c r="Q4" s="65">
         <v>46186</v>
       </c>
-      <c r="Q4" s="65">
+      <c r="R4" s="65">
         <v>46202</v>
       </c>
-      <c r="R4" s="65">
+      <c r="S4" s="65">
         <v>46207</v>
       </c>
-      <c r="S4" s="136"/>
       <c r="T4" s="136"/>
-    </row>
-    <row r="5" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U4" s="136"/>
+    </row>
+    <row r="5" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>31</v>
       </c>
@@ -5504,25 +5562,26 @@
         <v>0</v>
       </c>
       <c r="M5" s="2"/>
-      <c r="N5" s="64" t="s">
+      <c r="N5" s="2"/>
+      <c r="O5" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="65">
+      <c r="P5" s="65">
         <v>46167</v>
       </c>
-      <c r="P5" s="65">
+      <c r="Q5" s="65">
         <v>46174</v>
       </c>
-      <c r="Q5" s="65">
+      <c r="R5" s="65">
         <v>46188</v>
       </c>
-      <c r="R5" s="65">
+      <c r="S5" s="65">
         <v>46195</v>
       </c>
-      <c r="S5" s="136"/>
       <c r="T5" s="136"/>
-    </row>
-    <row r="6" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U5" s="136"/>
+    </row>
+    <row r="6" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>32</v>
       </c>
@@ -5560,25 +5619,26 @@
         <v>0</v>
       </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="64" t="s">
+      <c r="N6" s="2"/>
+      <c r="O6" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="O6" s="65">
+      <c r="P6" s="65">
         <v>46179</v>
       </c>
-      <c r="P6" s="65">
+      <c r="Q6" s="65">
         <v>46186</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="R6" s="65">
         <v>46202</v>
       </c>
-      <c r="R6" s="65">
+      <c r="S6" s="65">
         <v>46207</v>
       </c>
-      <c r="S6" s="136"/>
       <c r="T6" s="136"/>
-    </row>
-    <row r="7" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U6" s="136"/>
+    </row>
+    <row r="7" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>34</v>
       </c>
@@ -5616,25 +5676,26 @@
         <v>0</v>
       </c>
       <c r="M7" s="2"/>
-      <c r="N7" s="64" t="s">
+      <c r="N7" s="2"/>
+      <c r="O7" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="65">
+      <c r="P7" s="65">
         <v>46167</v>
       </c>
-      <c r="P7" s="65">
+      <c r="Q7" s="65">
         <v>46174</v>
       </c>
-      <c r="Q7" s="65">
+      <c r="R7" s="65">
         <v>46188</v>
       </c>
-      <c r="R7" s="65">
+      <c r="S7" s="65">
         <v>46195</v>
       </c>
-      <c r="S7" s="136"/>
       <c r="T7" s="136"/>
-    </row>
-    <row r="8" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U7" s="136"/>
+    </row>
+    <row r="8" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>35</v>
       </c>
@@ -5672,25 +5733,26 @@
         <v>0</v>
       </c>
       <c r="M8" s="2"/>
-      <c r="N8" s="64" t="s">
+      <c r="N8" s="2"/>
+      <c r="O8" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="O8" s="65">
+      <c r="P8" s="65">
         <v>46273</v>
       </c>
-      <c r="P8" s="65">
+      <c r="Q8" s="65">
         <v>46280</v>
       </c>
-      <c r="Q8" s="65">
+      <c r="R8" s="65">
         <v>46295</v>
       </c>
-      <c r="R8" s="65">
+      <c r="S8" s="65">
         <v>46301</v>
       </c>
-      <c r="S8" s="136"/>
       <c r="T8" s="136"/>
-    </row>
-    <row r="9" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U8" s="136"/>
+    </row>
+    <row r="9" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>38</v>
       </c>
@@ -5728,25 +5790,26 @@
         <v>0</v>
       </c>
       <c r="M9" s="2"/>
-      <c r="N9" s="64" t="s">
+      <c r="N9" s="2"/>
+      <c r="O9" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O9" s="65">
+      <c r="P9" s="65">
         <v>46259</v>
       </c>
-      <c r="P9" s="65">
+      <c r="Q9" s="65">
         <v>46266</v>
       </c>
-      <c r="Q9" s="65">
+      <c r="R9" s="65">
         <v>46280</v>
       </c>
-      <c r="R9" s="65">
+      <c r="S9" s="65">
         <v>46286</v>
       </c>
-      <c r="S9" s="136"/>
       <c r="T9" s="136"/>
-    </row>
-    <row r="10" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U9" s="136"/>
+    </row>
+    <row r="10" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>40</v>
       </c>
@@ -5784,25 +5847,26 @@
         <v>0</v>
       </c>
       <c r="M10" s="2"/>
-      <c r="N10" s="64" t="s">
+      <c r="N10" s="2"/>
+      <c r="O10" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="O10" s="65">
+      <c r="P10" s="65">
         <v>46273</v>
       </c>
-      <c r="P10" s="65">
+      <c r="Q10" s="65">
         <v>46280</v>
       </c>
-      <c r="Q10" s="65">
+      <c r="R10" s="65">
         <v>46295</v>
       </c>
-      <c r="R10" s="65">
+      <c r="S10" s="65">
         <v>46301</v>
       </c>
-      <c r="S10" s="136"/>
       <c r="T10" s="136"/>
-    </row>
-    <row r="11" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U10" s="136"/>
+    </row>
+    <row r="11" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>41</v>
       </c>
@@ -5840,25 +5904,26 @@
         <v>0</v>
       </c>
       <c r="M11" s="2"/>
-      <c r="N11" s="64" t="s">
+      <c r="N11" s="2"/>
+      <c r="O11" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="65">
+      <c r="P11" s="65">
         <v>46259</v>
       </c>
-      <c r="P11" s="65">
+      <c r="Q11" s="65">
         <v>46266</v>
       </c>
-      <c r="Q11" s="65">
+      <c r="R11" s="65">
         <v>46280</v>
       </c>
-      <c r="R11" s="65">
+      <c r="S11" s="65">
         <v>46286</v>
       </c>
-      <c r="S11" s="136"/>
       <c r="T11" s="136"/>
-    </row>
-    <row r="12" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U11" s="136"/>
+    </row>
+    <row r="12" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>42</v>
       </c>
@@ -5896,25 +5961,26 @@
         <v>0</v>
       </c>
       <c r="M12" s="2"/>
-      <c r="N12" s="64" t="s">
+      <c r="N12" s="2"/>
+      <c r="O12" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="65">
+      <c r="P12" s="65">
         <v>46273</v>
       </c>
-      <c r="P12" s="65">
+      <c r="Q12" s="65">
         <v>46280</v>
       </c>
-      <c r="Q12" s="65">
+      <c r="R12" s="65">
         <v>46295</v>
       </c>
-      <c r="R12" s="65">
+      <c r="S12" s="65">
         <v>46301</v>
       </c>
-      <c r="S12" s="136"/>
       <c r="T12" s="136"/>
-    </row>
-    <row r="13" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U12" s="136"/>
+    </row>
+    <row r="13" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
         <v>43</v>
       </c>
@@ -5952,25 +6018,26 @@
         <v>0</v>
       </c>
       <c r="M13" s="2"/>
-      <c r="N13" s="64" t="s">
+      <c r="N13" s="2"/>
+      <c r="O13" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="65">
+      <c r="P13" s="65">
         <v>46259</v>
       </c>
-      <c r="P13" s="65">
+      <c r="Q13" s="65">
         <v>46266</v>
       </c>
-      <c r="Q13" s="65">
+      <c r="R13" s="65">
         <v>46280</v>
       </c>
-      <c r="R13" s="65">
+      <c r="S13" s="65">
         <v>46286</v>
       </c>
-      <c r="S13" s="136"/>
       <c r="T13" s="136"/>
-    </row>
-    <row r="14" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U13" s="136"/>
+    </row>
+    <row r="14" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>44</v>
       </c>
@@ -6008,25 +6075,26 @@
         <v>0</v>
       </c>
       <c r="M14" s="2"/>
-      <c r="N14" s="64" t="s">
+      <c r="N14" s="2"/>
+      <c r="O14" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O14" s="65">
+      <c r="P14" s="65">
         <v>46259</v>
       </c>
-      <c r="P14" s="65">
+      <c r="Q14" s="65">
         <v>46266</v>
       </c>
-      <c r="Q14" s="65">
+      <c r="R14" s="65">
         <v>46280</v>
       </c>
-      <c r="R14" s="65">
+      <c r="S14" s="65">
         <v>46286</v>
       </c>
-      <c r="S14" s="136"/>
       <c r="T14" s="136"/>
-    </row>
-    <row r="15" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U14" s="136"/>
+    </row>
+    <row r="15" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>45</v>
       </c>
@@ -6064,25 +6132,26 @@
         <v>0</v>
       </c>
       <c r="M15" s="2"/>
-      <c r="N15" s="64" t="s">
+      <c r="N15" s="2"/>
+      <c r="O15" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="O15" s="65">
+      <c r="P15" s="65">
         <v>46273</v>
       </c>
-      <c r="P15" s="65">
+      <c r="Q15" s="65">
         <v>46280</v>
       </c>
-      <c r="Q15" s="65">
+      <c r="R15" s="65">
         <v>46295</v>
       </c>
-      <c r="R15" s="65">
+      <c r="S15" s="65">
         <v>46301</v>
       </c>
-      <c r="S15" s="136"/>
       <c r="T15" s="136"/>
-    </row>
-    <row r="16" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U15" s="136"/>
+    </row>
+    <row r="16" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>47</v>
       </c>
@@ -6120,25 +6189,26 @@
         <v>0</v>
       </c>
       <c r="M16" s="2"/>
-      <c r="N16" s="64" t="s">
+      <c r="N16" s="2"/>
+      <c r="O16" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="O16" s="65">
+      <c r="P16" s="65">
         <v>46273</v>
       </c>
-      <c r="P16" s="65">
+      <c r="Q16" s="65">
         <v>46280</v>
       </c>
-      <c r="Q16" s="65">
+      <c r="R16" s="65">
         <v>46295</v>
       </c>
-      <c r="R16" s="65">
+      <c r="S16" s="65">
         <v>46301</v>
       </c>
-      <c r="S16" s="136"/>
       <c r="T16" s="136"/>
-    </row>
-    <row r="17" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U16" s="136"/>
+    </row>
+    <row r="17" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
         <v>48</v>
       </c>
@@ -6176,25 +6246,26 @@
         <v>0</v>
       </c>
       <c r="M17" s="2"/>
-      <c r="N17" s="64" t="s">
+      <c r="N17" s="2"/>
+      <c r="O17" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O17" s="65">
+      <c r="P17" s="65">
         <v>46259</v>
       </c>
-      <c r="P17" s="65">
+      <c r="Q17" s="65">
         <v>46266</v>
       </c>
-      <c r="Q17" s="65">
+      <c r="R17" s="65">
         <v>46280</v>
       </c>
-      <c r="R17" s="65">
+      <c r="S17" s="65">
         <v>46286</v>
       </c>
-      <c r="S17" s="136"/>
       <c r="T17" s="136"/>
-    </row>
-    <row r="18" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U17" s="136"/>
+    </row>
+    <row r="18" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>49</v>
       </c>
@@ -6232,25 +6303,26 @@
         <v>0</v>
       </c>
       <c r="M18" s="2"/>
-      <c r="N18" s="64" t="s">
+      <c r="N18" s="2"/>
+      <c r="O18" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="O18" s="65">
+      <c r="P18" s="65">
         <v>46273</v>
       </c>
-      <c r="P18" s="65">
+      <c r="Q18" s="65">
         <v>46280</v>
       </c>
-      <c r="Q18" s="65">
+      <c r="R18" s="65">
         <v>46295</v>
       </c>
-      <c r="R18" s="65">
+      <c r="S18" s="65">
         <v>46301</v>
       </c>
-      <c r="S18" s="136"/>
       <c r="T18" s="136"/>
-    </row>
-    <row r="19" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U18" s="136"/>
+    </row>
+    <row r="19" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
         <v>50</v>
       </c>
@@ -6288,25 +6360,26 @@
         <v>0</v>
       </c>
       <c r="M19" s="2"/>
-      <c r="N19" s="64" t="s">
+      <c r="N19" s="2"/>
+      <c r="O19" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O19" s="65">
+      <c r="P19" s="65">
         <v>46259</v>
       </c>
-      <c r="P19" s="65">
+      <c r="Q19" s="65">
         <v>46266</v>
       </c>
-      <c r="Q19" s="65">
+      <c r="R19" s="65">
         <v>46280</v>
       </c>
-      <c r="R19" s="65">
+      <c r="S19" s="65">
         <v>46286</v>
       </c>
-      <c r="S19" s="136"/>
       <c r="T19" s="136"/>
-    </row>
-    <row r="20" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U19" s="136"/>
+    </row>
+    <row r="20" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>51</v>
       </c>
@@ -6344,25 +6417,26 @@
         <v>0</v>
       </c>
       <c r="M20" s="2"/>
-      <c r="N20" s="64" t="s">
+      <c r="N20" s="2"/>
+      <c r="O20" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="O20" s="65">
+      <c r="P20" s="65">
         <v>46273</v>
       </c>
-      <c r="P20" s="65">
+      <c r="Q20" s="65">
         <v>46280</v>
       </c>
-      <c r="Q20" s="65">
+      <c r="R20" s="65">
         <v>46295</v>
       </c>
-      <c r="R20" s="65">
+      <c r="S20" s="65">
         <v>46301</v>
       </c>
-      <c r="S20" s="136"/>
       <c r="T20" s="136"/>
-    </row>
-    <row r="21" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U20" s="136"/>
+    </row>
+    <row r="21" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
         <v>52</v>
       </c>
@@ -6400,25 +6474,26 @@
         <v>0</v>
       </c>
       <c r="M21" s="2"/>
-      <c r="N21" s="64" t="s">
+      <c r="N21" s="2"/>
+      <c r="O21" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O21" s="65">
+      <c r="P21" s="65">
         <v>46259</v>
       </c>
-      <c r="P21" s="65">
+      <c r="Q21" s="65">
         <v>46266</v>
       </c>
-      <c r="Q21" s="65">
+      <c r="R21" s="65">
         <v>46280</v>
       </c>
-      <c r="R21" s="65">
+      <c r="S21" s="65">
         <v>46286</v>
       </c>
-      <c r="S21" s="136"/>
       <c r="T21" s="136"/>
-    </row>
-    <row r="22" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U21" s="136"/>
+    </row>
+    <row r="22" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>53</v>
       </c>
@@ -6456,25 +6531,26 @@
         <v>0</v>
       </c>
       <c r="M22" s="2"/>
-      <c r="N22" s="64" t="s">
+      <c r="N22" s="2"/>
+      <c r="O22" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="O22" s="65">
+      <c r="P22" s="65">
         <v>46259</v>
       </c>
-      <c r="P22" s="65">
+      <c r="Q22" s="65">
         <v>46266</v>
       </c>
-      <c r="Q22" s="65">
+      <c r="R22" s="65">
         <v>46280</v>
       </c>
-      <c r="R22" s="65">
+      <c r="S22" s="65">
         <v>46286</v>
       </c>
-      <c r="S22" s="136"/>
       <c r="T22" s="136"/>
-    </row>
-    <row r="23" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U22" s="136"/>
+    </row>
+    <row r="23" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>54</v>
       </c>
@@ -6511,28 +6587,29 @@
       <c r="L23" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M23" s="2">
-        <v>1</v>
-      </c>
-      <c r="N23" s="64" t="s">
+      <c r="M23" s="2"/>
+      <c r="N23" s="2">
+        <v>1</v>
+      </c>
+      <c r="O23" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="O23" s="65">
+      <c r="P23" s="65">
         <v>46226</v>
       </c>
-      <c r="P23" s="65">
+      <c r="Q23" s="65">
         <v>46233</v>
       </c>
-      <c r="Q23" s="65">
+      <c r="R23" s="65">
         <v>46248</v>
       </c>
-      <c r="R23" s="65">
+      <c r="S23" s="65">
         <v>46254</v>
       </c>
-      <c r="S23" s="136"/>
       <c r="T23" s="136"/>
-    </row>
-    <row r="24" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U23" s="136"/>
+    </row>
+    <row r="24" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>57</v>
       </c>
@@ -6569,28 +6646,29 @@
       <c r="L24" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M24" s="2">
+      <c r="M24" s="2"/>
+      <c r="N24" s="2">
         <v>7</v>
       </c>
-      <c r="N24" s="64" t="s">
+      <c r="O24" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="O24" s="65">
+      <c r="P24" s="65">
         <v>46226</v>
       </c>
-      <c r="P24" s="65">
+      <c r="Q24" s="65">
         <v>46233</v>
       </c>
-      <c r="Q24" s="65">
+      <c r="R24" s="65">
         <v>46248</v>
       </c>
-      <c r="R24" s="65">
+      <c r="S24" s="65">
         <v>46254</v>
       </c>
-      <c r="S24" s="136"/>
       <c r="T24" s="136"/>
-    </row>
-    <row r="25" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U24" s="136"/>
+    </row>
+    <row r="25" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>58</v>
       </c>
@@ -6627,28 +6705,29 @@
       <c r="L25" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M25" s="2">
+      <c r="M25" s="2"/>
+      <c r="N25" s="2">
         <v>2</v>
       </c>
-      <c r="N25" s="64" t="s">
+      <c r="O25" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="O25" s="65">
+      <c r="P25" s="65">
         <v>46226</v>
       </c>
-      <c r="P25" s="65">
+      <c r="Q25" s="65">
         <v>46233</v>
       </c>
-      <c r="Q25" s="65">
+      <c r="R25" s="65">
         <v>46248</v>
       </c>
-      <c r="R25" s="65">
+      <c r="S25" s="65">
         <v>46254</v>
       </c>
-      <c r="S25" s="136"/>
       <c r="T25" s="136"/>
-    </row>
-    <row r="26" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U25" s="136"/>
+    </row>
+    <row r="26" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>59</v>
       </c>
@@ -6685,28 +6764,29 @@
       <c r="L26" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M26" s="2">
+      <c r="M26" s="2"/>
+      <c r="N26" s="2">
         <v>3</v>
       </c>
-      <c r="N26" s="64" t="s">
+      <c r="O26" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="O26" s="65">
+      <c r="P26" s="65">
         <v>46226</v>
       </c>
-      <c r="P26" s="65">
+      <c r="Q26" s="65">
         <v>46233</v>
       </c>
-      <c r="Q26" s="65">
+      <c r="R26" s="65">
         <v>46248</v>
       </c>
-      <c r="R26" s="65">
+      <c r="S26" s="65">
         <v>46254</v>
       </c>
-      <c r="S26" s="136"/>
       <c r="T26" s="136"/>
-    </row>
-    <row r="27" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U26" s="136"/>
+    </row>
+    <row r="27" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
         <v>60</v>
       </c>
@@ -6743,28 +6823,29 @@
       <c r="L27" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M27" s="2">
+      <c r="M27" s="2"/>
+      <c r="N27" s="2">
         <v>8</v>
       </c>
-      <c r="N27" s="64" t="s">
+      <c r="O27" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="O27" s="65">
+      <c r="P27" s="65">
         <v>46226</v>
       </c>
-      <c r="P27" s="65">
+      <c r="Q27" s="65">
         <v>46233</v>
       </c>
-      <c r="Q27" s="65">
+      <c r="R27" s="65">
         <v>46248</v>
       </c>
-      <c r="R27" s="65">
+      <c r="S27" s="65">
         <v>46254</v>
       </c>
-      <c r="S27" s="136"/>
       <c r="T27" s="136"/>
-    </row>
-    <row r="28" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U27" s="136"/>
+    </row>
+    <row r="28" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>61</v>
       </c>
@@ -6801,28 +6882,29 @@
       <c r="L28" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M28" s="2">
+      <c r="M28" s="2"/>
+      <c r="N28" s="2">
         <v>4</v>
       </c>
-      <c r="N28" s="64" t="s">
+      <c r="O28" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="O28" s="65">
+      <c r="P28" s="65">
         <v>46226</v>
       </c>
-      <c r="P28" s="65">
+      <c r="Q28" s="65">
         <v>46233</v>
       </c>
-      <c r="Q28" s="65">
+      <c r="R28" s="65">
         <v>46248</v>
       </c>
-      <c r="R28" s="65">
+      <c r="S28" s="65">
         <v>46254</v>
       </c>
-      <c r="S28" s="136"/>
       <c r="T28" s="136"/>
-    </row>
-    <row r="29" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U28" s="136"/>
+    </row>
+    <row r="29" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>62</v>
       </c>
@@ -6859,28 +6941,29 @@
       <c r="L29" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M29" s="2">
+      <c r="M29" s="2"/>
+      <c r="N29" s="2">
         <v>5</v>
       </c>
-      <c r="N29" s="64" t="s">
+      <c r="O29" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="O29" s="65">
+      <c r="P29" s="65">
         <v>46226</v>
       </c>
-      <c r="P29" s="65">
+      <c r="Q29" s="65">
         <v>46233</v>
       </c>
-      <c r="Q29" s="65">
+      <c r="R29" s="65">
         <v>46248</v>
       </c>
-      <c r="R29" s="65">
+      <c r="S29" s="65">
         <v>46254</v>
       </c>
-      <c r="S29" s="136"/>
       <c r="T29" s="136"/>
-    </row>
-    <row r="30" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U29" s="136"/>
+    </row>
+    <row r="30" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
         <v>63</v>
       </c>
@@ -6917,28 +7000,29 @@
       <c r="L30" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M30" s="2">
+      <c r="M30" s="2"/>
+      <c r="N30" s="2">
         <v>6</v>
       </c>
-      <c r="N30" s="64" t="s">
+      <c r="O30" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="O30" s="65">
+      <c r="P30" s="65">
         <v>46226</v>
       </c>
-      <c r="P30" s="65">
+      <c r="Q30" s="65">
         <v>46233</v>
       </c>
-      <c r="Q30" s="65">
+      <c r="R30" s="65">
         <v>46248</v>
       </c>
-      <c r="R30" s="65">
+      <c r="S30" s="65">
         <v>46254</v>
       </c>
-      <c r="S30" s="136"/>
       <c r="T30" s="136"/>
-    </row>
-    <row r="31" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U30" s="136"/>
+    </row>
+    <row r="31" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
         <v>64</v>
       </c>
@@ -6975,28 +7059,31 @@
       <c r="L31" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M31" s="2">
-        <v>1</v>
-      </c>
-      <c r="N31" s="64" t="s">
+      <c r="M31" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="N31" s="2">
+        <v>1</v>
+      </c>
+      <c r="O31" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="O31" s="65">
+      <c r="P31" s="65">
         <v>46224</v>
       </c>
-      <c r="P31" s="65">
+      <c r="Q31" s="65">
         <v>46231</v>
       </c>
-      <c r="Q31" s="65">
+      <c r="R31" s="65">
         <v>46246</v>
       </c>
-      <c r="R31" s="65">
+      <c r="S31" s="65">
         <v>46252</v>
       </c>
-      <c r="S31" s="136"/>
       <c r="T31" s="136"/>
-    </row>
-    <row r="32" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U31" s="136"/>
+    </row>
+    <row r="32" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
         <v>68</v>
       </c>
@@ -7033,28 +7120,31 @@
       <c r="L32" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M32" s="2">
+      <c r="M32" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="N32" s="2">
         <v>2</v>
       </c>
-      <c r="N32" s="64" t="s">
+      <c r="O32" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="O32" s="65">
+      <c r="P32" s="65">
         <v>46211</v>
       </c>
-      <c r="P32" s="65">
+      <c r="Q32" s="65">
         <v>46218</v>
       </c>
-      <c r="Q32" s="65">
+      <c r="R32" s="65">
         <v>46232</v>
       </c>
-      <c r="R32" s="65">
+      <c r="S32" s="65">
         <v>46238</v>
       </c>
-      <c r="S32" s="136"/>
       <c r="T32" s="136"/>
-    </row>
-    <row r="33" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U32" s="136"/>
+    </row>
+    <row r="33" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
         <v>70</v>
       </c>
@@ -7091,28 +7181,31 @@
       <c r="L33" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M33" s="2">
+      <c r="M33" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="N33" s="2">
         <v>3</v>
       </c>
-      <c r="N33" s="64" t="s">
+      <c r="O33" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="O33" s="65">
+      <c r="P33" s="65">
         <v>46211</v>
       </c>
-      <c r="P33" s="65">
+      <c r="Q33" s="65">
         <v>46218</v>
       </c>
-      <c r="Q33" s="65">
+      <c r="R33" s="65">
         <v>46232</v>
       </c>
-      <c r="R33" s="65">
+      <c r="S33" s="65">
         <v>46238</v>
       </c>
-      <c r="S33" s="136"/>
       <c r="T33" s="136"/>
-    </row>
-    <row r="34" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U33" s="136"/>
+    </row>
+    <row r="34" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
         <v>71</v>
       </c>
@@ -7149,28 +7242,31 @@
       <c r="L34" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M34" s="2">
+      <c r="M34" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="N34" s="2">
         <v>4</v>
       </c>
-      <c r="N34" s="64" t="s">
+      <c r="O34" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="O34" s="65">
+      <c r="P34" s="65">
         <v>46211</v>
       </c>
-      <c r="P34" s="65">
+      <c r="Q34" s="65">
         <v>46218</v>
       </c>
-      <c r="Q34" s="65">
+      <c r="R34" s="65">
         <v>46232</v>
       </c>
-      <c r="R34" s="65">
+      <c r="S34" s="65">
         <v>46238</v>
       </c>
-      <c r="S34" s="136"/>
       <c r="T34" s="136"/>
-    </row>
-    <row r="35" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U34" s="136"/>
+    </row>
+    <row r="35" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
         <v>72</v>
       </c>
@@ -7207,28 +7303,31 @@
       <c r="L35" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M35" s="2">
+      <c r="M35" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="N35" s="2">
         <v>5</v>
       </c>
-      <c r="N35" s="64" t="s">
+      <c r="O35" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="O35" s="65">
+      <c r="P35" s="65">
         <v>46211</v>
       </c>
-      <c r="P35" s="65">
+      <c r="Q35" s="65">
         <v>46218</v>
       </c>
-      <c r="Q35" s="65">
+      <c r="R35" s="65">
         <v>46232</v>
       </c>
-      <c r="R35" s="65">
+      <c r="S35" s="65">
         <v>46238</v>
       </c>
-      <c r="S35" s="136"/>
       <c r="T35" s="136"/>
-    </row>
-    <row r="36" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U35" s="136"/>
+    </row>
+    <row r="36" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
         <v>73</v>
       </c>
@@ -7265,28 +7364,31 @@
       <c r="L36" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M36" s="2">
+      <c r="M36" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="N36" s="2">
         <v>6</v>
       </c>
-      <c r="N36" s="64" t="s">
+      <c r="O36" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="O36" s="65">
+      <c r="P36" s="65">
         <v>46211</v>
       </c>
-      <c r="P36" s="65">
+      <c r="Q36" s="65">
         <v>46218</v>
       </c>
-      <c r="Q36" s="65">
+      <c r="R36" s="65">
         <v>46232</v>
       </c>
-      <c r="R36" s="65">
+      <c r="S36" s="65">
         <v>46238</v>
       </c>
-      <c r="S36" s="136"/>
       <c r="T36" s="136"/>
-    </row>
-    <row r="37" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U36" s="136"/>
+    </row>
+    <row r="37" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
         <v>74</v>
       </c>
@@ -7323,28 +7425,31 @@
       <c r="L37" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M37" s="2">
+      <c r="M37" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="N37" s="2">
         <v>9</v>
       </c>
-      <c r="N37" s="64" t="s">
+      <c r="O37" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="O37" s="65">
+      <c r="P37" s="65">
         <v>46227</v>
       </c>
-      <c r="P37" s="65">
+      <c r="Q37" s="65">
         <v>46234</v>
       </c>
-      <c r="Q37" s="65">
+      <c r="R37" s="65">
         <v>46249</v>
       </c>
-      <c r="R37" s="65">
+      <c r="S37" s="65">
         <v>46255</v>
       </c>
-      <c r="S37" s="136"/>
       <c r="T37" s="136"/>
-    </row>
-    <row r="38" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U37" s="136"/>
+    </row>
+    <row r="38" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>77</v>
       </c>
@@ -7381,28 +7486,31 @@
       <c r="L38" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M38" s="2">
+      <c r="M38" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="N38" s="2">
         <v>6</v>
       </c>
-      <c r="N38" s="64" t="s">
+      <c r="O38" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="O38" s="65">
+      <c r="P38" s="65">
         <v>46227</v>
       </c>
-      <c r="P38" s="65">
+      <c r="Q38" s="65">
         <v>46234</v>
       </c>
-      <c r="Q38" s="65">
+      <c r="R38" s="65">
         <v>46249</v>
       </c>
-      <c r="R38" s="65">
+      <c r="S38" s="65">
         <v>46255</v>
       </c>
-      <c r="S38" s="136"/>
       <c r="T38" s="136"/>
-    </row>
-    <row r="39" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U38" s="136"/>
+    </row>
+    <row r="39" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
         <v>78</v>
       </c>
@@ -7439,32 +7547,35 @@
       <c r="L39" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M39" s="2">
+      <c r="M39" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="N39" s="2">
         <v>8</v>
       </c>
-      <c r="N39" s="64" t="s">
+      <c r="O39" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="O39" s="65">
+      <c r="P39" s="65">
         <v>46125</v>
       </c>
-      <c r="P39" s="65">
+      <c r="Q39" s="65">
         <v>46132</v>
       </c>
-      <c r="Q39" s="65">
+      <c r="R39" s="65">
         <v>46148</v>
       </c>
-      <c r="R39" s="65">
+      <c r="S39" s="65">
         <v>46154</v>
       </c>
-      <c r="S39" s="137">
+      <c r="T39" s="137">
         <v>46204.652083333334</v>
       </c>
-      <c r="T39" s="138">
+      <c r="U39" s="138">
         <v>36.700000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
         <v>81</v>
       </c>
@@ -7501,28 +7612,31 @@
       <c r="L40" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M40" s="2">
+      <c r="M40" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="N40" s="2">
         <v>5</v>
       </c>
-      <c r="N40" s="64" t="s">
+      <c r="O40" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="O40" s="65">
+      <c r="P40" s="65">
         <v>46227</v>
       </c>
-      <c r="P40" s="65">
+      <c r="Q40" s="65">
         <v>46234</v>
       </c>
-      <c r="Q40" s="65">
+      <c r="R40" s="65">
         <v>46249</v>
       </c>
-      <c r="R40" s="65">
+      <c r="S40" s="65">
         <v>46255</v>
       </c>
-      <c r="S40" s="136"/>
       <c r="T40" s="136"/>
-    </row>
-    <row r="41" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U40" s="136"/>
+    </row>
+    <row r="41" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
         <v>82</v>
       </c>
@@ -7559,32 +7673,35 @@
       <c r="L41" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M41" s="2">
+      <c r="M41" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="N41" s="2">
         <v>7</v>
       </c>
-      <c r="N41" s="64" t="s">
+      <c r="O41" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="O41" s="65">
+      <c r="P41" s="65">
         <v>46125</v>
       </c>
-      <c r="P41" s="65">
+      <c r="Q41" s="65">
         <v>46132</v>
       </c>
-      <c r="Q41" s="65">
+      <c r="R41" s="65">
         <v>46148</v>
       </c>
-      <c r="R41" s="65">
+      <c r="S41" s="65">
         <v>46154</v>
       </c>
-      <c r="S41" s="137">
+      <c r="T41" s="137">
         <v>46204.714583333334</v>
       </c>
-      <c r="T41" s="138">
+      <c r="U41" s="138">
         <v>11.590999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
         <v>83</v>
       </c>
@@ -7621,28 +7738,31 @@
       <c r="L42" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M42" s="2">
+      <c r="M42" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="N42" s="2">
         <v>4</v>
       </c>
-      <c r="N42" s="64" t="s">
+      <c r="O42" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="O42" s="65">
+      <c r="P42" s="65">
         <v>46227</v>
       </c>
-      <c r="P42" s="65">
+      <c r="Q42" s="65">
         <v>46234</v>
       </c>
-      <c r="Q42" s="65">
+      <c r="R42" s="65">
         <v>46249</v>
       </c>
-      <c r="R42" s="65">
+      <c r="S42" s="65">
         <v>46255</v>
       </c>
-      <c r="S42" s="136"/>
       <c r="T42" s="136"/>
-    </row>
-    <row r="43" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U42" s="136"/>
+    </row>
+    <row r="43" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
         <v>84</v>
       </c>
@@ -7679,28 +7799,31 @@
       <c r="L43" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M43" s="2">
+      <c r="M43" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="N43" s="2">
         <v>3</v>
       </c>
-      <c r="N43" s="64" t="s">
+      <c r="O43" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="O43" s="65">
+      <c r="P43" s="65">
         <v>46227</v>
       </c>
-      <c r="P43" s="65">
+      <c r="Q43" s="65">
         <v>46234</v>
       </c>
-      <c r="Q43" s="65">
+      <c r="R43" s="65">
         <v>46249</v>
       </c>
-      <c r="R43" s="65">
+      <c r="S43" s="65">
         <v>46255</v>
       </c>
-      <c r="S43" s="136"/>
       <c r="T43" s="136"/>
-    </row>
-    <row r="44" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U43" s="136"/>
+    </row>
+    <row r="44" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
         <v>85</v>
       </c>
@@ -7737,28 +7860,31 @@
       <c r="L44" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M44" s="2">
+      <c r="M44" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="N44" s="2">
         <v>2</v>
       </c>
-      <c r="N44" s="64" t="s">
+      <c r="O44" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="O44" s="65">
+      <c r="P44" s="65">
         <v>46227</v>
       </c>
-      <c r="P44" s="65">
+      <c r="Q44" s="65">
         <v>46234</v>
       </c>
-      <c r="Q44" s="65">
+      <c r="R44" s="65">
         <v>46249</v>
       </c>
-      <c r="R44" s="65">
+      <c r="S44" s="65">
         <v>46255</v>
       </c>
-      <c r="S44" s="136"/>
       <c r="T44" s="136"/>
-    </row>
-    <row r="45" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U44" s="136"/>
+    </row>
+    <row r="45" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
         <v>86</v>
       </c>
@@ -7795,28 +7921,31 @@
       <c r="L45" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M45" s="2">
-        <v>1</v>
-      </c>
-      <c r="N45" s="64" t="s">
+      <c r="M45" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="N45" s="2">
+        <v>1</v>
+      </c>
+      <c r="O45" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="O45" s="65">
+      <c r="P45" s="65">
         <v>46227</v>
       </c>
-      <c r="P45" s="65">
+      <c r="Q45" s="65">
         <v>46234</v>
       </c>
-      <c r="Q45" s="65">
+      <c r="R45" s="65">
         <v>46249</v>
       </c>
-      <c r="R45" s="65">
+      <c r="S45" s="65">
         <v>46255</v>
       </c>
-      <c r="S45" s="136"/>
       <c r="T45" s="136"/>
-    </row>
-    <row r="46" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U45" s="136"/>
+    </row>
+    <row r="46" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
         <v>87</v>
       </c>
@@ -7853,28 +7982,29 @@
       <c r="L46" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M46" s="2">
+      <c r="M46" s="2"/>
+      <c r="N46" s="2">
         <v>6</v>
       </c>
-      <c r="N46" s="64" t="s">
+      <c r="O46" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="O46" s="65">
+      <c r="P46" s="65">
         <v>46211</v>
       </c>
-      <c r="P46" s="65">
+      <c r="Q46" s="65">
         <v>46218</v>
       </c>
-      <c r="Q46" s="65">
+      <c r="R46" s="65">
         <v>46232</v>
       </c>
-      <c r="R46" s="65">
+      <c r="S46" s="65">
         <v>46238</v>
       </c>
-      <c r="S46" s="136"/>
       <c r="T46" s="136"/>
-    </row>
-    <row r="47" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U46" s="136"/>
+    </row>
+    <row r="47" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
         <v>90</v>
       </c>
@@ -7911,28 +8041,29 @@
       <c r="L47" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M47" s="2">
+      <c r="M47" s="2"/>
+      <c r="N47" s="2">
         <v>3</v>
       </c>
-      <c r="N47" s="64" t="s">
+      <c r="O47" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="O47" s="65">
+      <c r="P47" s="65">
         <v>46211</v>
       </c>
-      <c r="P47" s="65">
+      <c r="Q47" s="65">
         <v>46218</v>
       </c>
-      <c r="Q47" s="65">
+      <c r="R47" s="65">
         <v>46232</v>
       </c>
-      <c r="R47" s="65">
+      <c r="S47" s="65">
         <v>46238</v>
       </c>
-      <c r="S47" s="136"/>
       <c r="T47" s="136"/>
-    </row>
-    <row r="48" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U47" s="136"/>
+    </row>
+    <row r="48" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
         <v>91</v>
       </c>
@@ -7969,28 +8100,29 @@
       <c r="L48" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M48" s="2">
+      <c r="M48" s="2"/>
+      <c r="N48" s="2">
         <v>2</v>
       </c>
-      <c r="N48" s="64" t="s">
+      <c r="O48" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="O48" s="65">
+      <c r="P48" s="65">
         <v>46211</v>
       </c>
-      <c r="P48" s="65">
+      <c r="Q48" s="65">
         <v>46218</v>
       </c>
-      <c r="Q48" s="65">
+      <c r="R48" s="65">
         <v>46232</v>
       </c>
-      <c r="R48" s="65">
+      <c r="S48" s="65">
         <v>46238</v>
       </c>
-      <c r="S48" s="136"/>
       <c r="T48" s="136"/>
-    </row>
-    <row r="49" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U48" s="136"/>
+    </row>
+    <row r="49" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
         <v>92</v>
       </c>
@@ -8027,28 +8159,29 @@
       <c r="L49" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M49" s="2">
-        <v>1</v>
-      </c>
-      <c r="N49" s="64" t="s">
+      <c r="M49" s="2"/>
+      <c r="N49" s="2">
+        <v>1</v>
+      </c>
+      <c r="O49" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="O49" s="65">
+      <c r="P49" s="65">
         <v>46211</v>
       </c>
-      <c r="P49" s="65">
+      <c r="Q49" s="65">
         <v>46218</v>
       </c>
-      <c r="Q49" s="65">
+      <c r="R49" s="65">
         <v>46232</v>
       </c>
-      <c r="R49" s="65">
+      <c r="S49" s="65">
         <v>46238</v>
       </c>
-      <c r="S49" s="136"/>
       <c r="T49" s="136"/>
-    </row>
-    <row r="50" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U49" s="136"/>
+    </row>
+    <row r="50" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
         <v>93</v>
       </c>
@@ -8085,28 +8218,29 @@
       <c r="L50" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M50" s="2">
+      <c r="M50" s="2"/>
+      <c r="N50" s="2">
         <v>5</v>
       </c>
-      <c r="N50" s="64" t="s">
+      <c r="O50" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="O50" s="65">
+      <c r="P50" s="65">
         <v>46211</v>
       </c>
-      <c r="P50" s="65">
+      <c r="Q50" s="65">
         <v>46218</v>
       </c>
-      <c r="Q50" s="65">
+      <c r="R50" s="65">
         <v>46232</v>
       </c>
-      <c r="R50" s="65">
+      <c r="S50" s="65">
         <v>46238</v>
       </c>
-      <c r="S50" s="136"/>
       <c r="T50" s="136"/>
-    </row>
-    <row r="51" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U50" s="136"/>
+    </row>
+    <row r="51" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
         <v>94</v>
       </c>
@@ -8143,28 +8277,29 @@
       <c r="L51" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M51" s="2">
+      <c r="M51" s="2"/>
+      <c r="N51" s="2">
         <v>7</v>
       </c>
-      <c r="N51" s="64" t="s">
+      <c r="O51" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="O51" s="65">
+      <c r="P51" s="65">
         <v>46211</v>
       </c>
-      <c r="P51" s="65">
+      <c r="Q51" s="65">
         <v>46218</v>
       </c>
-      <c r="Q51" s="65">
+      <c r="R51" s="65">
         <v>46232</v>
       </c>
-      <c r="R51" s="65">
+      <c r="S51" s="65">
         <v>46238</v>
       </c>
-      <c r="S51" s="136"/>
       <c r="T51" s="136"/>
-    </row>
-    <row r="52" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U51" s="136"/>
+    </row>
+    <row r="52" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
         <v>95</v>
       </c>
@@ -8201,28 +8336,29 @@
       <c r="L52" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M52" s="2">
+      <c r="M52" s="2"/>
+      <c r="N52" s="2">
         <v>4</v>
       </c>
-      <c r="N52" s="64" t="s">
+      <c r="O52" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="O52" s="65">
+      <c r="P52" s="65">
         <v>46211</v>
       </c>
-      <c r="P52" s="65">
+      <c r="Q52" s="65">
         <v>46218</v>
       </c>
-      <c r="Q52" s="65">
+      <c r="R52" s="65">
         <v>46232</v>
       </c>
-      <c r="R52" s="65">
+      <c r="S52" s="65">
         <v>46238</v>
       </c>
-      <c r="S52" s="136"/>
       <c r="T52" s="136"/>
-    </row>
-    <row r="53" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U52" s="136"/>
+    </row>
+    <row r="53" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
         <v>96</v>
       </c>
@@ -8259,32 +8395,35 @@
       <c r="L53" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M53" s="2">
+      <c r="M53" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="N53" s="2">
         <v>3</v>
       </c>
-      <c r="N53" s="64" t="s">
+      <c r="O53" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="O53" s="65">
+      <c r="P53" s="65">
         <v>46190</v>
       </c>
-      <c r="P53" s="65">
+      <c r="Q53" s="65">
         <v>46197</v>
       </c>
-      <c r="Q53" s="65">
+      <c r="R53" s="65">
         <v>46211</v>
       </c>
-      <c r="R53" s="65">
+      <c r="S53" s="65">
         <v>46217</v>
       </c>
-      <c r="S53" s="139">
+      <c r="T53" s="139">
         <v>46234</v>
       </c>
-      <c r="T53" s="136" t="s">
+      <c r="U53" s="136" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
         <v>99</v>
       </c>
@@ -8321,32 +8460,35 @@
       <c r="L54" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M54" s="2">
+      <c r="M54" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="N54" s="2">
         <v>4</v>
       </c>
-      <c r="N54" s="64" t="s">
+      <c r="O54" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="O54" s="65">
+      <c r="P54" s="65">
         <v>46190</v>
       </c>
-      <c r="P54" s="65">
+      <c r="Q54" s="65">
         <v>46197</v>
       </c>
-      <c r="Q54" s="65">
+      <c r="R54" s="65">
         <v>46211</v>
       </c>
-      <c r="R54" s="65">
+      <c r="S54" s="65">
         <v>46217</v>
       </c>
-      <c r="S54" s="139">
+      <c r="T54" s="139">
         <v>46234</v>
       </c>
-      <c r="T54" s="136" t="s">
+      <c r="U54" s="136" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
         <v>100</v>
       </c>
@@ -8383,32 +8525,35 @@
       <c r="L55" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M55" s="2">
+      <c r="M55" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="N55" s="2">
         <v>5</v>
       </c>
-      <c r="N55" s="64" t="s">
+      <c r="O55" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="O55" s="65">
+      <c r="P55" s="65">
         <v>46190</v>
       </c>
-      <c r="P55" s="65">
+      <c r="Q55" s="65">
         <v>46197</v>
       </c>
-      <c r="Q55" s="65">
+      <c r="R55" s="65">
         <v>46211</v>
       </c>
-      <c r="R55" s="65">
+      <c r="S55" s="65">
         <v>46217</v>
       </c>
-      <c r="S55" s="139">
+      <c r="T55" s="139">
         <v>46234</v>
       </c>
-      <c r="T55" s="136" t="s">
+      <c r="U55" s="136" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>101</v>
       </c>
@@ -8445,43 +8590,46 @@
       <c r="L56" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M56" s="2">
-        <v>1</v>
-      </c>
-      <c r="N56" s="64" t="s">
+      <c r="M56" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="N56" s="2">
+        <v>1</v>
+      </c>
+      <c r="O56" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="O56" s="65">
+      <c r="P56" s="65">
         <v>46190</v>
       </c>
-      <c r="P56" s="65">
+      <c r="Q56" s="65">
         <v>46197</v>
       </c>
-      <c r="Q56" s="65">
+      <c r="R56" s="65">
         <v>46211</v>
       </c>
-      <c r="R56" s="65">
+      <c r="S56" s="65">
         <v>46217</v>
       </c>
-      <c r="S56" s="139">
+      <c r="T56" s="139">
         <v>46234</v>
       </c>
-      <c r="T56" s="136" t="s">
+      <c r="U56" s="136" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>102</v>
+        <v>240</v>
       </c>
       <c r="B57" s="26" t="s">
         <v>65</v>
       </c>
       <c r="C57" s="2">
-        <v>14558069291</v>
+        <v>14558068806</v>
       </c>
       <c r="D57" s="2">
-        <v>82929684</v>
+        <v>71205556</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>20</v>
@@ -8492,8 +8640,8 @@
       <c r="G57" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H57" s="7" t="s">
-        <v>23</v>
+      <c r="H57" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="I57" s="42" t="s">
         <v>97</v>
@@ -8507,36 +8655,43 @@
       <c r="L57" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M57" s="2">
-        <v>6</v>
-      </c>
-      <c r="N57" s="64" t="s">
-        <v>69</v>
-      </c>
-      <c r="O57" s="65">
-        <v>46211</v>
+      <c r="M57" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="N57" s="2">
+        <v>8</v>
+      </c>
+      <c r="O57" s="64" t="s">
+        <v>242</v>
       </c>
       <c r="P57" s="65">
-        <v>46218</v>
+        <v>46175</v>
       </c>
       <c r="Q57" s="65">
-        <v>46232</v>
+        <v>46182</v>
       </c>
       <c r="R57" s="65">
-        <v>46238</v>
-      </c>
-      <c r="S57" s="136"/>
-      <c r="T57" s="136"/>
-    </row>
-    <row r="58" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+        <v>46197</v>
+      </c>
+      <c r="S57" s="65">
+        <v>46203</v>
+      </c>
+      <c r="T57" s="139">
+        <v>46234</v>
+      </c>
+      <c r="U57" s="136" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B58" s="26" t="s">
         <v>65</v>
       </c>
       <c r="C58" s="2">
-        <v>14558069036</v>
+        <v>14558069291</v>
       </c>
       <c r="D58" s="2">
         <v>82929684</v>
@@ -8550,8 +8705,8 @@
       <c r="G58" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H58" s="2" t="s">
-        <v>30</v>
+      <c r="H58" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="I58" s="42" t="s">
         <v>97</v>
@@ -8565,36 +8720,39 @@
       <c r="L58" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M58" s="2">
-        <v>7</v>
-      </c>
-      <c r="N58" s="64" t="s">
+      <c r="M58" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="N58" s="2">
+        <v>6</v>
+      </c>
+      <c r="O58" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="O58" s="65">
+      <c r="P58" s="65">
         <v>46211</v>
       </c>
-      <c r="P58" s="65">
+      <c r="Q58" s="65">
         <v>46218</v>
       </c>
-      <c r="Q58" s="65">
+      <c r="R58" s="65">
         <v>46232</v>
       </c>
-      <c r="R58" s="65">
+      <c r="S58" s="65">
         <v>46238</v>
       </c>
-      <c r="S58" s="136"/>
       <c r="T58" s="136"/>
-    </row>
-    <row r="59" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U58" s="136"/>
+    </row>
+    <row r="59" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B59" s="26" t="s">
         <v>65</v>
       </c>
       <c r="C59" s="2">
-        <v>14558068897</v>
+        <v>14558069036</v>
       </c>
       <c r="D59" s="2">
         <v>82929684</v>
@@ -8608,8 +8766,8 @@
       <c r="G59" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H59" s="8" t="s">
-        <v>33</v>
+      <c r="H59" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="I59" s="42" t="s">
         <v>97</v>
@@ -8623,39 +8781,42 @@
       <c r="L59" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M59" s="2">
-        <v>2</v>
-      </c>
-      <c r="N59" s="64" t="s">
+      <c r="M59" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="N59" s="2">
+        <v>7</v>
+      </c>
+      <c r="O59" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="O59" s="65">
+      <c r="P59" s="65">
         <v>46211</v>
       </c>
-      <c r="P59" s="65">
+      <c r="Q59" s="65">
         <v>46218</v>
       </c>
-      <c r="Q59" s="65">
+      <c r="R59" s="65">
         <v>46232</v>
       </c>
-      <c r="R59" s="65">
+      <c r="S59" s="65">
         <v>46238</v>
       </c>
-      <c r="S59" s="136"/>
       <c r="T59" s="136"/>
-    </row>
-    <row r="60" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U59" s="136"/>
+    </row>
+    <row r="60" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
-        <v>240</v>
+        <v>104</v>
       </c>
       <c r="B60" s="26" t="s">
         <v>65</v>
       </c>
       <c r="C60" s="2">
-        <v>14558068806</v>
+        <v>14558068897</v>
       </c>
       <c r="D60" s="2">
-        <v>71205556</v>
+        <v>82929684</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>20</v>
@@ -8681,32 +8842,31 @@
       <c r="L60" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M60" s="2">
-        <v>8</v>
-      </c>
-      <c r="N60" s="64" t="s">
-        <v>242</v>
-      </c>
-      <c r="O60" s="65">
-        <v>46175</v>
+      <c r="M60" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="N60" s="2">
+        <v>2</v>
+      </c>
+      <c r="O60" s="64" t="s">
+        <v>69</v>
       </c>
       <c r="P60" s="65">
-        <v>46182</v>
+        <v>46211</v>
       </c>
       <c r="Q60" s="65">
-        <v>46197</v>
+        <v>46218</v>
       </c>
       <c r="R60" s="65">
-        <v>46203</v>
-      </c>
-      <c r="S60" s="139">
-        <v>46234</v>
-      </c>
-      <c r="T60" s="136" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+        <v>46232</v>
+      </c>
+      <c r="S60" s="65">
+        <v>46238</v>
+      </c>
+      <c r="T60" s="136"/>
+      <c r="U60" s="136"/>
+    </row>
+    <row r="61" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
         <v>105</v>
       </c>
@@ -8743,28 +8903,31 @@
       <c r="L61" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M61" s="2">
+      <c r="M61" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="N61" s="2">
         <v>9</v>
       </c>
-      <c r="N61" s="64" t="s">
+      <c r="O61" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="O61" s="65">
+      <c r="P61" s="65">
         <v>46213</v>
       </c>
-      <c r="P61" s="65">
+      <c r="Q61" s="65">
         <v>46220</v>
       </c>
-      <c r="Q61" s="65">
+      <c r="R61" s="65">
         <v>46234</v>
       </c>
-      <c r="R61" s="65">
+      <c r="S61" s="65">
         <v>46240</v>
       </c>
-      <c r="S61" s="136"/>
       <c r="T61" s="136"/>
-    </row>
-    <row r="62" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U61" s="136"/>
+    </row>
+    <row r="62" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
         <v>108</v>
       </c>
@@ -8801,28 +8964,31 @@
       <c r="L62" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M62" s="2">
+      <c r="M62" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="N62" s="2">
         <v>8</v>
       </c>
-      <c r="N62" s="64" t="s">
+      <c r="O62" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="O62" s="65">
+      <c r="P62" s="65">
         <v>46213</v>
       </c>
-      <c r="P62" s="65">
+      <c r="Q62" s="65">
         <v>46220</v>
       </c>
-      <c r="Q62" s="65">
+      <c r="R62" s="65">
         <v>46234</v>
       </c>
-      <c r="R62" s="65">
+      <c r="S62" s="65">
         <v>46240</v>
       </c>
-      <c r="S62" s="136"/>
       <c r="T62" s="136"/>
-    </row>
-    <row r="63" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U62" s="136"/>
+    </row>
+    <row r="63" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A63" s="12" t="s">
         <v>109</v>
       </c>
@@ -8859,28 +9025,31 @@
       <c r="L63" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M63" s="2">
+      <c r="M63" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="N63" s="2">
         <v>7</v>
       </c>
-      <c r="N63" s="64" t="s">
+      <c r="O63" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="O63" s="65">
+      <c r="P63" s="65">
         <v>46213</v>
       </c>
-      <c r="P63" s="65">
+      <c r="Q63" s="65">
         <v>46220</v>
       </c>
-      <c r="Q63" s="65">
+      <c r="R63" s="65">
         <v>46234</v>
       </c>
-      <c r="R63" s="65">
+      <c r="S63" s="65">
         <v>46240</v>
       </c>
-      <c r="S63" s="136"/>
       <c r="T63" s="136"/>
-    </row>
-    <row r="64" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U63" s="136"/>
+    </row>
+    <row r="64" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A64" s="12" t="s">
         <v>110</v>
       </c>
@@ -8917,32 +9086,35 @@
       <c r="L64" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M64" s="2">
+      <c r="M64" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="N64" s="2">
         <v>4</v>
       </c>
-      <c r="N64" s="64" t="s">
+      <c r="O64" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="O64" s="65">
+      <c r="P64" s="65">
         <v>46125</v>
       </c>
-      <c r="P64" s="65">
+      <c r="Q64" s="65">
         <v>46132</v>
       </c>
-      <c r="Q64" s="65">
+      <c r="R64" s="65">
         <v>46148</v>
       </c>
-      <c r="R64" s="65">
+      <c r="S64" s="65">
         <v>46154</v>
       </c>
-      <c r="S64" s="137">
+      <c r="T64" s="137">
         <v>46204.425000000003</v>
       </c>
-      <c r="T64" s="138">
+      <c r="U64" s="138">
         <v>19.7</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A65" s="12" t="s">
         <v>111</v>
       </c>
@@ -8979,28 +9151,31 @@
       <c r="L65" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M65" s="2">
+      <c r="M65" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="N65" s="2">
         <v>6</v>
       </c>
-      <c r="N65" s="64" t="s">
+      <c r="O65" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="O65" s="65">
+      <c r="P65" s="65">
         <v>46213</v>
       </c>
-      <c r="P65" s="65">
+      <c r="Q65" s="65">
         <v>46220</v>
       </c>
-      <c r="Q65" s="65">
+      <c r="R65" s="65">
         <v>46234</v>
       </c>
-      <c r="R65" s="65">
+      <c r="S65" s="65">
         <v>46240</v>
       </c>
-      <c r="S65" s="136"/>
       <c r="T65" s="136"/>
-    </row>
-    <row r="66" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U65" s="136"/>
+    </row>
+    <row r="66" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
         <v>112</v>
       </c>
@@ -9037,32 +9212,35 @@
       <c r="L66" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M66" s="2">
+      <c r="M66" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="N66" s="2">
         <v>3</v>
       </c>
-      <c r="N66" s="64" t="s">
+      <c r="O66" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="O66" s="65">
+      <c r="P66" s="65">
         <v>46125</v>
       </c>
-      <c r="P66" s="65">
+      <c r="Q66" s="65">
         <v>46132</v>
       </c>
-      <c r="Q66" s="65">
+      <c r="R66" s="65">
         <v>46148</v>
       </c>
-      <c r="R66" s="65">
+      <c r="S66" s="65">
         <v>46154</v>
       </c>
-      <c r="S66" s="137">
+      <c r="T66" s="137">
         <v>46204.704861111109</v>
       </c>
-      <c r="T66" s="138">
+      <c r="U66" s="138">
         <v>39.33</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A67" s="12" t="s">
         <v>113</v>
       </c>
@@ -9099,28 +9277,31 @@
       <c r="L67" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M67" s="2">
+      <c r="M67" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="N67" s="2">
         <v>5</v>
       </c>
-      <c r="N67" s="64" t="s">
+      <c r="O67" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="O67" s="65">
+      <c r="P67" s="65">
         <v>46227</v>
       </c>
-      <c r="P67" s="65">
+      <c r="Q67" s="65">
         <v>46234</v>
       </c>
-      <c r="Q67" s="65">
+      <c r="R67" s="65">
         <v>46249</v>
       </c>
-      <c r="R67" s="65">
+      <c r="S67" s="65">
         <v>46255</v>
       </c>
-      <c r="S67" s="136"/>
       <c r="T67" s="136"/>
-    </row>
-    <row r="68" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U67" s="136"/>
+    </row>
+    <row r="68" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
         <v>114</v>
       </c>
@@ -9157,32 +9338,35 @@
       <c r="L68" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M68" s="2">
+      <c r="M68" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="N68" s="2">
         <v>2</v>
       </c>
-      <c r="N68" s="64" t="s">
+      <c r="O68" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="O68" s="65">
+      <c r="P68" s="65">
         <v>46125</v>
       </c>
-      <c r="P68" s="65">
+      <c r="Q68" s="65">
         <v>46132</v>
       </c>
-      <c r="Q68" s="65">
+      <c r="R68" s="65">
         <v>46148</v>
       </c>
-      <c r="R68" s="65">
+      <c r="S68" s="65">
         <v>46154</v>
       </c>
-      <c r="S68" s="137">
+      <c r="T68" s="137">
         <v>46204.424305555556</v>
       </c>
-      <c r="T68" s="138">
+      <c r="U68" s="138">
         <v>35.67</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A69" s="12" t="s">
         <v>115</v>
       </c>
@@ -9219,32 +9403,35 @@
       <c r="L69" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M69" s="2">
-        <v>1</v>
-      </c>
-      <c r="N69" s="64" t="s">
+      <c r="M69" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="N69" s="2">
+        <v>1</v>
+      </c>
+      <c r="O69" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="O69" s="65">
+      <c r="P69" s="65">
         <v>46125</v>
       </c>
-      <c r="P69" s="65">
+      <c r="Q69" s="65">
         <v>46132</v>
       </c>
-      <c r="Q69" s="65">
+      <c r="R69" s="65">
         <v>46148</v>
       </c>
-      <c r="R69" s="65">
+      <c r="S69" s="65">
         <v>46154</v>
       </c>
-      <c r="S69" s="137">
+      <c r="T69" s="137">
         <v>46204.657638888886</v>
       </c>
-      <c r="T69" s="138">
+      <c r="U69" s="138">
         <v>37.427999999999997</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>116</v>
       </c>
@@ -9281,28 +9468,31 @@
       <c r="L70" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M70" s="2">
-        <v>1</v>
-      </c>
-      <c r="N70" s="64" t="s">
+      <c r="M70" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="N70" s="2">
+        <v>1</v>
+      </c>
+      <c r="O70" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="O70" s="65">
+      <c r="P70" s="65">
         <v>46273</v>
       </c>
-      <c r="P70" s="65">
+      <c r="Q70" s="65">
         <v>46280</v>
       </c>
-      <c r="Q70" s="65">
+      <c r="R70" s="65">
         <v>46295</v>
       </c>
-      <c r="R70" s="65">
+      <c r="S70" s="65">
         <v>46301</v>
       </c>
-      <c r="S70" s="136"/>
       <c r="T70" s="136"/>
-    </row>
-    <row r="71" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U70" s="136"/>
+    </row>
+    <row r="71" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A71" s="12" t="s">
         <v>119</v>
       </c>
@@ -9339,28 +9529,31 @@
       <c r="L71" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M71" s="2">
+      <c r="M71" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="N71" s="2">
         <v>2</v>
       </c>
-      <c r="N71" s="64" t="s">
+      <c r="O71" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="O71" s="65">
+      <c r="P71" s="65">
         <v>46273</v>
       </c>
-      <c r="P71" s="65">
+      <c r="Q71" s="65">
         <v>46280</v>
       </c>
-      <c r="Q71" s="65">
+      <c r="R71" s="65">
         <v>46295</v>
       </c>
-      <c r="R71" s="65">
+      <c r="S71" s="65">
         <v>46301</v>
       </c>
-      <c r="S71" s="136"/>
       <c r="T71" s="136"/>
-    </row>
-    <row r="72" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U71" s="136"/>
+    </row>
+    <row r="72" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
         <v>120</v>
       </c>
@@ -9397,28 +9590,31 @@
       <c r="L72" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M72" s="2">
+      <c r="M72" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="N72" s="2">
         <v>6</v>
       </c>
-      <c r="N72" s="64" t="s">
+      <c r="O72" s="64" t="s">
         <v>121</v>
       </c>
-      <c r="O72" s="65">
+      <c r="P72" s="65">
         <v>46213</v>
       </c>
-      <c r="P72" s="65">
+      <c r="Q72" s="65">
         <v>46220</v>
       </c>
-      <c r="Q72" s="65">
+      <c r="R72" s="65">
         <v>46234</v>
       </c>
-      <c r="R72" s="65">
+      <c r="S72" s="65">
         <v>46240</v>
       </c>
-      <c r="S72" s="136"/>
       <c r="T72" s="136"/>
-    </row>
-    <row r="73" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U72" s="136"/>
+    </row>
+    <row r="73" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
         <v>122</v>
       </c>
@@ -9455,28 +9651,31 @@
       <c r="L73" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M73" s="2">
+      <c r="M73" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="N73" s="2">
         <v>3</v>
       </c>
-      <c r="N73" s="64" t="s">
+      <c r="O73" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="O73" s="65">
+      <c r="P73" s="65">
         <v>46273</v>
       </c>
-      <c r="P73" s="65">
+      <c r="Q73" s="65">
         <v>46280</v>
       </c>
-      <c r="Q73" s="65">
+      <c r="R73" s="65">
         <v>46295</v>
       </c>
-      <c r="R73" s="65">
+      <c r="S73" s="65">
         <v>46301</v>
       </c>
-      <c r="S73" s="136"/>
       <c r="T73" s="136"/>
-    </row>
-    <row r="74" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U73" s="136"/>
+    </row>
+    <row r="74" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
         <v>123</v>
       </c>
@@ -9513,28 +9712,31 @@
       <c r="L74" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M74" s="2">
+      <c r="M74" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="N74" s="2">
         <v>7</v>
       </c>
-      <c r="N74" s="64" t="s">
+      <c r="O74" s="64" t="s">
         <v>121</v>
       </c>
-      <c r="O74" s="65">
+      <c r="P74" s="65">
         <v>46213</v>
       </c>
-      <c r="P74" s="65">
+      <c r="Q74" s="65">
         <v>46220</v>
       </c>
-      <c r="Q74" s="65">
+      <c r="R74" s="65">
         <v>46234</v>
       </c>
-      <c r="R74" s="65">
+      <c r="S74" s="65">
         <v>46240</v>
       </c>
-      <c r="S74" s="136"/>
       <c r="T74" s="136"/>
-    </row>
-    <row r="75" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U74" s="136"/>
+    </row>
+    <row r="75" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
         <v>124</v>
       </c>
@@ -9571,28 +9773,31 @@
       <c r="L75" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M75" s="2">
+      <c r="M75" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="N75" s="2">
         <v>4</v>
       </c>
-      <c r="N75" s="64" t="s">
+      <c r="O75" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="O75" s="65">
+      <c r="P75" s="65">
         <v>46273</v>
       </c>
-      <c r="P75" s="65">
+      <c r="Q75" s="65">
         <v>46280</v>
       </c>
-      <c r="Q75" s="65">
+      <c r="R75" s="65">
         <v>46295</v>
       </c>
-      <c r="R75" s="65">
+      <c r="S75" s="65">
         <v>46301</v>
       </c>
-      <c r="S75" s="136"/>
       <c r="T75" s="136"/>
-    </row>
-    <row r="76" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U75" s="136"/>
+    </row>
+    <row r="76" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
         <v>125</v>
       </c>
@@ -9629,28 +9834,31 @@
       <c r="L76" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M76" s="2">
+      <c r="M76" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="N76" s="2">
         <v>5</v>
       </c>
-      <c r="N76" s="64" t="s">
+      <c r="O76" s="64" t="s">
         <v>121</v>
       </c>
-      <c r="O76" s="65">
+      <c r="P76" s="65">
         <v>46213</v>
       </c>
-      <c r="P76" s="65">
+      <c r="Q76" s="65">
         <v>46220</v>
       </c>
-      <c r="Q76" s="65">
+      <c r="R76" s="65">
         <v>46234</v>
       </c>
-      <c r="R76" s="65">
+      <c r="S76" s="65">
         <v>46240</v>
       </c>
-      <c r="S76" s="136"/>
       <c r="T76" s="136"/>
-    </row>
-    <row r="77" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U76" s="136"/>
+    </row>
+    <row r="77" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
         <v>126</v>
       </c>
@@ -9687,28 +9895,31 @@
       <c r="L77" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M77" s="2">
+      <c r="M77" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="N77" s="2">
         <v>9</v>
       </c>
-      <c r="N77" s="64" t="s">
+      <c r="O77" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="O77" s="65">
+      <c r="P77" s="65">
         <v>46273</v>
       </c>
-      <c r="P77" s="65">
+      <c r="Q77" s="65">
         <v>46280</v>
       </c>
-      <c r="Q77" s="65">
+      <c r="R77" s="65">
         <v>46295</v>
       </c>
-      <c r="R77" s="65">
+      <c r="S77" s="65">
         <v>46301</v>
       </c>
-      <c r="S77" s="136"/>
       <c r="T77" s="136"/>
-    </row>
-    <row r="78" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U77" s="136"/>
+    </row>
+    <row r="78" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
         <v>127</v>
       </c>
@@ -9745,28 +9956,31 @@
       <c r="L78" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M78" s="2">
+      <c r="M78" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="N78" s="2">
         <v>8</v>
       </c>
-      <c r="N78" s="64" t="s">
+      <c r="O78" s="64" t="s">
         <v>121</v>
       </c>
-      <c r="O78" s="65">
+      <c r="P78" s="65">
         <v>46213</v>
       </c>
-      <c r="P78" s="65">
+      <c r="Q78" s="65">
         <v>46220</v>
       </c>
-      <c r="Q78" s="65">
+      <c r="R78" s="65">
         <v>46234</v>
       </c>
-      <c r="R78" s="65">
+      <c r="S78" s="65">
         <v>46240</v>
       </c>
-      <c r="S78" s="136"/>
       <c r="T78" s="136"/>
-    </row>
-    <row r="79" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U78" s="136"/>
+    </row>
+    <row r="79" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A79" s="12" t="s">
         <v>128</v>
       </c>
@@ -9803,28 +10017,31 @@
       <c r="L79" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M79" s="2">
+      <c r="M79" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="N79" s="2">
         <v>6</v>
       </c>
-      <c r="N79" s="64" t="s">
+      <c r="O79" s="64" t="s">
         <v>130</v>
       </c>
-      <c r="O79" s="65">
+      <c r="P79" s="65">
         <v>46167</v>
       </c>
-      <c r="P79" s="65">
+      <c r="Q79" s="65">
         <v>46174</v>
       </c>
-      <c r="Q79" s="65">
+      <c r="R79" s="65">
         <v>46188</v>
       </c>
-      <c r="R79" s="65">
+      <c r="S79" s="65">
         <v>46195</v>
       </c>
-      <c r="S79" s="136"/>
       <c r="T79" s="136"/>
-    </row>
-    <row r="80" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U79" s="136"/>
+    </row>
+    <row r="80" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
         <v>131</v>
       </c>
@@ -9861,28 +10078,31 @@
       <c r="L80" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M80" s="2">
+      <c r="M80" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="N80" s="2">
         <v>5</v>
       </c>
-      <c r="N80" s="64" t="s">
+      <c r="O80" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="O80" s="65">
+      <c r="P80" s="65">
         <v>46153</v>
       </c>
-      <c r="P80" s="65">
+      <c r="Q80" s="65">
         <v>46160</v>
       </c>
-      <c r="Q80" s="65">
+      <c r="R80" s="65">
         <v>46174</v>
       </c>
-      <c r="R80" s="65">
+      <c r="S80" s="65">
         <v>46179</v>
       </c>
-      <c r="S80" s="136"/>
       <c r="T80" s="136"/>
-    </row>
-    <row r="81" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U80" s="136"/>
+    </row>
+    <row r="81" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
         <v>133</v>
       </c>
@@ -9919,28 +10139,31 @@
       <c r="L81" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M81" s="2">
+      <c r="M81" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="N81" s="2">
         <v>7</v>
       </c>
-      <c r="N81" s="64" t="s">
+      <c r="O81" s="64" t="s">
         <v>130</v>
       </c>
-      <c r="O81" s="65">
+      <c r="P81" s="65">
         <v>46167</v>
       </c>
-      <c r="P81" s="65">
+      <c r="Q81" s="65">
         <v>46174</v>
       </c>
-      <c r="Q81" s="65">
+      <c r="R81" s="65">
         <v>46188</v>
       </c>
-      <c r="R81" s="65">
+      <c r="S81" s="65">
         <v>46195</v>
       </c>
-      <c r="S81" s="136"/>
       <c r="T81" s="136"/>
-    </row>
-    <row r="82" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U81" s="136"/>
+    </row>
+    <row r="82" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
         <v>134</v>
       </c>
@@ -9977,28 +10200,31 @@
       <c r="L82" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M82" s="2">
-        <v>1</v>
-      </c>
-      <c r="N82" s="64" t="s">
+      <c r="M82" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="N82" s="2">
+        <v>1</v>
+      </c>
+      <c r="O82" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="O82" s="65">
+      <c r="P82" s="65">
         <v>46153</v>
       </c>
-      <c r="P82" s="65">
+      <c r="Q82" s="65">
         <v>46160</v>
       </c>
-      <c r="Q82" s="65">
+      <c r="R82" s="65">
         <v>46174</v>
       </c>
-      <c r="R82" s="65">
+      <c r="S82" s="65">
         <v>46179</v>
       </c>
-      <c r="S82" s="136"/>
       <c r="T82" s="136"/>
-    </row>
-    <row r="83" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U82" s="136"/>
+    </row>
+    <row r="83" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A83" s="12" t="s">
         <v>135</v>
       </c>
@@ -10035,28 +10261,31 @@
       <c r="L83" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M83" s="2">
+      <c r="M83" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="N83" s="2">
         <v>8</v>
       </c>
-      <c r="N83" s="64" t="s">
+      <c r="O83" s="64" t="s">
         <v>130</v>
       </c>
-      <c r="O83" s="65">
+      <c r="P83" s="65">
         <v>46167</v>
       </c>
-      <c r="P83" s="65">
+      <c r="Q83" s="65">
         <v>46174</v>
       </c>
-      <c r="Q83" s="65">
+      <c r="R83" s="65">
         <v>46188</v>
       </c>
-      <c r="R83" s="65">
+      <c r="S83" s="65">
         <v>46195</v>
       </c>
-      <c r="S83" s="136"/>
       <c r="T83" s="136"/>
-    </row>
-    <row r="84" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U83" s="136"/>
+    </row>
+    <row r="84" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
         <v>136</v>
       </c>
@@ -10093,28 +10322,31 @@
       <c r="L84" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M84" s="2">
+      <c r="M84" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="N84" s="2">
         <v>2</v>
       </c>
-      <c r="N84" s="64" t="s">
+      <c r="O84" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="O84" s="65">
+      <c r="P84" s="65">
         <v>46153</v>
       </c>
-      <c r="P84" s="65">
+      <c r="Q84" s="65">
         <v>46160</v>
       </c>
-      <c r="Q84" s="65">
+      <c r="R84" s="65">
         <v>46174</v>
       </c>
-      <c r="R84" s="65">
+      <c r="S84" s="65">
         <v>46179</v>
       </c>
-      <c r="S84" s="136"/>
       <c r="T84" s="136"/>
-    </row>
-    <row r="85" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U84" s="136"/>
+    </row>
+    <row r="85" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A85" s="12" t="s">
         <v>137</v>
       </c>
@@ -10151,28 +10383,31 @@
       <c r="L85" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M85" s="2">
+      <c r="M85" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="N85" s="2">
         <v>4</v>
       </c>
-      <c r="N85" s="64" t="s">
+      <c r="O85" s="64" t="s">
         <v>130</v>
       </c>
-      <c r="O85" s="65">
+      <c r="P85" s="65">
         <v>46167</v>
       </c>
-      <c r="P85" s="65">
+      <c r="Q85" s="65">
         <v>46174</v>
       </c>
-      <c r="Q85" s="65">
+      <c r="R85" s="65">
         <v>46188</v>
       </c>
-      <c r="R85" s="65">
+      <c r="S85" s="65">
         <v>46195</v>
       </c>
-      <c r="S85" s="136"/>
       <c r="T85" s="136"/>
-    </row>
-    <row r="86" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U85" s="136"/>
+    </row>
+    <row r="86" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A86" s="12" t="s">
         <v>138</v>
       </c>
@@ -10209,28 +10444,31 @@
       <c r="L86" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M86" s="2">
+      <c r="M86" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="N86" s="2">
         <v>3</v>
       </c>
-      <c r="N86" s="64" t="s">
+      <c r="O86" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="O86" s="65">
+      <c r="P86" s="65">
         <v>46153</v>
       </c>
-      <c r="P86" s="65">
+      <c r="Q86" s="65">
         <v>46160</v>
       </c>
-      <c r="Q86" s="65">
+      <c r="R86" s="65">
         <v>46174</v>
       </c>
-      <c r="R86" s="65">
+      <c r="S86" s="65">
         <v>46179</v>
       </c>
-      <c r="S86" s="136"/>
       <c r="T86" s="136"/>
-    </row>
-    <row r="87" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U86" s="136"/>
+    </row>
+    <row r="87" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
         <v>139</v>
       </c>
@@ -10267,28 +10505,31 @@
       <c r="L87" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M87" s="2">
+      <c r="M87" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="N87" s="2">
         <v>9</v>
       </c>
-      <c r="N87" s="64" t="s">
+      <c r="O87" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="O87" s="65">
+      <c r="P87" s="65">
         <v>46213</v>
       </c>
-      <c r="P87" s="65">
+      <c r="Q87" s="65">
         <v>46220</v>
       </c>
-      <c r="Q87" s="65">
+      <c r="R87" s="65">
         <v>46234</v>
       </c>
-      <c r="R87" s="65">
+      <c r="S87" s="65">
         <v>46240</v>
       </c>
-      <c r="S87" s="136"/>
       <c r="T87" s="136"/>
-    </row>
-    <row r="88" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U87" s="136"/>
+    </row>
+    <row r="88" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A88" s="12" t="s">
         <v>141</v>
       </c>
@@ -10325,28 +10566,31 @@
       <c r="L88" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M88" s="2">
+      <c r="M88" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="N88" s="2">
         <v>8</v>
       </c>
-      <c r="N88" s="64" t="s">
+      <c r="O88" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="O88" s="65">
+      <c r="P88" s="65">
         <v>46213</v>
       </c>
-      <c r="P88" s="65">
+      <c r="Q88" s="65">
         <v>46220</v>
       </c>
-      <c r="Q88" s="65">
+      <c r="R88" s="65">
         <v>46234</v>
       </c>
-      <c r="R88" s="65">
+      <c r="S88" s="65">
         <v>46240</v>
       </c>
-      <c r="S88" s="136"/>
       <c r="T88" s="136"/>
-    </row>
-    <row r="89" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U88" s="136"/>
+    </row>
+    <row r="89" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A89" s="12" t="s">
         <v>142</v>
       </c>
@@ -10383,32 +10627,35 @@
       <c r="L89" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M89" s="2">
+      <c r="M89" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="N89" s="2">
         <v>5</v>
       </c>
-      <c r="N89" s="64" t="s">
+      <c r="O89" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="O89" s="65">
+      <c r="P89" s="65">
         <v>46134</v>
       </c>
-      <c r="P89" s="65">
+      <c r="Q89" s="65">
         <v>46142</v>
       </c>
-      <c r="Q89" s="65">
+      <c r="R89" s="65">
         <v>46157</v>
       </c>
-      <c r="R89" s="65">
+      <c r="S89" s="65">
         <v>46163</v>
       </c>
-      <c r="S89" s="137">
+      <c r="T89" s="137">
         <v>46204.70416666667</v>
       </c>
-      <c r="T89" s="138">
+      <c r="U89" s="138">
         <v>102.95</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A90" s="12" t="s">
         <v>144</v>
       </c>
@@ -10445,28 +10692,31 @@
       <c r="L90" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M90" s="2">
+      <c r="M90" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="N90" s="2">
         <v>7</v>
       </c>
-      <c r="N90" s="64" t="s">
+      <c r="O90" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="O90" s="65">
+      <c r="P90" s="65">
         <v>46213</v>
       </c>
-      <c r="P90" s="65">
+      <c r="Q90" s="65">
         <v>46220</v>
       </c>
-      <c r="Q90" s="65">
+      <c r="R90" s="65">
         <v>46234</v>
       </c>
-      <c r="R90" s="65">
+      <c r="S90" s="65">
         <v>46240</v>
       </c>
-      <c r="S90" s="136"/>
       <c r="T90" s="136"/>
-    </row>
-    <row r="91" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U90" s="136"/>
+    </row>
+    <row r="91" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A91" s="12" t="s">
         <v>145</v>
       </c>
@@ -10503,32 +10753,35 @@
       <c r="L91" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M91" s="2">
+      <c r="M91" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="N91" s="2">
         <v>4</v>
       </c>
-      <c r="N91" s="64" t="s">
+      <c r="O91" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="O91" s="65">
+      <c r="P91" s="65">
         <v>46134</v>
       </c>
-      <c r="P91" s="65">
+      <c r="Q91" s="65">
         <v>46142</v>
       </c>
-      <c r="Q91" s="65">
+      <c r="R91" s="65">
         <v>46157</v>
       </c>
-      <c r="R91" s="65">
+      <c r="S91" s="65">
         <v>46163</v>
       </c>
-      <c r="S91" s="137">
+      <c r="T91" s="137">
         <v>46204.657638888886</v>
       </c>
-      <c r="T91" s="138">
+      <c r="U91" s="138">
         <v>70.277000000000001</v>
       </c>
     </row>
-    <row r="92" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A92" s="12" t="s">
         <v>146</v>
       </c>
@@ -10565,28 +10818,31 @@
       <c r="L92" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M92" s="2">
+      <c r="M92" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="N92" s="2">
         <v>6</v>
       </c>
-      <c r="N92" s="64" t="s">
+      <c r="O92" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="O92" s="65">
+      <c r="P92" s="65">
         <v>46213</v>
       </c>
-      <c r="P92" s="65">
+      <c r="Q92" s="65">
         <v>46220</v>
       </c>
-      <c r="Q92" s="65">
+      <c r="R92" s="65">
         <v>46234</v>
       </c>
-      <c r="R92" s="65">
+      <c r="S92" s="65">
         <v>46240</v>
       </c>
-      <c r="S92" s="136"/>
       <c r="T92" s="136"/>
-    </row>
-    <row r="93" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U92" s="136"/>
+    </row>
+    <row r="93" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A93" s="12" t="s">
         <v>147</v>
       </c>
@@ -10623,32 +10879,35 @@
       <c r="L93" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M93" s="2">
+      <c r="M93" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="N93" s="2">
         <v>3</v>
       </c>
-      <c r="N93" s="64" t="s">
+      <c r="O93" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="O93" s="65">
+      <c r="P93" s="65">
         <v>46134</v>
       </c>
-      <c r="P93" s="65">
+      <c r="Q93" s="65">
         <v>46142</v>
       </c>
-      <c r="Q93" s="65">
+      <c r="R93" s="65">
         <v>46157</v>
       </c>
-      <c r="R93" s="65">
+      <c r="S93" s="65">
         <v>46163</v>
       </c>
-      <c r="S93" s="137">
+      <c r="T93" s="137">
         <v>46204.413194444445</v>
       </c>
-      <c r="T93" s="138">
+      <c r="U93" s="138">
         <v>77.23</v>
       </c>
     </row>
-    <row r="94" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A94" s="12" t="s">
         <v>148</v>
       </c>
@@ -10685,32 +10944,35 @@
       <c r="L94" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M94" s="2">
+      <c r="M94" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="N94" s="2">
         <v>2</v>
       </c>
-      <c r="N94" s="64" t="s">
+      <c r="O94" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="O94" s="65">
+      <c r="P94" s="65">
         <v>46125</v>
       </c>
-      <c r="P94" s="65">
+      <c r="Q94" s="65">
         <v>46132</v>
       </c>
-      <c r="Q94" s="65">
+      <c r="R94" s="65">
         <v>46148</v>
       </c>
-      <c r="R94" s="65">
+      <c r="S94" s="65">
         <v>46154</v>
       </c>
-      <c r="S94" s="137">
+      <c r="T94" s="137">
         <v>46204.426388888889</v>
       </c>
-      <c r="T94" s="138">
+      <c r="U94" s="138">
         <v>25.35</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A95" s="12" t="s">
         <v>149</v>
       </c>
@@ -10747,32 +11009,35 @@
       <c r="L95" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M95" s="2">
-        <v>1</v>
-      </c>
-      <c r="N95" s="64" t="s">
+      <c r="M95" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="N95" s="2">
+        <v>1</v>
+      </c>
+      <c r="O95" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="O95" s="65">
+      <c r="P95" s="65">
         <v>46125</v>
       </c>
-      <c r="P95" s="65">
+      <c r="Q95" s="65">
         <v>46132</v>
       </c>
-      <c r="Q95" s="65">
+      <c r="R95" s="65">
         <v>46148</v>
       </c>
-      <c r="R95" s="65">
+      <c r="S95" s="65">
         <v>46154</v>
       </c>
-      <c r="S95" s="137">
+      <c r="T95" s="137">
         <v>46204.657638888886</v>
       </c>
-      <c r="T95" s="138">
+      <c r="U95" s="138">
         <v>45.284999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A96" s="12" t="s">
         <v>150</v>
       </c>
@@ -10809,28 +11074,31 @@
       <c r="L96" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M96" s="2">
+      <c r="M96" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="N96" s="2">
         <v>3</v>
       </c>
-      <c r="N96" s="64" t="s">
+      <c r="O96" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="O96" s="65">
+      <c r="P96" s="65">
         <v>46273</v>
       </c>
-      <c r="P96" s="65">
+      <c r="Q96" s="65">
         <v>46280</v>
       </c>
-      <c r="Q96" s="65">
+      <c r="R96" s="65">
         <v>46295</v>
       </c>
-      <c r="R96" s="65">
+      <c r="S96" s="65">
         <v>46301</v>
       </c>
-      <c r="S96" s="136"/>
       <c r="T96" s="136"/>
-    </row>
-    <row r="97" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U96" s="136"/>
+    </row>
+    <row r="97" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A97" s="12" t="s">
         <v>152</v>
       </c>
@@ -10867,28 +11135,31 @@
       <c r="L97" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M97" s="2">
+      <c r="M97" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="N97" s="2">
         <v>5</v>
       </c>
-      <c r="N97" s="64" t="s">
+      <c r="O97" s="64" t="s">
         <v>121</v>
       </c>
-      <c r="O97" s="65">
+      <c r="P97" s="65">
         <v>46213</v>
       </c>
-      <c r="P97" s="65">
+      <c r="Q97" s="65">
         <v>46220</v>
       </c>
-      <c r="Q97" s="65">
+      <c r="R97" s="65">
         <v>46234</v>
       </c>
-      <c r="R97" s="65">
+      <c r="S97" s="65">
         <v>46240</v>
       </c>
-      <c r="S97" s="136"/>
       <c r="T97" s="136"/>
-    </row>
-    <row r="98" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U97" s="136"/>
+    </row>
+    <row r="98" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A98" s="12" t="s">
         <v>153</v>
       </c>
@@ -10925,28 +11196,31 @@
       <c r="L98" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M98" s="2">
+      <c r="M98" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="N98" s="2">
         <v>2</v>
       </c>
-      <c r="N98" s="64" t="s">
+      <c r="O98" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="O98" s="65">
+      <c r="P98" s="65">
         <v>46273</v>
       </c>
-      <c r="P98" s="65">
+      <c r="Q98" s="65">
         <v>46280</v>
       </c>
-      <c r="Q98" s="65">
+      <c r="R98" s="65">
         <v>46295</v>
       </c>
-      <c r="R98" s="65">
+      <c r="S98" s="65">
         <v>46301</v>
       </c>
-      <c r="S98" s="136"/>
       <c r="T98" s="136"/>
-    </row>
-    <row r="99" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U98" s="136"/>
+    </row>
+    <row r="99" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A99" s="12" t="s">
         <v>154</v>
       </c>
@@ -10983,28 +11257,31 @@
       <c r="L99" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M99" s="2">
+      <c r="M99" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="N99" s="2">
         <v>9</v>
       </c>
-      <c r="N99" s="64" t="s">
+      <c r="O99" s="64" t="s">
         <v>121</v>
       </c>
-      <c r="O99" s="65">
+      <c r="P99" s="65">
         <v>46213</v>
       </c>
-      <c r="P99" s="65">
+      <c r="Q99" s="65">
         <v>46220</v>
       </c>
-      <c r="Q99" s="65">
+      <c r="R99" s="65">
         <v>46234</v>
       </c>
-      <c r="R99" s="65">
+      <c r="S99" s="65">
         <v>46240</v>
       </c>
-      <c r="S99" s="136"/>
       <c r="T99" s="136"/>
-    </row>
-    <row r="100" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U99" s="136"/>
+    </row>
+    <row r="100" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A100" s="12" t="s">
         <v>155</v>
       </c>
@@ -11041,28 +11318,31 @@
       <c r="L100" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M100" s="2">
-        <v>1</v>
-      </c>
-      <c r="N100" s="64" t="s">
+      <c r="M100" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="N100" s="2">
+        <v>1</v>
+      </c>
+      <c r="O100" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="O100" s="65">
+      <c r="P100" s="65">
         <v>46273</v>
       </c>
-      <c r="P100" s="65">
+      <c r="Q100" s="65">
         <v>46280</v>
       </c>
-      <c r="Q100" s="65">
+      <c r="R100" s="65">
         <v>46295</v>
       </c>
-      <c r="R100" s="65">
+      <c r="S100" s="65">
         <v>46301</v>
       </c>
-      <c r="S100" s="136"/>
       <c r="T100" s="136"/>
-    </row>
-    <row r="101" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U100" s="136"/>
+    </row>
+    <row r="101" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A101" s="12" t="s">
         <v>156</v>
       </c>
@@ -11099,28 +11379,31 @@
       <c r="L101" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M101" s="2">
+      <c r="M101" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="N101" s="2">
         <v>8</v>
       </c>
-      <c r="N101" s="64" t="s">
+      <c r="O101" s="64" t="s">
         <v>121</v>
       </c>
-      <c r="O101" s="65">
+      <c r="P101" s="65">
         <v>46213</v>
       </c>
-      <c r="P101" s="65">
+      <c r="Q101" s="65">
         <v>46220</v>
       </c>
-      <c r="Q101" s="65">
+      <c r="R101" s="65">
         <v>46234</v>
       </c>
-      <c r="R101" s="65">
+      <c r="S101" s="65">
         <v>46240</v>
       </c>
-      <c r="S101" s="136"/>
       <c r="T101" s="136"/>
-    </row>
-    <row r="102" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U101" s="136"/>
+    </row>
+    <row r="102" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A102" s="12" t="s">
         <v>157</v>
       </c>
@@ -11157,28 +11440,31 @@
       <c r="L102" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M102" s="2">
+      <c r="M102" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="N102" s="2">
         <v>6</v>
       </c>
-      <c r="N102" s="64" t="s">
+      <c r="O102" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="O102" s="65">
+      <c r="P102" s="65">
         <v>46273</v>
       </c>
-      <c r="P102" s="65">
+      <c r="Q102" s="65">
         <v>46280</v>
       </c>
-      <c r="Q102" s="65">
+      <c r="R102" s="65">
         <v>46295</v>
       </c>
-      <c r="R102" s="65">
+      <c r="S102" s="65">
         <v>46301</v>
       </c>
-      <c r="S102" s="136"/>
       <c r="T102" s="136"/>
-    </row>
-    <row r="103" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U102" s="136"/>
+    </row>
+    <row r="103" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A103" s="12" t="s">
         <v>158</v>
       </c>
@@ -11215,28 +11501,31 @@
       <c r="L103" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M103" s="2">
+      <c r="M103" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="N103" s="2">
         <v>7</v>
       </c>
-      <c r="N103" s="64" t="s">
+      <c r="O103" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="O103" s="65">
+      <c r="P103" s="65">
         <v>46197</v>
       </c>
-      <c r="P103" s="65">
+      <c r="Q103" s="65">
         <v>46204</v>
       </c>
-      <c r="Q103" s="65">
+      <c r="R103" s="65">
         <v>46218</v>
       </c>
-      <c r="R103" s="65">
+      <c r="S103" s="65">
         <v>46224</v>
       </c>
-      <c r="S103" s="136"/>
       <c r="T103" s="136"/>
-    </row>
-    <row r="104" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U103" s="136"/>
+    </row>
+    <row r="104" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A104" s="12" t="s">
         <v>160</v>
       </c>
@@ -11273,28 +11562,31 @@
       <c r="L104" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M104" s="2">
+      <c r="M104" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="N104" s="2">
         <v>4</v>
       </c>
-      <c r="N104" s="64" t="s">
+      <c r="O104" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="O104" s="65">
+      <c r="P104" s="65">
         <v>46273</v>
       </c>
-      <c r="P104" s="65">
+      <c r="Q104" s="65">
         <v>46280</v>
       </c>
-      <c r="Q104" s="65">
+      <c r="R104" s="65">
         <v>46295</v>
       </c>
-      <c r="R104" s="65">
+      <c r="S104" s="65">
         <v>46301</v>
       </c>
-      <c r="S104" s="136"/>
       <c r="T104" s="136"/>
-    </row>
-    <row r="105" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U104" s="136"/>
+    </row>
+    <row r="105" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A105" s="12" t="s">
         <v>161</v>
       </c>
@@ -11332,25 +11624,26 @@
         <v>0</v>
       </c>
       <c r="M105" s="2"/>
-      <c r="N105" s="64" t="s">
+      <c r="N105" s="2"/>
+      <c r="O105" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="O105" s="65">
+      <c r="P105" s="65">
         <v>46179</v>
       </c>
-      <c r="P105" s="65">
+      <c r="Q105" s="65">
         <v>46186</v>
       </c>
-      <c r="Q105" s="65">
+      <c r="R105" s="65">
         <v>46202</v>
       </c>
-      <c r="R105" s="65">
+      <c r="S105" s="65">
         <v>46207</v>
       </c>
-      <c r="S105" s="136"/>
       <c r="T105" s="136"/>
-    </row>
-    <row r="106" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U105" s="136"/>
+    </row>
+    <row r="106" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A106" s="12" t="s">
         <v>163</v>
       </c>
@@ -11388,25 +11681,26 @@
         <v>0</v>
       </c>
       <c r="M106" s="2"/>
-      <c r="N106" s="64" t="s">
+      <c r="N106" s="2"/>
+      <c r="O106" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="O106" s="65">
+      <c r="P106" s="65">
         <v>46179</v>
       </c>
-      <c r="P106" s="65">
+      <c r="Q106" s="65">
         <v>46186</v>
       </c>
-      <c r="Q106" s="65">
+      <c r="R106" s="65">
         <v>46202</v>
       </c>
-      <c r="R106" s="65">
+      <c r="S106" s="65">
         <v>46207</v>
       </c>
-      <c r="S106" s="136"/>
       <c r="T106" s="136"/>
-    </row>
-    <row r="107" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U106" s="136"/>
+    </row>
+    <row r="107" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A107" s="12" t="s">
         <v>164</v>
       </c>
@@ -11444,25 +11738,26 @@
         <v>0</v>
       </c>
       <c r="M107" s="2"/>
-      <c r="N107" s="64" t="s">
+      <c r="N107" s="2"/>
+      <c r="O107" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="O107" s="65">
+      <c r="P107" s="65">
         <v>46153</v>
       </c>
-      <c r="P107" s="65">
+      <c r="Q107" s="65">
         <v>46160</v>
       </c>
-      <c r="Q107" s="65">
+      <c r="R107" s="65">
         <v>46174</v>
       </c>
-      <c r="R107" s="65">
+      <c r="S107" s="65">
         <v>46179</v>
       </c>
-      <c r="S107" s="136"/>
       <c r="T107" s="136"/>
-    </row>
-    <row r="108" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U107" s="136"/>
+    </row>
+    <row r="108" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A108" s="12" t="s">
         <v>165</v>
       </c>
@@ -11500,25 +11795,26 @@
         <v>0</v>
       </c>
       <c r="M108" s="2"/>
-      <c r="N108" s="64" t="s">
+      <c r="N108" s="2"/>
+      <c r="O108" s="64" t="s">
         <v>130</v>
       </c>
-      <c r="O108" s="65">
+      <c r="P108" s="65">
         <v>46167</v>
       </c>
-      <c r="P108" s="65">
+      <c r="Q108" s="65">
         <v>46174</v>
       </c>
-      <c r="Q108" s="65">
+      <c r="R108" s="65">
         <v>46188</v>
       </c>
-      <c r="R108" s="65">
+      <c r="S108" s="65">
         <v>46195</v>
       </c>
-      <c r="S108" s="136"/>
       <c r="T108" s="136"/>
-    </row>
-    <row r="109" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U108" s="136"/>
+    </row>
+    <row r="109" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A109" s="12" t="s">
         <v>166</v>
       </c>
@@ -11556,25 +11852,26 @@
         <v>0</v>
       </c>
       <c r="M109" s="2"/>
-      <c r="N109" s="64" t="s">
+      <c r="N109" s="2"/>
+      <c r="O109" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="O109" s="65">
+      <c r="P109" s="65">
         <v>46153</v>
       </c>
-      <c r="P109" s="65">
+      <c r="Q109" s="65">
         <v>46160</v>
       </c>
-      <c r="Q109" s="65">
+      <c r="R109" s="65">
         <v>46174</v>
       </c>
-      <c r="R109" s="65">
+      <c r="S109" s="65">
         <v>46179</v>
       </c>
-      <c r="S109" s="136"/>
       <c r="T109" s="136"/>
-    </row>
-    <row r="110" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U109" s="136"/>
+    </row>
+    <row r="110" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A110" s="12" t="s">
         <v>167</v>
       </c>
@@ -11612,25 +11909,26 @@
         <v>0</v>
       </c>
       <c r="M110" s="2"/>
-      <c r="N110" s="64" t="s">
+      <c r="N110" s="2"/>
+      <c r="O110" s="64" t="s">
         <v>130</v>
       </c>
-      <c r="O110" s="65">
+      <c r="P110" s="65">
         <v>46167</v>
       </c>
-      <c r="P110" s="65">
+      <c r="Q110" s="65">
         <v>46174</v>
       </c>
-      <c r="Q110" s="65">
+      <c r="R110" s="65">
         <v>46188</v>
       </c>
-      <c r="R110" s="65">
+      <c r="S110" s="65">
         <v>46195</v>
       </c>
-      <c r="S110" s="136"/>
       <c r="T110" s="136"/>
-    </row>
-    <row r="111" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U110" s="136"/>
+    </row>
+    <row r="111" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A111" s="12" t="s">
         <v>168</v>
       </c>
@@ -11668,25 +11966,26 @@
         <v>0</v>
       </c>
       <c r="M111" s="2"/>
-      <c r="N111" s="64" t="s">
+      <c r="N111" s="2"/>
+      <c r="O111" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="O111" s="65">
+      <c r="P111" s="65">
         <v>46153</v>
       </c>
-      <c r="P111" s="65">
+      <c r="Q111" s="65">
         <v>46160</v>
       </c>
-      <c r="Q111" s="65">
+      <c r="R111" s="65">
         <v>46174</v>
       </c>
-      <c r="R111" s="65">
+      <c r="S111" s="65">
         <v>46179</v>
       </c>
-      <c r="S111" s="136"/>
       <c r="T111" s="136"/>
-    </row>
-    <row r="112" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U111" s="136"/>
+    </row>
+    <row r="112" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A112" s="12" t="s">
         <v>169</v>
       </c>
@@ -11724,25 +12023,26 @@
         <v>0</v>
       </c>
       <c r="M112" s="2"/>
-      <c r="N112" s="64" t="s">
+      <c r="N112" s="2"/>
+      <c r="O112" s="64" t="s">
         <v>130</v>
       </c>
-      <c r="O112" s="65">
+      <c r="P112" s="65">
         <v>46167</v>
       </c>
-      <c r="P112" s="65">
+      <c r="Q112" s="65">
         <v>46174</v>
       </c>
-      <c r="Q112" s="65">
+      <c r="R112" s="65">
         <v>46188</v>
       </c>
-      <c r="R112" s="65">
+      <c r="S112" s="65">
         <v>46195</v>
       </c>
-      <c r="S112" s="136"/>
       <c r="T112" s="136"/>
-    </row>
-    <row r="113" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U112" s="136"/>
+    </row>
+    <row r="113" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A113" s="12" t="s">
         <v>170</v>
       </c>
@@ -11780,25 +12080,26 @@
         <v>0</v>
       </c>
       <c r="M113" s="2"/>
-      <c r="N113" s="64" t="s">
+      <c r="N113" s="2"/>
+      <c r="O113" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="O113" s="65">
+      <c r="P113" s="65">
         <v>46153</v>
       </c>
-      <c r="P113" s="65">
+      <c r="Q113" s="65">
         <v>46160</v>
       </c>
-      <c r="Q113" s="65">
+      <c r="R113" s="65">
         <v>46174</v>
       </c>
-      <c r="R113" s="65">
+      <c r="S113" s="65">
         <v>46179</v>
       </c>
-      <c r="S113" s="136"/>
       <c r="T113" s="136"/>
-    </row>
-    <row r="114" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U113" s="136"/>
+    </row>
+    <row r="114" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A114" s="12" t="s">
         <v>171</v>
       </c>
@@ -11835,32 +12136,35 @@
       <c r="L114" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M114" s="2">
+      <c r="M114" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="N114" s="2">
         <v>5</v>
       </c>
-      <c r="N114" s="64" t="s">
+      <c r="O114" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="O114" s="65">
+      <c r="P114" s="65">
         <v>46134</v>
       </c>
-      <c r="P114" s="65">
+      <c r="Q114" s="65">
         <v>46142</v>
       </c>
-      <c r="Q114" s="65">
+      <c r="R114" s="65">
         <v>46157</v>
       </c>
-      <c r="R114" s="65">
+      <c r="S114" s="65">
         <v>46163</v>
       </c>
-      <c r="S114" s="137">
+      <c r="T114" s="137">
         <v>46204.65625</v>
       </c>
-      <c r="T114" s="138">
+      <c r="U114" s="138">
         <v>47.1</v>
       </c>
     </row>
-    <row r="115" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A115" s="12" t="s">
         <v>173</v>
       </c>
@@ -11897,32 +12201,35 @@
       <c r="L115" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M115" s="2">
+      <c r="M115" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="N115" s="2">
         <v>8</v>
       </c>
-      <c r="N115" s="64" t="s">
+      <c r="O115" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="O115" s="65">
+      <c r="P115" s="65">
         <v>46140</v>
       </c>
-      <c r="P115" s="65">
+      <c r="Q115" s="65">
         <v>46148</v>
       </c>
-      <c r="Q115" s="65">
+      <c r="R115" s="65">
         <v>46162</v>
       </c>
-      <c r="R115" s="65">
+      <c r="S115" s="65">
         <v>46168</v>
       </c>
-      <c r="S115" s="139">
+      <c r="T115" s="139">
         <v>46204.918749999997</v>
       </c>
-      <c r="T115" s="136">
+      <c r="U115" s="136">
         <v>38.9</v>
       </c>
     </row>
-    <row r="116" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A116" s="12" t="s">
         <v>175</v>
       </c>
@@ -11959,32 +12266,35 @@
       <c r="L116" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M116" s="2">
+      <c r="M116" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="N116" s="2">
         <v>4</v>
       </c>
-      <c r="N116" s="64" t="s">
+      <c r="O116" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="O116" s="65">
+      <c r="P116" s="65">
         <v>46134</v>
       </c>
-      <c r="P116" s="65">
+      <c r="Q116" s="65">
         <v>46142</v>
       </c>
-      <c r="Q116" s="65">
+      <c r="R116" s="65">
         <v>46157</v>
       </c>
-      <c r="R116" s="65">
+      <c r="S116" s="65">
         <v>46163</v>
       </c>
-      <c r="S116" s="137">
+      <c r="T116" s="137">
         <v>46204.875</v>
       </c>
-      <c r="T116" s="138">
+      <c r="U116" s="138">
         <v>53.9</v>
       </c>
     </row>
-    <row r="117" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A117" s="12" t="s">
         <v>176</v>
       </c>
@@ -12021,32 +12331,35 @@
       <c r="L117" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M117" s="2">
+      <c r="M117" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="N117" s="2">
         <v>7</v>
       </c>
-      <c r="N117" s="64" t="s">
+      <c r="O117" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="O117" s="65">
+      <c r="P117" s="65">
         <v>46140</v>
       </c>
-      <c r="P117" s="65">
+      <c r="Q117" s="65">
         <v>46148</v>
       </c>
-      <c r="Q117" s="65">
+      <c r="R117" s="65">
         <v>46162</v>
       </c>
-      <c r="R117" s="65">
+      <c r="S117" s="65">
         <v>46168</v>
       </c>
-      <c r="S117" s="139">
+      <c r="T117" s="139">
         <v>46204.657638888886</v>
       </c>
-      <c r="T117" s="136">
+      <c r="U117" s="136">
         <v>61.851999999999997</v>
       </c>
     </row>
-    <row r="118" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A118" s="12" t="s">
         <v>177</v>
       </c>
@@ -12083,32 +12396,35 @@
       <c r="L118" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M118" s="2">
+      <c r="M118" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="N118" s="2">
         <v>3</v>
       </c>
-      <c r="N118" s="64" t="s">
+      <c r="O118" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="O118" s="65">
+      <c r="P118" s="65">
         <v>46134</v>
       </c>
-      <c r="P118" s="65">
+      <c r="Q118" s="65">
         <v>46142</v>
       </c>
-      <c r="Q118" s="65">
+      <c r="R118" s="65">
         <v>46157</v>
       </c>
-      <c r="R118" s="65">
+      <c r="S118" s="65">
         <v>46163</v>
       </c>
-      <c r="S118" s="137">
+      <c r="T118" s="137">
         <v>46204.65625</v>
       </c>
-      <c r="T118" s="138">
+      <c r="U118" s="138">
         <v>47.4</v>
       </c>
     </row>
-    <row r="119" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A119" s="12" t="s">
         <v>178</v>
       </c>
@@ -12145,32 +12461,35 @@
       <c r="L119" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M119" s="2">
+      <c r="M119" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="N119" s="2">
         <v>6</v>
       </c>
-      <c r="N119" s="64" t="s">
+      <c r="O119" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="O119" s="65">
+      <c r="P119" s="65">
         <v>46140</v>
       </c>
-      <c r="P119" s="65">
+      <c r="Q119" s="65">
         <v>46148</v>
       </c>
-      <c r="Q119" s="65">
+      <c r="R119" s="65">
         <v>46162</v>
       </c>
-      <c r="R119" s="65">
+      <c r="S119" s="65">
         <v>46168</v>
       </c>
-      <c r="S119" s="139">
+      <c r="T119" s="139">
         <v>46204.918749999997</v>
       </c>
-      <c r="T119" s="136">
+      <c r="U119" s="136">
         <v>43.3</v>
       </c>
     </row>
-    <row r="120" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A120" s="12" t="s">
         <v>179</v>
       </c>
@@ -12207,32 +12526,35 @@
       <c r="L120" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M120" s="2">
+      <c r="M120" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="N120" s="2">
         <v>2</v>
       </c>
-      <c r="N120" s="64" t="s">
+      <c r="O120" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="O120" s="65">
+      <c r="P120" s="65">
         <v>46134</v>
       </c>
-      <c r="P120" s="65">
+      <c r="Q120" s="65">
         <v>46142</v>
       </c>
-      <c r="Q120" s="65">
+      <c r="R120" s="65">
         <v>46157</v>
       </c>
-      <c r="R120" s="65">
+      <c r="S120" s="65">
         <v>46163</v>
       </c>
-      <c r="S120" s="137">
+      <c r="T120" s="137">
         <v>46204.65625</v>
       </c>
-      <c r="T120" s="138">
+      <c r="U120" s="138">
         <v>47.1</v>
       </c>
     </row>
-    <row r="121" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A121" s="12" t="s">
         <v>180</v>
       </c>
@@ -12269,32 +12591,35 @@
       <c r="L121" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M121" s="2">
-        <v>1</v>
-      </c>
-      <c r="N121" s="64" t="s">
+      <c r="M121" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="N121" s="2">
+        <v>1</v>
+      </c>
+      <c r="O121" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="O121" s="65">
+      <c r="P121" s="65">
         <v>46134</v>
       </c>
-      <c r="P121" s="65">
+      <c r="Q121" s="65">
         <v>46142</v>
       </c>
-      <c r="Q121" s="65">
+      <c r="R121" s="65">
         <v>46157</v>
       </c>
-      <c r="R121" s="65">
+      <c r="S121" s="65">
         <v>46163</v>
       </c>
-      <c r="S121" s="137">
+      <c r="T121" s="137">
         <v>46204.65625</v>
       </c>
-      <c r="T121" s="138">
+      <c r="U121" s="138">
         <v>56.3</v>
       </c>
     </row>
-    <row r="122" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A122" s="12" t="s">
         <v>181</v>
       </c>
@@ -12331,28 +12656,31 @@
       <c r="L122" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M122" s="2">
+      <c r="M122" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="N122" s="2">
         <v>4</v>
       </c>
-      <c r="N122" s="64" t="s">
+      <c r="O122" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="O122" s="65">
+      <c r="P122" s="65">
         <v>46197</v>
       </c>
-      <c r="P122" s="65">
+      <c r="Q122" s="65">
         <v>46204</v>
       </c>
-      <c r="Q122" s="65">
+      <c r="R122" s="65">
         <v>46218</v>
       </c>
-      <c r="R122" s="65">
+      <c r="S122" s="65">
         <v>46224</v>
       </c>
-      <c r="S122" s="136"/>
       <c r="T122" s="136"/>
-    </row>
-    <row r="123" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U122" s="136"/>
+    </row>
+    <row r="123" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A123" s="12" t="s">
         <v>183</v>
       </c>
@@ -12389,28 +12717,31 @@
       <c r="L123" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M123" s="2">
-        <v>1</v>
-      </c>
-      <c r="N123" s="64" t="s">
+      <c r="M123" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="N123" s="2">
+        <v>1</v>
+      </c>
+      <c r="O123" s="64" t="s">
         <v>184</v>
       </c>
-      <c r="O123" s="65">
+      <c r="P123" s="65">
         <v>46259</v>
       </c>
-      <c r="P123" s="65">
+      <c r="Q123" s="65">
         <v>46266</v>
       </c>
-      <c r="Q123" s="65">
+      <c r="R123" s="65">
         <v>46280</v>
       </c>
-      <c r="R123" s="65">
+      <c r="S123" s="65">
         <v>46286</v>
       </c>
-      <c r="S123" s="136"/>
       <c r="T123" s="136"/>
-    </row>
-    <row r="124" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U123" s="136"/>
+    </row>
+    <row r="124" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A124" s="12" t="s">
         <v>185</v>
       </c>
@@ -12447,28 +12778,31 @@
       <c r="L124" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M124" s="2">
+      <c r="M124" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="N124" s="2">
         <v>3</v>
       </c>
-      <c r="N124" s="64" t="s">
+      <c r="O124" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="O124" s="65">
+      <c r="P124" s="65">
         <v>46197</v>
       </c>
-      <c r="P124" s="65">
+      <c r="Q124" s="65">
         <v>46204</v>
       </c>
-      <c r="Q124" s="65">
+      <c r="R124" s="65">
         <v>46218</v>
       </c>
-      <c r="R124" s="65">
+      <c r="S124" s="65">
         <v>46224</v>
       </c>
-      <c r="S124" s="136"/>
       <c r="T124" s="136"/>
-    </row>
-    <row r="125" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U124" s="136"/>
+    </row>
+    <row r="125" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A125" s="12" t="s">
         <v>186</v>
       </c>
@@ -12505,28 +12839,31 @@
       <c r="L125" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M125" s="2">
+      <c r="M125" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="N125" s="2">
         <v>2</v>
       </c>
-      <c r="N125" s="64" t="s">
+      <c r="O125" s="64" t="s">
         <v>184</v>
       </c>
-      <c r="O125" s="65">
+      <c r="P125" s="65">
         <v>46259</v>
       </c>
-      <c r="P125" s="65">
+      <c r="Q125" s="65">
         <v>46266</v>
       </c>
-      <c r="Q125" s="65">
+      <c r="R125" s="65">
         <v>46280</v>
       </c>
-      <c r="R125" s="65">
+      <c r="S125" s="65">
         <v>46286</v>
       </c>
-      <c r="S125" s="136"/>
       <c r="T125" s="136"/>
-    </row>
-    <row r="126" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U125" s="136"/>
+    </row>
+    <row r="126" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A126" s="12" t="s">
         <v>187</v>
       </c>
@@ -12563,28 +12900,31 @@
       <c r="L126" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M126" s="2">
+      <c r="M126" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="N126" s="2">
         <v>5</v>
       </c>
-      <c r="N126" s="64" t="s">
+      <c r="O126" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="O126" s="65">
+      <c r="P126" s="65">
         <v>46197</v>
       </c>
-      <c r="P126" s="65">
+      <c r="Q126" s="65">
         <v>46204</v>
       </c>
-      <c r="Q126" s="65">
+      <c r="R126" s="65">
         <v>46218</v>
       </c>
-      <c r="R126" s="65">
+      <c r="S126" s="65">
         <v>46224</v>
       </c>
-      <c r="S126" s="136"/>
       <c r="T126" s="136"/>
-    </row>
-    <row r="127" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U126" s="136"/>
+    </row>
+    <row r="127" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A127" s="12" t="s">
         <v>188</v>
       </c>
@@ -12621,28 +12961,31 @@
       <c r="L127" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M127" s="2">
+      <c r="M127" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="N127" s="2">
         <v>6</v>
       </c>
-      <c r="N127" s="64" t="s">
+      <c r="O127" s="64" t="s">
         <v>184</v>
       </c>
-      <c r="O127" s="65">
+      <c r="P127" s="65">
         <v>46259</v>
       </c>
-      <c r="P127" s="65">
+      <c r="Q127" s="65">
         <v>46266</v>
       </c>
-      <c r="Q127" s="65">
+      <c r="R127" s="65">
         <v>46280</v>
       </c>
-      <c r="R127" s="65">
+      <c r="S127" s="65">
         <v>46286</v>
       </c>
-      <c r="S127" s="136"/>
       <c r="T127" s="136"/>
-    </row>
-    <row r="128" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U127" s="136"/>
+    </row>
+    <row r="128" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A128" s="12" t="s">
         <v>189</v>
       </c>
@@ -12680,25 +13023,26 @@
         <v>0</v>
       </c>
       <c r="M128" s="2"/>
-      <c r="N128" s="64" t="s">
+      <c r="N128" s="2"/>
+      <c r="O128" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="O128" s="65">
+      <c r="P128" s="65">
         <v>46179</v>
       </c>
-      <c r="P128" s="65">
+      <c r="Q128" s="65">
         <v>46186</v>
       </c>
-      <c r="Q128" s="65">
+      <c r="R128" s="65">
         <v>46202</v>
       </c>
-      <c r="R128" s="65">
+      <c r="S128" s="65">
         <v>46207</v>
       </c>
-      <c r="S128" s="136"/>
       <c r="T128" s="136"/>
-    </row>
-    <row r="129" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U128" s="136"/>
+    </row>
+    <row r="129" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A129" s="12" t="s">
         <v>191</v>
       </c>
@@ -12736,25 +13080,26 @@
         <v>0</v>
       </c>
       <c r="M129" s="2"/>
-      <c r="N129" s="64" t="s">
+      <c r="N129" s="2"/>
+      <c r="O129" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="O129" s="65">
+      <c r="P129" s="65">
         <v>46167</v>
       </c>
-      <c r="P129" s="65">
+      <c r="Q129" s="65">
         <v>46174</v>
       </c>
-      <c r="Q129" s="65">
+      <c r="R129" s="65">
         <v>46188</v>
       </c>
-      <c r="R129" s="65">
+      <c r="S129" s="65">
         <v>46195</v>
       </c>
-      <c r="S129" s="136"/>
       <c r="T129" s="136"/>
-    </row>
-    <row r="130" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U129" s="136"/>
+    </row>
+    <row r="130" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A130" s="12" t="s">
         <v>192</v>
       </c>
@@ -12792,25 +13137,26 @@
         <v>0</v>
       </c>
       <c r="M130" s="2"/>
-      <c r="N130" s="64" t="s">
+      <c r="N130" s="2"/>
+      <c r="O130" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="O130" s="65">
+      <c r="P130" s="65">
         <v>46179</v>
       </c>
-      <c r="P130" s="65">
+      <c r="Q130" s="65">
         <v>46186</v>
       </c>
-      <c r="Q130" s="65">
+      <c r="R130" s="65">
         <v>46202</v>
       </c>
-      <c r="R130" s="65">
+      <c r="S130" s="65">
         <v>46207</v>
       </c>
-      <c r="S130" s="136"/>
       <c r="T130" s="136"/>
-    </row>
-    <row r="131" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U130" s="136"/>
+    </row>
+    <row r="131" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A131" s="12" t="s">
         <v>193</v>
       </c>
@@ -12848,25 +13194,26 @@
         <v>0</v>
       </c>
       <c r="M131" s="2"/>
-      <c r="N131" s="64" t="s">
+      <c r="N131" s="2"/>
+      <c r="O131" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="O131" s="65">
+      <c r="P131" s="65">
         <v>46167</v>
       </c>
-      <c r="P131" s="65">
+      <c r="Q131" s="65">
         <v>46174</v>
       </c>
-      <c r="Q131" s="65">
+      <c r="R131" s="65">
         <v>46188</v>
       </c>
-      <c r="R131" s="65">
+      <c r="S131" s="65">
         <v>46195</v>
       </c>
-      <c r="S131" s="136"/>
       <c r="T131" s="136"/>
-    </row>
-    <row r="132" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U131" s="136"/>
+    </row>
+    <row r="132" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A132" s="12" t="s">
         <v>194</v>
       </c>
@@ -12904,25 +13251,26 @@
         <v>0</v>
       </c>
       <c r="M132" s="2"/>
-      <c r="N132" s="64" t="s">
+      <c r="N132" s="2"/>
+      <c r="O132" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="O132" s="65">
+      <c r="P132" s="65">
         <v>46179</v>
       </c>
-      <c r="P132" s="65">
+      <c r="Q132" s="65">
         <v>46186</v>
       </c>
-      <c r="Q132" s="65">
+      <c r="R132" s="65">
         <v>46202</v>
       </c>
-      <c r="R132" s="65">
+      <c r="S132" s="65">
         <v>46207</v>
       </c>
-      <c r="S132" s="136"/>
       <c r="T132" s="136"/>
-    </row>
-    <row r="133" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U132" s="136"/>
+    </row>
+    <row r="133" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A133" s="12" t="s">
         <v>195</v>
       </c>
@@ -12960,25 +13308,26 @@
         <v>0</v>
       </c>
       <c r="M133" s="2"/>
-      <c r="N133" s="64" t="s">
+      <c r="N133" s="2"/>
+      <c r="O133" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="O133" s="65">
+      <c r="P133" s="65">
         <v>46167</v>
       </c>
-      <c r="P133" s="65">
+      <c r="Q133" s="65">
         <v>46174</v>
       </c>
-      <c r="Q133" s="65">
+      <c r="R133" s="65">
         <v>46188</v>
       </c>
-      <c r="R133" s="65">
+      <c r="S133" s="65">
         <v>46195</v>
       </c>
-      <c r="S133" s="136"/>
       <c r="T133" s="136"/>
-    </row>
-    <row r="134" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U133" s="136"/>
+    </row>
+    <row r="134" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A134" s="12" t="s">
         <v>196</v>
       </c>
@@ -13016,25 +13365,26 @@
         <v>0</v>
       </c>
       <c r="M134" s="2"/>
-      <c r="N134" s="64" t="s">
+      <c r="N134" s="2"/>
+      <c r="O134" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="O134" s="65">
+      <c r="P134" s="65">
         <v>46167</v>
       </c>
-      <c r="P134" s="65">
+      <c r="Q134" s="65">
         <v>46174</v>
       </c>
-      <c r="Q134" s="65">
+      <c r="R134" s="65">
         <v>46188</v>
       </c>
-      <c r="R134" s="65">
+      <c r="S134" s="65">
         <v>46195</v>
       </c>
-      <c r="S134" s="136"/>
       <c r="T134" s="136"/>
-    </row>
-    <row r="135" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U134" s="136"/>
+    </row>
+    <row r="135" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A135" s="12" t="s">
         <v>197</v>
       </c>
@@ -13071,32 +13421,35 @@
       <c r="L135" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M135" s="2">
+      <c r="M135" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="N135" s="2">
         <v>5</v>
       </c>
-      <c r="N135" s="64" t="s">
+      <c r="O135" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="O135" s="65">
+      <c r="P135" s="65">
         <v>46140</v>
       </c>
-      <c r="P135" s="65">
+      <c r="Q135" s="65">
         <v>46148</v>
       </c>
-      <c r="Q135" s="65">
+      <c r="R135" s="65">
         <v>46162</v>
       </c>
-      <c r="R135" s="65">
+      <c r="S135" s="65">
         <v>46168</v>
       </c>
-      <c r="S135" s="139">
+      <c r="T135" s="139">
         <v>46204.919444444444</v>
       </c>
-      <c r="T135" s="136">
+      <c r="U135" s="136">
         <v>76.2</v>
       </c>
     </row>
-    <row r="136" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A136" s="12" t="s">
         <v>199</v>
       </c>
@@ -13133,32 +13486,35 @@
       <c r="L136" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M136" s="2">
+      <c r="M136" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="N136" s="2">
         <v>2</v>
       </c>
-      <c r="N136" s="64" t="s">
+      <c r="O136" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="O136" s="65">
+      <c r="P136" s="65">
         <v>46134</v>
       </c>
-      <c r="P136" s="65">
+      <c r="Q136" s="65">
         <v>46142</v>
       </c>
-      <c r="Q136" s="65">
+      <c r="R136" s="65">
         <v>46157</v>
       </c>
-      <c r="R136" s="65">
+      <c r="S136" s="65">
         <v>46163</v>
       </c>
-      <c r="S136" s="137">
+      <c r="T136" s="137">
         <v>46204.657638888886</v>
       </c>
-      <c r="T136" s="138">
+      <c r="U136" s="138">
         <v>31.8</v>
       </c>
     </row>
-    <row r="137" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A137" s="12" t="s">
         <v>200</v>
       </c>
@@ -13195,32 +13551,35 @@
       <c r="L137" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M137" s="2">
+      <c r="M137" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="N137" s="2">
         <v>4</v>
       </c>
-      <c r="N137" s="64" t="s">
+      <c r="O137" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="O137" s="65">
+      <c r="P137" s="65">
         <v>46140</v>
       </c>
-      <c r="P137" s="65">
+      <c r="Q137" s="65">
         <v>46148</v>
       </c>
-      <c r="Q137" s="65">
+      <c r="R137" s="65">
         <v>46162</v>
       </c>
-      <c r="R137" s="65">
+      <c r="S137" s="65">
         <v>46168</v>
       </c>
-      <c r="S137" s="139">
+      <c r="T137" s="139">
         <v>46204.919444444444</v>
       </c>
-      <c r="T137" s="136">
+      <c r="U137" s="136">
         <v>100.4</v>
       </c>
     </row>
-    <row r="138" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A138" s="12" t="s">
         <v>201</v>
       </c>
@@ -13257,32 +13616,35 @@
       <c r="L138" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M138" s="2">
-        <v>1</v>
-      </c>
-      <c r="N138" s="64" t="s">
+      <c r="M138" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="N138" s="2">
+        <v>1</v>
+      </c>
+      <c r="O138" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="O138" s="65">
+      <c r="P138" s="65">
         <v>46134</v>
       </c>
-      <c r="P138" s="65">
+      <c r="Q138" s="65">
         <v>46142</v>
       </c>
-      <c r="Q138" s="65">
+      <c r="R138" s="65">
         <v>46157</v>
       </c>
-      <c r="R138" s="65">
+      <c r="S138" s="65">
         <v>46163</v>
       </c>
-      <c r="S138" s="137">
+      <c r="T138" s="137">
         <v>46204.919444444444</v>
       </c>
-      <c r="T138" s="138">
+      <c r="U138" s="138">
         <v>73</v>
       </c>
     </row>
-    <row r="139" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A139" s="12" t="s">
         <v>202</v>
       </c>
@@ -13319,32 +13681,35 @@
       <c r="L139" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M139" s="2">
+      <c r="M139" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="N139" s="2">
         <v>3</v>
       </c>
-      <c r="N139" s="64" t="s">
+      <c r="O139" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="O139" s="65">
+      <c r="P139" s="65">
         <v>46140</v>
       </c>
-      <c r="P139" s="65">
+      <c r="Q139" s="65">
         <v>46148</v>
       </c>
-      <c r="Q139" s="65">
+      <c r="R139" s="65">
         <v>46162</v>
       </c>
-      <c r="R139" s="65">
+      <c r="S139" s="65">
         <v>46168</v>
       </c>
-      <c r="S139" s="139">
+      <c r="T139" s="139">
         <v>46204.919444444444</v>
       </c>
-      <c r="T139" s="136">
+      <c r="U139" s="136">
         <v>55.5</v>
       </c>
     </row>
-    <row r="140" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A140" s="12" t="s">
         <v>203</v>
       </c>
@@ -13381,28 +13746,31 @@
       <c r="L140" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M140" s="2">
+      <c r="M140" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N140" s="2">
         <v>5</v>
       </c>
-      <c r="N140" s="64" t="s">
+      <c r="O140" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="O140" s="65">
+      <c r="P140" s="65">
         <v>46197</v>
       </c>
-      <c r="P140" s="65">
+      <c r="Q140" s="65">
         <v>46204</v>
       </c>
-      <c r="Q140" s="65">
+      <c r="R140" s="65">
         <v>46218</v>
       </c>
-      <c r="R140" s="65">
+      <c r="S140" s="65">
         <v>46224</v>
       </c>
-      <c r="S140" s="136"/>
       <c r="T140" s="136"/>
-    </row>
-    <row r="141" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U140" s="136"/>
+    </row>
+    <row r="141" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A141" s="12" t="s">
         <v>205</v>
       </c>
@@ -13439,28 +13807,31 @@
       <c r="L141" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M141" s="2">
+      <c r="M141" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N141" s="2">
         <v>7</v>
       </c>
-      <c r="N141" s="64" t="s">
+      <c r="O141" s="64" t="s">
         <v>184</v>
       </c>
-      <c r="O141" s="65">
+      <c r="P141" s="65">
         <v>46259</v>
       </c>
-      <c r="P141" s="65">
+      <c r="Q141" s="65">
         <v>46266</v>
       </c>
-      <c r="Q141" s="65">
+      <c r="R141" s="65">
         <v>46280</v>
       </c>
-      <c r="R141" s="65">
+      <c r="S141" s="65">
         <v>46286</v>
       </c>
-      <c r="S141" s="136"/>
       <c r="T141" s="136"/>
-    </row>
-    <row r="142" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U141" s="136"/>
+    </row>
+    <row r="142" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A142" s="12" t="s">
         <v>206</v>
       </c>
@@ -13497,28 +13868,31 @@
       <c r="L142" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M142" s="2">
+      <c r="M142" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N142" s="2">
         <v>9</v>
       </c>
-      <c r="N142" s="64" t="s">
+      <c r="O142" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="O142" s="65">
+      <c r="P142" s="65">
         <v>46197</v>
       </c>
-      <c r="P142" s="65">
+      <c r="Q142" s="65">
         <v>46204</v>
       </c>
-      <c r="Q142" s="65">
+      <c r="R142" s="65">
         <v>46218</v>
       </c>
-      <c r="R142" s="65">
+      <c r="S142" s="65">
         <v>46224</v>
       </c>
-      <c r="S142" s="136"/>
       <c r="T142" s="136"/>
-    </row>
-    <row r="143" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U142" s="136"/>
+    </row>
+    <row r="143" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A143" s="12" t="s">
         <v>207</v>
       </c>
@@ -13555,28 +13929,31 @@
       <c r="L143" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M143" s="2">
+      <c r="M143" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N143" s="2">
         <v>3</v>
       </c>
-      <c r="N143" s="64" t="s">
+      <c r="O143" s="64" t="s">
         <v>184</v>
       </c>
-      <c r="O143" s="65">
+      <c r="P143" s="65">
         <v>46259</v>
       </c>
-      <c r="P143" s="65">
+      <c r="Q143" s="65">
         <v>46266</v>
       </c>
-      <c r="Q143" s="65">
+      <c r="R143" s="65">
         <v>46280</v>
       </c>
-      <c r="R143" s="65">
+      <c r="S143" s="65">
         <v>46286</v>
       </c>
-      <c r="S143" s="136"/>
       <c r="T143" s="136"/>
-    </row>
-    <row r="144" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U143" s="136"/>
+    </row>
+    <row r="144" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A144" s="12" t="s">
         <v>208</v>
       </c>
@@ -13613,28 +13990,31 @@
       <c r="L144" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M144" s="2">
-        <v>1</v>
-      </c>
-      <c r="N144" s="64" t="s">
+      <c r="M144" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N144" s="2">
+        <v>1</v>
+      </c>
+      <c r="O144" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="O144" s="65">
+      <c r="P144" s="65">
         <v>46197</v>
       </c>
-      <c r="P144" s="65">
+      <c r="Q144" s="65">
         <v>46204</v>
       </c>
-      <c r="Q144" s="65">
+      <c r="R144" s="65">
         <v>46218</v>
       </c>
-      <c r="R144" s="65">
+      <c r="S144" s="65">
         <v>46224</v>
       </c>
-      <c r="S144" s="136"/>
       <c r="T144" s="136"/>
-    </row>
-    <row r="145" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U144" s="136"/>
+    </row>
+    <row r="145" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A145" s="12" t="s">
         <v>209</v>
       </c>
@@ -13671,28 +14051,31 @@
       <c r="L145" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M145" s="2">
+      <c r="M145" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N145" s="2">
         <v>2</v>
       </c>
-      <c r="N145" s="64" t="s">
+      <c r="O145" s="64" t="s">
         <v>184</v>
       </c>
-      <c r="O145" s="65">
+      <c r="P145" s="65">
         <v>46259</v>
       </c>
-      <c r="P145" s="65">
+      <c r="Q145" s="65">
         <v>46266</v>
       </c>
-      <c r="Q145" s="65">
+      <c r="R145" s="65">
         <v>46280</v>
       </c>
-      <c r="R145" s="65">
+      <c r="S145" s="65">
         <v>46286</v>
       </c>
-      <c r="S145" s="136"/>
       <c r="T145" s="136"/>
-    </row>
-    <row r="146" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U145" s="136"/>
+    </row>
+    <row r="146" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A146" s="12" t="s">
         <v>210</v>
       </c>
@@ -13729,28 +14112,31 @@
       <c r="L146" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M146" s="2">
+      <c r="M146" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N146" s="2">
         <v>8</v>
       </c>
-      <c r="N146" s="64" t="s">
+      <c r="O146" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="O146" s="65">
+      <c r="P146" s="65">
         <v>46197</v>
       </c>
-      <c r="P146" s="65">
+      <c r="Q146" s="65">
         <v>46204</v>
       </c>
-      <c r="Q146" s="65">
+      <c r="R146" s="65">
         <v>46218</v>
       </c>
-      <c r="R146" s="65">
+      <c r="S146" s="65">
         <v>46224</v>
       </c>
-      <c r="S146" s="136"/>
       <c r="T146" s="136"/>
-    </row>
-    <row r="147" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U146" s="136"/>
+    </row>
+    <row r="147" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A147" s="12" t="s">
         <v>211</v>
       </c>
@@ -13787,28 +14173,31 @@
       <c r="L147" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M147" s="2">
+      <c r="M147" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N147" s="2">
         <v>4</v>
       </c>
-      <c r="N147" s="64" t="s">
+      <c r="O147" s="64" t="s">
         <v>184</v>
       </c>
-      <c r="O147" s="65">
+      <c r="P147" s="65">
         <v>46259</v>
       </c>
-      <c r="P147" s="65">
+      <c r="Q147" s="65">
         <v>46266</v>
       </c>
-      <c r="Q147" s="65">
+      <c r="R147" s="65">
         <v>46280</v>
       </c>
-      <c r="R147" s="65">
+      <c r="S147" s="65">
         <v>46286</v>
       </c>
-      <c r="S147" s="136"/>
       <c r="T147" s="136"/>
-    </row>
-    <row r="148" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U147" s="136"/>
+    </row>
+    <row r="148" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A148" s="12" t="s">
         <v>212</v>
       </c>
@@ -13845,28 +14234,31 @@
       <c r="L148" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M148" s="2">
+      <c r="M148" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N148" s="2">
         <v>6</v>
       </c>
-      <c r="N148" s="64" t="s">
+      <c r="O148" s="64" t="s">
         <v>184</v>
       </c>
-      <c r="O148" s="65">
+      <c r="P148" s="65">
         <v>46259</v>
       </c>
-      <c r="P148" s="65">
+      <c r="Q148" s="65">
         <v>46266</v>
       </c>
-      <c r="Q148" s="65">
+      <c r="R148" s="65">
         <v>46280</v>
       </c>
-      <c r="R148" s="65">
+      <c r="S148" s="65">
         <v>46286</v>
       </c>
-      <c r="S148" s="136"/>
       <c r="T148" s="136"/>
-    </row>
-    <row r="149" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U148" s="136"/>
+    </row>
+    <row r="149" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A149" s="12" t="s">
         <v>213</v>
       </c>
@@ -13903,28 +14295,31 @@
       <c r="L149" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M149" s="2">
-        <v>1</v>
-      </c>
-      <c r="N149" s="64" t="s">
+      <c r="M149" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="N149" s="2">
+        <v>1</v>
+      </c>
+      <c r="O149" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="O149" s="65">
+      <c r="P149" s="65">
         <v>46224</v>
       </c>
-      <c r="P149" s="65">
+      <c r="Q149" s="65">
         <v>46231</v>
       </c>
-      <c r="Q149" s="65">
+      <c r="R149" s="65">
         <v>46246</v>
       </c>
-      <c r="R149" s="65">
+      <c r="S149" s="65">
         <v>46252</v>
       </c>
-      <c r="S149" s="136"/>
       <c r="T149" s="136"/>
-    </row>
-    <row r="150" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U149" s="136"/>
+    </row>
+    <row r="150" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A150" s="12" t="s">
         <v>215</v>
       </c>
@@ -13961,28 +14356,31 @@
       <c r="L150" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M150" s="2">
+      <c r="M150" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="N150" s="2">
         <v>2</v>
       </c>
-      <c r="N150" s="64" t="s">
+      <c r="O150" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="O150" s="65">
+      <c r="P150" s="65">
         <v>46224</v>
       </c>
-      <c r="P150" s="65">
+      <c r="Q150" s="65">
         <v>46231</v>
       </c>
-      <c r="Q150" s="65">
+      <c r="R150" s="65">
         <v>46246</v>
       </c>
-      <c r="R150" s="65">
+      <c r="S150" s="65">
         <v>46252</v>
       </c>
-      <c r="S150" s="136"/>
       <c r="T150" s="136"/>
-    </row>
-    <row r="151" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U150" s="136"/>
+    </row>
+    <row r="151" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A151" s="12" t="s">
         <v>216</v>
       </c>
@@ -14019,28 +14417,31 @@
       <c r="L151" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M151" s="2">
+      <c r="M151" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="N151" s="2">
         <v>3</v>
       </c>
-      <c r="N151" s="64" t="s">
+      <c r="O151" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="O151" s="65">
+      <c r="P151" s="65">
         <v>46224</v>
       </c>
-      <c r="P151" s="65">
+      <c r="Q151" s="65">
         <v>46231</v>
       </c>
-      <c r="Q151" s="65">
+      <c r="R151" s="65">
         <v>46246</v>
       </c>
-      <c r="R151" s="65">
+      <c r="S151" s="65">
         <v>46252</v>
       </c>
-      <c r="S151" s="136"/>
       <c r="T151" s="136"/>
-    </row>
-    <row r="152" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U151" s="136"/>
+    </row>
+    <row r="152" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A152" s="12" t="s">
         <v>217</v>
       </c>
@@ -14077,28 +14478,31 @@
       <c r="L152" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M152" s="2">
+      <c r="M152" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="N152" s="2">
         <v>4</v>
       </c>
-      <c r="N152" s="64" t="s">
+      <c r="O152" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="O152" s="65">
+      <c r="P152" s="65">
         <v>46224</v>
       </c>
-      <c r="P152" s="65">
+      <c r="Q152" s="65">
         <v>46231</v>
       </c>
-      <c r="Q152" s="65">
+      <c r="R152" s="65">
         <v>46246</v>
       </c>
-      <c r="R152" s="65">
+      <c r="S152" s="65">
         <v>46252</v>
       </c>
-      <c r="S152" s="136"/>
       <c r="T152" s="136"/>
-    </row>
-    <row r="153" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U152" s="136"/>
+    </row>
+    <row r="153" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A153" s="12" t="s">
         <v>218</v>
       </c>
@@ -14135,28 +14539,31 @@
       <c r="L153" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M153" s="2">
+      <c r="M153" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="N153" s="2">
         <v>5</v>
       </c>
-      <c r="N153" s="64" t="s">
+      <c r="O153" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="O153" s="65">
+      <c r="P153" s="65">
         <v>46224</v>
       </c>
-      <c r="P153" s="65">
+      <c r="Q153" s="65">
         <v>46231</v>
       </c>
-      <c r="Q153" s="65">
+      <c r="R153" s="65">
         <v>46246</v>
       </c>
-      <c r="R153" s="65">
+      <c r="S153" s="65">
         <v>46252</v>
       </c>
-      <c r="S153" s="136"/>
       <c r="T153" s="136"/>
-    </row>
-    <row r="154" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U153" s="136"/>
+    </row>
+    <row r="154" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A154" s="12" t="s">
         <v>219</v>
       </c>
@@ -14193,28 +14600,31 @@
       <c r="L154" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M154" s="2">
+      <c r="M154" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="N154" s="2">
         <v>6</v>
       </c>
-      <c r="N154" s="64" t="s">
+      <c r="O154" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="O154" s="65">
+      <c r="P154" s="65">
         <v>46224</v>
       </c>
-      <c r="P154" s="65">
+      <c r="Q154" s="65">
         <v>46231</v>
       </c>
-      <c r="Q154" s="65">
+      <c r="R154" s="65">
         <v>46246</v>
       </c>
-      <c r="R154" s="65">
+      <c r="S154" s="65">
         <v>46252</v>
       </c>
-      <c r="S154" s="136"/>
       <c r="T154" s="136"/>
-    </row>
-    <row r="155" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U154" s="136"/>
+    </row>
+    <row r="155" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A155" s="12" t="s">
         <v>220</v>
       </c>
@@ -14251,28 +14661,31 @@
       <c r="L155" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M155" s="2">
-        <v>1</v>
-      </c>
-      <c r="N155" s="64" t="s">
+      <c r="M155" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="N155" s="2">
+        <v>1</v>
+      </c>
+      <c r="O155" s="64" t="s">
         <v>222</v>
       </c>
-      <c r="O155" s="65">
+      <c r="P155" s="65">
         <v>46238</v>
       </c>
-      <c r="P155" s="65">
+      <c r="Q155" s="65">
         <v>46246</v>
       </c>
-      <c r="Q155" s="65">
+      <c r="R155" s="65">
         <v>46260</v>
       </c>
-      <c r="R155" s="65">
+      <c r="S155" s="65">
         <v>46266</v>
       </c>
-      <c r="S155" s="136"/>
       <c r="T155" s="136"/>
-    </row>
-    <row r="156" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U155" s="136"/>
+    </row>
+    <row r="156" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A156" s="12" t="s">
         <v>223</v>
       </c>
@@ -14309,28 +14722,31 @@
       <c r="L156" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M156" s="2">
+      <c r="M156" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="N156" s="2">
         <v>2</v>
       </c>
-      <c r="N156" s="64" t="s">
+      <c r="O156" s="64" t="s">
         <v>222</v>
       </c>
-      <c r="O156" s="65">
+      <c r="P156" s="65">
         <v>46238</v>
       </c>
-      <c r="P156" s="65">
+      <c r="Q156" s="65">
         <v>46246</v>
       </c>
-      <c r="Q156" s="65">
+      <c r="R156" s="65">
         <v>46260</v>
       </c>
-      <c r="R156" s="65">
+      <c r="S156" s="65">
         <v>46266</v>
       </c>
-      <c r="S156" s="136"/>
       <c r="T156" s="136"/>
-    </row>
-    <row r="157" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U156" s="136"/>
+    </row>
+    <row r="157" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A157" s="12" t="s">
         <v>224</v>
       </c>
@@ -14367,28 +14783,31 @@
       <c r="L157" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M157" s="2">
+      <c r="M157" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="N157" s="2">
         <v>3</v>
       </c>
-      <c r="N157" s="64" t="s">
+      <c r="O157" s="64" t="s">
         <v>222</v>
       </c>
-      <c r="O157" s="65">
+      <c r="P157" s="65">
         <v>46238</v>
       </c>
-      <c r="P157" s="65">
+      <c r="Q157" s="65">
         <v>46246</v>
       </c>
-      <c r="Q157" s="65">
+      <c r="R157" s="65">
         <v>46260</v>
       </c>
-      <c r="R157" s="65">
+      <c r="S157" s="65">
         <v>46266</v>
       </c>
-      <c r="S157" s="136"/>
       <c r="T157" s="136"/>
-    </row>
-    <row r="158" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U157" s="136"/>
+    </row>
+    <row r="158" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A158" s="12" t="s">
         <v>225</v>
       </c>
@@ -14425,28 +14844,31 @@
       <c r="L158" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M158" s="2">
+      <c r="M158" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="N158" s="2">
         <v>4</v>
       </c>
-      <c r="N158" s="64" t="s">
+      <c r="O158" s="64" t="s">
         <v>222</v>
       </c>
-      <c r="O158" s="65">
+      <c r="P158" s="65">
         <v>46238</v>
       </c>
-      <c r="P158" s="65">
+      <c r="Q158" s="65">
         <v>46246</v>
       </c>
-      <c r="Q158" s="65">
+      <c r="R158" s="65">
         <v>46260</v>
       </c>
-      <c r="R158" s="65">
+      <c r="S158" s="65">
         <v>46266</v>
       </c>
-      <c r="S158" s="136"/>
       <c r="T158" s="136"/>
-    </row>
-    <row r="159" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U158" s="136"/>
+    </row>
+    <row r="159" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A159" s="12" t="s">
         <v>226</v>
       </c>
@@ -14483,28 +14905,31 @@
       <c r="L159" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M159" s="2">
+      <c r="M159" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="N159" s="2">
         <v>5</v>
       </c>
-      <c r="N159" s="64" t="s">
+      <c r="O159" s="64" t="s">
         <v>222</v>
       </c>
-      <c r="O159" s="65">
+      <c r="P159" s="65">
         <v>46238</v>
       </c>
-      <c r="P159" s="65">
+      <c r="Q159" s="65">
         <v>46246</v>
       </c>
-      <c r="Q159" s="65">
+      <c r="R159" s="65">
         <v>46260</v>
       </c>
-      <c r="R159" s="65">
+      <c r="S159" s="65">
         <v>46266</v>
       </c>
-      <c r="S159" s="136"/>
       <c r="T159" s="136"/>
-    </row>
-    <row r="160" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U159" s="136"/>
+    </row>
+    <row r="160" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A160" s="12" t="s">
         <v>227</v>
       </c>
@@ -14541,28 +14966,31 @@
       <c r="L160" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M160" s="2">
+      <c r="M160" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="N160" s="2">
         <v>6</v>
       </c>
-      <c r="N160" s="64" t="s">
+      <c r="O160" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="O160" s="65">
+      <c r="P160" s="65">
         <v>46224</v>
       </c>
-      <c r="P160" s="65">
+      <c r="Q160" s="65">
         <v>46231</v>
       </c>
-      <c r="Q160" s="65">
+      <c r="R160" s="65">
         <v>46246</v>
       </c>
-      <c r="R160" s="65">
+      <c r="S160" s="65">
         <v>46252</v>
       </c>
-      <c r="S160" s="136"/>
       <c r="T160" s="136"/>
-    </row>
-    <row r="161" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U160" s="136"/>
+    </row>
+    <row r="161" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A161" s="12" t="s">
         <v>228</v>
       </c>
@@ -14599,32 +15027,35 @@
       <c r="L161" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M161" s="2">
-        <v>1</v>
-      </c>
-      <c r="N161" s="64" t="s">
+      <c r="M161" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="N161" s="2">
+        <v>1</v>
+      </c>
+      <c r="O161" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="O161" s="65">
+      <c r="P161" s="65">
         <v>46155</v>
       </c>
-      <c r="P161" s="65">
+      <c r="Q161" s="65">
         <v>46162</v>
       </c>
-      <c r="Q161" s="65">
+      <c r="R161" s="65">
         <v>46176</v>
       </c>
-      <c r="R161" s="65">
+      <c r="S161" s="65">
         <v>46182</v>
       </c>
-      <c r="S161" s="139">
+      <c r="T161" s="139">
         <v>46234</v>
       </c>
-      <c r="T161" s="136" t="s">
+      <c r="U161" s="136" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="162" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A162" s="12" t="s">
         <v>231</v>
       </c>
@@ -14661,32 +15092,35 @@
       <c r="L162" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M162" s="2">
+      <c r="M162" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="N162" s="2">
         <v>2</v>
       </c>
-      <c r="N162" s="64" t="s">
+      <c r="O162" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="O162" s="65">
+      <c r="P162" s="65">
         <v>46155</v>
       </c>
-      <c r="P162" s="65">
+      <c r="Q162" s="65">
         <v>46162</v>
       </c>
-      <c r="Q162" s="65">
+      <c r="R162" s="65">
         <v>46176</v>
       </c>
-      <c r="R162" s="65">
+      <c r="S162" s="65">
         <v>46182</v>
       </c>
-      <c r="S162" s="139">
+      <c r="T162" s="139">
         <v>46234</v>
       </c>
-      <c r="T162" s="136" t="s">
+      <c r="U162" s="136" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="163" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A163" s="12" t="s">
         <v>232</v>
       </c>
@@ -14723,32 +15157,35 @@
       <c r="L163" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="M163" s="2">
+      <c r="M163" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="N163" s="2">
         <v>3</v>
       </c>
-      <c r="N163" s="64" t="s">
+      <c r="O163" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="O163" s="65">
+      <c r="P163" s="65">
         <v>46155</v>
       </c>
-      <c r="P163" s="65">
+      <c r="Q163" s="65">
         <v>46162</v>
       </c>
-      <c r="Q163" s="65">
+      <c r="R163" s="65">
         <v>46176</v>
       </c>
-      <c r="R163" s="65">
+      <c r="S163" s="65">
         <v>46182</v>
       </c>
-      <c r="S163" s="139">
+      <c r="T163" s="139">
         <v>46234</v>
       </c>
-      <c r="T163" s="136" t="s">
+      <c r="U163" s="136" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="164" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A164" s="12" t="s">
         <v>233</v>
       </c>
@@ -14786,25 +15223,26 @@
         <v>0</v>
       </c>
       <c r="M164" s="2"/>
-      <c r="N164" s="64" t="s">
+      <c r="N164" s="2"/>
+      <c r="O164" s="64" t="s">
         <v>235</v>
       </c>
-      <c r="O164" s="65">
+      <c r="P164" s="65">
         <v>46195</v>
       </c>
-      <c r="P164" s="65">
+      <c r="Q164" s="65">
         <v>46202</v>
-      </c>
-      <c r="Q164" s="65">
-        <v>46221</v>
       </c>
       <c r="R164" s="65">
         <v>46221</v>
       </c>
-      <c r="S164" s="136"/>
+      <c r="S164" s="65">
+        <v>46221</v>
+      </c>
       <c r="T164" s="136"/>
-    </row>
-    <row r="165" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U164" s="136"/>
+    </row>
+    <row r="165" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A165" s="12" t="s">
         <v>236</v>
       </c>
@@ -14842,25 +15280,26 @@
         <v>0</v>
       </c>
       <c r="M165" s="2"/>
-      <c r="N165" s="64" t="s">
+      <c r="N165" s="2"/>
+      <c r="O165" s="64" t="s">
         <v>237</v>
       </c>
-      <c r="O165" s="65">
+      <c r="P165" s="65">
         <v>46179</v>
       </c>
-      <c r="P165" s="65">
+      <c r="Q165" s="65">
         <v>46186</v>
       </c>
-      <c r="Q165" s="65">
+      <c r="R165" s="65">
         <v>46202</v>
       </c>
-      <c r="R165" s="65">
+      <c r="S165" s="65">
         <v>46207</v>
       </c>
-      <c r="S165" s="136"/>
       <c r="T165" s="136"/>
-    </row>
-    <row r="166" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U165" s="136"/>
+    </row>
+    <row r="166" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A166" s="12" t="s">
         <v>238</v>
       </c>
@@ -14898,25 +15337,26 @@
         <v>0</v>
       </c>
       <c r="M166" s="2"/>
-      <c r="N166" s="64" t="s">
+      <c r="N166" s="2"/>
+      <c r="O166" s="64" t="s">
         <v>235</v>
       </c>
-      <c r="O166" s="65">
+      <c r="P166" s="65">
         <v>46195</v>
       </c>
-      <c r="P166" s="65">
+      <c r="Q166" s="65">
         <v>46202</v>
-      </c>
-      <c r="Q166" s="65">
-        <v>46221</v>
       </c>
       <c r="R166" s="65">
         <v>46221</v>
       </c>
-      <c r="S166" s="136"/>
+      <c r="S166" s="65">
+        <v>46221</v>
+      </c>
       <c r="T166" s="136"/>
-    </row>
-    <row r="167" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U166" s="136"/>
+    </row>
+    <row r="167" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A167" s="12" t="s">
         <v>239</v>
       </c>
@@ -14954,25 +15394,26 @@
         <v>0</v>
       </c>
       <c r="M167" s="2"/>
-      <c r="N167" s="64" t="s">
+      <c r="N167" s="2"/>
+      <c r="O167" s="64" t="s">
         <v>237</v>
       </c>
-      <c r="O167" s="65">
+      <c r="P167" s="65">
         <v>46179</v>
       </c>
-      <c r="P167" s="65">
+      <c r="Q167" s="65">
         <v>46186</v>
       </c>
-      <c r="Q167" s="65">
+      <c r="R167" s="65">
         <v>46202</v>
       </c>
-      <c r="R167" s="65">
+      <c r="S167" s="65">
         <v>46207</v>
       </c>
-      <c r="S167" s="136"/>
       <c r="T167" s="136"/>
-    </row>
-    <row r="168" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U167" s="136"/>
+    </row>
+    <row r="168" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A168" s="12" t="s">
         <v>243</v>
       </c>
@@ -15009,30 +15450,35 @@
       <c r="L168" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M168" s="2"/>
-      <c r="N168" s="64" t="s">
+      <c r="M168" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="N168" s="2">
+        <v>1</v>
+      </c>
+      <c r="O168" s="64" t="s">
         <v>242</v>
       </c>
-      <c r="O168" s="65">
+      <c r="P168" s="65">
         <v>46175</v>
       </c>
-      <c r="P168" s="65">
+      <c r="Q168" s="65">
         <v>46182</v>
       </c>
-      <c r="Q168" s="65">
+      <c r="R168" s="65">
         <v>46197</v>
       </c>
-      <c r="R168" s="65">
+      <c r="S168" s="65">
         <v>46203</v>
       </c>
-      <c r="S168" s="139">
+      <c r="T168" s="139">
         <v>46234</v>
       </c>
-      <c r="T168" s="136" t="s">
+      <c r="U168" s="136" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="169" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A169" s="12" t="s">
         <v>244</v>
       </c>
@@ -15069,30 +15515,35 @@
       <c r="L169" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M169" s="2"/>
-      <c r="N169" s="64" t="s">
+      <c r="M169" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="N169" s="2">
+        <v>2</v>
+      </c>
+      <c r="O169" s="64" t="s">
         <v>242</v>
       </c>
-      <c r="O169" s="65">
+      <c r="P169" s="65">
         <v>46175</v>
       </c>
-      <c r="P169" s="65">
+      <c r="Q169" s="65">
         <v>46182</v>
       </c>
-      <c r="Q169" s="65">
+      <c r="R169" s="65">
         <v>46197</v>
       </c>
-      <c r="R169" s="65">
+      <c r="S169" s="65">
         <v>46203</v>
       </c>
-      <c r="S169" s="139">
+      <c r="T169" s="139">
         <v>46234</v>
       </c>
-      <c r="T169" s="136" t="s">
+      <c r="U169" s="136" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="170" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A170" s="12" t="s">
         <v>245</v>
       </c>
@@ -15129,30 +15580,35 @@
       <c r="L170" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M170" s="2"/>
-      <c r="N170" s="64" t="s">
+      <c r="M170" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="N170" s="2">
+        <v>3</v>
+      </c>
+      <c r="O170" s="64" t="s">
         <v>242</v>
       </c>
-      <c r="O170" s="65">
+      <c r="P170" s="65">
         <v>46175</v>
       </c>
-      <c r="P170" s="65">
+      <c r="Q170" s="65">
         <v>46182</v>
       </c>
-      <c r="Q170" s="65">
+      <c r="R170" s="65">
         <v>46197</v>
       </c>
-      <c r="R170" s="65">
+      <c r="S170" s="65">
         <v>46203</v>
       </c>
-      <c r="S170" s="139">
+      <c r="T170" s="139">
         <v>46234</v>
       </c>
-      <c r="T170" s="136" t="s">
+      <c r="U170" s="136" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="171" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A171" s="12" t="s">
         <v>246</v>
       </c>
@@ -15189,30 +15645,35 @@
       <c r="L171" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M171" s="2"/>
-      <c r="N171" s="64" t="s">
+      <c r="M171" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="N171" s="2">
+        <v>4</v>
+      </c>
+      <c r="O171" s="64" t="s">
         <v>242</v>
       </c>
-      <c r="O171" s="65">
+      <c r="P171" s="65">
         <v>46175</v>
       </c>
-      <c r="P171" s="65">
+      <c r="Q171" s="65">
         <v>46182</v>
       </c>
-      <c r="Q171" s="65">
+      <c r="R171" s="65">
         <v>46197</v>
       </c>
-      <c r="R171" s="65">
+      <c r="S171" s="65">
         <v>46203</v>
       </c>
-      <c r="S171" s="139">
+      <c r="T171" s="139">
         <v>46234</v>
       </c>
-      <c r="T171" s="136" t="s">
+      <c r="U171" s="136" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="172" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A172" s="12" t="s">
         <v>247</v>
       </c>
@@ -15249,30 +15710,35 @@
       <c r="L172" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M172" s="2"/>
-      <c r="N172" s="64" t="s">
+      <c r="M172" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="N172" s="2">
+        <v>5</v>
+      </c>
+      <c r="O172" s="64" t="s">
         <v>242</v>
       </c>
-      <c r="O172" s="65">
+      <c r="P172" s="65">
         <v>46175</v>
       </c>
-      <c r="P172" s="65">
+      <c r="Q172" s="65">
         <v>46182</v>
       </c>
-      <c r="Q172" s="65">
+      <c r="R172" s="65">
         <v>46197</v>
       </c>
-      <c r="R172" s="65">
+      <c r="S172" s="65">
         <v>46203</v>
       </c>
-      <c r="S172" s="139">
+      <c r="T172" s="139">
         <v>46234</v>
       </c>
-      <c r="T172" s="136" t="s">
+      <c r="U172" s="136" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="173" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A173" s="12" t="s">
         <v>248</v>
       </c>
@@ -15309,30 +15775,35 @@
       <c r="L173" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M173" s="2"/>
-      <c r="N173" s="64" t="s">
+      <c r="M173" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="N173" s="2">
+        <v>6</v>
+      </c>
+      <c r="O173" s="64" t="s">
         <v>242</v>
       </c>
-      <c r="O173" s="65">
+      <c r="P173" s="65">
         <v>46175</v>
       </c>
-      <c r="P173" s="65">
+      <c r="Q173" s="65">
         <v>46182</v>
       </c>
-      <c r="Q173" s="65">
+      <c r="R173" s="65">
         <v>46197</v>
       </c>
-      <c r="R173" s="65">
+      <c r="S173" s="65">
         <v>46203</v>
       </c>
-      <c r="S173" s="139">
+      <c r="T173" s="139">
         <v>46234</v>
       </c>
-      <c r="T173" s="136" t="s">
+      <c r="U173" s="136" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="174" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A174" s="12" t="s">
         <v>249</v>
       </c>
@@ -15369,30 +15840,35 @@
       <c r="L174" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M174" s="2"/>
-      <c r="N174" s="64" t="s">
+      <c r="M174" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="N174" s="2">
+        <v>7</v>
+      </c>
+      <c r="O174" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="O174" s="65">
+      <c r="P174" s="65">
         <v>46155</v>
       </c>
-      <c r="P174" s="65">
+      <c r="Q174" s="65">
         <v>46162</v>
       </c>
-      <c r="Q174" s="65">
+      <c r="R174" s="65">
         <v>46176</v>
       </c>
-      <c r="R174" s="65">
+      <c r="S174" s="65">
         <v>46182</v>
       </c>
-      <c r="S174" s="139">
+      <c r="T174" s="139">
         <v>46234</v>
       </c>
-      <c r="T174" s="136" t="s">
+      <c r="U174" s="136" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="175" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A175" s="12" t="s">
         <v>250</v>
       </c>
@@ -15429,30 +15905,35 @@
       <c r="L175" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M175" s="2"/>
-      <c r="N175" s="64" t="s">
+      <c r="M175" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="N175" s="2">
+        <v>8</v>
+      </c>
+      <c r="O175" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="O175" s="65">
+      <c r="P175" s="65">
         <v>46155</v>
       </c>
-      <c r="P175" s="65">
+      <c r="Q175" s="65">
         <v>46162</v>
       </c>
-      <c r="Q175" s="65">
+      <c r="R175" s="65">
         <v>46176</v>
       </c>
-      <c r="R175" s="65">
+      <c r="S175" s="65">
         <v>46182</v>
       </c>
-      <c r="S175" s="139">
+      <c r="T175" s="139">
         <v>46234</v>
       </c>
-      <c r="T175" s="136" t="s">
+      <c r="U175" s="136" t="s">
         <v>1199</v>
       </c>
     </row>
-    <row r="176" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A176" s="12" t="s">
         <v>251</v>
       </c>
@@ -15490,25 +15971,26 @@
         <v>0</v>
       </c>
       <c r="M176" s="2"/>
-      <c r="N176" s="64" t="s">
+      <c r="N176" s="2"/>
+      <c r="O176" s="64" t="s">
         <v>235</v>
       </c>
-      <c r="O176" s="65">
+      <c r="P176" s="65">
         <v>46195</v>
       </c>
-      <c r="P176" s="65">
+      <c r="Q176" s="65">
         <v>46202</v>
-      </c>
-      <c r="Q176" s="65">
-        <v>46221</v>
       </c>
       <c r="R176" s="65">
         <v>46221</v>
       </c>
-      <c r="S176" s="136"/>
+      <c r="S176" s="65">
+        <v>46221</v>
+      </c>
       <c r="T176" s="136"/>
-    </row>
-    <row r="177" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U176" s="136"/>
+    </row>
+    <row r="177" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A177" s="12" t="s">
         <v>253</v>
       </c>
@@ -15546,25 +16028,26 @@
         <v>0</v>
       </c>
       <c r="M177" s="2"/>
-      <c r="N177" s="64" t="s">
+      <c r="N177" s="2"/>
+      <c r="O177" s="64" t="s">
         <v>237</v>
       </c>
-      <c r="O177" s="65">
+      <c r="P177" s="65">
         <v>46179</v>
       </c>
-      <c r="P177" s="65">
+      <c r="Q177" s="65">
         <v>46186</v>
       </c>
-      <c r="Q177" s="65">
+      <c r="R177" s="65">
         <v>46202</v>
       </c>
-      <c r="R177" s="65">
+      <c r="S177" s="65">
         <v>46207</v>
       </c>
-      <c r="S177" s="136"/>
       <c r="T177" s="136"/>
-    </row>
-    <row r="178" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U177" s="136"/>
+    </row>
+    <row r="178" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A178" s="12" t="s">
         <v>254</v>
       </c>
@@ -15602,25 +16085,26 @@
         <v>0</v>
       </c>
       <c r="M178" s="2"/>
-      <c r="N178" s="64" t="s">
+      <c r="N178" s="2"/>
+      <c r="O178" s="64" t="s">
         <v>235</v>
       </c>
-      <c r="O178" s="65">
+      <c r="P178" s="65">
         <v>46195</v>
       </c>
-      <c r="P178" s="65">
+      <c r="Q178" s="65">
         <v>46202</v>
-      </c>
-      <c r="Q178" s="65">
-        <v>46221</v>
       </c>
       <c r="R178" s="65">
         <v>46221</v>
       </c>
-      <c r="S178" s="136"/>
+      <c r="S178" s="65">
+        <v>46221</v>
+      </c>
       <c r="T178" s="136"/>
-    </row>
-    <row r="179" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U178" s="136"/>
+    </row>
+    <row r="179" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A179" s="12" t="s">
         <v>255</v>
       </c>
@@ -15658,25 +16142,26 @@
         <v>0</v>
       </c>
       <c r="M179" s="2"/>
-      <c r="N179" s="64" t="s">
+      <c r="N179" s="2"/>
+      <c r="O179" s="64" t="s">
         <v>237</v>
       </c>
-      <c r="O179" s="65">
+      <c r="P179" s="65">
         <v>46179</v>
       </c>
-      <c r="P179" s="65">
+      <c r="Q179" s="65">
         <v>46186</v>
       </c>
-      <c r="Q179" s="65">
+      <c r="R179" s="65">
         <v>46202</v>
       </c>
-      <c r="R179" s="65">
+      <c r="S179" s="65">
         <v>46207</v>
       </c>
-      <c r="S179" s="136"/>
       <c r="T179" s="136"/>
-    </row>
-    <row r="180" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U179" s="136"/>
+    </row>
+    <row r="180" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A180" s="12" t="s">
         <v>256</v>
       </c>
@@ -15714,25 +16199,26 @@
         <v>0</v>
       </c>
       <c r="M180" s="2"/>
-      <c r="N180" s="64" t="s">
+      <c r="N180" s="2"/>
+      <c r="O180" s="64" t="s">
         <v>235</v>
       </c>
-      <c r="O180" s="65">
+      <c r="P180" s="65">
         <v>46195</v>
       </c>
-      <c r="P180" s="65">
+      <c r="Q180" s="65">
         <v>46202</v>
-      </c>
-      <c r="Q180" s="65">
-        <v>46221</v>
       </c>
       <c r="R180" s="65">
         <v>46221</v>
       </c>
-      <c r="S180" s="136"/>
+      <c r="S180" s="65">
+        <v>46221</v>
+      </c>
       <c r="T180" s="136"/>
-    </row>
-    <row r="181" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U180" s="136"/>
+    </row>
+    <row r="181" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A181" s="12" t="s">
         <v>257</v>
       </c>
@@ -15770,25 +16256,26 @@
         <v>0</v>
       </c>
       <c r="M181" s="2"/>
-      <c r="N181" s="64" t="s">
+      <c r="N181" s="2"/>
+      <c r="O181" s="64" t="s">
         <v>237</v>
       </c>
-      <c r="O181" s="65">
+      <c r="P181" s="65">
         <v>46179</v>
       </c>
-      <c r="P181" s="65">
+      <c r="Q181" s="65">
         <v>46186</v>
       </c>
-      <c r="Q181" s="65">
+      <c r="R181" s="65">
         <v>46202</v>
       </c>
-      <c r="R181" s="65">
+      <c r="S181" s="65">
         <v>46207</v>
       </c>
-      <c r="S181" s="136"/>
       <c r="T181" s="136"/>
-    </row>
-    <row r="182" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U181" s="136"/>
+    </row>
+    <row r="182" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A182" s="12" t="s">
         <v>258</v>
       </c>
@@ -15826,25 +16313,26 @@
         <v>0</v>
       </c>
       <c r="M182" s="2"/>
-      <c r="N182" s="64" t="s">
+      <c r="N182" s="2"/>
+      <c r="O182" s="64" t="s">
         <v>235</v>
       </c>
-      <c r="O182" s="65">
+      <c r="P182" s="65">
         <v>46195</v>
       </c>
-      <c r="P182" s="65">
+      <c r="Q182" s="65">
         <v>46202</v>
-      </c>
-      <c r="Q182" s="65">
-        <v>46221</v>
       </c>
       <c r="R182" s="65">
         <v>46221</v>
       </c>
-      <c r="S182" s="136"/>
+      <c r="S182" s="65">
+        <v>46221</v>
+      </c>
       <c r="T182" s="136"/>
-    </row>
-    <row r="183" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U182" s="136"/>
+    </row>
+    <row r="183" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A183" s="12" t="s">
         <v>259</v>
       </c>
@@ -15882,25 +16370,26 @@
         <v>0</v>
       </c>
       <c r="M183" s="2"/>
-      <c r="N183" s="64" t="s">
+      <c r="N183" s="2"/>
+      <c r="O183" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="O183" s="65">
+      <c r="P183" s="65">
         <v>46167</v>
       </c>
-      <c r="P183" s="65">
+      <c r="Q183" s="65">
         <v>46174</v>
       </c>
-      <c r="Q183" s="65">
+      <c r="R183" s="65">
         <v>46188</v>
       </c>
-      <c r="R183" s="65">
+      <c r="S183" s="65">
         <v>46195</v>
       </c>
-      <c r="S183" s="136"/>
       <c r="T183" s="136"/>
-    </row>
-    <row r="184" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U183" s="136"/>
+    </row>
+    <row r="184" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A184" s="12" t="s">
         <v>260</v>
       </c>
@@ -15932,25 +16421,26 @@
         <v>0</v>
       </c>
       <c r="M184" s="2"/>
-      <c r="N184" s="64" t="s">
+      <c r="N184" s="2"/>
+      <c r="O184" s="64" t="s">
         <v>262</v>
       </c>
-      <c r="O184" s="65">
+      <c r="P184" s="65">
         <v>46242</v>
       </c>
-      <c r="P184" s="65">
+      <c r="Q184" s="65">
         <v>46251</v>
       </c>
-      <c r="Q184" s="65">
+      <c r="R184" s="65">
         <v>46265</v>
       </c>
-      <c r="R184" s="65">
+      <c r="S184" s="65">
         <v>46270</v>
       </c>
-      <c r="S184" s="136"/>
       <c r="T184" s="136"/>
-    </row>
-    <row r="185" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U184" s="136"/>
+    </row>
+    <row r="185" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A185" s="12" t="s">
         <v>263</v>
       </c>
@@ -15982,25 +16472,26 @@
         <v>0</v>
       </c>
       <c r="M185" s="2"/>
-      <c r="N185" s="64" t="s">
+      <c r="N185" s="2"/>
+      <c r="O185" s="64" t="s">
         <v>262</v>
       </c>
-      <c r="O185" s="65">
+      <c r="P185" s="65">
         <v>46242</v>
       </c>
-      <c r="P185" s="65">
+      <c r="Q185" s="65">
         <v>46251</v>
       </c>
-      <c r="Q185" s="65">
+      <c r="R185" s="65">
         <v>46265</v>
       </c>
-      <c r="R185" s="65">
+      <c r="S185" s="65">
         <v>46270</v>
       </c>
-      <c r="S185" s="136"/>
       <c r="T185" s="136"/>
-    </row>
-    <row r="186" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U185" s="136"/>
+    </row>
+    <row r="186" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A186" s="12" t="s">
         <v>264</v>
       </c>
@@ -16038,25 +16529,26 @@
         <v>0</v>
       </c>
       <c r="M186" s="2"/>
-      <c r="N186" s="64" t="s">
+      <c r="N186" s="2"/>
+      <c r="O186" s="64" t="s">
         <v>262</v>
       </c>
-      <c r="O186" s="65">
+      <c r="P186" s="65">
         <v>46242</v>
       </c>
-      <c r="P186" s="65">
+      <c r="Q186" s="65">
         <v>46251</v>
       </c>
-      <c r="Q186" s="65">
+      <c r="R186" s="65">
         <v>46265</v>
       </c>
-      <c r="R186" s="65">
+      <c r="S186" s="65">
         <v>46270</v>
       </c>
-      <c r="S186" s="136"/>
       <c r="T186" s="136"/>
-    </row>
-    <row r="187" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U186" s="136"/>
+    </row>
+    <row r="187" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A187" s="12" t="s">
         <v>265</v>
       </c>
@@ -16094,25 +16586,26 @@
         <v>0</v>
       </c>
       <c r="M187" s="2"/>
-      <c r="N187" s="64" t="s">
+      <c r="N187" s="2"/>
+      <c r="O187" s="64" t="s">
         <v>262</v>
       </c>
-      <c r="O187" s="65">
+      <c r="P187" s="65">
         <v>46242</v>
       </c>
-      <c r="P187" s="65">
+      <c r="Q187" s="65">
         <v>46251</v>
       </c>
-      <c r="Q187" s="65">
+      <c r="R187" s="65">
         <v>46265</v>
       </c>
-      <c r="R187" s="65">
+      <c r="S187" s="65">
         <v>46270</v>
       </c>
-      <c r="S187" s="136"/>
       <c r="T187" s="136"/>
-    </row>
-    <row r="188" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U187" s="136"/>
+    </row>
+    <row r="188" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A188" s="12" t="s">
         <v>266</v>
       </c>
@@ -16150,25 +16643,26 @@
         <v>0</v>
       </c>
       <c r="M188" s="2"/>
-      <c r="N188" s="64" t="s">
+      <c r="N188" s="2"/>
+      <c r="O188" s="64" t="s">
         <v>262</v>
       </c>
-      <c r="O188" s="65">
+      <c r="P188" s="65">
         <v>46242</v>
       </c>
-      <c r="P188" s="65">
+      <c r="Q188" s="65">
         <v>46251</v>
       </c>
-      <c r="Q188" s="65">
+      <c r="R188" s="65">
         <v>46265</v>
       </c>
-      <c r="R188" s="65">
+      <c r="S188" s="65">
         <v>46270</v>
       </c>
-      <c r="S188" s="136"/>
       <c r="T188" s="136"/>
-    </row>
-    <row r="189" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U188" s="136"/>
+    </row>
+    <row r="189" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A189" s="12" t="s">
         <v>267</v>
       </c>
@@ -16206,25 +16700,26 @@
         <v>0</v>
       </c>
       <c r="M189" s="2"/>
-      <c r="N189" s="64" t="s">
+      <c r="N189" s="2"/>
+      <c r="O189" s="64" t="s">
         <v>262</v>
       </c>
-      <c r="O189" s="65">
+      <c r="P189" s="65">
         <v>46242</v>
       </c>
-      <c r="P189" s="65">
+      <c r="Q189" s="65">
         <v>46251</v>
       </c>
-      <c r="Q189" s="65">
+      <c r="R189" s="65">
         <v>46265</v>
       </c>
-      <c r="R189" s="65">
+      <c r="S189" s="65">
         <v>46270</v>
       </c>
-      <c r="S189" s="136"/>
       <c r="T189" s="136"/>
-    </row>
-    <row r="190" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U189" s="136"/>
+    </row>
+    <row r="190" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A190" s="12" t="s">
         <v>268</v>
       </c>
@@ -16262,25 +16757,26 @@
         <v>0</v>
       </c>
       <c r="M190" s="2"/>
-      <c r="N190" s="64" t="s">
+      <c r="N190" s="2"/>
+      <c r="O190" s="64" t="s">
         <v>262</v>
       </c>
-      <c r="O190" s="65">
+      <c r="P190" s="65">
         <v>46242</v>
       </c>
-      <c r="P190" s="65">
+      <c r="Q190" s="65">
         <v>46251</v>
       </c>
-      <c r="Q190" s="65">
+      <c r="R190" s="65">
         <v>46265</v>
       </c>
-      <c r="R190" s="65">
+      <c r="S190" s="65">
         <v>46270</v>
       </c>
-      <c r="S190" s="136"/>
       <c r="T190" s="136"/>
-    </row>
-    <row r="191" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U190" s="136"/>
+    </row>
+    <row r="191" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A191" s="12" t="s">
         <v>269</v>
       </c>
@@ -16318,25 +16814,26 @@
         <v>0</v>
       </c>
       <c r="M191" s="2"/>
-      <c r="N191" s="64" t="s">
+      <c r="N191" s="2"/>
+      <c r="O191" s="64" t="s">
         <v>262</v>
       </c>
-      <c r="O191" s="65">
+      <c r="P191" s="65">
         <v>46242</v>
       </c>
-      <c r="P191" s="65">
+      <c r="Q191" s="65">
         <v>46251</v>
       </c>
-      <c r="Q191" s="65">
+      <c r="R191" s="65">
         <v>46265</v>
       </c>
-      <c r="R191" s="65">
+      <c r="S191" s="65">
         <v>46270</v>
       </c>
-      <c r="S191" s="136"/>
       <c r="T191" s="136"/>
-    </row>
-    <row r="192" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="U191" s="136"/>
+    </row>
+    <row r="192" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A192" s="14" t="s">
         <v>270</v>
       </c>
@@ -16374,26 +16871,27 @@
         <v>0</v>
       </c>
       <c r="M192" s="134"/>
-      <c r="N192" s="64" t="s">
+      <c r="N192" s="134"/>
+      <c r="O192" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="O192" s="65">
+      <c r="P192" s="65">
         <v>46125</v>
       </c>
-      <c r="P192" s="65">
+      <c r="Q192" s="65">
         <v>46132</v>
       </c>
-      <c r="Q192" s="65">
+      <c r="R192" s="65">
         <v>46148</v>
       </c>
-      <c r="R192" s="65">
+      <c r="S192" s="65">
         <v>46154</v>
       </c>
-      <c r="S192" s="136"/>
       <c r="T192" s="136"/>
+      <c r="U192" s="136"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T192">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U192">
     <sortCondition ref="I2:I192"/>
   </sortState>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -16411,6 +16909,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B63819-1E8D-4373-81A1-1D7798E6B1FB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -26304,7 +26811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C333377-49F2-4AC6-BADC-C87EC68BCEC4}">
   <dimension ref="A1:F285"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -32025,7 +32532,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F989DF2-D219-4727-85A3-518D5D4459E8}">
   <dimension ref="A1:E251"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -36329,7 +36836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B93FC0-6D15-40D2-9100-0C4EDEC8F020}">
   <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -37492,7 +37999,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,22 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3154" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C3E3831-1778-47D4-B8ED-D86CBD3605A8}"/>
+  <xr:revisionPtr revIDLastSave="3166" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BAFD5DA-A3C5-43A0-8B1C-9F37E428F8DA}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="-8550" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FS Elec" sheetId="4" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="11" r:id="rId2"/>
-    <sheet name="FS Water" sheetId="1" r:id="rId3"/>
-    <sheet name="Aprt Elec" sheetId="8" r:id="rId4"/>
-    <sheet name="Aprt Water" sheetId="9" r:id="rId5"/>
-    <sheet name="Kiosk Plan" sheetId="5" r:id="rId6"/>
-    <sheet name="Temp ME162 open and closings" sheetId="2" r:id="rId7"/>
+    <sheet name="FS Water" sheetId="1" r:id="rId2"/>
+    <sheet name="Aprt Elec" sheetId="8" r:id="rId3"/>
+    <sheet name="Aprt Water" sheetId="9" r:id="rId4"/>
+    <sheet name="Kiosk Plan" sheetId="5" r:id="rId5"/>
+    <sheet name="Temp ME162 open and closings" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FS Elec'!$A$1:$U$192</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'FS Water'!$A$1:$S$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FS Water'!$A$1:$S$193</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -4784,14 +4783,14 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6616,7 +6615,7 @@
       <c r="B24" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="142">
+      <c r="C24" s="140">
         <v>14558069598</v>
       </c>
       <c r="D24" s="2">
@@ -10231,7 +10230,7 @@
       <c r="B83" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C83" s="142">
+      <c r="C83" s="140">
         <v>14558068442</v>
       </c>
       <c r="D83" s="2">
@@ -15448,7 +15447,7 @@
         <v>46196</v>
       </c>
       <c r="L168" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M168" s="2" t="s">
         <v>1234</v>
@@ -15513,7 +15512,7 @@
         <v>46196</v>
       </c>
       <c r="L169" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M169" s="2" t="s">
         <v>1234</v>
@@ -15578,7 +15577,7 @@
         <v>46196</v>
       </c>
       <c r="L170" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M170" s="2" t="s">
         <v>1234</v>
@@ -15643,7 +15642,7 @@
         <v>46196</v>
       </c>
       <c r="L171" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M171" s="2" t="s">
         <v>1234</v>
@@ -15708,7 +15707,7 @@
         <v>46196</v>
       </c>
       <c r="L172" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M172" s="2" t="s">
         <v>1234</v>
@@ -15773,7 +15772,7 @@
         <v>46196</v>
       </c>
       <c r="L173" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M173" s="2" t="s">
         <v>1234</v>
@@ -15838,7 +15837,7 @@
         <v>46196</v>
       </c>
       <c r="L174" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M174" s="2" t="s">
         <v>1234</v>
@@ -15903,7 +15902,7 @@
         <v>46196</v>
       </c>
       <c r="L175" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M175" s="2" t="s">
         <v>1234</v>
@@ -16909,15 +16908,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B63819-1E8D-4373-81A1-1D7798E6B1FB}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -26811,7 +26801,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C333377-49F2-4AC6-BADC-C87EC68BCEC4}">
   <dimension ref="A1:F285"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -32532,7 +32522,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F989DF2-D219-4727-85A3-518D5D4459E8}">
   <dimension ref="A1:E251"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -36836,7 +36826,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B93FC0-6D15-40D2-9100-0C4EDEC8F020}">
   <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -36853,34 +36843,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A1" s="140" t="s">
+      <c r="A1" s="141" t="s">
         <v>1170</v>
       </c>
-      <c r="B1" s="140" t="s">
+      <c r="B1" s="141" t="s">
         <v>1171</v>
       </c>
-      <c r="C1" s="140" t="s">
+      <c r="C1" s="141" t="s">
         <v>1172</v>
       </c>
-      <c r="D1" s="141" t="s">
+      <c r="D1" s="142" t="s">
         <v>1173</v>
       </c>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141" t="s">
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142" t="s">
         <v>1174</v>
       </c>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
       <c r="J1" s="108"/>
       <c r="K1" s="109" t="s">
         <v>1175</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A2" s="140"/>
-      <c r="B2" s="140"/>
-      <c r="C2" s="140"/>
+      <c r="A2" s="141"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
       <c r="D2" s="107" t="s">
         <v>1176</v>
       </c>
@@ -37999,7 +37989,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3166" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BAFD5DA-A3C5-43A0-8B1C-9F37E428F8DA}"/>
+  <xr:revisionPtr revIDLastSave="3174" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F006E32E-8FEA-41DD-A5AF-33F38E2021F9}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FS Elec" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4941" uniqueCount="1235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4942" uniqueCount="1236">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -3750,6 +3750,9 @@
   </si>
   <si>
     <t>2cf7f12072901fa5</t>
+  </si>
+  <si>
+    <t>2cf7f1207310074f</t>
   </si>
 </sst>
 </file>
@@ -3759,12 +3762,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4357,36 +4367,36 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="37" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4397,7 +4407,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -4405,32 +4415,32 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -4438,82 +4448,82 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -4521,99 +4531,99 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="35" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="35" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="38" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="39" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="38" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="39" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="38" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="35" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="35" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
@@ -4623,89 +4633,89 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="42" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="42" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="43" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="43" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="44" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="44" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="45" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="45" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="40" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="41" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="41" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4723,43 +4733,43 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4768,7 +4778,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4783,13 +4793,16 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -16832,7 +16845,7 @@
       <c r="T191" s="136"/>
       <c r="U191" s="136"/>
     </row>
-    <row r="192" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:21" ht="18.75" x14ac:dyDescent="0.45">
       <c r="A192" s="14" t="s">
         <v>270</v>
       </c>
@@ -16867,10 +16880,14 @@
         <v>46182</v>
       </c>
       <c r="L192" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="M192" s="134"/>
-      <c r="N192" s="134"/>
+        <v>1</v>
+      </c>
+      <c r="M192" s="143" t="s">
+        <v>1235</v>
+      </c>
+      <c r="N192" s="134">
+        <v>10</v>
+      </c>
       <c r="O192" s="64" t="s">
         <v>80</v>
       </c>
@@ -16893,7 +16910,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U192">
     <sortCondition ref="I2:I192"/>
   </sortState>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="C25:C192 C2:C23">
     <cfRule type="duplicateValues" dxfId="13" priority="8"/>
   </conditionalFormatting>
@@ -26789,7 +26806,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N193">
     <sortCondition ref="A2:A193"/>
   </sortState>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="C2:C63">
     <cfRule type="duplicateValues" dxfId="10" priority="2"/>
     <cfRule type="duplicateValues" dxfId="9" priority="5"/>
@@ -29331,7 +29348,7 @@
         <v>275</v>
       </c>
       <c r="F126" s="81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="14.25" x14ac:dyDescent="0.3">
@@ -37984,7 +38001,7 @@
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="G1:I1"/>
   </mergeCells>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3174" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F006E32E-8FEA-41DD-A5AF-33F38E2021F9}"/>
+  <xr:revisionPtr revIDLastSave="3257" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAAA7020-BD77-4218-87E5-37DA3159A5A7}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="59280" yWindow="-2430" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FS Elec" sheetId="4" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FS Elec'!$A$1:$U$192</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FS Water'!$A$1:$S$193</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4942" uniqueCount="1236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4959" uniqueCount="1253">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -3753,6 +3753,57 @@
   </si>
   <si>
     <t>2cf7f1207310074f</t>
+  </si>
+  <si>
+    <t>54789040</t>
+  </si>
+  <si>
+    <t>54789077</t>
+  </si>
+  <si>
+    <t>54789045</t>
+  </si>
+  <si>
+    <t>54789042</t>
+  </si>
+  <si>
+    <t>54789038</t>
+  </si>
+  <si>
+    <t>54789034</t>
+  </si>
+  <si>
+    <t>54789048</t>
+  </si>
+  <si>
+    <t>54789039</t>
+  </si>
+  <si>
+    <t>54789037</t>
+  </si>
+  <si>
+    <t>54789036</t>
+  </si>
+  <si>
+    <t>54789041</t>
+  </si>
+  <si>
+    <t>54789044</t>
+  </si>
+  <si>
+    <t>54789047</t>
+  </si>
+  <si>
+    <t>54789035</t>
+  </si>
+  <si>
+    <t>54789046</t>
+  </si>
+  <si>
+    <t>54789043</t>
+  </si>
+  <si>
+    <t>54789074</t>
   </si>
 </sst>
 </file>
@@ -4796,13 +4847,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -16882,7 +16933,7 @@
       <c r="L192" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="M192" s="143" t="s">
+      <c r="M192" s="141" t="s">
         <v>1235</v>
       </c>
       <c r="N192" s="134">
@@ -16936,8 +16987,8 @@
     <col min="5" max="5" width="19.73046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.59765625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="31.1328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.46484375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.46484375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="39.53125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.86328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27.3984375" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="20.265625" customWidth="1"/>
     <col min="14" max="14" width="35.46484375" customWidth="1"/>
@@ -17954,18 +18005,24 @@
       <c r="B22" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="53"/>
+      <c r="C22" s="53" t="s">
+        <v>1252</v>
+      </c>
       <c r="D22" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F22" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="G22" s="3">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="H22" s="57">
+        <v>46248</v>
+      </c>
       <c r="I22" s="21" t="b">
         <v>0</v>
       </c>
@@ -18048,18 +18105,24 @@
       <c r="B24" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="53"/>
+      <c r="C24" s="53" t="s">
+        <v>1251</v>
+      </c>
       <c r="D24" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E24" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F24" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="G24" s="3">
+        <v>0.151</v>
+      </c>
+      <c r="H24" s="57">
+        <v>46248</v>
+      </c>
       <c r="I24" s="21" t="b">
         <v>0</v>
       </c>
@@ -18424,18 +18487,24 @@
       <c r="B32" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="53"/>
+      <c r="C32" s="53" t="s">
+        <v>1250</v>
+      </c>
       <c r="D32" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E32" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F32" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
+      <c r="G32" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="H32" s="57">
+        <v>46248</v>
+      </c>
       <c r="I32" s="21" t="b">
         <v>0</v>
       </c>
@@ -18471,18 +18540,24 @@
       <c r="B33" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="53"/>
+      <c r="C33" s="53" t="s">
+        <v>1243</v>
+      </c>
       <c r="D33" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E33" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F33" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
+      <c r="G33" s="3">
+        <v>0.151</v>
+      </c>
+      <c r="H33" s="57">
+        <v>46248</v>
+      </c>
       <c r="I33" s="21" t="b">
         <v>0</v>
       </c>
@@ -18518,18 +18593,24 @@
       <c r="B34" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="53"/>
+      <c r="C34" s="53" t="s">
+        <v>1242</v>
+      </c>
       <c r="D34" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E34" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F34" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
+      <c r="G34" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="H34" s="57">
+        <v>46248</v>
+      </c>
       <c r="I34" s="21" t="b">
         <v>0</v>
       </c>
@@ -25292,18 +25373,24 @@
       <c r="B164" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C164" s="53"/>
+      <c r="C164" s="53" t="s">
+        <v>1241</v>
+      </c>
       <c r="D164" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E164" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F164" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G164" s="3"/>
-      <c r="H164" s="3"/>
+      <c r="G164" s="3">
+        <v>0.153</v>
+      </c>
+      <c r="H164" s="57">
+        <v>46248</v>
+      </c>
       <c r="I164" s="21" t="b">
         <v>0</v>
       </c>
@@ -25339,18 +25426,24 @@
       <c r="B165" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C165" s="53"/>
+      <c r="C165" s="53" t="s">
+        <v>1240</v>
+      </c>
       <c r="D165" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E165" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F165" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G165" s="3"/>
-      <c r="H165" s="3"/>
+      <c r="G165" s="3">
+        <v>0.152</v>
+      </c>
+      <c r="H165" s="57">
+        <v>46248</v>
+      </c>
       <c r="I165" s="21" t="b">
         <v>0</v>
       </c>
@@ -25386,18 +25479,24 @@
       <c r="B166" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C166" s="53"/>
+      <c r="C166" s="53" t="s">
+        <v>1239</v>
+      </c>
       <c r="D166" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E166" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F166" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G166" s="3"/>
-      <c r="H166" s="3"/>
+      <c r="G166" s="3">
+        <v>0.152</v>
+      </c>
+      <c r="H166" s="57">
+        <v>46248</v>
+      </c>
       <c r="I166" s="21" t="b">
         <v>0</v>
       </c>
@@ -25433,18 +25532,24 @@
       <c r="B167" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C167" s="53"/>
+      <c r="C167" s="53" t="s">
+        <v>1238</v>
+      </c>
       <c r="D167" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E167" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F167" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G167" s="3"/>
-      <c r="H167" s="3"/>
+      <c r="G167" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="H167" s="57">
+        <v>46248</v>
+      </c>
       <c r="I167" s="21" t="b">
         <v>0</v>
       </c>
@@ -25480,18 +25585,24 @@
       <c r="B168" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C168" s="53"/>
+      <c r="C168" s="53" t="s">
+        <v>1237</v>
+      </c>
       <c r="D168" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E168" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F168" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G168" s="3"/>
-      <c r="H168" s="3"/>
+      <c r="G168" s="3">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="H168" s="57">
+        <v>46248</v>
+      </c>
       <c r="I168" s="21" t="b">
         <v>0</v>
       </c>
@@ -25527,18 +25638,24 @@
       <c r="B169" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C169" s="53"/>
+      <c r="C169" s="53" t="s">
+        <v>1236</v>
+      </c>
       <c r="D169" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E169" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F169" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G169" s="3"/>
-      <c r="H169" s="3"/>
+      <c r="G169" s="3">
+        <v>0.151</v>
+      </c>
+      <c r="H169" s="57">
+        <v>46248</v>
+      </c>
       <c r="I169" s="21" t="b">
         <v>0</v>
       </c>
@@ -25621,18 +25738,24 @@
       <c r="B171" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="C171" s="53"/>
+      <c r="C171" s="53" t="s">
+        <v>1247</v>
+      </c>
       <c r="D171" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E171" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F171" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G171" s="3"/>
-      <c r="H171" s="3"/>
+      <c r="G171" s="3">
+        <v>0.121</v>
+      </c>
+      <c r="H171" s="57">
+        <v>46248</v>
+      </c>
       <c r="I171" s="21" t="b">
         <v>0</v>
       </c>
@@ -25668,18 +25791,24 @@
       <c r="B172" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="C172" s="53"/>
+      <c r="C172" s="53" t="s">
+        <v>1244</v>
+      </c>
       <c r="D172" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E172" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F172" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G172" s="3"/>
-      <c r="H172" s="3"/>
+      <c r="G172" s="3">
+        <v>0.152</v>
+      </c>
+      <c r="H172" s="57">
+        <v>46248</v>
+      </c>
       <c r="I172" s="21" t="b">
         <v>0</v>
       </c>
@@ -25715,18 +25844,24 @@
       <c r="B173" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="C173" s="53"/>
+      <c r="C173" s="53" t="s">
+        <v>1245</v>
+      </c>
       <c r="D173" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E173" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F173" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G173" s="3"/>
-      <c r="H173" s="3"/>
+      <c r="G173" s="3">
+        <v>0.152</v>
+      </c>
+      <c r="H173" s="57">
+        <v>46248</v>
+      </c>
       <c r="I173" s="21" t="b">
         <v>0</v>
       </c>
@@ -25762,18 +25897,24 @@
       <c r="B174" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="C174" s="53"/>
+      <c r="C174" s="53" t="s">
+        <v>1246</v>
+      </c>
       <c r="D174" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E174" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F174" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G174" s="3"/>
-      <c r="H174" s="3"/>
+      <c r="G174" s="3">
+        <v>0.152</v>
+      </c>
+      <c r="H174" s="57">
+        <v>46248</v>
+      </c>
       <c r="I174" s="21" t="b">
         <v>0</v>
       </c>
@@ -26180,18 +26321,24 @@
       <c r="B182" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="C182" s="53"/>
+      <c r="C182" s="53" t="s">
+        <v>1248</v>
+      </c>
       <c r="D182" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E182" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F182" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G182" s="3"/>
-      <c r="H182" s="3"/>
+      <c r="G182" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="H182" s="57">
+        <v>46248</v>
+      </c>
       <c r="I182" s="21" t="b">
         <v>0</v>
       </c>
@@ -26227,18 +26374,24 @@
       <c r="B183" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="C183" s="53"/>
+      <c r="C183" s="53" t="s">
+        <v>1249</v>
+      </c>
       <c r="D183" s="53" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="E183" s="53" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="F183" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G183" s="3"/>
-      <c r="H183" s="3"/>
+      <c r="G183" s="3">
+        <v>0.152</v>
+      </c>
+      <c r="H183" s="57">
+        <v>46248</v>
+      </c>
       <c r="I183" s="21" t="b">
         <v>0</v>
       </c>
@@ -36860,34 +37013,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="142" t="s">
         <v>1170</v>
       </c>
-      <c r="B1" s="141" t="s">
+      <c r="B1" s="142" t="s">
         <v>1171</v>
       </c>
-      <c r="C1" s="141" t="s">
+      <c r="C1" s="142" t="s">
         <v>1172</v>
       </c>
-      <c r="D1" s="142" t="s">
+      <c r="D1" s="143" t="s">
         <v>1173</v>
       </c>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142" t="s">
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143" t="s">
         <v>1174</v>
       </c>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
       <c r="J1" s="108"/>
       <c r="K1" s="109" t="s">
         <v>1175</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A2" s="141"/>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
+      <c r="A2" s="142"/>
+      <c r="B2" s="142"/>
+      <c r="C2" s="142"/>
       <c r="D2" s="107" t="s">
         <v>1176</v>
       </c>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3417" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F88C7F61-75C8-4ABB-B71B-665CB30D1C32}"/>
+  <xr:revisionPtr revIDLastSave="3549" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9DEF16A-C557-4089-9CFF-8B4A4B172C5F}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-11010" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="88080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FS Elec" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4986" uniqueCount="1278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5061" uniqueCount="1292">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -3879,6 +3879,48 @@
   </si>
   <si>
     <t>10596189</t>
+  </si>
+  <si>
+    <t>10596229</t>
+  </si>
+  <si>
+    <t>10596237</t>
+  </si>
+  <si>
+    <t>10596377</t>
+  </si>
+  <si>
+    <t>10596304</t>
+  </si>
+  <si>
+    <t>10596231</t>
+  </si>
+  <si>
+    <t>2cf7f12072903411</t>
+  </si>
+  <si>
+    <t>2cf7f12072903bab</t>
+  </si>
+  <si>
+    <t>2cf7f120729018c1</t>
+  </si>
+  <si>
+    <t>2cf7f12072902fd1</t>
+  </si>
+  <si>
+    <t>2cf7f12072903b79</t>
+  </si>
+  <si>
+    <t>2cf7f120731008bf</t>
+  </si>
+  <si>
+    <t>2cf7f12072902d12</t>
+  </si>
+  <si>
+    <t>2cf7f12072901d88</t>
+  </si>
+  <si>
+    <t>2cf7f12072901e3a</t>
   </si>
 </sst>
 </file>
@@ -5418,7 +5460,8 @@
     <col min="9" max="9" width="16.59765625" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26.3984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="27.265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="16.59765625" customWidth="1"/>
+    <col min="12" max="12" width="16.59765625" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.3984375" bestFit="1" customWidth="1"/>
     <col min="16" max="19" width="11.265625" bestFit="1" customWidth="1"/>
@@ -5526,10 +5569,14 @@
         <v>46206</v>
       </c>
       <c r="L2" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="N2" s="2">
+        <v>6</v>
+      </c>
       <c r="O2" s="64" t="s">
         <v>25</v>
       </c>
@@ -5583,10 +5630,14 @@
         <v>46206</v>
       </c>
       <c r="L3" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="N3" s="2">
+        <v>3</v>
+      </c>
       <c r="O3" s="64" t="s">
         <v>28</v>
       </c>
@@ -5640,10 +5691,14 @@
         <v>46206</v>
       </c>
       <c r="L4" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="N4" s="2">
+        <v>5</v>
+      </c>
       <c r="O4" s="64" t="s">
         <v>25</v>
       </c>
@@ -5697,10 +5752,14 @@
         <v>46206</v>
       </c>
       <c r="L5" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="N5" s="2">
+        <v>2</v>
+      </c>
       <c r="O5" s="64" t="s">
         <v>28</v>
       </c>
@@ -5754,10 +5813,14 @@
         <v>46206</v>
       </c>
       <c r="L6" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="N6" s="2">
+        <v>4</v>
+      </c>
       <c r="O6" s="64" t="s">
         <v>25</v>
       </c>
@@ -5811,10 +5874,14 @@
         <v>46206</v>
       </c>
       <c r="L7" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="N7" s="2">
+        <v>1</v>
+      </c>
       <c r="O7" s="64" t="s">
         <v>28</v>
       </c>
@@ -5870,8 +5937,10 @@
       <c r="L8" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+      <c r="M8" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="N8" s="7"/>
       <c r="O8" s="64" t="s">
         <v>37</v>
       </c>
@@ -5927,8 +5996,10 @@
       <c r="L9" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
+      <c r="M9" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="N9" s="7"/>
       <c r="O9" s="64" t="s">
         <v>39</v>
       </c>
@@ -5984,8 +6055,10 @@
       <c r="L10" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="M10" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="N10" s="7"/>
       <c r="O10" s="64" t="s">
         <v>37</v>
       </c>
@@ -6041,8 +6114,10 @@
       <c r="L11" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
+      <c r="M11" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="N11" s="7"/>
       <c r="O11" s="64" t="s">
         <v>39</v>
       </c>
@@ -6098,8 +6173,10 @@
       <c r="L12" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+      <c r="M12" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="N12" s="7"/>
       <c r="O12" s="64" t="s">
         <v>37</v>
       </c>
@@ -6155,8 +6232,10 @@
       <c r="L13" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
+      <c r="M13" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="N13" s="7"/>
       <c r="O13" s="64" t="s">
         <v>39</v>
       </c>
@@ -6212,8 +6291,10 @@
       <c r="L14" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
+      <c r="M14" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="N14" s="7"/>
       <c r="O14" s="64" t="s">
         <v>39</v>
       </c>
@@ -6269,8 +6350,10 @@
       <c r="L15" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
+      <c r="M15" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="N15" s="7"/>
       <c r="O15" s="64" t="s">
         <v>37</v>
       </c>
@@ -6326,8 +6409,10 @@
       <c r="L16" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
+      <c r="M16" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="N16" s="7"/>
       <c r="O16" s="64" t="s">
         <v>37</v>
       </c>
@@ -6383,8 +6468,10 @@
       <c r="L17" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
+      <c r="M17" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="N17" s="7"/>
       <c r="O17" s="64" t="s">
         <v>39</v>
       </c>
@@ -6440,8 +6527,10 @@
       <c r="L18" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
+      <c r="M18" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="N18" s="7"/>
       <c r="O18" s="64" t="s">
         <v>37</v>
       </c>
@@ -6497,8 +6586,10 @@
       <c r="L19" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
+      <c r="M19" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="N19" s="7"/>
       <c r="O19" s="64" t="s">
         <v>39</v>
       </c>
@@ -6554,8 +6645,10 @@
       <c r="L20" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
+      <c r="M20" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="N20" s="7"/>
       <c r="O20" s="64" t="s">
         <v>37</v>
       </c>
@@ -6611,8 +6704,10 @@
       <c r="L21" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
+      <c r="M21" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="N21" s="7"/>
       <c r="O21" s="64" t="s">
         <v>39</v>
       </c>
@@ -6668,8 +6763,10 @@
       <c r="L22" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
+      <c r="M22" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="N22" s="7"/>
       <c r="O22" s="64" t="s">
         <v>39</v>
       </c>
@@ -6725,8 +6822,10 @@
       <c r="L23" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2">
+      <c r="M23" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="N23" s="7">
         <v>1</v>
       </c>
       <c r="O23" s="64" t="s">
@@ -6784,8 +6883,10 @@
       <c r="L24" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2">
+      <c r="M24" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="N24" s="7">
         <v>7</v>
       </c>
       <c r="O24" s="64" t="s">
@@ -6843,8 +6944,10 @@
       <c r="L25" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2">
+      <c r="M25" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="N25" s="7">
         <v>2</v>
       </c>
       <c r="O25" s="64" t="s">
@@ -6902,8 +7005,10 @@
       <c r="L26" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2">
+      <c r="M26" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="N26" s="7">
         <v>3</v>
       </c>
       <c r="O26" s="64" t="s">
@@ -6961,8 +7066,10 @@
       <c r="L27" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2">
+      <c r="M27" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="N27" s="7">
         <v>8</v>
       </c>
       <c r="O27" s="64" t="s">
@@ -7020,8 +7127,10 @@
       <c r="L28" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2">
+      <c r="M28" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="N28" s="7">
         <v>4</v>
       </c>
       <c r="O28" s="64" t="s">
@@ -7079,8 +7188,10 @@
       <c r="L29" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2">
+      <c r="M29" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="N29" s="7">
         <v>5</v>
       </c>
       <c r="O29" s="64" t="s">
@@ -7138,8 +7249,10 @@
       <c r="L30" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2">
+      <c r="M30" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="N30" s="7">
         <v>6</v>
       </c>
       <c r="O30" s="64" t="s">
@@ -7200,7 +7313,7 @@
       <c r="M31" s="2" t="s">
         <v>1214</v>
       </c>
-      <c r="N31" s="2">
+      <c r="N31" s="7">
         <v>1</v>
       </c>
       <c r="O31" s="64" t="s">
@@ -7261,7 +7374,7 @@
       <c r="M32" s="2" t="s">
         <v>1214</v>
       </c>
-      <c r="N32" s="2">
+      <c r="N32" s="7">
         <v>2</v>
       </c>
       <c r="O32" s="64" t="s">
@@ -7322,7 +7435,7 @@
       <c r="M33" s="2" t="s">
         <v>1214</v>
       </c>
-      <c r="N33" s="2">
+      <c r="N33" s="7">
         <v>3</v>
       </c>
       <c r="O33" s="64" t="s">
@@ -7383,7 +7496,7 @@
       <c r="M34" s="2" t="s">
         <v>1214</v>
       </c>
-      <c r="N34" s="2">
+      <c r="N34" s="7">
         <v>4</v>
       </c>
       <c r="O34" s="64" t="s">
@@ -7566,7 +7679,7 @@
       <c r="M37" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="N37" s="2">
+      <c r="N37" s="7">
         <v>9</v>
       </c>
       <c r="O37" s="64" t="s">
@@ -7627,7 +7740,7 @@
       <c r="M38" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="N38" s="2">
+      <c r="N38" s="7">
         <v>6</v>
       </c>
       <c r="O38" s="64" t="s">
@@ -7753,7 +7866,7 @@
       <c r="M40" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="N40" s="2">
+      <c r="N40" s="7">
         <v>5</v>
       </c>
       <c r="O40" s="64" t="s">
@@ -7879,7 +7992,7 @@
       <c r="M42" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="N42" s="2">
+      <c r="N42" s="7">
         <v>4</v>
       </c>
       <c r="O42" s="64" t="s">
@@ -7940,7 +8053,7 @@
       <c r="M43" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="N43" s="2">
+      <c r="N43" s="7">
         <v>3</v>
       </c>
       <c r="O43" s="64" t="s">
@@ -8001,7 +8114,7 @@
       <c r="M44" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="N44" s="2">
+      <c r="N44" s="7">
         <v>2</v>
       </c>
       <c r="O44" s="64" t="s">
@@ -8120,8 +8233,10 @@
       <c r="L46" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2">
+      <c r="M46" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="N46" s="7">
         <v>6</v>
       </c>
       <c r="O46" s="64" t="s">
@@ -8179,8 +8294,10 @@
       <c r="L47" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M47" s="2"/>
-      <c r="N47" s="2">
+      <c r="M47" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="N47" s="7">
         <v>3</v>
       </c>
       <c r="O47" s="64" t="s">
@@ -8238,8 +8355,10 @@
       <c r="L48" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M48" s="2"/>
-      <c r="N48" s="2">
+      <c r="M48" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="N48" s="7">
         <v>2</v>
       </c>
       <c r="O48" s="64" t="s">
@@ -8297,8 +8416,10 @@
       <c r="L49" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2">
+      <c r="M49" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="N49" s="7">
         <v>1</v>
       </c>
       <c r="O49" s="64" t="s">
@@ -8356,8 +8477,10 @@
       <c r="L50" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2">
+      <c r="M50" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="N50" s="7">
         <v>5</v>
       </c>
       <c r="O50" s="64" t="s">
@@ -8415,8 +8538,10 @@
       <c r="L51" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2">
+      <c r="M51" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="N51" s="7">
         <v>7</v>
       </c>
       <c r="O51" s="64" t="s">
@@ -8474,8 +8599,10 @@
       <c r="L52" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2">
+      <c r="M52" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="N52" s="7">
         <v>4</v>
       </c>
       <c r="O52" s="64" t="s">
@@ -9044,7 +9171,7 @@
       <c r="M61" s="2" t="s">
         <v>1217</v>
       </c>
-      <c r="N61" s="2">
+      <c r="N61" s="7">
         <v>9</v>
       </c>
       <c r="O61" s="64" t="s">
@@ -9105,7 +9232,7 @@
       <c r="M62" s="2" t="s">
         <v>1217</v>
       </c>
-      <c r="N62" s="2">
+      <c r="N62" s="7">
         <v>8</v>
       </c>
       <c r="O62" s="64" t="s">
@@ -9292,7 +9419,7 @@
       <c r="M65" s="2" t="s">
         <v>1217</v>
       </c>
-      <c r="N65" s="2">
+      <c r="N65" s="7">
         <v>6</v>
       </c>
       <c r="O65" s="64" t="s">
@@ -9418,7 +9545,7 @@
       <c r="M67" s="2" t="s">
         <v>1217</v>
       </c>
-      <c r="N67" s="2">
+      <c r="N67" s="7">
         <v>5</v>
       </c>
       <c r="O67" s="64" t="s">
@@ -9609,7 +9736,7 @@
       <c r="M70" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="N70" s="2">
+      <c r="N70" s="7">
         <v>1</v>
       </c>
       <c r="O70" s="64" t="s">
@@ -9670,7 +9797,7 @@
       <c r="M71" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="N71" s="2">
+      <c r="N71" s="7">
         <v>2</v>
       </c>
       <c r="O71" s="64" t="s">
@@ -9731,7 +9858,7 @@
       <c r="M72" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="N72" s="2">
+      <c r="N72" s="7">
         <v>6</v>
       </c>
       <c r="O72" s="64" t="s">
@@ -9792,7 +9919,7 @@
       <c r="M73" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="N73" s="2">
+      <c r="N73" s="7">
         <v>3</v>
       </c>
       <c r="O73" s="64" t="s">
@@ -9853,7 +9980,7 @@
       <c r="M74" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="N74" s="2">
+      <c r="N74" s="7">
         <v>7</v>
       </c>
       <c r="O74" s="64" t="s">
@@ -9914,7 +10041,7 @@
       <c r="M75" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="N75" s="2">
+      <c r="N75" s="7">
         <v>4</v>
       </c>
       <c r="O75" s="64" t="s">
@@ -9975,7 +10102,7 @@
       <c r="M76" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="N76" s="2">
+      <c r="N76" s="7">
         <v>5</v>
       </c>
       <c r="O76" s="64" t="s">
@@ -10036,7 +10163,7 @@
       <c r="M77" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="N77" s="2">
+      <c r="N77" s="7">
         <v>9</v>
       </c>
       <c r="O77" s="64" t="s">
@@ -10097,7 +10224,7 @@
       <c r="M78" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="N78" s="2">
+      <c r="N78" s="7">
         <v>8</v>
       </c>
       <c r="O78" s="64" t="s">
@@ -10158,7 +10285,7 @@
       <c r="M79" s="2" t="s">
         <v>1219</v>
       </c>
-      <c r="N79" s="2">
+      <c r="N79" s="7">
         <v>6</v>
       </c>
       <c r="O79" s="64" t="s">
@@ -10280,7 +10407,7 @@
       <c r="M81" s="2" t="s">
         <v>1219</v>
       </c>
-      <c r="N81" s="2">
+      <c r="N81" s="7">
         <v>7</v>
       </c>
       <c r="O81" s="64" t="s">
@@ -10463,7 +10590,7 @@
       <c r="M84" s="2" t="s">
         <v>1219</v>
       </c>
-      <c r="N84" s="2">
+      <c r="N84" s="7">
         <v>2</v>
       </c>
       <c r="O84" s="64" t="s">
@@ -10646,7 +10773,7 @@
       <c r="M87" s="2" t="s">
         <v>1220</v>
       </c>
-      <c r="N87" s="2">
+      <c r="N87" s="7">
         <v>9</v>
       </c>
       <c r="O87" s="64" t="s">
@@ -10707,7 +10834,7 @@
       <c r="M88" s="2" t="s">
         <v>1220</v>
       </c>
-      <c r="N88" s="2">
+      <c r="N88" s="7">
         <v>8</v>
       </c>
       <c r="O88" s="64" t="s">
@@ -10833,7 +10960,7 @@
       <c r="M90" s="2" t="s">
         <v>1220</v>
       </c>
-      <c r="N90" s="2">
+      <c r="N90" s="7">
         <v>7</v>
       </c>
       <c r="O90" s="64" t="s">
@@ -11215,7 +11342,7 @@
       <c r="M96" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="N96" s="2">
+      <c r="N96" s="7">
         <v>3</v>
       </c>
       <c r="O96" s="64" t="s">
@@ -11276,7 +11403,7 @@
       <c r="M97" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="N97" s="2">
+      <c r="N97" s="7">
         <v>5</v>
       </c>
       <c r="O97" s="64" t="s">
@@ -11337,7 +11464,7 @@
       <c r="M98" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="N98" s="2">
+      <c r="N98" s="7">
         <v>2</v>
       </c>
       <c r="O98" s="64" t="s">
@@ -11398,7 +11525,7 @@
       <c r="M99" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="N99" s="2">
+      <c r="N99" s="7">
         <v>9</v>
       </c>
       <c r="O99" s="64" t="s">
@@ -11459,7 +11586,7 @@
       <c r="M100" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="N100" s="2">
+      <c r="N100" s="7">
         <v>1</v>
       </c>
       <c r="O100" s="64" t="s">
@@ -11520,7 +11647,7 @@
       <c r="M101" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="N101" s="2">
+      <c r="N101" s="7">
         <v>8</v>
       </c>
       <c r="O101" s="64" t="s">
@@ -11581,7 +11708,7 @@
       <c r="M102" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="N102" s="2">
+      <c r="N102" s="7">
         <v>6</v>
       </c>
       <c r="O102" s="64" t="s">
@@ -11642,7 +11769,7 @@
       <c r="M103" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="N103" s="2">
+      <c r="N103" s="7">
         <v>7</v>
       </c>
       <c r="O103" s="64" t="s">
@@ -11703,7 +11830,7 @@
       <c r="M104" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="N104" s="2">
+      <c r="N104" s="7">
         <v>4</v>
       </c>
       <c r="O104" s="64" t="s">
@@ -11759,10 +11886,14 @@
         <v>46197</v>
       </c>
       <c r="L105" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M105" s="2"/>
-      <c r="N105" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="N105" s="2">
+        <v>9</v>
+      </c>
       <c r="O105" s="64" t="s">
         <v>25</v>
       </c>
@@ -11816,10 +11947,14 @@
         <v>46197</v>
       </c>
       <c r="L106" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M106" s="2"/>
-      <c r="N106" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="N106" s="2">
+        <v>8</v>
+      </c>
       <c r="O106" s="64" t="s">
         <v>25</v>
       </c>
@@ -11873,10 +12008,14 @@
         <v>46197</v>
       </c>
       <c r="L107" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M107" s="2"/>
-      <c r="N107" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="N107" s="2">
+        <v>1</v>
+      </c>
       <c r="O107" s="64" t="s">
         <v>132</v>
       </c>
@@ -11930,10 +12069,14 @@
         <v>46197</v>
       </c>
       <c r="L108" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M108" s="2"/>
-      <c r="N108" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M108" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="N108" s="2">
+        <v>7</v>
+      </c>
       <c r="O108" s="64" t="s">
         <v>130</v>
       </c>
@@ -11989,8 +12132,12 @@
       <c r="L109" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M109" s="2"/>
-      <c r="N109" s="2"/>
+      <c r="M109" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="N109" s="7">
+        <v>2</v>
+      </c>
       <c r="O109" s="64" t="s">
         <v>132</v>
       </c>
@@ -12044,10 +12191,14 @@
         <v>46197</v>
       </c>
       <c r="L110" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M110" s="2"/>
-      <c r="N110" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M110" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="N110" s="2">
+        <v>6</v>
+      </c>
       <c r="O110" s="64" t="s">
         <v>130</v>
       </c>
@@ -12101,10 +12252,14 @@
         <v>46197</v>
       </c>
       <c r="L111" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M111" s="2"/>
-      <c r="N111" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M111" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="N111" s="2">
+        <v>3</v>
+      </c>
       <c r="O111" s="64" t="s">
         <v>132</v>
       </c>
@@ -12158,10 +12313,14 @@
         <v>46197</v>
       </c>
       <c r="L112" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M112" s="2"/>
-      <c r="N112" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M112" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="N112" s="2">
+        <v>5</v>
+      </c>
       <c r="O112" s="64" t="s">
         <v>130</v>
       </c>
@@ -12215,10 +12374,14 @@
         <v>46197</v>
       </c>
       <c r="L113" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M113" s="2"/>
-      <c r="N113" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="N113" s="2">
+        <v>4</v>
+      </c>
       <c r="O113" s="64" t="s">
         <v>132</v>
       </c>
@@ -12797,7 +12960,7 @@
       <c r="M122" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="N122" s="2">
+      <c r="N122" s="7">
         <v>4</v>
       </c>
       <c r="O122" s="64" t="s">
@@ -12919,7 +13082,7 @@
       <c r="M124" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="N124" s="2">
+      <c r="N124" s="7">
         <v>3</v>
       </c>
       <c r="O124" s="64" t="s">
@@ -13041,7 +13204,7 @@
       <c r="M126" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="N126" s="2">
+      <c r="N126" s="7">
         <v>5</v>
       </c>
       <c r="O126" s="64" t="s">
@@ -13102,7 +13265,7 @@
       <c r="M127" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="N127" s="2">
+      <c r="N127" s="7">
         <v>6</v>
       </c>
       <c r="O127" s="64" t="s">
@@ -13158,10 +13321,14 @@
         <v>46206</v>
       </c>
       <c r="L128" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M128" s="2"/>
-      <c r="N128" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M128" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="N128" s="2">
+        <v>6</v>
+      </c>
       <c r="O128" s="64" t="s">
         <v>25</v>
       </c>
@@ -13215,10 +13382,14 @@
         <v>46206</v>
       </c>
       <c r="L129" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M129" s="2"/>
-      <c r="N129" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M129" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="N129" s="2">
+        <v>4</v>
+      </c>
       <c r="O129" s="64" t="s">
         <v>28</v>
       </c>
@@ -13272,10 +13443,14 @@
         <v>46206</v>
       </c>
       <c r="L130" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M130" s="2"/>
-      <c r="N130" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M130" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="N130" s="2">
+        <v>7</v>
+      </c>
       <c r="O130" s="64" t="s">
         <v>25</v>
       </c>
@@ -13329,10 +13504,14 @@
         <v>46206</v>
       </c>
       <c r="L131" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M131" s="2"/>
-      <c r="N131" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M131" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="N131" s="2">
+        <v>3</v>
+      </c>
       <c r="O131" s="64" t="s">
         <v>28</v>
       </c>
@@ -13386,10 +13565,14 @@
         <v>46206</v>
       </c>
       <c r="L132" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M132" s="2"/>
-      <c r="N132" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M132" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="N132" s="2">
+        <v>5</v>
+      </c>
       <c r="O132" s="64" t="s">
         <v>25</v>
       </c>
@@ -13443,10 +13626,14 @@
         <v>46206</v>
       </c>
       <c r="L133" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M133" s="2"/>
-      <c r="N133" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M133" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="N133" s="2">
+        <v>2</v>
+      </c>
       <c r="O133" s="64" t="s">
         <v>28</v>
       </c>
@@ -13500,10 +13687,14 @@
         <v>46206</v>
       </c>
       <c r="L134" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M134" s="2"/>
-      <c r="N134" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="M134" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="N134" s="2">
+        <v>1</v>
+      </c>
       <c r="O134" s="64" t="s">
         <v>28</v>
       </c>
@@ -13887,7 +14078,7 @@
       <c r="M140" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="N140" s="2">
+      <c r="N140" s="7">
         <v>5</v>
       </c>
       <c r="O140" s="64" t="s">
@@ -13948,7 +14139,7 @@
       <c r="M141" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="N141" s="2">
+      <c r="N141" s="7">
         <v>7</v>
       </c>
       <c r="O141" s="64" t="s">
@@ -14009,7 +14200,7 @@
       <c r="M142" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="N142" s="2">
+      <c r="N142" s="7">
         <v>9</v>
       </c>
       <c r="O142" s="64" t="s">
@@ -14070,7 +14261,7 @@
       <c r="M143" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="N143" s="2">
+      <c r="N143" s="7">
         <v>3</v>
       </c>
       <c r="O143" s="64" t="s">
@@ -14131,7 +14322,7 @@
       <c r="M144" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="N144" s="2">
+      <c r="N144" s="7">
         <v>1</v>
       </c>
       <c r="O144" s="64" t="s">
@@ -14192,7 +14383,7 @@
       <c r="M145" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="N145" s="2">
+      <c r="N145" s="7">
         <v>2</v>
       </c>
       <c r="O145" s="64" t="s">
@@ -14253,7 +14444,7 @@
       <c r="M146" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="N146" s="2">
+      <c r="N146" s="7">
         <v>8</v>
       </c>
       <c r="O146" s="64" t="s">
@@ -14314,7 +14505,7 @@
       <c r="M147" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="N147" s="2">
+      <c r="N147" s="7">
         <v>4</v>
       </c>
       <c r="O147" s="64" t="s">
@@ -14375,7 +14566,7 @@
       <c r="M148" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="N148" s="2">
+      <c r="N148" s="7">
         <v>6</v>
       </c>
       <c r="O148" s="64" t="s">
@@ -14436,7 +14627,7 @@
       <c r="M149" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N149" s="2">
+      <c r="N149" s="7">
         <v>1</v>
       </c>
       <c r="O149" s="64" t="s">
@@ -14497,7 +14688,7 @@
       <c r="M150" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N150" s="2">
+      <c r="N150" s="7">
         <v>2</v>
       </c>
       <c r="O150" s="64" t="s">
@@ -14558,7 +14749,7 @@
       <c r="M151" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N151" s="2">
+      <c r="N151" s="7">
         <v>3</v>
       </c>
       <c r="O151" s="64" t="s">
@@ -14680,7 +14871,7 @@
       <c r="M153" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N153" s="2">
+      <c r="N153" s="7">
         <v>5</v>
       </c>
       <c r="O153" s="64" t="s">
@@ -14741,7 +14932,7 @@
       <c r="M154" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N154" s="2">
+      <c r="N154" s="7">
         <v>6</v>
       </c>
       <c r="O154" s="64" t="s">
@@ -14863,7 +15054,7 @@
       <c r="M156" s="2" t="s">
         <v>1227</v>
       </c>
-      <c r="N156" s="2">
+      <c r="N156" s="7">
         <v>2</v>
       </c>
       <c r="O156" s="64" t="s">
@@ -14985,7 +15176,7 @@
       <c r="M158" s="2" t="s">
         <v>1227</v>
       </c>
-      <c r="N158" s="2">
+      <c r="N158" s="7">
         <v>4</v>
       </c>
       <c r="O158" s="64" t="s">
@@ -15107,7 +15298,7 @@
       <c r="M160" s="2" t="s">
         <v>1227</v>
       </c>
-      <c r="N160" s="2">
+      <c r="N160" s="7">
         <v>6</v>
       </c>
       <c r="O160" s="64" t="s">
@@ -15360,8 +15551,12 @@
       <c r="L164" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M164" s="2"/>
-      <c r="N164" s="2"/>
+      <c r="M164" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="N164" s="7">
+        <v>1</v>
+      </c>
       <c r="O164" s="64" t="s">
         <v>235</v>
       </c>
@@ -15417,8 +15612,12 @@
       <c r="L165" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M165" s="2"/>
-      <c r="N165" s="2"/>
+      <c r="M165" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="N165" s="7">
+        <v>3</v>
+      </c>
       <c r="O165" s="64" t="s">
         <v>237</v>
       </c>
@@ -15474,8 +15673,12 @@
       <c r="L166" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M166" s="2"/>
-      <c r="N166" s="2"/>
+      <c r="M166" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="N166" s="7">
+        <v>2</v>
+      </c>
       <c r="O166" s="64" t="s">
         <v>235</v>
       </c>
@@ -15531,8 +15734,12 @@
       <c r="L167" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M167" s="2"/>
-      <c r="N167" s="2"/>
+      <c r="M167" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="N167" s="7">
+        <v>4</v>
+      </c>
       <c r="O167" s="64" t="s">
         <v>237</v>
       </c>
@@ -16108,8 +16315,12 @@
       <c r="L176" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M176" s="2"/>
-      <c r="N176" s="2"/>
+      <c r="M176" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="N176" s="7">
+        <v>8</v>
+      </c>
       <c r="O176" s="64" t="s">
         <v>235</v>
       </c>
@@ -16165,8 +16376,12 @@
       <c r="L177" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M177" s="2"/>
-      <c r="N177" s="2"/>
+      <c r="M177" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="N177" s="7">
+        <v>4</v>
+      </c>
       <c r="O177" s="64" t="s">
         <v>237</v>
       </c>
@@ -16222,8 +16437,12 @@
       <c r="L178" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M178" s="2"/>
-      <c r="N178" s="2"/>
+      <c r="M178" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="N178" s="7">
+        <v>7</v>
+      </c>
       <c r="O178" s="64" t="s">
         <v>235</v>
       </c>
@@ -16279,8 +16498,12 @@
       <c r="L179" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M179" s="2"/>
-      <c r="N179" s="2"/>
+      <c r="M179" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="N179" s="7">
+        <v>3</v>
+      </c>
       <c r="O179" s="64" t="s">
         <v>237</v>
       </c>
@@ -16336,8 +16559,12 @@
       <c r="L180" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M180" s="2"/>
-      <c r="N180" s="2"/>
+      <c r="M180" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="N180" s="7">
+        <v>6</v>
+      </c>
       <c r="O180" s="64" t="s">
         <v>235</v>
       </c>
@@ -16393,8 +16620,12 @@
       <c r="L181" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M181" s="2"/>
-      <c r="N181" s="2"/>
+      <c r="M181" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="N181" s="7">
+        <v>1</v>
+      </c>
       <c r="O181" s="64" t="s">
         <v>237</v>
       </c>
@@ -16450,8 +16681,12 @@
       <c r="L182" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M182" s="2"/>
-      <c r="N182" s="2"/>
+      <c r="M182" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="N182" s="7">
+        <v>5</v>
+      </c>
       <c r="O182" s="64" t="s">
         <v>235</v>
       </c>
@@ -16507,8 +16742,12 @@
       <c r="L183" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M183" s="2"/>
-      <c r="N183" s="2"/>
+      <c r="M183" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="N183" s="7">
+        <v>2</v>
+      </c>
       <c r="O183" s="64" t="s">
         <v>28</v>
       </c>
@@ -17080,8 +17319,8 @@
     <col min="11" max="13" width="20.265625" customWidth="1"/>
     <col min="14" max="14" width="35.46484375" customWidth="1"/>
     <col min="15" max="15" width="20.1328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.86328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.265625" customWidth="1"/>
+    <col min="16" max="16" width="24.59765625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="22.86328125" customWidth="1"/>
     <col min="19" max="19" width="11.6640625" customWidth="1"/>
   </cols>
@@ -17358,7 +17597,9 @@
       <c r="B6" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="53"/>
+      <c r="C6" s="53" t="s">
+        <v>1281</v>
+      </c>
       <c r="D6" s="53" t="s">
         <v>284</v>
       </c>
@@ -17368,8 +17609,12 @@
       <c r="F6" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="G6" s="3">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="H6" s="57">
+        <v>46255</v>
+      </c>
       <c r="I6" s="21" t="b">
         <v>0</v>
       </c>
@@ -17458,7 +17703,9 @@
       <c r="B8" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="53"/>
+      <c r="C8" s="53" t="s">
+        <v>1282</v>
+      </c>
       <c r="D8" s="53" t="s">
         <v>284</v>
       </c>
@@ -17468,8 +17715,12 @@
       <c r="F8" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="G8" s="3">
+        <v>0.104</v>
+      </c>
+      <c r="H8" s="57">
+        <v>46255</v>
+      </c>
       <c r="I8" s="21" t="b">
         <v>0</v>
       </c>
@@ -25240,7 +25491,9 @@
       <c r="B156" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C156" s="53"/>
+      <c r="C156" s="53" t="s">
+        <v>1280</v>
+      </c>
       <c r="D156" s="53" t="s">
         <v>284</v>
       </c>
@@ -25250,8 +25503,12 @@
       <c r="F156" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G156" s="3"/>
-      <c r="H156" s="3"/>
+      <c r="G156" s="3">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="H156" s="57">
+        <v>46255</v>
+      </c>
       <c r="I156" s="21" t="b">
         <v>0</v>
       </c>
@@ -25287,7 +25544,9 @@
       <c r="B157" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C157" s="53"/>
+      <c r="C157" s="53" t="s">
+        <v>1279</v>
+      </c>
       <c r="D157" s="53" t="s">
         <v>284</v>
       </c>
@@ -25297,8 +25556,12 @@
       <c r="F157" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G157" s="3"/>
-      <c r="H157" s="3"/>
+      <c r="G157" s="3">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="H157" s="57">
+        <v>46255</v>
+      </c>
       <c r="I157" s="21" t="b">
         <v>0</v>
       </c>
@@ -25334,7 +25597,9 @@
       <c r="B158" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C158" s="53"/>
+      <c r="C158" s="53" t="s">
+        <v>1278</v>
+      </c>
       <c r="D158" s="53" t="s">
         <v>284</v>
       </c>
@@ -25344,8 +25609,12 @@
       <c r="F158" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G158" s="3"/>
-      <c r="H158" s="3"/>
+      <c r="G158" s="3">
+        <v>0.104</v>
+      </c>
+      <c r="H158" s="57">
+        <v>46255</v>
+      </c>
       <c r="I158" s="21" t="b">
         <v>0</v>
       </c>
@@ -25381,7 +25650,9 @@
       <c r="B159" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C159" s="53"/>
+      <c r="C159" s="53" t="s">
+        <v>1191</v>
+      </c>
       <c r="D159" s="53" t="s">
         <v>284</v>
       </c>
@@ -25391,8 +25662,12 @@
       <c r="F159" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G159" s="3"/>
-      <c r="H159" s="3"/>
+      <c r="G159" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H159" s="57">
+        <v>46255</v>
+      </c>
       <c r="I159" s="21" t="b">
         <v>0</v>
       </c>
@@ -25428,7 +25703,9 @@
       <c r="B160" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C160" s="53"/>
+      <c r="C160" s="53" t="s">
+        <v>1191</v>
+      </c>
       <c r="D160" s="53" t="s">
         <v>284</v>
       </c>
@@ -25438,8 +25715,12 @@
       <c r="F160" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G160" s="3"/>
-      <c r="H160" s="3"/>
+      <c r="G160" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H160" s="57">
+        <v>46255</v>
+      </c>
       <c r="I160" s="21" t="b">
         <v>0</v>
       </c>
@@ -25475,7 +25756,9 @@
       <c r="B161" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C161" s="53"/>
+      <c r="C161" s="53" t="s">
+        <v>1191</v>
+      </c>
       <c r="D161" s="53" t="s">
         <v>284</v>
       </c>
@@ -25485,8 +25768,12 @@
       <c r="F161" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G161" s="3"/>
-      <c r="H161" s="3"/>
+      <c r="G161" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H161" s="57">
+        <v>46255</v>
+      </c>
       <c r="I161" s="21" t="b">
         <v>0</v>
       </c>

--- a/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
+++ b/EVG_SIT_FS_Meter_Commissioning_2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voltano-my.sharepoint.com/personal/ruan_vh_voltano_com/Documents/Desktop/Voltano/Clients/Evergreen/Evergreen Sitari/Site initialization/Freestanding/EVG_FS_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3549" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9DEF16A-C557-4089-9CFF-8B4A4B172C5F}"/>
+  <xr:revisionPtr revIDLastSave="3902" documentId="8_{C97FC332-2E41-401D-B97C-40A4EC775E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDF7F987-EB3E-43EE-B2B2-34BB27E5F936}"/>
   <bookViews>
     <workbookView xWindow="88080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,10 +19,11 @@
     <sheet name="Aprt Water" sheetId="9" r:id="rId4"/>
     <sheet name="Kiosk Plan" sheetId="5" r:id="rId5"/>
     <sheet name="Temp ME162 open and closings" sheetId="2" r:id="rId6"/>
+    <sheet name="Replaced meters" sheetId="10" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FS Elec'!$A$1:$U$192</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FS Water'!$A$1:$S$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FS Water'!$A$1:$T$193</definedName>
   </definedNames>
   <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5061" uniqueCount="1292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5125" uniqueCount="1312">
   <si>
     <t xml:space="preserve">Stand Number </t>
   </si>
@@ -3921,6 +3922,66 @@
   </si>
   <si>
     <t>2cf7f12072901e3a</t>
+  </si>
+  <si>
+    <t>10596295</t>
+  </si>
+  <si>
+    <t>10596246</t>
+  </si>
+  <si>
+    <t>10596197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New meter serial </t>
+  </si>
+  <si>
+    <t>New meter opening</t>
+  </si>
+  <si>
+    <t>10596238</t>
+  </si>
+  <si>
+    <t>10596306</t>
+  </si>
+  <si>
+    <t>Faulty replaced twice</t>
+  </si>
+  <si>
+    <t>10596198</t>
+  </si>
+  <si>
+    <t>10596190</t>
+  </si>
+  <si>
+    <t>10596292</t>
+  </si>
+  <si>
+    <t>10596297</t>
+  </si>
+  <si>
+    <t>10596218</t>
+  </si>
+  <si>
+    <t>10596272</t>
+  </si>
+  <si>
+    <t>10596233</t>
+  </si>
+  <si>
+    <t>10596254</t>
+  </si>
+  <si>
+    <t>10596307</t>
+  </si>
+  <si>
+    <t>10596299</t>
+  </si>
+  <si>
+    <t>10596247</t>
+  </si>
+  <si>
+    <t>10596241</t>
   </si>
 </sst>
 </file>
@@ -3930,12 +3991,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4086,6 +4154,13 @@
     </font>
     <font>
       <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -4535,36 +4610,36 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4575,7 +4650,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -4583,32 +4658,32 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -4616,82 +4691,82 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -4699,99 +4774,99 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="35" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="36" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="38" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="39" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="38" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="39" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="35" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
@@ -4801,89 +4876,89 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="42" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="42" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="43" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="43" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="44" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="44" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="45" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="45" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="41" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4901,43 +4976,43 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4946,7 +5021,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4961,17 +5036,57 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4979,7 +5094,57 @@
     <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{EDB79C3E-33DC-4A47-B5C8-E4BE66ABEE17}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5446,6 +5611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB9F803-2DDE-485F-989C-C0688D786923}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U192"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5542,7 +5708,7 @@
         <v>19</v>
       </c>
       <c r="C2" s="2">
-        <v>1455868871</v>
+        <v>14558068871</v>
       </c>
       <c r="D2" s="2">
         <v>82929684</v>
@@ -5900,7 +6066,7 @@
       <c r="T7" s="136"/>
       <c r="U7" s="136"/>
     </row>
-    <row r="8" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>35</v>
       </c>
@@ -5940,7 +6106,9 @@
       <c r="M8" s="2" t="s">
         <v>1291</v>
       </c>
-      <c r="N8" s="7"/>
+      <c r="N8" s="7">
+        <v>5</v>
+      </c>
       <c r="O8" s="64" t="s">
         <v>37</v>
       </c>
@@ -5959,7 +6127,7 @@
       <c r="T8" s="136"/>
       <c r="U8" s="136"/>
     </row>
-    <row r="9" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>38</v>
       </c>
@@ -5999,7 +6167,9 @@
       <c r="M9" s="2" t="s">
         <v>1291</v>
       </c>
-      <c r="N9" s="7"/>
+      <c r="N9" s="7">
+        <v>1</v>
+      </c>
       <c r="O9" s="64" t="s">
         <v>39</v>
       </c>
@@ -6018,7 +6188,7 @@
       <c r="T9" s="136"/>
       <c r="U9" s="136"/>
     </row>
-    <row r="10" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>40</v>
       </c>
@@ -6058,7 +6228,9 @@
       <c r="M10" s="2" t="s">
         <v>1291</v>
       </c>
-      <c r="N10" s="7"/>
+      <c r="N10" s="7">
+        <v>6</v>
+      </c>
       <c r="O10" s="64" t="s">
         <v>37</v>
       </c>
@@ -6077,7 +6249,7 @@
       <c r="T10" s="136"/>
       <c r="U10" s="136"/>
     </row>
-    <row r="11" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>41</v>
       </c>
@@ -6117,7 +6289,9 @@
       <c r="M11" s="2" t="s">
         <v>1291</v>
       </c>
-      <c r="N11" s="7"/>
+      <c r="N11" s="7">
+        <v>2</v>
+      </c>
       <c r="O11" s="64" t="s">
         <v>39</v>
       </c>
@@ -6136,7 +6310,7 @@
       <c r="T11" s="136"/>
       <c r="U11" s="136"/>
     </row>
-    <row r="12" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>42</v>
       </c>
@@ -6176,7 +6350,9 @@
       <c r="M12" s="2" t="s">
         <v>1291</v>
       </c>
-      <c r="N12" s="7"/>
+      <c r="N12" s="7">
+        <v>7</v>
+      </c>
       <c r="O12" s="64" t="s">
         <v>37</v>
       </c>
@@ -6195,7 +6371,7 @@
       <c r="T12" s="136"/>
       <c r="U12" s="136"/>
     </row>
-    <row r="13" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
         <v>43</v>
       </c>
@@ -6235,7 +6411,9 @@
       <c r="M13" s="2" t="s">
         <v>1291</v>
       </c>
-      <c r="N13" s="7"/>
+      <c r="N13" s="7">
+        <v>3</v>
+      </c>
       <c r="O13" s="64" t="s">
         <v>39</v>
       </c>
@@ -6254,7 +6432,7 @@
       <c r="T13" s="136"/>
       <c r="U13" s="136"/>
     </row>
-    <row r="14" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>44</v>
       </c>
@@ -6294,7 +6472,9 @@
       <c r="M14" s="2" t="s">
         <v>1291</v>
       </c>
-      <c r="N14" s="7"/>
+      <c r="N14" s="7">
+        <v>4</v>
+      </c>
       <c r="O14" s="64" t="s">
         <v>39</v>
       </c>
@@ -6313,7 +6493,7 @@
       <c r="T14" s="136"/>
       <c r="U14" s="136"/>
     </row>
-    <row r="15" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>45</v>
       </c>
@@ -6353,7 +6533,9 @@
       <c r="M15" s="2" t="s">
         <v>1290</v>
       </c>
-      <c r="N15" s="7"/>
+      <c r="N15" s="7">
+        <v>5</v>
+      </c>
       <c r="O15" s="64" t="s">
         <v>37</v>
       </c>
@@ -6372,7 +6554,7 @@
       <c r="T15" s="136"/>
       <c r="U15" s="136"/>
     </row>
-    <row r="16" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>47</v>
       </c>
@@ -6412,7 +6594,9 @@
       <c r="M16" s="2" t="s">
         <v>1290</v>
       </c>
-      <c r="N16" s="7"/>
+      <c r="N16" s="7">
+        <v>6</v>
+      </c>
       <c r="O16" s="64" t="s">
         <v>37</v>
       </c>
@@ -6431,7 +6615,7 @@
       <c r="T16" s="136"/>
       <c r="U16" s="136"/>
     </row>
-    <row r="17" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
         <v>48</v>
       </c>
@@ -6471,7 +6655,9 @@
       <c r="M17" s="2" t="s">
         <v>1290</v>
       </c>
-      <c r="N17" s="7"/>
+      <c r="N17" s="7">
+        <v>1</v>
+      </c>
       <c r="O17" s="64" t="s">
         <v>39</v>
       </c>
@@ -6490,7 +6676,7 @@
       <c r="T17" s="136"/>
       <c r="U17" s="136"/>
     </row>
-    <row r="18" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>49</v>
       </c>
@@ -6530,7 +6716,9 @@
       <c r="M18" s="2" t="s">
         <v>1290</v>
       </c>
-      <c r="N18" s="7"/>
+      <c r="N18" s="7">
+        <v>7</v>
+      </c>
       <c r="O18" s="64" t="s">
         <v>37</v>
       </c>
@@ -6549,7 +6737,7 @@
       <c r="T18" s="136"/>
       <c r="U18" s="136"/>
     </row>
-    <row r="19" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
         <v>50</v>
       </c>
@@ -6589,7 +6777,9 @@
       <c r="M19" s="2" t="s">
         <v>1290</v>
       </c>
-      <c r="N19" s="7"/>
+      <c r="N19" s="7">
+        <v>2</v>
+      </c>
       <c r="O19" s="64" t="s">
         <v>39</v>
       </c>
@@ -6608,7 +6798,7 @@
       <c r="T19" s="136"/>
       <c r="U19" s="136"/>
     </row>
-    <row r="20" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>51</v>
       </c>
@@ -6648,7 +6838,9 @@
       <c r="M20" s="2" t="s">
         <v>1290</v>
       </c>
-      <c r="N20" s="7"/>
+      <c r="N20" s="7">
+        <v>8</v>
+      </c>
       <c r="O20" s="64" t="s">
         <v>37</v>
       </c>
@@ -6667,7 +6859,7 @@
       <c r="T20" s="136"/>
       <c r="U20" s="136"/>
     </row>
-    <row r="21" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
         <v>52</v>
       </c>
@@ -6707,7 +6899,9 @@
       <c r="M21" s="2" t="s">
         <v>1290</v>
       </c>
-      <c r="N21" s="7"/>
+      <c r="N21" s="7">
+        <v>3</v>
+      </c>
       <c r="O21" s="64" t="s">
         <v>39</v>
       </c>
@@ -6726,7 +6920,7 @@
       <c r="T21" s="136"/>
       <c r="U21" s="136"/>
     </row>
-    <row r="22" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>53</v>
       </c>
@@ -6766,7 +6960,9 @@
       <c r="M22" s="2" t="s">
         <v>1290</v>
       </c>
-      <c r="N22" s="7"/>
+      <c r="N22" s="7">
+        <v>4</v>
+      </c>
       <c r="O22" s="64" t="s">
         <v>39</v>
       </c>
@@ -6785,7 +6981,7 @@
       <c r="T22" s="136"/>
       <c r="U22" s="136"/>
     </row>
-    <row r="23" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>54</v>
       </c>
@@ -6846,14 +7042,14 @@
       <c r="T23" s="136"/>
       <c r="U23" s="136"/>
     </row>
-    <row r="24" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="140">
+      <c r="C24" s="152">
         <v>14558069598</v>
       </c>
       <c r="D24" s="2">
@@ -6907,7 +7103,7 @@
       <c r="T24" s="136"/>
       <c r="U24" s="136"/>
     </row>
-    <row r="25" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>58</v>
       </c>
@@ -6968,7 +7164,7 @@
       <c r="T25" s="136"/>
       <c r="U25" s="136"/>
     </row>
-    <row r="26" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>59</v>
       </c>
@@ -7029,7 +7225,7 @@
       <c r="T26" s="136"/>
       <c r="U26" s="136"/>
     </row>
-    <row r="27" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
         <v>60</v>
       </c>
@@ -7090,7 +7286,7 @@
       <c r="T27" s="136"/>
       <c r="U27" s="136"/>
     </row>
-    <row r="28" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>61</v>
       </c>
@@ -7151,7 +7347,7 @@
       <c r="T28" s="136"/>
       <c r="U28" s="136"/>
     </row>
-    <row r="29" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>62</v>
       </c>
@@ -7212,7 +7408,7 @@
       <c r="T29" s="136"/>
       <c r="U29" s="136"/>
     </row>
-    <row r="30" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
         <v>63</v>
       </c>
@@ -7273,7 +7469,7 @@
       <c r="T30" s="136"/>
       <c r="U30" s="136"/>
     </row>
-    <row r="31" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
         <v>64</v>
       </c>
@@ -7369,12 +7565,12 @@
         <v>46210</v>
       </c>
       <c r="L32" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>1214</v>
       </c>
-      <c r="N32" s="7">
+      <c r="N32" s="153">
         <v>2</v>
       </c>
       <c r="O32" s="64" t="s">
@@ -7430,12 +7626,12 @@
         <v>46210</v>
       </c>
       <c r="L33" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>1214</v>
       </c>
-      <c r="N33" s="7">
+      <c r="N33" s="153">
         <v>3</v>
       </c>
       <c r="O33" s="64" t="s">
@@ -7491,12 +7687,12 @@
         <v>46210</v>
       </c>
       <c r="L34" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>1214</v>
       </c>
-      <c r="N34" s="7">
+      <c r="N34" s="153">
         <v>4</v>
       </c>
       <c r="O34" s="64" t="s">
@@ -7639,7 +7835,7 @@
       <c r="T36" s="136"/>
       <c r="U36" s="136"/>
     </row>
-    <row r="37" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
         <v>74</v>
       </c>
@@ -7700,7 +7896,7 @@
       <c r="T37" s="136"/>
       <c r="U37" s="136"/>
     </row>
-    <row r="38" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>77</v>
       </c>
@@ -7826,7 +8022,7 @@
         <v>36.700000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
         <v>81</v>
       </c>
@@ -7952,7 +8148,7 @@
         <v>11.590999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
         <v>83</v>
       </c>
@@ -8013,7 +8209,7 @@
       <c r="T42" s="136"/>
       <c r="U42" s="136"/>
     </row>
-    <row r="43" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
         <v>84</v>
       </c>
@@ -8074,7 +8270,7 @@
       <c r="T43" s="136"/>
       <c r="U43" s="136"/>
     </row>
-    <row r="44" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
         <v>85</v>
       </c>
@@ -8231,12 +8427,12 @@
         <v>46220</v>
       </c>
       <c r="L46" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>1283</v>
       </c>
-      <c r="N46" s="7">
+      <c r="N46" s="153">
         <v>6</v>
       </c>
       <c r="O46" s="64" t="s">
@@ -8257,7 +8453,7 @@
       <c r="T46" s="136"/>
       <c r="U46" s="136"/>
     </row>
-    <row r="47" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
         <v>90</v>
       </c>
@@ -8318,7 +8514,7 @@
       <c r="T47" s="136"/>
       <c r="U47" s="136"/>
     </row>
-    <row r="48" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
         <v>91</v>
       </c>
@@ -8379,7 +8575,7 @@
       <c r="T48" s="136"/>
       <c r="U48" s="136"/>
     </row>
-    <row r="49" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
         <v>92</v>
       </c>
@@ -8440,7 +8636,7 @@
       <c r="T49" s="136"/>
       <c r="U49" s="136"/>
     </row>
-    <row r="50" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
         <v>93</v>
       </c>
@@ -8501,7 +8697,7 @@
       <c r="T50" s="136"/>
       <c r="U50" s="136"/>
     </row>
-    <row r="51" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
         <v>94</v>
       </c>
@@ -8562,7 +8758,7 @@
       <c r="T51" s="136"/>
       <c r="U51" s="136"/>
     </row>
-    <row r="52" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
         <v>95</v>
       </c>
@@ -9131,7 +9327,7 @@
       <c r="T60" s="136"/>
       <c r="U60" s="136"/>
     </row>
-    <row r="61" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
         <v>105</v>
       </c>
@@ -9192,7 +9388,7 @@
       <c r="T61" s="136"/>
       <c r="U61" s="136"/>
     </row>
-    <row r="62" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
         <v>108</v>
       </c>
@@ -9379,7 +9575,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="12" t="s">
         <v>111</v>
       </c>
@@ -9505,7 +9701,7 @@
         <v>39.33</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="12" t="s">
         <v>113</v>
       </c>
@@ -9696,7 +9892,7 @@
         <v>37.427999999999997</v>
       </c>
     </row>
-    <row r="70" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>116</v>
       </c>
@@ -9792,12 +9988,12 @@
         <v>46219</v>
       </c>
       <c r="L71" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="N71" s="7">
+      <c r="N71" s="153">
         <v>2</v>
       </c>
       <c r="O71" s="64" t="s">
@@ -9818,7 +10014,7 @@
       <c r="T71" s="136"/>
       <c r="U71" s="136"/>
     </row>
-    <row r="72" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
         <v>120</v>
       </c>
@@ -9879,7 +10075,7 @@
       <c r="T72" s="136"/>
       <c r="U72" s="136"/>
     </row>
-    <row r="73" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
         <v>122</v>
       </c>
@@ -9940,7 +10136,7 @@
       <c r="T73" s="136"/>
       <c r="U73" s="136"/>
     </row>
-    <row r="74" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
         <v>123</v>
       </c>
@@ -10001,7 +10197,7 @@
       <c r="T74" s="136"/>
       <c r="U74" s="136"/>
     </row>
-    <row r="75" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
         <v>124</v>
       </c>
@@ -10062,7 +10258,7 @@
       <c r="T75" s="136"/>
       <c r="U75" s="136"/>
     </row>
-    <row r="76" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
         <v>125</v>
       </c>
@@ -10123,7 +10319,7 @@
       <c r="T76" s="136"/>
       <c r="U76" s="136"/>
     </row>
-    <row r="77" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
         <v>126</v>
       </c>
@@ -10184,7 +10380,7 @@
       <c r="T77" s="136"/>
       <c r="U77" s="136"/>
     </row>
-    <row r="78" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
         <v>127</v>
       </c>
@@ -10280,12 +10476,12 @@
         <v>46197</v>
       </c>
       <c r="L79" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="s">
         <v>1219</v>
       </c>
-      <c r="N79" s="7">
+      <c r="N79" s="153">
         <v>6</v>
       </c>
       <c r="O79" s="64" t="s">
@@ -10402,12 +10598,12 @@
         <v>46197</v>
       </c>
       <c r="L81" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="s">
         <v>1219</v>
       </c>
-      <c r="N81" s="7">
+      <c r="N81" s="153">
         <v>7</v>
       </c>
       <c r="O81" s="64" t="s">
@@ -10496,7 +10692,7 @@
       <c r="B83" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C83" s="140">
+      <c r="C83" s="152">
         <v>14558068442</v>
       </c>
       <c r="D83" s="2">
@@ -10585,12 +10781,12 @@
         <v>46197</v>
       </c>
       <c r="L84" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="s">
         <v>1219</v>
       </c>
-      <c r="N84" s="7">
+      <c r="N84" s="153">
         <v>2</v>
       </c>
       <c r="O84" s="64" t="s">
@@ -10733,7 +10929,7 @@
       <c r="T86" s="136"/>
       <c r="U86" s="136"/>
     </row>
-    <row r="87" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
         <v>139</v>
       </c>
@@ -10794,7 +10990,7 @@
       <c r="T87" s="136"/>
       <c r="U87" s="136"/>
     </row>
-    <row r="88" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="12" t="s">
         <v>141</v>
       </c>
@@ -10920,7 +11116,7 @@
         <v>102.95</v>
       </c>
     </row>
-    <row r="90" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="12" t="s">
         <v>144</v>
       </c>
@@ -11302,7 +11498,7 @@
         <v>45.284999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="12" t="s">
         <v>150</v>
       </c>
@@ -11363,7 +11559,7 @@
       <c r="T96" s="136"/>
       <c r="U96" s="136"/>
     </row>
-    <row r="97" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="12" t="s">
         <v>152</v>
       </c>
@@ -11424,7 +11620,7 @@
       <c r="T97" s="136"/>
       <c r="U97" s="136"/>
     </row>
-    <row r="98" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="12" t="s">
         <v>153</v>
       </c>
@@ -11485,7 +11681,7 @@
       <c r="T98" s="136"/>
       <c r="U98" s="136"/>
     </row>
-    <row r="99" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="12" t="s">
         <v>154</v>
       </c>
@@ -11546,7 +11742,7 @@
       <c r="T99" s="136"/>
       <c r="U99" s="136"/>
     </row>
-    <row r="100" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="12" t="s">
         <v>155</v>
       </c>
@@ -11607,7 +11803,7 @@
       <c r="T100" s="136"/>
       <c r="U100" s="136"/>
     </row>
-    <row r="101" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="12" t="s">
         <v>156</v>
       </c>
@@ -11668,7 +11864,7 @@
       <c r="T101" s="136"/>
       <c r="U101" s="136"/>
     </row>
-    <row r="102" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="12" t="s">
         <v>157</v>
       </c>
@@ -11729,7 +11925,7 @@
       <c r="T102" s="136"/>
       <c r="U102" s="136"/>
     </row>
-    <row r="103" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="12" t="s">
         <v>158</v>
       </c>
@@ -11790,7 +11986,7 @@
       <c r="T103" s="136"/>
       <c r="U103" s="136"/>
     </row>
-    <row r="104" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="12" t="s">
         <v>160</v>
       </c>
@@ -12095,7 +12291,7 @@
       <c r="T108" s="136"/>
       <c r="U108" s="136"/>
     </row>
-    <row r="109" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="12" t="s">
         <v>166</v>
       </c>
@@ -12955,12 +13151,12 @@
         <v>46218</v>
       </c>
       <c r="L122" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="N122" s="7">
+      <c r="N122" s="153">
         <v>4</v>
       </c>
       <c r="O122" s="64" t="s">
@@ -13042,7 +13238,7 @@
       <c r="T123" s="136"/>
       <c r="U123" s="136"/>
     </row>
-    <row r="124" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="12" t="s">
         <v>185</v>
       </c>
@@ -13164,7 +13360,7 @@
       <c r="T125" s="136"/>
       <c r="U125" s="136"/>
     </row>
-    <row r="126" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="12" t="s">
         <v>187</v>
       </c>
@@ -13225,7 +13421,7 @@
       <c r="T126" s="136"/>
       <c r="U126" s="136"/>
     </row>
-    <row r="127" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="12" t="s">
         <v>188</v>
       </c>
@@ -14038,7 +14234,7 @@
         <v>55.5</v>
       </c>
     </row>
-    <row r="140" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="12" t="s">
         <v>203</v>
       </c>
@@ -14099,7 +14295,7 @@
       <c r="T140" s="136"/>
       <c r="U140" s="136"/>
     </row>
-    <row r="141" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="12" t="s">
         <v>205</v>
       </c>
@@ -14160,7 +14356,7 @@
       <c r="T141" s="136"/>
       <c r="U141" s="136"/>
     </row>
-    <row r="142" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="12" t="s">
         <v>206</v>
       </c>
@@ -14221,7 +14417,7 @@
       <c r="T142" s="136"/>
       <c r="U142" s="136"/>
     </row>
-    <row r="143" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="12" t="s">
         <v>207</v>
       </c>
@@ -14282,7 +14478,7 @@
       <c r="T143" s="136"/>
       <c r="U143" s="136"/>
     </row>
-    <row r="144" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="12" t="s">
         <v>208</v>
       </c>
@@ -14343,7 +14539,7 @@
       <c r="T144" s="136"/>
       <c r="U144" s="136"/>
     </row>
-    <row r="145" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="12" t="s">
         <v>209</v>
       </c>
@@ -14404,7 +14600,7 @@
       <c r="T145" s="136"/>
       <c r="U145" s="136"/>
     </row>
-    <row r="146" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="12" t="s">
         <v>210</v>
       </c>
@@ -14465,7 +14661,7 @@
       <c r="T146" s="136"/>
       <c r="U146" s="136"/>
     </row>
-    <row r="147" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="12" t="s">
         <v>211</v>
       </c>
@@ -14526,7 +14722,7 @@
       <c r="T147" s="136"/>
       <c r="U147" s="136"/>
     </row>
-    <row r="148" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="12" t="s">
         <v>212</v>
       </c>
@@ -14622,12 +14818,12 @@
         <v>46210</v>
       </c>
       <c r="L149" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M149" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N149" s="7">
+      <c r="N149" s="153">
         <v>1</v>
       </c>
       <c r="O149" s="64" t="s">
@@ -14683,12 +14879,12 @@
         <v>46210</v>
       </c>
       <c r="L150" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M150" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N150" s="7">
+      <c r="N150" s="153">
         <v>2</v>
       </c>
       <c r="O150" s="64" t="s">
@@ -14744,12 +14940,12 @@
         <v>46210</v>
       </c>
       <c r="L151" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M151" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N151" s="7">
+      <c r="N151" s="153">
         <v>3</v>
       </c>
       <c r="O151" s="64" t="s">
@@ -14866,12 +15062,12 @@
         <v>46210</v>
       </c>
       <c r="L153" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M153" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N153" s="7">
+      <c r="N153" s="153">
         <v>5</v>
       </c>
       <c r="O153" s="64" t="s">
@@ -14927,12 +15123,12 @@
         <v>46210</v>
       </c>
       <c r="L154" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="N154" s="7">
+      <c r="N154" s="153">
         <v>6</v>
       </c>
       <c r="O154" s="64" t="s">
@@ -15014,7 +15210,7 @@
       <c r="T155" s="136"/>
       <c r="U155" s="136"/>
     </row>
-    <row r="156" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="12" t="s">
         <v>223</v>
       </c>
@@ -15136,7 +15332,7 @@
       <c r="T157" s="136"/>
       <c r="U157" s="136"/>
     </row>
-    <row r="158" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="12" t="s">
         <v>225</v>
       </c>
@@ -15258,7 +15454,7 @@
       <c r="T159" s="136"/>
       <c r="U159" s="136"/>
     </row>
-    <row r="160" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="12" t="s">
         <v>227</v>
       </c>
@@ -15514,7 +15710,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="164" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="12" t="s">
         <v>233</v>
       </c>
@@ -15575,7 +15771,7 @@
       <c r="T164" s="136"/>
       <c r="U164" s="136"/>
     </row>
-    <row r="165" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="12" t="s">
         <v>236</v>
       </c>
@@ -15636,7 +15832,7 @@
       <c r="T165" s="136"/>
       <c r="U165" s="136"/>
     </row>
-    <row r="166" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="12" t="s">
         <v>238</v>
       </c>
@@ -15697,7 +15893,7 @@
       <c r="T166" s="136"/>
       <c r="U166" s="136"/>
     </row>
-    <row r="167" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="12" t="s">
         <v>239</v>
       </c>
@@ -16278,7 +16474,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="176" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="12" t="s">
         <v>251</v>
       </c>
@@ -16339,7 +16535,7 @@
       <c r="T176" s="136"/>
       <c r="U176" s="136"/>
     </row>
-    <row r="177" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="12" t="s">
         <v>253</v>
       </c>
@@ -16400,7 +16596,7 @@
       <c r="T177" s="136"/>
       <c r="U177" s="136"/>
     </row>
-    <row r="178" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="12" t="s">
         <v>254</v>
       </c>
@@ -16461,7 +16657,7 @@
       <c r="T178" s="136"/>
       <c r="U178" s="136"/>
     </row>
-    <row r="179" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="12" t="s">
         <v>255</v>
       </c>
@@ -16522,7 +16718,7 @@
       <c r="T179" s="136"/>
       <c r="U179" s="136"/>
     </row>
-    <row r="180" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="12" t="s">
         <v>256</v>
       </c>
@@ -16618,12 +16814,12 @@
         <v>46206</v>
       </c>
       <c r="L181" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M181" s="2" t="s">
         <v>1285</v>
       </c>
-      <c r="N181" s="7">
+      <c r="N181" s="153">
         <v>1</v>
       </c>
       <c r="O181" s="64" t="s">
@@ -16679,12 +16875,12 @@
         <v>46206</v>
       </c>
       <c r="L182" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M182" s="2" t="s">
         <v>1285</v>
       </c>
-      <c r="N182" s="7">
+      <c r="N182" s="153">
         <v>5</v>
       </c>
       <c r="O182" s="64" t="s">
@@ -16705,7 +16901,7 @@
       <c r="T182" s="136"/>
       <c r="U182" s="136"/>
     </row>
-    <row r="183" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="12" t="s">
         <v>259</v>
       </c>
@@ -16766,7 +16962,7 @@
       <c r="T183" s="136"/>
       <c r="U183" s="136"/>
     </row>
-    <row r="184" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="12" t="s">
         <v>260</v>
       </c>
@@ -16823,7 +17019,7 @@
       <c r="T184" s="136"/>
       <c r="U184" s="136"/>
     </row>
-    <row r="185" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="12" t="s">
         <v>263</v>
       </c>
@@ -16880,7 +17076,7 @@
       <c r="T185" s="136"/>
       <c r="U185" s="136"/>
     </row>
-    <row r="186" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="12" t="s">
         <v>264</v>
       </c>
@@ -16937,7 +17133,7 @@
       <c r="T186" s="136"/>
       <c r="U186" s="136"/>
     </row>
-    <row r="187" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="12" t="s">
         <v>265</v>
       </c>
@@ -16994,7 +17190,7 @@
       <c r="T187" s="136"/>
       <c r="U187" s="136"/>
     </row>
-    <row r="188" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="12" t="s">
         <v>266</v>
       </c>
@@ -17051,7 +17247,7 @@
       <c r="T188" s="136"/>
       <c r="U188" s="136"/>
     </row>
-    <row r="189" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="12" t="s">
         <v>267</v>
       </c>
@@ -17108,7 +17304,7 @@
       <c r="T189" s="136"/>
       <c r="U189" s="136"/>
     </row>
-    <row r="190" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="12" t="s">
         <v>268</v>
       </c>
@@ -17165,7 +17361,7 @@
       <c r="T190" s="136"/>
       <c r="U190" s="136"/>
     </row>
-    <row r="191" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:21" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="12" t="s">
         <v>269</v>
       </c>
@@ -17259,7 +17455,7 @@
       <c r="L192" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="M192" s="141" t="s">
+      <c r="M192" s="140" t="s">
         <v>1230</v>
       </c>
       <c r="N192" s="134">
@@ -17284,18 +17480,25 @@
       <c r="U192" s="136"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:U192" xr:uid="{CFB9F803-2DDE-485F-989C-C0688D786923}">
+    <filterColumn colId="11">
+      <filters>
+        <filter val="TRUE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U192">
     <sortCondition ref="I2:I192"/>
   </sortState>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="C25:C192 C2:C23">
-    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C117:C122">
-    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C124:C132">
-    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17303,7 +17506,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S204"/>
+  <dimension ref="A1:T204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.33203125" customWidth="1"/>
@@ -17410,7 +17613,7 @@
         <v>46254</v>
       </c>
       <c r="I2" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="63" t="s">
         <v>118</v>
@@ -17463,7 +17666,7 @@
         <v>46254</v>
       </c>
       <c r="I3" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="63" t="s">
         <v>118</v>
@@ -17563,7 +17766,7 @@
         <v>46254</v>
       </c>
       <c r="I5" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="63" t="s">
         <v>118</v>
@@ -17616,7 +17819,7 @@
         <v>46255</v>
       </c>
       <c r="I6" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="63" t="s">
         <v>121</v>
@@ -17669,7 +17872,7 @@
         <v>46254</v>
       </c>
       <c r="I7" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="63" t="s">
         <v>118</v>
@@ -17722,7 +17925,7 @@
         <v>46255</v>
       </c>
       <c r="I8" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="63" t="s">
         <v>121</v>
@@ -17775,7 +17978,7 @@
         <v>46254</v>
       </c>
       <c r="I9" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="63" t="s">
         <v>118</v>
@@ -17828,7 +18031,7 @@
         <v>46254</v>
       </c>
       <c r="I10" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="63" t="s">
         <v>121</v>
@@ -17881,7 +18084,7 @@
         <v>46254</v>
       </c>
       <c r="I11" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="63" t="s">
         <v>118</v>
@@ -17934,7 +18137,7 @@
         <v>46254</v>
       </c>
       <c r="I12" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="63" t="s">
         <v>121</v>
@@ -17987,7 +18190,7 @@
         <v>46254</v>
       </c>
       <c r="I13" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="63" t="s">
         <v>118</v>
@@ -18040,7 +18243,7 @@
         <v>46254</v>
       </c>
       <c r="I14" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="63" t="s">
         <v>121</v>
@@ -18093,7 +18296,7 @@
         <v>46254</v>
       </c>
       <c r="I15" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="63" t="s">
         <v>118</v>
@@ -18146,7 +18349,7 @@
         <v>46254</v>
       </c>
       <c r="I16" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="63" t="s">
         <v>121</v>
@@ -18199,7 +18402,7 @@
         <v>46254</v>
       </c>
       <c r="I17" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="63" t="s">
         <v>118</v>
@@ -18252,7 +18455,7 @@
         <v>46254</v>
       </c>
       <c r="I18" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="63" t="s">
         <v>159</v>
@@ -18305,7 +18508,7 @@
         <v>46254</v>
       </c>
       <c r="I19" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="63" t="s">
         <v>118</v>
@@ -18358,7 +18561,7 @@
         <v>46254</v>
       </c>
       <c r="I20" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="63" t="s">
         <v>159</v>
@@ -18411,7 +18614,7 @@
         <v>46254</v>
       </c>
       <c r="I21" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="63" t="s">
         <v>184</v>
@@ -18517,7 +18720,7 @@
         <v>46254</v>
       </c>
       <c r="I23" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="63" t="s">
         <v>184</v>
@@ -18623,7 +18826,7 @@
         <v>46254</v>
       </c>
       <c r="I25" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="63" t="s">
         <v>184</v>
@@ -18835,7 +19038,7 @@
         <v>46254</v>
       </c>
       <c r="I29" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="63" t="s">
         <v>184</v>
@@ -18888,7 +19091,7 @@
         <v>46254</v>
       </c>
       <c r="I30" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="63" t="s">
         <v>159</v>
@@ -18941,7 +19144,7 @@
         <v>46254</v>
       </c>
       <c r="I31" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="63" t="s">
         <v>184</v>
@@ -20904,7 +21107,7 @@
         <v>46186</v>
       </c>
       <c r="I68" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" s="63" t="s">
         <v>132</v>
@@ -21589,7 +21792,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A81" s="23" t="s">
         <v>240</v>
       </c>
@@ -21646,15 +21849,15 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A82" s="23" t="s">
         <v>243</v>
       </c>
       <c r="B82" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="C82" s="53">
-        <v>10172263</v>
+      <c r="C82" s="53" t="s">
+        <v>1311</v>
       </c>
       <c r="D82" s="53" t="s">
         <v>284</v>
@@ -21672,7 +21875,7 @@
         <v>46171</v>
       </c>
       <c r="I82" s="21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" s="63" t="s">
         <v>242</v>
@@ -21693,9 +21896,11 @@
         <v>1</v>
       </c>
       <c r="P82" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="Q82" s="57">
+        <v>46258</v>
+      </c>
       <c r="R82" s="139">
         <v>46234</v>
       </c>
@@ -21703,7 +21908,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="83" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A83" s="23" t="s">
         <v>244</v>
       </c>
@@ -21760,7 +21965,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A84" s="23" t="s">
         <v>245</v>
       </c>
@@ -21817,7 +22022,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="85" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A85" s="23" t="s">
         <v>246</v>
       </c>
@@ -21874,7 +22079,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="86" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A86" s="23" t="s">
         <v>247</v>
       </c>
@@ -21931,7 +22136,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="87" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A87" s="23" t="s">
         <v>248</v>
       </c>
@@ -21988,7 +22193,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A88" s="23" t="s">
         <v>249</v>
       </c>
@@ -22045,7 +22250,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="89" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A89" s="23" t="s">
         <v>250</v>
       </c>
@@ -22102,7 +22307,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="90" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A90" s="23" t="s">
         <v>228</v>
       </c>
@@ -22159,7 +22364,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="91" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A91" s="23" t="s">
         <v>231</v>
       </c>
@@ -22216,7 +22421,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="92" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A92" s="23" t="s">
         <v>232</v>
       </c>
@@ -22273,7 +22478,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="93" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A93" s="23" t="s">
         <v>197</v>
       </c>
@@ -22330,7 +22535,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="94" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A94" s="23" t="s">
         <v>199</v>
       </c>
@@ -22387,15 +22592,15 @@
         <v>11.769</v>
       </c>
     </row>
-    <row r="95" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:20" ht="21.4" x14ac:dyDescent="0.45">
       <c r="A95" s="23" t="s">
         <v>200</v>
       </c>
       <c r="B95" s="58" t="s">
         <v>174</v>
       </c>
-      <c r="C95" s="53">
-        <v>10172140</v>
+      <c r="C95" s="53" t="s">
+        <v>1297</v>
       </c>
       <c r="D95" s="53" t="s">
         <v>284</v>
@@ -22431,20 +22636,25 @@
         <v>46168</v>
       </c>
       <c r="O95" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P95" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="57"/>
+        <v>1</v>
+      </c>
+      <c r="Q95" s="150">
+        <v>46216</v>
+      </c>
       <c r="R95" s="139">
         <v>46204.240972222222</v>
       </c>
       <c r="S95" s="136">
         <v>8.2000000000000003E-2</v>
       </c>
-    </row>
-    <row r="96" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="T95" s="151" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A96" s="23" t="s">
         <v>201</v>
       </c>
@@ -22501,7 +22711,7 @@
         <v>2.952</v>
       </c>
     </row>
-    <row r="97" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A97" s="23" t="s">
         <v>202</v>
       </c>
@@ -22560,7 +22770,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A98" s="23" t="s">
         <v>171</v>
       </c>
@@ -22617,7 +22827,7 @@
         <v>32.673999999999999</v>
       </c>
     </row>
-    <row r="99" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A99" s="23" t="s">
         <v>173</v>
       </c>
@@ -22674,7 +22884,7 @@
         <v>4.1719999999999997</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A100" s="23" t="s">
         <v>175</v>
       </c>
@@ -22731,7 +22941,7 @@
         <v>4.3360000000000003</v>
       </c>
     </row>
-    <row r="101" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="s">
         <v>176</v>
       </c>
@@ -22788,7 +22998,7 @@
         <v>4.3209</v>
       </c>
     </row>
-    <row r="102" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A102" s="23" t="s">
         <v>177</v>
       </c>
@@ -22845,7 +23055,7 @@
         <v>9.7119999999999997</v>
       </c>
     </row>
-    <row r="103" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A103" s="23" t="s">
         <v>178</v>
       </c>
@@ -22902,7 +23112,7 @@
         <v>4.1757999999999997</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A104" s="23" t="s">
         <v>179</v>
       </c>
@@ -22961,7 +23171,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="s">
         <v>139</v>
       </c>
@@ -23008,7 +23218,7 @@
       <c r="R105" s="136"/>
       <c r="S105" s="136"/>
     </row>
-    <row r="106" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:20" ht="21.4" x14ac:dyDescent="0.45">
       <c r="A106" s="23" t="s">
         <v>180</v>
       </c>
@@ -23016,7 +23226,7 @@
         <v>79</v>
       </c>
       <c r="C106" s="53" t="s">
-        <v>339</v>
+        <v>1298</v>
       </c>
       <c r="D106" s="53" t="s">
         <v>284</v>
@@ -23028,7 +23238,7 @@
         <v>286</v>
       </c>
       <c r="G106" s="3">
-        <v>7.4999999999999997E-2</v>
+        <v>0.104</v>
       </c>
       <c r="H106" s="57">
         <v>46168</v>
@@ -23057,7 +23267,7 @@
       <c r="P106" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="Q106" s="57">
+      <c r="Q106" s="150">
         <v>46206</v>
       </c>
       <c r="R106" s="139">
@@ -23066,8 +23276,11 @@
       <c r="S106" s="138">
         <v>7.4999999999999997E-2</v>
       </c>
-    </row>
-    <row r="107" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+      <c r="T106" s="151" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A107" s="23" t="s">
         <v>141</v>
       </c>
@@ -23114,7 +23327,7 @@
       <c r="R107" s="136"/>
       <c r="S107" s="136"/>
     </row>
-    <row r="108" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A108" s="23" t="s">
         <v>142</v>
       </c>
@@ -23171,7 +23384,7 @@
         <v>20.81</v>
       </c>
     </row>
-    <row r="109" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A109" s="23" t="s">
         <v>144</v>
       </c>
@@ -23218,7 +23431,7 @@
       <c r="R109" s="136"/>
       <c r="S109" s="136"/>
     </row>
-    <row r="110" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A110" s="23" t="s">
         <v>145</v>
       </c>
@@ -23277,7 +23490,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A111" s="23" t="s">
         <v>146</v>
       </c>
@@ -23324,7 +23537,7 @@
       <c r="R111" s="136"/>
       <c r="S111" s="136"/>
     </row>
-    <row r="112" spans="1:19" ht="21.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:20" ht="21.4" x14ac:dyDescent="0.3">
       <c r="A112" s="23" t="s">
         <v>147</v>
       </c>
@@ -24833,7 +25046,9 @@
       <c r="B142" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C142" s="53"/>
+      <c r="C142" s="53" t="s">
+        <v>1302</v>
+      </c>
       <c r="D142" s="53" t="s">
         <v>284</v>
       </c>
@@ -24843,8 +25058,12 @@
       <c r="F142" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G142" s="3"/>
-      <c r="H142" s="3"/>
+      <c r="G142" s="3">
+        <v>0.104</v>
+      </c>
+      <c r="H142" s="57">
+        <v>46258</v>
+      </c>
       <c r="I142" s="21" t="b">
         <v>0</v>
       </c>
@@ -24880,7 +25099,9 @@
       <c r="B143" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C143" s="53"/>
+      <c r="C143" s="53" t="s">
+        <v>1300</v>
+      </c>
       <c r="D143" s="53" t="s">
         <v>284</v>
       </c>
@@ -24890,8 +25111,12 @@
       <c r="F143" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G143" s="3"/>
-      <c r="H143" s="3"/>
+      <c r="G143" s="3">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="H143" s="57">
+        <v>46258</v>
+      </c>
       <c r="I143" s="21" t="b">
         <v>0</v>
       </c>
@@ -24927,7 +25152,9 @@
       <c r="B144" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C144" s="53"/>
+      <c r="C144" s="53" t="s">
+        <v>1303</v>
+      </c>
       <c r="D144" s="53" t="s">
         <v>284</v>
       </c>
@@ -24937,8 +25164,12 @@
       <c r="F144" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G144" s="3"/>
-      <c r="H144" s="3"/>
+      <c r="G144" s="3">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="H144" s="57">
+        <v>46258</v>
+      </c>
       <c r="I144" s="21" t="b">
         <v>0</v>
       </c>
@@ -24974,7 +25205,9 @@
       <c r="B145" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C145" s="53"/>
+      <c r="C145" s="53" t="s">
+        <v>1301</v>
+      </c>
       <c r="D145" s="53" t="s">
         <v>284</v>
       </c>
@@ -24984,8 +25217,12 @@
       <c r="F145" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G145" s="3"/>
-      <c r="H145" s="3"/>
+      <c r="G145" s="3">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="H145" s="57">
+        <v>46258</v>
+      </c>
       <c r="I145" s="21" t="b">
         <v>0</v>
       </c>
@@ -25021,7 +25258,9 @@
       <c r="B146" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C146" s="53"/>
+      <c r="C146" s="53" t="s">
+        <v>1308</v>
+      </c>
       <c r="D146" s="53" t="s">
         <v>284</v>
       </c>
@@ -25031,8 +25270,12 @@
       <c r="F146" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G146" s="3"/>
-      <c r="H146" s="3"/>
+      <c r="G146" s="3">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="H146" s="57">
+        <v>46258</v>
+      </c>
       <c r="I146" s="21" t="b">
         <v>0</v>
       </c>
@@ -25068,7 +25311,9 @@
       <c r="B147" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C147" s="53"/>
+      <c r="C147" s="53" t="s">
+        <v>1304</v>
+      </c>
       <c r="D147" s="53" t="s">
         <v>284</v>
       </c>
@@ -25078,8 +25323,12 @@
       <c r="F147" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G147" s="3"/>
-      <c r="H147" s="3"/>
+      <c r="G147" s="3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="H147" s="57">
+        <v>46258</v>
+      </c>
       <c r="I147" s="21" t="b">
         <v>0</v>
       </c>
@@ -25162,7 +25411,9 @@
       <c r="B149" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C149" s="53"/>
+      <c r="C149" s="53" t="s">
+        <v>1305</v>
+      </c>
       <c r="D149" s="53" t="s">
         <v>284</v>
       </c>
@@ -25172,8 +25423,12 @@
       <c r="F149" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G149" s="3"/>
-      <c r="H149" s="3"/>
+      <c r="G149" s="3">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="H149" s="57">
+        <v>46258</v>
+      </c>
       <c r="I149" s="21" t="b">
         <v>0</v>
       </c>
@@ -25256,7 +25511,9 @@
       <c r="B151" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C151" s="53"/>
+      <c r="C151" s="53" t="s">
+        <v>1306</v>
+      </c>
       <c r="D151" s="53" t="s">
         <v>284</v>
       </c>
@@ -25266,8 +25523,12 @@
       <c r="F151" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G151" s="3"/>
-      <c r="H151" s="3"/>
+      <c r="G151" s="3">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="H151" s="57">
+        <v>46258</v>
+      </c>
       <c r="I151" s="21" t="b">
         <v>0</v>
       </c>
@@ -25350,7 +25611,9 @@
       <c r="B153" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C153" s="53"/>
+      <c r="C153" s="53" t="s">
+        <v>1307</v>
+      </c>
       <c r="D153" s="53" t="s">
         <v>284</v>
       </c>
@@ -25360,8 +25623,12 @@
       <c r="F153" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G153" s="3"/>
-      <c r="H153" s="3"/>
+      <c r="G153" s="3">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="H153" s="57">
+        <v>46258</v>
+      </c>
       <c r="I153" s="21" t="b">
         <v>0</v>
       </c>
@@ -25510,7 +25777,7 @@
         <v>46255</v>
       </c>
       <c r="I156" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J156" s="63" t="s">
         <v>56</v>
@@ -25563,7 +25830,7 @@
         <v>46255</v>
       </c>
       <c r="I157" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J157" s="63" t="s">
         <v>56</v>
@@ -25616,7 +25883,7 @@
         <v>46255</v>
       </c>
       <c r="I158" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J158" s="63" t="s">
         <v>56</v>
@@ -25651,7 +25918,7 @@
         <v>19</v>
       </c>
       <c r="C159" s="53" t="s">
-        <v>1191</v>
+        <v>1292</v>
       </c>
       <c r="D159" s="53" t="s">
         <v>284</v>
@@ -25662,14 +25929,14 @@
       <c r="F159" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G159" s="3" t="s">
-        <v>1191</v>
+      <c r="G159" s="3">
+        <v>0.104</v>
       </c>
       <c r="H159" s="57">
         <v>46255</v>
       </c>
       <c r="I159" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J159" s="63" t="s">
         <v>56</v>
@@ -25704,7 +25971,7 @@
         <v>19</v>
       </c>
       <c r="C160" s="53" t="s">
-        <v>1191</v>
+        <v>1293</v>
       </c>
       <c r="D160" s="53" t="s">
         <v>284</v>
@@ -25715,14 +25982,14 @@
       <c r="F160" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G160" s="3" t="s">
-        <v>1191</v>
+      <c r="G160" s="3">
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="H160" s="57">
         <v>46255</v>
       </c>
       <c r="I160" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160" s="63" t="s">
         <v>56</v>
@@ -25757,7 +26024,7 @@
         <v>19</v>
       </c>
       <c r="C161" s="53" t="s">
-        <v>1191</v>
+        <v>1294</v>
       </c>
       <c r="D161" s="53" t="s">
         <v>284</v>
@@ -25768,14 +26035,14 @@
       <c r="F161" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G161" s="3" t="s">
-        <v>1191</v>
+      <c r="G161" s="3">
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="H161" s="57">
         <v>46255</v>
       </c>
       <c r="I161" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J161" s="63" t="s">
         <v>56</v>
@@ -25809,7 +26076,9 @@
       <c r="B162" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C162" s="53"/>
+      <c r="C162" s="53" t="s">
+        <v>1309</v>
+      </c>
       <c r="D162" s="53" t="s">
         <v>284</v>
       </c>
@@ -25819,10 +26088,14 @@
       <c r="F162" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G162" s="3"/>
-      <c r="H162" s="3"/>
+      <c r="G162" s="3">
+        <v>0.104</v>
+      </c>
+      <c r="H162" s="57">
+        <v>46258</v>
+      </c>
       <c r="I162" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J162" s="63" t="s">
         <v>56</v>
@@ -25856,7 +26129,9 @@
       <c r="B163" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C163" s="53"/>
+      <c r="C163" s="53" t="s">
+        <v>1310</v>
+      </c>
       <c r="D163" s="53" t="s">
         <v>284</v>
       </c>
@@ -25866,10 +26141,14 @@
       <c r="F163" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="G163" s="3"/>
-      <c r="H163" s="3"/>
+      <c r="G163" s="3">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="H163" s="57">
+        <v>46258</v>
+      </c>
       <c r="I163" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" s="63" t="s">
         <v>56</v>
@@ -27135,7 +27414,7 @@
         <v>46186</v>
       </c>
       <c r="I187" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J187" s="63" t="s">
         <v>69</v>
@@ -27190,7 +27469,7 @@
         <v>46186</v>
       </c>
       <c r="I188" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J188" s="63" t="s">
         <v>69</v>
@@ -27491,12 +27770,12 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N193">
     <sortCondition ref="A2:A193"/>
   </sortState>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="C2:C63">
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -33218,7 +33497,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C143:C268">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -37505,22 +37784,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:D125">
-    <cfRule type="duplicateValues" dxfId="5" priority="6" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="6" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C126:D251">
-    <cfRule type="duplicateValues" dxfId="4" priority="5" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="5" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E126:E251">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"Maybe"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37545,34 +37824,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="141" t="s">
         <v>1165</v>
       </c>
-      <c r="B1" s="142" t="s">
+      <c r="B1" s="141" t="s">
         <v>1166</v>
       </c>
-      <c r="C1" s="142" t="s">
+      <c r="C1" s="141" t="s">
         <v>1167</v>
       </c>
-      <c r="D1" s="143" t="s">
+      <c r="D1" s="142" t="s">
         <v>1168</v>
       </c>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143" t="s">
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142" t="s">
         <v>1169</v>
       </c>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
       <c r="J1" s="108"/>
       <c r="K1" s="109" t="s">
         <v>1170</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A2" s="142"/>
-      <c r="B2" s="142"/>
-      <c r="C2" s="142"/>
+      <c r="A2" s="141"/>
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
       <c r="D2" s="107" t="s">
         <v>1171</v>
       </c>
@@ -38686,7 +38965,7 @@
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="G1:I1"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -40065,4 +40344,501 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8F51D9-DC2A-407D-9B2E-297FBBC4C6A6}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.53125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.53125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.9296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.06640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.86328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="F1" s="67" t="s">
+        <v>282</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="H1" s="143" t="s">
+        <v>1295</v>
+      </c>
+      <c r="I1" s="143" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="146">
+        <v>9898003</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D2" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E2" s="57">
+        <v>46168</v>
+      </c>
+      <c r="F2" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="57">
+        <v>46206</v>
+      </c>
+      <c r="H2" s="53" t="s">
+        <v>339</v>
+      </c>
+      <c r="I2" s="145">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="146">
+        <v>9898037</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D3" s="3">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="E3" s="57">
+        <v>46142</v>
+      </c>
+      <c r="F3" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="57">
+        <v>46206</v>
+      </c>
+      <c r="H3" s="53" t="s">
+        <v>341</v>
+      </c>
+      <c r="I3" s="145">
+        <v>6.8000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="146">
+        <v>9898001</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="E4" s="57">
+        <v>46168</v>
+      </c>
+      <c r="F4" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="57">
+        <v>46206</v>
+      </c>
+      <c r="H4" s="53" t="s">
+        <v>349</v>
+      </c>
+      <c r="I4" s="145">
+        <v>9.0999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="147">
+        <v>10172140</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D5" s="3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="E5" s="57">
+        <v>46161</v>
+      </c>
+      <c r="F5" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="57">
+        <v>46210</v>
+      </c>
+      <c r="H5" s="144">
+        <v>10192054</v>
+      </c>
+      <c r="I5" s="145">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="148">
+        <v>10172252</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D6" s="3">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="E6" s="57">
+        <v>46177</v>
+      </c>
+      <c r="F6" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="57">
+        <v>46216</v>
+      </c>
+      <c r="H6" s="53" t="s">
+        <v>326</v>
+      </c>
+      <c r="I6" s="145">
+        <v>9.6000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" s="146">
+        <v>10172132</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D7" s="3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="E7" s="57">
+        <v>46161</v>
+      </c>
+      <c r="F7" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="57">
+        <v>46216</v>
+      </c>
+      <c r="H7" s="53" t="s">
+        <v>334</v>
+      </c>
+      <c r="I7" s="145">
+        <v>8.5999999999999993E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="149">
+        <v>9897912</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D8" s="3">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="E8" s="57">
+        <v>46168</v>
+      </c>
+      <c r="F8" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="57">
+        <v>46216</v>
+      </c>
+      <c r="H8" s="147" t="s">
+        <v>338</v>
+      </c>
+      <c r="I8" s="145">
+        <v>9.7000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="146">
+        <v>9993266</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D9" s="3">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="E9" s="57">
+        <v>46186</v>
+      </c>
+      <c r="F9" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="57">
+        <v>46254</v>
+      </c>
+      <c r="H9" s="53" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I9" s="145">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="B10" s="146">
+        <v>10192015</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.113</v>
+      </c>
+      <c r="E10" s="57">
+        <v>46186</v>
+      </c>
+      <c r="F10" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="57">
+        <v>46254</v>
+      </c>
+      <c r="H10" s="53" t="s">
+        <v>1263</v>
+      </c>
+      <c r="I10" s="145">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" s="146">
+        <v>9897914</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="E11" s="57">
+        <v>46182</v>
+      </c>
+      <c r="F11" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="57">
+        <v>46254</v>
+      </c>
+      <c r="H11" s="53" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I11" s="145">
+        <v>0.10100000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="149">
+        <v>10192013</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.106</v>
+      </c>
+      <c r="E12" s="57">
+        <v>46186</v>
+      </c>
+      <c r="F12" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="57">
+        <v>46254</v>
+      </c>
+      <c r="H12" s="53" t="s">
+        <v>1251</v>
+      </c>
+      <c r="I12" s="145">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="149">
+        <v>10192019</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.104</v>
+      </c>
+      <c r="E13" s="57">
+        <v>46186</v>
+      </c>
+      <c r="F13" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="57">
+        <v>46254</v>
+      </c>
+      <c r="H13" s="53" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I13" s="145">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="B14" s="146">
+        <v>10192054</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D14" s="3">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="E14" s="57">
+        <v>46210</v>
+      </c>
+      <c r="F14" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="57">
+        <v>46258</v>
+      </c>
+      <c r="H14" s="145">
+        <v>10596238</v>
+      </c>
+      <c r="I14" s="145">
+        <v>9.7000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B15" s="147" t="s">
+        <v>339</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D15" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E15" s="57">
+        <v>46206</v>
+      </c>
+      <c r="F15" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="57">
+        <v>46258</v>
+      </c>
+      <c r="H15" s="53" t="s">
+        <v>1298</v>
+      </c>
+      <c r="I15" s="136">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="155" t="s">
+        <v>243</v>
+      </c>
+      <c r="B16" s="156">
+        <v>10172263</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D16" s="157">
+        <v>10.404</v>
+      </c>
+      <c r="E16" s="57">
+        <v>46171</v>
+      </c>
+      <c r="F16" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="57">
+        <v>46258</v>
+      </c>
+      <c r="H16" s="144">
+        <v>10596241</v>
+      </c>
+      <c r="I16" s="154">
+        <v>8.5999999999999993E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I15">
+    <sortCondition ref="G2:G15"/>
+  </sortState>
+  <conditionalFormatting sqref="H2">
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A16">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>